--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-17.xlsx
@@ -860,10 +860,10 @@
         <v>3.7</v>
       </c>
       <c r="G2" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="H2" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="I2" t="n">
         <v>2.16</v>
@@ -872,37 +872,37 @@
         <v>3.6</v>
       </c>
       <c r="K2" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L2" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="O2" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="P2" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="R2" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="S2" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="T2" t="n">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="U2" t="n">
-        <v>1.84</v>
+        <v>2.22</v>
       </c>
       <c r="V2" t="n">
         <v>1.86</v>
@@ -911,112 +911,112 @@
         <v>1.32</v>
       </c>
       <c r="X2" t="n">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AA2" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI2" t="n">
         <v>34</v>
       </c>
-      <c r="AB2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>25</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>40</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>22</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>48</v>
-      </c>
       <c r="AJ2" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AK2" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AL2" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.3</v>
+        <v>7</v>
       </c>
       <c r="AQ2" t="n">
-        <v>2.18</v>
+        <v>9</v>
       </c>
       <c r="AR2" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AS2" t="n">
-        <v>18.5</v>
+        <v>7.8</v>
       </c>
       <c r="AT2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BG2" t="n">
         <v>11</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>20</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>2.56</v>
       </c>
       <c r="BH2" t="n">
         <v>1000</v>
@@ -1058,7 +1058,7 @@
         <v>6.6</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="BV2" t="n">
         <v>20</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-15 00:38:13</t>
+          <t>2026-07-15 02:46:45</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
         <v>1.22</v>
       </c>
       <c r="H3" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="I3" t="n">
         <v>23</v>
@@ -1126,7 +1126,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-15 00:38:13</t>
+          <t>2026-07-15 02:46:45</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-15 00:38:13</t>
+          <t>2026-07-15 02:46:45</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-15 00:38:13</t>
+          <t>2026-07-15 02:46:45</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-15 00:38:13</t>
+          <t>2026-07-15 02:46:45</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-15 00:38:13</t>
+          <t>2026-07-15 02:46:45</t>
         </is>
       </c>
     </row>
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="G8" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="H8" t="n">
         <v>7</v>
@@ -2396,7 +2396,7 @@
         <v>5</v>
       </c>
       <c r="K8" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-15 00:38:13</t>
+          <t>2026-07-15 02:46:45</t>
         </is>
       </c>
     </row>
@@ -2638,46 +2638,46 @@
         <v>2.08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H9" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J9" t="n">
         <v>3.4</v>
       </c>
       <c r="K9" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L9" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="M9" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N9" t="n">
         <v>3.2</v>
       </c>
       <c r="O9" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P9" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="Q9" t="n">
         <v>2.16</v>
       </c>
       <c r="R9" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
       </c>
       <c r="T9" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U9" t="n">
         <v>1.9</v>
@@ -2686,25 +2686,25 @@
         <v>1.29</v>
       </c>
       <c r="W9" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="X9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y9" t="n">
         <v>14.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA9" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB9" t="n">
         <v>8.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD9" t="n">
         <v>18.5</v>
@@ -2722,7 +2722,7 @@
         <v>22</v>
       </c>
       <c r="AI9" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AJ9" t="n">
         <v>26</v>
@@ -2749,13 +2749,13 @@
         <v>11.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS9" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AT9" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU9" t="n">
         <v>6.8</v>
@@ -2764,7 +2764,7 @@
         <v>15</v>
       </c>
       <c r="AW9" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AX9" t="n">
         <v>10</v>
@@ -2776,7 +2776,7 @@
         <v>17</v>
       </c>
       <c r="BA9" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BB9" t="n">
         <v>20</v>
@@ -2785,19 +2785,19 @@
         <v>20</v>
       </c>
       <c r="BD9" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BE9" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF9" t="n">
         <v>15.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BI9" t="n">
         <v>2.6</v>
@@ -2806,59 +2806,59 @@
         <v>11</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BN9" t="n">
         <v>4.8</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BP9" t="n">
         <v>16</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BR9" t="n">
         <v>34</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BT9" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BV9" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX9" t="n">
         <v>55</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BZ9" t="n">
         <v>32</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-15 00:38:13</t>
+          <t>2026-07-15 02:46:45</t>
         </is>
       </c>
     </row>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="G10" t="n">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="H10" t="n">
         <v>4.4</v>
@@ -2901,10 +2901,10 @@
         <v>4.6</v>
       </c>
       <c r="J10" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K10" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-15 00:38:13</t>
+          <t>2026-07-15 02:46:45</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-15 00:38:13</t>
+          <t>2026-07-15 02:46:45</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-15 00:38:13</t>
+          <t>2026-07-15 02:46:45</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-17.xlsx
@@ -866,7 +866,7 @@
         <v>2.04</v>
       </c>
       <c r="I2" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="J2" t="n">
         <v>3.6</v>
@@ -875,7 +875,7 @@
         <v>3.9</v>
       </c>
       <c r="L2" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="M2" t="n">
         <v>1.06</v>
@@ -893,10 +893,10 @@
         <v>1.86</v>
       </c>
       <c r="R2" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S2" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T2" t="n">
         <v>1.73</v>
@@ -905,7 +905,7 @@
         <v>2.22</v>
       </c>
       <c r="V2" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="W2" t="n">
         <v>1.32</v>
@@ -920,7 +920,7 @@
         <v>14</v>
       </c>
       <c r="AA2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AB2" t="n">
         <v>15.5</v>
@@ -962,10 +962,10 @@
         <v>44</v>
       </c>
       <c r="AO2" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AP2" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AQ2" t="n">
         <v>9</v>
@@ -974,10 +974,10 @@
         <v>12</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AU2" t="n">
         <v>7.6</v>
@@ -992,7 +992,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AY2" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AZ2" t="n">
         <v>6.8</v>
@@ -1004,7 +1004,7 @@
         <v>10</v>
       </c>
       <c r="BC2" t="n">
-        <v>9.4</v>
+        <v>38</v>
       </c>
       <c r="BD2" t="n">
         <v>9.4</v>
@@ -1013,22 +1013,22 @@
         <v>10</v>
       </c>
       <c r="BF2" t="n">
-        <v>9.199999999999999</v>
+        <v>32</v>
       </c>
       <c r="BG2" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BH2" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="BJ2" t="n">
-        <v>13</v>
+        <v>9.4</v>
       </c>
       <c r="BK2" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
@@ -1037,50 +1037,50 @@
         <v>21</v>
       </c>
       <c r="BN2" t="n">
-        <v>9.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BP2" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="BT2" t="n">
-        <v>6.6</v>
+        <v>4.9</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="BV2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>11</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY2" t="n">
         <v>20</v>
       </c>
-      <c r="BW2" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>38</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>16.5</v>
-      </c>
       <c r="BZ2" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-15 02:46:45</t>
+          <t>2026-07-15 04:55:19</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="Q3" t="n">
         <v>1.26</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-15 02:46:45</t>
+          <t>2026-07-15 04:55:19</t>
         </is>
       </c>
     </row>
@@ -1377,10 +1377,10 @@
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K4" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-15 02:46:45</t>
+          <t>2026-07-15 04:55:19</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-15 02:46:45</t>
+          <t>2026-07-15 04:55:19</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-15 02:46:45</t>
+          <t>2026-07-15 04:55:19</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-15 02:46:45</t>
+          <t>2026-07-15 04:55:19</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-15 02:46:45</t>
+          <t>2026-07-15 04:55:19</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
         <v>2.08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="H9" t="n">
         <v>4</v>
@@ -2659,7 +2659,7 @@
         <v>1.09</v>
       </c>
       <c r="N9" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O9" t="n">
         <v>1.39</v>
@@ -2668,7 +2668,7 @@
         <v>1.74</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="R9" t="n">
         <v>1.27</v>
@@ -2686,7 +2686,7 @@
         <v>1.29</v>
       </c>
       <c r="W9" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="X9" t="n">
         <v>12</v>
@@ -2701,7 +2701,7 @@
         <v>110</v>
       </c>
       <c r="AB9" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC9" t="n">
         <v>8.199999999999999</v>
@@ -2749,13 +2749,13 @@
         <v>11.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>7.4</v>
+        <v>23</v>
       </c>
       <c r="AS9" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AT9" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU9" t="n">
         <v>6.8</v>
@@ -2764,7 +2764,7 @@
         <v>15</v>
       </c>
       <c r="AW9" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX9" t="n">
         <v>10</v>
@@ -2776,7 +2776,7 @@
         <v>17</v>
       </c>
       <c r="BA9" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB9" t="n">
         <v>20</v>
@@ -2785,16 +2785,16 @@
         <v>20</v>
       </c>
       <c r="BD9" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BE9" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF9" t="n">
         <v>15.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BH9" t="n">
         <v>3.2</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-15 02:46:45</t>
+          <t>2026-07-15 04:55:19</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
         <v>3.55</v>
       </c>
       <c r="K10" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-15 02:46:45</t>
+          <t>2026-07-15 04:55:19</t>
         </is>
       </c>
     </row>
@@ -3158,7 +3158,7 @@
         <v>1.01</v>
       </c>
       <c r="K11" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-15 02:46:45</t>
+          <t>2026-07-15 04:55:19</t>
         </is>
       </c>
     </row>
@@ -3412,7 +3412,7 @@
         <v>1.01</v>
       </c>
       <c r="K12" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-15 02:46:45</t>
+          <t>2026-07-15 04:55:19</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-17.xlsx
@@ -860,10 +860,10 @@
         <v>3.7</v>
       </c>
       <c r="G2" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H2" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="I2" t="n">
         <v>2.18</v>
@@ -872,10 +872,10 @@
         <v>3.6</v>
       </c>
       <c r="K2" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L2" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="M2" t="n">
         <v>1.06</v>
@@ -908,7 +908,7 @@
         <v>1.85</v>
       </c>
       <c r="W2" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X2" t="n">
         <v>18.5</v>
@@ -989,7 +989,7 @@
         <v>7.6</v>
       </c>
       <c r="AX2" t="n">
-        <v>8.199999999999999</v>
+        <v>24</v>
       </c>
       <c r="AY2" t="n">
         <v>14</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-15 04:55:19</t>
+          <t>2026-07-15 07:03:56</t>
         </is>
       </c>
     </row>
@@ -1114,16 +1114,16 @@
         <v>1.18</v>
       </c>
       <c r="G3" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="H3" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="I3" t="n">
         <v>23</v>
       </c>
       <c r="J3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K3" t="n">
         <v>9.800000000000001</v>
@@ -1144,7 +1144,7 @@
         <v>3.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-15 04:55:19</t>
+          <t>2026-07-15 07:03:56</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-15 04:55:19</t>
+          <t>2026-07-15 07:03:56</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-15 04:55:19</t>
+          <t>2026-07-15 07:03:56</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-15 04:55:19</t>
+          <t>2026-07-15 07:03:56</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-15 04:55:19</t>
+          <t>2026-07-15 07:03:56</t>
         </is>
       </c>
     </row>
@@ -2381,22 +2381,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="G8" t="n">
         <v>1.5</v>
       </c>
       <c r="H8" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="I8" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J8" t="n">
         <v>5</v>
       </c>
       <c r="K8" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-15 04:55:19</t>
+          <t>2026-07-15 07:03:56</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
         <v>2.08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="H9" t="n">
         <v>4</v>
@@ -2650,7 +2650,7 @@
         <v>3.4</v>
       </c>
       <c r="K9" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="L9" t="n">
         <v>1.45</v>
@@ -2662,7 +2662,7 @@
         <v>3.25</v>
       </c>
       <c r="O9" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P9" t="n">
         <v>1.74</v>
@@ -2671,7 +2671,7 @@
         <v>2.12</v>
       </c>
       <c r="R9" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -2680,13 +2680,13 @@
         <v>1.9</v>
       </c>
       <c r="U9" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="V9" t="n">
         <v>1.29</v>
       </c>
       <c r="W9" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="X9" t="n">
         <v>12</v>
@@ -2722,7 +2722,7 @@
         <v>22</v>
       </c>
       <c r="AI9" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ9" t="n">
         <v>26</v>
@@ -2737,7 +2737,7 @@
         <v>150</v>
       </c>
       <c r="AN9" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AO9" t="n">
         <v>80</v>
@@ -2752,7 +2752,7 @@
         <v>23</v>
       </c>
       <c r="AS9" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT9" t="n">
         <v>7.2</v>
@@ -2764,7 +2764,7 @@
         <v>15</v>
       </c>
       <c r="AW9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AX9" t="n">
         <v>10</v>
@@ -2776,7 +2776,7 @@
         <v>17</v>
       </c>
       <c r="BA9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB9" t="n">
         <v>20</v>
@@ -2788,13 +2788,13 @@
         <v>7.8</v>
       </c>
       <c r="BE9" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF9" t="n">
         <v>15.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH9" t="n">
         <v>3.2</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-15 04:55:19</t>
+          <t>2026-07-15 07:03:56</t>
         </is>
       </c>
     </row>
@@ -2892,7 +2892,7 @@
         <v>1.95</v>
       </c>
       <c r="G10" t="n">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="H10" t="n">
         <v>4.4</v>
@@ -2901,10 +2901,10 @@
         <v>4.6</v>
       </c>
       <c r="J10" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="K10" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-15 04:55:19</t>
+          <t>2026-07-15 07:03:56</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-15 04:55:19</t>
+          <t>2026-07-15 07:03:56</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-15 04:55:19</t>
+          <t>2026-07-15 07:03:56</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB12"/>
+  <dimension ref="A1:CB20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -866,7 +866,7 @@
         <v>2.06</v>
       </c>
       <c r="I2" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="J2" t="n">
         <v>3.6</v>
@@ -881,13 +881,13 @@
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="O2" t="n">
         <v>1.29</v>
       </c>
       <c r="P2" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q2" t="n">
         <v>1.86</v>
@@ -899,13 +899,13 @@
         <v>3.15</v>
       </c>
       <c r="T2" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U2" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V2" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="W2" t="n">
         <v>1.33</v>
@@ -914,7 +914,7 @@
         <v>18.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="Z2" t="n">
         <v>14</v>
@@ -935,34 +935,34 @@
         <v>22</v>
       </c>
       <c r="AF2" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AG2" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AH2" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AJ2" t="n">
         <v>75</v>
       </c>
       <c r="AK2" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL2" t="n">
         <v>55</v>
       </c>
-      <c r="AL2" t="n">
+      <c r="AM2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN2" t="n">
         <v>50</v>
       </c>
-      <c r="AM2" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>44</v>
-      </c>
       <c r="AO2" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AP2" t="n">
         <v>14</v>
@@ -974,7 +974,7 @@
         <v>12</v>
       </c>
       <c r="AS2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AT2" t="n">
         <v>13.5</v>
@@ -986,43 +986,43 @@
         <v>9.6</v>
       </c>
       <c r="AW2" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="AX2" t="n">
-        <v>24</v>
+        <v>7.4</v>
       </c>
       <c r="AY2" t="n">
         <v>14</v>
       </c>
       <c r="AZ2" t="n">
-        <v>6.8</v>
+        <v>15</v>
       </c>
       <c r="BA2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB2" t="n">
         <v>8.6</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>10</v>
       </c>
       <c r="BC2" t="n">
         <v>38</v>
       </c>
       <c r="BD2" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE2" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF2" t="n">
         <v>32</v>
       </c>
       <c r="BG2" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BH2" t="n">
         <v>3.6</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.98</v>
+        <v>3.25</v>
       </c>
       <c r="BJ2" t="n">
         <v>9.4</v>
@@ -1080,14 +1080,14 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-15 07:03:56</t>
+          <t>2026-07-15 09:14:49</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Norwegian Eliteserien</t>
+          <t>Chinese League 1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,251 +1097,251 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>14:15:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Bodo Glimt</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="R3" t="n">
         <v>1.18</v>
       </c>
-      <c r="G3" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="H3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="I3" t="n">
-        <v>23</v>
-      </c>
-      <c r="J3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="K3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-15 07:03:56</t>
+          <t>2026-07-15 09:14:49</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Chinese League 1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,17 +1351,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Njardvik</t>
+          <t>Shenzhen Juniors FC</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -1377,225 +1377,225 @@
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="K4" t="n">
         <v>1000</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P4" t="n">
         <v>1.24</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-15 07:03:56</t>
+          <t>2026-07-15 09:14:49</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Chinese Super League</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,36 +1605,36 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sao Bernardo</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Avai</t>
+          <t>Chengdu Rongcheng</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1649,10 +1649,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.25</v>
+        <v>2.32</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1842,14 +1842,14 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-15 07:03:56</t>
+          <t>2026-07-15 09:14:49</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Chinese League 1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,251 +1859,251 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>08:30:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Foshan Nanshi FC</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cuiaba</t>
+          <t>Nantong Zhiyun F.C</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P6" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-15 07:03:56</t>
+          <t>2026-07-15 09:14:49</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Chinese League 1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,251 +2113,251 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>08:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>America MG</t>
+          <t>Shijiazhuang Gongfu FC</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ceara SC Fortaleza</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P7" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BI7" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-15 07:03:56</t>
+          <t>2026-07-15 09:14:49</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Chinese Super League</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,251 +2367,251 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>08:35:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Henan Songshan Longmen</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Qingdao Hainiu</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="G8" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="H8" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="I8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="X8" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>27</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>170</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>42</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>60</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>55</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>26</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>60</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>21</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BQ8" t="n">
         <v>7.2</v>
       </c>
-      <c r="I8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="J8" t="n">
-        <v>5</v>
-      </c>
-      <c r="K8" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>0</v>
-      </c>
       <c r="BR8" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BS8" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BT8" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BU8" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BV8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BX8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="CA8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-15 07:03:56</t>
+          <t>2026-07-15 09:14:49</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Chinese Super League</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2621,251 +2621,251 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>08:35:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gremio</t>
+          <t>Liaoning Tieren FC</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.08</v>
+        <v>1.43</v>
       </c>
       <c r="G9" t="n">
-        <v>2.14</v>
+        <v>1.46</v>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>6.6</v>
       </c>
       <c r="I9" t="n">
-        <v>4.6</v>
+        <v>9</v>
       </c>
       <c r="J9" t="n">
-        <v>3.4</v>
+        <v>5.4</v>
       </c>
       <c r="K9" t="n">
-        <v>3.7</v>
+        <v>6</v>
       </c>
       <c r="L9" t="n">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
       <c r="M9" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>3.25</v>
+        <v>2.98</v>
       </c>
       <c r="O9" t="n">
-        <v>1.38</v>
+        <v>1.12</v>
       </c>
       <c r="P9" t="n">
-        <v>1.74</v>
+        <v>2.98</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.12</v>
+        <v>1.41</v>
       </c>
       <c r="R9" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T9" t="n">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="U9" t="n">
-        <v>1.92</v>
+        <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="W9" t="n">
-        <v>1.88</v>
+        <v>3.15</v>
       </c>
       <c r="X9" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="Y9" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="AF9" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>21</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>11</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>25</v>
+      </c>
+      <c r="BS9" t="n">
         <v>11.5</v>
       </c>
-      <c r="AH9" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>19</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>80</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>23</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>9</v>
-      </c>
-      <c r="BF9" t="n">
+      <c r="BT9" t="n">
         <v>15.5</v>
       </c>
-      <c r="BG9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>16</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>34</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BU9" t="n">
-        <v>4.6</v>
+        <v>7.4</v>
       </c>
       <c r="BV9" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>8.800000000000001</v>
+        <v>21</v>
       </c>
       <c r="BX9" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>9.4</v>
+        <v>21</v>
       </c>
       <c r="BZ9" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="CA9" t="n">
-        <v>8.4</v>
+        <v>6.2</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-15 07:03:56</t>
+          <t>2026-07-15 09:14:49</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Chinese Super League</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,234 +2875,234 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Red Bull Bragantino</t>
+          <t>Shanghai Port FC</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="G10" t="n">
-        <v>2.08</v>
+        <v>2.9</v>
       </c>
       <c r="H10" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>29</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>29</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>18</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>30</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>18</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>27</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>7</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>21</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BO10" t="n">
         <v>4.4</v>
       </c>
-      <c r="I10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K10" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>0</v>
-      </c>
       <c r="BP10" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BR10" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BS10" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BT10" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU10" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BV10" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BX10" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BY10" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,14 +3112,14 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-15 07:03:56</t>
+          <t>2026-07-15 09:14:49</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>Norwegian Eliteserien</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3129,36 +3129,36 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>14:15:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Atletico Ottawa</t>
+          <t>Bodo Glimt</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Inter Toronto FC</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.04</v>
+        <v>1.19</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>1.2</v>
       </c>
       <c r="H11" t="n">
-        <v>1.04</v>
+        <v>17.5</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="J11" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -3173,10 +3173,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.24</v>
+        <v>3.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -3366,14 +3366,14 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-15 07:03:56</t>
+          <t>2026-07-15 09:14:49</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3383,17 +3383,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>FC Supra du Quebec</t>
+          <t>Fylkir</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Njardvik</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -3409,7 +3409,7 @@
         <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,2039 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-15 07:03:56</t>
+          <t>2026-07-15 09:14:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Sao Bernardo</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Avai</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>2026-07-15 09:14:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Juventude</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Cuiaba</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>2026-07-15 09:14:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>America MG</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Ceara SC Fortaleza</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>2026-07-15 09:14:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>19:30:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Chapecoense</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="I16" t="n">
+        <v>8</v>
+      </c>
+      <c r="J16" t="n">
+        <v>5</v>
+      </c>
+      <c r="K16" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="inlineStr">
+        <is>
+          <t>2026-07-15 09:14:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Mirassol</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Gremio</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4</v>
+      </c>
+      <c r="I17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S17" t="n">
+        <v>4</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="X17" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>19</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>16</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>34</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>40</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>55</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>32</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="CB17" t="inlineStr">
+        <is>
+          <t>2026-07-15 09:14:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Red Bull Bragantino</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="H18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB18" t="inlineStr">
+        <is>
+          <t>2026-07-15 09:14:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Canadian Premier League</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Atletico Ottawa</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Inter Toronto FC</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB19" t="inlineStr">
+        <is>
+          <t>2026-07-15 09:14:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Canadian Premier League</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>FC Supra du Quebec</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Vancouver FC</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB20" t="inlineStr">
+        <is>
+          <t>2026-07-15 09:14:49</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-17.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="G2" t="n">
         <v>4.1</v>
@@ -866,7 +866,7 @@
         <v>2.06</v>
       </c>
       <c r="I2" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="J2" t="n">
         <v>3.6</v>
@@ -875,7 +875,7 @@
         <v>3.85</v>
       </c>
       <c r="L2" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="M2" t="n">
         <v>1.06</v>
@@ -905,7 +905,7 @@
         <v>2.2</v>
       </c>
       <c r="V2" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="W2" t="n">
         <v>1.33</v>
@@ -959,7 +959,7 @@
         <v>100</v>
       </c>
       <c r="AN2" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AO2" t="n">
         <v>14.5</v>
@@ -974,7 +974,7 @@
         <v>12</v>
       </c>
       <c r="AS2" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AT2" t="n">
         <v>13.5</v>
@@ -986,10 +986,10 @@
         <v>9.6</v>
       </c>
       <c r="AW2" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX2" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AY2" t="n">
         <v>14</v>
@@ -998,22 +998,22 @@
         <v>15</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC2" t="n">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="BD2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF2" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="BG2" t="n">
         <v>11</v>
@@ -1022,7 +1022,7 @@
         <v>3.6</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.25</v>
+        <v>2.98</v>
       </c>
       <c r="BJ2" t="n">
         <v>9.4</v>
@@ -1040,13 +1040,13 @@
         <v>7.2</v>
       </c>
       <c r="BO2" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
@@ -1055,13 +1055,13 @@
         <v>29</v>
       </c>
       <c r="BT2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BU2" t="n">
         <v>3.95</v>
       </c>
       <c r="BV2" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
         <v>11</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-15 09:14:49</t>
+          <t>2026-07-15 11:24:42</t>
         </is>
       </c>
     </row>
@@ -1111,230 +1111,230 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.04</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>1000</v>
+        <v>2.16</v>
       </c>
       <c r="H3" t="n">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="J3" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="K3" t="n">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.24</v>
+        <v>3.9</v>
       </c>
       <c r="O3" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="P3" t="n">
-        <v>1.24</v>
+        <v>1.99</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.33</v>
+        <v>1.81</v>
       </c>
       <c r="R3" t="n">
-        <v>1.18</v>
+        <v>1.39</v>
       </c>
       <c r="S3" t="n">
-        <v>1.33</v>
+        <v>2.88</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="U3" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BH3" t="n">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BN3" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BP3" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BR3" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BT3" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BV3" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-15 09:14:49</t>
+          <t>2026-07-15 11:24:42</t>
         </is>
       </c>
     </row>
@@ -1365,230 +1365,230 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="H4" t="n">
-        <v>1.04</v>
+        <v>1.9</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>1.97</v>
       </c>
       <c r="J4" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="K4" t="n">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>1.24</v>
+        <v>3.5</v>
       </c>
       <c r="O4" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="P4" t="n">
-        <v>1.24</v>
+        <v>1.85</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.37</v>
+        <v>1.98</v>
       </c>
       <c r="R4" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="S4" t="n">
-        <v>1.37</v>
+        <v>3.4</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH4" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BN4" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BP4" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BT4" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BV4" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-15 09:14:49</t>
+          <t>2026-07-15 11:24:42</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-15 09:14:49</t>
+          <t>2026-07-15 11:24:42</t>
         </is>
       </c>
     </row>
@@ -1873,230 +1873,230 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="H6" t="n">
-        <v>1.04</v>
+        <v>1.98</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>2.22</v>
       </c>
       <c r="J6" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="K6" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N6" t="n">
-        <v>1.24</v>
+        <v>2.58</v>
       </c>
       <c r="O6" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="P6" t="n">
-        <v>1.24</v>
+        <v>1.62</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.37</v>
+        <v>2.18</v>
       </c>
       <c r="R6" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="S6" t="n">
-        <v>1.37</v>
+        <v>1.02</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH6" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="BN6" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="BT6" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BV6" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-15 09:14:49</t>
+          <t>2026-07-15 11:24:42</t>
         </is>
       </c>
     </row>
@@ -2127,230 +2127,230 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="G7" t="n">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="I7" t="n">
-        <v>2.78</v>
+        <v>2.48</v>
       </c>
       <c r="J7" t="n">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="K7" t="n">
-        <v>5.6</v>
+        <v>3.4</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N7" t="n">
-        <v>1.58</v>
+        <v>2.5</v>
       </c>
       <c r="O7" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="P7" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.22</v>
+        <v>2.34</v>
       </c>
       <c r="R7" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S7" t="n">
-        <v>2.22</v>
+        <v>3.45</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="V7" t="n">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="W7" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.18</v>
+        <v>2.46</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BN7" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BP7" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BR7" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BT7" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BV7" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BX7" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-15 09:14:49</t>
+          <t>2026-07-15 11:24:42</t>
         </is>
       </c>
     </row>
@@ -2381,22 +2381,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="G8" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="H8" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="I8" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="J8" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K8" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="L8" t="n">
         <v>1.28</v>
@@ -2405,73 +2405,73 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O8" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P8" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="R8" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="S8" t="n">
         <v>2.66</v>
       </c>
       <c r="T8" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="U8" t="n">
-        <v>1.89</v>
+        <v>2.04</v>
       </c>
       <c r="V8" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="W8" t="n">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="X8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y8" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Z8" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AA8" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AB8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC8" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AE8" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AF8" t="n">
         <v>10.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH8" t="n">
         <v>23</v>
       </c>
       <c r="AI8" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AJ8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK8" t="n">
         <v>16</v>
@@ -2483,10 +2483,10 @@
         <v>110</v>
       </c>
       <c r="AN8" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AO8" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AP8" t="n">
         <v>20</v>
@@ -2498,13 +2498,13 @@
         <v>42</v>
       </c>
       <c r="AS8" t="n">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="AT8" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AU8" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AV8" t="n">
         <v>19</v>
@@ -2513,19 +2513,19 @@
         <v>60</v>
       </c>
       <c r="AX8" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AY8" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ8" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA8" t="n">
         <v>55</v>
       </c>
       <c r="BB8" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BC8" t="n">
         <v>13.5</v>
@@ -2534,16 +2534,16 @@
         <v>26</v>
       </c>
       <c r="BE8" t="n">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="BF8" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BG8" t="n">
         <v>60</v>
       </c>
       <c r="BH8" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BI8" t="n">
         <v>3.2</v>
@@ -2552,59 +2552,59 @@
         <v>10.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>7.4</v>
+        <v>5.1</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>21</v>
+        <v>9.4</v>
       </c>
       <c r="BN8" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BP8" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BQ8" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BR8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BS8" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="BT8" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BU8" t="n">
-        <v>7.2</v>
+        <v>5.3</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>34</v>
+        <v>8.6</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>36</v>
+        <v>8.6</v>
       </c>
       <c r="BZ8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CA8" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-15 09:14:49</t>
+          <t>2026-07-15 11:24:42</t>
         </is>
       </c>
     </row>
@@ -2638,10 +2638,10 @@
         <v>1.43</v>
       </c>
       <c r="G9" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="H9" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="I9" t="n">
         <v>9</v>
@@ -2653,34 +2653,34 @@
         <v>6</v>
       </c>
       <c r="L9" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>2.98</v>
+        <v>6.8</v>
       </c>
       <c r="O9" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="P9" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="Q9" t="n">
         <v>1.41</v>
       </c>
       <c r="R9" t="n">
-        <v>1.34</v>
+        <v>1.81</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="T9" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="V9" t="n">
         <v>1.13</v>
@@ -2692,127 +2692,127 @@
         <v>40</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AE9" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI9" t="n">
         <v>75</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.02</v>
+        <v>5.2</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.05</v>
+        <v>5.3</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.05</v>
+        <v>5.6</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.05</v>
+        <v>5.9</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.05</v>
+        <v>11.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.05</v>
+        <v>11.5</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.05</v>
+        <v>5.1</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.05</v>
+        <v>10</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.05</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.05</v>
+        <v>17.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.05</v>
+        <v>11.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.05</v>
+        <v>11.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.05</v>
+        <v>21</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.05</v>
+        <v>5.6</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.05</v>
+        <v>3.55</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.05</v>
+        <v>5.6</v>
       </c>
       <c r="BH9" t="n">
         <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.55</v>
+        <v>2.18</v>
       </c>
       <c r="BJ9" t="n">
         <v>13.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>6.4</v>
+        <v>1.89</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>21</v>
+        <v>2.18</v>
       </c>
       <c r="BN9" t="n">
         <v>5.9</v>
@@ -2830,35 +2830,35 @@
         <v>25</v>
       </c>
       <c r="BS9" t="n">
-        <v>11.5</v>
+        <v>2.02</v>
       </c>
       <c r="BT9" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BU9" t="n">
-        <v>7.4</v>
+        <v>1.93</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>21</v>
+        <v>2.12</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>21</v>
+        <v>2.12</v>
       </c>
       <c r="BZ9" t="n">
         <v>13</v>
       </c>
       <c r="CA9" t="n">
-        <v>6.2</v>
+        <v>1.88</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-15 09:14:49</t>
+          <t>2026-07-15 11:24:42</t>
         </is>
       </c>
     </row>
@@ -2889,172 +2889,172 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G10" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="H10" t="n">
         <v>2.44</v>
       </c>
       <c r="I10" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="J10" t="n">
         <v>4.1</v>
       </c>
       <c r="K10" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>2.96</v>
+        <v>6.8</v>
       </c>
       <c r="O10" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="P10" t="n">
         <v>2.96</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="R10" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="S10" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="T10" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="U10" t="n">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="V10" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="W10" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AP10" t="n">
-        <v>29</v>
+        <v>7.8</v>
       </c>
       <c r="AQ10" t="n">
         <v>17.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AS10" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="AT10" t="n">
         <v>18</v>
       </c>
       <c r="AU10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AV10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>19</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>9</v>
+      </c>
+      <c r="BG10" t="n">
         <v>9.6</v>
       </c>
-      <c r="AW10" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>30</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>18</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>27</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BH10" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.55</v>
+        <v>1.49</v>
       </c>
       <c r="BJ10" t="n">
         <v>11</v>
@@ -3066,7 +3066,7 @@
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>21</v>
+        <v>1.49</v>
       </c>
       <c r="BN10" t="n">
         <v>8.800000000000001</v>
@@ -3078,16 +3078,16 @@
         <v>23</v>
       </c>
       <c r="BQ10" t="n">
-        <v>11</v>
+        <v>1.4</v>
       </c>
       <c r="BR10" t="n">
         <v>30</v>
       </c>
       <c r="BS10" t="n">
-        <v>13.5</v>
+        <v>1.42</v>
       </c>
       <c r="BT10" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BU10" t="n">
         <v>4.3</v>
@@ -3096,13 +3096,13 @@
         <v>22</v>
       </c>
       <c r="BW10" t="n">
-        <v>10</v>
+        <v>1.4</v>
       </c>
       <c r="BX10" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>13.5</v>
+        <v>1.49</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-15 09:14:49</t>
+          <t>2026-07-15 11:24:42</t>
         </is>
       </c>
     </row>
@@ -3152,13 +3152,13 @@
         <v>17.5</v>
       </c>
       <c r="I11" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J11" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-15 09:14:49</t>
+          <t>2026-07-15 11:24:42</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-15 09:14:49</t>
+          <t>2026-07-15 11:24:42</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-15 09:14:49</t>
+          <t>2026-07-15 11:24:42</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-15 09:14:49</t>
+          <t>2026-07-15 11:24:42</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-15 09:14:49</t>
+          <t>2026-07-15 11:24:42</t>
         </is>
       </c>
     </row>
@@ -4416,10 +4416,10 @@
         <v>1.45</v>
       </c>
       <c r="G16" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="H16" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="I16" t="n">
         <v>8</v>
@@ -4428,7 +4428,7 @@
         <v>5</v>
       </c>
       <c r="K16" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-15 09:14:49</t>
+          <t>2026-07-15 11:24:42</t>
         </is>
       </c>
     </row>
@@ -4682,7 +4682,7 @@
         <v>3.4</v>
       </c>
       <c r="K17" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L17" t="n">
         <v>1.45</v>
@@ -4706,7 +4706,7 @@
         <v>1.28</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="T17" t="n">
         <v>1.9</v>
@@ -4718,10 +4718,10 @@
         <v>1.29</v>
       </c>
       <c r="W17" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X17" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y17" t="n">
         <v>14.5</v>
@@ -4766,13 +4766,13 @@
         <v>44</v>
       </c>
       <c r="AM17" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN17" t="n">
         <v>19</v>
       </c>
       <c r="AO17" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AP17" t="n">
         <v>10</v>
@@ -4784,7 +4784,7 @@
         <v>23</v>
       </c>
       <c r="AS17" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AT17" t="n">
         <v>7.2</v>
@@ -4796,7 +4796,7 @@
         <v>15</v>
       </c>
       <c r="AW17" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX17" t="n">
         <v>10</v>
@@ -4820,13 +4820,13 @@
         <v>7.8</v>
       </c>
       <c r="BE17" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF17" t="n">
         <v>15.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BH17" t="n">
         <v>3.2</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-15 09:14:49</t>
+          <t>2026-07-15 11:24:42</t>
         </is>
       </c>
     </row>
@@ -4924,7 +4924,7 @@
         <v>1.95</v>
       </c>
       <c r="G18" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H18" t="n">
         <v>4.4</v>
@@ -4951,7 +4951,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="Q18" t="n">
         <v>2.1</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-15 09:14:49</t>
+          <t>2026-07-15 11:24:42</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-15 09:14:49</t>
+          <t>2026-07-15 11:24:42</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-15 09:14:49</t>
+          <t>2026-07-15 11:24:42</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB20"/>
+  <dimension ref="A1:CB27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,58 +857,58 @@
         </is>
       </c>
       <c r="F2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="J2" t="n">
         <v>3.65</v>
-      </c>
-      <c r="G2" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H2" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3.6</v>
       </c>
       <c r="K2" t="n">
         <v>3.85</v>
       </c>
       <c r="L2" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="M2" t="n">
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="O2" t="n">
         <v>1.29</v>
       </c>
       <c r="P2" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R2" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S2" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="T2" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U2" t="n">
         <v>2.2</v>
       </c>
       <c r="V2" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="W2" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="X2" t="n">
         <v>18.5</v>
@@ -917,67 +917,67 @@
         <v>12</v>
       </c>
       <c r="Z2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AA2" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AB2" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD2" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AF2" t="n">
         <v>34</v>
       </c>
       <c r="AG2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AH2" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AI2" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AJ2" t="n">
         <v>75</v>
       </c>
       <c r="AK2" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AL2" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM2" t="n">
         <v>100</v>
       </c>
       <c r="AN2" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AO2" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AP2" t="n">
         <v>14</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR2" t="n">
         <v>12</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.2</v>
+        <v>4.8</v>
       </c>
       <c r="AT2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AU2" t="n">
         <v>7.6</v>
@@ -986,37 +986,37 @@
         <v>9.6</v>
       </c>
       <c r="AW2" t="n">
-        <v>6.8</v>
+        <v>4.6</v>
       </c>
       <c r="AX2" t="n">
-        <v>7.6</v>
+        <v>21</v>
       </c>
       <c r="AY2" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AZ2" t="n">
         <v>15</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.8</v>
+        <v>5</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.800000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="BC2" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="BD2" t="n">
-        <v>8.4</v>
+        <v>5.1</v>
       </c>
       <c r="BE2" t="n">
-        <v>9</v>
+        <v>5.2</v>
       </c>
       <c r="BF2" t="n">
-        <v>8</v>
+        <v>5.1</v>
       </c>
       <c r="BG2" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BH2" t="n">
         <v>3.6</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-15 11:24:42</t>
+          <t>2026-07-15 13:35:15</t>
         </is>
       </c>
     </row>
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="G3" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="H3" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="I3" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J3" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K3" t="n">
         <v>3.95</v>
@@ -1135,16 +1135,16 @@
         <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="O3" t="n">
         <v>1.29</v>
       </c>
       <c r="P3" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="R3" t="n">
         <v>1.39</v>
@@ -1153,16 +1153,16 @@
         <v>2.88</v>
       </c>
       <c r="T3" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="U3" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V3" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W3" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="X3" t="n">
         <v>18.5</v>
@@ -1171,22 +1171,22 @@
         <v>18.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA3" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AB3" t="n">
         <v>12</v>
       </c>
       <c r="AC3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD3" t="n">
         <v>20</v>
       </c>
       <c r="AE3" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF3" t="n">
         <v>16.5</v>
@@ -1198,7 +1198,7 @@
         <v>22</v>
       </c>
       <c r="AI3" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ3" t="n">
         <v>32</v>
@@ -1207,7 +1207,7 @@
         <v>27</v>
       </c>
       <c r="AL3" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AM3" t="n">
         <v>110</v>
@@ -1216,61 +1216,61 @@
         <v>18</v>
       </c>
       <c r="AO3" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="AR3" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BC3" t="n">
         <v>3.8</v>
       </c>
-      <c r="AS3" t="n">
+      <c r="BD3" t="n">
         <v>4</v>
       </c>
-      <c r="AT3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AZ3" t="n">
+      <c r="BE3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF3" t="n">
         <v>3.55</v>
       </c>
-      <c r="BA3" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>4</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>3.4</v>
-      </c>
       <c r="BG3" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BH3" t="n">
         <v>3.55</v>
@@ -1279,34 +1279,34 @@
         <v>3.15</v>
       </c>
       <c r="BJ3" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BK3" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>14</v>
+        <v>3.65</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BO3" t="n">
         <v>3.75</v>
       </c>
       <c r="BP3" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BR3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BS3" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BT3" t="n">
         <v>7.4</v>
@@ -1315,26 +1315,26 @@
         <v>5.4</v>
       </c>
       <c r="BV3" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BW3" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BZ3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="CA3" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-15 11:24:42</t>
+          <t>2026-07-15 13:35:15</t>
         </is>
       </c>
     </row>
@@ -1365,16 +1365,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="G4" t="n">
         <v>4.8</v>
       </c>
       <c r="H4" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="I4" t="n">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="J4" t="n">
         <v>3.55</v>
@@ -1413,7 +1413,7 @@
         <v>2.02</v>
       </c>
       <c r="V4" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="W4" t="n">
         <v>1.26</v>
@@ -1422,7 +1422,7 @@
         <v>16</v>
       </c>
       <c r="Y4" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="Z4" t="n">
         <v>13</v>
@@ -1473,58 +1473,58 @@
         <v>15.5</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AQ4" t="n">
         <v>3.6</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AT4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY4" t="n">
         <v>4.5</v>
       </c>
-      <c r="AU4" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>4.7</v>
-      </c>
       <c r="AZ4" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BA4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC4" t="n">
         <v>5.3</v>
       </c>
-      <c r="BB4" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BC4" t="n">
+      <c r="BD4" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE4" t="n">
         <v>5.5</v>
       </c>
-      <c r="BD4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BF4" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BH4" t="n">
         <v>3.4</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-15 11:24:42</t>
+          <t>2026-07-15 13:35:15</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-15 11:24:42</t>
+          <t>2026-07-15 13:35:15</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="G6" t="n">
         <v>5.5</v>
@@ -1906,22 +1906,22 @@
         <v>1.62</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="R6" t="n">
         <v>1.23</v>
       </c>
       <c r="S6" t="n">
-        <v>1.02</v>
+        <v>3.9</v>
       </c>
       <c r="T6" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="U6" t="n">
         <v>1.83</v>
       </c>
       <c r="V6" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="W6" t="n">
         <v>1.22</v>
@@ -1942,7 +1942,7 @@
         <v>15.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD6" t="n">
         <v>13.5</v>
@@ -1981,64 +1981,64 @@
         <v>27</v>
       </c>
       <c r="AP6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AT6" t="n">
         <v>3.4</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>3.6</v>
       </c>
       <c r="AU6" t="n">
         <v>2.96</v>
       </c>
       <c r="AV6" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="AW6" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC6" t="n">
         <v>4.1</v>
       </c>
-      <c r="AX6" t="n">
+      <c r="BD6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE6" t="n">
         <v>4.2</v>
       </c>
-      <c r="AY6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BF6" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="BH6" t="n">
         <v>3.05</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="BJ6" t="n">
         <v>11.5</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-15 11:24:42</t>
+          <t>2026-07-15 13:35:15</t>
         </is>
       </c>
     </row>
@@ -2136,10 +2136,10 @@
         <v>2.18</v>
       </c>
       <c r="I7" t="n">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="J7" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="K7" t="n">
         <v>3.4</v>
@@ -2160,7 +2160,7 @@
         <v>1.53</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="R7" t="n">
         <v>1.19</v>
@@ -2169,13 +2169,13 @@
         <v>3.45</v>
       </c>
       <c r="T7" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U7" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="V7" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="W7" t="n">
         <v>1.3</v>
@@ -2304,7 +2304,7 @@
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>7.2</v>
+        <v>2.22</v>
       </c>
       <c r="BN7" t="n">
         <v>7.2</v>
@@ -2316,13 +2316,13 @@
         <v>40</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6.2</v>
+        <v>2.12</v>
       </c>
       <c r="BR7" t="n">
         <v>65</v>
       </c>
       <c r="BS7" t="n">
-        <v>6.6</v>
+        <v>2.16</v>
       </c>
       <c r="BT7" t="n">
         <v>5.1</v>
@@ -2334,23 +2334,23 @@
         <v>21</v>
       </c>
       <c r="BW7" t="n">
-        <v>5.5</v>
+        <v>2.02</v>
       </c>
       <c r="BX7" t="n">
         <v>44</v>
       </c>
       <c r="BY7" t="n">
-        <v>6.4</v>
+        <v>2.14</v>
       </c>
       <c r="BZ7" t="n">
         <v>48</v>
       </c>
       <c r="CA7" t="n">
-        <v>6.4</v>
+        <v>2.14</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-15 11:24:42</t>
+          <t>2026-07-15 13:35:15</t>
         </is>
       </c>
     </row>
@@ -2381,82 +2381,82 @@
         </is>
       </c>
       <c r="F8" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="G8" t="n">
         <v>1.52</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1.55</v>
       </c>
       <c r="H8" t="n">
         <v>6.2</v>
       </c>
       <c r="I8" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="J8" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K8" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="L8" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="M8" t="n">
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="O8" t="n">
         <v>1.22</v>
       </c>
       <c r="P8" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="R8" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="S8" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="T8" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="U8" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="V8" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W8" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="X8" t="n">
         <v>22</v>
       </c>
       <c r="Y8" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AA8" t="n">
-        <v>180</v>
+        <v>260</v>
       </c>
       <c r="AB8" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC8" t="n">
         <v>11.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AE8" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AF8" t="n">
         <v>10.5</v>
@@ -2468,13 +2468,13 @@
         <v>23</v>
       </c>
       <c r="AI8" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AJ8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK8" t="n">
         <v>15</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>16</v>
       </c>
       <c r="AL8" t="n">
         <v>32</v>
@@ -2483,10 +2483,10 @@
         <v>110</v>
       </c>
       <c r="AN8" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AO8" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AP8" t="n">
         <v>20</v>
@@ -2498,7 +2498,7 @@
         <v>42</v>
       </c>
       <c r="AS8" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AT8" t="n">
         <v>8.800000000000001</v>
@@ -2513,13 +2513,13 @@
         <v>60</v>
       </c>
       <c r="AX8" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY8" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ8" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BA8" t="n">
         <v>55</v>
@@ -2528,49 +2528,49 @@
         <v>12.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BD8" t="n">
         <v>26</v>
       </c>
       <c r="BE8" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BF8" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="BG8" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BH8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BN8" t="n">
         <v>4.3</v>
       </c>
-      <c r="BI8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
+      <c r="BO8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BP8" t="n">
         <v>9.4</v>
       </c>
-      <c r="BN8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BQ8" t="n">
-        <v>7</v>
+        <v>4.8</v>
       </c>
       <c r="BR8" t="n">
         <v>23</v>
@@ -2579,7 +2579,7 @@
         <v>7</v>
       </c>
       <c r="BT8" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BU8" t="n">
         <v>5.3</v>
@@ -2597,14 +2597,14 @@
         <v>8.6</v>
       </c>
       <c r="BZ8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="CA8" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-15 11:24:42</t>
+          <t>2026-07-15 13:35:15</t>
         </is>
       </c>
     </row>
@@ -2635,10 +2635,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="G9" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="H9" t="n">
         <v>7.6</v>
@@ -2665,19 +2665,19 @@
         <v>1.14</v>
       </c>
       <c r="P9" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="R9" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="S9" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="T9" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="U9" t="n">
         <v>2.26</v>
@@ -2704,13 +2704,13 @@
         <v>16</v>
       </c>
       <c r="AC9" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AD9" t="n">
         <v>36</v>
       </c>
       <c r="AE9" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AF9" t="n">
         <v>13.5</v>
@@ -2728,7 +2728,7 @@
         <v>15.5</v>
       </c>
       <c r="AK9" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AL9" t="n">
         <v>30</v>
@@ -2737,34 +2737,34 @@
         <v>90</v>
       </c>
       <c r="AN9" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AO9" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AP9" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AQ9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV9" t="n">
         <v>5.3</v>
       </c>
-      <c r="AR9" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AS9" t="n">
+      <c r="AW9" t="n">
         <v>5.9</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>5.6</v>
       </c>
       <c r="AX9" t="n">
         <v>10</v>
@@ -2776,25 +2776,25 @@
         <v>17.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BB9" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BC9" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BF9" t="n">
         <v>3.55</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BH9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-15 11:24:42</t>
+          <t>2026-07-15 13:35:15</t>
         </is>
       </c>
     </row>
@@ -2892,16 +2892,16 @@
         <v>2.52</v>
       </c>
       <c r="G10" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="H10" t="n">
         <v>2.44</v>
       </c>
       <c r="I10" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="J10" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
         <v>4.4</v>
@@ -2913,13 +2913,13 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="O10" t="n">
         <v>1.14</v>
       </c>
       <c r="P10" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="Q10" t="n">
         <v>1.42</v>
@@ -2937,10 +2937,10 @@
         <v>2.9</v>
       </c>
       <c r="V10" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W10" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="X10" t="n">
         <v>36</v>
@@ -2985,7 +2985,7 @@
         <v>25</v>
       </c>
       <c r="AL10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AM10" t="n">
         <v>46</v>
@@ -2994,31 +2994,31 @@
         <v>12</v>
       </c>
       <c r="AO10" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AP10" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ10" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AR10" t="n">
         <v>20</v>
       </c>
       <c r="AS10" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AT10" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AU10" t="n">
         <v>9.6</v>
       </c>
       <c r="AV10" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AW10" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AX10" t="n">
         <v>21</v>
@@ -3033,7 +3033,7 @@
         <v>18.5</v>
       </c>
       <c r="BB10" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BC10" t="n">
         <v>20</v>
@@ -3042,7 +3042,7 @@
         <v>19</v>
       </c>
       <c r="BE10" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BF10" t="n">
         <v>9</v>
@@ -3054,7 +3054,7 @@
         <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.49</v>
+        <v>2.18</v>
       </c>
       <c r="BJ10" t="n">
         <v>11</v>
@@ -3066,7 +3066,7 @@
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.49</v>
+        <v>2.14</v>
       </c>
       <c r="BN10" t="n">
         <v>8.800000000000001</v>
@@ -3078,16 +3078,16 @@
         <v>23</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="BR10" t="n">
         <v>30</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.42</v>
+        <v>2.04</v>
       </c>
       <c r="BT10" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BU10" t="n">
         <v>4.3</v>
@@ -3096,13 +3096,13 @@
         <v>22</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="BX10" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.49</v>
+        <v>2.04</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,14 +3112,14 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-15 11:24:42</t>
+          <t>2026-07-15 13:35:15</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Norwegian Eliteserien</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3129,251 +3129,251 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>14:15:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Bodo Glimt</t>
+          <t>FC Voluntari</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Botosani</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.19</v>
+        <v>2.44</v>
       </c>
       <c r="G11" t="n">
-        <v>1.2</v>
+        <v>2.68</v>
       </c>
       <c r="H11" t="n">
-        <v>17.5</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>18</v>
+        <v>3.35</v>
       </c>
       <c r="J11" t="n">
-        <v>9.199999999999999</v>
+        <v>3.25</v>
       </c>
       <c r="K11" t="n">
-        <v>9.6</v>
+        <v>3.7</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="P11" t="n">
-        <v>3.75</v>
+        <v>1.66</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.31</v>
+        <v>2.2</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BG11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BH11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BK11" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BL11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN11" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BO11" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="BP11" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BR11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BT11" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BU11" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BV11" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BW11" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BX11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-15 11:24:42</t>
+          <t>2026-07-15 13:35:15</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3383,251 +3383,251 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Njardvik</t>
+          <t>Nomme Utd</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="G12" t="n">
-        <v>1000</v>
+        <v>1.38</v>
       </c>
       <c r="H12" t="n">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="J12" t="n">
-        <v>1.02</v>
+        <v>5.3</v>
       </c>
       <c r="K12" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="P12" t="n">
-        <v>1.24</v>
+        <v>3.25</v>
       </c>
       <c r="Q12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="X12" t="n">
+        <v>55</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>120</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>290</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>42</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>30</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>90</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI12" t="n">
         <v>1.01</v>
       </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>0</v>
-      </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-15 11:24:42</t>
+          <t>2026-07-15 13:35:15</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Slovenian Premier League</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3637,234 +3637,234 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Sao Bernardo</t>
+          <t>Nafta Lendava</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Avai</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="P13" t="n">
-        <v>1.25</v>
+        <v>2.16</v>
       </c>
       <c r="Q13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T13" t="n">
         <v>1.01</v>
       </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ13" t="n">
         <v>0</v>
@@ -3874,14 +3874,14 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-15 11:24:42</t>
+          <t>2026-07-15 13:35:15</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3891,251 +3891,251 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cuiaba</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="P14" t="n">
-        <v>1.25</v>
+        <v>1.85</v>
       </c>
       <c r="Q14" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="V14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>21</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>65</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>29</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>220</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>120</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>120</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>160</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI14" t="n">
         <v>1.01</v>
       </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>0</v>
-      </c>
       <c r="BJ14" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BL14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN14" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BO14" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BP14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BR14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BT14" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BU14" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="BV14" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BW14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BX14" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BY14" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="CA14" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-15 11:24:42</t>
+          <t>2026-07-15 13:35:15</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Norwegian Eliteserien</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4145,36 +4145,36 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>14:15:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>America MG</t>
+          <t>Bodo Glimt</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ceara SC Fortaleza</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -4189,10 +4189,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.25</v>
+        <v>3.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -4382,14 +4382,14 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-15 11:24:42</t>
+          <t>2026-07-15 13:35:15</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4399,36 +4399,36 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>15:15:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>PFC Levski Sofia</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Dunav Ruse</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.45</v>
+        <v>1.16</v>
       </c>
       <c r="G16" t="n">
-        <v>1.49</v>
+        <v>1.17</v>
       </c>
       <c r="H16" t="n">
-        <v>7.4</v>
+        <v>22</v>
       </c>
       <c r="I16" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="J16" t="n">
-        <v>5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>5.4</v>
+        <v>10</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -4443,10 +4443,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -4636,14 +4636,14 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-15 11:24:42</t>
+          <t>2026-07-15 13:35:15</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Slovenian Premier League</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4653,251 +4653,251 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>15:15:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>NK Celje</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Gremio</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.75</v>
+        <v>1.24</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="R17" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BH17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="BJ17" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BK17" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BL17" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM17" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BN17" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BO17" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="BP17" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BQ17" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BR17" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BS17" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BT17" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BU17" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BV17" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BW17" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BY17" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BZ17" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="CA17" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-15 11:24:42</t>
+          <t>2026-07-15 13:35:15</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4907,36 +4907,36 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Red Bull Bragantino</t>
+          <t>Arges Pitesti</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="G18" t="n">
-        <v>2.06</v>
+        <v>1.71</v>
       </c>
       <c r="H18" t="n">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="I18" t="n">
-        <v>4.6</v>
+        <v>6.8</v>
       </c>
       <c r="J18" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="K18" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -4951,10 +4951,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -5144,14 +5144,14 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-15 11:24:42</t>
+          <t>2026-07-15 13:35:15</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5161,17 +5161,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Atletico Ottawa</t>
+          <t>Fylkir</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Inter Toronto FC</t>
+          <t>Njardvik</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -5187,7 +5187,7 @@
         <v>1000</v>
       </c>
       <c r="J19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K19" t="n">
         <v>1000</v>
@@ -5398,14 +5398,14 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-15 11:24:42</t>
+          <t>2026-07-15 13:35:15</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5415,36 +5415,36 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>FC Supra du Quebec</t>
+          <t>Sao Bernardo</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Avai</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -5459,7 +5459,7 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q20" t="n">
         <v>1.01</v>
@@ -5652,7 +5652,1785 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-15 11:24:42</t>
+          <t>2026-07-15 13:35:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Juventude</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Cuiaba</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB21" t="inlineStr">
+        <is>
+          <t>2026-07-15 13:35:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>America MG</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Ceara SC Fortaleza</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB22" t="inlineStr">
+        <is>
+          <t>2026-07-15 13:35:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>19:30:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Chapecoense</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="H23" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="I23" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="J23" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB23" t="inlineStr">
+        <is>
+          <t>2026-07-15 13:35:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Canadian Premier League</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Atletico Ottawa</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Inter Toronto FC</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB24" t="inlineStr">
+        <is>
+          <t>2026-07-15 13:35:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Mirassol</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Gremio</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="H25" t="n">
+        <v>4</v>
+      </c>
+      <c r="I25" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="X25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>19</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>16</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>34</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>8</v>
+      </c>
+      <c r="BT25" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BU25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BV25" t="n">
+        <v>42</v>
+      </c>
+      <c r="BW25" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BX25" t="n">
+        <v>55</v>
+      </c>
+      <c r="BY25" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BZ25" t="n">
+        <v>32</v>
+      </c>
+      <c r="CA25" t="n">
+        <v>8</v>
+      </c>
+      <c r="CB25" t="inlineStr">
+        <is>
+          <t>2026-07-15 13:35:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Red Bull Bragantino</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="H26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I26" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB26" t="inlineStr">
+        <is>
+          <t>2026-07-15 13:35:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Canadian Premier League</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>FC Supra du Quebec</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Vancouver FC</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB27" t="inlineStr">
+        <is>
+          <t>2026-07-15 13:35:15</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB27"/>
+  <dimension ref="A1:CB33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -875,7 +875,7 @@
         <v>3.85</v>
       </c>
       <c r="L2" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M2" t="n">
         <v>1.06</v>
@@ -884,25 +884,25 @@
         <v>4.1</v>
       </c>
       <c r="O2" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P2" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="R2" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S2" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="T2" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="U2" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="V2" t="n">
         <v>1.86</v>
@@ -956,19 +956,19 @@
         <v>60</v>
       </c>
       <c r="AM2" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AN2" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AO2" t="n">
         <v>16.5</v>
       </c>
       <c r="AP2" t="n">
-        <v>14</v>
+        <v>4.4</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AR2" t="n">
         <v>12</v>
@@ -977,7 +977,7 @@
         <v>4.8</v>
       </c>
       <c r="AT2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AU2" t="n">
         <v>7.6</v>
@@ -986,7 +986,7 @@
         <v>9.6</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AX2" t="n">
         <v>21</v>
@@ -1001,10 +1001,10 @@
         <v>5</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BC2" t="n">
-        <v>36</v>
+        <v>5.1</v>
       </c>
       <c r="BD2" t="n">
         <v>5.1</v>
@@ -1013,19 +1013,19 @@
         <v>5.2</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BG2" t="n">
         <v>12.5</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.98</v>
+        <v>3.35</v>
       </c>
       <c r="BJ2" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK2" t="n">
         <v>7.2</v>
@@ -1052,13 +1052,13 @@
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BT2" t="n">
         <v>5</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
@@ -1076,11 +1076,11 @@
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:35:15</t>
+          <t>2026-07-15 15:46:37</t>
         </is>
       </c>
     </row>
@@ -1117,16 +1117,16 @@
         <v>2.26</v>
       </c>
       <c r="H3" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="I3" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="J3" t="n">
         <v>3.5</v>
       </c>
       <c r="K3" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L3" t="n">
         <v>1.39</v>
@@ -1144,7 +1144,7 @@
         <v>1.98</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="R3" t="n">
         <v>1.39</v>
@@ -1159,7 +1159,7 @@
         <v>2.18</v>
       </c>
       <c r="V3" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W3" t="n">
         <v>1.79</v>
@@ -1180,7 +1180,7 @@
         <v>12</v>
       </c>
       <c r="AC3" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="AD3" t="n">
         <v>20</v>
@@ -1207,7 +1207,7 @@
         <v>27</v>
       </c>
       <c r="AL3" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM3" t="n">
         <v>110</v>
@@ -1219,58 +1219,58 @@
         <v>48</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="AR3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AV3" t="n">
         <v>3.95</v>
       </c>
-      <c r="AS3" t="n">
+      <c r="AW3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB3" t="n">
         <v>4.2</v>
       </c>
-      <c r="AT3" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AW3" t="n">
+      <c r="BC3" t="n">
         <v>4.1</v>
       </c>
-      <c r="AX3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>3.8</v>
-      </c>
       <c r="BD3" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BH3" t="n">
         <v>3.55</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-15 13:35:15</t>
+          <t>2026-07-15 15:46:37</t>
         </is>
       </c>
     </row>
@@ -1368,10 +1368,10 @@
         <v>4.3</v>
       </c>
       <c r="G4" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="H4" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="I4" t="n">
         <v>2.04</v>
@@ -1380,7 +1380,7 @@
         <v>3.55</v>
       </c>
       <c r="K4" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L4" t="n">
         <v>1.42</v>
@@ -1410,13 +1410,13 @@
         <v>1.83</v>
       </c>
       <c r="U4" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V4" t="n">
         <v>1.98</v>
       </c>
       <c r="W4" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X4" t="n">
         <v>16</v>
@@ -1434,7 +1434,7 @@
         <v>18</v>
       </c>
       <c r="AC4" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD4" t="n">
         <v>12</v>
@@ -1443,7 +1443,7 @@
         <v>24</v>
       </c>
       <c r="AF4" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AG4" t="n">
         <v>22</v>
@@ -1455,10 +1455,10 @@
         <v>44</v>
       </c>
       <c r="AJ4" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AK4" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AL4" t="n">
         <v>75</v>
@@ -1467,70 +1467,70 @@
         <v>130</v>
       </c>
       <c r="AN4" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AO4" t="n">
         <v>15.5</v>
       </c>
       <c r="AP4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AV4" t="n">
         <v>4.2</v>
       </c>
-      <c r="AQ4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AS4" t="n">
+      <c r="AW4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG4" t="n">
         <v>4.6</v>
       </c>
-      <c r="AT4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BH4" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BJ4" t="n">
         <v>10</v>
@@ -1542,7 +1542,7 @@
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BN4" t="n">
         <v>7.8</v>
@@ -1551,10 +1551,10 @@
         <v>6</v>
       </c>
       <c r="BP4" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BQ4" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
@@ -1563,19 +1563,19 @@
         <v>11.5</v>
       </c>
       <c r="BT4" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BU4" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BV4" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BW4" t="n">
         <v>7.4</v>
       </c>
       <c r="BX4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BY4" t="n">
         <v>10</v>
@@ -1584,11 +1584,11 @@
         <v>26</v>
       </c>
       <c r="CA4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-15 13:35:15</t>
+          <t>2026-07-15 15:46:37</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
         <v>5.5</v>
       </c>
       <c r="H5" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="I5" t="n">
         <v>1.92</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-15 13:35:15</t>
+          <t>2026-07-15 15:46:37</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
         <v>3.65</v>
       </c>
       <c r="G6" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="H6" t="n">
         <v>1.98</v>
@@ -1897,7 +1897,7 @@
         <v>1.1</v>
       </c>
       <c r="N6" t="n">
-        <v>2.58</v>
+        <v>2.72</v>
       </c>
       <c r="O6" t="n">
         <v>1.43</v>
@@ -1912,10 +1912,10 @@
         <v>1.23</v>
       </c>
       <c r="S6" t="n">
-        <v>3.9</v>
+        <v>1.02</v>
       </c>
       <c r="T6" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="U6" t="n">
         <v>1.83</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-15 13:35:15</t>
+          <t>2026-07-15 15:46:37</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2160,7 @@
         <v>1.53</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.36</v>
+        <v>2.48</v>
       </c>
       <c r="R7" t="n">
         <v>1.19</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-15 13:35:15</t>
+          <t>2026-07-15 15:46:37</t>
         </is>
       </c>
     </row>
@@ -2381,70 +2381,70 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="G8" t="n">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="H8" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="I8" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="J8" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="K8" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="O8" t="n">
         <v>1.22</v>
       </c>
       <c r="P8" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="R8" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="S8" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T8" t="n">
-        <v>1.84</v>
+        <v>1.74</v>
       </c>
       <c r="U8" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="V8" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="W8" t="n">
-        <v>2.88</v>
+        <v>2.58</v>
       </c>
       <c r="X8" t="n">
         <v>22</v>
       </c>
       <c r="Y8" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="Z8" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AA8" t="n">
-        <v>260</v>
+        <v>210</v>
       </c>
       <c r="AB8" t="n">
         <v>10.5</v>
@@ -2453,76 +2453,76 @@
         <v>11.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AE8" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AF8" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH8" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI8" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AJ8" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AK8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL8" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM8" t="n">
         <v>110</v>
       </c>
       <c r="AN8" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="AO8" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AP8" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AQ8" t="n">
         <v>21</v>
       </c>
       <c r="AR8" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AS8" t="n">
-        <v>12.5</v>
+        <v>9.4</v>
       </c>
       <c r="AT8" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU8" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AV8" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AX8" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AY8" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ8" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="BA8" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BB8" t="n">
         <v>12.5</v>
@@ -2531,80 +2531,80 @@
         <v>13</v>
       </c>
       <c r="BD8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BE8" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="BF8" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BG8" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="BH8" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="BJ8" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BN8" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="BP8" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BQ8" t="n">
         <v>4.8</v>
       </c>
       <c r="BR8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BS8" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BT8" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="BZ8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="CA8" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-15 13:35:15</t>
+          <t>2026-07-15 15:46:37</t>
         </is>
       </c>
     </row>
@@ -2650,7 +2650,7 @@
         <v>5.4</v>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2740,7 +2740,7 @@
         <v>5</v>
       </c>
       <c r="AO9" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AP9" t="n">
         <v>5.4</v>
@@ -2749,7 +2749,7 @@
         <v>5.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AS9" t="n">
         <v>6</v>
@@ -2788,7 +2788,7 @@
         <v>19.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BF9" t="n">
         <v>3.55</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-15 13:35:15</t>
+          <t>2026-07-15 15:46:37</t>
         </is>
       </c>
     </row>
@@ -2889,16 +2889,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="G10" t="n">
-        <v>2.84</v>
+        <v>2.72</v>
       </c>
       <c r="H10" t="n">
-        <v>2.44</v>
+        <v>2.54</v>
       </c>
       <c r="I10" t="n">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="J10" t="n">
         <v>4</v>
@@ -2907,7 +2907,7 @@
         <v>4.4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="M10" t="n">
         <v>1.01</v>
@@ -2916,16 +2916,16 @@
         <v>6.6</v>
       </c>
       <c r="O10" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P10" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="Q10" t="n">
         <v>1.42</v>
       </c>
       <c r="R10" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="S10" t="n">
         <v>2.04</v>
@@ -2937,37 +2937,37 @@
         <v>2.9</v>
       </c>
       <c r="V10" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="W10" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="X10" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Y10" t="n">
         <v>24</v>
       </c>
       <c r="Z10" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AA10" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AB10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AC10" t="n">
         <v>11.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE10" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AF10" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AG10" t="n">
         <v>14</v>
@@ -2976,40 +2976,40 @@
         <v>14.5</v>
       </c>
       <c r="AI10" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK10" t="n">
         <v>27</v>
       </c>
-      <c r="AJ10" t="n">
-        <v>46</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>25</v>
-      </c>
       <c r="AL10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM10" t="n">
         <v>46</v>
       </c>
       <c r="AN10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO10" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AP10" t="n">
-        <v>7.6</v>
+        <v>5.6</v>
       </c>
       <c r="AQ10" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AR10" t="n">
         <v>20</v>
       </c>
       <c r="AS10" t="n">
-        <v>7.6</v>
+        <v>5.9</v>
       </c>
       <c r="AT10" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AU10" t="n">
         <v>9.6</v>
@@ -3018,10 +3018,10 @@
         <v>10</v>
       </c>
       <c r="AW10" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX10" t="n">
         <v>17.5</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>21</v>
       </c>
       <c r="AY10" t="n">
         <v>11.5</v>
@@ -3033,28 +3033,28 @@
         <v>18.5</v>
       </c>
       <c r="BB10" t="n">
-        <v>8</v>
+        <v>5.8</v>
       </c>
       <c r="BC10" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BD10" t="n">
         <v>19</v>
       </c>
       <c r="BE10" t="n">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
       <c r="BF10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BG10" t="n">
         <v>9</v>
       </c>
-      <c r="BG10" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BH10" t="n">
         <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="BJ10" t="n">
         <v>11</v>
@@ -3066,43 +3066,43 @@
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="BN10" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BO10" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BP10" t="n">
         <v>23</v>
       </c>
       <c r="BQ10" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="BR10" t="n">
         <v>30</v>
       </c>
       <c r="BS10" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="BT10" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU10" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BV10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BW10" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="BX10" t="n">
         <v>30</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-15 13:35:15</t>
+          <t>2026-07-15 15:46:37</t>
         </is>
       </c>
     </row>
@@ -3167,28 +3167,28 @@
         <v>1.09</v>
       </c>
       <c r="N11" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="O11" t="n">
         <v>1.42</v>
       </c>
       <c r="P11" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="Q11" t="n">
         <v>2.2</v>
       </c>
       <c r="R11" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S11" t="n">
         <v>4.2</v>
       </c>
       <c r="T11" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="U11" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="V11" t="n">
         <v>1.42</v>
@@ -3197,183 +3197,183 @@
         <v>1.59</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y11" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD11" t="n">
         <v>15</v>
       </c>
-      <c r="Z11" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>80</v>
-      </c>
-      <c r="AB11" t="n">
+      <c r="AE11" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV11" t="n">
         <v>12</v>
       </c>
-      <c r="AC11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AV11" t="n">
+      <c r="AW11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY11" t="n">
         <v>10</v>
       </c>
-      <c r="AW11" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AZ11" t="n">
-        <v>2.14</v>
+        <v>17.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>2.24</v>
+        <v>6.8</v>
       </c>
       <c r="BB11" t="n">
-        <v>2.22</v>
+        <v>6.4</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.18</v>
+        <v>6.2</v>
       </c>
       <c r="BD11" t="n">
-        <v>2.24</v>
+        <v>6.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>2.3</v>
+        <v>7.2</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.3</v>
+        <v>6.4</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.3</v>
+        <v>6.6</v>
       </c>
       <c r="BH11" t="n">
         <v>1000</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="BJ11" t="n">
         <v>15</v>
       </c>
       <c r="BK11" t="n">
-        <v>6.4</v>
+        <v>1.55</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>21</v>
+        <v>1.73</v>
       </c>
       <c r="BN11" t="n">
         <v>7.6</v>
       </c>
       <c r="BO11" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="BP11" t="n">
         <v>32</v>
       </c>
       <c r="BQ11" t="n">
-        <v>13</v>
+        <v>1.64</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>21</v>
+        <v>1.68</v>
       </c>
       <c r="BT11" t="n">
         <v>8.6</v>
       </c>
       <c r="BU11" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="BV11" t="n">
         <v>40</v>
       </c>
       <c r="BW11" t="n">
-        <v>16.5</v>
+        <v>1.66</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>21</v>
+        <v>1.69</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>21</v>
+        <v>1.68</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-15 13:35:15</t>
+          <t>2026-07-15 15:46:37</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3388,246 +3388,246 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nomme Utd</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.3</v>
+        <v>5.8</v>
       </c>
       <c r="G12" t="n">
-        <v>1.38</v>
+        <v>7</v>
       </c>
       <c r="H12" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="V12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>29</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>220</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>120</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>160</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AR12" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="I12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="J12" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="K12" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="P12" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="T12" t="n">
+      <c r="AS12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BK12" t="n">
         <v>1.63</v>
       </c>
-      <c r="U12" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="X12" t="n">
-        <v>55</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>60</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>120</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>290</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>42</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>15</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>30</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>90</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>10</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="BN12" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="BT12" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BU12" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="BV12" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="BX12" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA12" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-15 13:35:15</t>
+          <t>2026-07-15 15:46:37</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Slovenian Premier League</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3642,31 +3642,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Nafta Lendava</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Nomme Utd</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>5.1</v>
+        <v>1.3</v>
       </c>
       <c r="G13" t="n">
-        <v>10</v>
+        <v>1.38</v>
       </c>
       <c r="H13" t="n">
-        <v>1.44</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>1.67</v>
+        <v>10.5</v>
       </c>
       <c r="J13" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="K13" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
@@ -3675,142 +3675,142 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="O13" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="P13" t="n">
-        <v>2.16</v>
+        <v>3.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="R13" t="n">
-        <v>1.48</v>
+        <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="T13" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="U13" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="V13" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="W13" t="n">
-        <v>1.11</v>
+        <v>3.5</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BH13" t="n">
         <v>1000</v>
@@ -3867,21 +3867,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-15 13:35:15</t>
+          <t>2026-07-15 15:46:37</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Slovenian Premier League</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3896,175 +3896,175 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Nafta Lendava</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="G14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H14" t="n">
-        <v>1.63</v>
+        <v>1.46</v>
       </c>
       <c r="I14" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="J14" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K14" t="n">
-        <v>4.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="O14" t="n">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="P14" t="n">
-        <v>1.85</v>
+        <v>2.16</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.94</v>
+        <v>1.48</v>
       </c>
       <c r="R14" t="n">
-        <v>1.32</v>
+        <v>1.48</v>
       </c>
       <c r="S14" t="n">
-        <v>3.45</v>
+        <v>2.2</v>
       </c>
       <c r="T14" t="n">
-        <v>1.93</v>
+        <v>1.01</v>
       </c>
       <c r="U14" t="n">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="X14" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ14" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="AR14" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AS14" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AT14" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AU14" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AV14" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AW14" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AX14" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="AY14" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ14" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA14" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BF14" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="n">
         <v>1000</v>
@@ -4073,69 +4073,69 @@
         <v>1.01</v>
       </c>
       <c r="BJ14" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN14" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BO14" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BT14" t="n">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>2.84</v>
+        <v>1.01</v>
       </c>
       <c r="BV14" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BX14" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ14" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="CA14" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-15 13:35:15</t>
+          <t>2026-07-15 15:46:37</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Norwegian Eliteserien</t>
+          <t>Swedish Allsvenskan</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4145,251 +4145,251 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>14:15:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Bodo Glimt</t>
+          <t>IFK Goteborg</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.18</v>
+        <v>2</v>
       </c>
       <c r="G15" t="n">
-        <v>1.2</v>
+        <v>2.04</v>
       </c>
       <c r="H15" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="I15" t="n">
+        <v>4</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="X15" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y15" t="n">
         <v>18.5</v>
       </c>
-      <c r="I15" t="n">
+      <c r="Z15" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>44</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>29</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB15" t="n">
         <v>19.5</v>
       </c>
-      <c r="J15" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="K15" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>0</v>
-      </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG15" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BH15" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BI15" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BK15" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="BL15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="BN15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BO15" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BP15" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="BR15" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BS15" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="BT15" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BU15" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BV15" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BW15" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="BX15" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BY15" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="CA15" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-15 13:35:15</t>
+          <t>2026-07-15 15:46:37</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Swedish Allsvenskan</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4399,251 +4399,251 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>15:15:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>PFC Levski Sofia</t>
+          <t>Mjallby</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dunav Ruse</t>
+          <t>Vasteras SK</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.16</v>
+        <v>1.86</v>
       </c>
       <c r="G16" t="n">
-        <v>1.17</v>
+        <v>1.94</v>
       </c>
       <c r="H16" t="n">
-        <v>22</v>
+        <v>4.1</v>
       </c>
       <c r="I16" t="n">
-        <v>36</v>
+        <v>4.5</v>
       </c>
       <c r="J16" t="n">
+        <v>4</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU16" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="K16" t="n">
-        <v>10</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>0</v>
-      </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BG16" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BH16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI16" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BK16" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BL16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BN16" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BO16" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BP16" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BR16" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BS16" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BT16" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BU16" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BV16" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BW16" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BX16" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BY16" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="CA16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-15 13:35:15</t>
+          <t>2026-07-15 15:46:37</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Slovenian Premier League</t>
+          <t>Norwegian Eliteserien</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4653,251 +4653,251 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>15:15:00</t>
+          <t>14:15:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NK Celje</t>
+          <t>Bodo Glimt</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="P17" t="n">
-        <v>1.24</v>
+        <v>3.8</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AO17" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="BG17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BH17" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BI17" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BK17" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BL17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BN17" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BO17" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BP17" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BR17" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BS17" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BT17" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BU17" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BV17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BX17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="CA17" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-15 13:35:15</t>
+          <t>2026-07-15 15:46:37</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Romanian Liga I</t>
+          <t>Peruvian Primera Division</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4907,251 +4907,251 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>FC Cajamarca</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Arges Pitesti</t>
+          <t>Juan Pablo II College</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.62</v>
+        <v>1.99</v>
       </c>
       <c r="G18" t="n">
-        <v>1.71</v>
+        <v>2.24</v>
       </c>
       <c r="H18" t="n">
-        <v>5.7</v>
+        <v>3.5</v>
       </c>
       <c r="I18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="X18" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>48</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>28</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>23</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG18" t="n">
         <v>6.8</v>
       </c>
-      <c r="J18" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>0</v>
-      </c>
       <c r="BH18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-15 13:35:15</t>
+          <t>2026-07-15 15:46:37</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5161,234 +5161,234 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Albion FC</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Njardvik</t>
+          <t>Juventud De Las Piedras</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.04</v>
+        <v>2.3</v>
       </c>
       <c r="G19" t="n">
-        <v>1000</v>
+        <v>2.48</v>
       </c>
       <c r="H19" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="I19" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="J19" t="n">
-        <v>1.02</v>
+        <v>3.2</v>
       </c>
       <c r="K19" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="P19" t="n">
-        <v>1.24</v>
+        <v>1.67</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AO19" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BG19" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BH19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BI19" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BK19" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BL19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BN19" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BO19" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BP19" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BQ19" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BR19" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BS19" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BT19" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BU19" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BV19" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BW19" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BX19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BZ19" t="n">
         <v>0</v>
@@ -5398,14 +5398,14 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-15 13:35:15</t>
+          <t>2026-07-15 15:46:37</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5415,251 +5415,251 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>15:15:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Sao Bernardo</t>
+          <t>PFC Levski Sofia</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Avai</t>
+          <t>Dunav Ruse</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="P20" t="n">
-        <v>1.25</v>
+        <v>2.42</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>590</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>550</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AO20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BG20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BI20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BK20" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BL20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN20" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BO20" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BP20" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BQ20" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BR20" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BS20" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BT20" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BU20" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BV20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BX20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BZ20" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="CA20" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-15 13:35:15</t>
+          <t>2026-07-15 15:46:37</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Slovenian Premier League</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5669,251 +5669,251 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>15:15:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>NK Celje</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cuiaba</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="P21" t="n">
-        <v>1.25</v>
+        <v>2.26</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-15 13:35:15</t>
+          <t>2026-07-15 15:46:37</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5923,251 +5923,251 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>America MG</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ceara SC Fortaleza</t>
+          <t>Arges Pitesti</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="P22" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="BG22" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="BH22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ22" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BK22" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BL22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BN22" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BO22" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="BP22" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BQ22" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BR22" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BS22" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BT22" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BU22" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BV22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BX22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BZ22" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="CA22" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-15 13:35:15</t>
+          <t>2026-07-15 15:46:37</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6177,36 +6177,36 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Fylkir</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Njardvik</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.43</v>
+        <v>1.04</v>
       </c>
       <c r="G23" t="n">
-        <v>1.49</v>
+        <v>1000</v>
       </c>
       <c r="H23" t="n">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="I23" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="J23" t="n">
-        <v>5.1</v>
+        <v>1.02</v>
       </c>
       <c r="K23" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -6221,10 +6221,10 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.44</v>
+        <v>1.24</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -6414,14 +6414,14 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-15 13:35:15</t>
+          <t>2026-07-15 15:46:37</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>Peruvian Primera Division</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6431,36 +6431,36 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>17:15:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Atletico Ottawa</t>
+          <t>Sporting Cristal</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Inter Toronto FC</t>
+          <t>Deportivo Garcilaso</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -6668,14 +6668,14 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-15 13:35:15</t>
+          <t>2026-07-15 15:46:37</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6685,251 +6685,251 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Sao Bernardo</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Gremio</t>
+          <t>Avai</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="R25" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AQ25" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AR25" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AS25" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AT25" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AU25" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AV25" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AX25" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AY25" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AZ25" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="BA25" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BC25" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BD25" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="BG25" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BH25" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="BI25" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="BJ25" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BK25" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="BL25" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM25" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BN25" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BO25" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BP25" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BQ25" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BR25" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BS25" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BT25" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BU25" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BV25" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BW25" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BX25" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BY25" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BZ25" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="CA25" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-15 13:35:15</t>
+          <t>2026-07-15 15:46:37</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6939,36 +6939,36 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Red Bull Bragantino</t>
+          <t>Cuiaba</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -6983,10 +6983,10 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1.78</v>
+        <v>1.25</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -7176,261 +7176,1785 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-15 13:35:15</t>
+          <t>2026-07-15 15:46:37</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>America MG</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Ceara SC Fortaleza</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB27" t="inlineStr">
+        <is>
+          <t>2026-07-15 15:46:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>19:30:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Chapecoense</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="H28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="I28" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="J28" t="n">
+        <v>5</v>
+      </c>
+      <c r="K28" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB28" t="inlineStr">
+        <is>
+          <t>2026-07-15 15:46:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Uruguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>19:30:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Nacional (Uru)</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Wanderers (Uru)</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="I29" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="J29" t="n">
+        <v>4</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB29" t="inlineStr">
+        <is>
+          <t>2026-07-15 15:46:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Mirassol</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Gremio</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="H30" t="n">
+        <v>4</v>
+      </c>
+      <c r="I30" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="X30" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>19</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BH30" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BI30" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BJ30" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK30" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM30" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN30" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BO30" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BP30" t="n">
+        <v>16</v>
+      </c>
+      <c r="BQ30" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BR30" t="n">
+        <v>34</v>
+      </c>
+      <c r="BS30" t="n">
+        <v>8</v>
+      </c>
+      <c r="BT30" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BU30" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BV30" t="n">
+        <v>42</v>
+      </c>
+      <c r="BW30" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BX30" t="n">
+        <v>55</v>
+      </c>
+      <c r="BY30" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BZ30" t="n">
+        <v>32</v>
+      </c>
+      <c r="CA30" t="n">
+        <v>8</v>
+      </c>
+      <c r="CB30" t="inlineStr">
+        <is>
+          <t>2026-07-15 15:46:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Red Bull Bragantino</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="H31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB31" t="inlineStr">
+        <is>
+          <t>2026-07-15 15:46:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>Canadian Premier League</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Atletico Ottawa</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Inter Toronto FC</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB32" t="inlineStr">
+        <is>
+          <t>2026-07-15 15:46:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Canadian Premier League</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
         <is>
           <t>FC Supra du Quebec</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Vancouver FC</t>
         </is>
       </c>
-      <c r="F27" t="n">
+      <c r="F33" t="n">
         <v>1.04</v>
       </c>
-      <c r="G27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H27" t="n">
+      <c r="G33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H33" t="n">
         <v>1.04</v>
       </c>
-      <c r="I27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J27" t="n">
+      <c r="I33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J33" t="n">
         <v>1.02</v>
       </c>
-      <c r="K27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
+      <c r="K33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB27" t="inlineStr">
-        <is>
-          <t>2026-07-15 13:35:15</t>
+      <c r="Q33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB33" t="inlineStr">
+        <is>
+          <t>2026-07-15 15:46:37</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-17.xlsx
@@ -863,10 +863,10 @@
         <v>3.85</v>
       </c>
       <c r="H2" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="I2" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="J2" t="n">
         <v>3.65</v>
@@ -881,7 +881,7 @@
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O2" t="n">
         <v>1.28</v>
@@ -890,7 +890,7 @@
         <v>2.08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="R2" t="n">
         <v>1.43</v>
@@ -902,10 +902,10 @@
         <v>1.72</v>
       </c>
       <c r="U2" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V2" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="W2" t="n">
         <v>1.35</v>
@@ -917,7 +917,7 @@
         <v>12</v>
       </c>
       <c r="Z2" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AA2" t="n">
         <v>30</v>
@@ -926,31 +926,31 @@
         <v>17.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE2" t="n">
         <v>25</v>
       </c>
       <c r="AF2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AG2" t="n">
         <v>18</v>
       </c>
       <c r="AH2" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ2" t="n">
         <v>75</v>
       </c>
       <c r="AK2" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AL2" t="n">
         <v>60</v>
@@ -962,10 +962,10 @@
         <v>40</v>
       </c>
       <c r="AO2" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AQ2" t="n">
         <v>9.6</v>
@@ -974,7 +974,7 @@
         <v>12</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="AT2" t="n">
         <v>13.5</v>
@@ -983,10 +983,10 @@
         <v>7.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AX2" t="n">
         <v>21</v>
@@ -998,31 +998,31 @@
         <v>15</v>
       </c>
       <c r="BA2" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BF2" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BG2" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BH2" t="n">
         <v>3.7</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="BJ2" t="n">
         <v>9.199999999999999</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-15 15:46:37</t>
+          <t>2026-07-15 17:58:21</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-15 15:46:37</t>
+          <t>2026-07-15 17:58:21</t>
         </is>
       </c>
     </row>
@@ -1365,28 +1365,28 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="G4" t="n">
         <v>4.6</v>
       </c>
       <c r="H4" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="I4" t="n">
         <v>2.04</v>
       </c>
       <c r="J4" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="K4" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L4" t="n">
         <v>1.42</v>
       </c>
       <c r="M4" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N4" t="n">
         <v>3.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-15 15:46:37</t>
+          <t>2026-07-15 17:58:21</t>
         </is>
       </c>
     </row>
@@ -1634,7 +1634,7 @@
         <v>3.95</v>
       </c>
       <c r="K5" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-15 15:46:37</t>
+          <t>2026-07-15 17:58:21</t>
         </is>
       </c>
     </row>
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="G6" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="H6" t="n">
         <v>1.98</v>
@@ -1897,7 +1897,7 @@
         <v>1.1</v>
       </c>
       <c r="N6" t="n">
-        <v>2.72</v>
+        <v>2.58</v>
       </c>
       <c r="O6" t="n">
         <v>1.43</v>
@@ -1912,7 +1912,7 @@
         <v>1.23</v>
       </c>
       <c r="S6" t="n">
-        <v>1.02</v>
+        <v>3.9</v>
       </c>
       <c r="T6" t="n">
         <v>1.98</v>
@@ -1924,7 +1924,7 @@
         <v>1.82</v>
       </c>
       <c r="W6" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="X6" t="n">
         <v>12.5</v>
@@ -1966,7 +1966,7 @@
         <v>140</v>
       </c>
       <c r="AK6" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AL6" t="n">
         <v>100</v>
@@ -1981,7 +1981,7 @@
         <v>27</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AQ6" t="n">
         <v>2.94</v>
@@ -1996,7 +1996,7 @@
         <v>3.4</v>
       </c>
       <c r="AU6" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="AV6" t="n">
         <v>3.3</v>
@@ -2005,7 +2005,7 @@
         <v>3.85</v>
       </c>
       <c r="AX6" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AY6" t="n">
         <v>3.65</v>
@@ -2014,7 +2014,7 @@
         <v>3.75</v>
       </c>
       <c r="BA6" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BB6" t="n">
         <v>4.2</v>
@@ -2023,10 +2023,10 @@
         <v>4.1</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF6" t="n">
         <v>4.2</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-15 15:46:37</t>
+          <t>2026-07-15 17:58:21</t>
         </is>
       </c>
     </row>
@@ -2169,10 +2169,10 @@
         <v>3.45</v>
       </c>
       <c r="T7" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U7" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="V7" t="n">
         <v>1.62</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-15 15:46:37</t>
+          <t>2026-07-15 17:58:21</t>
         </is>
       </c>
     </row>
@@ -2381,28 +2381,28 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="G8" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="H8" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="I8" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="J8" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K8" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="L8" t="n">
         <v>1.27</v>
       </c>
       <c r="M8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
         <v>4.5</v>
@@ -2423,28 +2423,28 @@
         <v>2.62</v>
       </c>
       <c r="T8" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="U8" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="V8" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="W8" t="n">
-        <v>2.58</v>
+        <v>2.72</v>
       </c>
       <c r="X8" t="n">
         <v>22</v>
       </c>
       <c r="Y8" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Z8" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AA8" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AB8" t="n">
         <v>10.5</v>
@@ -2453,31 +2453,31 @@
         <v>11.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AE8" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AF8" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AI8" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AJ8" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AK8" t="n">
         <v>16</v>
       </c>
       <c r="AL8" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AM8" t="n">
         <v>110</v>
@@ -2486,7 +2486,7 @@
         <v>8</v>
       </c>
       <c r="AO8" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AP8" t="n">
         <v>18</v>
@@ -2498,7 +2498,7 @@
         <v>40</v>
       </c>
       <c r="AS8" t="n">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="AT8" t="n">
         <v>9.199999999999999</v>
@@ -2507,13 +2507,13 @@
         <v>9.6</v>
       </c>
       <c r="AV8" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AW8" t="n">
         <v>55</v>
       </c>
       <c r="AX8" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AY8" t="n">
         <v>8.800000000000001</v>
@@ -2531,13 +2531,13 @@
         <v>13</v>
       </c>
       <c r="BD8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BE8" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="BF8" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BG8" t="n">
         <v>46</v>
@@ -2549,62 +2549,62 @@
         <v>3.2</v>
       </c>
       <c r="BJ8" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK8" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BN8" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BP8" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BR8" t="n">
         <v>24</v>
       </c>
       <c r="BS8" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BT8" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BU8" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BZ8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CA8" t="n">
         <v>5.7</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-15 15:46:37</t>
+          <t>2026-07-15 17:58:21</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="G9" t="n">
         <v>1.46</v>
@@ -2650,7 +2650,7 @@
         <v>5.4</v>
       </c>
       <c r="K9" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2683,7 +2683,7 @@
         <v>2.26</v>
       </c>
       <c r="V9" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="W9" t="n">
         <v>3.15</v>
@@ -2752,7 +2752,7 @@
         <v>5.9</v>
       </c>
       <c r="AS9" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AT9" t="n">
         <v>10.5</v>
@@ -2761,7 +2761,7 @@
         <v>10.5</v>
       </c>
       <c r="AV9" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AW9" t="n">
         <v>5.9</v>
@@ -2794,7 +2794,7 @@
         <v>3.55</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BH9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-15 15:46:37</t>
+          <t>2026-07-15 17:58:21</t>
         </is>
       </c>
     </row>
@@ -2892,7 +2892,7 @@
         <v>2.48</v>
       </c>
       <c r="G10" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="H10" t="n">
         <v>2.54</v>
@@ -2907,28 +2907,28 @@
         <v>4.4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="M10" t="n">
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="O10" t="n">
         <v>1.13</v>
       </c>
       <c r="P10" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="R10" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="S10" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="T10" t="n">
         <v>1.43</v>
@@ -2943,7 +2943,7 @@
         <v>1.58</v>
       </c>
       <c r="X10" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Y10" t="n">
         <v>24</v>
@@ -2976,7 +2976,7 @@
         <v>14.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AJ10" t="n">
         <v>44</v>
@@ -2991,25 +2991,25 @@
         <v>46</v>
       </c>
       <c r="AN10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AO10" t="n">
         <v>13</v>
       </c>
-      <c r="AO10" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AP10" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AQ10" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AR10" t="n">
         <v>20</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AT10" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AU10" t="n">
         <v>9.6</v>
@@ -3021,7 +3021,7 @@
         <v>20</v>
       </c>
       <c r="AX10" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AY10" t="n">
         <v>11.5</v>
@@ -3033,7 +3033,7 @@
         <v>18.5</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BC10" t="n">
         <v>19.5</v>
@@ -3042,7 +3042,7 @@
         <v>19</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BF10" t="n">
         <v>9.6</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-15 15:46:37</t>
+          <t>2026-07-15 17:58:21</t>
         </is>
       </c>
     </row>
@@ -3143,13 +3143,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G11" t="n">
         <v>2.68</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I11" t="n">
         <v>3.35</v>
@@ -3158,7 +3158,7 @@
         <v>3.25</v>
       </c>
       <c r="K11" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="L11" t="n">
         <v>1.41</v>
@@ -3188,7 +3188,7 @@
         <v>1.9</v>
       </c>
       <c r="U11" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="V11" t="n">
         <v>1.42</v>
@@ -3212,13 +3212,13 @@
         <v>9</v>
       </c>
       <c r="AC11" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD11" t="n">
         <v>15</v>
       </c>
       <c r="AE11" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF11" t="n">
         <v>16.5</v>
@@ -3227,7 +3227,7 @@
         <v>12.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI11" t="n">
         <v>65</v>
@@ -3239,13 +3239,13 @@
         <v>34</v>
       </c>
       <c r="AL11" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM11" t="n">
         <v>160</v>
       </c>
       <c r="AN11" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AO11" t="n">
         <v>60</v>
@@ -3260,7 +3260,7 @@
         <v>17.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AT11" t="n">
         <v>7.4</v>
@@ -3272,7 +3272,7 @@
         <v>12</v>
       </c>
       <c r="AW11" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AX11" t="n">
         <v>13</v>
@@ -3284,25 +3284,25 @@
         <v>17.5</v>
       </c>
       <c r="BA11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC11" t="n">
         <v>6.8</v>
       </c>
-      <c r="BB11" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BD11" t="n">
-        <v>6.6</v>
+        <v>40</v>
       </c>
       <c r="BE11" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BF11" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BG11" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BH11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-15 15:46:37</t>
+          <t>2026-07-15 17:58:21</t>
         </is>
       </c>
     </row>
@@ -3415,7 +3415,7 @@
         <v>4.3</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M12" t="n">
         <v>1.06</v>
@@ -3598,7 +3598,7 @@
         <v>5.8</v>
       </c>
       <c r="BU12" t="n">
-        <v>2.84</v>
+        <v>3.15</v>
       </c>
       <c r="BV12" t="n">
         <v>16</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-15 15:46:37</t>
+          <t>2026-07-15 17:58:21</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
         <v>10.5</v>
       </c>
       <c r="J13" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="K13" t="n">
         <v>7.6</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-15 15:46:37</t>
+          <t>2026-07-15 17:58:21</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-15 15:46:37</t>
+          <t>2026-07-15 17:58:21</t>
         </is>
       </c>
     </row>
@@ -4165,7 +4165,7 @@
         <v>2.04</v>
       </c>
       <c r="H15" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="I15" t="n">
         <v>4</v>
@@ -4174,7 +4174,7 @@
         <v>3.95</v>
       </c>
       <c r="K15" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L15" t="n">
         <v>1.31</v>
@@ -4186,7 +4186,7 @@
         <v>4.7</v>
       </c>
       <c r="O15" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P15" t="n">
         <v>2.2</v>
@@ -4195,10 +4195,10 @@
         <v>1.71</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="S15" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="T15" t="n">
         <v>1.66</v>
@@ -4228,7 +4228,7 @@
         <v>12.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD15" t="n">
         <v>17</v>
@@ -4273,7 +4273,7 @@
         <v>15</v>
       </c>
       <c r="AR15" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AS15" t="n">
         <v>8</v>
@@ -4309,7 +4309,7 @@
         <v>16.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE15" t="n">
         <v>8</v>
@@ -4324,37 +4324,37 @@
         <v>5.4</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.74</v>
+        <v>1.91</v>
       </c>
       <c r="BJ15" t="n">
         <v>13</v>
       </c>
       <c r="BK15" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="BN15" t="n">
         <v>7</v>
       </c>
       <c r="BO15" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="BP15" t="n">
         <v>19</v>
       </c>
       <c r="BQ15" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="BR15" t="n">
         <v>34</v>
       </c>
       <c r="BS15" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="BT15" t="n">
         <v>10.5</v>
@@ -4366,23 +4366,23 @@
         <v>44</v>
       </c>
       <c r="BW15" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="BX15" t="n">
         <v>50</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="BZ15" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="CA15" t="n">
         <v>2.66</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-15 15:46:37</t>
+          <t>2026-07-15 17:58:21</t>
         </is>
       </c>
     </row>
@@ -4416,25 +4416,25 @@
         <v>1.86</v>
       </c>
       <c r="G16" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="H16" t="n">
         <v>4.1</v>
       </c>
       <c r="I16" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J16" t="n">
         <v>4</v>
       </c>
       <c r="K16" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N16" t="n">
         <v>4.7</v>
@@ -4443,82 +4443,82 @@
         <v>1.23</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q16" t="n">
         <v>1.69</v>
       </c>
       <c r="R16" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S16" t="n">
-        <v>2.58</v>
+        <v>2.74</v>
       </c>
       <c r="T16" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U16" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="V16" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W16" t="n">
         <v>2.06</v>
       </c>
       <c r="X16" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD16" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AE16" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF16" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH16" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK16" t="n">
         <v>19</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM16" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AP16" t="n">
         <v>17.5</v>
@@ -4527,10 +4527,10 @@
         <v>16</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.07</v>
+        <v>4.7</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.07</v>
+        <v>5</v>
       </c>
       <c r="AT16" t="n">
         <v>9.6</v>
@@ -4542,7 +4542,7 @@
         <v>14.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.05</v>
+        <v>4.8</v>
       </c>
       <c r="AX16" t="n">
         <v>11</v>
@@ -4554,7 +4554,7 @@
         <v>14.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.07</v>
+        <v>4.9</v>
       </c>
       <c r="BB16" t="n">
         <v>18</v>
@@ -4563,16 +4563,16 @@
         <v>15</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.07</v>
+        <v>4.6</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.07</v>
+        <v>5</v>
       </c>
       <c r="BF16" t="n">
         <v>7.6</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.07</v>
+        <v>4.8</v>
       </c>
       <c r="BH16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-15 15:46:37</t>
+          <t>2026-07-15 17:58:21</t>
         </is>
       </c>
     </row>
@@ -4667,22 +4667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="G17" t="n">
         <v>1.21</v>
       </c>
       <c r="H17" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="I17" t="n">
         <v>19</v>
       </c>
       <c r="J17" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="L17" t="n">
         <v>1.19</v>
@@ -4697,10 +4697,10 @@
         <v>1.1</v>
       </c>
       <c r="P17" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="R17" t="n">
         <v>2.14</v>
@@ -4709,10 +4709,10 @@
         <v>1.76</v>
       </c>
       <c r="T17" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="U17" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V17" t="n">
         <v>1.04</v>
@@ -4724,10 +4724,10 @@
         <v>55</v>
       </c>
       <c r="Y17" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="Z17" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AA17" t="n">
         <v>1000</v>
@@ -4736,13 +4736,13 @@
         <v>19.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AD17" t="n">
         <v>75</v>
       </c>
       <c r="AE17" t="n">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="AF17" t="n">
         <v>13.5</v>
@@ -4751,10 +4751,10 @@
         <v>16.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AI17" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AJ17" t="n">
         <v>13</v>
@@ -4766,49 +4766,49 @@
         <v>40</v>
       </c>
       <c r="AM17" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN17" t="n">
         <v>2.74</v>
       </c>
       <c r="AO17" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AP17" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AQ17" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AR17" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AS17" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT17" t="n">
         <v>11.5</v>
       </c>
       <c r="AU17" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="AV17" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AW17" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AX17" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AY17" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ17" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BB17" t="n">
         <v>9.199999999999999</v>
@@ -4817,34 +4817,34 @@
         <v>10</v>
       </c>
       <c r="BD17" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BE17" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF17" t="n">
         <v>2.54</v>
       </c>
       <c r="BG17" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BH17" t="n">
         <v>6.4</v>
       </c>
       <c r="BI17" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BJ17" t="n">
         <v>12.5</v>
       </c>
       <c r="BK17" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN17" t="n">
         <v>4.3</v>
@@ -4853,7 +4853,7 @@
         <v>3.35</v>
       </c>
       <c r="BP17" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BQ17" t="n">
         <v>4.7</v>
@@ -4862,25 +4862,25 @@
         <v>18</v>
       </c>
       <c r="BS17" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BT17" t="n">
         <v>17.5</v>
       </c>
       <c r="BU17" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BZ17" t="n">
         <v>6.2</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-15 15:46:37</t>
+          <t>2026-07-15 17:58:21</t>
         </is>
       </c>
     </row>
@@ -4927,7 +4927,7 @@
         <v>2.24</v>
       </c>
       <c r="H18" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I18" t="n">
         <v>4.2</v>
@@ -4939,7 +4939,7 @@
         <v>4.1</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="M18" t="n">
         <v>1.05</v>
@@ -4984,7 +4984,7 @@
         <v>40</v>
       </c>
       <c r="AA18" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AB18" t="n">
         <v>11.5</v>
@@ -4996,7 +4996,7 @@
         <v>16.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AF18" t="n">
         <v>15</v>
@@ -5008,7 +5008,7 @@
         <v>17.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="AJ18" t="n">
         <v>27</v>
@@ -5020,13 +5020,13 @@
         <v>46</v>
       </c>
       <c r="AM18" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AN18" t="n">
         <v>16.5</v>
       </c>
       <c r="AO18" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AP18" t="n">
         <v>14.5</v>
@@ -5077,10 +5077,10 @@
         <v>7.6</v>
       </c>
       <c r="BF18" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG18" t="n">
-        <v>6.8</v>
+        <v>24</v>
       </c>
       <c r="BH18" t="n">
         <v>1000</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-15 15:46:37</t>
+          <t>2026-07-15 17:58:21</t>
         </is>
       </c>
     </row>
@@ -5181,7 +5181,7 @@
         <v>2.48</v>
       </c>
       <c r="H19" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="I19" t="n">
         <v>3.8</v>
@@ -5190,10 +5190,10 @@
         <v>3.2</v>
       </c>
       <c r="K19" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L19" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="M19" t="n">
         <v>1.09</v>
@@ -5202,7 +5202,7 @@
         <v>3</v>
       </c>
       <c r="O19" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P19" t="n">
         <v>1.67</v>
@@ -5211,13 +5211,13 @@
         <v>2.2</v>
       </c>
       <c r="R19" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S19" t="n">
         <v>4.1</v>
       </c>
       <c r="T19" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U19" t="n">
         <v>1.93</v>
@@ -5292,7 +5292,7 @@
         <v>18</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AT19" t="n">
         <v>7</v>
@@ -5304,55 +5304,55 @@
         <v>11</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AX19" t="n">
         <v>11</v>
       </c>
       <c r="AY19" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AZ19" t="n">
         <v>14.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BF19" t="n">
         <v>20</v>
       </c>
       <c r="BG19" t="n">
-        <v>42</v>
+        <v>4.8</v>
       </c>
       <c r="BH19" t="n">
         <v>3.1</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="BJ19" t="n">
         <v>10.5</v>
       </c>
       <c r="BK19" t="n">
-        <v>7.8</v>
+        <v>5.6</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="BN19" t="n">
         <v>5.2</v>
@@ -5364,31 +5364,31 @@
         <v>19</v>
       </c>
       <c r="BQ19" t="n">
-        <v>14</v>
+        <v>7.4</v>
       </c>
       <c r="BR19" t="n">
         <v>38</v>
       </c>
       <c r="BS19" t="n">
-        <v>27</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT19" t="n">
         <v>6.8</v>
       </c>
       <c r="BU19" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BV19" t="n">
         <v>34</v>
       </c>
       <c r="BW19" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>34</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ19" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-15 15:46:37</t>
+          <t>2026-07-15 17:58:21</t>
         </is>
       </c>
     </row>
@@ -5471,10 +5471,10 @@
         <v>2.4</v>
       </c>
       <c r="T20" t="n">
-        <v>2.54</v>
+        <v>2.72</v>
       </c>
       <c r="U20" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="V20" t="n">
         <v>1.03</v>
@@ -5507,31 +5507,31 @@
         <v>1000</v>
       </c>
       <c r="AF20" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AG20" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AH20" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AI20" t="n">
         <v>590</v>
       </c>
       <c r="AJ20" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AK20" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL20" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM20" t="n">
         <v>550</v>
       </c>
       <c r="AN20" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="AO20" t="n">
         <v>1000</v>
@@ -5540,13 +5540,13 @@
         <v>20</v>
       </c>
       <c r="AQ20" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="AR20" t="n">
-        <v>90</v>
+        <v>1.01</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT20" t="n">
         <v>6.8</v>
@@ -5555,19 +5555,19 @@
         <v>16</v>
       </c>
       <c r="AV20" t="n">
-        <v>80</v>
+        <v>1.01</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX20" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AY20" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>48</v>
+        <v>1.01</v>
       </c>
       <c r="BA20" t="n">
         <v>1.01</v>
@@ -5579,7 +5579,7 @@
         <v>12.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BE20" t="n">
         <v>1.01</v>
@@ -5600,13 +5600,13 @@
         <v>25</v>
       </c>
       <c r="BK20" t="n">
-        <v>11.5</v>
+        <v>2.98</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>21</v>
+        <v>3.35</v>
       </c>
       <c r="BN20" t="n">
         <v>4.4</v>
@@ -5624,35 +5624,35 @@
         <v>40</v>
       </c>
       <c r="BS20" t="n">
-        <v>17.5</v>
+        <v>3.1</v>
       </c>
       <c r="BT20" t="n">
         <v>34</v>
       </c>
       <c r="BU20" t="n">
-        <v>15.5</v>
+        <v>3.05</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>21</v>
+        <v>3.35</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>21</v>
+        <v>3.35</v>
       </c>
       <c r="BZ20" t="n">
         <v>11.5</v>
       </c>
       <c r="CA20" t="n">
-        <v>5.6</v>
+        <v>2.62</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-15 15:46:37</t>
+          <t>2026-07-15 17:58:21</t>
         </is>
       </c>
     </row>
@@ -5692,7 +5692,7 @@
         <v>6.4</v>
       </c>
       <c r="I21" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="J21" t="n">
         <v>4.8</v>
@@ -5719,10 +5719,10 @@
         <v>1.44</v>
       </c>
       <c r="R21" t="n">
-        <v>1.21</v>
+        <v>1.45</v>
       </c>
       <c r="S21" t="n">
-        <v>1.44</v>
+        <v>1.93</v>
       </c>
       <c r="T21" t="n">
         <v>1.01</v>
@@ -5791,52 +5791,52 @@
         <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF21" t="n">
         <v>1.01</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-15 15:46:37</t>
+          <t>2026-07-15 17:58:21</t>
         </is>
       </c>
     </row>
@@ -5940,7 +5940,7 @@
         <v>1.62</v>
       </c>
       <c r="G22" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="H22" t="n">
         <v>5.6</v>
@@ -5952,19 +5952,19 @@
         <v>4.1</v>
       </c>
       <c r="K22" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L22" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="M22" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N22" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="O22" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P22" t="n">
         <v>2</v>
@@ -5973,194 +5973,194 @@
         <v>1.88</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="S22" t="n">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="T22" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="U22" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="V22" t="n">
         <v>1.17</v>
       </c>
       <c r="W22" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="X22" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="Y22" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>190</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD22" t="n">
         <v>24</v>
       </c>
-      <c r="Z22" t="n">
+      <c r="AE22" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>130</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>8</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>8</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>28</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BT22" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BU22" t="n">
+        <v>7</v>
+      </c>
+      <c r="BV22" t="n">
         <v>60</v>
       </c>
-      <c r="AA22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>32</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BH22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ22" t="n">
-        <v>15</v>
-      </c>
-      <c r="BK22" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BL22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM22" t="n">
+      <c r="BW22" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BX22" t="n">
+        <v>65</v>
+      </c>
+      <c r="BY22" t="n">
+        <v>9</v>
+      </c>
+      <c r="BZ22" t="n">
         <v>22</v>
       </c>
-      <c r="BN22" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BO22" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BP22" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BQ22" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BR22" t="n">
-        <v>38</v>
-      </c>
-      <c r="BS22" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BT22" t="n">
-        <v>13</v>
-      </c>
-      <c r="BU22" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BV22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW22" t="n">
-        <v>22</v>
-      </c>
-      <c r="BX22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY22" t="n">
-        <v>22</v>
-      </c>
-      <c r="BZ22" t="n">
-        <v>30</v>
-      </c>
       <c r="CA22" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-15 15:46:37</t>
+          <t>2026-07-15 17:58:21</t>
         </is>
       </c>
     </row>
@@ -6191,230 +6191,230 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.04</v>
+        <v>1.96</v>
       </c>
       <c r="G23" t="n">
-        <v>1000</v>
+        <v>2.08</v>
       </c>
       <c r="H23" t="n">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="I23" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="J23" t="n">
-        <v>1.02</v>
+        <v>4</v>
       </c>
       <c r="K23" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="P23" t="n">
-        <v>1.24</v>
+        <v>2.56</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AO23" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BH23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-15 15:46:37</t>
+          <t>2026-07-15 17:58:21</t>
         </is>
       </c>
     </row>
@@ -6445,230 +6445,230 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="P24" t="n">
-        <v>1.24</v>
+        <v>2.02</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-15 15:46:37</t>
+          <t>2026-07-15 17:58:21</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-15 15:46:37</t>
+          <t>2026-07-15 17:58:21</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-15 15:46:37</t>
+          <t>2026-07-15 17:58:21</t>
         </is>
       </c>
     </row>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-15 15:46:37</t>
+          <t>2026-07-15 17:58:21</t>
         </is>
       </c>
     </row>
@@ -7461,22 +7461,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="G28" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="H28" t="n">
+        <v>7</v>
+      </c>
+      <c r="I28" t="n">
         <v>7.4</v>
       </c>
-      <c r="I28" t="n">
-        <v>8.4</v>
-      </c>
       <c r="J28" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="K28" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -7491,10 +7491,10 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-15 15:46:37</t>
+          <t>2026-07-15 17:58:21</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-15 15:46:37</t>
+          <t>2026-07-15 17:58:21</t>
         </is>
       </c>
     </row>
@@ -7990,7 +7990,7 @@
         <v>1.4</v>
       </c>
       <c r="M30" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N30" t="n">
         <v>3.25</v>
@@ -8113,10 +8113,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BB30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD30" t="n">
         <v>34</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-15 15:46:37</t>
+          <t>2026-07-15 17:58:21</t>
         </is>
       </c>
     </row>
@@ -8223,10 +8223,10 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="G31" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H31" t="n">
         <v>4.4</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-15 15:46:37</t>
+          <t>2026-07-15 17:58:21</t>
         </is>
       </c>
     </row>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-15 15:46:37</t>
+          <t>2026-07-15 17:58:21</t>
         </is>
       </c>
     </row>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-15 15:46:37</t>
+          <t>2026-07-15 17:58:21</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-17.xlsx
@@ -857,16 +857,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="G2" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="H2" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="I2" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="J2" t="n">
         <v>3.65</v>
@@ -887,10 +887,10 @@
         <v>1.28</v>
       </c>
       <c r="P2" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="R2" t="n">
         <v>1.43</v>
@@ -902,118 +902,118 @@
         <v>1.72</v>
       </c>
       <c r="U2" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V2" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="W2" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="X2" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="Y2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG2" t="n">
         <v>15.5</v>
       </c>
-      <c r="AA2" t="n">
-        <v>30</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>25</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>32</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>18</v>
-      </c>
       <c r="AH2" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AI2" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AJ2" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AK2" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL2" t="n">
         <v>48</v>
       </c>
-      <c r="AL2" t="n">
-        <v>60</v>
-      </c>
       <c r="AM2" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN2" t="n">
         <v>40</v>
       </c>
       <c r="AO2" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.9</v>
+        <v>14.5</v>
       </c>
       <c r="AQ2" t="n">
         <v>9.6</v>
       </c>
       <c r="AR2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.4</v>
+        <v>9.4</v>
       </c>
       <c r="AT2" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AU2" t="n">
         <v>7.6</v>
       </c>
       <c r="AV2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AX2" t="n">
         <v>9.800000000000001</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>21</v>
       </c>
       <c r="AY2" t="n">
         <v>13.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.7</v>
+        <v>10</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.9</v>
+        <v>12</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.8</v>
+        <v>10.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="BE2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.7</v>
+        <v>10.5</v>
       </c>
       <c r="BG2" t="n">
         <v>12</v>
@@ -1046,13 +1046,13 @@
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BT2" t="n">
         <v>5</v>
@@ -1061,7 +1061,7 @@
         <v>4</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BW2" t="n">
         <v>11</v>
@@ -1076,11 +1076,11 @@
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-15 17:58:21</t>
+          <t>2026-07-15 20:09:37</t>
         </is>
       </c>
     </row>
@@ -1111,49 +1111,49 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="G3" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="H3" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="I3" t="n">
         <v>3.95</v>
       </c>
       <c r="J3" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K3" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L3" t="n">
         <v>1.39</v>
       </c>
       <c r="M3" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="O3" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P3" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="R3" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S3" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="T3" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="U3" t="n">
         <v>2.18</v>
@@ -1162,13 +1162,13 @@
         <v>1.33</v>
       </c>
       <c r="W3" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="X3" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Y3" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Z3" t="n">
         <v>34</v>
@@ -1180,31 +1180,31 @@
         <v>12</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AE3" t="n">
         <v>55</v>
       </c>
       <c r="AF3" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AG3" t="n">
         <v>13</v>
       </c>
       <c r="AH3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI3" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ3" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AK3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL3" t="n">
         <v>42</v>
@@ -1213,128 +1213,128 @@
         <v>110</v>
       </c>
       <c r="AN3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO3" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AP3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BC3" t="n">
         <v>3.85</v>
       </c>
-      <c r="AQ3" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AR3" t="n">
+      <c r="BD3" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE3" t="n">
         <v>4.3</v>
       </c>
-      <c r="AS3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC3" t="n">
+      <c r="BF3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BG3" t="n">
         <v>4.1</v>
       </c>
-      <c r="BD3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BH3" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.15</v>
+        <v>2.84</v>
       </c>
       <c r="BJ3" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BN3" t="n">
         <v>5.1</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BP3" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BR3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BS3" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT3" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="BV3" t="n">
         <v>29</v>
       </c>
       <c r="BW3" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX3" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="CA3" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-15 17:58:21</t>
+          <t>2026-07-15 20:09:37</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
         <v>4.1</v>
       </c>
       <c r="G4" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="H4" t="n">
         <v>1.94</v>
@@ -1380,31 +1380,31 @@
         <v>3.45</v>
       </c>
       <c r="K4" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M4" t="n">
         <v>1.07</v>
       </c>
       <c r="N4" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O4" t="n">
         <v>1.33</v>
       </c>
       <c r="P4" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="R4" t="n">
         <v>1.33</v>
       </c>
       <c r="S4" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="T4" t="n">
         <v>1.83</v>
@@ -1422,34 +1422,34 @@
         <v>16</v>
       </c>
       <c r="Y4" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA4" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AB4" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AC4" t="n">
         <v>8.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AF4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AG4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH4" t="n">
         <v>22</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>23</v>
       </c>
       <c r="AI4" t="n">
         <v>44</v>
@@ -1458,7 +1458,7 @@
         <v>110</v>
       </c>
       <c r="AK4" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AL4" t="n">
         <v>75</v>
@@ -1470,125 +1470,125 @@
         <v>75</v>
       </c>
       <c r="AO4" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.6</v>
+        <v>12</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.9</v>
+        <v>7.8</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AS4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD4" t="n">
         <v>5.2</v>
       </c>
-      <c r="AT4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AY4" t="n">
+      <c r="BE4" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF4" t="n">
         <v>5.1</v>
       </c>
-      <c r="AZ4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>6</v>
-      </c>
       <c r="BG4" t="n">
-        <v>4.6</v>
+        <v>13</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BI4" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="BJ4" t="n">
         <v>10</v>
       </c>
       <c r="BK4" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>13.5</v>
+        <v>2.7</v>
       </c>
       <c r="BN4" t="n">
         <v>7.8</v>
       </c>
       <c r="BO4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BP4" t="n">
         <v>38</v>
       </c>
       <c r="BQ4" t="n">
-        <v>10.5</v>
+        <v>2.58</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>11.5</v>
+        <v>2.6</v>
       </c>
       <c r="BT4" t="n">
         <v>4.7</v>
       </c>
       <c r="BU4" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="BV4" t="n">
         <v>14.5</v>
       </c>
       <c r="BW4" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BX4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BY4" t="n">
-        <v>10</v>
+        <v>2.52</v>
       </c>
       <c r="BZ4" t="n">
         <v>26</v>
       </c>
       <c r="CA4" t="n">
-        <v>9.6</v>
+        <v>2.5</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-15 17:58:21</t>
+          <t>2026-07-15 20:09:37</t>
         </is>
       </c>
     </row>
@@ -1622,13 +1622,13 @@
         <v>4.2</v>
       </c>
       <c r="G5" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="H5" t="n">
         <v>1.81</v>
       </c>
       <c r="I5" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="J5" t="n">
         <v>3.95</v>
@@ -1652,7 +1652,7 @@
         <v>2.32</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-15 17:58:21</t>
+          <t>2026-07-15 20:09:37</t>
         </is>
       </c>
     </row>
@@ -1873,13 +1873,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="G6" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="H6" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="I6" t="n">
         <v>2.22</v>
@@ -1888,7 +1888,7 @@
         <v>3.1</v>
       </c>
       <c r="K6" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L6" t="n">
         <v>1.42</v>
@@ -1897,13 +1897,13 @@
         <v>1.1</v>
       </c>
       <c r="N6" t="n">
-        <v>2.58</v>
+        <v>2.86</v>
       </c>
       <c r="O6" t="n">
         <v>1.43</v>
       </c>
       <c r="P6" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q6" t="n">
         <v>2.28</v>
@@ -1912,7 +1912,7 @@
         <v>1.23</v>
       </c>
       <c r="S6" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="T6" t="n">
         <v>1.98</v>
@@ -1921,10 +1921,10 @@
         <v>1.83</v>
       </c>
       <c r="V6" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="W6" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="X6" t="n">
         <v>12.5</v>
@@ -1981,37 +1981,37 @@
         <v>27</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.25</v>
+        <v>7.6</v>
       </c>
       <c r="AQ6" t="n">
-        <v>2.94</v>
+        <v>5.6</v>
       </c>
       <c r="AR6" t="n">
-        <v>3.35</v>
+        <v>10</v>
       </c>
       <c r="AS6" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.4</v>
+        <v>10.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>2.98</v>
+        <v>5.7</v>
       </c>
       <c r="AV6" t="n">
-        <v>3.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW6" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AX6" t="n">
         <v>3.95</v>
       </c>
       <c r="AY6" t="n">
-        <v>3.65</v>
+        <v>15.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>3.75</v>
+        <v>18</v>
       </c>
       <c r="BA6" t="n">
         <v>4.1</v>
@@ -2032,7 +2032,7 @@
         <v>4.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.75</v>
+        <v>19</v>
       </c>
       <c r="BH6" t="n">
         <v>3.05</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-15 17:58:21</t>
+          <t>2026-07-15 20:09:37</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="G7" t="n">
         <v>4.3</v>
@@ -2136,37 +2136,37 @@
         <v>2.18</v>
       </c>
       <c r="I7" t="n">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="J7" t="n">
-        <v>2.72</v>
+        <v>2.92</v>
       </c>
       <c r="K7" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L7" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="M7" t="n">
         <v>1.12</v>
       </c>
       <c r="N7" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="O7" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="P7" t="n">
         <v>1.53</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="R7" t="n">
         <v>1.19</v>
       </c>
       <c r="S7" t="n">
-        <v>3.45</v>
+        <v>5.1</v>
       </c>
       <c r="T7" t="n">
         <v>2.06</v>
@@ -2175,43 +2175,43 @@
         <v>1.77</v>
       </c>
       <c r="V7" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="W7" t="n">
         <v>1.3</v>
       </c>
       <c r="X7" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y7" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="Z7" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AA7" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AB7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD7" t="n">
         <v>12.5</v>
       </c>
-      <c r="AC7" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>14</v>
-      </c>
       <c r="AE7" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AF7" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AG7" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AH7" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AI7" t="n">
         <v>70</v>
@@ -2232,67 +2232,67 @@
         <v>110</v>
       </c>
       <c r="AO7" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.45</v>
+        <v>6.8</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.15</v>
+        <v>6.2</v>
       </c>
       <c r="AR7" t="n">
-        <v>3.85</v>
+        <v>11</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.5</v>
+        <v>7.2</v>
       </c>
       <c r="AT7" t="n">
-        <v>3.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.15</v>
+        <v>6.2</v>
       </c>
       <c r="AV7" t="n">
-        <v>3.75</v>
+        <v>10</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX7" t="n">
-        <v>4.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY7" t="n">
-        <v>4</v>
+        <v>14.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4.3</v>
+        <v>6.6</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.7</v>
+        <v>8</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.9</v>
+        <v>8.4</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.8</v>
+        <v>8</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE7" t="n">
-        <v>5</v>
+        <v>8.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.9</v>
+        <v>8.4</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH7" t="n">
         <v>2.82</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="BJ7" t="n">
         <v>12</v>
@@ -2334,7 +2334,7 @@
         <v>21</v>
       </c>
       <c r="BW7" t="n">
-        <v>2.02</v>
+        <v>7.2</v>
       </c>
       <c r="BX7" t="n">
         <v>44</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-15 17:58:21</t>
+          <t>2026-07-15 20:09:37</t>
         </is>
       </c>
     </row>
@@ -2381,22 +2381,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="G8" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="H8" t="n">
         <v>6.2</v>
       </c>
       <c r="I8" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J8" t="n">
         <v>4.6</v>
       </c>
       <c r="K8" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="L8" t="n">
         <v>1.27</v>
@@ -2408,7 +2408,7 @@
         <v>4.5</v>
       </c>
       <c r="O8" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P8" t="n">
         <v>2.32</v>
@@ -2420,37 +2420,37 @@
         <v>1.49</v>
       </c>
       <c r="S8" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="T8" t="n">
         <v>1.77</v>
       </c>
       <c r="U8" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="V8" t="n">
         <v>1.15</v>
       </c>
       <c r="W8" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="X8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y8" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="Z8" t="n">
         <v>65</v>
       </c>
       <c r="AA8" t="n">
-        <v>200</v>
+        <v>260</v>
       </c>
       <c r="AB8" t="n">
         <v>10.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AD8" t="n">
         <v>27</v>
@@ -2459,58 +2459,58 @@
         <v>95</v>
       </c>
       <c r="AF8" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AG8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH8" t="n">
         <v>23</v>
       </c>
       <c r="AI8" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AJ8" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AK8" t="n">
         <v>16</v>
       </c>
       <c r="AL8" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AM8" t="n">
         <v>110</v>
       </c>
       <c r="AN8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO8" t="n">
         <v>100</v>
       </c>
       <c r="AP8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ8" t="n">
         <v>21</v>
       </c>
       <c r="AR8" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT8" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AU8" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AV8" t="n">
         <v>21</v>
       </c>
       <c r="AW8" t="n">
-        <v>55</v>
+        <v>8.4</v>
       </c>
       <c r="AX8" t="n">
         <v>8.6</v>
@@ -2519,10 +2519,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ8" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BB8" t="n">
         <v>12.5</v>
@@ -2534,10 +2534,10 @@
         <v>24</v>
       </c>
       <c r="BE8" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BF8" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BG8" t="n">
         <v>46</v>
@@ -2546,7 +2546,7 @@
         <v>4.3</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BJ8" t="n">
         <v>11</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-15 17:58:21</t>
+          <t>2026-07-15 20:09:37</t>
         </is>
       </c>
     </row>
@@ -2641,16 +2641,16 @@
         <v>1.46</v>
       </c>
       <c r="H9" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="I9" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J9" t="n">
         <v>5.4</v>
       </c>
       <c r="K9" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2665,25 +2665,25 @@
         <v>1.14</v>
       </c>
       <c r="P9" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="S9" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="T9" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="U9" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V9" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W9" t="n">
         <v>3.15</v>
@@ -2704,19 +2704,19 @@
         <v>16</v>
       </c>
       <c r="AC9" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AD9" t="n">
         <v>36</v>
       </c>
       <c r="AE9" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AF9" t="n">
         <v>13.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH9" t="n">
         <v>24</v>
@@ -2728,7 +2728,7 @@
         <v>15.5</v>
       </c>
       <c r="AK9" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AL9" t="n">
         <v>30</v>
@@ -2743,28 +2743,28 @@
         <v>85</v>
       </c>
       <c r="AP9" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="AQ9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AR9" t="n">
         <v>5.5</v>
       </c>
-      <c r="AR9" t="n">
-        <v>5.9</v>
-      </c>
       <c r="AS9" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AT9" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AV9" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="AX9" t="n">
         <v>10</v>
@@ -2776,31 +2776,31 @@
         <v>17.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="BB9" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BD9" t="n">
         <v>19.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="BF9" t="n">
         <v>3.55</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="BH9" t="n">
         <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="BJ9" t="n">
         <v>13.5</v>
@@ -2812,13 +2812,13 @@
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="BN9" t="n">
         <v>5.9</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="BP9" t="n">
         <v>11</v>
@@ -2833,7 +2833,7 @@
         <v>2.02</v>
       </c>
       <c r="BT9" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BU9" t="n">
         <v>1.93</v>
@@ -2842,7 +2842,7 @@
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-15 17:58:21</t>
+          <t>2026-07-15 20:09:37</t>
         </is>
       </c>
     </row>
@@ -2907,7 +2907,7 @@
         <v>4.4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
         <v>1.01</v>
@@ -2922,7 +2922,7 @@
         <v>2.94</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="R10" t="n">
         <v>1.79</v>
@@ -2934,7 +2934,7 @@
         <v>1.43</v>
       </c>
       <c r="U10" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="V10" t="n">
         <v>1.55</v>
@@ -2943,37 +2943,37 @@
         <v>1.58</v>
       </c>
       <c r="X10" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="Y10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Z10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA10" t="n">
         <v>46</v>
       </c>
       <c r="AB10" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AC10" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AD10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AE10" t="n">
         <v>28</v>
       </c>
       <c r="AF10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AG10" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI10" t="n">
         <v>30</v>
@@ -2985,10 +2985,10 @@
         <v>27</v>
       </c>
       <c r="AL10" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AM10" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AN10" t="n">
         <v>12.5</v>
@@ -2997,25 +2997,25 @@
         <v>13</v>
       </c>
       <c r="AP10" t="n">
-        <v>5.9</v>
+        <v>4.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AR10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS10" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="AT10" t="n">
         <v>17.5</v>
       </c>
       <c r="AU10" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV10" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AW10" t="n">
         <v>20</v>
@@ -3030,31 +3030,31 @@
         <v>12</v>
       </c>
       <c r="BA10" t="n">
-        <v>18.5</v>
+        <v>4.4</v>
       </c>
       <c r="BB10" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="BC10" t="n">
         <v>19.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>19</v>
+        <v>4.4</v>
       </c>
       <c r="BE10" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="BF10" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="BG10" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH10" t="n">
         <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="BJ10" t="n">
         <v>11</v>
@@ -3066,25 +3066,25 @@
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="BN10" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BO10" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BP10" t="n">
         <v>23</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="BR10" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BS10" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="BT10" t="n">
         <v>8.800000000000001</v>
@@ -3096,13 +3096,13 @@
         <v>23</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="BX10" t="n">
         <v>30</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-15 17:58:21</t>
+          <t>2026-07-15 20:09:37</t>
         </is>
       </c>
     </row>
@@ -3143,19 +3143,19 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="G11" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="H11" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J11" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="K11" t="n">
         <v>3.4</v>
@@ -3173,10 +3173,10 @@
         <v>1.42</v>
       </c>
       <c r="P11" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R11" t="n">
         <v>1.25</v>
@@ -3191,13 +3191,13 @@
         <v>1.92</v>
       </c>
       <c r="V11" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W11" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="X11" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y11" t="n">
         <v>11</v>
@@ -3209,10 +3209,10 @@
         <v>60</v>
       </c>
       <c r="AB11" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC11" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD11" t="n">
         <v>15</v>
@@ -3221,7 +3221,7 @@
         <v>44</v>
       </c>
       <c r="AF11" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AG11" t="n">
         <v>12.5</v>
@@ -3230,7 +3230,7 @@
         <v>21</v>
       </c>
       <c r="AI11" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ11" t="n">
         <v>42</v>
@@ -3239,7 +3239,7 @@
         <v>34</v>
       </c>
       <c r="AL11" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM11" t="n">
         <v>160</v>
@@ -3248,61 +3248,61 @@
         <v>34</v>
       </c>
       <c r="AO11" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AP11" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AQ11" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR11" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.4</v>
+        <v>42</v>
       </c>
       <c r="AT11" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU11" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV11" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="AX11" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY11" t="n">
         <v>10</v>
       </c>
       <c r="AZ11" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA11" t="n">
+        <v>42</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC11" t="n">
         <v>7.4</v>
       </c>
-      <c r="BB11" t="n">
+      <c r="BD11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BG11" t="n">
         <v>32</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>40</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>7.4</v>
       </c>
       <c r="BH11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-15 17:58:21</t>
+          <t>2026-07-15 20:09:37</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
         <v>7</v>
       </c>
       <c r="H12" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="I12" t="n">
         <v>1.76</v>
@@ -3412,13 +3412,13 @@
         <v>3.75</v>
       </c>
       <c r="K12" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L12" t="n">
-        <v>1.37</v>
+        <v>1.14</v>
       </c>
       <c r="M12" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N12" t="n">
         <v>3.45</v>
@@ -3427,7 +3427,7 @@
         <v>1.32</v>
       </c>
       <c r="P12" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="Q12" t="n">
         <v>1.94</v>
@@ -3436,7 +3436,7 @@
         <v>1.32</v>
       </c>
       <c r="S12" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="T12" t="n">
         <v>1.93</v>
@@ -3451,40 +3451,40 @@
         <v>1.16</v>
       </c>
       <c r="X12" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="Y12" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z12" t="n">
         <v>10.5</v>
       </c>
       <c r="AA12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AB12" t="n">
         <v>20</v>
       </c>
-      <c r="AB12" t="n">
-        <v>24</v>
-      </c>
       <c r="AC12" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD12" t="n">
         <v>10.5</v>
       </c>
-      <c r="AD12" t="n">
-        <v>12</v>
-      </c>
       <c r="AE12" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AF12" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AG12" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AH12" t="n">
         <v>24</v>
       </c>
       <c r="AI12" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AJ12" t="n">
         <v>220</v>
@@ -3502,7 +3502,7 @@
         <v>160</v>
       </c>
       <c r="AO12" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AP12" t="n">
         <v>12</v>
@@ -3529,7 +3529,7 @@
         <v>15.5</v>
       </c>
       <c r="AX12" t="n">
-        <v>4.7</v>
+        <v>7.4</v>
       </c>
       <c r="AY12" t="n">
         <v>20</v>
@@ -3538,22 +3538,22 @@
         <v>19</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.6</v>
+        <v>32</v>
       </c>
       <c r="BB12" t="n">
-        <v>5.1</v>
+        <v>8.4</v>
       </c>
       <c r="BC12" t="n">
-        <v>5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.9</v>
+        <v>8</v>
       </c>
       <c r="BE12" t="n">
-        <v>5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF12" t="n">
-        <v>5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG12" t="n">
         <v>8.199999999999999</v>
@@ -3562,65 +3562,65 @@
         <v>1000</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="BJ12" t="n">
         <v>15.5</v>
       </c>
       <c r="BK12" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="BN12" t="n">
         <v>13.5</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="BT12" t="n">
         <v>5.8</v>
       </c>
       <c r="BU12" t="n">
-        <v>3.15</v>
+        <v>1.33</v>
       </c>
       <c r="BV12" t="n">
         <v>16</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="BX12" t="n">
         <v>40</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="BZ12" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="CA12" t="n">
         <v>1.73</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-15 17:58:21</t>
+          <t>2026-07-15 20:09:37</t>
         </is>
       </c>
     </row>
@@ -3657,13 +3657,13 @@
         <v>1.38</v>
       </c>
       <c r="H13" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="J13" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="K13" t="n">
         <v>7.6</v>
@@ -3681,7 +3681,7 @@
         <v>1.1</v>
       </c>
       <c r="P13" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="Q13" t="n">
         <v>1.32</v>
@@ -3699,10 +3699,10 @@
         <v>2.26</v>
       </c>
       <c r="V13" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="W13" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="X13" t="n">
         <v>55</v>
@@ -3720,7 +3720,7 @@
         <v>19.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AD13" t="n">
         <v>42</v>
@@ -3738,7 +3738,7 @@
         <v>27</v>
       </c>
       <c r="AI13" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AJ13" t="n">
         <v>15</v>
@@ -3750,7 +3750,7 @@
         <v>30</v>
       </c>
       <c r="AM13" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AN13" t="n">
         <v>3.5</v>
@@ -3759,58 +3759,58 @@
         <v>90</v>
       </c>
       <c r="AP13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BA13" t="n">
         <v>5.9</v>
       </c>
-      <c r="AQ13" t="n">
+      <c r="BB13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE13" t="n">
         <v>5.9</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>6</v>
       </c>
       <c r="BF13" t="n">
         <v>3</v>
       </c>
       <c r="BG13" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BH13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-15 17:58:21</t>
+          <t>2026-07-15 20:09:37</t>
         </is>
       </c>
     </row>
@@ -3914,13 +3914,13 @@
         <v>1.46</v>
       </c>
       <c r="I14" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="J14" t="n">
         <v>3.7</v>
       </c>
       <c r="K14" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
@@ -3929,7 +3929,7 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>4.2</v>
+        <v>2.16</v>
       </c>
       <c r="O14" t="n">
         <v>1.17</v>
@@ -3941,10 +3941,10 @@
         <v>1.48</v>
       </c>
       <c r="R14" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="S14" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="T14" t="n">
         <v>1.01</v>
@@ -3953,7 +3953,7 @@
         <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="W14" t="n">
         <v>1.11</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-15 17:58:21</t>
+          <t>2026-07-15 20:09:37</t>
         </is>
       </c>
     </row>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="G15" t="n">
         <v>2.04</v>
@@ -4195,13 +4195,13 @@
         <v>1.71</v>
       </c>
       <c r="R15" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S15" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="T15" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U15" t="n">
         <v>2.36</v>
@@ -4213,16 +4213,16 @@
         <v>1.96</v>
       </c>
       <c r="X15" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="Y15" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="Z15" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AA15" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AB15" t="n">
         <v>12.5</v>
@@ -4231,7 +4231,7 @@
         <v>9.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AE15" t="n">
         <v>50</v>
@@ -4255,7 +4255,7 @@
         <v>21</v>
       </c>
       <c r="AL15" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AM15" t="n">
         <v>85</v>
@@ -4264,22 +4264,22 @@
         <v>11.5</v>
       </c>
       <c r="AO15" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AP15" t="n">
-        <v>6.2</v>
+        <v>17.5</v>
       </c>
       <c r="AQ15" t="n">
         <v>15</v>
       </c>
       <c r="AR15" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AS15" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AT15" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU15" t="n">
         <v>8.199999999999999</v>
@@ -4288,7 +4288,7 @@
         <v>13.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AX15" t="n">
         <v>11.5</v>
@@ -4300,61 +4300,61 @@
         <v>14</v>
       </c>
       <c r="BA15" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="BB15" t="n">
         <v>19.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BD15" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="BE15" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BF15" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG15" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BH15" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BI15" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="BJ15" t="n">
         <v>13</v>
       </c>
       <c r="BK15" t="n">
-        <v>2.4</v>
+        <v>1.67</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>2.94</v>
+        <v>1.92</v>
       </c>
       <c r="BN15" t="n">
         <v>7</v>
       </c>
       <c r="BO15" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="BP15" t="n">
         <v>19</v>
       </c>
       <c r="BQ15" t="n">
-        <v>2.54</v>
+        <v>1.74</v>
       </c>
       <c r="BR15" t="n">
         <v>34</v>
       </c>
       <c r="BS15" t="n">
-        <v>2.7</v>
+        <v>1.82</v>
       </c>
       <c r="BT15" t="n">
         <v>10.5</v>
@@ -4366,23 +4366,23 @@
         <v>44</v>
       </c>
       <c r="BW15" t="n">
-        <v>2.76</v>
+        <v>1.84</v>
       </c>
       <c r="BX15" t="n">
         <v>50</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.78</v>
+        <v>1.85</v>
       </c>
       <c r="BZ15" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="CA15" t="n">
-        <v>2.66</v>
+        <v>1.79</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-15 17:58:21</t>
+          <t>2026-07-15 20:09:37</t>
         </is>
       </c>
     </row>
@@ -4416,16 +4416,16 @@
         <v>1.86</v>
       </c>
       <c r="G16" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="H16" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I16" t="n">
         <v>4.6</v>
       </c>
       <c r="J16" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K16" t="n">
         <v>4.3</v>
@@ -4437,7 +4437,7 @@
         <v>1.05</v>
       </c>
       <c r="N16" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O16" t="n">
         <v>1.23</v>
@@ -4458,16 +4458,16 @@
         <v>1.66</v>
       </c>
       <c r="U16" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V16" t="n">
         <v>1.28</v>
       </c>
       <c r="W16" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y16" t="n">
         <v>23</v>
@@ -4488,7 +4488,7 @@
         <v>20</v>
       </c>
       <c r="AE16" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AF16" t="n">
         <v>15.5</v>
@@ -4497,7 +4497,7 @@
         <v>12</v>
       </c>
       <c r="AH16" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI16" t="n">
         <v>60</v>
@@ -4506,7 +4506,7 @@
         <v>25</v>
       </c>
       <c r="AK16" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AL16" t="n">
         <v>34</v>
@@ -4515,7 +4515,7 @@
         <v>85</v>
       </c>
       <c r="AN16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO16" t="n">
         <v>48</v>
@@ -4524,37 +4524,37 @@
         <v>17.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR16" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AS16" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW16" t="n">
         <v>5</v>
       </c>
-      <c r="AT16" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>4.8</v>
-      </c>
       <c r="AX16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY16" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ16" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BB16" t="n">
         <v>18</v>
@@ -4563,25 +4563,25 @@
         <v>15</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BE16" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BF16" t="n">
         <v>7.6</v>
       </c>
       <c r="BG16" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BH16" t="n">
         <v>1000</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.84</v>
+        <v>2</v>
       </c>
       <c r="BJ16" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BK16" t="n">
         <v>1.73</v>
@@ -4596,7 +4596,7 @@
         <v>6.4</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BP16" t="n">
         <v>17.5</v>
@@ -4617,26 +4617,26 @@
         <v>5.1</v>
       </c>
       <c r="BV16" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="BX16" t="n">
         <v>50</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="BZ16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-15 17:58:21</t>
+          <t>2026-07-15 20:09:37</t>
         </is>
       </c>
     </row>
@@ -4667,25 +4667,25 @@
         </is>
       </c>
       <c r="F17" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="G17" t="n">
         <v>1.2</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1.21</v>
       </c>
       <c r="H17" t="n">
         <v>18</v>
       </c>
       <c r="I17" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="J17" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="K17" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="M17" t="n">
         <v>1.01</v>
@@ -4706,10 +4706,10 @@
         <v>2.14</v>
       </c>
       <c r="S17" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="T17" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U17" t="n">
         <v>2</v>
@@ -4721,7 +4721,7 @@
         <v>1.01</v>
       </c>
       <c r="X17" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="Y17" t="n">
         <v>90</v>
@@ -4769,13 +4769,13 @@
         <v>150</v>
       </c>
       <c r="AN17" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="AO17" t="n">
         <v>240</v>
       </c>
       <c r="AP17" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AQ17" t="n">
         <v>6</v>
@@ -4790,7 +4790,7 @@
         <v>11.5</v>
       </c>
       <c r="AU17" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AV17" t="n">
         <v>5.9</v>
@@ -4799,7 +4799,7 @@
         <v>6.2</v>
       </c>
       <c r="AX17" t="n">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY17" t="n">
         <v>10</v>
@@ -4811,7 +4811,7 @@
         <v>6.2</v>
       </c>
       <c r="BB17" t="n">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BC17" t="n">
         <v>10</v>
@@ -4850,13 +4850,13 @@
         <v>4.3</v>
       </c>
       <c r="BO17" t="n">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="BP17" t="n">
         <v>6.2</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="BR17" t="n">
         <v>18</v>
@@ -4877,7 +4877,7 @@
         <v>13.5</v>
       </c>
       <c r="BX17" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BY17" t="n">
         <v>13</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-15 17:58:21</t>
+          <t>2026-07-15 20:09:37</t>
         </is>
       </c>
     </row>
@@ -4942,7 +4942,7 @@
         <v>1.11</v>
       </c>
       <c r="M18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N18" t="n">
         <v>4.1</v>
@@ -4951,7 +4951,7 @@
         <v>1.26</v>
       </c>
       <c r="P18" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q18" t="n">
         <v>1.79</v>
@@ -4963,13 +4963,13 @@
         <v>2.96</v>
       </c>
       <c r="T18" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="U18" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V18" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W18" t="n">
         <v>1.8</v>
@@ -4981,7 +4981,7 @@
         <v>16.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AA18" t="n">
         <v>75</v>
@@ -5017,64 +5017,64 @@
         <v>22</v>
       </c>
       <c r="AL18" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AM18" t="n">
         <v>85</v>
       </c>
       <c r="AN18" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AO18" t="n">
         <v>42</v>
       </c>
       <c r="AP18" t="n">
-        <v>14.5</v>
+        <v>6</v>
       </c>
       <c r="AQ18" t="n">
-        <v>13.5</v>
+        <v>5.9</v>
       </c>
       <c r="AR18" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AT18" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AU18" t="n">
-        <v>7.4</v>
+        <v>4.5</v>
       </c>
       <c r="AV18" t="n">
-        <v>13</v>
+        <v>5.9</v>
       </c>
       <c r="AW18" t="n">
         <v>28</v>
       </c>
       <c r="AX18" t="n">
-        <v>12</v>
+        <v>5.7</v>
       </c>
       <c r="AY18" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ18" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="BA18" t="n">
         <v>30</v>
       </c>
       <c r="BB18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD18" t="n">
         <v>21</v>
       </c>
-      <c r="BC18" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>23</v>
-      </c>
       <c r="BE18" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF18" t="n">
         <v>9.800000000000001</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-15 17:58:21</t>
+          <t>2026-07-15 20:09:37</t>
         </is>
       </c>
     </row>
@@ -5181,10 +5181,10 @@
         <v>2.48</v>
       </c>
       <c r="H19" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I19" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J19" t="n">
         <v>3.2</v>
@@ -5199,19 +5199,19 @@
         <v>1.09</v>
       </c>
       <c r="N19" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O19" t="n">
         <v>1.4</v>
       </c>
       <c r="P19" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="Q19" t="n">
         <v>2.2</v>
       </c>
       <c r="R19" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S19" t="n">
         <v>4.1</v>
@@ -5310,7 +5310,7 @@
         <v>11</v>
       </c>
       <c r="AY19" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ19" t="n">
         <v>14.5</v>
@@ -5340,7 +5340,7 @@
         <v>3.1</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.52</v>
+        <v>2.72</v>
       </c>
       <c r="BJ19" t="n">
         <v>10.5</v>
@@ -5358,7 +5358,7 @@
         <v>5.2</v>
       </c>
       <c r="BO19" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BP19" t="n">
         <v>19</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-15 17:58:21</t>
+          <t>2026-07-15 20:09:37</t>
         </is>
       </c>
     </row>
@@ -5447,7 +5447,7 @@
         <v>10</v>
       </c>
       <c r="L20" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="M20" t="n">
         <v>1.03</v>
@@ -5480,7 +5480,7 @@
         <v>1.03</v>
       </c>
       <c r="W20" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="X20" t="n">
         <v>32</v>
@@ -5495,10 +5495,10 @@
         <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC20" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AD20" t="n">
         <v>130</v>
@@ -5513,19 +5513,19 @@
         <v>15</v>
       </c>
       <c r="AH20" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AI20" t="n">
         <v>590</v>
       </c>
       <c r="AJ20" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AK20" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AL20" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AM20" t="n">
         <v>550</v>
@@ -5585,74 +5585,74 @@
         <v>1.01</v>
       </c>
       <c r="BF20" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="BG20" t="n">
         <v>1.01</v>
       </c>
       <c r="BH20" t="n">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="BI20" t="n">
-        <v>3.2</v>
+        <v>2.14</v>
       </c>
       <c r="BJ20" t="n">
         <v>25</v>
       </c>
       <c r="BK20" t="n">
-        <v>2.98</v>
+        <v>1.98</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>3.35</v>
+        <v>2.14</v>
       </c>
       <c r="BN20" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BO20" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="BP20" t="n">
         <v>7.8</v>
       </c>
       <c r="BQ20" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BR20" t="n">
         <v>40</v>
       </c>
       <c r="BS20" t="n">
-        <v>3.1</v>
+        <v>2.04</v>
       </c>
       <c r="BT20" t="n">
         <v>34</v>
       </c>
       <c r="BU20" t="n">
-        <v>3.05</v>
+        <v>2.02</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>3.35</v>
+        <v>2.14</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>3.35</v>
+        <v>2.14</v>
       </c>
       <c r="BZ20" t="n">
         <v>11.5</v>
       </c>
       <c r="CA20" t="n">
-        <v>2.62</v>
+        <v>1.81</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-15 17:58:21</t>
+          <t>2026-07-15 20:09:37</t>
         </is>
       </c>
     </row>
@@ -5686,19 +5686,19 @@
         <v>1.28</v>
       </c>
       <c r="G21" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="H21" t="n">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="I21" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J21" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="K21" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="L21" t="n">
         <v>1.01</v>
@@ -5707,13 +5707,13 @@
         <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="O21" t="n">
         <v>1.16</v>
       </c>
       <c r="P21" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="Q21" t="n">
         <v>1.44</v>
@@ -5731,10 +5731,10 @@
         <v>1.01</v>
       </c>
       <c r="V21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W21" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="X21" t="n">
         <v>1000</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-15 17:58:21</t>
+          <t>2026-07-15 20:09:37</t>
         </is>
       </c>
     </row>
@@ -5946,19 +5946,19 @@
         <v>5.6</v>
       </c>
       <c r="I22" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J22" t="n">
         <v>4.1</v>
       </c>
       <c r="K22" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="L22" t="n">
         <v>1.33</v>
       </c>
       <c r="M22" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N22" t="n">
         <v>3.7</v>
@@ -5970,10 +5970,10 @@
         <v>2</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="R22" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S22" t="n">
         <v>3.25</v>
@@ -5982,10 +5982,10 @@
         <v>1.91</v>
       </c>
       <c r="U22" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="V22" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W22" t="n">
         <v>2.4</v>
@@ -5997,7 +5997,7 @@
         <v>20</v>
       </c>
       <c r="Z22" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AA22" t="n">
         <v>190</v>
@@ -6024,7 +6024,7 @@
         <v>24</v>
       </c>
       <c r="AI22" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AJ22" t="n">
         <v>17</v>
@@ -6039,7 +6039,7 @@
         <v>160</v>
       </c>
       <c r="AN22" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AO22" t="n">
         <v>130</v>
@@ -6051,10 +6051,10 @@
         <v>16</v>
       </c>
       <c r="AR22" t="n">
-        <v>7.4</v>
+        <v>36</v>
       </c>
       <c r="AS22" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT22" t="n">
         <v>6.8</v>
@@ -6066,7 +6066,7 @@
         <v>19.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AX22" t="n">
         <v>8.199999999999999</v>
@@ -6078,7 +6078,7 @@
         <v>19.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB22" t="n">
         <v>13.5</v>
@@ -6087,28 +6087,28 @@
         <v>15</v>
       </c>
       <c r="BD22" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BE22" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BF22" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BG22" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BH22" t="n">
         <v>3.6</v>
       </c>
       <c r="BI22" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="BJ22" t="n">
         <v>11</v>
       </c>
       <c r="BK22" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
@@ -6126,7 +6126,7 @@
         <v>11.5</v>
       </c>
       <c r="BQ22" t="n">
-        <v>5.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR22" t="n">
         <v>28</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-15 17:58:21</t>
+          <t>2026-07-15 20:09:37</t>
         </is>
       </c>
     </row>
@@ -6191,22 +6191,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="G23" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H23" t="n">
         <v>3.55</v>
       </c>
       <c r="I23" t="n">
+        <v>4</v>
+      </c>
+      <c r="J23" t="n">
         <v>3.9</v>
       </c>
-      <c r="J23" t="n">
-        <v>4</v>
-      </c>
       <c r="K23" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
@@ -6215,76 +6215,76 @@
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="O23" t="n">
         <v>1.17</v>
       </c>
       <c r="P23" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="Q23" t="n">
         <v>1.5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="S23" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="T23" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="U23" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="V23" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W23" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="X23" t="n">
         <v>32</v>
       </c>
       <c r="Y23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Z23" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AA23" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AB23" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AC23" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AF23" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AG23" t="n">
         <v>13</v>
       </c>
       <c r="AH23" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AI23" t="n">
         <v>42</v>
       </c>
       <c r="AJ23" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL23" t="n">
         <v>30</v>
@@ -6293,10 +6293,10 @@
         <v>65</v>
       </c>
       <c r="AN23" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AO23" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AP23" t="n">
         <v>4.7</v>
@@ -6311,7 +6311,7 @@
         <v>5.1</v>
       </c>
       <c r="AT23" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AU23" t="n">
         <v>3.8</v>
@@ -6320,34 +6320,34 @@
         <v>4.2</v>
       </c>
       <c r="AW23" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AX23" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AY23" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AZ23" t="n">
         <v>4.2</v>
       </c>
       <c r="BA23" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BB23" t="n">
         <v>4.6</v>
       </c>
       <c r="BC23" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BE23" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BF23" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="BG23" t="n">
         <v>4.6</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-15 17:58:21</t>
+          <t>2026-07-15 20:09:37</t>
         </is>
       </c>
     </row>
@@ -6445,10 +6445,10 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.04</v>
+        <v>1.37</v>
       </c>
       <c r="G24" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="H24" t="n">
         <v>1.04</v>
@@ -6457,19 +6457,19 @@
         <v>1000</v>
       </c>
       <c r="J24" t="n">
-        <v>4.3</v>
+        <v>1.02</v>
       </c>
       <c r="K24" t="n">
         <v>1000</v>
       </c>
       <c r="L24" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M24" t="n">
         <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>2.02</v>
+        <v>3.45</v>
       </c>
       <c r="O24" t="n">
         <v>1.25</v>
@@ -6481,10 +6481,10 @@
         <v>1.74</v>
       </c>
       <c r="R24" t="n">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="S24" t="n">
-        <v>1.74</v>
+        <v>2.62</v>
       </c>
       <c r="T24" t="n">
         <v>1.01</v>
@@ -6493,10 +6493,10 @@
         <v>1.01</v>
       </c>
       <c r="V24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W24" t="n">
-        <v>2.84</v>
+        <v>2.72</v>
       </c>
       <c r="X24" t="n">
         <v>1000</v>
@@ -6553,52 +6553,52 @@
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AQ24" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR24" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AS24" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AT24" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU24" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV24" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AW24" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AX24" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY24" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ24" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA24" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BB24" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BC24" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD24" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BE24" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BF24" t="n">
         <v>1.01</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-15 17:58:21</t>
+          <t>2026-07-15 20:09:37</t>
         </is>
       </c>
     </row>
@@ -6699,230 +6699,230 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="P25" t="n">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BG25" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BH25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-15 17:58:21</t>
+          <t>2026-07-15 20:09:37</t>
         </is>
       </c>
     </row>
@@ -6953,230 +6953,230 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="P26" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AR26" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AS26" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AU26" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AV26" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AW26" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AX26" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AY26" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BA26" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BG26" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BH26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-15 17:58:21</t>
+          <t>2026-07-15 20:09:37</t>
         </is>
       </c>
     </row>
@@ -7207,230 +7207,230 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="P27" t="n">
         <v>1.25</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BG27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BH27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-15 17:58:21</t>
+          <t>2026-07-15 20:09:37</t>
         </is>
       </c>
     </row>
@@ -7461,230 +7461,230 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="G28" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="H28" t="n">
         <v>7</v>
       </c>
       <c r="I28" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="J28" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K28" t="n">
         <v>5.1</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="P28" t="n">
         <v>2.42</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AO28" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BG28" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BH28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ28" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BK28" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BL28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM28" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN28" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BO28" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="BP28" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BQ28" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BR28" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BS28" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BT28" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BU28" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BV28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW28" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BX28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY28" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BZ28" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="CA28" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-15 17:58:21</t>
+          <t>2026-07-15 20:09:37</t>
         </is>
       </c>
     </row>
@@ -7715,16 +7715,16 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="G29" t="n">
-        <v>1.75</v>
+        <v>1000</v>
       </c>
       <c r="H29" t="n">
-        <v>2.38</v>
+        <v>1.04</v>
       </c>
       <c r="I29" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="J29" t="n">
         <v>4</v>
@@ -7733,16 +7733,16 @@
         <v>1000</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="P29" t="n">
         <v>1.86</v>
@@ -7751,194 +7751,194 @@
         <v>1.9</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH29" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BI29" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BJ29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-15 17:58:21</t>
+          <t>2026-07-15 20:09:37</t>
         </is>
       </c>
     </row>
@@ -7972,7 +7972,7 @@
         <v>2.08</v>
       </c>
       <c r="G30" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H30" t="n">
         <v>4</v>
@@ -7981,7 +7981,7 @@
         <v>4.6</v>
       </c>
       <c r="J30" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K30" t="n">
         <v>3.65</v>
@@ -7999,7 +7999,7 @@
         <v>1.38</v>
       </c>
       <c r="P30" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="Q30" t="n">
         <v>2.08</v>
@@ -8017,16 +8017,16 @@
         <v>1.92</v>
       </c>
       <c r="V30" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W30" t="n">
         <v>1.87</v>
       </c>
       <c r="X30" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y30" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z30" t="n">
         <v>32</v>
@@ -8038,7 +8038,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AC30" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AD30" t="n">
         <v>18.5</v>
@@ -8050,7 +8050,7 @@
         <v>12.5</v>
       </c>
       <c r="AG30" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH30" t="n">
         <v>22</v>
@@ -8062,31 +8062,31 @@
         <v>26</v>
       </c>
       <c r="AK30" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL30" t="n">
         <v>44</v>
       </c>
       <c r="AM30" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AN30" t="n">
         <v>19</v>
       </c>
       <c r="AO30" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AP30" t="n">
         <v>10</v>
       </c>
       <c r="AQ30" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AR30" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AS30" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AT30" t="n">
         <v>7.2</v>
@@ -8095,10 +8095,10 @@
         <v>6.8</v>
       </c>
       <c r="AV30" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX30" t="n">
         <v>10</v>
@@ -8110,25 +8110,25 @@
         <v>17</v>
       </c>
       <c r="BA30" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB30" t="n">
         <v>21</v>
       </c>
       <c r="BC30" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD30" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BE30" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF30" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG30" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH30" t="n">
         <v>3.25</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-15 17:58:21</t>
+          <t>2026-07-15 20:09:37</t>
         </is>
       </c>
     </row>
@@ -8223,10 +8223,10 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="G31" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H31" t="n">
         <v>4.4</v>
@@ -8235,10 +8235,10 @@
         <v>4.6</v>
       </c>
       <c r="J31" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K31" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -8253,10 +8253,10 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-15 17:58:21</t>
+          <t>2026-07-15 20:09:37</t>
         </is>
       </c>
     </row>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-15 17:58:21</t>
+          <t>2026-07-15 20:09:37</t>
         </is>
       </c>
     </row>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-15 17:58:21</t>
+          <t>2026-07-15 20:09:37</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-17.xlsx
@@ -857,55 +857,55 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="G2" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="H2" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="I2" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="J2" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="K2" t="n">
         <v>3.85</v>
       </c>
       <c r="L2" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M2" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="O2" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="P2" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="R2" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="S2" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="T2" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="U2" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="V2" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="W2" t="n">
         <v>1.34</v>
@@ -914,94 +914,94 @@
         <v>17</v>
       </c>
       <c r="Y2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z2" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AA2" t="n">
         <v>26</v>
       </c>
       <c r="AB2" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD2" t="n">
         <v>11</v>
       </c>
       <c r="AE2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF2" t="n">
         <v>29</v>
       </c>
       <c r="AG2" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AH2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI2" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AJ2" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AK2" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AL2" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AM2" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AN2" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AO2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP2" t="n">
         <v>13.5</v>
       </c>
-      <c r="AP2" t="n">
-        <v>14.5</v>
-      </c>
       <c r="AQ2" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AR2" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AS2" t="n">
         <v>9.4</v>
       </c>
       <c r="AT2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV2" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AW2" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AX2" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AY2" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AZ2" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA2" t="n">
         <v>10</v>
       </c>
       <c r="BB2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BC2" t="n">
         <v>10.5</v>
@@ -1010,22 +1010,22 @@
         <v>11</v>
       </c>
       <c r="BE2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BG2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="BI2" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="BJ2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BK2" t="n">
         <v>7.2</v>
@@ -1046,22 +1046,22 @@
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BT2" t="n">
         <v>5</v>
       </c>
       <c r="BU2" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BV2" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BW2" t="n">
         <v>11</v>
@@ -1076,11 +1076,11 @@
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-15 20:09:37</t>
+          <t>2026-07-15 22:20:35</t>
         </is>
       </c>
     </row>
@@ -1114,10 +1114,10 @@
         <v>2.08</v>
       </c>
       <c r="G3" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="H3" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I3" t="n">
         <v>3.95</v>
@@ -1141,10 +1141,10 @@
         <v>1.3</v>
       </c>
       <c r="P3" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="R3" t="n">
         <v>1.38</v>
@@ -1153,16 +1153,16 @@
         <v>3.25</v>
       </c>
       <c r="T3" t="n">
-        <v>1.74</v>
+        <v>1.34</v>
       </c>
       <c r="U3" t="n">
         <v>2.18</v>
       </c>
       <c r="V3" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W3" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="X3" t="n">
         <v>18</v>
@@ -1180,7 +1180,7 @@
         <v>12</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
         <v>19</v>
@@ -1219,122 +1219,122 @@
         <v>50</v>
       </c>
       <c r="AP3" t="n">
-        <v>13</v>
+        <v>2.64</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3.6</v>
+        <v>2.64</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.4</v>
+        <v>2.82</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.2</v>
+        <v>2.98</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.25</v>
+        <v>2.46</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.2</v>
+        <v>3.05</v>
       </c>
       <c r="AV3" t="n">
-        <v>13.5</v>
+        <v>2.66</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.1</v>
+        <v>2.92</v>
       </c>
       <c r="AX3" t="n">
-        <v>3.55</v>
+        <v>2.6</v>
       </c>
       <c r="AY3" t="n">
-        <v>8</v>
+        <v>2.48</v>
       </c>
       <c r="AZ3" t="n">
-        <v>3.7</v>
+        <v>2.68</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.2</v>
+        <v>2.94</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.3</v>
+        <v>2.82</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.85</v>
+        <v>2.78</v>
       </c>
       <c r="BD3" t="n">
-        <v>4</v>
+        <v>2.88</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.6</v>
+        <v>2.66</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.1</v>
+        <v>2.9</v>
       </c>
       <c r="BH3" t="n">
         <v>3.5</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="BJ3" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BN3" t="n">
         <v>5.1</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BP3" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BR3" t="n">
         <v>29</v>
       </c>
       <c r="BS3" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT3" t="n">
         <v>7</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BV3" t="n">
         <v>29</v>
       </c>
       <c r="BW3" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BX3" t="n">
         <v>40</v>
       </c>
       <c r="BY3" t="n">
-        <v>10.5</v>
+        <v>3.5</v>
       </c>
       <c r="BZ3" t="n">
         <v>25</v>
       </c>
       <c r="CA3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-15 20:09:37</t>
+          <t>2026-07-15 22:20:35</t>
         </is>
       </c>
     </row>
@@ -1473,19 +1473,19 @@
         <v>17.5</v>
       </c>
       <c r="AP4" t="n">
-        <v>12</v>
+        <v>4.1</v>
       </c>
       <c r="AQ4" t="n">
         <v>7.8</v>
       </c>
       <c r="AR4" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AS4" t="n">
-        <v>20</v>
+        <v>4.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>13</v>
+        <v>4.2</v>
       </c>
       <c r="AU4" t="n">
         <v>6.4</v>
@@ -1494,28 +1494,28 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AW4" t="n">
-        <v>19</v>
+        <v>4.5</v>
       </c>
       <c r="AX4" t="n">
         <v>4.8</v>
       </c>
       <c r="AY4" t="n">
-        <v>15</v>
+        <v>4.3</v>
       </c>
       <c r="AZ4" t="n">
-        <v>16.5</v>
+        <v>4.4</v>
       </c>
       <c r="BA4" t="n">
         <v>4.9</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BC4" t="n">
         <v>5.1</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BE4" t="n">
         <v>5.3</v>
@@ -1524,71 +1524,71 @@
         <v>5.1</v>
       </c>
       <c r="BG4" t="n">
-        <v>13</v>
+        <v>4.2</v>
       </c>
       <c r="BH4" t="n">
         <v>3.4</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BJ4" t="n">
         <v>10</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="BN4" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BO4" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BP4" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="BT4" t="n">
         <v>4.7</v>
       </c>
       <c r="BU4" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BV4" t="n">
         <v>14.5</v>
       </c>
       <c r="BW4" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BX4" t="n">
         <v>29</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="BZ4" t="n">
         <v>26</v>
       </c>
       <c r="CA4" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-15 20:09:37</t>
+          <t>2026-07-15 22:20:35</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="G5" t="n">
         <v>4.9</v>
@@ -1631,7 +1631,7 @@
         <v>1.91</v>
       </c>
       <c r="J5" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K5" t="n">
         <v>4.2</v>
@@ -1652,7 +1652,7 @@
         <v>2.32</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-15 20:09:37</t>
+          <t>2026-07-15 22:20:35</t>
         </is>
       </c>
     </row>
@@ -1987,13 +1987,13 @@
         <v>5.6</v>
       </c>
       <c r="AR6" t="n">
-        <v>10</v>
+        <v>3.35</v>
       </c>
       <c r="AS6" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AT6" t="n">
-        <v>10.5</v>
+        <v>3.4</v>
       </c>
       <c r="AU6" t="n">
         <v>5.7</v>
@@ -2002,16 +2002,16 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW6" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AX6" t="n">
         <v>3.95</v>
       </c>
       <c r="AY6" t="n">
-        <v>15.5</v>
+        <v>3.65</v>
       </c>
       <c r="AZ6" t="n">
-        <v>18</v>
+        <v>3.75</v>
       </c>
       <c r="BA6" t="n">
         <v>4.1</v>
@@ -2032,7 +2032,7 @@
         <v>4.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>19</v>
+        <v>3.75</v>
       </c>
       <c r="BH6" t="n">
         <v>3.05</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-15 20:09:37</t>
+          <t>2026-07-15 22:20:35</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2133,7 @@
         <v>4.3</v>
       </c>
       <c r="H7" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="I7" t="n">
         <v>2.48</v>
@@ -2241,10 +2241,10 @@
         <v>6.2</v>
       </c>
       <c r="AR7" t="n">
-        <v>11</v>
+        <v>5.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>7.2</v>
+        <v>22</v>
       </c>
       <c r="AT7" t="n">
         <v>9.199999999999999</v>
@@ -2256,13 +2256,13 @@
         <v>10</v>
       </c>
       <c r="AW7" t="n">
-        <v>9.199999999999999</v>
+        <v>21</v>
       </c>
       <c r="AX7" t="n">
-        <v>9.199999999999999</v>
+        <v>17.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>14.5</v>
+        <v>6</v>
       </c>
       <c r="AZ7" t="n">
         <v>6.6</v>
@@ -2286,7 +2286,7 @@
         <v>8.4</v>
       </c>
       <c r="BG7" t="n">
-        <v>9.199999999999999</v>
+        <v>22</v>
       </c>
       <c r="BH7" t="n">
         <v>2.82</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-15 20:09:37</t>
+          <t>2026-07-15 22:20:35</t>
         </is>
       </c>
     </row>
@@ -2381,85 +2381,85 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="G8" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="H8" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="I8" t="n">
         <v>7.6</v>
       </c>
       <c r="J8" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="K8" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="L8" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="O8" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P8" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="R8" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="S8" t="n">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="T8" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="U8" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V8" t="n">
         <v>1.15</v>
       </c>
       <c r="W8" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="X8" t="n">
         <v>23</v>
       </c>
       <c r="Y8" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="Z8" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AA8" t="n">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
         <v>10.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE8" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG8" t="n">
         <v>10</v>
@@ -2468,55 +2468,55 @@
         <v>23</v>
       </c>
       <c r="AI8" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AJ8" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="AK8" t="n">
         <v>16</v>
       </c>
       <c r="AL8" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AM8" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AO8" t="n">
         <v>100</v>
       </c>
       <c r="AP8" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AR8" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AS8" t="n">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="AT8" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AU8" t="n">
         <v>10</v>
       </c>
       <c r="AV8" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AW8" t="n">
-        <v>8.4</v>
+        <v>36</v>
       </c>
       <c r="AX8" t="n">
         <v>8.6</v>
       </c>
       <c r="AY8" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ8" t="n">
         <v>18.5</v>
@@ -2531,19 +2531,19 @@
         <v>13</v>
       </c>
       <c r="BD8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BE8" t="n">
-        <v>8.6</v>
+        <v>38</v>
       </c>
       <c r="BF8" t="n">
         <v>5.8</v>
       </c>
       <c r="BG8" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BH8" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BI8" t="n">
         <v>3.25</v>
@@ -2564,25 +2564,25 @@
         <v>4.4</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BP8" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BR8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BS8" t="n">
         <v>6.6</v>
       </c>
       <c r="BT8" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BU8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
@@ -2597,14 +2597,14 @@
         <v>8</v>
       </c>
       <c r="BZ8" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="CA8" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-15 20:09:37</t>
+          <t>2026-07-15 22:20:35</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
         <v>1.42</v>
       </c>
       <c r="G9" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="H9" t="n">
         <v>7.4</v>
@@ -2656,37 +2656,37 @@
         <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N9" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="O9" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P9" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="R9" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="S9" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="T9" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="U9" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V9" t="n">
         <v>1.13</v>
       </c>
       <c r="W9" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="X9" t="n">
         <v>40</v>
@@ -2701,10 +2701,10 @@
         <v>240</v>
       </c>
       <c r="AB9" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AD9" t="n">
         <v>36</v>
@@ -2713,7 +2713,7 @@
         <v>90</v>
       </c>
       <c r="AF9" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AG9" t="n">
         <v>11</v>
@@ -2725,10 +2725,10 @@
         <v>75</v>
       </c>
       <c r="AJ9" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AK9" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AL9" t="n">
         <v>30</v>
@@ -2737,70 +2737,70 @@
         <v>90</v>
       </c>
       <c r="AN9" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="AO9" t="n">
         <v>85</v>
       </c>
       <c r="AP9" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="AQ9" t="n">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="AR9" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.7</v>
+        <v>8.4</v>
       </c>
       <c r="AT9" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU9" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AV9" t="n">
-        <v>5</v>
+        <v>7.2</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="AX9" t="n">
         <v>10</v>
       </c>
       <c r="AY9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ9" t="n">
         <v>17.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB9" t="n">
         <v>11.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BD9" t="n">
         <v>19.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="BF9" t="n">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="BH9" t="n">
         <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="BJ9" t="n">
         <v>13.5</v>
@@ -2812,7 +2812,7 @@
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="BN9" t="n">
         <v>5.9</v>
@@ -2833,7 +2833,7 @@
         <v>2.02</v>
       </c>
       <c r="BT9" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BU9" t="n">
         <v>1.93</v>
@@ -2842,7 +2842,7 @@
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-15 20:09:37</t>
+          <t>2026-07-15 22:20:35</t>
         </is>
       </c>
     </row>
@@ -2889,19 +2889,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G10" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="H10" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="I10" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="J10" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K10" t="n">
         <v>4.4</v>
@@ -2910,22 +2910,22 @@
         <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N10" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="O10" t="n">
         <v>1.13</v>
       </c>
       <c r="P10" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="R10" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="S10" t="n">
         <v>2.02</v>
@@ -2934,13 +2934,13 @@
         <v>1.43</v>
       </c>
       <c r="U10" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="V10" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W10" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X10" t="n">
         <v>40</v>
@@ -2955,10 +2955,10 @@
         <v>46</v>
       </c>
       <c r="AB10" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AC10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AD10" t="n">
         <v>16</v>
@@ -2970,7 +2970,7 @@
         <v>28</v>
       </c>
       <c r="AG10" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AH10" t="n">
         <v>16.5</v>
@@ -2997,7 +2997,7 @@
         <v>13</v>
       </c>
       <c r="AP10" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="AQ10" t="n">
         <v>18</v>
@@ -3006,10 +3006,10 @@
         <v>21</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="AT10" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AU10" t="n">
         <v>9.800000000000001</v>
@@ -3030,25 +3030,25 @@
         <v>12</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="BC10" t="n">
         <v>19.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="BF10" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BG10" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-15 20:09:37</t>
+          <t>2026-07-15 22:20:35</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
         <v>1.9</v>
       </c>
       <c r="U11" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="V11" t="n">
         <v>1.43</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-15 20:09:37</t>
+          <t>2026-07-15 22:20:35</t>
         </is>
       </c>
     </row>
@@ -3415,7 +3415,7 @@
         <v>4.4</v>
       </c>
       <c r="L12" t="n">
-        <v>1.14</v>
+        <v>1.37</v>
       </c>
       <c r="M12" t="n">
         <v>1.07</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-15 20:09:37</t>
+          <t>2026-07-15 22:20:35</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-15 20:09:37</t>
+          <t>2026-07-15 22:20:35</t>
         </is>
       </c>
     </row>
@@ -3905,22 +3905,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="G14" t="n">
-        <v>10</v>
+        <v>7.2</v>
       </c>
       <c r="H14" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="I14" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="J14" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="K14" t="n">
-        <v>8.4</v>
+        <v>5.2</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
@@ -3929,10 +3929,10 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>2.16</v>
+        <v>5</v>
       </c>
       <c r="O14" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="P14" t="n">
         <v>2.16</v>
@@ -3941,22 +3941,22 @@
         <v>1.48</v>
       </c>
       <c r="R14" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="S14" t="n">
-        <v>2</v>
+        <v>2.42</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="V14" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-15 20:09:37</t>
+          <t>2026-07-15 22:20:35</t>
         </is>
       </c>
     </row>
@@ -4159,16 +4159,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="G15" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H15" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I15" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J15" t="n">
         <v>3.95</v>
@@ -4189,19 +4189,19 @@
         <v>1.24</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q15" t="n">
         <v>1.71</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="S15" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="T15" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="U15" t="n">
         <v>2.36</v>
@@ -4210,7 +4210,7 @@
         <v>1.33</v>
       </c>
       <c r="W15" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="X15" t="n">
         <v>25</v>
@@ -4231,7 +4231,7 @@
         <v>9.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE15" t="n">
         <v>50</v>
@@ -4273,7 +4273,7 @@
         <v>15</v>
       </c>
       <c r="AR15" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS15" t="n">
         <v>7.4</v>
@@ -4318,7 +4318,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BG15" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH15" t="n">
         <v>1000</v>
@@ -4342,7 +4342,7 @@
         <v>7</v>
       </c>
       <c r="BO15" t="n">
-        <v>3.65</v>
+        <v>1.5</v>
       </c>
       <c r="BP15" t="n">
         <v>19</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-15 20:09:37</t>
+          <t>2026-07-15 22:20:35</t>
         </is>
       </c>
     </row>
@@ -4413,16 +4413,16 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="G16" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="H16" t="n">
         <v>4.2</v>
       </c>
       <c r="I16" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J16" t="n">
         <v>3.95</v>
@@ -4464,7 +4464,7 @@
         <v>1.28</v>
       </c>
       <c r="W16" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="X16" t="n">
         <v>24</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-15 20:09:37</t>
+          <t>2026-07-15 22:20:35</t>
         </is>
       </c>
     </row>
@@ -4790,7 +4790,7 @@
         <v>11.5</v>
       </c>
       <c r="AU17" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AV17" t="n">
         <v>5.9</v>
@@ -4799,7 +4799,7 @@
         <v>6.2</v>
       </c>
       <c r="AX17" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY17" t="n">
         <v>10</v>
@@ -4811,7 +4811,7 @@
         <v>6.2</v>
       </c>
       <c r="BB17" t="n">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="BC17" t="n">
         <v>10</v>
@@ -4877,7 +4877,7 @@
         <v>13.5</v>
       </c>
       <c r="BX17" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="BY17" t="n">
         <v>13</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-15 20:09:37</t>
+          <t>2026-07-15 22:20:35</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4972,7 @@
         <v>1.31</v>
       </c>
       <c r="W18" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="X18" t="n">
         <v>18</v>
@@ -5041,7 +5041,7 @@
         <v>8</v>
       </c>
       <c r="AT18" t="n">
-        <v>9.199999999999999</v>
+        <v>5.1</v>
       </c>
       <c r="AU18" t="n">
         <v>4.5</v>
@@ -5050,19 +5050,19 @@
         <v>5.9</v>
       </c>
       <c r="AW18" t="n">
-        <v>28</v>
+        <v>7.6</v>
       </c>
       <c r="AX18" t="n">
         <v>5.7</v>
       </c>
       <c r="AY18" t="n">
-        <v>9.199999999999999</v>
+        <v>5.1</v>
       </c>
       <c r="AZ18" t="n">
         <v>6</v>
       </c>
       <c r="BA18" t="n">
-        <v>30</v>
+        <v>7.6</v>
       </c>
       <c r="BB18" t="n">
         <v>6.8</v>
@@ -5080,7 +5080,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BG18" t="n">
-        <v>24</v>
+        <v>7.4</v>
       </c>
       <c r="BH18" t="n">
         <v>1000</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-15 20:09:37</t>
+          <t>2026-07-15 22:20:35</t>
         </is>
       </c>
     </row>
@@ -5265,7 +5265,7 @@
         <v>75</v>
       </c>
       <c r="AJ19" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK19" t="n">
         <v>34</v>
@@ -5292,7 +5292,7 @@
         <v>18</v>
       </c>
       <c r="AS19" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT19" t="n">
         <v>7</v>
@@ -5322,10 +5322,10 @@
         <v>4.5</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE19" t="n">
         <v>5</v>
@@ -5340,7 +5340,7 @@
         <v>3.1</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.72</v>
+        <v>2.52</v>
       </c>
       <c r="BJ19" t="n">
         <v>10.5</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-15 20:09:37</t>
+          <t>2026-07-15 22:20:35</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
         <v>2.72</v>
       </c>
       <c r="U20" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="V20" t="n">
         <v>1.03</v>
@@ -5489,7 +5489,7 @@
         <v>85</v>
       </c>
       <c r="Z20" t="n">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="AA20" t="n">
         <v>1000</v>
@@ -5516,7 +5516,7 @@
         <v>75</v>
       </c>
       <c r="AI20" t="n">
-        <v>590</v>
+        <v>560</v>
       </c>
       <c r="AJ20" t="n">
         <v>7.8</v>
@@ -5528,7 +5528,7 @@
         <v>80</v>
       </c>
       <c r="AM20" t="n">
-        <v>550</v>
+        <v>520</v>
       </c>
       <c r="AN20" t="n">
         <v>3.85</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-15 20:09:37</t>
+          <t>2026-07-15 22:20:35</t>
         </is>
       </c>
     </row>
@@ -5686,19 +5686,19 @@
         <v>1.28</v>
       </c>
       <c r="G21" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="H21" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="I21" t="n">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="J21" t="n">
         <v>5.2</v>
       </c>
       <c r="K21" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="L21" t="n">
         <v>1.01</v>
@@ -5734,7 +5734,7 @@
         <v>1.03</v>
       </c>
       <c r="W21" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="X21" t="n">
         <v>1000</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-15 20:09:37</t>
+          <t>2026-07-15 22:20:35</t>
         </is>
       </c>
     </row>
@@ -6102,7 +6102,7 @@
         <v>3.6</v>
       </c>
       <c r="BI22" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BJ22" t="n">
         <v>11</v>
@@ -6114,13 +6114,13 @@
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN22" t="n">
         <v>4.4</v>
       </c>
       <c r="BO22" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BP22" t="n">
         <v>11.5</v>
@@ -6132,35 +6132,35 @@
         <v>28</v>
       </c>
       <c r="BS22" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT22" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BU22" t="n">
         <v>7</v>
       </c>
       <c r="BV22" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BW22" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX22" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ22" t="n">
         <v>22</v>
       </c>
       <c r="CA22" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-15 20:09:37</t>
+          <t>2026-07-15 22:20:35</t>
         </is>
       </c>
     </row>
@@ -6191,19 +6191,19 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="G23" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="H23" t="n">
         <v>3.55</v>
       </c>
       <c r="I23" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="J23" t="n">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="K23" t="n">
         <v>4.8</v>
@@ -6227,7 +6227,7 @@
         <v>1.5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="S23" t="n">
         <v>2.24</v>
@@ -6239,10 +6239,10 @@
         <v>2.4</v>
       </c>
       <c r="V23" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W23" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="X23" t="n">
         <v>32</v>
@@ -6269,7 +6269,7 @@
         <v>42</v>
       </c>
       <c r="AF23" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AG23" t="n">
         <v>13</v>
@@ -6281,7 +6281,7 @@
         <v>42</v>
       </c>
       <c r="AJ23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK23" t="n">
         <v>21</v>
@@ -6293,64 +6293,64 @@
         <v>65</v>
       </c>
       <c r="AN23" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AO23" t="n">
         <v>28</v>
       </c>
       <c r="AP23" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AQ23" t="n">
         <v>4.7</v>
       </c>
-      <c r="AQ23" t="n">
+      <c r="AR23" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC23" t="n">
         <v>4.5</v>
       </c>
-      <c r="AR23" t="n">
+      <c r="BD23" t="n">
         <v>4.8</v>
       </c>
-      <c r="AS23" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BE23" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BF23" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BG23" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BH23" t="n">
         <v>1000</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-15 20:09:37</t>
+          <t>2026-07-15 22:20:35</t>
         </is>
       </c>
     </row>
@@ -6448,7 +6448,7 @@
         <v>1.37</v>
       </c>
       <c r="G24" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="H24" t="n">
         <v>1.04</v>
@@ -6457,7 +6457,7 @@
         <v>1000</v>
       </c>
       <c r="J24" t="n">
-        <v>1.02</v>
+        <v>4.5</v>
       </c>
       <c r="K24" t="n">
         <v>1000</v>
@@ -6481,7 +6481,7 @@
         <v>1.74</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S24" t="n">
         <v>2.62</v>
@@ -6493,10 +6493,10 @@
         <v>1.01</v>
       </c>
       <c r="V24" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W24" t="n">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="X24" t="n">
         <v>1000</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-15 20:09:37</t>
+          <t>2026-07-15 22:20:35</t>
         </is>
       </c>
     </row>
@@ -6702,7 +6702,7 @@
         <v>1.95</v>
       </c>
       <c r="G25" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="H25" t="n">
         <v>3.9</v>
@@ -6711,7 +6711,7 @@
         <v>5.5</v>
       </c>
       <c r="J25" t="n">
-        <v>2.84</v>
+        <v>2.6</v>
       </c>
       <c r="K25" t="n">
         <v>3.65</v>
@@ -6750,7 +6750,7 @@
         <v>1.22</v>
       </c>
       <c r="W25" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="X25" t="n">
         <v>15.5</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-15 20:09:37</t>
+          <t>2026-07-15 22:20:35</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="G26" t="n">
         <v>2.32</v>
@@ -6962,10 +6962,10 @@
         <v>4</v>
       </c>
       <c r="I26" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="J26" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="K26" t="n">
         <v>3.15</v>
@@ -6974,34 +6974,34 @@
         <v>1.01</v>
       </c>
       <c r="M26" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="O26" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="P26" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.66</v>
+        <v>2.66</v>
       </c>
       <c r="R26" t="n">
         <v>1.17</v>
       </c>
       <c r="S26" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="T26" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="U26" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="V26" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W26" t="n">
         <v>1.75</v>
@@ -7061,7 +7061,7 @@
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>6.2</v>
+        <v>2.8</v>
       </c>
       <c r="AQ26" t="n">
         <v>3.2</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-15 20:09:37</t>
+          <t>2026-07-15 22:20:35</t>
         </is>
       </c>
     </row>
@@ -7207,22 +7207,22 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.44</v>
+        <v>2.52</v>
       </c>
       <c r="G27" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="H27" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="I27" t="n">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="J27" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K27" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="L27" t="n">
         <v>1.01</v>
@@ -7231,43 +7231,43 @@
         <v>1.1</v>
       </c>
       <c r="N27" t="n">
-        <v>1.61</v>
+        <v>2.78</v>
       </c>
       <c r="O27" t="n">
         <v>1.47</v>
       </c>
       <c r="P27" t="n">
-        <v>1.25</v>
+        <v>1.64</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.47</v>
+        <v>2.24</v>
       </c>
       <c r="R27" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S27" t="n">
         <v>1.01</v>
       </c>
       <c r="T27" t="n">
-        <v>1.9</v>
+        <v>1.59</v>
       </c>
       <c r="U27" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="V27" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="W27" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X27" t="n">
         <v>1000</v>
       </c>
       <c r="Y27" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z27" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA27" t="n">
         <v>1000</v>
@@ -7279,22 +7279,22 @@
         <v>1000</v>
       </c>
       <c r="AD27" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF27" t="n">
         <v>1000</v>
       </c>
       <c r="AG27" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI27" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ27" t="n">
         <v>1000</v>
@@ -7315,58 +7315,58 @@
         <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.03</v>
+        <v>1.38</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.03</v>
+        <v>1.24</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.03</v>
+        <v>1.31</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.03</v>
+        <v>1.38</v>
       </c>
       <c r="AT27" t="n">
-        <v>1.03</v>
+        <v>1.38</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.03</v>
+        <v>1.38</v>
       </c>
       <c r="AV27" t="n">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.03</v>
+        <v>1.38</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.03</v>
+        <v>1.26</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.03</v>
+        <v>1.31</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.03</v>
+        <v>1.38</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.03</v>
+        <v>1.38</v>
       </c>
       <c r="BD27" t="n">
-        <v>1.03</v>
+        <v>1.38</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.03</v>
+        <v>1.38</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.03</v>
+        <v>1.38</v>
       </c>
       <c r="BG27" t="n">
-        <v>1.03</v>
+        <v>1.38</v>
       </c>
       <c r="BH27" t="n">
         <v>1000</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-15 20:09:37</t>
+          <t>2026-07-15 22:20:35</t>
         </is>
       </c>
     </row>
@@ -7461,37 +7461,37 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="G28" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="H28" t="n">
         <v>7</v>
       </c>
       <c r="I28" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="J28" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="K28" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="L28" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="M28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N28" t="n">
         <v>4.5</v>
       </c>
       <c r="O28" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="P28" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="Q28" t="n">
         <v>1.63</v>
@@ -7509,10 +7509,10 @@
         <v>1.92</v>
       </c>
       <c r="V28" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W28" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="X28" t="n">
         <v>24</v>
@@ -7626,19 +7626,19 @@
         <v>1000</v>
       </c>
       <c r="BI28" t="n">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="BJ28" t="n">
         <v>15</v>
       </c>
       <c r="BK28" t="n">
-        <v>6.4</v>
+        <v>1.74</v>
       </c>
       <c r="BL28" t="n">
         <v>1000</v>
       </c>
       <c r="BM28" t="n">
-        <v>21</v>
+        <v>1.97</v>
       </c>
       <c r="BN28" t="n">
         <v>5.8</v>
@@ -7650,41 +7650,41 @@
         <v>12.5</v>
       </c>
       <c r="BQ28" t="n">
-        <v>5.6</v>
+        <v>1.7</v>
       </c>
       <c r="BR28" t="n">
         <v>30</v>
       </c>
       <c r="BS28" t="n">
-        <v>13</v>
+        <v>1.85</v>
       </c>
       <c r="BT28" t="n">
         <v>16</v>
       </c>
       <c r="BU28" t="n">
-        <v>6.8</v>
+        <v>1.76</v>
       </c>
       <c r="BV28" t="n">
         <v>1000</v>
       </c>
       <c r="BW28" t="n">
-        <v>21</v>
+        <v>1.93</v>
       </c>
       <c r="BX28" t="n">
         <v>1000</v>
       </c>
       <c r="BY28" t="n">
-        <v>21</v>
+        <v>1.93</v>
       </c>
       <c r="BZ28" t="n">
         <v>18.5</v>
       </c>
       <c r="CA28" t="n">
-        <v>8</v>
+        <v>1.78</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-15 20:09:37</t>
+          <t>2026-07-15 22:20:35</t>
         </is>
       </c>
     </row>
@@ -7718,19 +7718,19 @@
         <v>1.58</v>
       </c>
       <c r="G29" t="n">
-        <v>1000</v>
+        <v>1.75</v>
       </c>
       <c r="H29" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="I29" t="n">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="J29" t="n">
         <v>4</v>
       </c>
       <c r="K29" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="L29" t="n">
         <v>1.01</v>
@@ -7739,7 +7739,7 @@
         <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>1.86</v>
+        <v>3.15</v>
       </c>
       <c r="O29" t="n">
         <v>1.29</v>
@@ -7763,10 +7763,10 @@
         <v>1.01</v>
       </c>
       <c r="V29" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="W29" t="n">
-        <v>1.57</v>
+        <v>2.32</v>
       </c>
       <c r="X29" t="n">
         <v>1000</v>
@@ -7823,52 +7823,52 @@
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF29" t="n">
         <v>1.01</v>
@@ -7886,59 +7886,59 @@
         <v>1000</v>
       </c>
       <c r="BK29" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BL29" t="n">
         <v>1000</v>
       </c>
       <c r="BM29" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BN29" t="n">
         <v>1000</v>
       </c>
       <c r="BO29" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BP29" t="n">
         <v>1000</v>
       </c>
       <c r="BQ29" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BR29" t="n">
         <v>1000</v>
       </c>
       <c r="BS29" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BT29" t="n">
         <v>1000</v>
       </c>
       <c r="BU29" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BV29" t="n">
         <v>1000</v>
       </c>
       <c r="BW29" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BX29" t="n">
         <v>1000</v>
       </c>
       <c r="BY29" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BZ29" t="n">
         <v>1000</v>
       </c>
       <c r="CA29" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-15 20:09:37</t>
+          <t>2026-07-15 22:20:35</t>
         </is>
       </c>
     </row>
@@ -7969,7 +7969,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="G30" t="n">
         <v>2.14</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-15 20:09:37</t>
+          <t>2026-07-15 22:20:35</t>
         </is>
       </c>
     </row>
@@ -8238,19 +8238,19 @@
         <v>3.45</v>
       </c>
       <c r="K31" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P31" t="n">
         <v>1.79</v>
@@ -8259,194 +8259,194 @@
         <v>2.04</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AO31" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AP31" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AR31" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AS31" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AU31" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BG31" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH31" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BI31" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BJ31" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BK31" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BL31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM31" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN31" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BO31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BP31" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BQ31" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BR31" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BS31" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BT31" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BU31" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BV31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW31" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BX31" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BY31" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BZ31" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="CA31" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-15 20:09:37</t>
+          <t>2026-07-15 22:20:35</t>
         </is>
       </c>
     </row>
@@ -8495,212 +8495,212 @@
         <v>1000</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q32" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q32" t="n">
-        <v>1.01</v>
-      </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-15 20:09:37</t>
+          <t>2026-07-15 22:20:35</t>
         </is>
       </c>
     </row>
@@ -8731,230 +8731,230 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.04</v>
+        <v>2.18</v>
       </c>
       <c r="G33" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="H33" t="n">
-        <v>1.04</v>
+        <v>2.3</v>
       </c>
       <c r="I33" t="n">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="J33" t="n">
-        <v>1.02</v>
+        <v>2.8</v>
       </c>
       <c r="K33" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="P33" t="n">
-        <v>1.24</v>
+        <v>2.14</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH33" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BI33" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="BJ33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-15 20:09:37</t>
+          <t>2026-07-15 22:20:35</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-17.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="G2" t="n">
         <v>4</v>
@@ -866,46 +866,46 @@
         <v>2.1</v>
       </c>
       <c r="I2" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="J2" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K2" t="n">
         <v>3.8</v>
       </c>
       <c r="L2" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="O2" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="R2" t="n">
         <v>1.4</v>
       </c>
       <c r="S2" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T2" t="n">
         <v>1.77</v>
       </c>
       <c r="U2" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="V2" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="W2" t="n">
         <v>1.33</v>
@@ -932,7 +932,7 @@
         <v>11</v>
       </c>
       <c r="AE2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF2" t="n">
         <v>29</v>
@@ -956,16 +956,16 @@
         <v>55</v>
       </c>
       <c r="AM2" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AN2" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AO2" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AP2" t="n">
-        <v>13.5</v>
+        <v>7.8</v>
       </c>
       <c r="AQ2" t="n">
         <v>9</v>
@@ -974,7 +974,7 @@
         <v>12</v>
       </c>
       <c r="AS2" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT2" t="n">
         <v>13</v>
@@ -983,13 +983,13 @@
         <v>7.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>10</v>
+        <v>6.2</v>
       </c>
       <c r="AW2" t="n">
         <v>19</v>
       </c>
       <c r="AX2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AY2" t="n">
         <v>14</v>
@@ -1007,10 +1007,10 @@
         <v>36</v>
       </c>
       <c r="BD2" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BE2" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BF2" t="n">
         <v>11</v>
@@ -1019,10 +1019,10 @@
         <v>13</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="BJ2" t="n">
         <v>9.4</v>
@@ -1040,10 +1040,10 @@
         <v>7.2</v>
       </c>
       <c r="BO2" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="BP2" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BQ2" t="n">
         <v>23</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -1111,230 +1111,230 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="G3" t="n">
         <v>2.22</v>
       </c>
       <c r="H3" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="J3" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="K3" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="L3" t="n">
         <v>1.39</v>
       </c>
       <c r="M3" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="O3" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P3" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="R3" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="S3" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="T3" t="n">
-        <v>1.74</v>
+        <v>1.34</v>
       </c>
       <c r="U3" t="n">
-        <v>2.18</v>
+        <v>1.82</v>
       </c>
       <c r="V3" t="n">
         <v>1.33</v>
       </c>
       <c r="W3" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="X3" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BR3" t="n">
         <v>28</v>
       </c>
-      <c r="AL3" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>19</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>50</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>13</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>16</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>29</v>
-      </c>
       <c r="BS3" t="n">
-        <v>9.800000000000001</v>
+        <v>2.66</v>
       </c>
       <c r="BT3" t="n">
         <v>7</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BV3" t="n">
         <v>29</v>
       </c>
       <c r="BW3" t="n">
-        <v>9.800000000000001</v>
+        <v>2.68</v>
       </c>
       <c r="BX3" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>10.5</v>
+        <v>2.74</v>
       </c>
       <c r="BZ3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="CA3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -1377,13 +1377,13 @@
         <v>2.04</v>
       </c>
       <c r="J4" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K4" t="n">
         <v>3.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="M4" t="n">
         <v>1.07</v>
@@ -1398,7 +1398,7 @@
         <v>1.87</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="R4" t="n">
         <v>1.33</v>
@@ -1470,28 +1470,28 @@
         <v>75</v>
       </c>
       <c r="AO4" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AP4" t="n">
-        <v>12</v>
+        <v>4.1</v>
       </c>
       <c r="AQ4" t="n">
-        <v>7.8</v>
+        <v>3.6</v>
       </c>
       <c r="AR4" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AS4" t="n">
-        <v>20</v>
+        <v>4.6</v>
       </c>
       <c r="AT4" t="n">
-        <v>13</v>
+        <v>4.2</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.4</v>
+        <v>3.35</v>
       </c>
       <c r="AV4" t="n">
-        <v>9.199999999999999</v>
+        <v>3.85</v>
       </c>
       <c r="AW4" t="n">
         <v>4.5</v>
@@ -1500,10 +1500,10 @@
         <v>4.8</v>
       </c>
       <c r="AY4" t="n">
-        <v>15</v>
+        <v>4.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>16.5</v>
+        <v>4.4</v>
       </c>
       <c r="BA4" t="n">
         <v>4.9</v>
@@ -1515,7 +1515,7 @@
         <v>5.1</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BE4" t="n">
         <v>5.3</v>
@@ -1524,71 +1524,71 @@
         <v>5.2</v>
       </c>
       <c r="BG4" t="n">
-        <v>13</v>
+        <v>4.2</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.4</v>
+        <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.78</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>2.7</v>
+        <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BP4" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>2.6</v>
+        <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="BV4" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BX4" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.52</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -1634,7 +1634,7 @@
         <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -1876,169 +1876,169 @@
         <v>4.1</v>
       </c>
       <c r="G6" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="H6" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="I6" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="J6" t="n">
         <v>3.1</v>
       </c>
       <c r="K6" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="L6" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="M6" t="n">
         <v>1.1</v>
       </c>
       <c r="N6" t="n">
-        <v>2.86</v>
+        <v>2.72</v>
       </c>
       <c r="O6" t="n">
         <v>1.43</v>
       </c>
       <c r="P6" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T6" t="n">
         <v>1.63</v>
       </c>
-      <c r="Q6" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.98</v>
-      </c>
       <c r="U6" t="n">
-        <v>1.83</v>
+        <v>1.42</v>
       </c>
       <c r="V6" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="W6" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="X6" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="AW6" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="n">
         <v>3.05</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="BJ6" t="n">
         <v>11.5</v>
@@ -2053,16 +2053,16 @@
         <v>10</v>
       </c>
       <c r="BN6" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BO6" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
@@ -2077,26 +2077,26 @@
         <v>3.3</v>
       </c>
       <c r="BV6" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BW6" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -2133,10 +2133,10 @@
         <v>4.3</v>
       </c>
       <c r="H7" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="I7" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="J7" t="n">
         <v>2.92</v>
@@ -2145,46 +2145,46 @@
         <v>3.35</v>
       </c>
       <c r="L7" t="n">
-        <v>1.55</v>
+        <v>1.28</v>
       </c>
       <c r="M7" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
         <v>2.56</v>
       </c>
       <c r="O7" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="P7" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="R7" t="n">
         <v>1.19</v>
       </c>
       <c r="S7" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="T7" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U7" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="V7" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W7" t="n">
         <v>1.3</v>
       </c>
       <c r="X7" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="Z7" t="n">
         <v>14</v>
@@ -2214,7 +2214,7 @@
         <v>24</v>
       </c>
       <c r="AI7" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ7" t="n">
         <v>110</v>
@@ -2235,58 +2235,58 @@
         <v>34</v>
       </c>
       <c r="AP7" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AQ7" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="AR7" t="n">
-        <v>5.5</v>
+        <v>10</v>
       </c>
       <c r="AS7" t="n">
-        <v>22</v>
+        <v>6.4</v>
       </c>
       <c r="AT7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AV7" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AU7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>10</v>
-      </c>
       <c r="AW7" t="n">
-        <v>21</v>
+        <v>6.4</v>
       </c>
       <c r="AX7" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>17.5</v>
       </c>
-      <c r="AY7" t="n">
-        <v>6</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BA7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BB7" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="BC7" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BD7" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BE7" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="BG7" t="n">
-        <v>22</v>
+        <v>6.4</v>
       </c>
       <c r="BH7" t="n">
         <v>2.82</v>
@@ -2319,7 +2319,7 @@
         <v>8.6</v>
       </c>
       <c r="BR7" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BS7" t="n">
         <v>9.4</v>
@@ -2328,7 +2328,7 @@
         <v>5.1</v>
       </c>
       <c r="BU7" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="BV7" t="n">
         <v>21</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -2381,67 +2381,67 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="G8" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="H8" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="I8" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="J8" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="K8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N8" t="n">
         <v>5.2</v>
       </c>
-      <c r="L8" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N8" t="n">
-        <v>5</v>
-      </c>
       <c r="O8" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P8" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="R8" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="S8" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="T8" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="U8" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V8" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="W8" t="n">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="X8" t="n">
         <v>23</v>
       </c>
       <c r="Y8" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="Z8" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AA8" t="n">
         <v>1000</v>
@@ -2450,161 +2450,161 @@
         <v>10.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF8" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG8" t="n">
         <v>10</v>
       </c>
       <c r="AH8" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AI8" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AJ8" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AK8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL8" t="n">
         <v>32</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN8" t="n">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="AO8" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AP8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>27</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>32</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>48</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV8" t="n">
         <v>19.5</v>
       </c>
-      <c r="AQ8" t="n">
-        <v>23</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>50</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>46</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>23</v>
-      </c>
       <c r="AW8" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AX8" t="n">
         <v>8.6</v>
       </c>
       <c r="AY8" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ8" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BA8" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="BB8" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BC8" t="n">
         <v>13</v>
       </c>
       <c r="BD8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BE8" t="n">
+        <v>40</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BG8" t="n">
         <v>38</v>
       </c>
-      <c r="BF8" t="n">
-        <v>6</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>48</v>
-      </c>
       <c r="BH8" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="BJ8" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BN8" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="BP8" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BR8" t="n">
         <v>23</v>
       </c>
       <c r="BS8" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BT8" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BU8" t="n">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BZ8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="CA8" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -2638,22 +2638,22 @@
         <v>1.42</v>
       </c>
       <c r="G9" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="H9" t="n">
         <v>7.4</v>
       </c>
       <c r="I9" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J9" t="n">
         <v>5.4</v>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="M9" t="n">
         <v>1.02</v>
@@ -2671,10 +2671,10 @@
         <v>1.44</v>
       </c>
       <c r="R9" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="S9" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="T9" t="n">
         <v>1.68</v>
@@ -2698,7 +2698,7 @@
         <v>90</v>
       </c>
       <c r="AA9" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AB9" t="n">
         <v>14.5</v>
@@ -2731,28 +2731,28 @@
         <v>14.5</v>
       </c>
       <c r="AL9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM9" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN9" t="n">
         <v>4.4</v>
       </c>
       <c r="AO9" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AP9" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ9" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AR9" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AT9" t="n">
         <v>12</v>
@@ -2761,10 +2761,10 @@
         <v>12</v>
       </c>
       <c r="AV9" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AW9" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX9" t="n">
         <v>10</v>
@@ -2776,7 +2776,7 @@
         <v>17.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB9" t="n">
         <v>11.5</v>
@@ -2785,80 +2785,80 @@
         <v>12</v>
       </c>
       <c r="BD9" t="n">
-        <v>19.5</v>
+        <v>16</v>
       </c>
       <c r="BE9" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF9" t="n">
         <v>3.95</v>
       </c>
       <c r="BG9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BP9" t="n">
         <v>8.6</v>
       </c>
-      <c r="BH9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>11</v>
-      </c>
       <c r="BQ9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>19</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>12</v>
+      </c>
+      <c r="BU9" t="n">
         <v>5.4</v>
       </c>
-      <c r="BR9" t="n">
-        <v>25</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>16</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>1.93</v>
-      </c>
       <c r="BV9" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW9" t="n">
-        <v>2.12</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX9" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.12</v>
+        <v>8</v>
       </c>
       <c r="BZ9" t="n">
-        <v>13</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.88</v>
+        <v>4.9</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -2889,16 +2889,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="G10" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="H10" t="n">
         <v>2.54</v>
       </c>
       <c r="I10" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="J10" t="n">
         <v>4.1</v>
@@ -2907,46 +2907,46 @@
         <v>4.4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="M10" t="n">
         <v>1.02</v>
       </c>
       <c r="N10" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="O10" t="n">
         <v>1.13</v>
       </c>
       <c r="P10" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="R10" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="S10" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="T10" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="U10" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="V10" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="W10" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="X10" t="n">
         <v>40</v>
       </c>
       <c r="Y10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z10" t="n">
         <v>29</v>
@@ -2958,7 +2958,7 @@
         <v>22</v>
       </c>
       <c r="AC10" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AD10" t="n">
         <v>16</v>
@@ -2970,7 +2970,7 @@
         <v>28</v>
       </c>
       <c r="AG10" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH10" t="n">
         <v>15</v>
@@ -2979,34 +2979,34 @@
         <v>30</v>
       </c>
       <c r="AJ10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AK10" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AL10" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AM10" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AN10" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AO10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AP10" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="AQ10" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AR10" t="n">
         <v>21</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="AT10" t="n">
         <v>18</v>
@@ -3030,79 +3030,79 @@
         <v>12</v>
       </c>
       <c r="BA10" t="n">
-        <v>5.4</v>
+        <v>18.5</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="BC10" t="n">
         <v>19.5</v>
       </c>
       <c r="BD10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>16</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>21</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>8</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BU10" t="n">
         <v>5.3</v>
       </c>
-      <c r="BE10" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>22</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>29</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BV10" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="BW10" t="n">
-        <v>2</v>
+        <v>7.4</v>
       </c>
       <c r="BX10" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.06</v>
+        <v>8</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -3155,19 +3155,19 @@
         <v>3.3</v>
       </c>
       <c r="J11" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K11" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L11" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M11" t="n">
         <v>1.09</v>
       </c>
       <c r="N11" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O11" t="n">
         <v>1.42</v>
@@ -3185,10 +3185,10 @@
         <v>4.2</v>
       </c>
       <c r="T11" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U11" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="V11" t="n">
         <v>1.43</v>
@@ -3254,16 +3254,16 @@
         <v>9.4</v>
       </c>
       <c r="AQ11" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AR11" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AS11" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AT11" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU11" t="n">
         <v>6.4</v>
@@ -3281,92 +3281,92 @@
         <v>10</v>
       </c>
       <c r="AZ11" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA11" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BB11" t="n">
-        <v>7.8</v>
+        <v>32</v>
       </c>
       <c r="BC11" t="n">
         <v>7.4</v>
       </c>
       <c r="BD11" t="n">
-        <v>8.199999999999999</v>
+        <v>40</v>
       </c>
       <c r="BE11" t="n">
         <v>9</v>
       </c>
       <c r="BF11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>8</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BP11" t="n">
         <v>23</v>
       </c>
-      <c r="BG11" t="n">
+      <c r="BQ11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>40</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>28</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>44</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BZ11" t="n">
         <v>38</v>
       </c>
-      <c r="BH11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>15</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>32</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="BT11" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BV11" t="n">
-        <v>40</v>
-      </c>
-      <c r="BW11" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="BX11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY11" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="BZ11" t="n">
-        <v>1000</v>
-      </c>
       <c r="CA11" t="n">
-        <v>1.68</v>
+        <v>8.4</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -3397,19 +3397,19 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="G12" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="H12" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="I12" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="J12" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="K12" t="n">
         <v>5.2</v>
@@ -3421,10 +3421,10 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="O12" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P12" t="n">
         <v>2.38</v>
@@ -3433,46 +3433,46 @@
         <v>1.58</v>
       </c>
       <c r="R12" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="S12" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="T12" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="U12" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V12" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="W12" t="n">
         <v>1.17</v>
       </c>
       <c r="X12" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Y12" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AB12" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="AC12" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AD12" t="n">
         <v>11</v>
       </c>
       <c r="AE12" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AF12" t="n">
         <v>65</v>
@@ -3481,82 +3481,82 @@
         <v>25</v>
       </c>
       <c r="AH12" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AI12" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AJ12" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="AK12" t="n">
         <v>85</v>
       </c>
       <c r="AL12" t="n">
+        <v>95</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN12" t="n">
         <v>85</v>
       </c>
-      <c r="AM12" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>75</v>
-      </c>
       <c r="AO12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BA12" t="n">
         <v>7</v>
       </c>
-      <c r="AP12" t="n">
-        <v>18</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>20</v>
-      </c>
-      <c r="AU12" t="n">
+      <c r="BB12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC12" t="n">
         <v>8.4</v>
       </c>
-      <c r="AV12" t="n">
-        <v>8</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>18</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>21</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>7</v>
-      </c>
       <c r="BD12" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE12" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BF12" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BG12" t="n">
-        <v>5.7</v>
+        <v>3.9</v>
       </c>
       <c r="BH12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="G13" t="n">
         <v>7</v>
@@ -3660,7 +3660,7 @@
         <v>1.62</v>
       </c>
       <c r="I13" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="J13" t="n">
         <v>3.75</v>
@@ -3669,37 +3669,37 @@
         <v>4.4</v>
       </c>
       <c r="L13" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M13" t="n">
         <v>1.07</v>
       </c>
       <c r="N13" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O13" t="n">
         <v>1.32</v>
       </c>
       <c r="P13" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="Q13" t="n">
         <v>1.94</v>
       </c>
       <c r="R13" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S13" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="T13" t="n">
         <v>1.93</v>
       </c>
       <c r="U13" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="V13" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="W13" t="n">
         <v>1.16</v>
@@ -3711,7 +3711,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="Z13" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AA13" t="n">
         <v>17.5</v>
@@ -3720,7 +3720,7 @@
         <v>20</v>
       </c>
       <c r="AC13" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD13" t="n">
         <v>10.5</v>
@@ -3747,7 +3747,7 @@
         <v>120</v>
       </c>
       <c r="AL13" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AM13" t="n">
         <v>170</v>
@@ -3759,122 +3759,122 @@
         <v>11.5</v>
       </c>
       <c r="AP13" t="n">
-        <v>12</v>
+        <v>5.2</v>
       </c>
       <c r="AQ13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA13" t="n">
         <v>6.6</v>
       </c>
-      <c r="AR13" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>14</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>16</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AX13" t="n">
+      <c r="BB13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC13" t="n">
         <v>7.4</v>
       </c>
-      <c r="AY13" t="n">
-        <v>20</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>32</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BD13" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BF13" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>8.199999999999999</v>
+        <v>4.7</v>
       </c>
       <c r="BH13" t="n">
         <v>1000</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="BJ13" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BK13" t="n">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="BN13" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="BP13" t="n">
         <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="BT13" t="n">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="BV13" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
       <c r="BX13" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="BZ13" t="n">
         <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
         <v>11.5</v>
       </c>
       <c r="J14" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="K14" t="n">
         <v>7.6</v>
@@ -3971,13 +3971,13 @@
         <v>290</v>
       </c>
       <c r="AB14" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AD14" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AE14" t="n">
         <v>120</v>
@@ -3992,7 +3992,7 @@
         <v>27</v>
       </c>
       <c r="AI14" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ14" t="n">
         <v>15</v>
@@ -4004,67 +4004,67 @@
         <v>30</v>
       </c>
       <c r="AM14" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN14" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AO14" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AP14" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AR14" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AS14" t="n">
         <v>6</v>
       </c>
-      <c r="AS14" t="n">
-        <v>6.2</v>
-      </c>
       <c r="AT14" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AV14" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="AW14" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AX14" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AY14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BB14" t="n">
         <v>4.3</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>4.4</v>
       </c>
       <c r="BC14" t="n">
         <v>4.4</v>
       </c>
       <c r="BD14" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BE14" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BF14" t="n">
         <v>3</v>
       </c>
       <c r="BG14" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BH14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -4159,16 +4159,16 @@
         </is>
       </c>
       <c r="F15" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="G15" t="n">
         <v>2</v>
-      </c>
-      <c r="G15" t="n">
-        <v>2.02</v>
       </c>
       <c r="H15" t="n">
         <v>3.95</v>
       </c>
       <c r="I15" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J15" t="n">
         <v>3.95</v>
@@ -4189,34 +4189,34 @@
         <v>1.24</v>
       </c>
       <c r="P15" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="S15" t="n">
         <v>2.78</v>
       </c>
       <c r="T15" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U15" t="n">
         <v>2.36</v>
       </c>
       <c r="V15" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W15" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X15" t="n">
         <v>25</v>
       </c>
       <c r="Y15" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Z15" t="n">
         <v>36</v>
@@ -4228,19 +4228,19 @@
         <v>12</v>
       </c>
       <c r="AC15" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE15" t="n">
         <v>50</v>
       </c>
       <c r="AF15" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG15" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH15" t="n">
         <v>17.5</v>
@@ -4261,7 +4261,7 @@
         <v>85</v>
       </c>
       <c r="AN15" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AO15" t="n">
         <v>42</v>
@@ -4270,119 +4270,119 @@
         <v>17.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR15" t="n">
         <v>22</v>
       </c>
       <c r="AS15" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT15" t="n">
-        <v>5</v>
+        <v>10.5</v>
       </c>
       <c r="AU15" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AV15" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="AX15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AY15" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ15" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB15" t="n">
         <v>19.5</v>
       </c>
       <c r="BC15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BP15" t="n">
         <v>14</v>
       </c>
-      <c r="BD15" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BE15" t="n">
+      <c r="BQ15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>25</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BT15" t="n">
         <v>7.8</v>
       </c>
-      <c r="BF15" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>7</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>13</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BP15" t="n">
+      <c r="BU15" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>32</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>38</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BZ15" t="n">
         <v>19</v>
       </c>
-      <c r="BQ15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="BR15" t="n">
-        <v>34</v>
-      </c>
-      <c r="BS15" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BT15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BU15" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BV15" t="n">
-        <v>46</v>
-      </c>
-      <c r="BW15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BX15" t="n">
-        <v>50</v>
-      </c>
-      <c r="BY15" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="BZ15" t="n">
-        <v>26</v>
-      </c>
       <c r="CA15" t="n">
-        <v>1.8</v>
+        <v>6.6</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -4413,19 +4413,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="G16" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="H16" t="n">
         <v>4.2</v>
       </c>
       <c r="I16" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J16" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K16" t="n">
         <v>4.3</v>
@@ -4437,22 +4437,22 @@
         <v>1.05</v>
       </c>
       <c r="N16" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O16" t="n">
         <v>1.23</v>
       </c>
       <c r="P16" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="R16" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S16" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="T16" t="n">
         <v>1.66</v>
@@ -4464,10 +4464,10 @@
         <v>1.28</v>
       </c>
       <c r="W16" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="X16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y16" t="n">
         <v>23</v>
@@ -4479,25 +4479,25 @@
         <v>100</v>
       </c>
       <c r="AB16" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC16" t="n">
         <v>11</v>
       </c>
       <c r="AD16" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AE16" t="n">
         <v>55</v>
       </c>
       <c r="AF16" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH16" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AI16" t="n">
         <v>60</v>
@@ -4515,7 +4515,7 @@
         <v>85</v>
       </c>
       <c r="AN16" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AO16" t="n">
         <v>48</v>
@@ -4524,119 +4524,119 @@
         <v>17.5</v>
       </c>
       <c r="AQ16" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV16" t="n">
         <v>15</v>
       </c>
-      <c r="AR16" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>13</v>
-      </c>
       <c r="AW16" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="AX16" t="n">
         <v>11</v>
       </c>
       <c r="AY16" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ16" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="BB16" t="n">
         <v>18</v>
       </c>
       <c r="BC16" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="BF16" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BG16" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="BH16" t="n">
         <v>1000</v>
       </c>
       <c r="BI16" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="BJ16" t="n">
         <v>12.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="BN16" t="n">
         <v>6.4</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BP16" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="BR16" t="n">
         <v>32</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="BT16" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BU16" t="n">
-        <v>5.1</v>
+        <v>1.69</v>
       </c>
       <c r="BV16" t="n">
         <v>44</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="BX16" t="n">
         <v>50</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="BZ16" t="n">
         <v>25</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -4679,10 +4679,10 @@
         <v>18.5</v>
       </c>
       <c r="J17" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="L17" t="n">
         <v>1.18</v>
@@ -4697,22 +4697,22 @@
         <v>1.1</v>
       </c>
       <c r="P17" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="R17" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="S17" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="T17" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="U17" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="V17" t="n">
         <v>1.04</v>
@@ -4724,109 +4724,109 @@
         <v>65</v>
       </c>
       <c r="Y17" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="Z17" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
         <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AC17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AD17" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AE17" t="n">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AG17" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AI17" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AK17" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AL17" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM17" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="AO17" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>5.9</v>
+        <v>46</v>
       </c>
       <c r="AQ17" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="AR17" t="n">
-        <v>6.2</v>
+        <v>46</v>
       </c>
       <c r="AS17" t="n">
-        <v>6.4</v>
+        <v>60</v>
       </c>
       <c r="AT17" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="AU17" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AV17" t="n">
-        <v>5.9</v>
+        <v>29</v>
       </c>
       <c r="AW17" t="n">
-        <v>6.2</v>
+        <v>48</v>
       </c>
       <c r="AX17" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AY17" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AZ17" t="n">
-        <v>5.5</v>
+        <v>25</v>
       </c>
       <c r="BA17" t="n">
-        <v>6.2</v>
+        <v>42</v>
       </c>
       <c r="BB17" t="n">
         <v>9.4</v>
       </c>
       <c r="BC17" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>5.5</v>
+        <v>25</v>
       </c>
       <c r="BE17" t="n">
-        <v>6.2</v>
+        <v>42</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="BG17" t="n">
-        <v>6.2</v>
+        <v>46</v>
       </c>
       <c r="BH17" t="n">
         <v>6.2</v>
@@ -4859,10 +4859,10 @@
         <v>5.6</v>
       </c>
       <c r="BR17" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BS17" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BT17" t="n">
         <v>17.5</v>
@@ -4880,7 +4880,7 @@
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BZ17" t="n">
         <v>6.2</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="G18" t="n">
         <v>2.48</v>
@@ -4930,13 +4930,13 @@
         <v>3.4</v>
       </c>
       <c r="I18" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="J18" t="n">
         <v>3.2</v>
       </c>
       <c r="K18" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L18" t="n">
         <v>1.47</v>
@@ -4945,10 +4945,10 @@
         <v>1.09</v>
       </c>
       <c r="N18" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O18" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P18" t="n">
         <v>1.69</v>
@@ -4960,16 +4960,16 @@
         <v>1.25</v>
       </c>
       <c r="S18" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="T18" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="U18" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="V18" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W18" t="n">
         <v>1.67</v>
@@ -4981,25 +4981,25 @@
         <v>13</v>
       </c>
       <c r="Z18" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AA18" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AB18" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC18" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF18" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AG18" t="n">
         <v>14</v>
@@ -5011,10 +5011,10 @@
         <v>65</v>
       </c>
       <c r="AJ18" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AK18" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AL18" t="n">
         <v>60</v>
@@ -5023,64 +5023,64 @@
         <v>150</v>
       </c>
       <c r="AN18" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AO18" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AP18" t="n">
-        <v>8.4</v>
+        <v>4.3</v>
       </c>
       <c r="AQ18" t="n">
-        <v>8.6</v>
+        <v>4.4</v>
       </c>
       <c r="AR18" t="n">
-        <v>18</v>
+        <v>5.4</v>
       </c>
       <c r="AS18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AZ18" t="n">
         <v>5.2</v>
       </c>
-      <c r="AT18" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BA18" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BB18" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BC18" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BF18" t="n">
-        <v>20</v>
+        <v>5.3</v>
       </c>
       <c r="BG18" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BH18" t="n">
         <v>3.1</v>
@@ -5089,7 +5089,7 @@
         <v>2.52</v>
       </c>
       <c r="BJ18" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK18" t="n">
         <v>5.6</v>
@@ -5098,43 +5098,43 @@
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>11</v>
+        <v>2.4</v>
       </c>
       <c r="BN18" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BO18" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="BP18" t="n">
         <v>19</v>
       </c>
       <c r="BQ18" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BR18" t="n">
         <v>38</v>
       </c>
       <c r="BS18" t="n">
-        <v>9.199999999999999</v>
+        <v>2.3</v>
       </c>
       <c r="BT18" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BU18" t="n">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
       <c r="BV18" t="n">
         <v>34</v>
       </c>
       <c r="BW18" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>9.800000000000001</v>
+        <v>2.32</v>
       </c>
       <c r="BZ18" t="n">
         <v>0</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
         <v>1000</v>
       </c>
       <c r="J19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K19" t="n">
         <v>1000</v>
@@ -5199,7 +5199,7 @@
         <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O19" t="n">
         <v>1.01</v>
@@ -5208,7 +5208,7 @@
         <v>1.24</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R19" t="n">
         <v>1.12</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -5441,7 +5441,7 @@
         <v>1000</v>
       </c>
       <c r="J20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K20" t="n">
         <v>1000</v>
@@ -5453,7 +5453,7 @@
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O20" t="n">
         <v>1.01</v>
@@ -5462,13 +5462,13 @@
         <v>1.24</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R20" t="n">
         <v>1.12</v>
       </c>
       <c r="S20" t="n">
-        <v>1.02</v>
+        <v>1.47</v>
       </c>
       <c r="T20" t="n">
         <v>1.01</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -5689,16 +5689,16 @@
         <v>2.24</v>
       </c>
       <c r="H21" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="I21" t="n">
         <v>4.2</v>
       </c>
       <c r="J21" t="n">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="K21" t="n">
-        <v>4.1</v>
+        <v>950</v>
       </c>
       <c r="L21" t="n">
         <v>1.11</v>
@@ -5707,7 +5707,7 @@
         <v>1.06</v>
       </c>
       <c r="N21" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="O21" t="n">
         <v>1.26</v>
@@ -5716,25 +5716,25 @@
         <v>2.04</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="R21" t="n">
         <v>1.41</v>
       </c>
       <c r="S21" t="n">
-        <v>2.96</v>
+        <v>2.82</v>
       </c>
       <c r="T21" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="U21" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="V21" t="n">
         <v>1.31</v>
       </c>
       <c r="W21" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="X21" t="n">
         <v>18</v>
@@ -5743,10 +5743,10 @@
         <v>16.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="AA21" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AB21" t="n">
         <v>11.5</v>
@@ -5758,7 +5758,7 @@
         <v>16.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AF21" t="n">
         <v>15</v>
@@ -5776,73 +5776,73 @@
         <v>27</v>
       </c>
       <c r="AK21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL21" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AM21" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AN21" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AO21" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AP21" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC21" t="n">
         <v>6</v>
       </c>
-      <c r="AQ21" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>26</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA21" t="n">
+      <c r="BD21" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE21" t="n">
         <v>7.6</v>
       </c>
-      <c r="BB21" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>21</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BF21" t="n">
-        <v>9.800000000000001</v>
+        <v>5.3</v>
       </c>
       <c r="BG21" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BH21" t="n">
         <v>1000</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -5940,16 +5940,16 @@
         <v>1.28</v>
       </c>
       <c r="G22" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="H22" t="n">
         <v>7.2</v>
       </c>
       <c r="I22" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="J22" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="K22" t="n">
         <v>12</v>
@@ -5979,16 +5979,16 @@
         <v>1.93</v>
       </c>
       <c r="T22" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U22" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V22" t="n">
         <v>1.03</v>
       </c>
       <c r="W22" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="X22" t="n">
         <v>1000</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -6197,25 +6197,25 @@
         <v>1.18</v>
       </c>
       <c r="H23" t="n">
-        <v>24</v>
+        <v>18.5</v>
       </c>
       <c r="I23" t="n">
         <v>36</v>
       </c>
       <c r="J23" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="K23" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="L23" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M23" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N23" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="O23" t="n">
         <v>1.19</v>
@@ -6227,13 +6227,13 @@
         <v>1.56</v>
       </c>
       <c r="R23" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="S23" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="T23" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="U23" t="n">
         <v>1.47</v>
@@ -6242,16 +6242,16 @@
         <v>1.03</v>
       </c>
       <c r="W23" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="X23" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Y23" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="Z23" t="n">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="AA23" t="n">
         <v>1000</v>
@@ -6263,7 +6263,7 @@
         <v>22</v>
       </c>
       <c r="AD23" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AE23" t="n">
         <v>1000</v>
@@ -6272,13 +6272,13 @@
         <v>7.2</v>
       </c>
       <c r="AG23" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AI23" t="n">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="AJ23" t="n">
         <v>7.8</v>
@@ -6287,10 +6287,10 @@
         <v>17</v>
       </c>
       <c r="AL23" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AM23" t="n">
-        <v>520</v>
+        <v>510</v>
       </c>
       <c r="AN23" t="n">
         <v>3.85</v>
@@ -6299,7 +6299,7 @@
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AQ23" t="n">
         <v>1.01</v>
@@ -6311,10 +6311,10 @@
         <v>1.03</v>
       </c>
       <c r="AT23" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU23" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AV23" t="n">
         <v>1.01</v>
@@ -6323,10 +6323,10 @@
         <v>1.03</v>
       </c>
       <c r="AX23" t="n">
-        <v>5.9</v>
+        <v>1.03</v>
       </c>
       <c r="AY23" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ23" t="n">
         <v>1.01</v>
@@ -6335,86 +6335,86 @@
         <v>1.01</v>
       </c>
       <c r="BB23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>18</v>
+      </c>
+      <c r="BK23" t="n">
         <v>6.4</v>
       </c>
-      <c r="BC23" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH23" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BI23" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BJ23" t="n">
-        <v>25</v>
-      </c>
-      <c r="BK23" t="n">
-        <v>3.05</v>
-      </c>
       <c r="BL23" t="n">
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>3.45</v>
+        <v>9.6</v>
       </c>
       <c r="BN23" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="BO23" t="n">
-        <v>2.64</v>
+        <v>2.84</v>
       </c>
       <c r="BP23" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="BQ23" t="n">
-        <v>2.42</v>
+        <v>5</v>
       </c>
       <c r="BR23" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS23" t="n">
-        <v>3.2</v>
+        <v>7.4</v>
       </c>
       <c r="BT23" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BU23" t="n">
-        <v>3.15</v>
+        <v>7</v>
       </c>
       <c r="BV23" t="n">
         <v>1000</v>
       </c>
       <c r="BW23" t="n">
-        <v>3.45</v>
+        <v>9.6</v>
       </c>
       <c r="BX23" t="n">
         <v>1000</v>
       </c>
       <c r="BY23" t="n">
-        <v>3.45</v>
+        <v>9.4</v>
       </c>
       <c r="BZ23" t="n">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="CA23" t="n">
-        <v>2.68</v>
+        <v>4.7</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -6448,10 +6448,10 @@
         <v>1.62</v>
       </c>
       <c r="G24" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="H24" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="I24" t="n">
         <v>6.6</v>
@@ -6463,7 +6463,7 @@
         <v>4.8</v>
       </c>
       <c r="L24" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M24" t="n">
         <v>1.06</v>
@@ -6478,7 +6478,7 @@
         <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R24" t="n">
         <v>1.36</v>
@@ -6496,7 +6496,7 @@
         <v>1.18</v>
       </c>
       <c r="W24" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="X24" t="n">
         <v>17</v>
@@ -6532,7 +6532,7 @@
         <v>24</v>
       </c>
       <c r="AI24" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AJ24" t="n">
         <v>17</v>
@@ -6553,13 +6553,13 @@
         <v>130</v>
       </c>
       <c r="AP24" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AQ24" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AR24" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AS24" t="n">
         <v>9.199999999999999</v>
@@ -6595,7 +6595,7 @@
         <v>15</v>
       </c>
       <c r="BD24" t="n">
-        <v>7.6</v>
+        <v>28</v>
       </c>
       <c r="BE24" t="n">
         <v>9</v>
@@ -6610,22 +6610,22 @@
         <v>3.6</v>
       </c>
       <c r="BI24" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="BJ24" t="n">
         <v>11</v>
       </c>
       <c r="BK24" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BN24" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BO24" t="n">
         <v>3.7</v>
@@ -6634,41 +6634,41 @@
         <v>11.5</v>
       </c>
       <c r="BQ24" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BR24" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BS24" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BT24" t="n">
         <v>9.6</v>
       </c>
       <c r="BU24" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BV24" t="n">
         <v>55</v>
       </c>
       <c r="BW24" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BX24" t="n">
         <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BZ24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CA24" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -6699,7 +6699,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="G25" t="n">
         <v>2.06</v>
@@ -6867,7 +6867,7 @@
         <v>1.01</v>
       </c>
       <c r="BJ25" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK25" t="n">
         <v>1.01</v>
@@ -6879,50 +6879,50 @@
         <v>1.01</v>
       </c>
       <c r="BN25" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BO25" t="n">
         <v>1.01</v>
       </c>
       <c r="BP25" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BQ25" t="n">
         <v>1.01</v>
       </c>
       <c r="BR25" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BS25" t="n">
         <v>1.01</v>
       </c>
       <c r="BT25" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BU25" t="n">
         <v>1.01</v>
       </c>
       <c r="BV25" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW25" t="n">
         <v>1.01</v>
       </c>
       <c r="BX25" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY25" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ25" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="CA25" t="n">
         <v>1.01</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -6956,19 +6956,19 @@
         <v>1.42</v>
       </c>
       <c r="G26" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="H26" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="I26" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="K26" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L26" t="n">
         <v>1.01</v>
@@ -6977,7 +6977,7 @@
         <v>1.05</v>
       </c>
       <c r="N26" t="n">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="O26" t="n">
         <v>1.26</v>
@@ -6986,7 +6986,7 @@
         <v>2.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="R26" t="n">
         <v>1.43</v>
@@ -6998,13 +6998,13 @@
         <v>2</v>
       </c>
       <c r="U26" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="V26" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W26" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="X26" t="n">
         <v>21</v>
@@ -7013,13 +7013,13 @@
         <v>32</v>
       </c>
       <c r="Z26" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AA26" t="n">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="AB26" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AC26" t="n">
         <v>13</v>
@@ -7028,10 +7028,10 @@
         <v>38</v>
       </c>
       <c r="AE26" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AF26" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG26" t="n">
         <v>12</v>
@@ -7052,68 +7052,68 @@
         <v>44</v>
       </c>
       <c r="AM26" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AN26" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AO26" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AP26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AZ26" t="n">
         <v>4.7</v>
       </c>
-      <c r="AQ26" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BA26" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="BB26" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="BC26" t="n">
-        <v>13.5</v>
+        <v>4.3</v>
       </c>
       <c r="BD26" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BE26" t="n">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="BF26" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BG26" t="n">
         <v>5.5</v>
       </c>
-      <c r="BG26" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BH26" t="n">
         <v>1000</v>
       </c>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -7207,22 +7207,22 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="G27" t="n">
-        <v>2.34</v>
+        <v>2.14</v>
       </c>
       <c r="H27" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="I27" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="J27" t="n">
-        <v>2.54</v>
+        <v>3.2</v>
       </c>
       <c r="K27" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L27" t="n">
         <v>1.37</v>
@@ -7231,142 +7231,142 @@
         <v>1.09</v>
       </c>
       <c r="N27" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="O27" t="n">
         <v>1.41</v>
       </c>
       <c r="P27" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="R27" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S27" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="T27" t="n">
-        <v>1.68</v>
+        <v>1.94</v>
       </c>
       <c r="U27" t="n">
-        <v>1.64</v>
+        <v>1.89</v>
       </c>
       <c r="V27" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="W27" t="n">
-        <v>1.74</v>
+        <v>1.88</v>
       </c>
       <c r="X27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV27" t="n">
         <v>15.5</v>
       </c>
-      <c r="Y27" t="n">
-        <v>19</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>44</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>95</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AQ27" t="n">
+      <c r="AW27" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AX27" t="n">
         <v>10</v>
       </c>
-      <c r="AR27" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AY27" t="n">
-        <v>2.28</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ27" t="n">
-        <v>2.48</v>
+        <v>18</v>
       </c>
       <c r="BA27" t="n">
-        <v>2.64</v>
+        <v>9</v>
       </c>
       <c r="BB27" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BC27" t="n">
-        <v>2.5</v>
+        <v>21</v>
       </c>
       <c r="BD27" t="n">
-        <v>2.6</v>
+        <v>38</v>
       </c>
       <c r="BE27" t="n">
-        <v>2.7</v>
+        <v>9.4</v>
       </c>
       <c r="BF27" t="n">
-        <v>2.7</v>
+        <v>15</v>
       </c>
       <c r="BG27" t="n">
-        <v>2.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH27" t="n">
         <v>1000</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -7464,22 +7464,22 @@
         <v>2.1</v>
       </c>
       <c r="G28" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H28" t="n">
         <v>4.5</v>
       </c>
       <c r="I28" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J28" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="K28" t="n">
         <v>3.15</v>
       </c>
       <c r="L28" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="M28" t="n">
         <v>1.16</v>
@@ -7488,10 +7488,10 @@
         <v>2.28</v>
       </c>
       <c r="O28" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="P28" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="Q28" t="n">
         <v>3.1</v>
@@ -7512,7 +7512,7 @@
         <v>1.24</v>
       </c>
       <c r="W28" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="X28" t="n">
         <v>7.2</v>
@@ -7557,7 +7557,7 @@
         <v>36</v>
       </c>
       <c r="AL28" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AM28" t="n">
         <v>370</v>
@@ -7623,13 +7623,13 @@
         <v>13</v>
       </c>
       <c r="BH28" t="n">
-        <v>1000</v>
+        <v>2.48</v>
       </c>
       <c r="BI28" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="BJ28" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK28" t="n">
         <v>1.01</v>
@@ -7641,10 +7641,10 @@
         <v>1.01</v>
       </c>
       <c r="BN28" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BO28" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BP28" t="n">
         <v>1000</v>
@@ -7659,7 +7659,7 @@
         <v>1.01</v>
       </c>
       <c r="BT28" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BU28" t="n">
         <v>1.01</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -7715,13 +7715,13 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="G29" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="H29" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="I29" t="n">
         <v>3.35</v>
@@ -7733,28 +7733,28 @@
         <v>3.4</v>
       </c>
       <c r="L29" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M29" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N29" t="n">
-        <v>2.72</v>
+        <v>2.9</v>
       </c>
       <c r="O29" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P29" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R29" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="S29" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="T29" t="n">
         <v>1.59</v>
@@ -7763,127 +7763,127 @@
         <v>1.56</v>
       </c>
       <c r="V29" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W29" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="X29" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG29" t="n">
         <v>13</v>
       </c>
-      <c r="Z29" t="n">
-        <v>26</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD29" t="n">
+      <c r="AH29" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>44</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR29" t="n">
         <v>17.5</v>
       </c>
-      <c r="AE29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AS29" t="n">
-        <v>1.38</v>
+        <v>5.6</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.38</v>
+        <v>7.4</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.38</v>
+        <v>6.2</v>
       </c>
       <c r="AV29" t="n">
-        <v>1.27</v>
+        <v>12</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.38</v>
+        <v>5.4</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.38</v>
+        <v>13.5</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.26</v>
+        <v>10.5</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.31</v>
+        <v>18</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.38</v>
+        <v>5.5</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.38</v>
+        <v>5.4</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.38</v>
+        <v>5.3</v>
       </c>
       <c r="BD29" t="n">
-        <v>1.38</v>
+        <v>5.5</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.38</v>
+        <v>5.8</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.38</v>
+        <v>5.3</v>
       </c>
       <c r="BG29" t="n">
-        <v>1.38</v>
+        <v>5.4</v>
       </c>
       <c r="BH29" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="BI29" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="BJ29" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK29" t="n">
         <v>1.01</v>
@@ -7895,50 +7895,50 @@
         <v>1.01</v>
       </c>
       <c r="BN29" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BO29" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BP29" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ29" t="n">
         <v>1.01</v>
       </c>
       <c r="BR29" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS29" t="n">
         <v>1.01</v>
       </c>
       <c r="BT29" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU29" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BV29" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BW29" t="n">
         <v>1.01</v>
       </c>
       <c r="BX29" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY29" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ29" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="CA29" t="n">
         <v>1.01</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -7969,16 +7969,16 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="G30" t="n">
         <v>1.52</v>
       </c>
       <c r="H30" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="I30" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="J30" t="n">
         <v>5</v>
@@ -7996,10 +7996,10 @@
         <v>5.1</v>
       </c>
       <c r="O30" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P30" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="Q30" t="n">
         <v>1.63</v>
@@ -8008,10 +8008,10 @@
         <v>1.56</v>
       </c>
       <c r="S30" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="T30" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="U30" t="n">
         <v>2.1</v>
@@ -8074,7 +8074,7 @@
         <v>6.2</v>
       </c>
       <c r="AO30" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AP30" t="n">
         <v>20</v>
@@ -8086,7 +8086,7 @@
         <v>55</v>
       </c>
       <c r="AS30" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AT30" t="n">
         <v>9.4</v>
@@ -8098,7 +8098,7 @@
         <v>23</v>
       </c>
       <c r="AW30" t="n">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="AX30" t="n">
         <v>9</v>
@@ -8119,10 +8119,10 @@
         <v>13</v>
       </c>
       <c r="BD30" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BE30" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BF30" t="n">
         <v>5.5</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -8223,13 +8223,13 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="G31" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="H31" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I31" t="n">
         <v>7.2</v>
@@ -8238,7 +8238,7 @@
         <v>4</v>
       </c>
       <c r="K31" t="n">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="L31" t="n">
         <v>1.01</v>
@@ -8274,7 +8274,7 @@
         <v>1.16</v>
       </c>
       <c r="W31" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="X31" t="n">
         <v>1000</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -8480,19 +8480,19 @@
         <v>2.18</v>
       </c>
       <c r="G32" t="n">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="H32" t="n">
         <v>2.3</v>
       </c>
       <c r="I32" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="J32" t="n">
         <v>2.8</v>
       </c>
       <c r="K32" t="n">
-        <v>100</v>
+        <v>9.4</v>
       </c>
       <c r="L32" t="n">
         <v>1.01</v>
@@ -8525,10 +8525,10 @@
         <v>1.01</v>
       </c>
       <c r="V32" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W32" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="X32" t="n">
         <v>1000</v>
@@ -8639,10 +8639,10 @@
         <v>1.01</v>
       </c>
       <c r="BH32" t="n">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="BI32" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="BJ32" t="n">
         <v>1000</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -8743,7 +8743,7 @@
         <v>1000</v>
       </c>
       <c r="J33" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="K33" t="n">
         <v>1000</v>
@@ -8773,10 +8773,10 @@
         <v>1.24</v>
       </c>
       <c r="T33" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U33" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V33" t="n">
         <v>1.01</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -9015,7 +9015,7 @@
         <v>1.36</v>
       </c>
       <c r="P34" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q34" t="n">
         <v>2.04</v>
@@ -9027,7 +9027,7 @@
         <v>3.7</v>
       </c>
       <c r="T34" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U34" t="n">
         <v>1.99</v>
@@ -9039,7 +9039,7 @@
         <v>1.94</v>
       </c>
       <c r="X34" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y34" t="n">
         <v>15</v>
@@ -9051,7 +9051,7 @@
         <v>120</v>
       </c>
       <c r="AB34" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC34" t="n">
         <v>8.6</v>
@@ -9063,7 +9063,7 @@
         <v>75</v>
       </c>
       <c r="AF34" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG34" t="n">
         <v>11</v>
@@ -9075,7 +9075,7 @@
         <v>80</v>
       </c>
       <c r="AJ34" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK34" t="n">
         <v>24</v>
@@ -9099,10 +9099,10 @@
         <v>12</v>
       </c>
       <c r="AR34" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AS34" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT34" t="n">
         <v>7.2</v>
@@ -9126,7 +9126,7 @@
         <v>16.5</v>
       </c>
       <c r="BA34" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB34" t="n">
         <v>19.5</v>
@@ -9138,13 +9138,13 @@
         <v>28</v>
       </c>
       <c r="BE34" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BF34" t="n">
         <v>13</v>
       </c>
       <c r="BG34" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BH34" t="n">
         <v>3.25</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -9239,16 +9239,16 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="G35" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="H35" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I35" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J35" t="n">
         <v>3.5</v>
@@ -9269,31 +9269,31 @@
         <v>1.38</v>
       </c>
       <c r="P35" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="R35" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S35" t="n">
         <v>3.9</v>
       </c>
       <c r="T35" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="U35" t="n">
         <v>1.92</v>
       </c>
       <c r="V35" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="W35" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="X35" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y35" t="n">
         <v>14</v>
@@ -9344,7 +9344,7 @@
         <v>19</v>
       </c>
       <c r="AO35" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AP35" t="n">
         <v>10</v>
@@ -9356,7 +9356,7 @@
         <v>25</v>
       </c>
       <c r="AS35" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT35" t="n">
         <v>7.2</v>
@@ -9380,43 +9380,43 @@
         <v>17</v>
       </c>
       <c r="BA35" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB35" t="n">
         <v>21</v>
       </c>
       <c r="BC35" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD35" t="n">
         <v>34</v>
       </c>
       <c r="BE35" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF35" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG35" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH35" t="n">
         <v>3.25</v>
       </c>
       <c r="BI35" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="BJ35" t="n">
         <v>11</v>
       </c>
       <c r="BK35" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BL35" t="n">
         <v>1000</v>
       </c>
       <c r="BM35" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN35" t="n">
         <v>4.8</v>
@@ -9425,10 +9425,10 @@
         <v>3.7</v>
       </c>
       <c r="BP35" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BQ35" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BR35" t="n">
         <v>34</v>
@@ -9437,10 +9437,10 @@
         <v>8</v>
       </c>
       <c r="BT35" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BU35" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="BV35" t="n">
         <v>42</v>
@@ -9458,11 +9458,11 @@
         <v>32</v>
       </c>
       <c r="CA35" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -9496,28 +9496,28 @@
         <v>1.04</v>
       </c>
       <c r="G36" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="H36" t="n">
         <v>1.04</v>
       </c>
       <c r="I36" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J36" t="n">
         <v>1.01</v>
       </c>
       <c r="K36" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="L36" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="M36" t="n">
         <v>1.01</v>
       </c>
       <c r="N36" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="O36" t="n">
         <v>1.09</v>
@@ -9529,16 +9529,16 @@
         <v>1.09</v>
       </c>
       <c r="R36" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="S36" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="T36" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U36" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V36" t="n">
         <v>1.01</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -9750,19 +9750,19 @@
         <v>2.38</v>
       </c>
       <c r="G37" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="H37" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I37" t="n">
         <v>4.1</v>
       </c>
       <c r="J37" t="n">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="K37" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="L37" t="n">
         <v>1.01</v>
@@ -9777,7 +9777,7 @@
         <v>1.41</v>
       </c>
       <c r="P37" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="Q37" t="n">
         <v>2.22</v>
@@ -9789,16 +9789,16 @@
         <v>4.4</v>
       </c>
       <c r="T37" t="n">
-        <v>1.71</v>
+        <v>1.11</v>
       </c>
       <c r="U37" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="V37" t="n">
         <v>1.32</v>
       </c>
       <c r="W37" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X37" t="n">
         <v>11.5</v>
@@ -9810,7 +9810,7 @@
         <v>32</v>
       </c>
       <c r="AA37" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AB37" t="n">
         <v>11</v>
@@ -9822,7 +9822,7 @@
         <v>21</v>
       </c>
       <c r="AE37" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF37" t="n">
         <v>21</v>
@@ -9834,7 +9834,7 @@
         <v>30</v>
       </c>
       <c r="AI37" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AJ37" t="n">
         <v>50</v>
@@ -9855,58 +9855,58 @@
         <v>1000</v>
       </c>
       <c r="AP37" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AT37" t="n">
         <v>2.42</v>
       </c>
-      <c r="AQ37" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AS37" t="n">
+      <c r="AU37" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AW37" t="n">
         <v>2.96</v>
       </c>
-      <c r="AT37" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>2.94</v>
-      </c>
       <c r="AX37" t="n">
-        <v>10</v>
+        <v>2.7</v>
       </c>
       <c r="AY37" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="AZ37" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BA37" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="BB37" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="BC37" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="BD37" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="BE37" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BF37" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BG37" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BH37" t="n">
         <v>1000</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="G38" t="n">
         <v>3.25</v>
@@ -10010,10 +10010,10 @@
         <v>2.84</v>
       </c>
       <c r="I38" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="J38" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="K38" t="n">
         <v>3.1</v>
@@ -10025,13 +10025,13 @@
         <v>1.01</v>
       </c>
       <c r="N38" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="O38" t="n">
         <v>1.58</v>
       </c>
       <c r="P38" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="Q38" t="n">
         <v>2.8</v>
@@ -10040,16 +10040,16 @@
         <v>1.18</v>
       </c>
       <c r="S38" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="T38" t="n">
-        <v>2.06</v>
+        <v>1.83</v>
       </c>
       <c r="U38" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="V38" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W38" t="n">
         <v>1.44</v>
@@ -10061,7 +10061,7 @@
         <v>11.5</v>
       </c>
       <c r="Z38" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AA38" t="n">
         <v>85</v>
@@ -10073,7 +10073,7 @@
         <v>10</v>
       </c>
       <c r="AD38" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE38" t="n">
         <v>70</v>
@@ -10109,58 +10109,58 @@
         <v>1000</v>
       </c>
       <c r="AP38" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AU38" t="n">
         <v>2.08</v>
       </c>
-      <c r="AQ38" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AV38" t="n">
-        <v>10</v>
+        <v>2.34</v>
       </c>
       <c r="AW38" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BB38" t="n">
         <v>2.56</v>
       </c>
-      <c r="AX38" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BA38" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BB38" t="n">
-        <v>2.58</v>
-      </c>
       <c r="BC38" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="BD38" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="BE38" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="BF38" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="BG38" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="BH38" t="n">
         <v>1000</v>
@@ -10184,7 +10184,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BO38" t="n">
-        <v>3.9</v>
+        <v>1.36</v>
       </c>
       <c r="BP38" t="n">
         <v>44</v>
@@ -10202,7 +10202,7 @@
         <v>8</v>
       </c>
       <c r="BU38" t="n">
-        <v>3.9</v>
+        <v>1.35</v>
       </c>
       <c r="BV38" t="n">
         <v>44</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -10255,28 +10255,28 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="G39" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="H39" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="I39" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J39" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="K39" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="L39" t="n">
         <v>1.34</v>
       </c>
       <c r="M39" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N39" t="n">
         <v>4.7</v>
@@ -10285,145 +10285,145 @@
         <v>1.25</v>
       </c>
       <c r="P39" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="R39" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S39" t="n">
         <v>2.92</v>
       </c>
       <c r="T39" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="U39" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V39" t="n">
         <v>1.14</v>
       </c>
       <c r="W39" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="X39" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y39" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Z39" t="n">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="AA39" t="n">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="AB39" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AC39" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD39" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AE39" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="AF39" t="n">
         <v>9.4</v>
       </c>
       <c r="AG39" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH39" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AI39" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AJ39" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>130</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>23</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>46</v>
+      </c>
+      <c r="AS39" t="n">
         <v>13</v>
       </c>
-      <c r="AK39" t="n">
-        <v>16</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>170</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AT39" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU39" t="n">
         <v>10</v>
       </c>
       <c r="AV39" t="n">
-        <v>7.4</v>
+        <v>23</v>
       </c>
       <c r="AW39" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AX39" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY39" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ39" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BA39" t="n">
-        <v>8.800000000000001</v>
+        <v>65</v>
       </c>
       <c r="BB39" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BC39" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BD39" t="n">
-        <v>7.6</v>
+        <v>29</v>
       </c>
       <c r="BE39" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="BF39" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BG39" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="BH39" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="BI39" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BJ39" t="n">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="BK39" t="n">
         <v>7.2</v>
@@ -10435,31 +10435,31 @@
         <v>21</v>
       </c>
       <c r="BN39" t="n">
-        <v>5.3</v>
+        <v>4.1</v>
       </c>
       <c r="BO39" t="n">
-        <v>2.84</v>
+        <v>3.55</v>
       </c>
       <c r="BP39" t="n">
-        <v>12.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BQ39" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BR39" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="BS39" t="n">
         <v>15</v>
       </c>
       <c r="BT39" t="n">
-        <v>16</v>
+        <v>11.5</v>
       </c>
       <c r="BU39" t="n">
         <v>7.4</v>
       </c>
       <c r="BV39" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BW39" t="n">
         <v>21</v>
@@ -10471,14 +10471,14 @@
         <v>21</v>
       </c>
       <c r="BZ39" t="n">
-        <v>20</v>
+        <v>15.5</v>
       </c>
       <c r="CA39" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -10509,40 +10509,40 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="G40" t="n">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="H40" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="I40" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="J40" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="K40" t="n">
         <v>4</v>
       </c>
       <c r="L40" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M40" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N40" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="O40" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P40" t="n">
         <v>1.98</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R40" t="n">
         <v>1.39</v>
@@ -10551,28 +10551,28 @@
         <v>3.1</v>
       </c>
       <c r="T40" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="U40" t="n">
         <v>2.16</v>
       </c>
       <c r="V40" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="W40" t="n">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="X40" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y40" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Z40" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA40" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AB40" t="n">
         <v>12.5</v>
@@ -10581,10 +10581,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD40" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AE40" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF40" t="n">
         <v>16</v>
@@ -10593,7 +10593,7 @@
         <v>13</v>
       </c>
       <c r="AH40" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI40" t="n">
         <v>55</v>
@@ -10614,73 +10614,73 @@
         <v>17</v>
       </c>
       <c r="AO40" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AP40" t="n">
         <v>13.5</v>
       </c>
       <c r="AQ40" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV40" t="n">
         <v>13</v>
       </c>
-      <c r="AR40" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AS40" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AT40" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU40" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV40" t="n">
-        <v>14</v>
-      </c>
       <c r="AW40" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AX40" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY40" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ40" t="n">
         <v>14.5</v>
       </c>
       <c r="BA40" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB40" t="n">
         <v>4.3</v>
       </c>
-      <c r="BB40" t="n">
-        <v>21</v>
-      </c>
       <c r="BC40" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BD40" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BE40" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BF40" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BG40" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BH40" t="n">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="BI40" t="n">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="BJ40" t="n">
-        <v>13.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK40" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BL40" t="n">
         <v>1000</v>
@@ -10689,50 +10689,50 @@
         <v>21</v>
       </c>
       <c r="BN40" t="n">
-        <v>6.8</v>
+        <v>5.2</v>
       </c>
       <c r="BO40" t="n">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="BP40" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BQ40" t="n">
+        <v>11</v>
+      </c>
+      <c r="BR40" t="n">
+        <v>28</v>
+      </c>
+      <c r="BS40" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BT40" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BU40" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BV40" t="n">
+        <v>30</v>
+      </c>
+      <c r="BW40" t="n">
         <v>20</v>
       </c>
-      <c r="BQ40" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BR40" t="n">
-        <v>38</v>
-      </c>
-      <c r="BS40" t="n">
-        <v>16</v>
-      </c>
-      <c r="BT40" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BU40" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BV40" t="n">
-        <v>46</v>
-      </c>
-      <c r="BW40" t="n">
-        <v>18.5</v>
-      </c>
       <c r="BX40" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY40" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="BZ40" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="CA40" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -10763,7 +10763,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="G41" t="n">
         <v>4.5</v>
@@ -10772,16 +10772,16 @@
         <v>1.89</v>
       </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="J41" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K41" t="n">
         <v>4.2</v>
       </c>
       <c r="L41" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M41" t="n">
         <v>1.05</v>
@@ -10793,13 +10793,13 @@
         <v>1.27</v>
       </c>
       <c r="P41" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="R41" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S41" t="n">
         <v>2.96</v>
@@ -10811,7 +10811,7 @@
         <v>2.22</v>
       </c>
       <c r="V41" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="W41" t="n">
         <v>1.28</v>
@@ -10871,7 +10871,7 @@
         <v>11.5</v>
       </c>
       <c r="AP41" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AQ41" t="n">
         <v>9.199999999999999</v>
@@ -10880,10 +10880,10 @@
         <v>11</v>
       </c>
       <c r="AS41" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AT41" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AU41" t="n">
         <v>8</v>
@@ -10910,10 +10910,10 @@
         <v>10.5</v>
       </c>
       <c r="BC41" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="BD41" t="n">
-        <v>40</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE41" t="n">
         <v>10.5</v>
@@ -10925,22 +10925,22 @@
         <v>10</v>
       </c>
       <c r="BH41" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BI41" t="n">
-        <v>2.94</v>
+        <v>1.89</v>
       </c>
       <c r="BJ41" t="n">
         <v>13.5</v>
       </c>
       <c r="BK41" t="n">
-        <v>2.58</v>
+        <v>1.66</v>
       </c>
       <c r="BL41" t="n">
         <v>1000</v>
       </c>
       <c r="BM41" t="n">
-        <v>3.2</v>
+        <v>1.89</v>
       </c>
       <c r="BN41" t="n">
         <v>11</v>
@@ -10952,13 +10952,13 @@
         <v>48</v>
       </c>
       <c r="BQ41" t="n">
-        <v>3</v>
+        <v>1.82</v>
       </c>
       <c r="BR41" t="n">
         <v>1000</v>
       </c>
       <c r="BS41" t="n">
-        <v>3</v>
+        <v>1.83</v>
       </c>
       <c r="BT41" t="n">
         <v>6.6</v>
@@ -10970,23 +10970,23 @@
         <v>19</v>
       </c>
       <c r="BW41" t="n">
-        <v>2.74</v>
+        <v>1.72</v>
       </c>
       <c r="BX41" t="n">
         <v>36</v>
       </c>
       <c r="BY41" t="n">
-        <v>2.94</v>
+        <v>1.8</v>
       </c>
       <c r="BZ41" t="n">
         <v>29</v>
       </c>
       <c r="CA41" t="n">
-        <v>2.88</v>
+        <v>1.77</v>
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -11017,166 +11017,166 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="G42" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="H42" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="I42" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J42" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K42" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N42" t="n">
+        <v>4</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P42" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S42" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="X42" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA42" t="n">
         <v>110</v>
       </c>
-      <c r="J42" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K42" t="n">
-        <v>950</v>
-      </c>
-      <c r="L42" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M42" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N42" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="O42" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P42" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S42" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="T42" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="X42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>1000</v>
-      </c>
       <c r="AB42" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC42" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD42" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AE42" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF42" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG42" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH42" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI42" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AK42" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AL42" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM42" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN42" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AO42" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AS42" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AT42" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AU42" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AV42" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AW42" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AX42" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AY42" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AZ42" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BA42" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BC42" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BD42" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BG42" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BH42" t="n">
         <v>1000</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>
@@ -11271,43 +11271,43 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="G43" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="H43" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="I43" t="n">
-        <v>2.52</v>
+        <v>2.42</v>
       </c>
       <c r="J43" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K43" t="n">
         <v>4.1</v>
       </c>
       <c r="L43" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="M43" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N43" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="O43" t="n">
         <v>1.2</v>
       </c>
       <c r="P43" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="Q43" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R43" t="n">
         <v>1.61</v>
-      </c>
-      <c r="R43" t="n">
-        <v>1.6</v>
       </c>
       <c r="S43" t="n">
         <v>2.48</v>
@@ -11319,10 +11319,10 @@
         <v>2.6</v>
       </c>
       <c r="V43" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="W43" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="X43" t="n">
         <v>24</v>
@@ -11337,13 +11337,13 @@
         <v>34</v>
       </c>
       <c r="AB43" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AC43" t="n">
         <v>9.6</v>
       </c>
       <c r="AD43" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE43" t="n">
         <v>23</v>
@@ -11352,7 +11352,7 @@
         <v>24</v>
       </c>
       <c r="AG43" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH43" t="n">
         <v>15</v>
@@ -11361,7 +11361,7 @@
         <v>30</v>
       </c>
       <c r="AJ43" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AK43" t="n">
         <v>29</v>
@@ -11370,10 +11370,10 @@
         <v>34</v>
       </c>
       <c r="AM43" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN43" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AO43" t="n">
         <v>13.5</v>
@@ -11385,10 +11385,10 @@
         <v>13</v>
       </c>
       <c r="AR43" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AS43" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT43" t="n">
         <v>14.5</v>
@@ -11400,7 +11400,7 @@
         <v>10.5</v>
       </c>
       <c r="AW43" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AX43" t="n">
         <v>20</v>
@@ -11412,25 +11412,25 @@
         <v>13</v>
       </c>
       <c r="BA43" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>38</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BD43" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BB43" t="n">
+      <c r="BE43" t="n">
         <v>9.800000000000001</v>
-      </c>
-      <c r="BC43" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BD43" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BE43" t="n">
-        <v>10.5</v>
       </c>
       <c r="BF43" t="n">
         <v>14</v>
       </c>
       <c r="BG43" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BH43" t="n">
         <v>1000</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-16 00:33:30</t>
+          <t>2026-07-16 02:46:23</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-17.xlsx
@@ -869,16 +869,16 @@
         <v>2.14</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K2" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L2" t="n">
         <v>1.39</v>
       </c>
       <c r="M2" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N2" t="n">
         <v>4.1</v>
@@ -890,7 +890,7 @@
         <v>2.02</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="R2" t="n">
         <v>1.4</v>
@@ -902,7 +902,7 @@
         <v>1.77</v>
       </c>
       <c r="U2" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V2" t="n">
         <v>1.87</v>
@@ -911,10 +911,10 @@
         <v>1.33</v>
       </c>
       <c r="X2" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z2" t="n">
         <v>13.5</v>
@@ -932,13 +932,13 @@
         <v>11</v>
       </c>
       <c r="AE2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AG2" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AH2" t="n">
         <v>17.5</v>
@@ -953,7 +953,7 @@
         <v>46</v>
       </c>
       <c r="AL2" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM2" t="n">
         <v>90</v>
@@ -965,64 +965,64 @@
         <v>15</v>
       </c>
       <c r="AP2" t="n">
-        <v>7.8</v>
+        <v>13.5</v>
       </c>
       <c r="AQ2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS2" t="n">
         <v>9</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>9.199999999999999</v>
       </c>
       <c r="AT2" t="n">
         <v>13</v>
       </c>
       <c r="AU2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY2" t="n">
         <v>7.4</v>
       </c>
-      <c r="AV2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>19</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>14</v>
-      </c>
       <c r="AZ2" t="n">
-        <v>15.5</v>
+        <v>7.6</v>
       </c>
       <c r="BA2" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="BB2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>36</v>
+        <v>10.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="BE2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="BG2" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BH2" t="n">
         <v>3.55</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="BJ2" t="n">
         <v>9.4</v>
@@ -1034,7 +1034,7 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BN2" t="n">
         <v>7.2</v>
@@ -1043,7 +1043,7 @@
         <v>5.7</v>
       </c>
       <c r="BP2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BQ2" t="n">
         <v>23</v>
@@ -1058,10 +1058,10 @@
         <v>4.9</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BW2" t="n">
         <v>11</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -1111,230 +1111,230 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G3" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H3" t="n">
         <v>3.85</v>
       </c>
       <c r="I3" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="K3" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L3" t="n">
         <v>1.39</v>
       </c>
       <c r="M3" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="O3" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="P3" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="R3" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="T3" t="n">
-        <v>1.34</v>
+        <v>1.75</v>
       </c>
       <c r="U3" t="n">
-        <v>1.82</v>
+        <v>2.16</v>
       </c>
       <c r="V3" t="n">
         <v>1.33</v>
       </c>
       <c r="W3" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="BJ3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>16</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>29</v>
+      </c>
+      <c r="BS3" t="n">
         <v>9.4</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>28</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>2.66</v>
       </c>
       <c r="BT3" t="n">
         <v>7</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BV3" t="n">
         <v>29</v>
       </c>
       <c r="BW3" t="n">
-        <v>2.68</v>
+        <v>9.4</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.74</v>
+        <v>10</v>
       </c>
       <c r="BZ3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="CA3" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -1377,13 +1377,13 @@
         <v>2.04</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K4" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L4" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="M4" t="n">
         <v>1.07</v>
@@ -1392,22 +1392,22 @@
         <v>3.55</v>
       </c>
       <c r="O4" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P4" t="n">
         <v>1.87</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R4" t="n">
         <v>1.33</v>
       </c>
       <c r="S4" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U4" t="n">
         <v>2.04</v>
@@ -1419,10 +1419,10 @@
         <v>1.27</v>
       </c>
       <c r="X4" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="Z4" t="n">
         <v>14</v>
@@ -1431,7 +1431,7 @@
         <v>27</v>
       </c>
       <c r="AB4" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AC4" t="n">
         <v>8.4</v>
@@ -1473,122 +1473,122 @@
         <v>17</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.1</v>
+        <v>10.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AR4" t="n">
-        <v>3.95</v>
+        <v>10.5</v>
       </c>
       <c r="AS4" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BG4" t="n">
         <v>4.6</v>
       </c>
-      <c r="AT4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BH4" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BN4" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BP4" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BT4" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BV4" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -1622,13 +1622,13 @@
         <v>4.3</v>
       </c>
       <c r="G5" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="H5" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="I5" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="J5" t="n">
         <v>4</v>
@@ -1649,7 +1649,7 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="Q5" t="n">
         <v>1.58</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -1873,172 +1873,172 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="G6" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="H6" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="I6" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="J6" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K6" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L6" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="M6" t="n">
         <v>1.1</v>
       </c>
       <c r="N6" t="n">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="O6" t="n">
         <v>1.43</v>
       </c>
       <c r="P6" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="R6" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="S6" t="n">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="T6" t="n">
-        <v>1.63</v>
+        <v>1.98</v>
       </c>
       <c r="U6" t="n">
-        <v>1.42</v>
+        <v>1.83</v>
       </c>
       <c r="V6" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="W6" t="n">
         <v>1.24</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BH6" t="n">
         <v>3.05</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="BJ6" t="n">
         <v>11.5</v>
@@ -2050,7 +2050,7 @@
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>10</v>
+        <v>2.34</v>
       </c>
       <c r="BN6" t="n">
         <v>8</v>
@@ -2062,19 +2062,19 @@
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>8.4</v>
+        <v>2.26</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>9</v>
+        <v>2.3</v>
       </c>
       <c r="BT6" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="BV6" t="n">
         <v>16.5</v>
@@ -2086,17 +2086,17 @@
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>8.199999999999999</v>
+        <v>2.24</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>8.199999999999999</v>
+        <v>2.24</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="G7" t="n">
         <v>4.3</v>
@@ -2136,61 +2136,61 @@
         <v>2.18</v>
       </c>
       <c r="I7" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="J7" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="K7" t="n">
         <v>3.35</v>
       </c>
       <c r="L7" t="n">
-        <v>1.28</v>
+        <v>1.54</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N7" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Q7" t="n">
         <v>2.56</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.5</v>
       </c>
       <c r="R7" t="n">
         <v>1.19</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T7" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="U7" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="V7" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="W7" t="n">
         <v>1.3</v>
       </c>
       <c r="X7" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y7" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="Z7" t="n">
         <v>14</v>
       </c>
       <c r="AA7" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AB7" t="n">
         <v>11.5</v>
@@ -2220,7 +2220,7 @@
         <v>110</v>
       </c>
       <c r="AK7" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AL7" t="n">
         <v>100</v>
@@ -2241,10 +2241,10 @@
         <v>5.8</v>
       </c>
       <c r="AR7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS7" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AT7" t="n">
         <v>8.4</v>
@@ -2256,43 +2256,43 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW7" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AX7" t="n">
-        <v>20</v>
+        <v>6.6</v>
       </c>
       <c r="AY7" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BA7" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BB7" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BC7" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BD7" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BE7" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BF7" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BG7" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BH7" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.46</v>
+        <v>2.32</v>
       </c>
       <c r="BJ7" t="n">
         <v>12</v>
@@ -2307,50 +2307,50 @@
         <v>10</v>
       </c>
       <c r="BN7" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BO7" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BP7" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BQ7" t="n">
         <v>8.6</v>
       </c>
       <c r="BR7" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BS7" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT7" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BU7" t="n">
         <v>3.9</v>
       </c>
       <c r="BV7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BW7" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BX7" t="n">
         <v>44</v>
       </c>
       <c r="BY7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="CA7" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -2384,25 +2384,25 @@
         <v>1.44</v>
       </c>
       <c r="G8" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="H8" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="I8" t="n">
         <v>8.6</v>
       </c>
       <c r="J8" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="K8" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L8" t="n">
         <v>1.24</v>
       </c>
       <c r="M8" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N8" t="n">
         <v>5.2</v>
@@ -2411,64 +2411,64 @@
         <v>1.21</v>
       </c>
       <c r="P8" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="R8" t="n">
         <v>1.58</v>
       </c>
       <c r="S8" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="T8" t="n">
         <v>1.87</v>
       </c>
       <c r="U8" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="V8" t="n">
         <v>1.13</v>
       </c>
       <c r="W8" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="X8" t="n">
         <v>23</v>
       </c>
       <c r="Y8" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="Z8" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AB8" t="n">
         <v>10.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD8" t="n">
         <v>30</v>
       </c>
       <c r="AE8" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG8" t="n">
         <v>10</v>
       </c>
       <c r="AH8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI8" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
         <v>13</v>
@@ -2483,7 +2483,7 @@
         <v>120</v>
       </c>
       <c r="AN8" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AO8" t="n">
         <v>120</v>
@@ -2507,13 +2507,13 @@
         <v>11</v>
       </c>
       <c r="AV8" t="n">
-        <v>19.5</v>
+        <v>26</v>
       </c>
       <c r="AW8" t="n">
         <v>38</v>
       </c>
       <c r="AX8" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY8" t="n">
         <v>9.199999999999999</v>
@@ -2525,7 +2525,7 @@
         <v>36</v>
       </c>
       <c r="BB8" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BC8" t="n">
         <v>13</v>
@@ -2537,7 +2537,7 @@
         <v>40</v>
       </c>
       <c r="BF8" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BG8" t="n">
         <v>38</v>
@@ -2552,7 +2552,7 @@
         <v>11.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
@@ -2570,10 +2570,10 @@
         <v>8.6</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BR8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BS8" t="n">
         <v>7</v>
@@ -2582,29 +2582,29 @@
         <v>12.5</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
+        <v>9</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY8" t="n">
         <v>8.800000000000001</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>8.6</v>
       </c>
       <c r="BZ8" t="n">
         <v>13</v>
       </c>
       <c r="CA8" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -2635,25 +2635,25 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="G9" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="H9" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="I9" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="K9" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="L9" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="M9" t="n">
         <v>1.02</v>
@@ -2668,37 +2668,37 @@
         <v>3</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="R9" t="n">
         <v>1.83</v>
       </c>
       <c r="S9" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="T9" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="U9" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="V9" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W9" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="X9" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Y9" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Z9" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AA9" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AB9" t="n">
         <v>14.5</v>
@@ -2707,19 +2707,19 @@
         <v>14</v>
       </c>
       <c r="AD9" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AE9" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AF9" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI9" t="n">
         <v>75</v>
@@ -2734,88 +2734,88 @@
         <v>29</v>
       </c>
       <c r="AM9" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN9" t="n">
         <v>4.4</v>
       </c>
       <c r="AO9" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AP9" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AQ9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AV9" t="n">
         <v>8</v>
       </c>
-      <c r="AR9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AT9" t="n">
+      <c r="AW9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB9" t="n">
         <v>12</v>
       </c>
-      <c r="AU9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BC9" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BD9" t="n">
         <v>16</v>
       </c>
       <c r="BE9" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF9" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BG9" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH9" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BI9" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BJ9" t="n">
         <v>10.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN9" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BO9" t="n">
         <v>3.6</v>
@@ -2824,41 +2824,41 @@
         <v>8.6</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BR9" t="n">
         <v>19</v>
       </c>
       <c r="BS9" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BT9" t="n">
         <v>12</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BV9" t="n">
         <v>55</v>
       </c>
       <c r="BW9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BX9" t="n">
         <v>48</v>
       </c>
       <c r="BY9" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BZ9" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -2889,139 +2889,139 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="G10" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="H10" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="I10" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="J10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K10" t="n">
         <v>4.4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="M10" t="n">
         <v>1.02</v>
       </c>
       <c r="N10" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="O10" t="n">
         <v>1.13</v>
       </c>
       <c r="P10" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="R10" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="T10" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="U10" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="V10" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W10" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="X10" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Y10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z10" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AA10" t="n">
         <v>46</v>
       </c>
       <c r="AB10" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AC10" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AE10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF10" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AG10" t="n">
         <v>13.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AJ10" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>26</v>
+      </c>
+      <c r="AM10" t="n">
         <v>42</v>
       </c>
-      <c r="AK10" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL10" t="n">
+      <c r="AN10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS10" t="n">
         <v>25</v>
       </c>
-      <c r="AM10" t="n">
-        <v>46</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>7</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>7.2</v>
-      </c>
       <c r="AT10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU10" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AV10" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW10" t="n">
         <v>20</v>
       </c>
       <c r="AX10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY10" t="n">
         <v>11.5</v>
@@ -3030,61 +3030,61 @@
         <v>12</v>
       </c>
       <c r="BA10" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="BB10" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="BC10" t="n">
         <v>19.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>6.2</v>
+        <v>21</v>
       </c>
       <c r="BE10" t="n">
-        <v>7.2</v>
+        <v>24</v>
       </c>
       <c r="BF10" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG10" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BH10" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BI10" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BJ10" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BK10" t="n">
-        <v>6.4</v>
+        <v>4.9</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BN10" t="n">
         <v>6.6</v>
       </c>
       <c r="BO10" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="BP10" t="n">
         <v>16</v>
       </c>
       <c r="BQ10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BR10" t="n">
         <v>21</v>
       </c>
       <c r="BS10" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BT10" t="n">
         <v>6.8</v>
@@ -3093,16 +3093,16 @@
         <v>5.3</v>
       </c>
       <c r="BV10" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BW10" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BX10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BY10" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="G11" t="n">
         <v>2.74</v>
@@ -3170,13 +3170,13 @@
         <v>3</v>
       </c>
       <c r="O11" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P11" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="R11" t="n">
         <v>1.25</v>
@@ -3185,13 +3185,13 @@
         <v>4.2</v>
       </c>
       <c r="T11" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="U11" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V11" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W11" t="n">
         <v>1.57</v>
@@ -3209,7 +3209,7 @@
         <v>60</v>
       </c>
       <c r="AB11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AC11" t="n">
         <v>7.8</v>
@@ -3224,7 +3224,7 @@
         <v>17</v>
       </c>
       <c r="AG11" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH11" t="n">
         <v>21</v>
@@ -3248,7 +3248,7 @@
         <v>34</v>
       </c>
       <c r="AO11" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AP11" t="n">
         <v>9.4</v>
@@ -3260,7 +3260,7 @@
         <v>17.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AT11" t="n">
         <v>7.8</v>
@@ -3284,28 +3284,28 @@
         <v>16.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BB11" t="n">
         <v>32</v>
       </c>
       <c r="BC11" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BD11" t="n">
         <v>40</v>
       </c>
       <c r="BE11" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BF11" t="n">
-        <v>7.4</v>
+        <v>20</v>
       </c>
       <c r="BG11" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BH11" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BI11" t="n">
         <v>2.44</v>
@@ -3314,31 +3314,31 @@
         <v>10.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BN11" t="n">
         <v>5.7</v>
       </c>
       <c r="BO11" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BP11" t="n">
         <v>23</v>
       </c>
       <c r="BQ11" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BR11" t="n">
         <v>40</v>
       </c>
       <c r="BS11" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT11" t="n">
         <v>6.4</v>
@@ -3350,23 +3350,23 @@
         <v>28</v>
       </c>
       <c r="BW11" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BX11" t="n">
         <v>44</v>
       </c>
       <c r="BY11" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BZ11" t="n">
         <v>38</v>
       </c>
       <c r="CA11" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -3400,19 +3400,19 @@
         <v>5.3</v>
       </c>
       <c r="G12" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="H12" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="I12" t="n">
         <v>1.65</v>
       </c>
       <c r="J12" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="K12" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -3427,7 +3427,7 @@
         <v>1.2</v>
       </c>
       <c r="P12" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="Q12" t="n">
         <v>1.58</v>
@@ -3436,7 +3436,7 @@
         <v>1.55</v>
       </c>
       <c r="S12" t="n">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="T12" t="n">
         <v>1.7</v>
@@ -3448,7 +3448,7 @@
         <v>2.52</v>
       </c>
       <c r="W12" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X12" t="n">
         <v>25</v>
@@ -3493,13 +3493,13 @@
         <v>85</v>
       </c>
       <c r="AL12" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AM12" t="n">
         <v>100</v>
       </c>
       <c r="AN12" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AO12" t="n">
         <v>6.8</v>
@@ -3508,109 +3508,109 @@
         <v>6.8</v>
       </c>
       <c r="AQ12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AV12" t="n">
         <v>5.1</v>
       </c>
-      <c r="AR12" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>5</v>
-      </c>
       <c r="AW12" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AX12" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AY12" t="n">
         <v>6.8</v>
       </c>
       <c r="AZ12" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BA12" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BB12" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BC12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BD12" t="n">
         <v>8.4</v>
       </c>
-      <c r="BD12" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BE12" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF12" t="n">
         <v>8.4</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BH12" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK12" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="BN12" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT12" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BU12" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BV12" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BX12" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BZ12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="G13" t="n">
         <v>7</v>
@@ -3669,19 +3669,19 @@
         <v>4.4</v>
       </c>
       <c r="L13" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="M13" t="n">
         <v>1.07</v>
       </c>
       <c r="N13" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O13" t="n">
         <v>1.32</v>
       </c>
       <c r="P13" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="Q13" t="n">
         <v>1.94</v>
@@ -3711,7 +3711,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="Z13" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AA13" t="n">
         <v>17.5</v>
@@ -3729,7 +3729,7 @@
         <v>19.5</v>
       </c>
       <c r="AF13" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AG13" t="n">
         <v>25</v>
@@ -3738,7 +3738,7 @@
         <v>24</v>
       </c>
       <c r="AI13" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AJ13" t="n">
         <v>220</v>
@@ -3759,122 +3759,122 @@
         <v>11.5</v>
       </c>
       <c r="AP13" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AQ13" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AR13" t="n">
         <v>4.8</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AT13" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AU13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>8</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>9</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BT13" t="n">
         <v>4.3</v>
       </c>
-      <c r="AV13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>6</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>1000</v>
-      </c>
       <c r="BU13" t="n">
-        <v>1.27</v>
+        <v>3.65</v>
       </c>
       <c r="BV13" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.46</v>
+        <v>5.6</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BZ13" t="n">
         <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -3929,13 +3929,13 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="O14" t="n">
         <v>1.1</v>
       </c>
       <c r="P14" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="Q14" t="n">
         <v>1.31</v>
@@ -3971,13 +3971,13 @@
         <v>290</v>
       </c>
       <c r="AB14" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AD14" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AE14" t="n">
         <v>120</v>
@@ -3992,7 +3992,7 @@
         <v>27</v>
       </c>
       <c r="AI14" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AJ14" t="n">
         <v>15</v>
@@ -4004,67 +4004,67 @@
         <v>30</v>
       </c>
       <c r="AM14" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AN14" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AO14" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AP14" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AV14" t="n">
         <v>5.5</v>
       </c>
-      <c r="AQ14" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AS14" t="n">
+      <c r="AW14" t="n">
         <v>6</v>
       </c>
-      <c r="AT14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>5.8</v>
-      </c>
       <c r="AX14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY14" t="n">
         <v>4.3</v>
       </c>
-      <c r="AY14" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AZ14" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BA14" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BC14" t="n">
         <v>4.4</v>
       </c>
       <c r="BD14" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BE14" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BF14" t="n">
         <v>3</v>
       </c>
       <c r="BG14" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BH14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
         <v>1.99</v>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="H15" t="n">
         <v>3.95</v>
@@ -4183,25 +4183,25 @@
         <v>1.05</v>
       </c>
       <c r="N15" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O15" t="n">
         <v>1.24</v>
       </c>
       <c r="P15" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="Q15" t="n">
         <v>1.72</v>
       </c>
       <c r="R15" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="S15" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="T15" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="U15" t="n">
         <v>2.36</v>
@@ -4210,31 +4210,31 @@
         <v>1.32</v>
       </c>
       <c r="W15" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="X15" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="Y15" t="n">
         <v>18.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AA15" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AB15" t="n">
         <v>12</v>
       </c>
       <c r="AC15" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD15" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AF15" t="n">
         <v>14</v>
@@ -4246,7 +4246,7 @@
         <v>17.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AJ15" t="n">
         <v>24</v>
@@ -4264,19 +4264,19 @@
         <v>11</v>
       </c>
       <c r="AO15" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AP15" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AQ15" t="n">
         <v>16</v>
       </c>
       <c r="AR15" t="n">
-        <v>22</v>
+        <v>8.4</v>
       </c>
       <c r="AS15" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AT15" t="n">
         <v>10.5</v>
@@ -4288,7 +4288,7 @@
         <v>14.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>8.6</v>
+        <v>29</v>
       </c>
       <c r="AX15" t="n">
         <v>12</v>
@@ -4300,25 +4300,25 @@
         <v>14.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>8.6</v>
+        <v>30</v>
       </c>
       <c r="BB15" t="n">
         <v>19.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BD15" t="n">
-        <v>7.8</v>
+        <v>22</v>
       </c>
       <c r="BE15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BF15" t="n">
         <v>9.4</v>
       </c>
       <c r="BG15" t="n">
-        <v>8.199999999999999</v>
+        <v>27</v>
       </c>
       <c r="BH15" t="n">
         <v>4.1</v>
@@ -4327,28 +4327,28 @@
         <v>3.1</v>
       </c>
       <c r="BJ15" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BK15" t="n">
-        <v>7</v>
+        <v>4.9</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN15" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BO15" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="BP15" t="n">
         <v>14</v>
       </c>
       <c r="BQ15" t="n">
-        <v>9.800000000000001</v>
+        <v>5.9</v>
       </c>
       <c r="BR15" t="n">
         <v>25</v>
@@ -4360,19 +4360,19 @@
         <v>7.8</v>
       </c>
       <c r="BU15" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BV15" t="n">
         <v>32</v>
       </c>
       <c r="BW15" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BX15" t="n">
         <v>38</v>
       </c>
       <c r="BY15" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BZ15" t="n">
         <v>19</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -4431,58 +4431,58 @@
         <v>4.3</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M16" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N16" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="O16" t="n">
         <v>1.23</v>
       </c>
       <c r="P16" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R16" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="S16" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="T16" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="U16" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V16" t="n">
         <v>1.28</v>
       </c>
       <c r="W16" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="X16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y16" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Z16" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AA16" t="n">
         <v>100</v>
       </c>
       <c r="AB16" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AC16" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AD16" t="n">
         <v>18</v>
@@ -4497,16 +4497,16 @@
         <v>11</v>
       </c>
       <c r="AH16" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI16" t="n">
         <v>60</v>
       </c>
       <c r="AJ16" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AK16" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AL16" t="n">
         <v>34</v>
@@ -4521,28 +4521,28 @@
         <v>48</v>
       </c>
       <c r="AP16" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AQ16" t="n">
         <v>17</v>
       </c>
       <c r="AR16" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AS16" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="AT16" t="n">
         <v>10</v>
       </c>
       <c r="AU16" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV16" t="n">
         <v>15</v>
       </c>
       <c r="AW16" t="n">
-        <v>6.8</v>
+        <v>40</v>
       </c>
       <c r="AX16" t="n">
         <v>11</v>
@@ -4554,7 +4554,7 @@
         <v>14.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB16" t="n">
         <v>18</v>
@@ -4563,80 +4563,80 @@
         <v>15.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BE16" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF16" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG16" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BH16" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.04</v>
+        <v>3.25</v>
       </c>
       <c r="BJ16" t="n">
-        <v>12.5</v>
+        <v>9.6</v>
       </c>
       <c r="BK16" t="n">
-        <v>1.75</v>
+        <v>4.9</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>2.04</v>
+        <v>9</v>
       </c>
       <c r="BN16" t="n">
-        <v>6.4</v>
+        <v>5</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BP16" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.82</v>
+        <v>5.7</v>
       </c>
       <c r="BR16" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.92</v>
+        <v>7</v>
       </c>
       <c r="BT16" t="n">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU16" t="n">
-        <v>1.69</v>
+        <v>6</v>
       </c>
       <c r="BV16" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.95</v>
+        <v>7.8</v>
       </c>
       <c r="BX16" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.96</v>
+        <v>8</v>
       </c>
       <c r="BZ16" t="n">
-        <v>25</v>
+        <v>18.5</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.89</v>
+        <v>13</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -4676,28 +4676,28 @@
         <v>18</v>
       </c>
       <c r="I17" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="J17" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="K17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N17" t="n">
         <v>9.6</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N17" t="n">
-        <v>9.4</v>
       </c>
       <c r="O17" t="n">
         <v>1.1</v>
       </c>
       <c r="P17" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="Q17" t="n">
         <v>1.31</v>
@@ -4706,10 +4706,10 @@
         <v>2.18</v>
       </c>
       <c r="S17" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="T17" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="U17" t="n">
         <v>2.06</v>
@@ -4721,7 +4721,7 @@
         <v>1.01</v>
       </c>
       <c r="X17" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
         <v>1000</v>
@@ -4733,37 +4733,37 @@
         <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AD17" t="n">
-        <v>70</v>
+        <v>540</v>
       </c>
       <c r="AE17" t="n">
         <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG17" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="AI17" t="n">
         <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AK17" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AL17" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AM17" t="n">
         <v>1000</v>
@@ -4775,7 +4775,7 @@
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="AQ17" t="n">
         <v>34</v>
@@ -4790,7 +4790,7 @@
         <v>14.5</v>
       </c>
       <c r="AU17" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AV17" t="n">
         <v>29</v>
@@ -4799,13 +4799,13 @@
         <v>48</v>
       </c>
       <c r="AX17" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY17" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ17" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="BA17" t="n">
         <v>42</v>
@@ -4817,19 +4817,19 @@
         <v>11.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BE17" t="n">
         <v>42</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="BG17" t="n">
         <v>46</v>
       </c>
       <c r="BH17" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BI17" t="n">
         <v>4.8</v>
@@ -4838,59 +4838,59 @@
         <v>12.5</v>
       </c>
       <c r="BK17" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BN17" t="n">
         <v>4.3</v>
       </c>
       <c r="BO17" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="BP17" t="n">
         <v>6.2</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.6</v>
+        <v>4.7</v>
       </c>
       <c r="BR17" t="n">
         <v>17.5</v>
       </c>
       <c r="BS17" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BT17" t="n">
         <v>17.5</v>
       </c>
       <c r="BU17" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BZ17" t="n">
         <v>6.2</v>
       </c>
       <c r="CA17" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -4930,211 +4930,211 @@
         <v>3.4</v>
       </c>
       <c r="I18" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="J18" t="n">
         <v>3.2</v>
       </c>
       <c r="K18" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="L18" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M18" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N18" t="n">
         <v>3</v>
       </c>
       <c r="O18" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="P18" t="n">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R18" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="S18" t="n">
-        <v>3.7</v>
+        <v>2.22</v>
       </c>
       <c r="T18" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="U18" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V18" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W18" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="X18" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Y18" t="n">
         <v>13</v>
       </c>
       <c r="Z18" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AA18" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AB18" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AC18" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD18" t="n">
         <v>17.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH18" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI18" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AJ18" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN18" t="n">
         <v>34</v>
       </c>
-      <c r="AK18" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>27</v>
-      </c>
       <c r="AO18" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>4.3</v>
+        <v>2</v>
       </c>
       <c r="AQ18" t="n">
-        <v>4.4</v>
+        <v>1.74</v>
       </c>
       <c r="AR18" t="n">
-        <v>5.4</v>
+        <v>2</v>
       </c>
       <c r="AS18" t="n">
-        <v>6.2</v>
+        <v>1.97</v>
       </c>
       <c r="AT18" t="n">
-        <v>3.85</v>
+        <v>1.7</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.55</v>
+        <v>1.63</v>
       </c>
       <c r="AV18" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="AW18" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AX18" t="n">
-        <v>4.6</v>
+        <v>1.8</v>
       </c>
       <c r="AY18" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="AZ18" t="n">
-        <v>5.2</v>
+        <v>2</v>
       </c>
       <c r="BA18" t="n">
-        <v>6</v>
+        <v>1.96</v>
       </c>
       <c r="BB18" t="n">
-        <v>5.6</v>
+        <v>1.91</v>
       </c>
       <c r="BC18" t="n">
-        <v>5.5</v>
+        <v>1.9</v>
       </c>
       <c r="BD18" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BE18" t="n">
-        <v>6.4</v>
+        <v>2</v>
       </c>
       <c r="BF18" t="n">
-        <v>5.3</v>
+        <v>1.9</v>
       </c>
       <c r="BG18" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BH18" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BI18" t="n">
         <v>2.52</v>
       </c>
       <c r="BJ18" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK18" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="BN18" t="n">
         <v>5.1</v>
       </c>
       <c r="BO18" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="BP18" t="n">
         <v>19</v>
       </c>
       <c r="BQ18" t="n">
-        <v>7</v>
+        <v>2.18</v>
       </c>
       <c r="BR18" t="n">
         <v>38</v>
       </c>
       <c r="BS18" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="BT18" t="n">
         <v>7</v>
       </c>
       <c r="BU18" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BV18" t="n">
         <v>34</v>
       </c>
       <c r="BW18" t="n">
-        <v>8.6</v>
+        <v>2.3</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="BZ18" t="n">
         <v>0</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -5175,22 +5175,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G19" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I19" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J19" t="n">
         <v>1.02</v>
       </c>
       <c r="K19" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
@@ -5199,28 +5199,28 @@
         <v>1.01</v>
       </c>
       <c r="N19" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P19" t="n">
         <v>1.25</v>
       </c>
-      <c r="O19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1.24</v>
-      </c>
       <c r="Q19" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R19" t="n">
         <v>1.12</v>
       </c>
       <c r="S19" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="T19" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U19" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V19" t="n">
         <v>1.01</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -5429,22 +5429,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G20" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I20" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J20" t="n">
         <v>1.02</v>
       </c>
       <c r="K20" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="L20" t="n">
         <v>1.01</v>
@@ -5453,13 +5453,13 @@
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O20" t="n">
         <v>1.01</v>
       </c>
       <c r="P20" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q20" t="n">
         <v>1.02</v>
@@ -5468,7 +5468,7 @@
         <v>1.12</v>
       </c>
       <c r="S20" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="T20" t="n">
         <v>1.01</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -5689,52 +5689,52 @@
         <v>2.24</v>
       </c>
       <c r="H21" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="I21" t="n">
         <v>4.2</v>
       </c>
       <c r="J21" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="K21" t="n">
-        <v>950</v>
+        <v>4.1</v>
       </c>
       <c r="L21" t="n">
         <v>1.11</v>
       </c>
       <c r="M21" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N21" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="O21" t="n">
         <v>1.26</v>
       </c>
       <c r="P21" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="R21" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S21" t="n">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="T21" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="U21" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="V21" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W21" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="X21" t="n">
         <v>18</v>
@@ -5746,7 +5746,7 @@
         <v>42</v>
       </c>
       <c r="AA21" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AB21" t="n">
         <v>11.5</v>
@@ -5776,7 +5776,7 @@
         <v>27</v>
       </c>
       <c r="AK21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL21" t="n">
         <v>40</v>
@@ -5785,64 +5785,64 @@
         <v>100</v>
       </c>
       <c r="AN21" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AO21" t="n">
         <v>48</v>
       </c>
       <c r="AP21" t="n">
-        <v>5.7</v>
+        <v>14.5</v>
       </c>
       <c r="AQ21" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF21" t="n">
         <v>5.5</v>
       </c>
-      <c r="AR21" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BG21" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BH21" t="n">
         <v>1000</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -5937,43 +5937,43 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="G22" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="H22" t="n">
         <v>7.2</v>
       </c>
       <c r="I22" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="J22" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="K22" t="n">
-        <v>12</v>
+        <v>6.4</v>
       </c>
       <c r="L22" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M22" t="n">
         <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>2.34</v>
+        <v>1.1</v>
       </c>
       <c r="O22" t="n">
         <v>1.16</v>
       </c>
       <c r="P22" t="n">
-        <v>2.34</v>
+        <v>1.25</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.44</v>
+        <v>1.2</v>
       </c>
       <c r="R22" t="n">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="S22" t="n">
         <v>1.93</v>
@@ -5985,182 +5985,182 @@
         <v>1.11</v>
       </c>
       <c r="V22" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="W22" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>19</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BO22" t="n">
         <v>3.1</v>
       </c>
-      <c r="X22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO22" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BP22" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BQ22" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BR22" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BS22" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BT22" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BU22" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BV22" t="n">
         <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX22" t="n">
         <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ22" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="CA22" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -6197,46 +6197,46 @@
         <v>1.18</v>
       </c>
       <c r="H23" t="n">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="I23" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J23" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="L23" t="n">
         <v>1.24</v>
       </c>
       <c r="M23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O23" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P23" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="R23" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S23" t="n">
         <v>2.38</v>
       </c>
       <c r="T23" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="U23" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="V23" t="n">
         <v>1.03</v>
@@ -6245,10 +6245,10 @@
         <v>6.2</v>
       </c>
       <c r="X23" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Y23" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="Z23" t="n">
         <v>380</v>
@@ -6278,10 +6278,10 @@
         <v>65</v>
       </c>
       <c r="AI23" t="n">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="AJ23" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AK23" t="n">
         <v>17</v>
@@ -6293,67 +6293,67 @@
         <v>510</v>
       </c>
       <c r="AN23" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AO23" t="n">
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BD23" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF23" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BH23" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BI23" t="n">
         <v>3.95</v>
@@ -6362,59 +6362,59 @@
         <v>18</v>
       </c>
       <c r="BK23" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>9.6</v>
+        <v>3</v>
       </c>
       <c r="BN23" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BO23" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="BP23" t="n">
         <v>6.2</v>
       </c>
       <c r="BQ23" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="BR23" t="n">
         <v>1000</v>
       </c>
       <c r="BS23" t="n">
-        <v>7.4</v>
+        <v>2.8</v>
       </c>
       <c r="BT23" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BU23" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BV23" t="n">
         <v>1000</v>
       </c>
       <c r="BW23" t="n">
-        <v>9.6</v>
+        <v>3</v>
       </c>
       <c r="BX23" t="n">
         <v>1000</v>
       </c>
       <c r="BY23" t="n">
-        <v>9.4</v>
+        <v>3</v>
       </c>
       <c r="BZ23" t="n">
         <v>9</v>
       </c>
       <c r="CA23" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -6445,13 +6445,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="G24" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="H24" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I24" t="n">
         <v>6.6</v>
@@ -6460,10 +6460,10 @@
         <v>4.1</v>
       </c>
       <c r="K24" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="L24" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="M24" t="n">
         <v>1.06</v>
@@ -6475,10 +6475,10 @@
         <v>1.3</v>
       </c>
       <c r="P24" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="R24" t="n">
         <v>1.36</v>
@@ -6487,7 +6487,7 @@
         <v>3.25</v>
       </c>
       <c r="T24" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="U24" t="n">
         <v>1.91</v>
@@ -6496,7 +6496,7 @@
         <v>1.18</v>
       </c>
       <c r="W24" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="X24" t="n">
         <v>17</v>
@@ -6523,7 +6523,7 @@
         <v>100</v>
       </c>
       <c r="AF24" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AG24" t="n">
         <v>10.5</v>
@@ -6532,7 +6532,7 @@
         <v>24</v>
       </c>
       <c r="AI24" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AJ24" t="n">
         <v>17</v>
@@ -6553,58 +6553,58 @@
         <v>130</v>
       </c>
       <c r="AP24" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AQ24" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AR24" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AS24" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT24" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU24" t="n">
         <v>8.4</v>
       </c>
       <c r="AV24" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AX24" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AY24" t="n">
         <v>8.4</v>
       </c>
       <c r="AZ24" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA24" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB24" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BC24" t="n">
         <v>15</v>
       </c>
       <c r="BD24" t="n">
-        <v>28</v>
+        <v>7.4</v>
       </c>
       <c r="BE24" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BF24" t="n">
         <v>8.6</v>
       </c>
       <c r="BG24" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BH24" t="n">
         <v>3.6</v>
@@ -6616,16 +6616,16 @@
         <v>11</v>
       </c>
       <c r="BK24" t="n">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BN24" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BO24" t="n">
         <v>3.7</v>
@@ -6634,41 +6634,41 @@
         <v>11.5</v>
       </c>
       <c r="BQ24" t="n">
-        <v>5.9</v>
+        <v>8.4</v>
       </c>
       <c r="BR24" t="n">
         <v>27</v>
       </c>
       <c r="BS24" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BT24" t="n">
         <v>9.6</v>
       </c>
       <c r="BU24" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="BV24" t="n">
         <v>55</v>
       </c>
       <c r="BW24" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BX24" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY24" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BZ24" t="n">
         <v>21</v>
       </c>
       <c r="CA24" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -6711,58 +6711,58 @@
         <v>4.3</v>
       </c>
       <c r="J25" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="K25" t="n">
         <v>4.8</v>
       </c>
       <c r="L25" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M25" t="n">
         <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="O25" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P25" t="n">
         <v>2.58</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="R25" t="n">
         <v>1.65</v>
       </c>
       <c r="S25" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="T25" t="n">
         <v>1.52</v>
       </c>
       <c r="U25" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="V25" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W25" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="X25" t="n">
         <v>32</v>
       </c>
       <c r="Y25" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Z25" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AA25" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AB25" t="n">
         <v>17</v>
@@ -6771,10 +6771,10 @@
         <v>12.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AF25" t="n">
         <v>18</v>
@@ -6786,7 +6786,7 @@
         <v>18</v>
       </c>
       <c r="AI25" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AJ25" t="n">
         <v>27</v>
@@ -6804,125 +6804,125 @@
         <v>8.6</v>
       </c>
       <c r="AO25" t="n">
+        <v>30</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>9</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>9</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>13</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>21</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BT25" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BV25" t="n">
         <v>28</v>
       </c>
-      <c r="AP25" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>5</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>4</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BG25" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BH25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ25" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN25" t="n">
-        <v>7</v>
-      </c>
-      <c r="BO25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP25" t="n">
-        <v>17</v>
-      </c>
-      <c r="BQ25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR25" t="n">
-        <v>29</v>
-      </c>
-      <c r="BS25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT25" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BU25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV25" t="n">
-        <v>38</v>
-      </c>
       <c r="BW25" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BX25" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BY25" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BZ25" t="n">
-        <v>19</v>
+        <v>14.5</v>
       </c>
       <c r="CA25" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -6956,19 +6956,19 @@
         <v>1.42</v>
       </c>
       <c r="G26" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="H26" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="I26" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="K26" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L26" t="n">
         <v>1.01</v>
@@ -6977,7 +6977,7 @@
         <v>1.05</v>
       </c>
       <c r="N26" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="O26" t="n">
         <v>1.26</v>
@@ -6986,7 +6986,7 @@
         <v>2.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="R26" t="n">
         <v>1.43</v>
@@ -6998,13 +6998,13 @@
         <v>2</v>
       </c>
       <c r="U26" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="V26" t="n">
         <v>1.11</v>
       </c>
       <c r="W26" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="X26" t="n">
         <v>21</v>
@@ -7013,10 +7013,10 @@
         <v>32</v>
       </c>
       <c r="Z26" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AA26" t="n">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="AB26" t="n">
         <v>9.6</v>
@@ -7028,7 +7028,7 @@
         <v>38</v>
       </c>
       <c r="AE26" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AF26" t="n">
         <v>8.800000000000001</v>
@@ -7052,13 +7052,13 @@
         <v>44</v>
       </c>
       <c r="AM26" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AN26" t="n">
         <v>8</v>
       </c>
       <c r="AO26" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AP26" t="n">
         <v>4.4</v>
@@ -7070,46 +7070,46 @@
         <v>5.3</v>
       </c>
       <c r="AS26" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AT26" t="n">
         <v>3.55</v>
       </c>
       <c r="AU26" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AV26" t="n">
         <v>4.9</v>
       </c>
       <c r="AW26" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AX26" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AY26" t="n">
-        <v>3.8</v>
+        <v>9</v>
       </c>
       <c r="AZ26" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BA26" t="n">
         <v>5.4</v>
       </c>
       <c r="BB26" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BC26" t="n">
-        <v>4.3</v>
+        <v>13.5</v>
       </c>
       <c r="BD26" t="n">
         <v>5</v>
       </c>
       <c r="BE26" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BF26" t="n">
-        <v>3.3</v>
+        <v>5.5</v>
       </c>
       <c r="BG26" t="n">
         <v>5.5</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -7207,58 +7207,58 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="G27" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H27" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I27" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J27" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K27" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L27" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="M27" t="n">
         <v>1.09</v>
       </c>
       <c r="N27" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O27" t="n">
         <v>1.41</v>
       </c>
       <c r="P27" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="Q27" t="n">
         <v>2.2</v>
       </c>
       <c r="R27" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S27" t="n">
         <v>4.1</v>
       </c>
       <c r="T27" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U27" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="V27" t="n">
         <v>1.26</v>
       </c>
       <c r="W27" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="X27" t="n">
         <v>11.5</v>
@@ -7273,43 +7273,43 @@
         <v>130</v>
       </c>
       <c r="AB27" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AC27" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="AF27" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG27" t="n">
         <v>11</v>
       </c>
       <c r="AH27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI27" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AJ27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL27" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AM27" t="n">
         <v>160</v>
       </c>
       <c r="AN27" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AO27" t="n">
         <v>110</v>
@@ -7321,10 +7321,10 @@
         <v>11.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS27" t="n">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="AT27" t="n">
         <v>6.8</v>
@@ -7336,7 +7336,7 @@
         <v>15.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AX27" t="n">
         <v>10</v>
@@ -7348,7 +7348,7 @@
         <v>18</v>
       </c>
       <c r="BA27" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BB27" t="n">
         <v>21</v>
@@ -7357,25 +7357,25 @@
         <v>21</v>
       </c>
       <c r="BD27" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="BE27" t="n">
-        <v>9.4</v>
+        <v>12</v>
       </c>
       <c r="BF27" t="n">
         <v>15</v>
       </c>
       <c r="BG27" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BH27" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="BI27" t="n">
-        <v>1.01</v>
+        <v>2.54</v>
       </c>
       <c r="BJ27" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK27" t="n">
         <v>1.01</v>
@@ -7387,50 +7387,50 @@
         <v>1.01</v>
       </c>
       <c r="BN27" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BO27" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BP27" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BQ27" t="n">
         <v>1.01</v>
       </c>
       <c r="BR27" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS27" t="n">
         <v>1.01</v>
       </c>
       <c r="BT27" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BU27" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BV27" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BW27" t="n">
         <v>1.01</v>
       </c>
       <c r="BX27" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY27" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ27" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA27" t="n">
         <v>1.01</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -7473,7 +7473,7 @@
         <v>5.1</v>
       </c>
       <c r="J28" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="K28" t="n">
         <v>3.15</v>
@@ -7488,19 +7488,19 @@
         <v>2.28</v>
       </c>
       <c r="O28" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="P28" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="R28" t="n">
         <v>1.15</v>
       </c>
       <c r="S28" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="T28" t="n">
         <v>2.42</v>
@@ -7533,7 +7533,7 @@
         <v>7.4</v>
       </c>
       <c r="AD28" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE28" t="n">
         <v>130</v>
@@ -7551,7 +7551,7 @@
         <v>170</v>
       </c>
       <c r="AJ28" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AK28" t="n">
         <v>36</v>
@@ -7572,13 +7572,13 @@
         <v>6.2</v>
       </c>
       <c r="AQ28" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AR28" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AS28" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AT28" t="n">
         <v>5.4</v>
@@ -7599,31 +7599,31 @@
         <v>11</v>
       </c>
       <c r="AZ28" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BA28" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BB28" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC28" t="n">
         <v>30</v>
       </c>
       <c r="BD28" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BE28" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BF28" t="n">
         <v>10</v>
       </c>
       <c r="BG28" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BH28" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="BI28" t="n">
         <v>2.04</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -7742,10 +7742,10 @@
         <v>2.9</v>
       </c>
       <c r="O29" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P29" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q29" t="n">
         <v>2.24</v>
@@ -7754,13 +7754,13 @@
         <v>1.23</v>
       </c>
       <c r="S29" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T29" t="n">
-        <v>1.59</v>
+        <v>1.92</v>
       </c>
       <c r="U29" t="n">
-        <v>1.56</v>
+        <v>1.9</v>
       </c>
       <c r="V29" t="n">
         <v>1.44</v>
@@ -7772,22 +7772,22 @@
         <v>12.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AA29" t="n">
         <v>75</v>
       </c>
       <c r="AB29" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC29" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD29" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AE29" t="n">
         <v>55</v>
@@ -7796,10 +7796,10 @@
         <v>19.5</v>
       </c>
       <c r="AG29" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AH29" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AI29" t="n">
         <v>65</v>
@@ -7823,76 +7823,76 @@
         <v>55</v>
       </c>
       <c r="AP29" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ29" t="n">
-        <v>8.6</v>
+        <v>3.5</v>
       </c>
       <c r="AR29" t="n">
-        <v>17.5</v>
+        <v>4</v>
       </c>
       <c r="AS29" t="n">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="AT29" t="n">
         <v>7.4</v>
       </c>
       <c r="AU29" t="n">
-        <v>6.2</v>
+        <v>3.1</v>
       </c>
       <c r="AV29" t="n">
-        <v>12</v>
+        <v>3.75</v>
       </c>
       <c r="AW29" t="n">
-        <v>5.4</v>
+        <v>4.4</v>
       </c>
       <c r="AX29" t="n">
-        <v>13.5</v>
+        <v>3.85</v>
       </c>
       <c r="AY29" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ29" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="BB29" t="n">
-        <v>5.4</v>
+        <v>4.4</v>
       </c>
       <c r="BC29" t="n">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="BD29" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="BE29" t="n">
-        <v>5.8</v>
+        <v>4.7</v>
       </c>
       <c r="BF29" t="n">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="BG29" t="n">
-        <v>5.4</v>
+        <v>4.4</v>
       </c>
       <c r="BH29" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BI29" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="BJ29" t="n">
         <v>11</v>
       </c>
       <c r="BK29" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BL29" t="n">
         <v>1000</v>
       </c>
       <c r="BM29" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BN29" t="n">
         <v>5.6</v>
@@ -7901,16 +7901,16 @@
         <v>4.1</v>
       </c>
       <c r="BP29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BQ29" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BR29" t="n">
         <v>42</v>
       </c>
       <c r="BS29" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BT29" t="n">
         <v>6.4</v>
@@ -7922,23 +7922,23 @@
         <v>29</v>
       </c>
       <c r="BW29" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BX29" t="n">
         <v>48</v>
       </c>
       <c r="BY29" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ29" t="n">
         <v>42</v>
       </c>
       <c r="CA29" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -7969,25 +7969,25 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="G30" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="H30" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="I30" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J30" t="n">
         <v>5</v>
       </c>
       <c r="K30" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L30" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M30" t="n">
         <v>1.04</v>
@@ -7999,7 +7999,7 @@
         <v>1.22</v>
       </c>
       <c r="P30" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="Q30" t="n">
         <v>1.63</v>
@@ -8011,7 +8011,7 @@
         <v>2.6</v>
       </c>
       <c r="T30" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U30" t="n">
         <v>2.1</v>
@@ -8020,7 +8020,7 @@
         <v>1.15</v>
       </c>
       <c r="W30" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="X30" t="n">
         <v>24</v>
@@ -8029,7 +8029,7 @@
         <v>32</v>
       </c>
       <c r="Z30" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AA30" t="n">
         <v>250</v>
@@ -8056,13 +8056,13 @@
         <v>22</v>
       </c>
       <c r="AI30" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ30" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AK30" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AL30" t="n">
         <v>30</v>
@@ -8074,19 +8074,19 @@
         <v>6.2</v>
       </c>
       <c r="AO30" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AP30" t="n">
         <v>20</v>
       </c>
       <c r="AQ30" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AR30" t="n">
         <v>55</v>
       </c>
       <c r="AS30" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AT30" t="n">
         <v>9.4</v>
@@ -8095,19 +8095,19 @@
         <v>10</v>
       </c>
       <c r="AV30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW30" t="n">
         <v>75</v>
       </c>
       <c r="AX30" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY30" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ30" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA30" t="n">
         <v>60</v>
@@ -8119,80 +8119,80 @@
         <v>13</v>
       </c>
       <c r="BD30" t="n">
-        <v>11.5</v>
+        <v>24</v>
       </c>
       <c r="BE30" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BF30" t="n">
         <v>5.5</v>
       </c>
       <c r="BG30" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="BH30" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BI30" t="n">
-        <v>1.97</v>
+        <v>3.35</v>
       </c>
       <c r="BJ30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK30" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM30" t="n">
         <v>15</v>
       </c>
-      <c r="BK30" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BL30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM30" t="n">
-        <v>1.97</v>
-      </c>
       <c r="BN30" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BO30" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BP30" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BQ30" t="n">
         <v>5.8</v>
       </c>
-      <c r="BO30" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BP30" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BQ30" t="n">
-        <v>1.7</v>
-      </c>
       <c r="BR30" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="BS30" t="n">
-        <v>1.85</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT30" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="BU30" t="n">
-        <v>1.76</v>
+        <v>6.6</v>
       </c>
       <c r="BV30" t="n">
         <v>1000</v>
       </c>
       <c r="BW30" t="n">
-        <v>1.93</v>
+        <v>13</v>
       </c>
       <c r="BX30" t="n">
         <v>1000</v>
       </c>
       <c r="BY30" t="n">
-        <v>1.93</v>
+        <v>13</v>
       </c>
       <c r="BZ30" t="n">
-        <v>18.5</v>
+        <v>13</v>
       </c>
       <c r="CA30" t="n">
-        <v>1.78</v>
+        <v>7.4</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -8223,16 +8223,16 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="G31" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="H31" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="I31" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="J31" t="n">
         <v>4</v>
@@ -8241,139 +8241,139 @@
         <v>4.4</v>
       </c>
       <c r="L31" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M31" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N31" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="O31" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="P31" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="R31" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="S31" t="n">
-        <v>3.25</v>
+        <v>2.98</v>
       </c>
       <c r="T31" t="n">
-        <v>1.64</v>
+        <v>1.96</v>
       </c>
       <c r="U31" t="n">
-        <v>1.52</v>
+        <v>1.89</v>
       </c>
       <c r="V31" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="W31" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="X31" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y31" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Z31" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA31" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AB31" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AC31" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD31" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AE31" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF31" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG31" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI31" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AK31" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL31" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM31" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN31" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AO31" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS31" t="n">
         <v>1.03</v>
       </c>
       <c r="AT31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW31" t="n">
         <v>1.03</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA31" t="n">
         <v>1.03</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE31" t="n">
         <v>1.03</v>
@@ -8385,68 +8385,68 @@
         <v>1.01</v>
       </c>
       <c r="BH31" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI31" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BJ31" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK31" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM31" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BN31" t="n">
         <v>4.2</v>
       </c>
-      <c r="BI31" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BJ31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK31" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="BL31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM31" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="BN31" t="n">
-        <v>1000</v>
-      </c>
       <c r="BO31" t="n">
-        <v>1.32</v>
+        <v>3.2</v>
       </c>
       <c r="BP31" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ31" t="n">
-        <v>1.32</v>
+        <v>6</v>
       </c>
       <c r="BR31" t="n">
         <v>1000</v>
       </c>
       <c r="BS31" t="n">
-        <v>1.32</v>
+        <v>6.4</v>
       </c>
       <c r="BT31" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU31" t="n">
-        <v>1.32</v>
+        <v>5.7</v>
       </c>
       <c r="BV31" t="n">
         <v>1000</v>
       </c>
       <c r="BW31" t="n">
-        <v>1.32</v>
+        <v>2.66</v>
       </c>
       <c r="BX31" t="n">
         <v>1000</v>
       </c>
       <c r="BY31" t="n">
-        <v>1.32</v>
+        <v>2.68</v>
       </c>
       <c r="BZ31" t="n">
         <v>1000</v>
       </c>
       <c r="CA31" t="n">
-        <v>1.32</v>
+        <v>6</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -8477,112 +8477,112 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="G32" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="H32" t="n">
-        <v>2.3</v>
+        <v>2.66</v>
       </c>
       <c r="I32" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="J32" t="n">
-        <v>2.8</v>
+        <v>3.45</v>
       </c>
       <c r="K32" t="n">
-        <v>9.4</v>
+        <v>4</v>
       </c>
       <c r="L32" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M32" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N32" t="n">
-        <v>1.81</v>
+        <v>4.1</v>
       </c>
       <c r="O32" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="P32" t="n">
-        <v>1.81</v>
+        <v>2.1</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="R32" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="S32" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="T32" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="U32" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="V32" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W32" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="X32" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y32" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z32" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA32" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AB32" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC32" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD32" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE32" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF32" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AG32" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH32" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AI32" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK32" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL32" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM32" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN32" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AO32" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AP32" t="n">
         <v>1.03</v>
@@ -8633,22 +8633,22 @@
         <v>1.03</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BG32" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BH32" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="BI32" t="n">
         <v>2.76</v>
       </c>
       <c r="BJ32" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK32" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BL32" t="n">
         <v>1000</v>
@@ -8657,50 +8657,50 @@
         <v>1.01</v>
       </c>
       <c r="BN32" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BO32" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BP32" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BQ32" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BR32" t="n">
         <v>1000</v>
       </c>
       <c r="BS32" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BT32" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU32" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BV32" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BW32" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BX32" t="n">
         <v>1000</v>
       </c>
       <c r="BY32" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BZ32" t="n">
         <v>1000</v>
       </c>
       <c r="CA32" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -8743,7 +8743,7 @@
         <v>1000</v>
       </c>
       <c r="J33" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="K33" t="n">
         <v>1000</v>
@@ -8764,13 +8764,13 @@
         <v>1.25</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="R33" t="n">
         <v>1.07</v>
       </c>
       <c r="S33" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="T33" t="n">
         <v>1.11</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -8985,7 +8985,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="G34" t="n">
         <v>2.06</v>
@@ -9003,7 +9003,7 @@
         <v>3.75</v>
       </c>
       <c r="L34" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M34" t="n">
         <v>1.08</v>
@@ -9015,22 +9015,22 @@
         <v>1.36</v>
       </c>
       <c r="P34" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="R34" t="n">
         <v>1.3</v>
       </c>
       <c r="S34" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T34" t="n">
         <v>1.86</v>
       </c>
       <c r="U34" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="V34" t="n">
         <v>1.27</v>
@@ -9114,13 +9114,13 @@
         <v>14.5</v>
       </c>
       <c r="AW34" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AX34" t="n">
         <v>10</v>
       </c>
       <c r="AY34" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ34" t="n">
         <v>16.5</v>
@@ -9135,13 +9135,13 @@
         <v>18.5</v>
       </c>
       <c r="BD34" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BE34" t="n">
         <v>9.4</v>
       </c>
       <c r="BF34" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BG34" t="n">
         <v>9</v>
@@ -9150,13 +9150,13 @@
         <v>3.25</v>
       </c>
       <c r="BI34" t="n">
-        <v>2.82</v>
+        <v>2.64</v>
       </c>
       <c r="BJ34" t="n">
         <v>11</v>
       </c>
       <c r="BK34" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BL34" t="n">
         <v>1000</v>
@@ -9186,7 +9186,7 @@
         <v>7.8</v>
       </c>
       <c r="BU34" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BV34" t="n">
         <v>1000</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -9272,19 +9272,19 @@
         <v>1.78</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R35" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S35" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="T35" t="n">
         <v>1.9</v>
       </c>
       <c r="U35" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="V35" t="n">
         <v>1.27</v>
@@ -9302,7 +9302,7 @@
         <v>32</v>
       </c>
       <c r="AA35" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AB35" t="n">
         <v>8.800000000000001</v>
@@ -9314,7 +9314,7 @@
         <v>18.5</v>
       </c>
       <c r="AE35" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AF35" t="n">
         <v>12.5</v>
@@ -9326,13 +9326,13 @@
         <v>22</v>
       </c>
       <c r="AI35" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AJ35" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK35" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL35" t="n">
         <v>44</v>
@@ -9341,19 +9341,19 @@
         <v>150</v>
       </c>
       <c r="AN35" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AO35" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AP35" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ35" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR35" t="n">
-        <v>25</v>
+        <v>7.2</v>
       </c>
       <c r="AS35" t="n">
         <v>8.800000000000001</v>
@@ -9362,10 +9362,10 @@
         <v>7.2</v>
       </c>
       <c r="AU35" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV35" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AW35" t="n">
         <v>8.199999999999999</v>
@@ -9383,19 +9383,19 @@
         <v>8.4</v>
       </c>
       <c r="BB35" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC35" t="n">
         <v>21</v>
       </c>
       <c r="BD35" t="n">
-        <v>34</v>
+        <v>7.8</v>
       </c>
       <c r="BE35" t="n">
         <v>9</v>
       </c>
       <c r="BF35" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BG35" t="n">
         <v>8.4</v>
@@ -9404,7 +9404,7 @@
         <v>3.25</v>
       </c>
       <c r="BI35" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="BJ35" t="n">
         <v>11</v>
@@ -9416,7 +9416,7 @@
         <v>1000</v>
       </c>
       <c r="BM35" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BN35" t="n">
         <v>4.8</v>
@@ -9425,7 +9425,7 @@
         <v>3.7</v>
       </c>
       <c r="BP35" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BQ35" t="n">
         <v>6.2</v>
@@ -9434,25 +9434,25 @@
         <v>34</v>
       </c>
       <c r="BS35" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BT35" t="n">
         <v>8</v>
       </c>
       <c r="BU35" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="BV35" t="n">
         <v>42</v>
       </c>
       <c r="BW35" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX35" t="n">
         <v>55</v>
       </c>
       <c r="BY35" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BZ35" t="n">
         <v>32</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -9517,7 +9517,7 @@
         <v>1.01</v>
       </c>
       <c r="N36" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="O36" t="n">
         <v>1.09</v>
@@ -9529,7 +9529,7 @@
         <v>1.09</v>
       </c>
       <c r="R36" t="n">
-        <v>1.18</v>
+        <v>1.45</v>
       </c>
       <c r="S36" t="n">
         <v>1.09</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -9747,230 +9747,230 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="G37" t="n">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="H37" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="I37" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="J37" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="K37" t="n">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="L37" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="M37" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N37" t="n">
-        <v>2.54</v>
+        <v>2.8</v>
       </c>
       <c r="O37" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="P37" t="n">
-        <v>1.46</v>
+        <v>1.6</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.22</v>
+        <v>2.44</v>
       </c>
       <c r="R37" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="S37" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="T37" t="n">
-        <v>1.11</v>
+        <v>2.02</v>
       </c>
       <c r="U37" t="n">
-        <v>1.61</v>
+        <v>1.87</v>
       </c>
       <c r="V37" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="W37" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="X37" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Y37" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="Z37" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="AA37" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AB37" t="n">
-        <v>11</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC37" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AD37" t="n">
-        <v>21</v>
+        <v>15.5</v>
       </c>
       <c r="AE37" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF37" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AG37" t="n">
-        <v>16.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH37" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="AI37" t="n">
         <v>90</v>
       </c>
       <c r="AJ37" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AK37" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="AL37" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AM37" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN37" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO37" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP37" t="n">
-        <v>2.44</v>
+        <v>8.6</v>
       </c>
       <c r="AQ37" t="n">
-        <v>2.56</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR37" t="n">
-        <v>2.82</v>
+        <v>20</v>
       </c>
       <c r="AS37" t="n">
-        <v>2.98</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT37" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>32</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>25</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>9</v>
+      </c>
+      <c r="BH37" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BI37" t="n">
         <v>2.42</v>
       </c>
-      <c r="AU37" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AY37" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AZ37" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BA37" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB37" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BC37" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BD37" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="BE37" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BF37" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BG37" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BH37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI37" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BJ37" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK37" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BL37" t="n">
         <v>1000</v>
       </c>
       <c r="BM37" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BN37" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO37" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BP37" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ37" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR37" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS37" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BT37" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU37" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BV37" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW37" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BX37" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY37" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BZ37" t="n">
         <v>1000</v>
       </c>
       <c r="CA37" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -10007,46 +10007,46 @@
         <v>3.25</v>
       </c>
       <c r="H38" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="I38" t="n">
         <v>3.25</v>
       </c>
       <c r="J38" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="K38" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="L38" t="n">
         <v>1.57</v>
       </c>
       <c r="M38" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="N38" t="n">
         <v>2.3</v>
       </c>
       <c r="O38" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="P38" t="n">
         <v>1.42</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="R38" t="n">
         <v>1.18</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="T38" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="U38" t="n">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="V38" t="n">
         <v>1.44</v>
@@ -10055,176 +10055,176 @@
         <v>1.44</v>
       </c>
       <c r="X38" t="n">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="Y38" t="n">
-        <v>11.5</v>
+        <v>8.4</v>
       </c>
       <c r="Z38" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="AA38" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="AB38" t="n">
-        <v>11.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC38" t="n">
-        <v>10</v>
+        <v>7.2</v>
       </c>
       <c r="AD38" t="n">
-        <v>22</v>
+        <v>15.5</v>
       </c>
       <c r="AE38" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AF38" t="n">
-        <v>28</v>
+        <v>19.5</v>
       </c>
       <c r="AG38" t="n">
-        <v>21</v>
+        <v>15.5</v>
       </c>
       <c r="AH38" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AI38" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ38" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="AK38" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>270</v>
+      </c>
+      <c r="AN38" t="n">
         <v>75</v>
       </c>
-      <c r="AL38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>1000</v>
-      </c>
       <c r="AO38" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP38" t="n">
-        <v>2.06</v>
+        <v>4.2</v>
       </c>
       <c r="AQ38" t="n">
-        <v>2.14</v>
+        <v>4.3</v>
       </c>
       <c r="AR38" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="AS38" t="n">
-        <v>2.54</v>
+        <v>7.8</v>
       </c>
       <c r="AT38" t="n">
-        <v>2.14</v>
+        <v>4.3</v>
       </c>
       <c r="AU38" t="n">
-        <v>2.08</v>
+        <v>4</v>
       </c>
       <c r="AV38" t="n">
-        <v>2.34</v>
+        <v>5.7</v>
       </c>
       <c r="AW38" t="n">
-        <v>2.54</v>
+        <v>7.8</v>
       </c>
       <c r="AX38" t="n">
-        <v>2.4</v>
+        <v>6.2</v>
       </c>
       <c r="AY38" t="n">
-        <v>2.34</v>
+        <v>5.7</v>
       </c>
       <c r="AZ38" t="n">
-        <v>2.44</v>
+        <v>7</v>
       </c>
       <c r="BA38" t="n">
-        <v>2.62</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB38" t="n">
-        <v>2.56</v>
+        <v>7.8</v>
       </c>
       <c r="BC38" t="n">
-        <v>2.54</v>
+        <v>7.8</v>
       </c>
       <c r="BD38" t="n">
-        <v>2.62</v>
+        <v>8.4</v>
       </c>
       <c r="BE38" t="n">
-        <v>2.62</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF38" t="n">
-        <v>2.62</v>
+        <v>8</v>
       </c>
       <c r="BG38" t="n">
-        <v>2.62</v>
+        <v>8</v>
       </c>
       <c r="BH38" t="n">
         <v>1000</v>
       </c>
       <c r="BI38" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="BJ38" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BK38" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="BL38" t="n">
         <v>1000</v>
       </c>
       <c r="BM38" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="BN38" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BO38" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="BP38" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BQ38" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="BR38" t="n">
         <v>1000</v>
       </c>
       <c r="BS38" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="BT38" t="n">
         <v>8</v>
       </c>
       <c r="BU38" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="BV38" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BW38" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="BX38" t="n">
         <v>1000</v>
       </c>
       <c r="BY38" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="BZ38" t="n">
         <v>1000</v>
       </c>
       <c r="CA38" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -10264,10 +10264,10 @@
         <v>7.2</v>
       </c>
       <c r="I39" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J39" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="K39" t="n">
         <v>5</v>
@@ -10276,7 +10276,7 @@
         <v>1.34</v>
       </c>
       <c r="M39" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N39" t="n">
         <v>4.7</v>
@@ -10288,13 +10288,13 @@
         <v>2.24</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="R39" t="n">
         <v>1.47</v>
       </c>
       <c r="S39" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="T39" t="n">
         <v>1.92</v>
@@ -10312,10 +10312,10 @@
         <v>21</v>
       </c>
       <c r="Y39" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="Z39" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AA39" t="n">
         <v>240</v>
@@ -10345,7 +10345,7 @@
         <v>100</v>
       </c>
       <c r="AJ39" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AK39" t="n">
         <v>15.5</v>
@@ -10357,22 +10357,22 @@
         <v>140</v>
       </c>
       <c r="AN39" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AO39" t="n">
         <v>130</v>
       </c>
       <c r="AP39" t="n">
-        <v>8.4</v>
+        <v>17.5</v>
       </c>
       <c r="AQ39" t="n">
         <v>23</v>
       </c>
       <c r="AR39" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AS39" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AT39" t="n">
         <v>8.199999999999999</v>
@@ -10381,10 +10381,10 @@
         <v>10</v>
       </c>
       <c r="AV39" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AW39" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX39" t="n">
         <v>8.199999999999999</v>
@@ -10396,7 +10396,7 @@
         <v>21</v>
       </c>
       <c r="BA39" t="n">
-        <v>65</v>
+        <v>12.5</v>
       </c>
       <c r="BB39" t="n">
         <v>12</v>
@@ -10408,13 +10408,13 @@
         <v>29</v>
       </c>
       <c r="BE39" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BF39" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BG39" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BH39" t="n">
         <v>4</v>
@@ -10426,59 +10426,59 @@
         <v>11.5</v>
       </c>
       <c r="BK39" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BL39" t="n">
         <v>1000</v>
       </c>
       <c r="BM39" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BN39" t="n">
         <v>4.1</v>
       </c>
       <c r="BO39" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BP39" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BQ39" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="BR39" t="n">
         <v>25</v>
       </c>
       <c r="BS39" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BT39" t="n">
         <v>11.5</v>
       </c>
       <c r="BU39" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BV39" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="BW39" t="n">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="BX39" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY39" t="n">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="BZ39" t="n">
         <v>15.5</v>
       </c>
       <c r="CA39" t="n">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -10515,22 +10515,22 @@
         <v>2.26</v>
       </c>
       <c r="H40" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I40" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J40" t="n">
         <v>3.55</v>
       </c>
       <c r="K40" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L40" t="n">
         <v>1.31</v>
       </c>
       <c r="M40" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N40" t="n">
         <v>3.85</v>
@@ -10539,31 +10539,31 @@
         <v>1.29</v>
       </c>
       <c r="P40" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="R40" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S40" t="n">
         <v>3.1</v>
       </c>
       <c r="T40" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U40" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V40" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W40" t="n">
         <v>1.79</v>
       </c>
       <c r="X40" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Y40" t="n">
         <v>18</v>
@@ -10578,7 +10578,7 @@
         <v>12.5</v>
       </c>
       <c r="AC40" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD40" t="n">
         <v>19</v>
@@ -10587,10 +10587,10 @@
         <v>55</v>
       </c>
       <c r="AF40" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AG40" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH40" t="n">
         <v>21</v>
@@ -10599,10 +10599,10 @@
         <v>55</v>
       </c>
       <c r="AJ40" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AK40" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL40" t="n">
         <v>42</v>
@@ -10611,7 +10611,7 @@
         <v>110</v>
       </c>
       <c r="AN40" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO40" t="n">
         <v>50</v>
@@ -10623,10 +10623,10 @@
         <v>12.5</v>
       </c>
       <c r="AR40" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AS40" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="AT40" t="n">
         <v>8.800000000000001</v>
@@ -10638,7 +10638,7 @@
         <v>13</v>
       </c>
       <c r="AW40" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AX40" t="n">
         <v>11.5</v>
@@ -10650,31 +10650,31 @@
         <v>14.5</v>
       </c>
       <c r="BA40" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="BB40" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="BC40" t="n">
         <v>18.5</v>
       </c>
       <c r="BD40" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="BE40" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="BF40" t="n">
         <v>11</v>
       </c>
       <c r="BG40" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="BH40" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BI40" t="n">
-        <v>2.86</v>
+        <v>3.15</v>
       </c>
       <c r="BJ40" t="n">
         <v>9.800000000000001</v>
@@ -10698,7 +10698,7 @@
         <v>15.5</v>
       </c>
       <c r="BQ40" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BR40" t="n">
         <v>28</v>
@@ -10710,13 +10710,13 @@
         <v>7.4</v>
       </c>
       <c r="BU40" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BV40" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BW40" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BX40" t="n">
         <v>40</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -10772,7 +10772,7 @@
         <v>1.89</v>
       </c>
       <c r="I41" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="J41" t="n">
         <v>3.75</v>
@@ -10781,25 +10781,25 @@
         <v>4.2</v>
       </c>
       <c r="L41" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="M41" t="n">
         <v>1.05</v>
       </c>
       <c r="N41" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O41" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P41" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="R41" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S41" t="n">
         <v>2.96</v>
@@ -10811,7 +10811,7 @@
         <v>2.22</v>
       </c>
       <c r="V41" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="W41" t="n">
         <v>1.28</v>
@@ -10829,7 +10829,7 @@
         <v>22</v>
       </c>
       <c r="AB41" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AC41" t="n">
         <v>9</v>
@@ -10877,7 +10877,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AR41" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AS41" t="n">
         <v>19.5</v>
@@ -10895,7 +10895,7 @@
         <v>17</v>
       </c>
       <c r="AX41" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AY41" t="n">
         <v>15</v>
@@ -10904,89 +10904,89 @@
         <v>15</v>
       </c>
       <c r="BA41" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB41" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BC41" t="n">
-        <v>30</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD41" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BE41" t="n">
         <v>10.5</v>
       </c>
       <c r="BF41" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BG41" t="n">
         <v>10</v>
       </c>
       <c r="BH41" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="BI41" t="n">
-        <v>1.89</v>
+        <v>3.05</v>
       </c>
       <c r="BJ41" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BK41" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BL41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM41" t="n">
         <v>13.5</v>
       </c>
-      <c r="BK41" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="BL41" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM41" t="n">
-        <v>1.89</v>
-      </c>
       <c r="BN41" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BO41" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BP41" t="n">
+        <v>34</v>
+      </c>
+      <c r="BQ41" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BR41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS41" t="n">
         <v>11</v>
       </c>
-      <c r="BO41" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BP41" t="n">
-        <v>48</v>
-      </c>
-      <c r="BQ41" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="BR41" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS41" t="n">
-        <v>1.83</v>
-      </c>
       <c r="BT41" t="n">
-        <v>6.6</v>
+        <v>4.8</v>
       </c>
       <c r="BU41" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="BV41" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="BW41" t="n">
-        <v>1.72</v>
+        <v>7</v>
       </c>
       <c r="BX41" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="BY41" t="n">
-        <v>1.8</v>
+        <v>9.6</v>
       </c>
       <c r="BZ41" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="CA41" t="n">
-        <v>1.77</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -11017,16 +11017,16 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="G42" t="n">
         <v>2.02</v>
       </c>
       <c r="H42" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I42" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J42" t="n">
         <v>3.65</v>
@@ -11035,7 +11035,7 @@
         <v>4.3</v>
       </c>
       <c r="L42" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M42" t="n">
         <v>1.05</v>
@@ -11044,34 +11044,34 @@
         <v>4</v>
       </c>
       <c r="O42" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P42" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="R42" t="n">
         <v>1.41</v>
       </c>
       <c r="S42" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="T42" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U42" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V42" t="n">
         <v>1.26</v>
       </c>
       <c r="W42" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="X42" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="Y42" t="n">
         <v>18.5</v>
@@ -11086,7 +11086,7 @@
         <v>11</v>
       </c>
       <c r="AC42" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AD42" t="n">
         <v>18.5</v>
@@ -11125,122 +11125,122 @@
         <v>55</v>
       </c>
       <c r="AP42" t="n">
-        <v>5.3</v>
+        <v>14.5</v>
       </c>
       <c r="AQ42" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF42" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BG42" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BH42" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BI42" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BJ42" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK42" t="n">
         <v>5.1</v>
       </c>
-      <c r="AR42" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AU42" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AV42" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AW42" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX42" t="n">
+      <c r="BL42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM42" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BN42" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BO42" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BP42" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BQ42" t="n">
+        <v>6</v>
+      </c>
+      <c r="BR42" t="n">
+        <v>26</v>
+      </c>
+      <c r="BS42" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BT42" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU42" t="n">
         <v>4.6</v>
       </c>
-      <c r="AY42" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AZ42" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BA42" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BB42" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BC42" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BD42" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BE42" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BF42" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BG42" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BH42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI42" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK42" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM42" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO42" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ42" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS42" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU42" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BV42" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW42" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX42" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY42" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="BZ42" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="CA42" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>
@@ -11277,22 +11277,22 @@
         <v>3.15</v>
       </c>
       <c r="H43" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="I43" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="J43" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K43" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L43" t="n">
         <v>1.29</v>
       </c>
       <c r="M43" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N43" t="n">
         <v>5.5</v>
@@ -11304,19 +11304,19 @@
         <v>2.52</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="R43" t="n">
         <v>1.61</v>
       </c>
       <c r="S43" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="T43" t="n">
         <v>1.56</v>
       </c>
       <c r="U43" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="V43" t="n">
         <v>1.71</v>
@@ -11331,19 +11331,19 @@
         <v>15.5</v>
       </c>
       <c r="Z43" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AA43" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AB43" t="n">
         <v>18</v>
       </c>
       <c r="AC43" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AD43" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AE43" t="n">
         <v>23</v>
@@ -11352,19 +11352,19 @@
         <v>24</v>
       </c>
       <c r="AG43" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AH43" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AI43" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AJ43" t="n">
         <v>48</v>
       </c>
       <c r="AK43" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AL43" t="n">
         <v>34</v>
@@ -11373,64 +11373,64 @@
         <v>55</v>
       </c>
       <c r="AN43" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AO43" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AP43" t="n">
         <v>20</v>
       </c>
       <c r="AQ43" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AR43" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AS43" t="n">
-        <v>8.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="AT43" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AU43" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV43" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW43" t="n">
         <v>19</v>
       </c>
       <c r="AX43" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AY43" t="n">
         <v>12</v>
       </c>
       <c r="AZ43" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA43" t="n">
-        <v>8.6</v>
+        <v>6.2</v>
       </c>
       <c r="BB43" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BC43" t="n">
-        <v>8.4</v>
+        <v>6.4</v>
       </c>
       <c r="BD43" t="n">
-        <v>8.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="BE43" t="n">
-        <v>9.800000000000001</v>
+        <v>40</v>
       </c>
       <c r="BF43" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BG43" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BH43" t="n">
         <v>1000</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-16 02:46:23</t>
+          <t>2026-07-16 05:00:01</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-17.xlsx
@@ -869,7 +869,7 @@
         <v>2.14</v>
       </c>
       <c r="J2" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K2" t="n">
         <v>3.75</v>
@@ -878,7 +878,7 @@
         <v>1.39</v>
       </c>
       <c r="M2" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N2" t="n">
         <v>4.1</v>
@@ -890,7 +890,7 @@
         <v>2.02</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="R2" t="n">
         <v>1.4</v>
@@ -902,7 +902,7 @@
         <v>1.77</v>
       </c>
       <c r="U2" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="V2" t="n">
         <v>1.87</v>
@@ -911,10 +911,10 @@
         <v>1.33</v>
       </c>
       <c r="X2" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Y2" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="Z2" t="n">
         <v>13.5</v>
@@ -935,7 +935,7 @@
         <v>23</v>
       </c>
       <c r="AF2" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AG2" t="n">
         <v>16.5</v>
@@ -947,13 +947,13 @@
         <v>36</v>
       </c>
       <c r="AJ2" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AK2" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AL2" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM2" t="n">
         <v>90</v>
@@ -965,16 +965,16 @@
         <v>15</v>
       </c>
       <c r="AP2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AQ2" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR2" t="n">
         <v>11.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AT2" t="n">
         <v>13</v>
@@ -986,31 +986,31 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX2" t="n">
         <v>8.6</v>
       </c>
-      <c r="AX2" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AY2" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AZ2" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BA2" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BB2" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BC2" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD2" t="n">
         <v>40</v>
       </c>
       <c r="BE2" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BF2" t="n">
         <v>34</v>
@@ -1034,7 +1034,7 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BN2" t="n">
         <v>7.2</v>
@@ -1043,7 +1043,7 @@
         <v>5.7</v>
       </c>
       <c r="BP2" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
         <v>23</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -1123,10 +1123,10 @@
         <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K3" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L3" t="n">
         <v>1.39</v>
@@ -1138,22 +1138,22 @@
         <v>3.8</v>
       </c>
       <c r="O3" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P3" t="n">
         <v>1.96</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="R3" t="n">
         <v>1.37</v>
       </c>
       <c r="S3" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T3" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="U3" t="n">
         <v>2.16</v>
@@ -1174,13 +1174,13 @@
         <v>34</v>
       </c>
       <c r="AA3" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD3" t="n">
         <v>19</v>
@@ -1198,13 +1198,13 @@
         <v>21</v>
       </c>
       <c r="AI3" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AJ3" t="n">
         <v>34</v>
       </c>
       <c r="AK3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL3" t="n">
         <v>42</v>
@@ -1213,64 +1213,64 @@
         <v>110</v>
       </c>
       <c r="AN3" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AO3" t="n">
         <v>50</v>
       </c>
       <c r="AP3" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AR3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS3" t="n">
         <v>4.7</v>
       </c>
-      <c r="AS3" t="n">
-        <v>5.1</v>
-      </c>
       <c r="AT3" t="n">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="AU3" t="n">
         <v>6.2</v>
       </c>
       <c r="AV3" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AX3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AY3" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.7</v>
+        <v>19.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="BF3" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="BH3" t="n">
         <v>3.55</v>
@@ -1288,7 +1288,7 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>3.65</v>
+        <v>12.5</v>
       </c>
       <c r="BN3" t="n">
         <v>5.1</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -1368,22 +1368,22 @@
         <v>4.1</v>
       </c>
       <c r="G4" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H4" t="n">
         <v>1.94</v>
       </c>
       <c r="I4" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="J4" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K4" t="n">
         <v>3.85</v>
       </c>
       <c r="L4" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M4" t="n">
         <v>1.07</v>
@@ -1392,28 +1392,28 @@
         <v>3.55</v>
       </c>
       <c r="O4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R4" t="n">
         <v>1.34</v>
       </c>
-      <c r="P4" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.33</v>
-      </c>
       <c r="S4" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T4" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="U4" t="n">
         <v>2.04</v>
       </c>
       <c r="V4" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="W4" t="n">
         <v>1.27</v>
@@ -1422,7 +1422,7 @@
         <v>15.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z4" t="n">
         <v>14</v>
@@ -1446,7 +1446,7 @@
         <v>38</v>
       </c>
       <c r="AG4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH4" t="n">
         <v>22</v>
@@ -1458,13 +1458,13 @@
         <v>110</v>
       </c>
       <c r="AK4" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AL4" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AM4" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN4" t="n">
         <v>75</v>
@@ -1473,13 +1473,13 @@
         <v>17</v>
       </c>
       <c r="AP4" t="n">
-        <v>10.5</v>
+        <v>4.3</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AR4" t="n">
-        <v>10.5</v>
+        <v>4.2</v>
       </c>
       <c r="AS4" t="n">
         <v>17.5</v>
@@ -1494,64 +1494,64 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AW4" t="n">
-        <v>5</v>
+        <v>18.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="AY4" t="n">
-        <v>13.5</v>
+        <v>4.6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>14.5</v>
+        <v>4.7</v>
       </c>
       <c r="BA4" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC4" t="n">
         <v>5.5</v>
       </c>
-      <c r="BB4" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BD4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE4" t="n">
         <v>5.7</v>
       </c>
-      <c r="BE4" t="n">
-        <v>6</v>
-      </c>
       <c r="BF4" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BH4" t="n">
         <v>3.4</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BJ4" t="n">
         <v>10</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BN4" t="n">
         <v>7.8</v>
       </c>
       <c r="BO4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BP4" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
         <v>10.5</v>
@@ -1572,23 +1572,23 @@
         <v>14.5</v>
       </c>
       <c r="BW4" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BX4" t="n">
         <v>29</v>
       </c>
       <c r="BY4" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ4" t="n">
         <v>26</v>
       </c>
       <c r="CA4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -1631,10 +1631,10 @@
         <v>1.9</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K5" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1649,10 +1649,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
         <v>4.2</v>
       </c>
       <c r="G6" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="H6" t="n">
         <v>1.95</v>
@@ -1891,13 +1891,13 @@
         <v>3.6</v>
       </c>
       <c r="L6" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M6" t="n">
         <v>1.1</v>
       </c>
       <c r="N6" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="O6" t="n">
         <v>1.43</v>
@@ -1993,7 +1993,7 @@
         <v>18</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AU6" t="n">
         <v>5.8</v>
@@ -2005,16 +2005,16 @@
         <v>3.85</v>
       </c>
       <c r="AX6" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AY6" t="n">
         <v>13.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BB6" t="n">
         <v>4.2</v>
@@ -2026,31 +2026,31 @@
         <v>4.2</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BF6" t="n">
         <v>4.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BH6" t="n">
         <v>3.05</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.42</v>
+        <v>2.64</v>
       </c>
       <c r="BJ6" t="n">
         <v>11.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="BN6" t="n">
         <v>8</v>
@@ -2080,7 +2080,7 @@
         <v>16.5</v>
       </c>
       <c r="BW6" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
         <v>5.1</v>
       </c>
       <c r="T7" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U7" t="n">
         <v>1.77</v>
@@ -2238,13 +2238,13 @@
         <v>7</v>
       </c>
       <c r="AQ7" t="n">
-        <v>5.8</v>
+        <v>4</v>
       </c>
       <c r="AR7" t="n">
-        <v>11</v>
+        <v>5.4</v>
       </c>
       <c r="AS7" t="n">
-        <v>6.8</v>
+        <v>21</v>
       </c>
       <c r="AT7" t="n">
         <v>8.4</v>
@@ -2253,19 +2253,19 @@
         <v>5.7</v>
       </c>
       <c r="AV7" t="n">
-        <v>9.199999999999999</v>
+        <v>5.1</v>
       </c>
       <c r="AW7" t="n">
-        <v>6.8</v>
+        <v>21</v>
       </c>
       <c r="AX7" t="n">
-        <v>6.6</v>
+        <v>17.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>14.5</v>
+        <v>5.9</v>
       </c>
       <c r="AZ7" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="BA7" t="n">
         <v>7.6</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
         <v>5.2</v>
       </c>
       <c r="K8" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="L8" t="n">
         <v>1.24</v>
@@ -2420,7 +2420,7 @@
         <v>1.58</v>
       </c>
       <c r="S8" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="T8" t="n">
         <v>1.87</v>
@@ -2519,7 +2519,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA8" t="n">
         <v>36</v>
@@ -2537,7 +2537,7 @@
         <v>40</v>
       </c>
       <c r="BF8" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BG8" t="n">
         <v>38</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -2650,7 +2650,7 @@
         <v>5.3</v>
       </c>
       <c r="K9" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="L9" t="n">
         <v>1.21</v>
@@ -2662,10 +2662,10 @@
         <v>7</v>
       </c>
       <c r="O9" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P9" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="Q9" t="n">
         <v>1.45</v>
@@ -2677,7 +2677,7 @@
         <v>2.1</v>
       </c>
       <c r="T9" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U9" t="n">
         <v>2.34</v>
@@ -2704,7 +2704,7 @@
         <v>14.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AD9" t="n">
         <v>34</v>
@@ -2713,7 +2713,7 @@
         <v>95</v>
       </c>
       <c r="AF9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG9" t="n">
         <v>11.5</v>
@@ -2743,16 +2743,16 @@
         <v>75</v>
       </c>
       <c r="AP9" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ9" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AR9" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AS9" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AT9" t="n">
         <v>12.5</v>
@@ -2761,10 +2761,10 @@
         <v>11.5</v>
       </c>
       <c r="AV9" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AW9" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AX9" t="n">
         <v>10.5</v>
@@ -2776,7 +2776,7 @@
         <v>17</v>
       </c>
       <c r="BA9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB9" t="n">
         <v>12</v>
@@ -2788,19 +2788,19 @@
         <v>16</v>
       </c>
       <c r="BE9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BF9" t="n">
         <v>4</v>
       </c>
       <c r="BG9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BH9" t="n">
         <v>5.3</v>
       </c>
       <c r="BI9" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BJ9" t="n">
         <v>10.5</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -2889,19 +2889,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="G10" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="H10" t="n">
         <v>2.62</v>
       </c>
       <c r="I10" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="J10" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K10" t="n">
         <v>4.4</v>
@@ -2919,22 +2919,22 @@
         <v>1.13</v>
       </c>
       <c r="P10" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="R10" t="n">
         <v>1.89</v>
       </c>
       <c r="S10" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="T10" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="U10" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="V10" t="n">
         <v>1.57</v>
@@ -2943,7 +2943,7 @@
         <v>1.63</v>
       </c>
       <c r="X10" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="Y10" t="n">
         <v>23</v>
@@ -2952,16 +2952,16 @@
         <v>27</v>
       </c>
       <c r="AA10" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AB10" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AC10" t="n">
         <v>11.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE10" t="n">
         <v>27</v>
@@ -2973,25 +2973,25 @@
         <v>13.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AI10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ10" t="n">
         <v>38</v>
       </c>
       <c r="AK10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL10" t="n">
         <v>25</v>
       </c>
-      <c r="AL10" t="n">
-        <v>26</v>
-      </c>
       <c r="AM10" t="n">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="AN10" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AO10" t="n">
         <v>11.5</v>
@@ -3072,7 +3072,7 @@
         <v>6.6</v>
       </c>
       <c r="BO10" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BP10" t="n">
         <v>16</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -3161,7 +3161,7 @@
         <v>3.35</v>
       </c>
       <c r="L11" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="M11" t="n">
         <v>1.09</v>
@@ -3305,7 +3305,7 @@
         <v>7.6</v>
       </c>
       <c r="BH11" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BI11" t="n">
         <v>2.44</v>
@@ -3314,13 +3314,13 @@
         <v>10.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BN11" t="n">
         <v>5.7</v>
@@ -3332,13 +3332,13 @@
         <v>23</v>
       </c>
       <c r="BQ11" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BR11" t="n">
         <v>40</v>
       </c>
       <c r="BS11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BT11" t="n">
         <v>6.4</v>
@@ -3350,23 +3350,23 @@
         <v>28</v>
       </c>
       <c r="BW11" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BX11" t="n">
         <v>44</v>
       </c>
       <c r="BY11" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BZ11" t="n">
         <v>38</v>
       </c>
       <c r="CA11" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -3412,7 +3412,7 @@
         <v>3.8</v>
       </c>
       <c r="K12" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -3433,10 +3433,10 @@
         <v>1.58</v>
       </c>
       <c r="R12" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S12" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="T12" t="n">
         <v>1.7</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -3669,7 +3669,7 @@
         <v>4.4</v>
       </c>
       <c r="L13" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M13" t="n">
         <v>1.07</v>
@@ -3681,7 +3681,7 @@
         <v>1.32</v>
       </c>
       <c r="P13" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="Q13" t="n">
         <v>1.94</v>
@@ -3729,7 +3729,7 @@
         <v>19.5</v>
       </c>
       <c r="AF13" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AG13" t="n">
         <v>25</v>
@@ -3738,7 +3738,7 @@
         <v>24</v>
       </c>
       <c r="AI13" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AJ13" t="n">
         <v>220</v>
@@ -3822,7 +3822,7 @@
         <v>11.5</v>
       </c>
       <c r="BK13" t="n">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
@@ -3852,7 +3852,7 @@
         <v>4.3</v>
       </c>
       <c r="BU13" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="BV13" t="n">
         <v>12</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -4004,19 +4004,19 @@
         <v>30</v>
       </c>
       <c r="AM14" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN14" t="n">
         <v>3.5</v>
       </c>
       <c r="AO14" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AP14" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AQ14" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AR14" t="n">
         <v>6</v>
@@ -4025,7 +4025,7 @@
         <v>6.2</v>
       </c>
       <c r="AT14" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AU14" t="n">
         <v>4.8</v>
@@ -4037,25 +4037,25 @@
         <v>6</v>
       </c>
       <c r="AX14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AY14" t="n">
         <v>4.4</v>
       </c>
-      <c r="AY14" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AZ14" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BA14" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BE14" t="n">
         <v>5.9</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -4159,10 +4159,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="G15" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
         <v>3.95</v>
@@ -4171,13 +4171,13 @@
         <v>4.1</v>
       </c>
       <c r="J15" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K15" t="n">
         <v>4.1</v>
       </c>
       <c r="L15" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M15" t="n">
         <v>1.05</v>
@@ -4186,10 +4186,10 @@
         <v>4.6</v>
       </c>
       <c r="O15" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P15" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="Q15" t="n">
         <v>1.72</v>
@@ -4198,19 +4198,19 @@
         <v>1.51</v>
       </c>
       <c r="S15" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="T15" t="n">
         <v>1.67</v>
       </c>
       <c r="U15" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V15" t="n">
         <v>1.32</v>
       </c>
       <c r="W15" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X15" t="n">
         <v>21</v>
@@ -4309,13 +4309,13 @@
         <v>17</v>
       </c>
       <c r="BD15" t="n">
-        <v>22</v>
+        <v>8.4</v>
       </c>
       <c r="BE15" t="n">
         <v>10</v>
       </c>
       <c r="BF15" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BG15" t="n">
         <v>27</v>
@@ -4324,22 +4324,22 @@
         <v>4.1</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BJ15" t="n">
         <v>9.4</v>
       </c>
       <c r="BK15" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BL15" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BM15" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN15" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BO15" t="n">
         <v>3.85</v>
@@ -4348,41 +4348,41 @@
         <v>14</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.9</v>
+        <v>10</v>
       </c>
       <c r="BR15" t="n">
         <v>25</v>
       </c>
       <c r="BS15" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BT15" t="n">
         <v>7.8</v>
       </c>
       <c r="BU15" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BV15" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BW15" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BX15" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BY15" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BZ15" t="n">
         <v>19</v>
       </c>
       <c r="CA15" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -4437,7 +4437,7 @@
         <v>1.04</v>
       </c>
       <c r="N16" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="O16" t="n">
         <v>1.23</v>
@@ -4446,7 +4446,7 @@
         <v>2.32</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R16" t="n">
         <v>1.52</v>
@@ -4455,10 +4455,10 @@
         <v>2.74</v>
       </c>
       <c r="T16" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U16" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V16" t="n">
         <v>1.28</v>
@@ -4494,7 +4494,7 @@
         <v>13.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH16" t="n">
         <v>17.5</v>
@@ -4503,7 +4503,7 @@
         <v>60</v>
       </c>
       <c r="AJ16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK16" t="n">
         <v>19</v>
@@ -4515,7 +4515,7 @@
         <v>85</v>
       </c>
       <c r="AN16" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO16" t="n">
         <v>48</v>
@@ -4527,22 +4527,22 @@
         <v>17</v>
       </c>
       <c r="AR16" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AS16" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT16" t="n">
         <v>10</v>
       </c>
       <c r="AU16" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV16" t="n">
         <v>15</v>
       </c>
       <c r="AW16" t="n">
-        <v>40</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX16" t="n">
         <v>11</v>
@@ -4566,13 +4566,13 @@
         <v>7.4</v>
       </c>
       <c r="BE16" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF16" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BG16" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BH16" t="n">
         <v>4.2</v>
@@ -4596,7 +4596,7 @@
         <v>5</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BP16" t="n">
         <v>13</v>
@@ -4632,11 +4632,11 @@
         <v>18.5</v>
       </c>
       <c r="CA16" t="n">
-        <v>13</v>
+        <v>6.4</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="G17" t="n">
         <v>1.2</v>
@@ -4676,13 +4676,13 @@
         <v>18</v>
       </c>
       <c r="I17" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="J17" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L17" t="n">
         <v>1.15</v>
@@ -4697,22 +4697,22 @@
         <v>1.1</v>
       </c>
       <c r="P17" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="R17" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="S17" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="T17" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="U17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V17" t="n">
         <v>1.04</v>
@@ -4736,10 +4736,10 @@
         <v>16.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AD17" t="n">
-        <v>540</v>
+        <v>650</v>
       </c>
       <c r="AE17" t="n">
         <v>1000</v>
@@ -4751,7 +4751,7 @@
         <v>13.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="AI17" t="n">
         <v>1000</v>
@@ -4769,7 +4769,7 @@
         <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AO17" t="n">
         <v>1000</v>
@@ -4787,13 +4787,13 @@
         <v>60</v>
       </c>
       <c r="AT17" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AU17" t="n">
-        <v>19.5</v>
+        <v>16</v>
       </c>
       <c r="AV17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AW17" t="n">
         <v>48</v>
@@ -4802,7 +4802,7 @@
         <v>10</v>
       </c>
       <c r="AY17" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ17" t="n">
         <v>22</v>
@@ -4823,7 +4823,7 @@
         <v>42</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="BG17" t="n">
         <v>46</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -4924,7 +4924,7 @@
         <v>2.28</v>
       </c>
       <c r="G18" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="H18" t="n">
         <v>3.4</v>
@@ -4936,7 +4936,7 @@
         <v>3.2</v>
       </c>
       <c r="K18" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="L18" t="n">
         <v>1.48</v>
@@ -4948,22 +4948,22 @@
         <v>3</v>
       </c>
       <c r="O18" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="P18" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="Q18" t="n">
         <v>2.22</v>
       </c>
       <c r="R18" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="S18" t="n">
-        <v>2.22</v>
+        <v>3.65</v>
       </c>
       <c r="T18" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="U18" t="n">
         <v>1.92</v>
@@ -4975,112 +4975,112 @@
         <v>1.68</v>
       </c>
       <c r="X18" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y18" t="n">
         <v>13</v>
       </c>
       <c r="Z18" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AA18" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AB18" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AC18" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AD18" t="n">
         <v>17.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF18" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AG18" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH18" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI18" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AJ18" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AK18" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AL18" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM18" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN18" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AO18" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP18" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.74</v>
+        <v>4.6</v>
       </c>
       <c r="AR18" t="n">
-        <v>2</v>
+        <v>5.8</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.97</v>
+        <v>6.6</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.7</v>
+        <v>4</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.63</v>
+        <v>3.7</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.8</v>
+        <v>5.1</v>
       </c>
       <c r="AW18" t="n">
-        <v>2</v>
+        <v>6.4</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="AY18" t="n">
-        <v>2</v>
+        <v>4.7</v>
       </c>
       <c r="AZ18" t="n">
-        <v>2</v>
+        <v>5.3</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.96</v>
+        <v>6.4</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.91</v>
+        <v>5.9</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.9</v>
+        <v>5.8</v>
       </c>
       <c r="BD18" t="n">
-        <v>2</v>
+        <v>6.4</v>
       </c>
       <c r="BE18" t="n">
-        <v>2</v>
+        <v>6.8</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.9</v>
+        <v>5.7</v>
       </c>
       <c r="BG18" t="n">
-        <v>2</v>
+        <v>6.4</v>
       </c>
       <c r="BH18" t="n">
         <v>3.05</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -5175,22 +5175,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="G19" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="H19" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="I19" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="J19" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K19" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
@@ -5199,7 +5199,7 @@
         <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="O19" t="n">
         <v>1.01</v>
@@ -5223,10 +5223,10 @@
         <v>1.11</v>
       </c>
       <c r="V19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X19" t="n">
         <v>1000</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -5429,37 +5429,37 @@
         </is>
       </c>
       <c r="F20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="O20" t="n">
         <v>1.02</v>
       </c>
-      <c r="G20" t="n">
-        <v>110</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="I20" t="n">
-        <v>110</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="K20" t="n">
-        <v>110</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N20" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.01</v>
-      </c>
       <c r="P20" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q20" t="n">
         <v>1.02</v>
@@ -5471,16 +5471,16 @@
         <v>1.46</v>
       </c>
       <c r="T20" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U20" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X20" t="n">
         <v>1000</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="G21" t="n">
         <v>2.24</v>
@@ -5692,7 +5692,7 @@
         <v>3.55</v>
       </c>
       <c r="I21" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J21" t="n">
         <v>3.6</v>
@@ -5716,7 +5716,7 @@
         <v>2.06</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="R21" t="n">
         <v>1.42</v>
@@ -5746,7 +5746,7 @@
         <v>42</v>
       </c>
       <c r="AA21" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AB21" t="n">
         <v>11.5</v>
@@ -5779,61 +5779,61 @@
         <v>22</v>
       </c>
       <c r="AL21" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AM21" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AN21" t="n">
         <v>14</v>
       </c>
       <c r="AO21" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AP21" t="n">
-        <v>14.5</v>
+        <v>6</v>
       </c>
       <c r="AQ21" t="n">
-        <v>13</v>
+        <v>5.9</v>
       </c>
       <c r="AR21" t="n">
-        <v>9.199999999999999</v>
+        <v>17.5</v>
       </c>
       <c r="AS21" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AT21" t="n">
-        <v>9.199999999999999</v>
+        <v>5.1</v>
       </c>
       <c r="AU21" t="n">
         <v>4.5</v>
       </c>
       <c r="AV21" t="n">
-        <v>13</v>
+        <v>5.9</v>
       </c>
       <c r="AW21" t="n">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AX21" t="n">
-        <v>12</v>
+        <v>5.7</v>
       </c>
       <c r="AY21" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ21" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="BA21" t="n">
         <v>7.8</v>
       </c>
       <c r="BB21" t="n">
-        <v>21</v>
+        <v>6.8</v>
       </c>
       <c r="BC21" t="n">
         <v>6.4</v>
       </c>
       <c r="BD21" t="n">
-        <v>9.199999999999999</v>
+        <v>20</v>
       </c>
       <c r="BE21" t="n">
         <v>8.199999999999999</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -5943,7 +5943,7 @@
         <v>1.39</v>
       </c>
       <c r="H22" t="n">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="I22" t="n">
         <v>11</v>
@@ -5961,28 +5961,28 @@
         <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>1.1</v>
+        <v>5.5</v>
       </c>
       <c r="O22" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="P22" t="n">
-        <v>1.25</v>
+        <v>2.54</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="R22" t="n">
-        <v>1.34</v>
+        <v>1.63</v>
       </c>
       <c r="S22" t="n">
-        <v>1.93</v>
+        <v>2.26</v>
       </c>
       <c r="T22" t="n">
-        <v>1.11</v>
+        <v>1.89</v>
       </c>
       <c r="U22" t="n">
-        <v>1.11</v>
+        <v>1.96</v>
       </c>
       <c r="V22" t="n">
         <v>1.1</v>
@@ -5991,112 +5991,112 @@
         <v>3.2</v>
       </c>
       <c r="X22" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Y22" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="Z22" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AA22" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="AB22" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AC22" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AD22" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AE22" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AF22" t="n">
-        <v>13</v>
+        <v>9.6</v>
       </c>
       <c r="AG22" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AH22" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="AI22" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ22" t="n">
-        <v>16</v>
+        <v>11.5</v>
       </c>
       <c r="AK22" t="n">
-        <v>19.5</v>
+        <v>14.5</v>
       </c>
       <c r="AL22" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="AM22" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN22" t="n">
-        <v>6.2</v>
+        <v>4.8</v>
       </c>
       <c r="AO22" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AP22" t="n">
-        <v>2.42</v>
+        <v>7.4</v>
       </c>
       <c r="AQ22" t="n">
-        <v>2.42</v>
+        <v>8</v>
       </c>
       <c r="AR22" t="n">
-        <v>2.42</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS22" t="n">
-        <v>2.42</v>
+        <v>9.4</v>
       </c>
       <c r="AT22" t="n">
-        <v>2.08</v>
+        <v>5.1</v>
       </c>
       <c r="AU22" t="n">
-        <v>2.14</v>
+        <v>5.7</v>
       </c>
       <c r="AV22" t="n">
-        <v>2.42</v>
+        <v>8</v>
       </c>
       <c r="AW22" t="n">
-        <v>2.42</v>
+        <v>9</v>
       </c>
       <c r="AX22" t="n">
-        <v>2.04</v>
+        <v>4.8</v>
       </c>
       <c r="AY22" t="n">
-        <v>2.08</v>
+        <v>5.1</v>
       </c>
       <c r="AZ22" t="n">
-        <v>2.26</v>
+        <v>7</v>
       </c>
       <c r="BA22" t="n">
-        <v>2.42</v>
+        <v>9</v>
       </c>
       <c r="BB22" t="n">
-        <v>2.1</v>
+        <v>5.2</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.14</v>
+        <v>5.8</v>
       </c>
       <c r="BD22" t="n">
-        <v>2.3</v>
+        <v>7.4</v>
       </c>
       <c r="BE22" t="n">
-        <v>2.42</v>
+        <v>9</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.74</v>
+        <v>3.2</v>
       </c>
       <c r="BG22" t="n">
-        <v>2.42</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH22" t="n">
         <v>4.6</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -6200,7 +6200,7 @@
         <v>23</v>
       </c>
       <c r="I23" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J23" t="n">
         <v>8.199999999999999</v>
@@ -6236,7 +6236,7 @@
         <v>2.68</v>
       </c>
       <c r="U23" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="V23" t="n">
         <v>1.03</v>
@@ -6275,7 +6275,7 @@
         <v>14.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AI23" t="n">
         <v>540</v>
@@ -6305,16 +6305,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AR23" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AS23" t="n">
         <v>6.8</v>
       </c>
       <c r="AT23" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AU23" t="n">
-        <v>6.8</v>
+        <v>15.5</v>
       </c>
       <c r="AV23" t="n">
         <v>9.199999999999999</v>
@@ -6332,19 +6332,19 @@
         <v>8.6</v>
       </c>
       <c r="BA23" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BB23" t="n">
         <v>4.4</v>
       </c>
       <c r="BC23" t="n">
-        <v>6.2</v>
+        <v>12</v>
       </c>
       <c r="BD23" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BE23" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF23" t="n">
         <v>3.25</v>
@@ -6356,7 +6356,7 @@
         <v>4.7</v>
       </c>
       <c r="BI23" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="BJ23" t="n">
         <v>18</v>
@@ -6410,11 +6410,11 @@
         <v>9</v>
       </c>
       <c r="CA23" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -6454,7 +6454,7 @@
         <v>5.5</v>
       </c>
       <c r="I24" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J24" t="n">
         <v>4.1</v>
@@ -6586,7 +6586,7 @@
         <v>19</v>
       </c>
       <c r="BA24" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB24" t="n">
         <v>14</v>
@@ -6598,7 +6598,7 @@
         <v>7.4</v>
       </c>
       <c r="BE24" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF24" t="n">
         <v>8.6</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -6699,7 +6699,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="G25" t="n">
         <v>2.06</v>
@@ -6708,7 +6708,7 @@
         <v>3.55</v>
       </c>
       <c r="I25" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J25" t="n">
         <v>4.1</v>
@@ -6723,7 +6723,7 @@
         <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>5.1</v>
+        <v>3.45</v>
       </c>
       <c r="O25" t="n">
         <v>1.16</v>
@@ -6744,7 +6744,7 @@
         <v>1.52</v>
       </c>
       <c r="U25" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="V25" t="n">
         <v>1.31</v>
@@ -6759,7 +6759,7 @@
         <v>26</v>
       </c>
       <c r="Z25" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA25" t="n">
         <v>80</v>
@@ -6771,7 +6771,7 @@
         <v>12.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AE25" t="n">
         <v>44</v>
@@ -6789,7 +6789,7 @@
         <v>44</v>
       </c>
       <c r="AJ25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK25" t="n">
         <v>21</v>
@@ -6804,58 +6804,58 @@
         <v>8.6</v>
       </c>
       <c r="AO25" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AP25" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AQ25" t="n">
         <v>4.6</v>
       </c>
-      <c r="AQ25" t="n">
+      <c r="AR25" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC25" t="n">
         <v>4.4</v>
       </c>
-      <c r="AR25" t="n">
+      <c r="BD25" t="n">
         <v>4.7</v>
       </c>
-      <c r="AS25" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BE25" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BF25" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BG25" t="n">
         <v>4.6</v>
@@ -6864,34 +6864,34 @@
         <v>4.8</v>
       </c>
       <c r="BI25" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BJ25" t="n">
         <v>9</v>
       </c>
       <c r="BK25" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BN25" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BO25" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="BP25" t="n">
         <v>13</v>
       </c>
       <c r="BQ25" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BR25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BS25" t="n">
         <v>6.8</v>
@@ -6900,29 +6900,29 @@
         <v>8</v>
       </c>
       <c r="BU25" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BV25" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BW25" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BX25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY25" t="n">
         <v>7.4</v>
-      </c>
-      <c r="BX25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY25" t="n">
-        <v>7.8</v>
       </c>
       <c r="BZ25" t="n">
         <v>14.5</v>
       </c>
       <c r="CA25" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="G26" t="n">
         <v>1.5</v>
@@ -6962,10 +6962,10 @@
         <v>7.2</v>
       </c>
       <c r="I26" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J26" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K26" t="n">
         <v>5.2</v>
@@ -6986,7 +6986,7 @@
         <v>2.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="R26" t="n">
         <v>1.43</v>
@@ -7085,10 +7085,10 @@
         <v>5.5</v>
       </c>
       <c r="AX26" t="n">
-        <v>3.45</v>
+        <v>7.6</v>
       </c>
       <c r="AY26" t="n">
-        <v>9</v>
+        <v>3.85</v>
       </c>
       <c r="AZ26" t="n">
         <v>4.8</v>
@@ -7100,7 +7100,7 @@
         <v>4.1</v>
       </c>
       <c r="BC26" t="n">
-        <v>13.5</v>
+        <v>4.3</v>
       </c>
       <c r="BD26" t="n">
         <v>5</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -7207,22 +7207,22 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="G27" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="H27" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="I27" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J27" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="K27" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L27" t="n">
         <v>1.42</v>
@@ -7240,7 +7240,7 @@
         <v>1.71</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="R27" t="n">
         <v>1.26</v>
@@ -7249,37 +7249,37 @@
         <v>4.1</v>
       </c>
       <c r="T27" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="U27" t="n">
         <v>1.91</v>
       </c>
       <c r="V27" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W27" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="X27" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y27" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA27" t="n">
         <v>130</v>
       </c>
       <c r="AB27" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC27" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE27" t="n">
         <v>90</v>
@@ -7309,10 +7309,10 @@
         <v>160</v>
       </c>
       <c r="AN27" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AO27" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AP27" t="n">
         <v>9.6</v>
@@ -7321,10 +7321,10 @@
         <v>11.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AS27" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AT27" t="n">
         <v>6.8</v>
@@ -7336,7 +7336,7 @@
         <v>15.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AX27" t="n">
         <v>10</v>
@@ -7372,19 +7372,19 @@
         <v>3.05</v>
       </c>
       <c r="BI27" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="BJ27" t="n">
         <v>10.5</v>
       </c>
       <c r="BK27" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BL27" t="n">
         <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BN27" t="n">
         <v>4.6</v>
@@ -7396,13 +7396,13 @@
         <v>15.5</v>
       </c>
       <c r="BQ27" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BR27" t="n">
         <v>34</v>
       </c>
       <c r="BS27" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BT27" t="n">
         <v>7.6</v>
@@ -7414,23 +7414,23 @@
         <v>42</v>
       </c>
       <c r="BW27" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BX27" t="n">
         <v>60</v>
       </c>
       <c r="BY27" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BZ27" t="n">
         <v>34</v>
       </c>
       <c r="CA27" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -7494,7 +7494,7 @@
         <v>1.42</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="R28" t="n">
         <v>1.15</v>
@@ -7512,7 +7512,7 @@
         <v>1.24</v>
       </c>
       <c r="W28" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="X28" t="n">
         <v>7.2</v>
@@ -7551,7 +7551,7 @@
         <v>170</v>
       </c>
       <c r="AJ28" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AK28" t="n">
         <v>36</v>
@@ -7587,7 +7587,7 @@
         <v>6.6</v>
       </c>
       <c r="AV28" t="n">
-        <v>8.6</v>
+        <v>19</v>
       </c>
       <c r="AW28" t="n">
         <v>12.5</v>
@@ -7626,65 +7626,65 @@
         <v>2.46</v>
       </c>
       <c r="BI28" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="BJ28" t="n">
         <v>13</v>
       </c>
       <c r="BK28" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BL28" t="n">
         <v>1000</v>
       </c>
       <c r="BM28" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="BN28" t="n">
         <v>4.6</v>
       </c>
       <c r="BO28" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BP28" t="n">
         <v>1000</v>
       </c>
       <c r="BQ28" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR28" t="n">
         <v>1000</v>
       </c>
       <c r="BS28" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BT28" t="n">
         <v>8</v>
       </c>
       <c r="BU28" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BV28" t="n">
         <v>1000</v>
       </c>
       <c r="BW28" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BX28" t="n">
         <v>1000</v>
       </c>
       <c r="BY28" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BZ28" t="n">
         <v>1000</v>
       </c>
       <c r="CA28" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -7715,10 +7715,10 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="G29" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="H29" t="n">
         <v>3.1</v>
@@ -7733,13 +7733,13 @@
         <v>3.4</v>
       </c>
       <c r="L29" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="M29" t="n">
         <v>1.1</v>
       </c>
       <c r="N29" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="O29" t="n">
         <v>1.46</v>
@@ -7748,7 +7748,7 @@
         <v>1.65</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="R29" t="n">
         <v>1.23</v>
@@ -7757,13 +7757,13 @@
         <v>4.5</v>
       </c>
       <c r="T29" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="U29" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="V29" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W29" t="n">
         <v>1.58</v>
@@ -7775,7 +7775,7 @@
         <v>12.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AA29" t="n">
         <v>75</v>
@@ -7784,10 +7784,10 @@
         <v>9</v>
       </c>
       <c r="AC29" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE29" t="n">
         <v>55</v>
@@ -7799,7 +7799,7 @@
         <v>15</v>
       </c>
       <c r="AH29" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AI29" t="n">
         <v>65</v>
@@ -7826,28 +7826,28 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AQ29" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="AR29" t="n">
-        <v>4</v>
+        <v>17.5</v>
       </c>
       <c r="AS29" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="AT29" t="n">
         <v>7.4</v>
       </c>
       <c r="AU29" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AV29" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="AW29" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX29" t="n">
         <v>4.4</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>3.85</v>
       </c>
       <c r="AY29" t="n">
         <v>10.5</v>
@@ -7856,31 +7856,31 @@
         <v>17.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="BB29" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="BC29" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BD29" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="BE29" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="BF29" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="BG29" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="BH29" t="n">
         <v>3</v>
       </c>
       <c r="BI29" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="BJ29" t="n">
         <v>11</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -7978,7 +7978,7 @@
         <v>7</v>
       </c>
       <c r="I30" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J30" t="n">
         <v>5</v>
@@ -8020,7 +8020,7 @@
         <v>1.15</v>
       </c>
       <c r="W30" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="X30" t="n">
         <v>24</v>
@@ -8059,7 +8059,7 @@
         <v>85</v>
       </c>
       <c r="AJ30" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AK30" t="n">
         <v>14.5</v>
@@ -8086,7 +8086,7 @@
         <v>55</v>
       </c>
       <c r="AS30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT30" t="n">
         <v>9.4</v>
@@ -8098,7 +8098,7 @@
         <v>24</v>
       </c>
       <c r="AW30" t="n">
-        <v>75</v>
+        <v>16.5</v>
       </c>
       <c r="AX30" t="n">
         <v>9.199999999999999</v>
@@ -8122,13 +8122,13 @@
         <v>24</v>
       </c>
       <c r="BE30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BF30" t="n">
         <v>5.5</v>
       </c>
       <c r="BG30" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BH30" t="n">
         <v>4.2</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -8232,7 +8232,7 @@
         <v>5.4</v>
       </c>
       <c r="I31" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="J31" t="n">
         <v>4</v>
@@ -8241,7 +8241,7 @@
         <v>4.4</v>
       </c>
       <c r="L31" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="M31" t="n">
         <v>1.07</v>
@@ -8253,16 +8253,16 @@
         <v>1.32</v>
       </c>
       <c r="P31" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="R31" t="n">
         <v>1.35</v>
       </c>
       <c r="S31" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="T31" t="n">
         <v>1.96</v>
@@ -8271,7 +8271,7 @@
         <v>1.89</v>
       </c>
       <c r="V31" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="W31" t="n">
         <v>2.44</v>
@@ -8331,58 +8331,58 @@
         <v>160</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AS31" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AT31" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BA31" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BD31" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BG31" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH31" t="n">
         <v>3.5</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -8486,10 +8486,10 @@
         <v>2.66</v>
       </c>
       <c r="I32" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J32" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="K32" t="n">
         <v>4</v>
@@ -8510,22 +8510,22 @@
         <v>2.1</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="R32" t="n">
         <v>1.44</v>
       </c>
       <c r="S32" t="n">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="T32" t="n">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="U32" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="V32" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W32" t="n">
         <v>1.55</v>
@@ -8579,10 +8579,10 @@
         <v>85</v>
       </c>
       <c r="AN32" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AO32" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AP32" t="n">
         <v>1.03</v>
@@ -8642,7 +8642,7 @@
         <v>3.85</v>
       </c>
       <c r="BI32" t="n">
-        <v>2.76</v>
+        <v>3.1</v>
       </c>
       <c r="BJ32" t="n">
         <v>9.199999999999999</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -8743,7 +8743,7 @@
         <v>1000</v>
       </c>
       <c r="J33" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="K33" t="n">
         <v>1000</v>
@@ -8770,7 +8770,7 @@
         <v>1.07</v>
       </c>
       <c r="S33" t="n">
-        <v>1.26</v>
+        <v>2.58</v>
       </c>
       <c r="T33" t="n">
         <v>1.11</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -9239,7 +9239,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="G35" t="n">
         <v>2.1</v>
@@ -9248,16 +9248,16 @@
         <v>4.1</v>
       </c>
       <c r="I35" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J35" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K35" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L35" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="M35" t="n">
         <v>1.08</v>
@@ -9284,7 +9284,7 @@
         <v>1.9</v>
       </c>
       <c r="U35" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="V35" t="n">
         <v>1.27</v>
@@ -9314,7 +9314,7 @@
         <v>18.5</v>
       </c>
       <c r="AE35" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AF35" t="n">
         <v>12.5</v>
@@ -9326,7 +9326,7 @@
         <v>22</v>
       </c>
       <c r="AI35" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AJ35" t="n">
         <v>25</v>
@@ -9341,7 +9341,7 @@
         <v>150</v>
       </c>
       <c r="AN35" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AO35" t="n">
         <v>80</v>
@@ -9353,10 +9353,10 @@
         <v>11.5</v>
       </c>
       <c r="AR35" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS35" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT35" t="n">
         <v>7.2</v>
@@ -9368,7 +9368,7 @@
         <v>15</v>
       </c>
       <c r="AW35" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AX35" t="n">
         <v>10</v>
@@ -9380,7 +9380,7 @@
         <v>17</v>
       </c>
       <c r="BA35" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB35" t="n">
         <v>20</v>
@@ -9389,16 +9389,16 @@
         <v>21</v>
       </c>
       <c r="BD35" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BE35" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF35" t="n">
         <v>15</v>
       </c>
       <c r="BG35" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH35" t="n">
         <v>3.25</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -9502,13 +9502,13 @@
         <v>1.04</v>
       </c>
       <c r="I36" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="J36" t="n">
         <v>1.01</v>
       </c>
       <c r="K36" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="L36" t="n">
         <v>1.01</v>
@@ -9523,7 +9523,7 @@
         <v>1.09</v>
       </c>
       <c r="P36" t="n">
-        <v>1.12</v>
+        <v>1.45</v>
       </c>
       <c r="Q36" t="n">
         <v>1.09</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -9753,7 +9753,7 @@
         <v>2.58</v>
       </c>
       <c r="H37" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I37" t="n">
         <v>3.65</v>
@@ -9762,10 +9762,10 @@
         <v>3.05</v>
       </c>
       <c r="K37" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L37" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="M37" t="n">
         <v>1.11</v>
@@ -9810,7 +9810,7 @@
         <v>23</v>
       </c>
       <c r="AA37" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="AB37" t="n">
         <v>8.199999999999999</v>
@@ -9822,13 +9822,13 @@
         <v>15.5</v>
       </c>
       <c r="AE37" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AF37" t="n">
         <v>15</v>
       </c>
       <c r="AG37" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH37" t="n">
         <v>22</v>
@@ -9864,7 +9864,7 @@
         <v>20</v>
       </c>
       <c r="AS37" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AT37" t="n">
         <v>7.2</v>
@@ -9888,7 +9888,7 @@
         <v>18.5</v>
       </c>
       <c r="BA37" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BB37" t="n">
         <v>25</v>
@@ -9897,16 +9897,16 @@
         <v>24</v>
       </c>
       <c r="BD37" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE37" t="n">
         <v>10</v>
       </c>
       <c r="BF37" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="BG37" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BH37" t="n">
         <v>2.84</v>
@@ -9948,7 +9948,7 @@
         <v>6.4</v>
       </c>
       <c r="BU37" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="BV37" t="n">
         <v>32</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -10007,7 +10007,7 @@
         <v>3.25</v>
       </c>
       <c r="H38" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="I38" t="n">
         <v>3.25</v>
@@ -10016,7 +10016,7 @@
         <v>2.76</v>
       </c>
       <c r="K38" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="L38" t="n">
         <v>1.57</v>
@@ -10028,13 +10028,13 @@
         <v>2.3</v>
       </c>
       <c r="O38" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="P38" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="R38" t="n">
         <v>1.18</v>
@@ -10043,10 +10043,10 @@
         <v>6.2</v>
       </c>
       <c r="T38" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="U38" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="V38" t="n">
         <v>1.44</v>
@@ -10058,7 +10058,7 @@
         <v>7.8</v>
       </c>
       <c r="Y38" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z38" t="n">
         <v>19</v>
@@ -10109,16 +10109,16 @@
         <v>75</v>
       </c>
       <c r="AP38" t="n">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ38" t="n">
         <v>4.3</v>
       </c>
       <c r="AR38" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AS38" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT38" t="n">
         <v>4.3</v>
@@ -10127,7 +10127,7 @@
         <v>4</v>
       </c>
       <c r="AV38" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AW38" t="n">
         <v>7.8</v>
@@ -10136,31 +10136,31 @@
         <v>6.2</v>
       </c>
       <c r="AY38" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AZ38" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BA38" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB38" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BC38" t="n">
         <v>7.8</v>
       </c>
       <c r="BD38" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BE38" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF38" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG38" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH38" t="n">
         <v>1000</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -10255,7 +10255,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="G39" t="n">
         <v>1.51</v>
@@ -10291,46 +10291,46 @@
         <v>1.75</v>
       </c>
       <c r="R39" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S39" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="T39" t="n">
         <v>1.92</v>
       </c>
       <c r="U39" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="V39" t="n">
         <v>1.14</v>
       </c>
       <c r="W39" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="X39" t="n">
         <v>21</v>
       </c>
       <c r="Y39" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Z39" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AA39" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AB39" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AC39" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD39" t="n">
         <v>28</v>
       </c>
       <c r="AE39" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AF39" t="n">
         <v>9.4</v>
@@ -10342,7 +10342,7 @@
         <v>24</v>
       </c>
       <c r="AI39" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ39" t="n">
         <v>13</v>
@@ -10357,7 +10357,7 @@
         <v>140</v>
       </c>
       <c r="AN39" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AO39" t="n">
         <v>130</v>
@@ -10372,10 +10372,10 @@
         <v>50</v>
       </c>
       <c r="AS39" t="n">
-        <v>13.5</v>
+        <v>48</v>
       </c>
       <c r="AT39" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AU39" t="n">
         <v>10</v>
@@ -10384,19 +10384,19 @@
         <v>25</v>
       </c>
       <c r="AW39" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="AX39" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AY39" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AZ39" t="n">
         <v>21</v>
       </c>
       <c r="BA39" t="n">
-        <v>12.5</v>
+        <v>36</v>
       </c>
       <c r="BB39" t="n">
         <v>12</v>
@@ -10408,13 +10408,13 @@
         <v>29</v>
       </c>
       <c r="BE39" t="n">
-        <v>13.5</v>
+        <v>42</v>
       </c>
       <c r="BF39" t="n">
         <v>6.2</v>
       </c>
       <c r="BG39" t="n">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="BH39" t="n">
         <v>4</v>
@@ -10426,13 +10426,13 @@
         <v>11.5</v>
       </c>
       <c r="BK39" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BL39" t="n">
         <v>1000</v>
       </c>
       <c r="BM39" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BN39" t="n">
         <v>4.1</v>
@@ -10444,13 +10444,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BQ39" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BR39" t="n">
         <v>25</v>
       </c>
       <c r="BS39" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="BT39" t="n">
         <v>11.5</v>
@@ -10465,7 +10465,7 @@
         <v>48</v>
       </c>
       <c r="BX39" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BY39" t="n">
         <v>48</v>
@@ -10474,11 +10474,11 @@
         <v>15.5</v>
       </c>
       <c r="CA39" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -10512,19 +10512,19 @@
         <v>2.1</v>
       </c>
       <c r="G40" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H40" t="n">
         <v>3.65</v>
       </c>
       <c r="I40" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="J40" t="n">
         <v>3.55</v>
       </c>
       <c r="K40" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L40" t="n">
         <v>1.31</v>
@@ -10557,13 +10557,13 @@
         <v>2.14</v>
       </c>
       <c r="V40" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W40" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="X40" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y40" t="n">
         <v>18</v>
@@ -10578,7 +10578,7 @@
         <v>12.5</v>
       </c>
       <c r="AC40" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD40" t="n">
         <v>19</v>
@@ -10611,7 +10611,7 @@
         <v>110</v>
       </c>
       <c r="AN40" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AO40" t="n">
         <v>50</v>
@@ -10623,10 +10623,10 @@
         <v>12.5</v>
       </c>
       <c r="AR40" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AS40" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AT40" t="n">
         <v>8.800000000000001</v>
@@ -10638,7 +10638,7 @@
         <v>13</v>
       </c>
       <c r="AW40" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AX40" t="n">
         <v>11.5</v>
@@ -10650,31 +10650,31 @@
         <v>14.5</v>
       </c>
       <c r="BA40" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BB40" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="BC40" t="n">
         <v>18.5</v>
       </c>
       <c r="BD40" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BE40" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BF40" t="n">
         <v>11</v>
       </c>
       <c r="BG40" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BH40" t="n">
         <v>3.7</v>
       </c>
       <c r="BI40" t="n">
-        <v>3.15</v>
+        <v>2.86</v>
       </c>
       <c r="BJ40" t="n">
         <v>9.800000000000001</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -10775,7 +10775,7 @@
         <v>2</v>
       </c>
       <c r="J41" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K41" t="n">
         <v>4.2</v>
@@ -10793,13 +10793,13 @@
         <v>1.26</v>
       </c>
       <c r="P41" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q41" t="n">
         <v>1.76</v>
       </c>
       <c r="R41" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S41" t="n">
         <v>2.96</v>
@@ -10925,16 +10925,16 @@
         <v>10</v>
       </c>
       <c r="BH41" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BI41" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="BJ41" t="n">
         <v>9.4</v>
       </c>
       <c r="BK41" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BL41" t="n">
         <v>1000</v>
@@ -10949,7 +10949,7 @@
         <v>5.8</v>
       </c>
       <c r="BP41" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BQ41" t="n">
         <v>10.5</v>
@@ -10979,14 +10979,14 @@
         <v>9.6</v>
       </c>
       <c r="BZ41" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="CA41" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -11017,28 +11017,28 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="G42" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="H42" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="I42" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="J42" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="K42" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="L42" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="M42" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N42" t="n">
         <v>4</v>
@@ -11047,142 +11047,142 @@
         <v>1.26</v>
       </c>
       <c r="P42" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="R42" t="n">
         <v>1.41</v>
       </c>
       <c r="S42" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="T42" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="U42" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="V42" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="W42" t="n">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="X42" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="Y42" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="Z42" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AA42" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AB42" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC42" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>48</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>22</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT42" t="n">
         <v>9.4</v>
       </c>
-      <c r="AD42" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF42" t="n">
+      <c r="AU42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV42" t="n">
         <v>13.5</v>
       </c>
-      <c r="AG42" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>20</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN42" t="n">
+      <c r="AW42" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ42" t="n">
         <v>12</v>
       </c>
-      <c r="AO42" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP42" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ42" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU42" t="n">
+      <c r="BA42" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>17</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>22</v>
+      </c>
+      <c r="BE42" t="n">
         <v>7.6</v>
       </c>
-      <c r="AV42" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW42" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AX42" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY42" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ42" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA42" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BB42" t="n">
-        <v>18</v>
-      </c>
-      <c r="BC42" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD42" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BE42" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BF42" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BG42" t="n">
-        <v>9.199999999999999</v>
+        <v>28</v>
       </c>
       <c r="BH42" t="n">
         <v>3.85</v>
       </c>
       <c r="BI42" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="BJ42" t="n">
         <v>9.800000000000001</v>
@@ -11194,7 +11194,7 @@
         <v>1000</v>
       </c>
       <c r="BM42" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="BN42" t="n">
         <v>4.9</v>
@@ -11209,16 +11209,16 @@
         <v>6</v>
       </c>
       <c r="BR42" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BS42" t="n">
         <v>7.6</v>
       </c>
       <c r="BT42" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BU42" t="n">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="BV42" t="n">
         <v>36</v>
@@ -11227,20 +11227,20 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BX42" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BY42" t="n">
         <v>2.66</v>
       </c>
       <c r="BZ42" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="CA42" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>
@@ -11271,7 +11271,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="G43" t="n">
         <v>3.15</v>
@@ -11280,10 +11280,10 @@
         <v>2.34</v>
       </c>
       <c r="I43" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="J43" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K43" t="n">
         <v>4</v>
@@ -11310,7 +11310,7 @@
         <v>1.61</v>
       </c>
       <c r="S43" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="T43" t="n">
         <v>1.56</v>
@@ -11319,7 +11319,7 @@
         <v>2.62</v>
       </c>
       <c r="V43" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="W43" t="n">
         <v>1.47</v>
@@ -11349,7 +11349,7 @@
         <v>23</v>
       </c>
       <c r="AF43" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG43" t="n">
         <v>16</v>
@@ -11370,7 +11370,7 @@
         <v>34</v>
       </c>
       <c r="AM43" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AN43" t="n">
         <v>20</v>
@@ -11379,7 +11379,7 @@
         <v>14</v>
       </c>
       <c r="AP43" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AQ43" t="n">
         <v>11.5</v>
@@ -11388,40 +11388,40 @@
         <v>14.5</v>
       </c>
       <c r="AS43" t="n">
-        <v>6.4</v>
+        <v>23</v>
       </c>
       <c r="AT43" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AU43" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV43" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AW43" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AX43" t="n">
         <v>18.5</v>
       </c>
       <c r="AY43" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AZ43" t="n">
         <v>11</v>
       </c>
       <c r="BA43" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BB43" t="n">
         <v>34</v>
       </c>
       <c r="BC43" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BD43" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BE43" t="n">
         <v>40</v>
@@ -11430,7 +11430,7 @@
         <v>14.5</v>
       </c>
       <c r="BG43" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BH43" t="n">
         <v>1000</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-16 05:00:01</t>
+          <t>2026-07-16 07:13:43</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-17.xlsx
@@ -896,13 +896,13 @@
         <v>1.4</v>
       </c>
       <c r="S2" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T2" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="U2" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V2" t="n">
         <v>1.87</v>
@@ -911,130 +911,130 @@
         <v>1.33</v>
       </c>
       <c r="X2" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>30</v>
+      </c>
+      <c r="AB2" t="n">
         <v>17</v>
       </c>
-      <c r="Y2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>26</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>15</v>
-      </c>
       <c r="AC2" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD2" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AF2" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AG2" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AH2" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AI2" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AJ2" t="n">
         <v>90</v>
       </c>
       <c r="AK2" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AL2" t="n">
         <v>55</v>
       </c>
       <c r="AM2" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AN2" t="n">
         <v>44</v>
       </c>
       <c r="AO2" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AP2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AR2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT2" t="n">
         <v>11.5</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>13</v>
       </c>
       <c r="AU2" t="n">
         <v>7.2</v>
       </c>
       <c r="AV2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AW2" t="n">
-        <v>8.199999999999999</v>
+        <v>17</v>
       </c>
       <c r="AX2" t="n">
-        <v>8.800000000000001</v>
+        <v>21</v>
       </c>
       <c r="AY2" t="n">
-        <v>7.2</v>
+        <v>14</v>
       </c>
       <c r="AZ2" t="n">
-        <v>7.4</v>
+        <v>4.5</v>
       </c>
       <c r="BA2" t="n">
         <v>30</v>
       </c>
       <c r="BB2" t="n">
-        <v>11</v>
+        <v>5.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>40</v>
+        <v>5.2</v>
       </c>
       <c r="BD2" t="n">
         <v>40</v>
       </c>
       <c r="BE2" t="n">
-        <v>11</v>
+        <v>5.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>34</v>
+        <v>5.2</v>
       </c>
       <c r="BG2" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BH2" t="n">
         <v>3.55</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="BJ2" t="n">
         <v>9.4</v>
       </c>
       <c r="BK2" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="BN2" t="n">
         <v>7.2</v>
@@ -1046,41 +1046,41 @@
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BT2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BU2" t="n">
         <v>3.95</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="G3" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="H3" t="n">
         <v>3.85</v>
@@ -1123,7 +1123,7 @@
         <v>4.1</v>
       </c>
       <c r="J3" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K3" t="n">
         <v>3.85</v>
@@ -1132,25 +1132,25 @@
         <v>1.39</v>
       </c>
       <c r="M3" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N3" t="n">
         <v>3.85</v>
       </c>
       <c r="O3" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P3" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="R3" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="S3" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T3" t="n">
         <v>1.73</v>
@@ -1162,28 +1162,28 @@
         <v>1.33</v>
       </c>
       <c r="W3" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="X3" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AA3" t="n">
         <v>90</v>
       </c>
       <c r="AB3" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD3" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AE3" t="n">
         <v>55</v>
@@ -1198,10 +1198,10 @@
         <v>21</v>
       </c>
       <c r="AI3" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AJ3" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK3" t="n">
         <v>27</v>
@@ -1213,10 +1213,10 @@
         <v>110</v>
       </c>
       <c r="AN3" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AO3" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AP3" t="n">
         <v>11</v>
@@ -1228,67 +1228,67 @@
         <v>20</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="AT3" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AV3" t="n">
         <v>11.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="AX3" t="n">
         <v>10</v>
       </c>
       <c r="AY3" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="AZ3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="BB3" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BC3" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="BF3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="BH3" t="n">
         <v>3.55</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="BJ3" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN3" t="n">
         <v>5.1</v>
@@ -1297,16 +1297,16 @@
         <v>3.9</v>
       </c>
       <c r="BP3" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BR3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BS3" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BT3" t="n">
         <v>7</v>
@@ -1318,23 +1318,23 @@
         <v>29</v>
       </c>
       <c r="BW3" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BX3" t="n">
         <v>40</v>
       </c>
       <c r="BY3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BZ3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="CA3" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="G4" t="n">
         <v>4.6</v>
       </c>
       <c r="H4" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="I4" t="n">
         <v>1.95</v>
@@ -1380,7 +1380,7 @@
         <v>3.65</v>
       </c>
       <c r="K4" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L4" t="n">
         <v>1.4</v>
@@ -1410,7 +1410,7 @@
         <v>1.77</v>
       </c>
       <c r="U4" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V4" t="n">
         <v>2.04</v>
@@ -1422,28 +1422,28 @@
         <v>17.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA4" t="n">
         <v>27</v>
       </c>
       <c r="AB4" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AD4" t="n">
         <v>12</v>
       </c>
       <c r="AE4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AF4" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AG4" t="n">
         <v>20</v>
@@ -1458,7 +1458,7 @@
         <v>110</v>
       </c>
       <c r="AK4" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AL4" t="n">
         <v>65</v>
@@ -1467,64 +1467,64 @@
         <v>110</v>
       </c>
       <c r="AN4" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AO4" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AP4" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AQ4" t="n">
         <v>8.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS4" t="n">
         <v>17.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU4" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV4" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AW4" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AX4" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="AY4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ4" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="BB4" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="BE4" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="BG4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BH4" t="n">
         <v>3.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -1625,10 +1625,10 @@
         <v>4.8</v>
       </c>
       <c r="H5" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="I5" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="J5" t="n">
         <v>4.1</v>
@@ -1637,73 +1637,73 @@
         <v>4.4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N5" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="O5" t="n">
         <v>1.21</v>
       </c>
       <c r="P5" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="R5" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="S5" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="T5" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="U5" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="V5" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="W5" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y5" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AC5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AD5" t="n">
-        <v>17.5</v>
+        <v>10.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AG5" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI5" t="n">
         <v>29</v>
@@ -1712,137 +1712,137 @@
         <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AM5" t="n">
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AO5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.97</v>
+        <v>16.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.7</v>
+        <v>11</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.97</v>
+        <v>12</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.97</v>
+        <v>17</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.97</v>
+        <v>18</v>
       </c>
       <c r="AU5" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AV5" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.97</v>
+        <v>14.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.97</v>
+        <v>22</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.78</v>
+        <v>15.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.77</v>
+        <v>14.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.84</v>
+        <v>19</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.97</v>
+        <v>36</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.97</v>
+        <v>26</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.97</v>
+        <v>38</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.97</v>
+        <v>32</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.97</v>
+        <v>24</v>
       </c>
       <c r="BG5" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BH5" t="n">
         <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN5" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BP5" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR5" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT5" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BV5" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX5" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -1876,16 +1876,16 @@
         <v>4.2</v>
       </c>
       <c r="G6" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="H6" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="I6" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="J6" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K6" t="n">
         <v>3.55</v>
@@ -1903,7 +1903,7 @@
         <v>1.43</v>
       </c>
       <c r="P6" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="Q6" t="n">
         <v>2.26</v>
@@ -1912,16 +1912,16 @@
         <v>1.23</v>
       </c>
       <c r="S6" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="T6" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="U6" t="n">
         <v>1.83</v>
       </c>
       <c r="V6" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="W6" t="n">
         <v>1.24</v>
@@ -1933,7 +1933,7 @@
         <v>9</v>
       </c>
       <c r="Z6" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AA6" t="n">
         <v>32</v>
@@ -1945,7 +1945,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD6" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AE6" t="n">
         <v>32</v>
@@ -1969,7 +1969,7 @@
         <v>90</v>
       </c>
       <c r="AL6" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AM6" t="n">
         <v>190</v>
@@ -1981,19 +1981,19 @@
         <v>26</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.3</v>
+        <v>7.6</v>
       </c>
       <c r="AQ6" t="n">
         <v>5.6</v>
       </c>
       <c r="AR6" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AS6" t="n">
-        <v>3.9</v>
+        <v>18.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.5</v>
+        <v>11</v>
       </c>
       <c r="AU6" t="n">
         <v>5.8</v>
@@ -2002,43 +2002,43 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW6" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AX6" t="n">
         <v>3.9</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>4</v>
       </c>
       <c r="AY6" t="n">
         <v>13.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>3.85</v>
+        <v>16</v>
       </c>
       <c r="BA6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC6" t="n">
         <v>4.1</v>
       </c>
-      <c r="BB6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BC6" t="n">
+      <c r="BD6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE6" t="n">
         <v>4.2</v>
       </c>
-      <c r="BD6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BF6" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.8</v>
+        <v>15.5</v>
       </c>
       <c r="BH6" t="n">
         <v>3.05</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="BJ6" t="n">
         <v>11.5</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -2148,16 +2148,16 @@
         <v>1.54</v>
       </c>
       <c r="M7" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="N7" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O7" t="n">
         <v>1.5</v>
       </c>
       <c r="P7" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="Q7" t="n">
         <v>2.5</v>
@@ -2166,13 +2166,13 @@
         <v>1.19</v>
       </c>
       <c r="S7" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="T7" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U7" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="V7" t="n">
         <v>1.69</v>
@@ -2181,7 +2181,7 @@
         <v>1.3</v>
       </c>
       <c r="X7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Y7" t="n">
         <v>7.6</v>
@@ -2205,22 +2205,22 @@
         <v>34</v>
       </c>
       <c r="AF7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG7" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AH7" t="n">
         <v>24</v>
       </c>
       <c r="AI7" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ7" t="n">
         <v>110</v>
       </c>
       <c r="AK7" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AL7" t="n">
         <v>100</v>
@@ -2247,7 +2247,7 @@
         <v>21</v>
       </c>
       <c r="AT7" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU7" t="n">
         <v>6.2</v>
@@ -2262,31 +2262,31 @@
         <v>17.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AZ7" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BA7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB7" t="n">
         <v>7.6</v>
       </c>
-      <c r="BB7" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BC7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE7" t="n">
         <v>7.8</v>
       </c>
-      <c r="BD7" t="n">
-        <v>8</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BF7" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BH7" t="n">
         <v>2.84</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -2381,100 +2381,100 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="G8" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="H8" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="I8" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="J8" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="K8" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="L8" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="M8" t="n">
         <v>1.03</v>
       </c>
       <c r="N8" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="O8" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="P8" t="n">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="R8" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="S8" t="n">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="T8" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="U8" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="V8" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="W8" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="X8" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Y8" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="Z8" t="n">
         <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>360</v>
       </c>
       <c r="AB8" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC8" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AD8" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AE8" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AF8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AG8" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH8" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="AI8" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AJ8" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AK8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AL8" t="n">
         <v>32</v>
@@ -2483,128 +2483,128 @@
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="AO8" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AP8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ8" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AR8" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="AS8" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AT8" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AU8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV8" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AW8" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AX8" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AY8" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA8" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BC8" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="BE8" t="n">
         <v>40</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="BG8" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BH8" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="BJ8" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BN8" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="BP8" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BR8" t="n">
         <v>22</v>
       </c>
       <c r="BS8" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BT8" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BU8" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="CA8" t="n">
-        <v>5.9</v>
+        <v>7.8</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="G9" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="H9" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="I9" t="n">
         <v>8</v>
       </c>
       <c r="J9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K9" t="n">
         <v>5.5</v>
-      </c>
-      <c r="K9" t="n">
-        <v>5.7</v>
       </c>
       <c r="L9" t="n">
         <v>1.21</v>
@@ -2662,43 +2662,43 @@
         <v>6.8</v>
       </c>
       <c r="O9" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="R9" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="S9" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="T9" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="U9" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="V9" t="n">
         <v>1.14</v>
       </c>
       <c r="W9" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="X9" t="n">
         <v>32</v>
       </c>
       <c r="Y9" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Z9" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AA9" t="n">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="AB9" t="n">
         <v>14.5</v>
@@ -2707,10 +2707,10 @@
         <v>13</v>
       </c>
       <c r="AD9" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AE9" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AF9" t="n">
         <v>12</v>
@@ -2719,10 +2719,10 @@
         <v>10.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI9" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ9" t="n">
         <v>14</v>
@@ -2737,22 +2737,22 @@
         <v>80</v>
       </c>
       <c r="AN9" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AO9" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AP9" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="AQ9" t="n">
         <v>32</v>
       </c>
       <c r="AR9" t="n">
-        <v>12.5</v>
+        <v>60</v>
       </c>
       <c r="AS9" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AT9" t="n">
         <v>12.5</v>
@@ -2761,10 +2761,10 @@
         <v>11.5</v>
       </c>
       <c r="AV9" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AW9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX9" t="n">
         <v>10.5</v>
@@ -2776,7 +2776,7 @@
         <v>17.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>12.5</v>
+        <v>55</v>
       </c>
       <c r="BB9" t="n">
         <v>12.5</v>
@@ -2788,13 +2788,13 @@
         <v>21</v>
       </c>
       <c r="BE9" t="n">
-        <v>12.5</v>
+        <v>60</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BG9" t="n">
-        <v>48</v>
+        <v>13.5</v>
       </c>
       <c r="BH9" t="n">
         <v>5.3</v>
@@ -2803,10 +2803,10 @@
         <v>4.4</v>
       </c>
       <c r="BJ9" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
@@ -2815,50 +2815,50 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BN9" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BP9" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BQ9" t="n">
         <v>4.7</v>
       </c>
       <c r="BR9" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BS9" t="n">
         <v>6.6</v>
       </c>
       <c r="BT9" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BV9" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BW9" t="n">
         <v>8.6</v>
       </c>
       <c r="BX9" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BY9" t="n">
         <v>8.4</v>
       </c>
       <c r="BZ9" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="CA9" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -2898,7 +2898,7 @@
         <v>2.62</v>
       </c>
       <c r="I10" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="J10" t="n">
         <v>4</v>
@@ -2925,7 +2925,7 @@
         <v>1.4</v>
       </c>
       <c r="R10" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="S10" t="n">
         <v>1.98</v>
@@ -2934,16 +2934,16 @@
         <v>1.4</v>
       </c>
       <c r="U10" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="V10" t="n">
         <v>1.57</v>
       </c>
       <c r="W10" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="X10" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="Y10" t="n">
         <v>24</v>
@@ -2955,7 +2955,7 @@
         <v>42</v>
       </c>
       <c r="AB10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AC10" t="n">
         <v>11.5</v>
@@ -2964,7 +2964,7 @@
         <v>14</v>
       </c>
       <c r="AE10" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AF10" t="n">
         <v>26</v>
@@ -2976,7 +2976,7 @@
         <v>13.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ10" t="n">
         <v>46</v>
@@ -2988,7 +2988,7 @@
         <v>25</v>
       </c>
       <c r="AM10" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN10" t="n">
         <v>10</v>
@@ -3021,13 +3021,13 @@
         <v>20</v>
       </c>
       <c r="AX10" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AY10" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BA10" t="n">
         <v>16.5</v>
@@ -3048,10 +3048,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BG10" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH10" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BI10" t="n">
         <v>4.8</v>
@@ -3060,31 +3060,31 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BN10" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BO10" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BP10" t="n">
         <v>16</v>
       </c>
       <c r="BQ10" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BR10" t="n">
         <v>20</v>
       </c>
       <c r="BS10" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BT10" t="n">
         <v>6.8</v>
@@ -3096,13 +3096,13 @@
         <v>17</v>
       </c>
       <c r="BW10" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BX10" t="n">
         <v>21</v>
       </c>
       <c r="BY10" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3146,7 @@
         <v>2.64</v>
       </c>
       <c r="G11" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="H11" t="n">
         <v>3</v>
@@ -3173,7 +3173,7 @@
         <v>1.41</v>
       </c>
       <c r="P11" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="Q11" t="n">
         <v>2.18</v>
@@ -3182,46 +3182,46 @@
         <v>1.25</v>
       </c>
       <c r="S11" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T11" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="U11" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="V11" t="n">
         <v>1.44</v>
       </c>
       <c r="W11" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X11" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Y11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB11" t="n">
         <v>11</v>
       </c>
-      <c r="Z11" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>9.4</v>
-      </c>
       <c r="AC11" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AD11" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AE11" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AF11" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AG11" t="n">
         <v>13</v>
@@ -3230,16 +3230,16 @@
         <v>21</v>
       </c>
       <c r="AI11" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL11" t="n">
         <v>60</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>55</v>
       </c>
       <c r="AM11" t="n">
         <v>160</v>
@@ -3257,10 +3257,10 @@
         <v>9</v>
       </c>
       <c r="AR11" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AS11" t="n">
-        <v>8</v>
+        <v>4.8</v>
       </c>
       <c r="AT11" t="n">
         <v>7.8</v>
@@ -3272,10 +3272,10 @@
         <v>11.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>34</v>
+        <v>4.7</v>
       </c>
       <c r="AX11" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY11" t="n">
         <v>10</v>
@@ -3284,22 +3284,22 @@
         <v>16.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>8</v>
+        <v>4.8</v>
       </c>
       <c r="BB11" t="n">
-        <v>32</v>
+        <v>4.7</v>
       </c>
       <c r="BC11" t="n">
-        <v>7.2</v>
+        <v>4.5</v>
       </c>
       <c r="BD11" t="n">
         <v>40</v>
       </c>
       <c r="BE11" t="n">
-        <v>8.6</v>
+        <v>5</v>
       </c>
       <c r="BF11" t="n">
-        <v>7.2</v>
+        <v>23</v>
       </c>
       <c r="BG11" t="n">
         <v>36</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -3400,10 +3400,10 @@
         <v>5.8</v>
       </c>
       <c r="G12" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="H12" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="I12" t="n">
         <v>1.64</v>
@@ -3412,7 +3412,7 @@
         <v>4.4</v>
       </c>
       <c r="K12" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -3421,16 +3421,16 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="O12" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P12" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="R12" t="n">
         <v>1.56</v>
@@ -3442,28 +3442,28 @@
         <v>1.7</v>
       </c>
       <c r="U12" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V12" t="n">
         <v>2.56</v>
       </c>
       <c r="W12" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X12" t="n">
         <v>25</v>
       </c>
       <c r="Y12" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="Z12" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AA12" t="n">
         <v>16</v>
       </c>
       <c r="AB12" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="AC12" t="n">
         <v>11.5</v>
@@ -3481,7 +3481,7 @@
         <v>25</v>
       </c>
       <c r="AH12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI12" t="n">
         <v>40</v>
@@ -3505,16 +3505,16 @@
         <v>6.8</v>
       </c>
       <c r="AP12" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="AQ12" t="n">
         <v>9.6</v>
       </c>
       <c r="AR12" t="n">
-        <v>5.2</v>
+        <v>9.4</v>
       </c>
       <c r="AS12" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AT12" t="n">
         <v>21</v>
@@ -3526,43 +3526,43 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AW12" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AX12" t="n">
-        <v>8.4</v>
+        <v>7</v>
       </c>
       <c r="AY12" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BD12" t="n">
         <v>7</v>
       </c>
-      <c r="AZ12" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BA12" t="n">
+      <c r="BE12" t="n">
         <v>7.2</v>
       </c>
-      <c r="BB12" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BF12" t="n">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="BG12" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="BH12" t="n">
         <v>4.5</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="BJ12" t="n">
         <v>10.5</v>
@@ -3574,7 +3574,7 @@
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.82</v>
+        <v>3.05</v>
       </c>
       <c r="BN12" t="n">
         <v>10.5</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3681,7 @@
         <v>1.1</v>
       </c>
       <c r="P13" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="Q13" t="n">
         <v>1.31</v>
@@ -3690,7 +3690,7 @@
         <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="T13" t="n">
         <v>1.63</v>
@@ -3702,10 +3702,10 @@
         <v>1.09</v>
       </c>
       <c r="W13" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="X13" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="Y13" t="n">
         <v>55</v>
@@ -3714,7 +3714,7 @@
         <v>120</v>
       </c>
       <c r="AA13" t="n">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="AB13" t="n">
         <v>19.5</v>
@@ -3738,7 +3738,7 @@
         <v>27</v>
       </c>
       <c r="AI13" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ13" t="n">
         <v>15</v>
@@ -3753,64 +3753,64 @@
         <v>85</v>
       </c>
       <c r="AN13" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="AO13" t="n">
         <v>85</v>
       </c>
       <c r="AP13" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="AQ13" t="n">
-        <v>5.7</v>
+        <v>30</v>
       </c>
       <c r="AR13" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="AS13" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="AT13" t="n">
-        <v>4.8</v>
+        <v>13</v>
       </c>
       <c r="AU13" t="n">
-        <v>4.8</v>
+        <v>13</v>
       </c>
       <c r="AV13" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AW13" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="AX13" t="n">
-        <v>4.5</v>
+        <v>10.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>4.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ13" t="n">
-        <v>5.2</v>
+        <v>19</v>
       </c>
       <c r="BA13" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="BB13" t="n">
-        <v>4.5</v>
+        <v>11</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.5</v>
+        <v>11.5</v>
       </c>
       <c r="BD13" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE13" t="n">
         <v>5.3</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>5.9</v>
       </c>
       <c r="BF13" t="n">
         <v>3</v>
       </c>
       <c r="BG13" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="BH13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -3935,7 +3935,7 @@
         <v>1.32</v>
       </c>
       <c r="P14" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="Q14" t="n">
         <v>1.94</v>
@@ -3944,7 +3944,7 @@
         <v>1.33</v>
       </c>
       <c r="S14" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="T14" t="n">
         <v>1.93</v>
@@ -3959,40 +3959,40 @@
         <v>1.16</v>
       </c>
       <c r="X14" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="Z14" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AA14" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AB14" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AD14" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AE14" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AF14" t="n">
         <v>55</v>
       </c>
       <c r="AG14" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AH14" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AI14" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AJ14" t="n">
         <v>220</v>
@@ -4010,61 +4010,61 @@
         <v>160</v>
       </c>
       <c r="AO14" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AP14" t="n">
-        <v>5.7</v>
+        <v>12</v>
       </c>
       <c r="AQ14" t="n">
-        <v>4.3</v>
+        <v>6.8</v>
       </c>
       <c r="AR14" t="n">
-        <v>4.8</v>
+        <v>8.4</v>
       </c>
       <c r="AS14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AT14" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>4.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV14" t="n">
-        <v>4.9</v>
+        <v>8.6</v>
       </c>
       <c r="AW14" t="n">
-        <v>6.2</v>
+        <v>15.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>7.8</v>
+        <v>4</v>
       </c>
       <c r="AY14" t="n">
-        <v>6.6</v>
+        <v>20</v>
       </c>
       <c r="AZ14" t="n">
-        <v>6.6</v>
+        <v>19</v>
       </c>
       <c r="BA14" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BB14" t="n">
-        <v>8.800000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="BC14" t="n">
-        <v>8.6</v>
+        <v>4.2</v>
       </c>
       <c r="BD14" t="n">
-        <v>8.6</v>
+        <v>4.2</v>
       </c>
       <c r="BE14" t="n">
-        <v>8.800000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="BF14" t="n">
-        <v>8.800000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="BG14" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="BH14" t="n">
         <v>3.5</v>
@@ -4076,37 +4076,37 @@
         <v>11.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>2.6</v>
+        <v>10</v>
       </c>
       <c r="BN14" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BO14" t="n">
-        <v>7</v>
+        <v>5.1</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>2.52</v>
+        <v>9</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>2.54</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT14" t="n">
         <v>4.3</v>
       </c>
       <c r="BU14" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="BV14" t="n">
         <v>12</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -4159,16 +4159,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="H15" t="n">
         <v>3.95</v>
       </c>
       <c r="I15" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J15" t="n">
         <v>4</v>
@@ -4177,22 +4177,22 @@
         <v>4.1</v>
       </c>
       <c r="L15" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M15" t="n">
         <v>1.05</v>
       </c>
       <c r="N15" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="O15" t="n">
         <v>1.24</v>
       </c>
       <c r="P15" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="R15" t="n">
         <v>1.52</v>
@@ -4204,7 +4204,7 @@
         <v>1.66</v>
       </c>
       <c r="U15" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="V15" t="n">
         <v>1.32</v>
@@ -4213,10 +4213,10 @@
         <v>2</v>
       </c>
       <c r="X15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y15" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="Z15" t="n">
         <v>32</v>
@@ -4231,22 +4231,22 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD15" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF15" t="n">
         <v>14</v>
       </c>
       <c r="AG15" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH15" t="n">
         <v>17</v>
       </c>
       <c r="AI15" t="n">
-        <v>140</v>
+        <v>48</v>
       </c>
       <c r="AJ15" t="n">
         <v>23</v>
@@ -4255,25 +4255,25 @@
         <v>19</v>
       </c>
       <c r="AL15" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM15" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN15" t="n">
         <v>10.5</v>
       </c>
       <c r="AO15" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AP15" t="n">
         <v>18</v>
       </c>
       <c r="AQ15" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="AS15" t="n">
         <v>48</v>
@@ -4288,7 +4288,7 @@
         <v>14.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="AX15" t="n">
         <v>12</v>
@@ -4297,92 +4297,92 @@
         <v>9.6</v>
       </c>
       <c r="AZ15" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA15" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="BB15" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BC15" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BE15" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="BF15" t="n">
         <v>9.6</v>
       </c>
       <c r="BG15" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BH15" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BJ15" t="n">
         <v>9.4</v>
       </c>
       <c r="BK15" t="n">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="BL15" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN15" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BO15" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="BP15" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BQ15" t="n">
-        <v>10</v>
+        <v>5.7</v>
       </c>
       <c r="BR15" t="n">
         <v>25</v>
       </c>
       <c r="BS15" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="BT15" t="n">
         <v>7.8</v>
       </c>
       <c r="BU15" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BV15" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BW15" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BX15" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BY15" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="BZ15" t="n">
         <v>19</v>
       </c>
       <c r="CA15" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -4413,25 +4413,25 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="G16" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="H16" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I16" t="n">
         <v>4.5</v>
       </c>
       <c r="J16" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K16" t="n">
         <v>4.3</v>
       </c>
       <c r="L16" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M16" t="n">
         <v>1.04</v>
@@ -4449,7 +4449,7 @@
         <v>1.69</v>
       </c>
       <c r="R16" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S16" t="n">
         <v>2.74</v>
@@ -4458,13 +4458,13 @@
         <v>1.67</v>
       </c>
       <c r="U16" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="V16" t="n">
         <v>1.28</v>
       </c>
       <c r="W16" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="X16" t="n">
         <v>22</v>
@@ -4476,7 +4476,7 @@
         <v>42</v>
       </c>
       <c r="AA16" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AB16" t="n">
         <v>12</v>
@@ -4485,10 +4485,10 @@
         <v>9.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF16" t="n">
         <v>13.5</v>
@@ -4512,16 +4512,16 @@
         <v>34</v>
       </c>
       <c r="AM16" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AN16" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AO16" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AP16" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AQ16" t="n">
         <v>16.5</v>
@@ -4548,7 +4548,7 @@
         <v>11</v>
       </c>
       <c r="AY16" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ16" t="n">
         <v>14.5</v>
@@ -4557,7 +4557,7 @@
         <v>8</v>
       </c>
       <c r="BB16" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BC16" t="n">
         <v>15.5</v>
@@ -4566,13 +4566,13 @@
         <v>7.2</v>
       </c>
       <c r="BE16" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF16" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BG16" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BH16" t="n">
         <v>4.2</v>
@@ -4596,7 +4596,7 @@
         <v>5</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="BP16" t="n">
         <v>13</v>
@@ -4614,7 +4614,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BU16" t="n">
-        <v>6.2</v>
+        <v>4.5</v>
       </c>
       <c r="BV16" t="n">
         <v>34</v>
@@ -4632,11 +4632,11 @@
         <v>18.5</v>
       </c>
       <c r="CA16" t="n">
-        <v>13</v>
+        <v>6.4</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -4676,7 +4676,7 @@
         <v>18</v>
       </c>
       <c r="I17" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="J17" t="n">
         <v>9.199999999999999</v>
@@ -4697,10 +4697,10 @@
         <v>1.1</v>
       </c>
       <c r="P17" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="R17" t="n">
         <v>2.2</v>
@@ -4709,7 +4709,7 @@
         <v>1.76</v>
       </c>
       <c r="T17" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="U17" t="n">
         <v>2.04</v>
@@ -4739,7 +4739,7 @@
         <v>32</v>
       </c>
       <c r="AD17" t="n">
-        <v>560</v>
+        <v>580</v>
       </c>
       <c r="AE17" t="n">
         <v>1000</v>
@@ -4763,13 +4763,13 @@
         <v>13.5</v>
       </c>
       <c r="AL17" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="AM17" t="n">
         <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="AO17" t="n">
         <v>1000</v>
@@ -4790,7 +4790,7 @@
         <v>15</v>
       </c>
       <c r="AU17" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AV17" t="n">
         <v>29</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -4921,19 +4921,19 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G18" t="n">
         <v>1000</v>
       </c>
       <c r="H18" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I18" t="n">
         <v>1000</v>
       </c>
       <c r="J18" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K18" t="n">
         <v>1000</v>
@@ -4945,13 +4945,13 @@
         <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="O18" t="n">
         <v>1.01</v>
       </c>
       <c r="P18" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="Q18" t="n">
         <v>1.01</v>
@@ -4960,13 +4960,13 @@
         <v>1.12</v>
       </c>
       <c r="S18" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="T18" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U18" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V18" t="n">
         <v>1.01</v>
@@ -5086,65 +5086,65 @@
         <v>1000</v>
       </c>
       <c r="BI18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ18" t="n">
         <v>1000</v>
       </c>
       <c r="BK18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN18" t="n">
         <v>1000</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP18" t="n">
         <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT18" t="n">
         <v>1000</v>
       </c>
       <c r="BU18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ18" t="n">
         <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -5175,112 +5175,112 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="G19" t="n">
-        <v>1000</v>
+        <v>2.54</v>
       </c>
       <c r="H19" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="I19" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="J19" t="n">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="K19" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="L19" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="M19" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="N19" t="n">
-        <v>1.08</v>
+        <v>2.12</v>
       </c>
       <c r="O19" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="P19" t="n">
-        <v>1.08</v>
+        <v>1.36</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="R19" t="n">
         <v>1.12</v>
       </c>
       <c r="S19" t="n">
-        <v>1.02</v>
+        <v>5.7</v>
       </c>
       <c r="T19" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="U19" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="V19" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="W19" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="X19" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="Y19" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z19" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB19" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AC19" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AE19" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF19" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AI19" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AK19" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL19" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AM19" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="AN19" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO19" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AP19" t="n">
         <v>1.01</v>
@@ -5298,7 +5298,7 @@
         <v>1.01</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AV19" t="n">
         <v>1.01</v>
@@ -5337,68 +5337,68 @@
         <v>1.01</v>
       </c>
       <c r="BH19" t="n">
-        <v>1000</v>
+        <v>2.7</v>
       </c>
       <c r="BI19" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="BJ19" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BK19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL19" t="n">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN19" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP19" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BQ19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR19" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BS19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT19" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV19" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BW19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX19" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ19" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="CA19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
         <v>2.26</v>
       </c>
       <c r="G20" t="n">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="H20" t="n">
         <v>3.2</v>
@@ -5450,10 +5450,10 @@
         <v>1.59</v>
       </c>
       <c r="M20" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="N20" t="n">
-        <v>2.4</v>
+        <v>2.16</v>
       </c>
       <c r="O20" t="n">
         <v>1.61</v>
@@ -5462,7 +5462,7 @@
         <v>1.38</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="R20" t="n">
         <v>1.13</v>
@@ -5480,61 +5480,61 @@
         <v>1.29</v>
       </c>
       <c r="W20" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="X20" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="Y20" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA20" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB20" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD20" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE20" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF20" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AG20" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI20" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AK20" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL20" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AM20" t="n">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AN20" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AO20" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AP20" t="n">
         <v>1.01</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -5683,112 +5683,112 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.26</v>
+        <v>2.14</v>
       </c>
       <c r="G21" t="n">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="H21" t="n">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="I21" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="J21" t="n">
         <v>2.62</v>
       </c>
       <c r="K21" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="L21" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M21" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N21" t="n">
-        <v>1.24</v>
+        <v>2.38</v>
       </c>
       <c r="O21" t="n">
-        <v>1.09</v>
+        <v>1.46</v>
       </c>
       <c r="P21" t="n">
-        <v>1.24</v>
+        <v>1.51</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.09</v>
+        <v>2.26</v>
       </c>
       <c r="R21" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="S21" t="n">
-        <v>1.09</v>
+        <v>4.2</v>
       </c>
       <c r="T21" t="n">
-        <v>1.11</v>
+        <v>1.95</v>
       </c>
       <c r="U21" t="n">
-        <v>1.11</v>
+        <v>1.75</v>
       </c>
       <c r="V21" t="n">
-        <v>1.02</v>
+        <v>1.29</v>
       </c>
       <c r="W21" t="n">
-        <v>1.04</v>
+        <v>1.51</v>
       </c>
       <c r="X21" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y21" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AA21" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AB21" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AC21" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF21" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH21" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI21" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AK21" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL21" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM21" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AN21" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AO21" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP21" t="n">
         <v>1.01</v>
@@ -5845,68 +5845,68 @@
         <v>1.01</v>
       </c>
       <c r="BH21" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="BI21" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="BJ21" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL21" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="BM21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN21" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP21" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BQ21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR21" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT21" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV21" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BW21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX21" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ21" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="CA21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -5937,25 +5937,25 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="G22" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="H22" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I22" t="n">
         <v>4.1</v>
       </c>
       <c r="J22" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K22" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L22" t="n">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="M22" t="n">
         <v>1.05</v>
@@ -5964,10 +5964,10 @@
         <v>4.2</v>
       </c>
       <c r="O22" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P22" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q22" t="n">
         <v>1.84</v>
@@ -5979,40 +5979,40 @@
         <v>2.92</v>
       </c>
       <c r="T22" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="U22" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V22" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W22" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="X22" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Z22" t="n">
         <v>42</v>
       </c>
       <c r="AA22" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AB22" t="n">
         <v>11.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD22" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AE22" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AF22" t="n">
         <v>15</v>
@@ -6027,140 +6027,140 @@
         <v>50</v>
       </c>
       <c r="AJ22" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK22" t="n">
         <v>22</v>
       </c>
       <c r="AL22" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AM22" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AN22" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AO22" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AP22" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="AQ22" t="n">
-        <v>5.9</v>
+        <v>13.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>17.5</v>
+        <v>6.4</v>
       </c>
       <c r="AS22" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AT22" t="n">
-        <v>5.1</v>
+        <v>9.4</v>
       </c>
       <c r="AU22" t="n">
-        <v>4.5</v>
+        <v>7.4</v>
       </c>
       <c r="AV22" t="n">
-        <v>5.9</v>
+        <v>13.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="AX22" t="n">
-        <v>5.7</v>
+        <v>11.5</v>
       </c>
       <c r="AY22" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ22" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="BA22" t="n">
-        <v>7.8</v>
+        <v>38</v>
       </c>
       <c r="BB22" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>28</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>27</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BT22" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BU22" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BV22" t="n">
+        <v>32</v>
+      </c>
+      <c r="BW22" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BX22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY22" t="n">
+        <v>8</v>
+      </c>
+      <c r="BZ22" t="n">
+        <v>22</v>
+      </c>
+      <c r="CA22" t="n">
         <v>6.8</v>
       </c>
-      <c r="BC22" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BH22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA22" t="n">
-        <v>1.01</v>
-      </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -6191,46 +6191,46 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="G23" t="n">
-        <v>2.14</v>
+        <v>1.97</v>
       </c>
       <c r="H23" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="I23" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="J23" t="n">
         <v>3.35</v>
       </c>
       <c r="K23" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L23" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M23" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N23" t="n">
-        <v>2.56</v>
+        <v>3.15</v>
       </c>
       <c r="O23" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="P23" t="n">
-        <v>1.57</v>
+        <v>1.76</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="R23" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="S23" t="n">
-        <v>2.6</v>
+        <v>3.55</v>
       </c>
       <c r="T23" t="n">
         <v>1.11</v>
@@ -6239,70 +6239,70 @@
         <v>1.11</v>
       </c>
       <c r="V23" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="W23" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="X23" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AA23" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB23" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AC23" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD23" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE23" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF23" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG23" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH23" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI23" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AK23" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL23" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM23" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN23" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AO23" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AR23" t="n">
         <v>1.01</v>
@@ -6311,34 +6311,34 @@
         <v>1.01</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AW23" t="n">
         <v>1.01</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BA23" t="n">
         <v>1.01</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BD23" t="n">
         <v>1.01</v>
@@ -6347,7 +6347,7 @@
         <v>1.01</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BG23" t="n">
         <v>1.01</v>
@@ -6356,55 +6356,55 @@
         <v>1000</v>
       </c>
       <c r="BI23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ23" t="n">
         <v>1000</v>
       </c>
       <c r="BK23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN23" t="n">
         <v>1000</v>
       </c>
       <c r="BO23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP23" t="n">
         <v>1000</v>
       </c>
       <c r="BQ23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR23" t="n">
         <v>1000</v>
       </c>
       <c r="BS23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT23" t="n">
         <v>1000</v>
       </c>
       <c r="BU23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV23" t="n">
         <v>1000</v>
       </c>
       <c r="BW23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX23" t="n">
         <v>1000</v>
       </c>
       <c r="BY23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ23" t="n">
         <v>0</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -6448,19 +6448,19 @@
         <v>1.04</v>
       </c>
       <c r="G24" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="H24" t="n">
         <v>1.04</v>
       </c>
       <c r="I24" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="J24" t="n">
         <v>1.02</v>
       </c>
       <c r="K24" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="L24" t="n">
         <v>1.01</v>
@@ -6610,55 +6610,55 @@
         <v>1000</v>
       </c>
       <c r="BI24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ24" t="n">
         <v>1000</v>
       </c>
       <c r="BK24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN24" t="n">
         <v>1000</v>
       </c>
       <c r="BO24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP24" t="n">
         <v>1000</v>
       </c>
       <c r="BQ24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR24" t="n">
         <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT24" t="n">
         <v>1000</v>
       </c>
       <c r="BU24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV24" t="n">
         <v>1000</v>
       </c>
       <c r="BW24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX24" t="n">
         <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ24" t="n">
         <v>0</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -6699,7 +6699,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="G25" t="n">
         <v>2.46</v>
@@ -6708,10 +6708,10 @@
         <v>3.4</v>
       </c>
       <c r="I25" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="J25" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K25" t="n">
         <v>3.5</v>
@@ -6726,7 +6726,7 @@
         <v>3</v>
       </c>
       <c r="O25" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P25" t="n">
         <v>1.67</v>
@@ -6738,16 +6738,16 @@
         <v>1.25</v>
       </c>
       <c r="S25" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="T25" t="n">
         <v>1.9</v>
       </c>
       <c r="U25" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="V25" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W25" t="n">
         <v>1.68</v>
@@ -6759,16 +6759,16 @@
         <v>13</v>
       </c>
       <c r="Z25" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA25" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AB25" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD25" t="n">
         <v>17.5</v>
@@ -6777,22 +6777,22 @@
         <v>60</v>
       </c>
       <c r="AF25" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AG25" t="n">
         <v>14</v>
       </c>
       <c r="AH25" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AI25" t="n">
         <v>65</v>
       </c>
       <c r="AJ25" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK25" t="n">
         <v>34</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>30</v>
       </c>
       <c r="AL25" t="n">
         <v>60</v>
@@ -6801,67 +6801,67 @@
         <v>150</v>
       </c>
       <c r="AN25" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AO25" t="n">
         <v>70</v>
       </c>
       <c r="AP25" t="n">
-        <v>4.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ25" t="n">
-        <v>4.6</v>
+        <v>8.6</v>
       </c>
       <c r="AR25" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AS25" t="n">
-        <v>6.6</v>
+        <v>4.8</v>
       </c>
       <c r="AT25" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AU25" t="n">
         <v>5.8</v>
       </c>
       <c r="AV25" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>6.4</v>
+        <v>4.7</v>
       </c>
       <c r="AX25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY25" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BG25" t="n">
         <v>4.8</v>
       </c>
-      <c r="AZ25" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BG25" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BH25" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BI25" t="n">
         <v>2.52</v>
@@ -6870,16 +6870,16 @@
         <v>10.5</v>
       </c>
       <c r="BK25" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BN25" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BO25" t="n">
         <v>3.65</v>
@@ -6888,31 +6888,31 @@
         <v>19</v>
       </c>
       <c r="BQ25" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BR25" t="n">
         <v>38</v>
       </c>
       <c r="BS25" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BT25" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BU25" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BV25" t="n">
         <v>34</v>
       </c>
       <c r="BW25" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX25" t="n">
         <v>1000</v>
       </c>
       <c r="BY25" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ25" t="n">
         <v>0</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -6959,13 +6959,13 @@
         <v>1.39</v>
       </c>
       <c r="H26" t="n">
-        <v>7</v>
+        <v>9.6</v>
       </c>
       <c r="I26" t="n">
         <v>11</v>
       </c>
       <c r="J26" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="K26" t="n">
         <v>6.4</v>
@@ -6977,7 +6977,7 @@
         <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="O26" t="n">
         <v>1.18</v>
@@ -6992,7 +6992,7 @@
         <v>1.63</v>
       </c>
       <c r="S26" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="T26" t="n">
         <v>1.89</v>
@@ -7004,7 +7004,7 @@
         <v>1.1</v>
       </c>
       <c r="W26" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="X26" t="n">
         <v>34</v>
@@ -7019,100 +7019,100 @@
         <v>400</v>
       </c>
       <c r="AB26" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AC26" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AE26" t="n">
         <v>170</v>
       </c>
       <c r="AF26" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AG26" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AH26" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AI26" t="n">
         <v>140</v>
       </c>
       <c r="AJ26" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AK26" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AL26" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AM26" t="n">
         <v>150</v>
       </c>
       <c r="AN26" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AO26" t="n">
         <v>190</v>
       </c>
       <c r="AP26" t="n">
-        <v>7.4</v>
+        <v>19.5</v>
       </c>
       <c r="AQ26" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT26" t="n">
         <v>8</v>
       </c>
-      <c r="AR26" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>5.1</v>
-      </c>
       <c r="AU26" t="n">
-        <v>5.7</v>
+        <v>10</v>
       </c>
       <c r="AV26" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY26" t="n">
         <v>8</v>
       </c>
-      <c r="AW26" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>5.1</v>
-      </c>
       <c r="AZ26" t="n">
-        <v>7</v>
+        <v>18.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>9</v>
+        <v>4.3</v>
       </c>
       <c r="BB26" t="n">
-        <v>5.2</v>
+        <v>8.4</v>
       </c>
       <c r="BC26" t="n">
-        <v>5.8</v>
+        <v>10</v>
       </c>
       <c r="BD26" t="n">
-        <v>7.4</v>
+        <v>4</v>
       </c>
       <c r="BE26" t="n">
-        <v>9</v>
+        <v>4.4</v>
       </c>
       <c r="BF26" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="BG26" t="n">
-        <v>9.199999999999999</v>
+        <v>4.4</v>
       </c>
       <c r="BH26" t="n">
         <v>4.6</v>
@@ -7160,13 +7160,13 @@
         <v>1000</v>
       </c>
       <c r="BW26" t="n">
+        <v>11</v>
+      </c>
+      <c r="BX26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY26" t="n">
         <v>3</v>
-      </c>
-      <c r="BX26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY26" t="n">
-        <v>8.800000000000001</v>
       </c>
       <c r="BZ26" t="n">
         <v>11</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -7210,7 +7210,7 @@
         <v>1.16</v>
       </c>
       <c r="G27" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="H27" t="n">
         <v>26</v>
@@ -7258,7 +7258,7 @@
         <v>1.03</v>
       </c>
       <c r="W27" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="X27" t="n">
         <v>36</v>
@@ -7396,16 +7396,16 @@
         <v>6.2</v>
       </c>
       <c r="BQ27" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="BR27" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS27" t="n">
         <v>7.8</v>
       </c>
       <c r="BT27" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BU27" t="n">
         <v>7.6</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -7479,7 +7479,7 @@
         <v>4.7</v>
       </c>
       <c r="L28" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M28" t="n">
         <v>1.06</v>
@@ -7491,13 +7491,13 @@
         <v>1.3</v>
       </c>
       <c r="P28" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="Q28" t="n">
         <v>1.86</v>
       </c>
       <c r="R28" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S28" t="n">
         <v>3.25</v>
@@ -7506,7 +7506,7 @@
         <v>1.9</v>
       </c>
       <c r="U28" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="V28" t="n">
         <v>1.19</v>
@@ -7518,13 +7518,13 @@
         <v>17</v>
       </c>
       <c r="Y28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z28" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AA28" t="n">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="AB28" t="n">
         <v>8.4</v>
@@ -7536,7 +7536,7 @@
         <v>24</v>
       </c>
       <c r="AE28" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AF28" t="n">
         <v>10.5</v>
@@ -7548,28 +7548,28 @@
         <v>24</v>
       </c>
       <c r="AI28" t="n">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="AJ28" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AK28" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AL28" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AM28" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AN28" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AO28" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AP28" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AQ28" t="n">
         <v>16</v>
@@ -7578,7 +7578,7 @@
         <v>38</v>
       </c>
       <c r="AS28" t="n">
-        <v>8.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="AT28" t="n">
         <v>7</v>
@@ -7587,104 +7587,104 @@
         <v>8.4</v>
       </c>
       <c r="AV28" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>8.4</v>
+        <v>6.4</v>
       </c>
       <c r="AX28" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY28" t="n">
         <v>8.4</v>
       </c>
       <c r="AZ28" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>8.4</v>
+        <v>6.4</v>
       </c>
       <c r="BB28" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BC28" t="n">
         <v>15</v>
       </c>
       <c r="BD28" t="n">
-        <v>7.4</v>
+        <v>26</v>
       </c>
       <c r="BE28" t="n">
-        <v>8.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="BF28" t="n">
         <v>8.6</v>
       </c>
       <c r="BG28" t="n">
-        <v>8.6</v>
+        <v>6.4</v>
       </c>
       <c r="BH28" t="n">
         <v>3.6</v>
       </c>
       <c r="BI28" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="BJ28" t="n">
         <v>11</v>
       </c>
       <c r="BK28" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BL28" t="n">
         <v>1000</v>
       </c>
       <c r="BM28" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN28" t="n">
         <v>4.4</v>
       </c>
       <c r="BO28" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BP28" t="n">
         <v>11.5</v>
       </c>
       <c r="BQ28" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR28" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BS28" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BT28" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU28" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BV28" t="n">
         <v>55</v>
       </c>
       <c r="BW28" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX28" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BY28" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BZ28" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="CA28" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -7727,7 +7727,7 @@
         <v>4.2</v>
       </c>
       <c r="J29" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K29" t="n">
         <v>4.8</v>
@@ -7739,16 +7739,16 @@
         <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>3.45</v>
+        <v>5.7</v>
       </c>
       <c r="O29" t="n">
         <v>1.16</v>
       </c>
       <c r="P29" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="R29" t="n">
         <v>1.65</v>
@@ -7757,13 +7757,13 @@
         <v>2.22</v>
       </c>
       <c r="T29" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="U29" t="n">
         <v>2.56</v>
       </c>
       <c r="V29" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W29" t="n">
         <v>1.95</v>
@@ -7790,10 +7790,10 @@
         <v>19</v>
       </c>
       <c r="AE29" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AF29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG29" t="n">
         <v>13</v>
@@ -7802,85 +7802,85 @@
         <v>18</v>
       </c>
       <c r="AI29" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AJ29" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK29" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AL29" t="n">
         <v>30</v>
       </c>
       <c r="AM29" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AN29" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO29" t="n">
         <v>29</v>
       </c>
       <c r="AP29" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AQ29" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AR29" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AS29" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AT29" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AU29" t="n">
-        <v>3.85</v>
+        <v>9</v>
       </c>
       <c r="AV29" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AW29" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD29" t="n">
         <v>4.9</v>
       </c>
-      <c r="AX29" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BE29" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BF29" t="n">
-        <v>3.35</v>
+        <v>6.4</v>
       </c>
       <c r="BG29" t="n">
-        <v>4.6</v>
+        <v>18.5</v>
       </c>
       <c r="BH29" t="n">
         <v>4.8</v>
       </c>
       <c r="BI29" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="BJ29" t="n">
         <v>9</v>
@@ -7898,7 +7898,7 @@
         <v>5.5</v>
       </c>
       <c r="BO29" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="BP29" t="n">
         <v>13</v>
@@ -7916,7 +7916,7 @@
         <v>8</v>
       </c>
       <c r="BU29" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="BV29" t="n">
         <v>1000</v>
@@ -7925,7 +7925,7 @@
         <v>7.2</v>
       </c>
       <c r="BX29" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY29" t="n">
         <v>7.4</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -7969,22 +7969,22 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="G30" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="H30" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="I30" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="J30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="K30" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="L30" t="n">
         <v>1.01</v>
@@ -7993,22 +7993,22 @@
         <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>1.25</v>
+        <v>2.24</v>
       </c>
       <c r="O30" t="n">
         <v>1.06</v>
       </c>
       <c r="P30" t="n">
-        <v>1.25</v>
+        <v>2.24</v>
       </c>
       <c r="Q30" t="n">
         <v>1.05</v>
       </c>
       <c r="R30" t="n">
-        <v>1.25</v>
+        <v>2.24</v>
       </c>
       <c r="S30" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="T30" t="n">
         <v>1.11</v>
@@ -8017,10 +8017,10 @@
         <v>1.11</v>
       </c>
       <c r="V30" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W30" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X30" t="n">
         <v>1000</v>
@@ -8134,65 +8134,65 @@
         <v>1000</v>
       </c>
       <c r="BI30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ30" t="n">
         <v>1000</v>
       </c>
       <c r="BK30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL30" t="n">
         <v>1000</v>
       </c>
       <c r="BM30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN30" t="n">
         <v>1000</v>
       </c>
       <c r="BO30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP30" t="n">
         <v>1000</v>
       </c>
       <c r="BQ30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR30" t="n">
         <v>1000</v>
       </c>
       <c r="BS30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT30" t="n">
         <v>1000</v>
       </c>
       <c r="BU30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV30" t="n">
         <v>1000</v>
       </c>
       <c r="BW30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX30" t="n">
         <v>1000</v>
       </c>
       <c r="BY30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ30" t="n">
         <v>1000</v>
       </c>
       <c r="CA30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -8226,19 +8226,19 @@
         <v>1.01</v>
       </c>
       <c r="G31" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="H31" t="n">
         <v>1.01</v>
       </c>
       <c r="I31" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="J31" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="K31" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="L31" t="n">
         <v>1.01</v>
@@ -8250,13 +8250,13 @@
         <v>1.25</v>
       </c>
       <c r="O31" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="P31" t="n">
         <v>1.25</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="R31" t="n">
         <v>1.25</v>
@@ -8271,10 +8271,10 @@
         <v>1.11</v>
       </c>
       <c r="V31" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W31" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X31" t="n">
         <v>1000</v>
@@ -8388,65 +8388,65 @@
         <v>1000</v>
       </c>
       <c r="BI31" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ31" t="n">
         <v>1000</v>
       </c>
       <c r="BK31" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL31" t="n">
         <v>1000</v>
       </c>
       <c r="BM31" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN31" t="n">
         <v>1000</v>
       </c>
       <c r="BO31" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP31" t="n">
         <v>1000</v>
       </c>
       <c r="BQ31" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR31" t="n">
         <v>1000</v>
       </c>
       <c r="BS31" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT31" t="n">
         <v>1000</v>
       </c>
       <c r="BU31" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV31" t="n">
         <v>1000</v>
       </c>
       <c r="BW31" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX31" t="n">
         <v>1000</v>
       </c>
       <c r="BY31" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ31" t="n">
         <v>1000</v>
       </c>
       <c r="CA31" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -8477,19 +8477,19 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G32" t="n">
         <v>1000</v>
       </c>
       <c r="H32" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I32" t="n">
         <v>1000</v>
       </c>
       <c r="J32" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K32" t="n">
         <v>1000</v>
@@ -8501,7 +8501,7 @@
         <v>1.01</v>
       </c>
       <c r="N32" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="O32" t="n">
         <v>1.06</v>
@@ -8519,10 +8519,10 @@
         <v>1.06</v>
       </c>
       <c r="T32" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U32" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V32" t="n">
         <v>1.01</v>
@@ -8642,65 +8642,65 @@
         <v>1000</v>
       </c>
       <c r="BI32" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ32" t="n">
         <v>1000</v>
       </c>
       <c r="BK32" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL32" t="n">
         <v>1000</v>
       </c>
       <c r="BM32" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN32" t="n">
         <v>1000</v>
       </c>
       <c r="BO32" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP32" t="n">
         <v>1000</v>
       </c>
       <c r="BQ32" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR32" t="n">
         <v>1000</v>
       </c>
       <c r="BS32" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT32" t="n">
         <v>1000</v>
       </c>
       <c r="BU32" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV32" t="n">
         <v>1000</v>
       </c>
       <c r="BW32" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX32" t="n">
         <v>1000</v>
       </c>
       <c r="BY32" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ32" t="n">
         <v>1000</v>
       </c>
       <c r="CA32" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -8731,19 +8731,19 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G33" t="n">
         <v>1000</v>
       </c>
       <c r="H33" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I33" t="n">
         <v>1000</v>
       </c>
       <c r="J33" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K33" t="n">
         <v>1000</v>
@@ -8755,7 +8755,7 @@
         <v>1.01</v>
       </c>
       <c r="N33" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O33" t="n">
         <v>1.03</v>
@@ -8770,13 +8770,13 @@
         <v>1.25</v>
       </c>
       <c r="S33" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="T33" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U33" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V33" t="n">
         <v>1.01</v>
@@ -8896,65 +8896,65 @@
         <v>1000</v>
       </c>
       <c r="BI33" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ33" t="n">
         <v>1000</v>
       </c>
       <c r="BK33" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL33" t="n">
         <v>1000</v>
       </c>
       <c r="BM33" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN33" t="n">
         <v>1000</v>
       </c>
       <c r="BO33" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP33" t="n">
         <v>1000</v>
       </c>
       <c r="BQ33" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR33" t="n">
         <v>1000</v>
       </c>
       <c r="BS33" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT33" t="n">
         <v>1000</v>
       </c>
       <c r="BU33" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV33" t="n">
         <v>1000</v>
       </c>
       <c r="BW33" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX33" t="n">
         <v>1000</v>
       </c>
       <c r="BY33" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ33" t="n">
         <v>1000</v>
       </c>
       <c r="CA33" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -8985,22 +8985,22 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="G34" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="H34" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="I34" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="J34" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="K34" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="L34" t="n">
         <v>1.01</v>
@@ -9033,10 +9033,10 @@
         <v>1.11</v>
       </c>
       <c r="V34" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W34" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X34" t="n">
         <v>1000</v>
@@ -9150,65 +9150,65 @@
         <v>1000</v>
       </c>
       <c r="BI34" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ34" t="n">
         <v>1000</v>
       </c>
       <c r="BK34" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL34" t="n">
         <v>1000</v>
       </c>
       <c r="BM34" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN34" t="n">
         <v>1000</v>
       </c>
       <c r="BO34" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP34" t="n">
         <v>1000</v>
       </c>
       <c r="BQ34" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR34" t="n">
         <v>1000</v>
       </c>
       <c r="BS34" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT34" t="n">
         <v>1000</v>
       </c>
       <c r="BU34" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV34" t="n">
         <v>1000</v>
       </c>
       <c r="BW34" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX34" t="n">
         <v>1000</v>
       </c>
       <c r="BY34" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ34" t="n">
         <v>1000</v>
       </c>
       <c r="CA34" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -9239,25 +9239,25 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="G35" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="H35" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="J35" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="K35" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L35" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M35" t="n">
         <v>1.05</v>
@@ -9266,34 +9266,34 @@
         <v>4.2</v>
       </c>
       <c r="O35" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P35" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="R35" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S35" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="T35" t="n">
         <v>2.02</v>
       </c>
       <c r="U35" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="V35" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="W35" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="X35" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y35" t="n">
         <v>32</v>
@@ -9317,7 +9317,7 @@
         <v>160</v>
       </c>
       <c r="AF35" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG35" t="n">
         <v>12</v>
@@ -9329,7 +9329,7 @@
         <v>140</v>
       </c>
       <c r="AJ35" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AK35" t="n">
         <v>18</v>
@@ -9341,128 +9341,128 @@
         <v>170</v>
       </c>
       <c r="AN35" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AO35" t="n">
         <v>220</v>
       </c>
       <c r="AP35" t="n">
-        <v>16</v>
+        <v>4.3</v>
       </c>
       <c r="AQ35" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="AR35" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="AS35" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="AT35" t="n">
-        <v>3.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU35" t="n">
-        <v>9.800000000000001</v>
+        <v>3.8</v>
       </c>
       <c r="AV35" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AW35" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="AX35" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AY35" t="n">
-        <v>9</v>
+        <v>3.7</v>
       </c>
       <c r="AZ35" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="BA35" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="BB35" t="n">
         <v>10.5</v>
       </c>
       <c r="BC35" t="n">
-        <v>13.5</v>
+        <v>4.1</v>
       </c>
       <c r="BD35" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="BE35" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="BF35" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="BG35" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="BH35" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="BI35" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BJ35" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK35" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BL35" t="n">
         <v>1000</v>
       </c>
       <c r="BM35" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BN35" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="BO35" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BP35" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BQ35" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BR35" t="n">
         <v>1000</v>
       </c>
       <c r="BS35" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BT35" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BU35" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BV35" t="n">
         <v>1000</v>
       </c>
       <c r="BW35" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BX35" t="n">
         <v>1000</v>
       </c>
       <c r="BY35" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BZ35" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="CA35" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -9493,46 +9493,46 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.04</v>
+        <v>2.22</v>
       </c>
       <c r="G36" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="H36" t="n">
-        <v>1.04</v>
+        <v>2.66</v>
       </c>
       <c r="I36" t="n">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="J36" t="n">
-        <v>1.02</v>
+        <v>2.48</v>
       </c>
       <c r="K36" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="L36" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M36" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N36" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="O36" t="n">
         <v>1.4</v>
       </c>
       <c r="P36" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R36" t="n">
         <v>1.25</v>
       </c>
-      <c r="Q36" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.18</v>
-      </c>
       <c r="S36" t="n">
-        <v>1.4</v>
+        <v>3.6</v>
       </c>
       <c r="T36" t="n">
         <v>1.11</v>
@@ -9541,10 +9541,10 @@
         <v>1.11</v>
       </c>
       <c r="V36" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="W36" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="X36" t="n">
         <v>1000</v>
@@ -9559,10 +9559,10 @@
         <v>1000</v>
       </c>
       <c r="AB36" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC36" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD36" t="n">
         <v>1000</v>
@@ -9655,68 +9655,68 @@
         <v>1.01</v>
       </c>
       <c r="BH36" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="BI36" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="BJ36" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK36" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL36" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="BM36" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN36" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BO36" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP36" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BQ36" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR36" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS36" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT36" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU36" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV36" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BW36" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX36" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY36" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ36" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="CA36" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -9747,16 +9747,16 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="G37" t="n">
         <v>2.24</v>
       </c>
       <c r="H37" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I37" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="J37" t="n">
         <v>2.9</v>
@@ -9765,7 +9765,7 @@
         <v>3.15</v>
       </c>
       <c r="L37" t="n">
-        <v>1.68</v>
+        <v>1.56</v>
       </c>
       <c r="M37" t="n">
         <v>1.16</v>
@@ -9786,52 +9786,52 @@
         <v>1.15</v>
       </c>
       <c r="S37" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="T37" t="n">
         <v>2.42</v>
       </c>
       <c r="U37" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="V37" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W37" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="X37" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="Y37" t="n">
         <v>13</v>
       </c>
       <c r="Z37" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AA37" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AB37" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AC37" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AD37" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AE37" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AF37" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AG37" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AH37" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AI37" t="n">
         <v>170</v>
@@ -9840,19 +9840,19 @@
         <v>32</v>
       </c>
       <c r="AK37" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AL37" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AM37" t="n">
         <v>370</v>
       </c>
       <c r="AN37" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="AO37" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AP37" t="n">
         <v>6.2</v>
@@ -9861,22 +9861,22 @@
         <v>9.4</v>
       </c>
       <c r="AR37" t="n">
-        <v>8.800000000000001</v>
+        <v>25</v>
       </c>
       <c r="AS37" t="n">
-        <v>11</v>
+        <v>5.3</v>
       </c>
       <c r="AT37" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AU37" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV37" t="n">
         <v>19</v>
       </c>
       <c r="AW37" t="n">
-        <v>10.5</v>
+        <v>5.2</v>
       </c>
       <c r="AX37" t="n">
         <v>10</v>
@@ -9885,34 +9885,34 @@
         <v>11</v>
       </c>
       <c r="AZ37" t="n">
-        <v>8.4</v>
+        <v>4.7</v>
       </c>
       <c r="BA37" t="n">
-        <v>11</v>
+        <v>5.3</v>
       </c>
       <c r="BB37" t="n">
-        <v>8.6</v>
+        <v>5.1</v>
       </c>
       <c r="BC37" t="n">
-        <v>30</v>
+        <v>4.8</v>
       </c>
       <c r="BD37" t="n">
-        <v>10</v>
+        <v>5.2</v>
       </c>
       <c r="BE37" t="n">
-        <v>11.5</v>
+        <v>5.4</v>
       </c>
       <c r="BF37" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="BG37" t="n">
-        <v>11</v>
+        <v>5.3</v>
       </c>
       <c r="BH37" t="n">
         <v>2.46</v>
       </c>
       <c r="BI37" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="BJ37" t="n">
         <v>13</v>
@@ -9924,13 +9924,13 @@
         <v>1000</v>
       </c>
       <c r="BM37" t="n">
-        <v>2.14</v>
+        <v>16</v>
       </c>
       <c r="BN37" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BO37" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BP37" t="n">
         <v>1000</v>
@@ -9945,32 +9945,32 @@
         <v>13</v>
       </c>
       <c r="BT37" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BU37" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BV37" t="n">
         <v>1000</v>
       </c>
       <c r="BW37" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BX37" t="n">
         <v>1000</v>
       </c>
       <c r="BY37" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BZ37" t="n">
         <v>1000</v>
       </c>
       <c r="CA37" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -10019,13 +10019,13 @@
         <v>3.5</v>
       </c>
       <c r="L38" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="M38" t="n">
         <v>1.1</v>
       </c>
       <c r="N38" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O38" t="n">
         <v>1.42</v>
@@ -10034,7 +10034,7 @@
         <v>1.7</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="R38" t="n">
         <v>1.26</v>
@@ -10046,7 +10046,7 @@
         <v>1.95</v>
       </c>
       <c r="U38" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V38" t="n">
         <v>1.27</v>
@@ -10118,13 +10118,13 @@
         <v>9</v>
       </c>
       <c r="AS38" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AT38" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU38" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV38" t="n">
         <v>15.5</v>
@@ -10133,13 +10133,13 @@
         <v>10.5</v>
       </c>
       <c r="AX38" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AY38" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ38" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BA38" t="n">
         <v>10.5</v>
@@ -10148,7 +10148,7 @@
         <v>21</v>
       </c>
       <c r="BC38" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BD38" t="n">
         <v>32</v>
@@ -10157,7 +10157,7 @@
         <v>11.5</v>
       </c>
       <c r="BF38" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="BG38" t="n">
         <v>11</v>
@@ -10166,7 +10166,7 @@
         <v>3.05</v>
       </c>
       <c r="BI38" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="BJ38" t="n">
         <v>10.5</v>
@@ -10190,13 +10190,13 @@
         <v>15.5</v>
       </c>
       <c r="BQ38" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR38" t="n">
         <v>34</v>
       </c>
       <c r="BS38" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BT38" t="n">
         <v>7.6</v>
@@ -10211,7 +10211,7 @@
         <v>12</v>
       </c>
       <c r="BX38" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY38" t="n">
         <v>13</v>
@@ -10220,11 +10220,11 @@
         <v>34</v>
       </c>
       <c r="CA38" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -10255,10 +10255,10 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="G39" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="H39" t="n">
         <v>3.1</v>
@@ -10285,7 +10285,7 @@
         <v>1.46</v>
       </c>
       <c r="P39" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="Q39" t="n">
         <v>2.28</v>
@@ -10300,7 +10300,7 @@
         <v>1.94</v>
       </c>
       <c r="U39" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="V39" t="n">
         <v>1.43</v>
@@ -10315,37 +10315,37 @@
         <v>12.5</v>
       </c>
       <c r="Z39" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AA39" t="n">
         <v>75</v>
       </c>
       <c r="AB39" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AC39" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD39" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AE39" t="n">
         <v>55</v>
       </c>
       <c r="AF39" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AG39" t="n">
         <v>15</v>
       </c>
       <c r="AH39" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI39" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AJ39" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AK39" t="n">
         <v>42</v>
@@ -10360,61 +10360,61 @@
         <v>44</v>
       </c>
       <c r="AO39" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AP39" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AQ39" t="n">
-        <v>3.7</v>
+        <v>7.4</v>
       </c>
       <c r="AR39" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AS39" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="AT39" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU39" t="n">
-        <v>3.3</v>
+        <v>6.2</v>
       </c>
       <c r="AV39" t="n">
-        <v>3.9</v>
+        <v>10</v>
       </c>
       <c r="AW39" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="AX39" t="n">
-        <v>4.1</v>
+        <v>11.5</v>
       </c>
       <c r="AY39" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AZ39" t="n">
         <v>17.5</v>
       </c>
       <c r="BA39" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="BB39" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="BC39" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="BD39" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="BE39" t="n">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="BF39" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="BG39" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="BH39" t="n">
         <v>3</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -10509,16 +10509,16 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="G40" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="H40" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I40" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J40" t="n">
         <v>4</v>
@@ -10548,58 +10548,58 @@
         <v>1.35</v>
       </c>
       <c r="S40" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="T40" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="U40" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="V40" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W40" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="X40" t="n">
         <v>17</v>
       </c>
       <c r="Y40" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Z40" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA40" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AB40" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC40" t="n">
         <v>11</v>
       </c>
       <c r="AD40" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AE40" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AF40" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG40" t="n">
         <v>11.5</v>
       </c>
       <c r="AH40" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI40" t="n">
         <v>110</v>
       </c>
       <c r="AJ40" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AK40" t="n">
         <v>21</v>
@@ -10614,19 +10614,19 @@
         <v>12</v>
       </c>
       <c r="AO40" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AP40" t="n">
         <v>11</v>
       </c>
       <c r="AQ40" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AR40" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS40" t="n">
         <v>5</v>
-      </c>
-      <c r="AS40" t="n">
-        <v>5.3</v>
       </c>
       <c r="AT40" t="n">
         <v>6.2</v>
@@ -10635,10 +10635,10 @@
         <v>7.2</v>
       </c>
       <c r="AV40" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AW40" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="AX40" t="n">
         <v>7.4</v>
@@ -10650,28 +10650,28 @@
         <v>17</v>
       </c>
       <c r="BA40" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BB40" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BC40" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BD40" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BE40" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BF40" t="n">
         <v>8</v>
       </c>
       <c r="BG40" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BH40" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BI40" t="n">
         <v>2.84</v>
@@ -10686,13 +10686,13 @@
         <v>1000</v>
       </c>
       <c r="BM40" t="n">
-        <v>3.15</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN40" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BO40" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="BP40" t="n">
         <v>11</v>
@@ -10704,35 +10704,35 @@
         <v>1000</v>
       </c>
       <c r="BS40" t="n">
-        <v>2.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT40" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BU40" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BV40" t="n">
         <v>1000</v>
       </c>
       <c r="BW40" t="n">
-        <v>3.05</v>
+        <v>12</v>
       </c>
       <c r="BX40" t="n">
         <v>1000</v>
       </c>
       <c r="BY40" t="n">
-        <v>3.05</v>
+        <v>12</v>
       </c>
       <c r="BZ40" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="CA40" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -10781,7 +10781,7 @@
         <v>5.2</v>
       </c>
       <c r="L41" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="M41" t="n">
         <v>1.04</v>
@@ -10790,19 +10790,19 @@
         <v>5.1</v>
       </c>
       <c r="O41" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P41" t="n">
         <v>2.44</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="R41" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="S41" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="T41" t="n">
         <v>1.83</v>
@@ -10901,10 +10901,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ41" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA41" t="n">
-        <v>60</v>
+        <v>13.5</v>
       </c>
       <c r="BB41" t="n">
         <v>12.5</v>
@@ -10916,16 +10916,16 @@
         <v>24</v>
       </c>
       <c r="BE41" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BF41" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BG41" t="n">
         <v>13</v>
       </c>
       <c r="BH41" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BI41" t="n">
         <v>3.35</v>
@@ -10934,59 +10934,59 @@
         <v>10.5</v>
       </c>
       <c r="BK41" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BL41" t="n">
         <v>1000</v>
       </c>
       <c r="BM41" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BN41" t="n">
         <v>4.2</v>
       </c>
       <c r="BO41" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="BP41" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BQ41" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BR41" t="n">
         <v>22</v>
       </c>
       <c r="BS41" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BT41" t="n">
         <v>11</v>
       </c>
       <c r="BU41" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BV41" t="n">
         <v>1000</v>
       </c>
       <c r="BW41" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BX41" t="n">
         <v>1000</v>
       </c>
       <c r="BY41" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BZ41" t="n">
         <v>13</v>
       </c>
       <c r="CA41" t="n">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -11017,7 +11017,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="G42" t="n">
         <v>2.12</v>
@@ -11026,49 +11026,49 @@
         <v>4</v>
       </c>
       <c r="I42" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J42" t="n">
         <v>3.5</v>
       </c>
       <c r="K42" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L42" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="M42" t="n">
         <v>1.09</v>
       </c>
       <c r="N42" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O42" t="n">
         <v>1.39</v>
       </c>
       <c r="P42" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="R42" t="n">
         <v>1.3</v>
       </c>
       <c r="S42" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="T42" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="U42" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="V42" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W42" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="X42" t="n">
         <v>12.5</v>
@@ -11077,34 +11077,34 @@
         <v>14</v>
       </c>
       <c r="Z42" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA42" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AB42" t="n">
-        <v>970</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC42" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD42" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AE42" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF42" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AG42" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AH42" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI42" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ42" t="n">
         <v>25</v>
@@ -11116,67 +11116,67 @@
         <v>44</v>
       </c>
       <c r="AM42" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AN42" t="n">
         <v>18.5</v>
       </c>
       <c r="AO42" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AP42" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ42" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR42" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AS42" t="n">
-        <v>4.6</v>
+        <v>75</v>
       </c>
       <c r="AT42" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AU42" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV42" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AW42" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AX42" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY42" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ42" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA42" t="n">
-        <v>9.4</v>
+        <v>55</v>
       </c>
       <c r="BB42" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BC42" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD42" t="n">
-        <v>8.800000000000001</v>
+        <v>36</v>
       </c>
       <c r="BE42" t="n">
-        <v>4.6</v>
+        <v>10.5</v>
       </c>
       <c r="BF42" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BG42" t="n">
-        <v>9.800000000000001</v>
+        <v>50</v>
       </c>
       <c r="BH42" t="n">
         <v>3.25</v>
@@ -11188,59 +11188,59 @@
         <v>11</v>
       </c>
       <c r="BK42" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BL42" t="n">
         <v>1000</v>
       </c>
       <c r="BM42" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BN42" t="n">
         <v>4.8</v>
       </c>
       <c r="BO42" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BP42" t="n">
         <v>16</v>
       </c>
       <c r="BQ42" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR42" t="n">
         <v>34</v>
       </c>
       <c r="BS42" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT42" t="n">
         <v>7.8</v>
-      </c>
-      <c r="BT42" t="n">
-        <v>8</v>
       </c>
       <c r="BU42" t="n">
         <v>4.5</v>
       </c>
       <c r="BV42" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BW42" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BX42" t="n">
         <v>55</v>
       </c>
       <c r="BY42" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BZ42" t="n">
         <v>32</v>
       </c>
       <c r="CA42" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -11277,16 +11277,16 @@
         <v>2.06</v>
       </c>
       <c r="H43" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I43" t="n">
         <v>4.6</v>
       </c>
       <c r="J43" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K43" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L43" t="n">
         <v>1.44</v>
@@ -11301,7 +11301,7 @@
         <v>1.37</v>
       </c>
       <c r="P43" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="Q43" t="n">
         <v>2.08</v>
@@ -11313,7 +11313,7 @@
         <v>3.85</v>
       </c>
       <c r="T43" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U43" t="n">
         <v>2</v>
@@ -11433,7 +11433,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BH43" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BI43" t="n">
         <v>2.64</v>
@@ -11442,13 +11442,13 @@
         <v>11</v>
       </c>
       <c r="BK43" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="BL43" t="n">
         <v>1000</v>
       </c>
       <c r="BM43" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BN43" t="n">
         <v>4.8</v>
@@ -11460,41 +11460,41 @@
         <v>15.5</v>
       </c>
       <c r="BQ43" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BR43" t="n">
         <v>34</v>
       </c>
       <c r="BS43" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BT43" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BU43" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="BV43" t="n">
         <v>1000</v>
       </c>
       <c r="BW43" t="n">
+        <v>8</v>
+      </c>
+      <c r="BX43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY43" t="n">
         <v>8.6</v>
-      </c>
-      <c r="BX43" t="n">
-        <v>55</v>
-      </c>
-      <c r="BY43" t="n">
-        <v>9.199999999999999</v>
       </c>
       <c r="BZ43" t="n">
         <v>32</v>
       </c>
       <c r="CA43" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -11525,22 +11525,22 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.04</v>
+        <v>1.84</v>
       </c>
       <c r="G44" t="n">
-        <v>1000</v>
+        <v>2.18</v>
       </c>
       <c r="H44" t="n">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="I44" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="J44" t="n">
-        <v>1.11</v>
+        <v>3.55</v>
       </c>
       <c r="K44" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="L44" t="n">
         <v>1.01</v>
@@ -11558,10 +11558,10 @@
         <v>1.25</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="R44" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="S44" t="n">
         <v>2.58</v>
@@ -11573,10 +11573,10 @@
         <v>1.11</v>
       </c>
       <c r="V44" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="W44" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="X44" t="n">
         <v>1000</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -11779,19 +11779,19 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G45" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="H45" t="n">
         <v>2.66</v>
       </c>
       <c r="I45" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="J45" t="n">
         <v>3.25</v>
-      </c>
-      <c r="J45" t="n">
-        <v>3.15</v>
       </c>
       <c r="K45" t="n">
         <v>4</v>
@@ -11803,7 +11803,7 @@
         <v>1.05</v>
       </c>
       <c r="N45" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O45" t="n">
         <v>1.26</v>
@@ -11818,7 +11818,7 @@
         <v>1.44</v>
       </c>
       <c r="S45" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="T45" t="n">
         <v>1.64</v>
@@ -11827,52 +11827,52 @@
         <v>2.3</v>
       </c>
       <c r="V45" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="W45" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="X45" t="n">
         <v>21</v>
       </c>
       <c r="Y45" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="Z45" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AA45" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AB45" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AC45" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD45" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AE45" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AF45" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AG45" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH45" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AI45" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ45" t="n">
         <v>44</v>
       </c>
       <c r="AK45" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AL45" t="n">
         <v>42</v>
@@ -11881,64 +11881,64 @@
         <v>85</v>
       </c>
       <c r="AN45" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AO45" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AR45" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AS45" t="n">
-        <v>1.03</v>
+        <v>30</v>
       </c>
       <c r="AT45" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AU45" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AV45" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AW45" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AX45" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="AY45" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AZ45" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="BA45" t="n">
-        <v>1.03</v>
+        <v>28</v>
       </c>
       <c r="BB45" t="n">
         <v>1.03</v>
       </c>
       <c r="BC45" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BD45" t="n">
-        <v>1.03</v>
+        <v>28</v>
       </c>
       <c r="BE45" t="n">
         <v>1.03</v>
       </c>
       <c r="BF45" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BG45" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BH45" t="n">
         <v>3.85</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -12039,7 +12039,7 @@
         <v>1.19</v>
       </c>
       <c r="H46" t="n">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="I46" t="n">
         <v>1000</v>
@@ -12063,13 +12063,13 @@
         <v>1.09</v>
       </c>
       <c r="P46" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="Q46" t="n">
         <v>1.09</v>
       </c>
       <c r="R46" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="S46" t="n">
         <v>1.13</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -12287,22 +12287,22 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="G47" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="H47" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="I47" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="J47" t="n">
         <v>3.1</v>
       </c>
       <c r="K47" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L47" t="n">
         <v>1.54</v>
@@ -12314,19 +12314,19 @@
         <v>2.8</v>
       </c>
       <c r="O47" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="P47" t="n">
         <v>1.61</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="R47" t="n">
         <v>1.22</v>
       </c>
       <c r="S47" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="T47" t="n">
         <v>2.02</v>
@@ -12335,37 +12335,37 @@
         <v>1.87</v>
       </c>
       <c r="V47" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="W47" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="X47" t="n">
         <v>12</v>
       </c>
       <c r="Y47" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z47" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AA47" t="n">
         <v>100</v>
       </c>
       <c r="AB47" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC47" t="n">
         <v>7.4</v>
       </c>
       <c r="AD47" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AE47" t="n">
         <v>55</v>
       </c>
       <c r="AF47" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG47" t="n">
         <v>12</v>
@@ -12377,19 +12377,19 @@
         <v>90</v>
       </c>
       <c r="AJ47" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="AK47" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="AL47" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM47" t="n">
         <v>190</v>
       </c>
       <c r="AN47" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AO47" t="n">
         <v>90</v>
@@ -12398,13 +12398,13 @@
         <v>8.6</v>
       </c>
       <c r="AQ47" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AR47" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS47" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AT47" t="n">
         <v>7.2</v>
@@ -12419,7 +12419,7 @@
         <v>32</v>
       </c>
       <c r="AX47" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="AY47" t="n">
         <v>10.5</v>
@@ -12428,25 +12428,25 @@
         <v>18.5</v>
       </c>
       <c r="BA47" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB47" t="n">
-        <v>32</v>
+        <v>7.8</v>
       </c>
       <c r="BC47" t="n">
         <v>24</v>
       </c>
       <c r="BD47" t="n">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="BE47" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BF47" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BG47" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH47" t="n">
         <v>2.84</v>
@@ -12464,34 +12464,34 @@
         <v>1000</v>
       </c>
       <c r="BM47" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BN47" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BO47" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="BP47" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BQ47" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BR47" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BS47" t="n">
         <v>12</v>
       </c>
       <c r="BT47" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BU47" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="BV47" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BW47" t="n">
         <v>11</v>
@@ -12500,7 +12500,7 @@
         <v>55</v>
       </c>
       <c r="BY47" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BZ47" t="n">
         <v>1000</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -12550,13 +12550,13 @@
         <v>2.86</v>
       </c>
       <c r="I48" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J48" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="K48" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="L48" t="n">
         <v>1.57</v>
@@ -12568,49 +12568,49 @@
         <v>2.32</v>
       </c>
       <c r="O48" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="P48" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="R48" t="n">
         <v>1.18</v>
       </c>
       <c r="S48" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="T48" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="U48" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="V48" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W48" t="n">
         <v>1.44</v>
       </c>
       <c r="X48" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y48" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="Z48" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AA48" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AB48" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AC48" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD48" t="n">
         <v>15.5</v>
@@ -12619,16 +12619,16 @@
         <v>55</v>
       </c>
       <c r="AF48" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AG48" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AH48" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AI48" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AJ48" t="n">
         <v>65</v>
@@ -12640,67 +12640,67 @@
         <v>110</v>
       </c>
       <c r="AM48" t="n">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="AN48" t="n">
+        <v>80</v>
+      </c>
+      <c r="AO48" t="n">
         <v>75</v>
-      </c>
-      <c r="AO48" t="n">
-        <v>70</v>
       </c>
       <c r="AP48" t="n">
         <v>6.4</v>
       </c>
       <c r="AQ48" t="n">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="AR48" t="n">
-        <v>6.4</v>
+        <v>13</v>
       </c>
       <c r="AS48" t="n">
-        <v>8.4</v>
+        <v>5.6</v>
       </c>
       <c r="AT48" t="n">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="AU48" t="n">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="AV48" t="n">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="AW48" t="n">
-        <v>8.4</v>
+        <v>36</v>
       </c>
       <c r="AX48" t="n">
-        <v>6.6</v>
+        <v>13.5</v>
       </c>
       <c r="AY48" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AZ48" t="n">
-        <v>7.2</v>
+        <v>18.5</v>
       </c>
       <c r="BA48" t="n">
-        <v>9</v>
+        <v>5.8</v>
       </c>
       <c r="BB48" t="n">
-        <v>8.6</v>
+        <v>5.5</v>
       </c>
       <c r="BC48" t="n">
-        <v>8.4</v>
+        <v>5.5</v>
       </c>
       <c r="BD48" t="n">
-        <v>9</v>
+        <v>5.8</v>
       </c>
       <c r="BE48" t="n">
-        <v>9.6</v>
+        <v>5.9</v>
       </c>
       <c r="BF48" t="n">
-        <v>8.800000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="BG48" t="n">
-        <v>8.6</v>
+        <v>5.6</v>
       </c>
       <c r="BH48" t="n">
         <v>1000</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -12795,19 +12795,19 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="G49" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="H49" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="I49" t="n">
         <v>8</v>
       </c>
       <c r="J49" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K49" t="n">
         <v>5.1</v>
@@ -12819,7 +12819,7 @@
         <v>1.05</v>
       </c>
       <c r="N49" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O49" t="n">
         <v>1.25</v>
@@ -12828,25 +12828,25 @@
         <v>2.24</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R49" t="n">
         <v>1.48</v>
       </c>
       <c r="S49" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="T49" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="U49" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V49" t="n">
         <v>1.14</v>
       </c>
       <c r="W49" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="X49" t="n">
         <v>21</v>
@@ -12855,7 +12855,7 @@
         <v>28</v>
       </c>
       <c r="Z49" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AA49" t="n">
         <v>1000</v>
@@ -12867,13 +12867,13 @@
         <v>11</v>
       </c>
       <c r="AD49" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="AE49" t="n">
         <v>1000</v>
       </c>
       <c r="AF49" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AG49" t="n">
         <v>10</v>
@@ -12894,10 +12894,10 @@
         <v>34</v>
       </c>
       <c r="AM49" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN49" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AO49" t="n">
         <v>130</v>
@@ -12909,13 +12909,13 @@
         <v>23</v>
       </c>
       <c r="AR49" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="AS49" t="n">
         <v>48</v>
       </c>
       <c r="AT49" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU49" t="n">
         <v>10</v>
@@ -12927,16 +12927,16 @@
         <v>38</v>
       </c>
       <c r="AX49" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY49" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ49" t="n">
         <v>21</v>
       </c>
       <c r="BA49" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BB49" t="n">
         <v>12</v>
@@ -12945,7 +12945,7 @@
         <v>13.5</v>
       </c>
       <c r="BD49" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BE49" t="n">
         <v>42</v>
@@ -12984,7 +12984,7 @@
         <v>9.6</v>
       </c>
       <c r="BQ49" t="n">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="BR49" t="n">
         <v>25</v>
@@ -12996,7 +12996,7 @@
         <v>11.5</v>
       </c>
       <c r="BU49" t="n">
-        <v>5.3</v>
+        <v>8.6</v>
       </c>
       <c r="BV49" t="n">
         <v>1000</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -13058,7 +13058,7 @@
         <v>1.89</v>
       </c>
       <c r="I50" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="J50" t="n">
         <v>3.8</v>
@@ -13079,7 +13079,7 @@
         <v>1.26</v>
       </c>
       <c r="P50" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="Q50" t="n">
         <v>1.76</v>
@@ -13088,7 +13088,7 @@
         <v>1.45</v>
       </c>
       <c r="S50" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="T50" t="n">
         <v>1.71</v>
@@ -13103,46 +13103,46 @@
         <v>1.28</v>
       </c>
       <c r="X50" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>27</v>
+      </c>
+      <c r="AB50" t="n">
         <v>22</v>
       </c>
-      <c r="Y50" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>22</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>17.5</v>
-      </c>
       <c r="AC50" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AD50" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE50" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="AF50" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AG50" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AH50" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AI50" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AJ50" t="n">
         <v>110</v>
       </c>
       <c r="AK50" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AL50" t="n">
         <v>55</v>
@@ -13151,25 +13151,25 @@
         <v>100</v>
       </c>
       <c r="AN50" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AO50" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AP50" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ50" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AR50" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AS50" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AT50" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AU50" t="n">
         <v>8</v>
@@ -13178,55 +13178,55 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW50" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AX50" t="n">
-        <v>9</v>
+        <v>3.9</v>
       </c>
       <c r="AY50" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AZ50" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="BA50" t="n">
-        <v>8.800000000000001</v>
+        <v>3.85</v>
       </c>
       <c r="BB50" t="n">
-        <v>11</v>
+        <v>4.1</v>
       </c>
       <c r="BC50" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD50" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE50" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF50" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG50" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="BD50" t="n">
-        <v>10</v>
-      </c>
-      <c r="BE50" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BF50" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BG50" t="n">
-        <v>10</v>
-      </c>
       <c r="BH50" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BI50" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="BJ50" t="n">
         <v>9.4</v>
       </c>
       <c r="BK50" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL50" t="n">
         <v>1000</v>
       </c>
       <c r="BM50" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BN50" t="n">
         <v>7.8</v>
@@ -13238,13 +13238,13 @@
         <v>1000</v>
       </c>
       <c r="BQ50" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BR50" t="n">
         <v>1000</v>
       </c>
       <c r="BS50" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BT50" t="n">
         <v>4.8</v>
@@ -13256,23 +13256,23 @@
         <v>13</v>
       </c>
       <c r="BW50" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BX50" t="n">
         <v>25</v>
       </c>
       <c r="BY50" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BZ50" t="n">
         <v>19.5</v>
       </c>
       <c r="CA50" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -13306,10 +13306,10 @@
         <v>1.95</v>
       </c>
       <c r="G51" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H51" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="I51" t="n">
         <v>4.4</v>
@@ -13354,7 +13354,7 @@
         <v>1.3</v>
       </c>
       <c r="W51" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="X51" t="n">
         <v>17</v>
@@ -13462,7 +13462,7 @@
         <v>10.5</v>
       </c>
       <c r="BG51" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BH51" t="n">
         <v>3.85</v>
@@ -13480,13 +13480,13 @@
         <v>1000</v>
       </c>
       <c r="BM51" t="n">
-        <v>2.78</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN51" t="n">
         <v>4.9</v>
       </c>
       <c r="BO51" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="BP51" t="n">
         <v>13.5</v>
@@ -13516,7 +13516,7 @@
         <v>42</v>
       </c>
       <c r="BY51" t="n">
-        <v>2.66</v>
+        <v>8.6</v>
       </c>
       <c r="BZ51" t="n">
         <v>22</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -13557,22 +13557,22 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="G52" t="n">
         <v>2.2</v>
       </c>
       <c r="H52" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="I52" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J52" t="n">
         <v>3.55</v>
       </c>
       <c r="K52" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L52" t="n">
         <v>1.31</v>
@@ -13584,25 +13584,25 @@
         <v>3.85</v>
       </c>
       <c r="O52" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P52" t="n">
         <v>2</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="R52" t="n">
         <v>1.38</v>
       </c>
       <c r="S52" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="T52" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="U52" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V52" t="n">
         <v>1.32</v>
@@ -13614,13 +13614,13 @@
         <v>19</v>
       </c>
       <c r="Y52" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Z52" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AA52" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AB52" t="n">
         <v>12.5</v>
@@ -13629,13 +13629,13 @@
         <v>10</v>
       </c>
       <c r="AD52" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AE52" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF52" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AG52" t="n">
         <v>13.5</v>
@@ -13644,10 +13644,10 @@
         <v>21</v>
       </c>
       <c r="AI52" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AJ52" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AK52" t="n">
         <v>27</v>
@@ -13659,37 +13659,37 @@
         <v>110</v>
       </c>
       <c r="AN52" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AO52" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AP52" t="n">
         <v>13.5</v>
       </c>
       <c r="AQ52" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AR52" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS52" t="n">
         <v>4.1</v>
       </c>
-      <c r="AS52" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AT52" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AU52" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV52" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW52" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="AX52" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AY52" t="n">
         <v>9.4</v>
@@ -13698,37 +13698,37 @@
         <v>14.5</v>
       </c>
       <c r="BA52" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BB52" t="n">
+        <v>19</v>
+      </c>
+      <c r="BC52" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD52" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BE52" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF52" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG52" t="n">
         <v>4</v>
-      </c>
-      <c r="BC52" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BD52" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE52" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BF52" t="n">
-        <v>11</v>
-      </c>
-      <c r="BG52" t="n">
-        <v>4.3</v>
       </c>
       <c r="BH52" t="n">
         <v>3.7</v>
       </c>
       <c r="BI52" t="n">
-        <v>2.86</v>
+        <v>3.15</v>
       </c>
       <c r="BJ52" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BK52" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BL52" t="n">
         <v>1000</v>
@@ -13749,7 +13749,7 @@
         <v>6.2</v>
       </c>
       <c r="BR52" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BS52" t="n">
         <v>7.6</v>
@@ -13758,7 +13758,7 @@
         <v>7.4</v>
       </c>
       <c r="BU52" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BV52" t="n">
         <v>32</v>
@@ -13770,7 +13770,7 @@
         <v>40</v>
       </c>
       <c r="BY52" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ52" t="n">
         <v>24</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>
@@ -13829,7 +13829,7 @@
         <v>4</v>
       </c>
       <c r="L53" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M53" t="n">
         <v>1.04</v>
@@ -13847,40 +13847,40 @@
         <v>1.6</v>
       </c>
       <c r="R53" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="S53" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="T53" t="n">
         <v>1.54</v>
       </c>
       <c r="U53" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="V53" t="n">
         <v>1.7</v>
       </c>
       <c r="W53" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="X53" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="Y53" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="Z53" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA53" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AB53" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AC53" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD53" t="n">
         <v>13.5</v>
@@ -13889,37 +13889,37 @@
         <v>21</v>
       </c>
       <c r="AF53" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AG53" t="n">
         <v>16</v>
       </c>
       <c r="AH53" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AI53" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AJ53" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AK53" t="n">
         <v>34</v>
       </c>
       <c r="AL53" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AM53" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AN53" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AO53" t="n">
         <v>14</v>
       </c>
       <c r="AP53" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ53" t="n">
         <v>13.5</v>
@@ -13928,43 +13928,43 @@
         <v>17</v>
       </c>
       <c r="AS53" t="n">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="AT53" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AU53" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AV53" t="n">
         <v>10.5</v>
       </c>
       <c r="AW53" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AX53" t="n">
-        <v>18.5</v>
+        <v>5.2</v>
       </c>
       <c r="AY53" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ53" t="n">
         <v>12.5</v>
       </c>
       <c r="BA53" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="BB53" t="n">
-        <v>34</v>
+        <v>5.7</v>
       </c>
       <c r="BC53" t="n">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="BD53" t="n">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="BE53" t="n">
-        <v>40</v>
+        <v>5.6</v>
       </c>
       <c r="BF53" t="n">
         <v>16.5</v>
@@ -13973,68 +13973,68 @@
         <v>10.5</v>
       </c>
       <c r="BH53" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BI53" t="n">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BJ53" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK53" t="n">
         <v>1.04</v>
       </c>
       <c r="BL53" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="BM53" t="n">
         <v>1.04</v>
       </c>
       <c r="BN53" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="BO53" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BP53" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="BQ53" t="n">
         <v>1.04</v>
       </c>
       <c r="BR53" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="BS53" t="n">
         <v>1.04</v>
       </c>
       <c r="BT53" t="n">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="BU53" t="n">
-        <v>3.95</v>
+        <v>5.1</v>
       </c>
       <c r="BV53" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BW53" t="n">
         <v>1.04</v>
       </c>
       <c r="BX53" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="BY53" t="n">
         <v>1.04</v>
       </c>
       <c r="BZ53" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="CA53" t="n">
         <v>1.04</v>
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-07-16 09:31:03</t>
+          <t>2026-07-16 11:49:17</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-17.xlsx
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="H2" t="n">
         <v>2.08</v>
       </c>
       <c r="I2" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K2" t="n">
         <v>3.8</v>
@@ -881,40 +881,40 @@
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O2" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P2" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="R2" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S2" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="T2" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="U2" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V2" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="W2" t="n">
         <v>1.33</v>
       </c>
       <c r="X2" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z2" t="n">
         <v>15.5</v>
@@ -923,10 +923,10 @@
         <v>30</v>
       </c>
       <c r="AB2" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AD2" t="n">
         <v>12.5</v>
@@ -938,7 +938,7 @@
         <v>32</v>
       </c>
       <c r="AG2" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AH2" t="n">
         <v>21</v>
@@ -959,25 +959,25 @@
         <v>110</v>
       </c>
       <c r="AN2" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AO2" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AP2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ2" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR2" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.9</v>
+        <v>19</v>
       </c>
       <c r="AT2" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AU2" t="n">
         <v>7.2</v>
@@ -986,37 +986,37 @@
         <v>9.6</v>
       </c>
       <c r="AW2" t="n">
-        <v>17</v>
+        <v>4.8</v>
       </c>
       <c r="AX2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AY2" t="n">
         <v>14</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA2" t="n">
         <v>30</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BD2" t="n">
-        <v>40</v>
+        <v>5.3</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BG2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BH2" t="n">
         <v>3.55</v>
@@ -1025,34 +1025,34 @@
         <v>2.92</v>
       </c>
       <c r="BJ2" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>13.5</v>
+        <v>5.5</v>
       </c>
       <c r="BN2" t="n">
         <v>7.2</v>
       </c>
       <c r="BO2" t="n">
-        <v>5.6</v>
+        <v>3.2</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>10.5</v>
+        <v>4.8</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="BT2" t="n">
         <v>5</v>
@@ -1061,26 +1061,26 @@
         <v>3.95</v>
       </c>
       <c r="BV2" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>7.6</v>
+        <v>4.1</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>10</v>
+        <v>4.8</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="CA2" t="n">
-        <v>9.4</v>
+        <v>4.8</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="G3" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="H3" t="n">
         <v>3.85</v>
@@ -1141,13 +1141,13 @@
         <v>1.29</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="Q3" t="n">
         <v>1.87</v>
       </c>
       <c r="R3" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S3" t="n">
         <v>3.2</v>
@@ -1156,13 +1156,13 @@
         <v>1.73</v>
       </c>
       <c r="U3" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V3" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W3" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="X3" t="n">
         <v>18.5</v>
@@ -1201,7 +1201,7 @@
         <v>55</v>
       </c>
       <c r="AJ3" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AK3" t="n">
         <v>27</v>
@@ -1213,7 +1213,7 @@
         <v>110</v>
       </c>
       <c r="AN3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO3" t="n">
         <v>55</v>
@@ -1228,7 +1228,7 @@
         <v>20</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AT3" t="n">
         <v>8.800000000000001</v>
@@ -1240,7 +1240,7 @@
         <v>11.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AX3" t="n">
         <v>10</v>
@@ -1252,7 +1252,7 @@
         <v>12</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BB3" t="n">
         <v>19</v>
@@ -1261,16 +1261,16 @@
         <v>16</v>
       </c>
       <c r="BD3" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BF3" t="n">
         <v>11</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BH3" t="n">
         <v>3.55</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
         <v>1.91</v>
       </c>
       <c r="I4" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="J4" t="n">
         <v>3.65</v>
@@ -1410,10 +1410,10 @@
         <v>1.77</v>
       </c>
       <c r="U4" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V4" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="W4" t="n">
         <v>1.28</v>
@@ -1449,7 +1449,7 @@
         <v>20</v>
       </c>
       <c r="AH4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI4" t="n">
         <v>40</v>
@@ -1461,7 +1461,7 @@
         <v>55</v>
       </c>
       <c r="AL4" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM4" t="n">
         <v>110</v>
@@ -1497,7 +1497,7 @@
         <v>15</v>
       </c>
       <c r="AX4" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AY4" t="n">
         <v>13</v>
@@ -1506,19 +1506,19 @@
         <v>13.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BC4" t="n">
         <v>4.8</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BF4" t="n">
         <v>4.9</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
         <v>4.8</v>
       </c>
       <c r="H5" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="I5" t="n">
         <v>1.85</v>
@@ -1649,16 +1649,16 @@
         <v>1.21</v>
       </c>
       <c r="P5" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R5" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="S5" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="T5" t="n">
         <v>1.64</v>
@@ -1670,7 +1670,7 @@
         <v>2.16</v>
       </c>
       <c r="W5" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="X5" t="n">
         <v>24</v>
@@ -1685,7 +1685,7 @@
         <v>20</v>
       </c>
       <c r="AB5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AC5" t="n">
         <v>10</v>
@@ -1697,13 +1697,13 @@
         <v>18</v>
       </c>
       <c r="AF5" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AG5" t="n">
         <v>18.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AI5" t="n">
         <v>29</v>
@@ -1712,52 +1712,52 @@
         <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AL5" t="n">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="AM5" t="n">
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AO5" t="n">
         <v>8.6</v>
       </c>
       <c r="AP5" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AQ5" t="n">
         <v>11</v>
       </c>
       <c r="AR5" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AS5" t="n">
         <v>17</v>
       </c>
       <c r="AT5" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AU5" t="n">
         <v>9</v>
       </c>
       <c r="AV5" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AW5" t="n">
         <v>14.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY5" t="n">
         <v>15.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA5" t="n">
         <v>19</v>
@@ -1775,28 +1775,28 @@
         <v>32</v>
       </c>
       <c r="BF5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BG5" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BH5" t="n">
         <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.04</v>
+        <v>2.02</v>
       </c>
       <c r="BJ5" t="n">
         <v>12.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.04</v>
+        <v>1.75</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.04</v>
+        <v>2.04</v>
       </c>
       <c r="BN5" t="n">
         <v>11</v>
@@ -1808,13 +1808,13 @@
         <v>48</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.04</v>
+        <v>1.95</v>
       </c>
       <c r="BR5" t="n">
         <v>50</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.04</v>
+        <v>1.96</v>
       </c>
       <c r="BT5" t="n">
         <v>6.4</v>
@@ -1826,23 +1826,23 @@
         <v>16</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.04</v>
+        <v>1.81</v>
       </c>
       <c r="BX5" t="n">
         <v>30</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.04</v>
+        <v>1.91</v>
       </c>
       <c r="BZ5" t="n">
         <v>22</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.04</v>
+        <v>1.86</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -1999,7 +1999,7 @@
         <v>5.8</v>
       </c>
       <c r="AV6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AW6" t="n">
         <v>18.5</v>
@@ -2038,7 +2038,7 @@
         <v>3.05</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="BJ6" t="n">
         <v>11.5</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -2381,19 +2381,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="G8" t="n">
         <v>1.39</v>
       </c>
       <c r="H8" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I8" t="n">
         <v>10.5</v>
       </c>
       <c r="J8" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="K8" t="n">
         <v>6.2</v>
@@ -2405,52 +2405,52 @@
         <v>1.03</v>
       </c>
       <c r="N8" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="O8" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P8" t="n">
         <v>2.62</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="R8" t="n">
         <v>1.66</v>
       </c>
       <c r="S8" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="T8" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="U8" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V8" t="n">
         <v>1.1</v>
       </c>
       <c r="W8" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="X8" t="n">
         <v>27</v>
       </c>
       <c r="Y8" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="Z8" t="n">
         <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>360</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
         <v>11</v>
       </c>
       <c r="AC8" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AD8" t="n">
         <v>36</v>
@@ -2465,13 +2465,13 @@
         <v>11</v>
       </c>
       <c r="AH8" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AI8" t="n">
         <v>120</v>
       </c>
       <c r="AJ8" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AK8" t="n">
         <v>14</v>
@@ -2483,10 +2483,10 @@
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AO8" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AP8" t="n">
         <v>22</v>
@@ -2495,7 +2495,7 @@
         <v>30</v>
       </c>
       <c r="AR8" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AS8" t="n">
         <v>50</v>
@@ -2513,7 +2513,7 @@
         <v>40</v>
       </c>
       <c r="AX8" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AY8" t="n">
         <v>9.800000000000001</v>
@@ -2522,7 +2522,7 @@
         <v>22</v>
       </c>
       <c r="BA8" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BB8" t="n">
         <v>10</v>
@@ -2537,7 +2537,7 @@
         <v>40</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BG8" t="n">
         <v>42</v>
@@ -2546,7 +2546,7 @@
         <v>4.8</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="BJ8" t="n">
         <v>12</v>
@@ -2558,28 +2558,28 @@
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BN8" t="n">
         <v>4.1</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="BP8" t="n">
         <v>7.8</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="BR8" t="n">
         <v>22</v>
       </c>
       <c r="BS8" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BT8" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BU8" t="n">
         <v>5.9</v>
@@ -2588,23 +2588,23 @@
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY8" t="n">
         <v>9</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>8.800000000000001</v>
       </c>
       <c r="BZ8" t="n">
         <v>11</v>
       </c>
       <c r="CA8" t="n">
-        <v>7.8</v>
+        <v>5.3</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -2641,13 +2641,13 @@
         <v>1.48</v>
       </c>
       <c r="H9" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="I9" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="K9" t="n">
         <v>5.5</v>
@@ -2659,10 +2659,10 @@
         <v>1.02</v>
       </c>
       <c r="N9" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="O9" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -2686,19 +2686,19 @@
         <v>1.14</v>
       </c>
       <c r="W9" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="X9" t="n">
         <v>32</v>
       </c>
       <c r="Y9" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="Z9" t="n">
         <v>75</v>
       </c>
       <c r="AA9" t="n">
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="AB9" t="n">
         <v>14.5</v>
@@ -2737,7 +2737,7 @@
         <v>80</v>
       </c>
       <c r="AN9" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AO9" t="n">
         <v>65</v>
@@ -2746,13 +2746,13 @@
         <v>11</v>
       </c>
       <c r="AQ9" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AR9" t="n">
         <v>60</v>
       </c>
       <c r="AS9" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AT9" t="n">
         <v>12.5</v>
@@ -2773,7 +2773,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ9" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA9" t="n">
         <v>55</v>
@@ -2794,71 +2794,71 @@
         <v>4.3</v>
       </c>
       <c r="BG9" t="n">
-        <v>13.5</v>
+        <v>48</v>
       </c>
       <c r="BH9" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BI9" t="n">
         <v>4.4</v>
       </c>
       <c r="BJ9" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BN9" t="n">
         <v>4.7</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BP9" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BR9" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BS9" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BT9" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BV9" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BW9" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BX9" t="n">
         <v>46</v>
       </c>
       <c r="BY9" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BZ9" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="CA9" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -2889,16 +2889,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="G10" t="n">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="H10" t="n">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="I10" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="J10" t="n">
         <v>4</v>
@@ -2913,7 +2913,7 @@
         <v>1.02</v>
       </c>
       <c r="N10" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="O10" t="n">
         <v>1.12</v>
@@ -2922,13 +2922,13 @@
         <v>3.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="R10" t="n">
         <v>1.94</v>
       </c>
       <c r="S10" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="T10" t="n">
         <v>1.4</v>
@@ -2937,22 +2937,22 @@
         <v>3.35</v>
       </c>
       <c r="V10" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W10" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="X10" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="Y10" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Z10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA10" t="n">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="AB10" t="n">
         <v>24</v>
@@ -2961,13 +2961,13 @@
         <v>11.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AF10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG10" t="n">
         <v>14</v>
@@ -2979,10 +2979,10 @@
         <v>25</v>
       </c>
       <c r="AJ10" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AK10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL10" t="n">
         <v>25</v>
@@ -2991,25 +2991,25 @@
         <v>85</v>
       </c>
       <c r="AN10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AP10" t="n">
         <v>23</v>
       </c>
       <c r="AQ10" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AR10" t="n">
         <v>17.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AT10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU10" t="n">
         <v>9.800000000000001</v>
@@ -3018,22 +3018,22 @@
         <v>12</v>
       </c>
       <c r="AW10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AX10" t="n">
         <v>20</v>
       </c>
-      <c r="AX10" t="n">
-        <v>17</v>
-      </c>
       <c r="AY10" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ10" t="n">
         <v>11.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="BB10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC10" t="n">
         <v>19.5</v>
@@ -3045,13 +3045,13 @@
         <v>23</v>
       </c>
       <c r="BF10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH10" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BI10" t="n">
         <v>4.8</v>
@@ -3060,49 +3060,49 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BK10" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>55</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>17</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>21</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BU10" t="n">
         <v>5.1</v>
       </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>16</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BR10" t="n">
+      <c r="BV10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BX10" t="n">
         <v>20</v>
       </c>
-      <c r="BS10" t="n">
-        <v>8</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>17</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BX10" t="n">
-        <v>21</v>
-      </c>
       <c r="BY10" t="n">
-        <v>8.199999999999999</v>
+        <v>5.6</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="G11" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="I11" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="J11" t="n">
         <v>3.1</v>
       </c>
       <c r="K11" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="L11" t="n">
         <v>1.47</v>
@@ -3167,61 +3167,61 @@
         <v>1.09</v>
       </c>
       <c r="N11" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="O11" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="P11" t="n">
         <v>1.67</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="R11" t="n">
         <v>1.25</v>
       </c>
       <c r="S11" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="T11" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U11" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="V11" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W11" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="X11" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Z11" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AA11" t="n">
         <v>70</v>
       </c>
       <c r="AB11" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE11" t="n">
         <v>55</v>
       </c>
       <c r="AF11" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AG11" t="n">
         <v>13</v>
@@ -3236,10 +3236,10 @@
         <v>50</v>
       </c>
       <c r="AK11" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AL11" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM11" t="n">
         <v>160</v>
@@ -3260,7 +3260,7 @@
         <v>15</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
       <c r="AT11" t="n">
         <v>7.8</v>
@@ -3269,10 +3269,10 @@
         <v>6.4</v>
       </c>
       <c r="AV11" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="AX11" t="n">
         <v>11.5</v>
@@ -3284,25 +3284,25 @@
         <v>16.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
       <c r="BB11" t="n">
-        <v>4.7</v>
+        <v>29</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="BD11" t="n">
         <v>40</v>
       </c>
       <c r="BE11" t="n">
-        <v>5</v>
+        <v>7.8</v>
       </c>
       <c r="BF11" t="n">
-        <v>23</v>
+        <v>6.6</v>
       </c>
       <c r="BG11" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BH11" t="n">
         <v>3.1</v>
@@ -3326,47 +3326,47 @@
         <v>5.7</v>
       </c>
       <c r="BO11" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BP11" t="n">
         <v>23</v>
       </c>
       <c r="BQ11" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BR11" t="n">
         <v>40</v>
       </c>
       <c r="BS11" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BT11" t="n">
         <v>6.4</v>
       </c>
       <c r="BU11" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BV11" t="n">
         <v>28</v>
       </c>
       <c r="BW11" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BX11" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BY11" t="n">
         <v>8.6</v>
       </c>
       <c r="BZ11" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="CA11" t="n">
         <v>8.4</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -3400,34 +3400,34 @@
         <v>5.8</v>
       </c>
       <c r="G12" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="H12" t="n">
         <v>1.54</v>
       </c>
       <c r="I12" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="J12" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K12" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N12" t="n">
         <v>5.1</v>
       </c>
-      <c r="L12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N12" t="n">
-        <v>5</v>
-      </c>
       <c r="O12" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P12" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q12" t="n">
         <v>1.58</v>
@@ -3439,13 +3439,13 @@
         <v>2.44</v>
       </c>
       <c r="T12" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U12" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V12" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="W12" t="n">
         <v>1.16</v>
@@ -3460,7 +3460,7 @@
         <v>13</v>
       </c>
       <c r="AA12" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AB12" t="n">
         <v>28</v>
@@ -3481,7 +3481,7 @@
         <v>25</v>
       </c>
       <c r="AH12" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="AI12" t="n">
         <v>40</v>
@@ -3502,7 +3502,7 @@
         <v>80</v>
       </c>
       <c r="AO12" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AP12" t="n">
         <v>20</v>
@@ -3511,7 +3511,7 @@
         <v>9.6</v>
       </c>
       <c r="AR12" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AS12" t="n">
         <v>13</v>
@@ -3520,7 +3520,7 @@
         <v>21</v>
       </c>
       <c r="AU12" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AV12" t="n">
         <v>8.800000000000001</v>
@@ -3541,7 +3541,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BB12" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BC12" t="n">
         <v>7.2</v>
@@ -3553,64 +3553,64 @@
         <v>7.2</v>
       </c>
       <c r="BF12" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BG12" t="n">
         <v>5.6</v>
       </c>
       <c r="BH12" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BI12" t="n">
         <v>3.5</v>
       </c>
       <c r="BJ12" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="BN12" t="n">
         <v>10.5</v>
       </c>
       <c r="BO12" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BT12" t="n">
         <v>4.5</v>
       </c>
       <c r="BU12" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="BV12" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BW12" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BX12" t="n">
         <v>22</v>
       </c>
       <c r="BY12" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BZ12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="G13" t="n">
         <v>1.38</v>
@@ -3660,13 +3660,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="J13" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="K13" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
@@ -3687,10 +3687,10 @@
         <v>1.31</v>
       </c>
       <c r="R13" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="S13" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="T13" t="n">
         <v>1.63</v>
@@ -3699,7 +3699,7 @@
         <v>2.28</v>
       </c>
       <c r="V13" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W13" t="n">
         <v>3.6</v>
@@ -3738,7 +3738,7 @@
         <v>27</v>
       </c>
       <c r="AI13" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AJ13" t="n">
         <v>15</v>
@@ -3750,25 +3750,25 @@
         <v>30</v>
       </c>
       <c r="AM13" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN13" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="AO13" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AP13" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AQ13" t="n">
-        <v>30</v>
+        <v>5.6</v>
       </c>
       <c r="AR13" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AT13" t="n">
         <v>13</v>
@@ -3777,22 +3777,22 @@
         <v>13</v>
       </c>
       <c r="AV13" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AX13" t="n">
         <v>10.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AZ13" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BB13" t="n">
         <v>11</v>
@@ -3804,13 +3804,13 @@
         <v>21</v>
       </c>
       <c r="BE13" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BF13" t="n">
         <v>3</v>
       </c>
       <c r="BG13" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BH13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -3911,7 +3911,7 @@
         <v>7</v>
       </c>
       <c r="H14" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="I14" t="n">
         <v>1.75</v>
@@ -3935,10 +3935,10 @@
         <v>1.32</v>
       </c>
       <c r="P14" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="R14" t="n">
         <v>1.33</v>
@@ -3947,7 +3947,7 @@
         <v>3.4</v>
       </c>
       <c r="T14" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="U14" t="n">
         <v>1.88</v>
@@ -3956,7 +3956,7 @@
         <v>2.32</v>
       </c>
       <c r="W14" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X14" t="n">
         <v>17.5</v>
@@ -3983,7 +3983,7 @@
         <v>23</v>
       </c>
       <c r="AF14" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AG14" t="n">
         <v>29</v>
@@ -4013,10 +4013,10 @@
         <v>13.5</v>
       </c>
       <c r="AP14" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="AR14" t="n">
         <v>8.4</v>
@@ -4025,7 +4025,7 @@
         <v>12</v>
       </c>
       <c r="AT14" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AU14" t="n">
         <v>7.8</v>
@@ -4034,28 +4034,28 @@
         <v>8.6</v>
       </c>
       <c r="AW14" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AX14" t="n">
         <v>4</v>
       </c>
       <c r="AY14" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AZ14" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BA14" t="n">
-        <v>28</v>
+        <v>3.95</v>
       </c>
       <c r="BB14" t="n">
         <v>4.2</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BE14" t="n">
         <v>4.2</v>
@@ -4064,43 +4064,43 @@
         <v>4.2</v>
       </c>
       <c r="BG14" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH14" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BI14" t="n">
         <v>2.72</v>
       </c>
       <c r="BJ14" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK14" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BN14" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BO14" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BT14" t="n">
         <v>4.3</v>
@@ -4109,26 +4109,26 @@
         <v>3.25</v>
       </c>
       <c r="BV14" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BW14" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -4159,16 +4159,16 @@
         </is>
       </c>
       <c r="F15" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="G15" t="n">
         <v>1.97</v>
       </c>
-      <c r="G15" t="n">
-        <v>1.99</v>
-      </c>
       <c r="H15" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I15" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J15" t="n">
         <v>4</v>
@@ -4177,40 +4177,40 @@
         <v>4.1</v>
       </c>
       <c r="L15" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M15" t="n">
         <v>1.05</v>
       </c>
       <c r="N15" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O15" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P15" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="R15" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="S15" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="T15" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="U15" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="V15" t="n">
         <v>1.32</v>
       </c>
       <c r="W15" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X15" t="n">
         <v>20</v>
@@ -4243,19 +4243,19 @@
         <v>10.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI15" t="n">
-        <v>48</v>
+        <v>150</v>
       </c>
       <c r="AJ15" t="n">
         <v>23</v>
       </c>
       <c r="AK15" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL15" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM15" t="n">
         <v>75</v>
@@ -4273,25 +4273,25 @@
         <v>16.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AS15" t="n">
         <v>48</v>
       </c>
       <c r="AT15" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU15" t="n">
         <v>8.4</v>
       </c>
       <c r="AV15" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AW15" t="n">
         <v>38</v>
       </c>
       <c r="AX15" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY15" t="n">
         <v>9.6</v>
@@ -4312,10 +4312,10 @@
         <v>26</v>
       </c>
       <c r="BE15" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BF15" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BG15" t="n">
         <v>30</v>
@@ -4324,7 +4324,7 @@
         <v>4.2</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BJ15" t="n">
         <v>9.4</v>
@@ -4336,7 +4336,7 @@
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BN15" t="n">
         <v>5.2</v>
@@ -4345,7 +4345,7 @@
         <v>4.3</v>
       </c>
       <c r="BP15" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BQ15" t="n">
         <v>5.7</v>
@@ -4366,13 +4366,13 @@
         <v>32</v>
       </c>
       <c r="BW15" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX15" t="n">
         <v>38</v>
       </c>
       <c r="BY15" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BZ15" t="n">
         <v>19</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -4413,31 +4413,31 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="G16" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="H16" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I16" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="J16" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K16" t="n">
         <v>4.3</v>
       </c>
       <c r="L16" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M16" t="n">
         <v>1.04</v>
       </c>
       <c r="N16" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O16" t="n">
         <v>1.23</v>
@@ -4455,82 +4455,82 @@
         <v>2.74</v>
       </c>
       <c r="T16" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U16" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V16" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W16" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="X16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y16" t="n">
         <v>21</v>
       </c>
       <c r="Z16" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA16" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD16" t="n">
         <v>18.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF16" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG16" t="n">
         <v>10.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI16" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ16" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AK16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>29</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>130</v>
+      </c>
+      <c r="AP16" t="n">
         <v>18.5</v>
       </c>
-      <c r="AL16" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>44</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>18</v>
-      </c>
       <c r="AQ16" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>7.6</v>
+        <v>32</v>
       </c>
       <c r="AS16" t="n">
-        <v>8.4</v>
+        <v>36</v>
       </c>
       <c r="AT16" t="n">
         <v>10</v>
@@ -4539,10 +4539,10 @@
         <v>8.4</v>
       </c>
       <c r="AV16" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="AX16" t="n">
         <v>11</v>
@@ -4551,28 +4551,28 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ16" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA16" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="BB16" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BC16" t="n">
         <v>15.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>7.2</v>
+        <v>25</v>
       </c>
       <c r="BE16" t="n">
-        <v>8.199999999999999</v>
+        <v>34</v>
       </c>
       <c r="BF16" t="n">
         <v>8.6</v>
       </c>
       <c r="BG16" t="n">
-        <v>7.6</v>
+        <v>36</v>
       </c>
       <c r="BH16" t="n">
         <v>4.2</v>
@@ -4590,25 +4590,25 @@
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN16" t="n">
         <v>5</v>
       </c>
       <c r="BO16" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="BP16" t="n">
         <v>13</v>
       </c>
       <c r="BQ16" t="n">
-        <v>9.6</v>
+        <v>5.7</v>
       </c>
       <c r="BR16" t="n">
         <v>24</v>
       </c>
       <c r="BS16" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BT16" t="n">
         <v>8.199999999999999</v>
@@ -4626,17 +4626,17 @@
         <v>40</v>
       </c>
       <c r="BY16" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ16" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="CA16" t="n">
         <v>6.4</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -4676,13 +4676,13 @@
         <v>18</v>
       </c>
       <c r="I17" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="J17" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="L17" t="n">
         <v>1.15</v>
@@ -4709,7 +4709,7 @@
         <v>1.76</v>
       </c>
       <c r="T17" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="U17" t="n">
         <v>2.04</v>
@@ -4736,10 +4736,10 @@
         <v>16.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="AD17" t="n">
-        <v>580</v>
+        <v>520</v>
       </c>
       <c r="AE17" t="n">
         <v>1000</v>
@@ -4751,7 +4751,7 @@
         <v>13.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="AI17" t="n">
         <v>1000</v>
@@ -4769,7 +4769,7 @@
         <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="AO17" t="n">
         <v>1000</v>
@@ -4787,7 +4787,7 @@
         <v>60</v>
       </c>
       <c r="AT17" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AU17" t="n">
         <v>19</v>
@@ -4817,7 +4817,7 @@
         <v>11.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BE17" t="n">
         <v>42</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -4921,112 +4921,112 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.02</v>
+        <v>2.78</v>
       </c>
       <c r="G18" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="H18" t="n">
-        <v>1.02</v>
+        <v>2.58</v>
       </c>
       <c r="I18" t="n">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="J18" t="n">
-        <v>1.02</v>
+        <v>2.48</v>
       </c>
       <c r="K18" t="n">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="M18" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="N18" t="n">
-        <v>1.25</v>
+        <v>2.16</v>
       </c>
       <c r="O18" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="P18" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="R18" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S18" t="n">
-        <v>1.05</v>
+        <v>6.2</v>
       </c>
       <c r="T18" t="n">
-        <v>1.11</v>
+        <v>2.28</v>
       </c>
       <c r="U18" t="n">
-        <v>1.11</v>
+        <v>1.61</v>
       </c>
       <c r="V18" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="W18" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="X18" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="Y18" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="Z18" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA18" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB18" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AC18" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD18" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE18" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF18" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG18" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI18" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AK18" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AL18" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AM18" t="n">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AN18" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AO18" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP18" t="n">
         <v>1.01</v>
@@ -5083,68 +5083,68 @@
         <v>1.01</v>
       </c>
       <c r="BH18" t="n">
-        <v>1000</v>
+        <v>2.66</v>
       </c>
       <c r="BI18" t="n">
-        <v>1.04</v>
+        <v>2.06</v>
       </c>
       <c r="BJ18" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK18" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BL18" t="n">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="BM18" t="n">
-        <v>1.04</v>
+        <v>1.87</v>
       </c>
       <c r="BN18" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="BP18" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BQ18" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BR18" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BS18" t="n">
-        <v>1.04</v>
+        <v>1.83</v>
       </c>
       <c r="BT18" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU18" t="n">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="BV18" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW18" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BX18" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.04</v>
+        <v>1.83</v>
       </c>
       <c r="BZ18" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="CA18" t="n">
-        <v>1.04</v>
+        <v>1.84</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="G19" t="n">
         <v>2.54</v>
@@ -5184,16 +5184,16 @@
         <v>3.45</v>
       </c>
       <c r="I19" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="J19" t="n">
-        <v>2.68</v>
+        <v>2.5</v>
       </c>
       <c r="K19" t="n">
         <v>3.15</v>
       </c>
       <c r="L19" t="n">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="M19" t="n">
         <v>1.16</v>
@@ -5205,10 +5205,10 @@
         <v>1.69</v>
       </c>
       <c r="P19" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.84</v>
+        <v>2.58</v>
       </c>
       <c r="R19" t="n">
         <v>1.12</v>
@@ -5217,13 +5217,13 @@
         <v>5.7</v>
       </c>
       <c r="T19" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="U19" t="n">
         <v>1.56</v>
       </c>
       <c r="V19" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="W19" t="n">
         <v>1.64</v>
@@ -5232,22 +5232,22 @@
         <v>8</v>
       </c>
       <c r="Y19" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AA19" t="n">
         <v>150</v>
       </c>
       <c r="AB19" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AC19" t="n">
         <v>7.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AE19" t="n">
         <v>120</v>
@@ -5256,7 +5256,7 @@
         <v>13.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH19" t="n">
         <v>38</v>
@@ -5274,7 +5274,7 @@
         <v>110</v>
       </c>
       <c r="AM19" t="n">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="AN19" t="n">
         <v>60</v>
@@ -5283,122 +5283,122 @@
         <v>210</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AU19" t="n">
         <v>4.8</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BH19" t="n">
-        <v>2.7</v>
+        <v>1000</v>
       </c>
       <c r="BI19" t="n">
-        <v>2</v>
+        <v>1.04</v>
       </c>
       <c r="BJ19" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BK19" t="n">
         <v>1.04</v>
       </c>
       <c r="BL19" t="n">
-        <v>380</v>
+        <v>1000</v>
       </c>
       <c r="BM19" t="n">
         <v>1.04</v>
       </c>
       <c r="BN19" t="n">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BO19" t="n">
         <v>1.04</v>
       </c>
       <c r="BP19" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BQ19" t="n">
         <v>1.04</v>
       </c>
       <c r="BR19" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BS19" t="n">
         <v>1.04</v>
       </c>
       <c r="BT19" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BU19" t="n">
         <v>1.04</v>
       </c>
       <c r="BV19" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BW19" t="n">
         <v>1.04</v>
       </c>
       <c r="BX19" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="BY19" t="n">
         <v>1.04</v>
       </c>
       <c r="BZ19" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="CA19" t="n">
         <v>1.04</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
         <v>2.26</v>
       </c>
       <c r="G20" t="n">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="H20" t="n">
         <v>3.2</v>
@@ -5444,7 +5444,7 @@
         <v>2.54</v>
       </c>
       <c r="K20" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="L20" t="n">
         <v>1.59</v>
@@ -5600,59 +5600,59 @@
         <v>14.5</v>
       </c>
       <c r="BK20" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BL20" t="n">
         <v>320</v>
       </c>
       <c r="BM20" t="n">
-        <v>1.04</v>
+        <v>1.89</v>
       </c>
       <c r="BN20" t="n">
         <v>5.8</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="BP20" t="n">
         <v>28</v>
       </c>
       <c r="BQ20" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BR20" t="n">
         <v>65</v>
       </c>
       <c r="BS20" t="n">
-        <v>1.04</v>
+        <v>1.85</v>
       </c>
       <c r="BT20" t="n">
         <v>7.6</v>
       </c>
       <c r="BU20" t="n">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="BV20" t="n">
         <v>46</v>
       </c>
       <c r="BW20" t="n">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BX20" t="n">
         <v>80</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.04</v>
+        <v>1.86</v>
       </c>
       <c r="BZ20" t="n">
         <v>75</v>
       </c>
       <c r="CA20" t="n">
-        <v>1.04</v>
+        <v>1.86</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -5683,22 +5683,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="G21" t="n">
         <v>2.96</v>
       </c>
       <c r="H21" t="n">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="I21" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="J21" t="n">
         <v>2.62</v>
       </c>
       <c r="K21" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="L21" t="n">
         <v>1.46</v>
@@ -5710,13 +5710,13 @@
         <v>2.38</v>
       </c>
       <c r="O21" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P21" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="R21" t="n">
         <v>1.18</v>
@@ -5731,7 +5731,7 @@
         <v>1.75</v>
       </c>
       <c r="V21" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="W21" t="n">
         <v>1.51</v>
@@ -5752,7 +5752,7 @@
         <v>9.4</v>
       </c>
       <c r="AC21" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AD21" t="n">
         <v>17.5</v>
@@ -5854,59 +5854,59 @@
         <v>13</v>
       </c>
       <c r="BK21" t="n">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BL21" t="n">
         <v>230</v>
       </c>
       <c r="BM21" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BN21" t="n">
         <v>6.2</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.04</v>
+        <v>2.72</v>
       </c>
       <c r="BP21" t="n">
         <v>26</v>
       </c>
       <c r="BQ21" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BR21" t="n">
         <v>55</v>
       </c>
       <c r="BS21" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BT21" t="n">
         <v>7.8</v>
       </c>
       <c r="BU21" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="BV21" t="n">
         <v>42</v>
       </c>
       <c r="BW21" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BX21" t="n">
         <v>65</v>
       </c>
       <c r="BY21" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BZ21" t="n">
         <v>60</v>
       </c>
       <c r="CA21" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -5937,10 +5937,10 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="G22" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="H22" t="n">
         <v>3.6</v>
@@ -5973,7 +5973,7 @@
         <v>1.84</v>
       </c>
       <c r="R22" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S22" t="n">
         <v>2.92</v>
@@ -5988,7 +5988,7 @@
         <v>1.33</v>
       </c>
       <c r="W22" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="X22" t="n">
         <v>18.5</v>
@@ -6009,10 +6009,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD22" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AF22" t="n">
         <v>15</v>
@@ -6024,10 +6024,10 @@
         <v>17.5</v>
       </c>
       <c r="AI22" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AJ22" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK22" t="n">
         <v>22</v>
@@ -6039,7 +6039,7 @@
         <v>95</v>
       </c>
       <c r="AN22" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AO22" t="n">
         <v>48</v>
@@ -6051,22 +6051,22 @@
         <v>13.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>6.4</v>
+        <v>22</v>
       </c>
       <c r="AS22" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AT22" t="n">
         <v>9.4</v>
       </c>
       <c r="AU22" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV22" t="n">
         <v>13.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>6.8</v>
+        <v>32</v>
       </c>
       <c r="AX22" t="n">
         <v>11.5</v>
@@ -6078,22 +6078,22 @@
         <v>14</v>
       </c>
       <c r="BA22" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BB22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC22" t="n">
         <v>17.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>6.6</v>
+        <v>24</v>
       </c>
       <c r="BE22" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BF22" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BG22" t="n">
         <v>28</v>
@@ -6102,7 +6102,7 @@
         <v>3.9</v>
       </c>
       <c r="BI22" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="BJ22" t="n">
         <v>9.6</v>
@@ -6123,25 +6123,25 @@
         <v>3.85</v>
       </c>
       <c r="BP22" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BQ22" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BR22" t="n">
         <v>27</v>
       </c>
       <c r="BS22" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BT22" t="n">
         <v>7.6</v>
       </c>
       <c r="BU22" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BV22" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW22" t="n">
         <v>7.6</v>
@@ -6156,11 +6156,11 @@
         <v>22</v>
       </c>
       <c r="CA22" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -6191,22 +6191,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="G23" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="H23" t="n">
         <v>4.7</v>
       </c>
       <c r="I23" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="J23" t="n">
         <v>3.35</v>
       </c>
       <c r="K23" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="L23" t="n">
         <v>1.28</v>
@@ -6215,7 +6215,7 @@
         <v>1.07</v>
       </c>
       <c r="N23" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O23" t="n">
         <v>1.31</v>
@@ -6224,31 +6224,31 @@
         <v>1.76</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="R23" t="n">
         <v>1.29</v>
       </c>
       <c r="S23" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="T23" t="n">
-        <v>1.11</v>
+        <v>1.83</v>
       </c>
       <c r="U23" t="n">
-        <v>1.11</v>
+        <v>1.88</v>
       </c>
       <c r="V23" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W23" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="X23" t="n">
         <v>15.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="Z23" t="n">
         <v>44</v>
@@ -6257,13 +6257,13 @@
         <v>150</v>
       </c>
       <c r="AB23" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC23" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD23" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AE23" t="n">
         <v>85</v>
@@ -6272,28 +6272,28 @@
         <v>12</v>
       </c>
       <c r="AG23" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI23" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AJ23" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK23" t="n">
         <v>23</v>
       </c>
-      <c r="AK23" t="n">
-        <v>24</v>
-      </c>
       <c r="AL23" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM23" t="n">
         <v>150</v>
       </c>
       <c r="AN23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO23" t="n">
         <v>110</v>
@@ -6302,31 +6302,31 @@
         <v>10</v>
       </c>
       <c r="AQ23" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="AS23" t="n">
         <v>1.01</v>
       </c>
       <c r="AT23" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU23" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV23" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AX23" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY23" t="n">
         <v>8.4</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>8</v>
       </c>
       <c r="AZ23" t="n">
         <v>16.5</v>
@@ -6335,13 +6335,13 @@
         <v>1.01</v>
       </c>
       <c r="BB23" t="n">
+        <v>16</v>
+      </c>
+      <c r="BC23" t="n">
         <v>16.5</v>
       </c>
-      <c r="BC23" t="n">
-        <v>17</v>
-      </c>
       <c r="BD23" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BE23" t="n">
         <v>1.01</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -6445,22 +6445,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="G24" t="n">
-        <v>1000</v>
+        <v>1.09</v>
       </c>
       <c r="H24" t="n">
-        <v>1.04</v>
+        <v>14</v>
       </c>
       <c r="I24" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="J24" t="n">
-        <v>1.02</v>
+        <v>4.2</v>
       </c>
       <c r="K24" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="L24" t="n">
         <v>1.01</v>
@@ -6469,40 +6469,40 @@
         <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>1.1</v>
+        <v>3.45</v>
       </c>
       <c r="O24" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="P24" t="n">
-        <v>1.07</v>
+        <v>3.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.07</v>
+        <v>1.28</v>
       </c>
       <c r="R24" t="n">
-        <v>1.07</v>
+        <v>2.2</v>
       </c>
       <c r="S24" t="n">
-        <v>1.07</v>
+        <v>1.7</v>
       </c>
       <c r="T24" t="n">
-        <v>1.11</v>
+        <v>2.96</v>
       </c>
       <c r="U24" t="n">
-        <v>1.11</v>
+        <v>1.44</v>
       </c>
       <c r="V24" t="n">
         <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X24" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="Y24" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z24" t="n">
         <v>1000</v>
@@ -6511,43 +6511,43 @@
         <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AD24" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE24" t="n">
         <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AG24" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AH24" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AI24" t="n">
         <v>1000</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AK24" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AL24" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AM24" t="n">
         <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>1000</v>
+        <v>2.4</v>
       </c>
       <c r="AO24" t="n">
         <v>1000</v>
@@ -6601,7 +6601,7 @@
         <v>1.01</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="BG24" t="n">
         <v>1.01</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -6786,7 +6786,7 @@
         <v>23</v>
       </c>
       <c r="AI25" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AJ25" t="n">
         <v>38</v>
@@ -6834,7 +6834,7 @@
         <v>11</v>
       </c>
       <c r="AY25" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AZ25" t="n">
         <v>15</v>
@@ -6852,13 +6852,13 @@
         <v>4.7</v>
       </c>
       <c r="BE25" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BF25" t="n">
-        <v>4.4</v>
+        <v>20</v>
       </c>
       <c r="BG25" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BH25" t="n">
         <v>3.05</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -6977,19 +6977,19 @@
         <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="O26" t="n">
         <v>1.18</v>
       </c>
       <c r="P26" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="R26" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="S26" t="n">
         <v>2.32</v>
@@ -7025,7 +7025,7 @@
         <v>16.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AE26" t="n">
         <v>170</v>
@@ -7082,7 +7082,7 @@
         <v>4.1</v>
       </c>
       <c r="AW26" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AX26" t="n">
         <v>7</v>
@@ -7106,7 +7106,7 @@
         <v>4</v>
       </c>
       <c r="BE26" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BF26" t="n">
         <v>3.65</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -7396,7 +7396,7 @@
         <v>6.2</v>
       </c>
       <c r="BQ27" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BR27" t="n">
         <v>1000</v>
@@ -7426,11 +7426,11 @@
         <v>9</v>
       </c>
       <c r="CA27" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -7461,13 +7461,13 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="G28" t="n">
         <v>1.7</v>
       </c>
       <c r="H28" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I28" t="n">
         <v>6.4</v>
@@ -7509,7 +7509,7 @@
         <v>1.91</v>
       </c>
       <c r="V28" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W28" t="n">
         <v>2.42</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -7763,10 +7763,10 @@
         <v>2.56</v>
       </c>
       <c r="V29" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W29" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="X29" t="n">
         <v>32</v>
@@ -7787,13 +7787,13 @@
         <v>12.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AE29" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AF29" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AG29" t="n">
         <v>13</v>
@@ -7802,7 +7802,7 @@
         <v>18</v>
       </c>
       <c r="AI29" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AJ29" t="n">
         <v>27</v>
@@ -7814,67 +7814,67 @@
         <v>30</v>
       </c>
       <c r="AM29" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AN29" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AO29" t="n">
         <v>29</v>
       </c>
       <c r="AP29" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="AQ29" t="n">
-        <v>4.8</v>
+        <v>16.5</v>
       </c>
       <c r="AR29" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS29" t="n">
         <v>5.1</v>
       </c>
-      <c r="AS29" t="n">
-        <v>5.5</v>
-      </c>
       <c r="AT29" t="n">
-        <v>4.3</v>
+        <v>11</v>
       </c>
       <c r="AU29" t="n">
         <v>9</v>
       </c>
       <c r="AV29" t="n">
-        <v>4.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW29" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AX29" t="n">
         <v>12</v>
       </c>
       <c r="AY29" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ29" t="n">
-        <v>4.4</v>
+        <v>11.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BB29" t="n">
         <v>17.5</v>
       </c>
       <c r="BC29" t="n">
-        <v>4.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD29" t="n">
-        <v>4.9</v>
+        <v>19</v>
       </c>
       <c r="BE29" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="BF29" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BG29" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BH29" t="n">
         <v>4.8</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -7975,13 +7975,13 @@
         <v>1000</v>
       </c>
       <c r="H30" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="I30" t="n">
         <v>1000</v>
       </c>
       <c r="J30" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="K30" t="n">
         <v>1000</v>
@@ -7993,7 +7993,7 @@
         <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>2.24</v>
+        <v>1.1</v>
       </c>
       <c r="O30" t="n">
         <v>1.06</v>
@@ -8002,7 +8002,7 @@
         <v>2.24</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="R30" t="n">
         <v>2.24</v>
@@ -8020,7 +8020,7 @@
         <v>1.02</v>
       </c>
       <c r="W30" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X30" t="n">
         <v>1000</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -8235,7 +8235,7 @@
         <v>1000</v>
       </c>
       <c r="J31" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="K31" t="n">
         <v>1000</v>
@@ -8274,7 +8274,7 @@
         <v>1.02</v>
       </c>
       <c r="W31" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X31" t="n">
         <v>1000</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -8477,19 +8477,19 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="G32" t="n">
         <v>1000</v>
       </c>
       <c r="H32" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="I32" t="n">
         <v>1000</v>
       </c>
       <c r="J32" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K32" t="n">
         <v>1000</v>
@@ -8501,7 +8501,7 @@
         <v>1.01</v>
       </c>
       <c r="N32" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="O32" t="n">
         <v>1.06</v>
@@ -8525,10 +8525,10 @@
         <v>1.11</v>
       </c>
       <c r="V32" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W32" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X32" t="n">
         <v>1000</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -8731,19 +8731,19 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="G33" t="n">
         <v>1000</v>
       </c>
       <c r="H33" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="I33" t="n">
         <v>1000</v>
       </c>
       <c r="J33" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K33" t="n">
         <v>1000</v>
@@ -8779,10 +8779,10 @@
         <v>1.11</v>
       </c>
       <c r="V33" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W33" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X33" t="n">
         <v>1000</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -8991,13 +8991,13 @@
         <v>1000</v>
       </c>
       <c r="H34" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="I34" t="n">
         <v>1000</v>
       </c>
       <c r="J34" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="K34" t="n">
         <v>1000</v>
@@ -9036,7 +9036,7 @@
         <v>1.02</v>
       </c>
       <c r="W34" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X34" t="n">
         <v>1000</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -9239,7 +9239,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="G35" t="n">
         <v>1.47</v>
@@ -9263,7 +9263,7 @@
         <v>1.05</v>
       </c>
       <c r="N35" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O35" t="n">
         <v>1.25</v>
@@ -9272,13 +9272,13 @@
         <v>2.12</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="R35" t="n">
         <v>1.44</v>
       </c>
       <c r="S35" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="T35" t="n">
         <v>2.02</v>
@@ -9296,25 +9296,25 @@
         <v>22</v>
       </c>
       <c r="Y35" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Z35" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AA35" t="n">
-        <v>350</v>
+        <v>390</v>
       </c>
       <c r="AB35" t="n">
         <v>9.6</v>
       </c>
       <c r="AC35" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AD35" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AE35" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="AF35" t="n">
         <v>9.800000000000001</v>
@@ -9323,10 +9323,10 @@
         <v>12</v>
       </c>
       <c r="AH35" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AI35" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AJ35" t="n">
         <v>14</v>
@@ -9338,67 +9338,67 @@
         <v>44</v>
       </c>
       <c r="AM35" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AN35" t="n">
         <v>8</v>
       </c>
       <c r="AO35" t="n">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="AP35" t="n">
-        <v>4.3</v>
+        <v>14.5</v>
       </c>
       <c r="AQ35" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AR35" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="AS35" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="AT35" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU35" t="n">
-        <v>3.8</v>
+        <v>10</v>
       </c>
       <c r="AV35" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AW35" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="AX35" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AY35" t="n">
-        <v>3.7</v>
+        <v>8</v>
       </c>
       <c r="AZ35" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD35" t="n">
         <v>4.5</v>
       </c>
-      <c r="BA35" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB35" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BC35" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BD35" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BE35" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BF35" t="n">
         <v>5.2</v>
       </c>
       <c r="BG35" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BH35" t="n">
         <v>3.9</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -9493,22 +9493,22 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.22</v>
+        <v>2.68</v>
       </c>
       <c r="G36" t="n">
-        <v>3.85</v>
+        <v>3.1</v>
       </c>
       <c r="H36" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="I36" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="J36" t="n">
-        <v>2.48</v>
+        <v>2.82</v>
       </c>
       <c r="K36" t="n">
-        <v>4.5</v>
+        <v>3.55</v>
       </c>
       <c r="L36" t="n">
         <v>1.4</v>
@@ -9517,88 +9517,88 @@
         <v>1.09</v>
       </c>
       <c r="N36" t="n">
-        <v>1.1</v>
+        <v>2.68</v>
       </c>
       <c r="O36" t="n">
         <v>1.4</v>
       </c>
       <c r="P36" t="n">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="R36" t="n">
         <v>1.25</v>
       </c>
       <c r="S36" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="T36" t="n">
-        <v>1.11</v>
+        <v>1.86</v>
       </c>
       <c r="U36" t="n">
-        <v>1.11</v>
+        <v>1.96</v>
       </c>
       <c r="V36" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="W36" t="n">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="X36" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y36" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z36" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AA36" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB36" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG36" t="n">
         <v>13.5</v>
       </c>
-      <c r="AC36" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>1000</v>
-      </c>
       <c r="AH36" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI36" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK36" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AL36" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM36" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN36" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AO36" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AP36" t="n">
         <v>1.01</v>
@@ -9616,13 +9616,13 @@
         <v>1.01</v>
       </c>
       <c r="AU36" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AV36" t="n">
         <v>1.01</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AX36" t="n">
         <v>1.01</v>
@@ -9640,7 +9640,7 @@
         <v>1.01</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BD36" t="n">
         <v>1.01</v>
@@ -9649,10 +9649,10 @@
         <v>1.01</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BG36" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BH36" t="n">
         <v>3.5</v>
@@ -9664,59 +9664,59 @@
         <v>12</v>
       </c>
       <c r="BK36" t="n">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BL36" t="n">
         <v>180</v>
       </c>
       <c r="BM36" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BN36" t="n">
         <v>6.8</v>
       </c>
       <c r="BO36" t="n">
-        <v>1.04</v>
+        <v>2.88</v>
       </c>
       <c r="BP36" t="n">
         <v>29</v>
       </c>
       <c r="BQ36" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BR36" t="n">
         <v>48</v>
       </c>
       <c r="BS36" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BT36" t="n">
         <v>6.8</v>
       </c>
       <c r="BU36" t="n">
-        <v>1.04</v>
+        <v>2.88</v>
       </c>
       <c r="BV36" t="n">
         <v>29</v>
       </c>
       <c r="BW36" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BX36" t="n">
         <v>48</v>
       </c>
       <c r="BY36" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BZ36" t="n">
         <v>44</v>
       </c>
       <c r="CA36" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -9747,7 +9747,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="G37" t="n">
         <v>2.24</v>
@@ -9756,7 +9756,7 @@
         <v>4.4</v>
       </c>
       <c r="I37" t="n">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="J37" t="n">
         <v>2.9</v>
@@ -9765,7 +9765,7 @@
         <v>3.15</v>
       </c>
       <c r="L37" t="n">
-        <v>1.56</v>
+        <v>1.68</v>
       </c>
       <c r="M37" t="n">
         <v>1.16</v>
@@ -9795,7 +9795,7 @@
         <v>1.62</v>
       </c>
       <c r="V37" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W37" t="n">
         <v>1.8</v>
@@ -9858,7 +9858,7 @@
         <v>6.2</v>
       </c>
       <c r="AQ37" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR37" t="n">
         <v>25</v>
@@ -9867,7 +9867,7 @@
         <v>5.3</v>
       </c>
       <c r="AT37" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AU37" t="n">
         <v>6.4</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -10013,13 +10013,13 @@
         <v>4.7</v>
       </c>
       <c r="J38" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K38" t="n">
         <v>3.5</v>
       </c>
       <c r="L38" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="M38" t="n">
         <v>1.1</v>
@@ -10028,7 +10028,7 @@
         <v>3.05</v>
       </c>
       <c r="O38" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P38" t="n">
         <v>1.7</v>
@@ -10049,10 +10049,10 @@
         <v>1.92</v>
       </c>
       <c r="V38" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W38" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="X38" t="n">
         <v>11</v>
@@ -10073,7 +10073,7 @@
         <v>7.6</v>
       </c>
       <c r="AD38" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AE38" t="n">
         <v>90</v>
@@ -10115,10 +10115,10 @@
         <v>11.5</v>
       </c>
       <c r="AR38" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AS38" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AT38" t="n">
         <v>7</v>
@@ -10127,10 +10127,10 @@
         <v>6.6</v>
       </c>
       <c r="AV38" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AW38" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX38" t="n">
         <v>9.4</v>
@@ -10142,7 +10142,7 @@
         <v>17.5</v>
       </c>
       <c r="BA38" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB38" t="n">
         <v>21</v>
@@ -10154,13 +10154,13 @@
         <v>32</v>
       </c>
       <c r="BE38" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BF38" t="n">
         <v>17.5</v>
       </c>
       <c r="BG38" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BH38" t="n">
         <v>3.05</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -10264,7 +10264,7 @@
         <v>3.1</v>
       </c>
       <c r="I39" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J39" t="n">
         <v>3.2</v>
@@ -10273,7 +10273,7 @@
         <v>3.4</v>
       </c>
       <c r="L39" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="M39" t="n">
         <v>1.1</v>
@@ -10288,7 +10288,7 @@
         <v>1.64</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="R39" t="n">
         <v>1.23</v>
@@ -10297,7 +10297,7 @@
         <v>4.5</v>
       </c>
       <c r="T39" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="U39" t="n">
         <v>1.89</v>
@@ -10339,7 +10339,7 @@
         <v>15</v>
       </c>
       <c r="AH39" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AI39" t="n">
         <v>75</v>
@@ -10372,10 +10372,10 @@
         <v>15</v>
       </c>
       <c r="AS39" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AT39" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU39" t="n">
         <v>6.2</v>
@@ -10384,7 +10384,7 @@
         <v>10</v>
       </c>
       <c r="AW39" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AX39" t="n">
         <v>11.5</v>
@@ -10396,25 +10396,25 @@
         <v>17.5</v>
       </c>
       <c r="BA39" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE39" t="n">
         <v>4.2</v>
       </c>
-      <c r="BB39" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC39" t="n">
+      <c r="BF39" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BG39" t="n">
         <v>4</v>
-      </c>
-      <c r="BD39" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE39" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BF39" t="n">
-        <v>4</v>
-      </c>
-      <c r="BG39" t="n">
-        <v>4.1</v>
       </c>
       <c r="BH39" t="n">
         <v>3</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -10512,13 +10512,13 @@
         <v>1.62</v>
       </c>
       <c r="G40" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="H40" t="n">
         <v>6</v>
       </c>
       <c r="I40" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J40" t="n">
         <v>4</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -10766,22 +10766,22 @@
         <v>1.48</v>
       </c>
       <c r="G41" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="H41" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="I41" t="n">
         <v>7.8</v>
       </c>
       <c r="J41" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="K41" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L41" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="M41" t="n">
         <v>1.04</v>
@@ -10793,7 +10793,7 @@
         <v>1.21</v>
       </c>
       <c r="P41" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="Q41" t="n">
         <v>1.62</v>
@@ -10802,19 +10802,19 @@
         <v>1.58</v>
       </c>
       <c r="S41" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="T41" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U41" t="n">
         <v>2.1</v>
       </c>
       <c r="V41" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W41" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="X41" t="n">
         <v>24</v>
@@ -10823,7 +10823,7 @@
         <v>32</v>
       </c>
       <c r="Z41" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AA41" t="n">
         <v>250</v>
@@ -10832,7 +10832,7 @@
         <v>10.5</v>
       </c>
       <c r="AC41" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AD41" t="n">
         <v>27</v>
@@ -10841,10 +10841,10 @@
         <v>95</v>
       </c>
       <c r="AF41" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG41" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH41" t="n">
         <v>22</v>
@@ -10853,7 +10853,7 @@
         <v>85</v>
       </c>
       <c r="AJ41" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AK41" t="n">
         <v>14.5</v>
@@ -10865,10 +10865,10 @@
         <v>110</v>
       </c>
       <c r="AN41" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AO41" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AP41" t="n">
         <v>20</v>
@@ -10880,7 +10880,7 @@
         <v>55</v>
       </c>
       <c r="AS41" t="n">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="AT41" t="n">
         <v>9.4</v>
@@ -10892,7 +10892,7 @@
         <v>24</v>
       </c>
       <c r="AW41" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AX41" t="n">
         <v>9.199999999999999</v>
@@ -10904,10 +10904,10 @@
         <v>19</v>
       </c>
       <c r="BA41" t="n">
-        <v>13.5</v>
+        <v>18.5</v>
       </c>
       <c r="BB41" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BC41" t="n">
         <v>13</v>
@@ -10916,13 +10916,13 @@
         <v>24</v>
       </c>
       <c r="BE41" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="BF41" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BG41" t="n">
-        <v>13</v>
+        <v>17.5</v>
       </c>
       <c r="BH41" t="n">
         <v>4.3</v>
@@ -10934,34 +10934,34 @@
         <v>10.5</v>
       </c>
       <c r="BK41" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL41" t="n">
         <v>1000</v>
       </c>
       <c r="BM41" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN41" t="n">
         <v>4.2</v>
       </c>
       <c r="BO41" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BP41" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BQ41" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BR41" t="n">
         <v>22</v>
       </c>
       <c r="BS41" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BT41" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BU41" t="n">
         <v>6.4</v>
@@ -10970,13 +10970,13 @@
         <v>1000</v>
       </c>
       <c r="BW41" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX41" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY41" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BZ41" t="n">
         <v>13</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -11017,16 +11017,16 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="G42" t="n">
         <v>2.12</v>
       </c>
       <c r="H42" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I42" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J42" t="n">
         <v>3.5</v>
@@ -11050,19 +11050,19 @@
         <v>1.78</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R42" t="n">
         <v>1.3</v>
       </c>
       <c r="S42" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="T42" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="U42" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="V42" t="n">
         <v>1.3</v>
@@ -11083,7 +11083,7 @@
         <v>100</v>
       </c>
       <c r="AB42" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC42" t="n">
         <v>8</v>
@@ -11098,7 +11098,7 @@
         <v>12.5</v>
       </c>
       <c r="AG42" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH42" t="n">
         <v>21</v>
@@ -11152,7 +11152,7 @@
         <v>10.5</v>
       </c>
       <c r="AY42" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ42" t="n">
         <v>17.5</v>
@@ -11170,7 +11170,7 @@
         <v>36</v>
       </c>
       <c r="BE42" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BF42" t="n">
         <v>16</v>
@@ -11200,7 +11200,7 @@
         <v>4.8</v>
       </c>
       <c r="BO42" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BP42" t="n">
         <v>16</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -11271,7 +11271,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="G43" t="n">
         <v>2.06</v>
@@ -11301,7 +11301,7 @@
         <v>1.37</v>
       </c>
       <c r="P43" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Q43" t="n">
         <v>2.08</v>
@@ -11337,10 +11337,10 @@
         <v>120</v>
       </c>
       <c r="AB43" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC43" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD43" t="n">
         <v>18</v>
@@ -11385,10 +11385,10 @@
         <v>12.5</v>
       </c>
       <c r="AR43" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS43" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AT43" t="n">
         <v>7.4</v>
@@ -11406,13 +11406,13 @@
         <v>10.5</v>
       </c>
       <c r="AY43" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ43" t="n">
         <v>17</v>
       </c>
       <c r="BA43" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB43" t="n">
         <v>19.5</v>
@@ -11424,13 +11424,13 @@
         <v>30</v>
       </c>
       <c r="BE43" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF43" t="n">
         <v>14.5</v>
       </c>
       <c r="BG43" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BH43" t="n">
         <v>3.3</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -11525,22 +11525,22 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.84</v>
+        <v>1.04</v>
       </c>
       <c r="G44" t="n">
-        <v>2.18</v>
+        <v>1000</v>
       </c>
       <c r="H44" t="n">
-        <v>3.2</v>
+        <v>1.04</v>
       </c>
       <c r="I44" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="J44" t="n">
-        <v>3.55</v>
+        <v>1.02</v>
       </c>
       <c r="K44" t="n">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="L44" t="n">
         <v>1.01</v>
@@ -11558,10 +11558,10 @@
         <v>1.25</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="R44" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="S44" t="n">
         <v>2.58</v>
@@ -11573,10 +11573,10 @@
         <v>1.11</v>
       </c>
       <c r="V44" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="W44" t="n">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="X44" t="n">
         <v>1000</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -11779,22 +11779,22 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G45" t="n">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="H45" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="I45" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="J45" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K45" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L45" t="n">
         <v>1.31</v>
@@ -11830,7 +11830,7 @@
         <v>1.51</v>
       </c>
       <c r="W45" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="X45" t="n">
         <v>21</v>
@@ -11899,10 +11899,10 @@
         <v>30</v>
       </c>
       <c r="AT45" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU45" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV45" t="n">
         <v>11</v>
@@ -11917,10 +11917,10 @@
         <v>10.5</v>
       </c>
       <c r="AZ45" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BA45" t="n">
-        <v>28</v>
+        <v>1.03</v>
       </c>
       <c r="BB45" t="n">
         <v>1.03</v>
@@ -11935,7 +11935,7 @@
         <v>1.03</v>
       </c>
       <c r="BF45" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BG45" t="n">
         <v>16</v>
@@ -11956,7 +11956,7 @@
         <v>1000</v>
       </c>
       <c r="BM45" t="n">
-        <v>2.86</v>
+        <v>11</v>
       </c>
       <c r="BN45" t="n">
         <v>5.9</v>
@@ -11974,7 +11974,7 @@
         <v>1000</v>
       </c>
       <c r="BS45" t="n">
-        <v>2.68</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT45" t="n">
         <v>6.2</v>
@@ -11992,7 +11992,7 @@
         <v>1000</v>
       </c>
       <c r="BY45" t="n">
-        <v>2.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ45" t="n">
         <v>1000</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -12042,7 +12042,7 @@
         <v>1.04</v>
       </c>
       <c r="I46" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="J46" t="n">
         <v>6.2</v>
@@ -12057,22 +12057,22 @@
         <v>1.01</v>
       </c>
       <c r="N46" t="n">
-        <v>2.12</v>
+        <v>1.91</v>
       </c>
       <c r="O46" t="n">
         <v>1.09</v>
       </c>
       <c r="P46" t="n">
-        <v>1.92</v>
+        <v>1.4</v>
       </c>
       <c r="Q46" t="n">
         <v>1.09</v>
       </c>
       <c r="R46" t="n">
-        <v>1.87</v>
+        <v>1.39</v>
       </c>
       <c r="S46" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="T46" t="n">
         <v>1.11</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -12287,40 +12287,40 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="G47" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="H47" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="I47" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="J47" t="n">
         <v>3.1</v>
       </c>
       <c r="K47" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L47" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="M47" t="n">
         <v>1.11</v>
       </c>
       <c r="N47" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="O47" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="P47" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="R47" t="n">
         <v>1.22</v>
@@ -12329,43 +12329,43 @@
         <v>4.9</v>
       </c>
       <c r="T47" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="U47" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="V47" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W47" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="X47" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y47" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="Z47" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AA47" t="n">
         <v>100</v>
       </c>
       <c r="AB47" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AC47" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD47" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AE47" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AF47" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG47" t="n">
         <v>12</v>
@@ -12383,13 +12383,13 @@
         <v>46</v>
       </c>
       <c r="AL47" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AM47" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AN47" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="AO47" t="n">
         <v>90</v>
@@ -12398,40 +12398,40 @@
         <v>8.6</v>
       </c>
       <c r="AQ47" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR47" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AS47" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT47" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AU47" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV47" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW47" t="n">
         <v>32</v>
       </c>
       <c r="AX47" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AY47" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ47" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA47" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BB47" t="n">
-        <v>7.8</v>
+        <v>24</v>
       </c>
       <c r="BC47" t="n">
         <v>24</v>
@@ -12440,40 +12440,40 @@
         <v>40</v>
       </c>
       <c r="BE47" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF47" t="n">
         <v>20</v>
       </c>
       <c r="BG47" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH47" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="BI47" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="BJ47" t="n">
         <v>11</v>
       </c>
       <c r="BK47" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL47" t="n">
         <v>1000</v>
       </c>
       <c r="BM47" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BN47" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BO47" t="n">
         <v>3.85</v>
       </c>
       <c r="BP47" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BQ47" t="n">
         <v>9.199999999999999</v>
@@ -12488,29 +12488,29 @@
         <v>6.8</v>
       </c>
       <c r="BU47" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BV47" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BW47" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BX47" t="n">
         <v>55</v>
       </c>
       <c r="BY47" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BZ47" t="n">
         <v>1000</v>
       </c>
       <c r="CA47" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -12607,7 +12607,7 @@
         <v>75</v>
       </c>
       <c r="AB48" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC48" t="n">
         <v>7.4</v>
@@ -12622,7 +12622,7 @@
         <v>23</v>
       </c>
       <c r="AG48" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AH48" t="n">
         <v>32</v>
@@ -12634,7 +12634,7 @@
         <v>65</v>
       </c>
       <c r="AK48" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AL48" t="n">
         <v>110</v>
@@ -12658,7 +12658,7 @@
         <v>13</v>
       </c>
       <c r="AS48" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="AT48" t="n">
         <v>6.8</v>
@@ -12670,7 +12670,7 @@
         <v>10.5</v>
       </c>
       <c r="AW48" t="n">
-        <v>36</v>
+        <v>5.1</v>
       </c>
       <c r="AX48" t="n">
         <v>13.5</v>
@@ -12682,25 +12682,25 @@
         <v>18.5</v>
       </c>
       <c r="BA48" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="BB48" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC48" t="n">
+        <v>38</v>
+      </c>
+      <c r="BD48" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BE48" t="n">
         <v>5.5</v>
       </c>
-      <c r="BC48" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BD48" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BE48" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BF48" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="BG48" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="BH48" t="n">
         <v>1000</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -12810,7 +12810,7 @@
         <v>4.9</v>
       </c>
       <c r="K49" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L49" t="n">
         <v>1.34</v>
@@ -12819,28 +12819,28 @@
         <v>1.05</v>
       </c>
       <c r="N49" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O49" t="n">
         <v>1.25</v>
       </c>
       <c r="P49" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="R49" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S49" t="n">
         <v>2.94</v>
       </c>
       <c r="T49" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="U49" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="V49" t="n">
         <v>1.14</v>
@@ -12873,7 +12873,7 @@
         <v>1000</v>
       </c>
       <c r="AF49" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG49" t="n">
         <v>10</v>
@@ -12945,7 +12945,7 @@
         <v>13.5</v>
       </c>
       <c r="BD49" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BE49" t="n">
         <v>42</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -13055,7 +13055,7 @@
         <v>4.5</v>
       </c>
       <c r="H50" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="I50" t="n">
         <v>1.99</v>
@@ -13109,31 +13109,31 @@
         <v>13</v>
       </c>
       <c r="Z50" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AA50" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AB50" t="n">
         <v>22</v>
       </c>
       <c r="AC50" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD50" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE50" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF50" t="n">
         <v>42</v>
       </c>
       <c r="AG50" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH50" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI50" t="n">
         <v>38</v>
@@ -13154,7 +13154,7 @@
         <v>55</v>
       </c>
       <c r="AO50" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AP50" t="n">
         <v>16</v>
@@ -13178,10 +13178,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW50" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AX50" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="AY50" t="n">
         <v>12.5</v>
@@ -13190,22 +13190,22 @@
         <v>12.5</v>
       </c>
       <c r="BA50" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="BB50" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BC50" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BD50" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BE50" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BF50" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BG50" t="n">
         <v>9.800000000000001</v>
@@ -13214,7 +13214,7 @@
         <v>3.8</v>
       </c>
       <c r="BI50" t="n">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="BJ50" t="n">
         <v>9.4</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -13306,19 +13306,19 @@
         <v>1.95</v>
       </c>
       <c r="G51" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="H51" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="I51" t="n">
         <v>4.4</v>
       </c>
       <c r="J51" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K51" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L51" t="n">
         <v>1.3</v>
@@ -13336,7 +13336,7 @@
         <v>2.02</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="R51" t="n">
         <v>1.41</v>
@@ -13351,10 +13351,10 @@
         <v>2.18</v>
       </c>
       <c r="V51" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W51" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="X51" t="n">
         <v>17</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -13590,19 +13590,19 @@
         <v>2</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="R52" t="n">
         <v>1.38</v>
       </c>
       <c r="S52" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T52" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="U52" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="V52" t="n">
         <v>1.32</v>
@@ -13635,7 +13635,7 @@
         <v>60</v>
       </c>
       <c r="AF52" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AG52" t="n">
         <v>13.5</v>
@@ -13674,7 +13674,7 @@
         <v>20</v>
       </c>
       <c r="AS52" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AT52" t="n">
         <v>8.6</v>
@@ -13686,19 +13686,19 @@
         <v>12</v>
       </c>
       <c r="AW52" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AX52" t="n">
         <v>10</v>
       </c>
       <c r="AY52" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ52" t="n">
         <v>14.5</v>
       </c>
       <c r="BA52" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BB52" t="n">
         <v>19</v>
@@ -13707,16 +13707,16 @@
         <v>16</v>
       </c>
       <c r="BD52" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="BE52" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BF52" t="n">
         <v>10.5</v>
       </c>
       <c r="BG52" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BH52" t="n">
         <v>3.7</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>
@@ -13814,37 +13814,37 @@
         <v>3</v>
       </c>
       <c r="G53" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H53" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="I53" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="J53" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K53" t="n">
         <v>4</v>
       </c>
       <c r="L53" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M53" t="n">
         <v>1.04</v>
       </c>
       <c r="N53" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="O53" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P53" t="n">
         <v>2.56</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="R53" t="n">
         <v>1.63</v>
@@ -13856,67 +13856,67 @@
         <v>1.54</v>
       </c>
       <c r="U53" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="V53" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="W53" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X53" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y53" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Z53" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AA53" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AB53" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AC53" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD53" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE53" t="n">
         <v>21</v>
       </c>
       <c r="AF53" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AG53" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH53" t="n">
         <v>16</v>
       </c>
-      <c r="AH53" t="n">
-        <v>17</v>
-      </c>
       <c r="AI53" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ53" t="n">
         <v>55</v>
       </c>
       <c r="AK53" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL53" t="n">
         <v>34</v>
-      </c>
-      <c r="AL53" t="n">
-        <v>38</v>
       </c>
       <c r="AM53" t="n">
         <v>65</v>
       </c>
       <c r="AN53" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AO53" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP53" t="n">
         <v>21</v>
@@ -13928,7 +13928,7 @@
         <v>17</v>
       </c>
       <c r="AS53" t="n">
-        <v>5.4</v>
+        <v>21</v>
       </c>
       <c r="AT53" t="n">
         <v>16</v>
@@ -13943,34 +13943,34 @@
         <v>18.5</v>
       </c>
       <c r="AX53" t="n">
-        <v>5.2</v>
+        <v>16.5</v>
       </c>
       <c r="AY53" t="n">
         <v>12.5</v>
       </c>
       <c r="AZ53" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BA53" t="n">
-        <v>5.4</v>
+        <v>19</v>
       </c>
       <c r="BB53" t="n">
-        <v>5.7</v>
+        <v>26</v>
       </c>
       <c r="BC53" t="n">
-        <v>5.4</v>
+        <v>23</v>
       </c>
       <c r="BD53" t="n">
-        <v>5.4</v>
+        <v>26</v>
       </c>
       <c r="BE53" t="n">
-        <v>5.6</v>
+        <v>29</v>
       </c>
       <c r="BF53" t="n">
         <v>16.5</v>
       </c>
       <c r="BG53" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH53" t="n">
         <v>5</v>
@@ -14012,7 +14012,7 @@
         <v>6.6</v>
       </c>
       <c r="BU53" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="BV53" t="n">
         <v>18</v>
@@ -14027,14 +14027,14 @@
         <v>1.04</v>
       </c>
       <c r="BZ53" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="CA53" t="n">
         <v>1.04</v>
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-07-16 11:49:17</t>
+          <t>2026-07-16 14:07:56</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-17.xlsx
@@ -860,61 +860,61 @@
         <v>3.75</v>
       </c>
       <c r="G2" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="H2" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="I2" t="n">
         <v>2.16</v>
       </c>
       <c r="J2" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K2" t="n">
         <v>3.8</v>
       </c>
       <c r="L2" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="O2" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="R2" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S2" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="T2" t="n">
         <v>1.78</v>
       </c>
       <c r="U2" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V2" t="n">
         <v>1.86</v>
       </c>
       <c r="W2" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X2" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Y2" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z2" t="n">
         <v>15.5</v>
@@ -929,10 +929,10 @@
         <v>9.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AE2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AF2" t="n">
         <v>32</v>
@@ -941,7 +941,7 @@
         <v>18.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI2" t="n">
         <v>42</v>
@@ -962,7 +962,7 @@
         <v>55</v>
       </c>
       <c r="AO2" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AP2" t="n">
         <v>13</v>
@@ -986,101 +986,101 @@
         <v>9.6</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.8</v>
+        <v>19.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY2" t="n">
         <v>14</v>
       </c>
       <c r="AZ2" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BA2" t="n">
         <v>30</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.6</v>
+        <v>70</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BG2" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="BI2" t="n">
         <v>2.92</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>5.5</v>
+        <v>15</v>
       </c>
       <c r="BN2" t="n">
         <v>7.2</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.8</v>
+        <v>11</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="BT2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BU2" t="n">
         <v>3.95</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BW2" t="n">
-        <v>4.1</v>
+        <v>8</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>4.8</v>
+        <v>10.5</v>
       </c>
       <c r="BZ2" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.8</v>
+        <v>10</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-16 14:07:56</t>
+          <t>2026-07-16 16:29:12</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         <v>4.1</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K3" t="n">
         <v>3.85</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-16 14:07:56</t>
+          <t>2026-07-16 16:29:12</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="G4" t="n">
         <v>4.6</v>
@@ -1377,7 +1377,7 @@
         <v>1.96</v>
       </c>
       <c r="J4" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K4" t="n">
         <v>3.95</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-16 14:07:56</t>
+          <t>2026-07-16 16:29:12</t>
         </is>
       </c>
     </row>
@@ -1655,10 +1655,10 @@
         <v>1.64</v>
       </c>
       <c r="R5" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="S5" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="T5" t="n">
         <v>1.64</v>
@@ -1694,7 +1694,7 @@
         <v>10.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AF5" t="n">
         <v>80</v>
@@ -1703,10 +1703,10 @@
         <v>18.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI5" t="n">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="AJ5" t="n">
         <v>1000</v>
@@ -1784,7 +1784,7 @@
         <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="BJ5" t="n">
         <v>12.5</v>
@@ -1805,7 +1805,7 @@
         <v>5.4</v>
       </c>
       <c r="BP5" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BQ5" t="n">
         <v>1.95</v>
@@ -1838,11 +1838,11 @@
         <v>22</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-16 14:07:56</t>
+          <t>2026-07-16 16:29:12</t>
         </is>
       </c>
     </row>
@@ -1879,13 +1879,13 @@
         <v>5.6</v>
       </c>
       <c r="H6" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="I6" t="n">
         <v>2.18</v>
       </c>
       <c r="J6" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K6" t="n">
         <v>3.55</v>
@@ -1966,10 +1966,10 @@
         <v>140</v>
       </c>
       <c r="AK6" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AL6" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AM6" t="n">
         <v>190</v>
@@ -1984,22 +1984,22 @@
         <v>7.6</v>
       </c>
       <c r="AQ6" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AR6" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AS6" t="n">
         <v>18.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AU6" t="n">
         <v>5.8</v>
       </c>
       <c r="AV6" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW6" t="n">
         <v>18.5</v>
@@ -2029,7 +2029,7 @@
         <v>4.2</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BG6" t="n">
         <v>15.5</v>
@@ -2038,7 +2038,7 @@
         <v>3.05</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.4</v>
+        <v>2.64</v>
       </c>
       <c r="BJ6" t="n">
         <v>11.5</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-16 14:07:56</t>
+          <t>2026-07-16 16:29:12</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-16 14:07:56</t>
+          <t>2026-07-16 16:29:12</t>
         </is>
       </c>
     </row>
@@ -2381,22 +2381,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="G8" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="H8" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I8" t="n">
         <v>10.5</v>
       </c>
       <c r="J8" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="K8" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="L8" t="n">
         <v>1.23</v>
@@ -2405,22 +2405,22 @@
         <v>1.03</v>
       </c>
       <c r="N8" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="O8" t="n">
         <v>1.19</v>
       </c>
       <c r="P8" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="R8" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="S8" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="T8" t="n">
         <v>1.92</v>
@@ -2429,10 +2429,10 @@
         <v>2.02</v>
       </c>
       <c r="V8" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W8" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="X8" t="n">
         <v>27</v>
@@ -2453,19 +2453,19 @@
         <v>13.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AE8" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AF8" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG8" t="n">
         <v>11</v>
       </c>
       <c r="AH8" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AI8" t="n">
         <v>120</v>
@@ -2483,7 +2483,7 @@
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AO8" t="n">
         <v>140</v>
@@ -2495,7 +2495,7 @@
         <v>30</v>
       </c>
       <c r="AR8" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AS8" t="n">
         <v>50</v>
@@ -2504,7 +2504,7 @@
         <v>10</v>
       </c>
       <c r="AU8" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AV8" t="n">
         <v>30</v>
@@ -2513,7 +2513,7 @@
         <v>40</v>
       </c>
       <c r="AX8" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AY8" t="n">
         <v>9.800000000000001</v>
@@ -2537,13 +2537,13 @@
         <v>40</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BG8" t="n">
         <v>42</v>
       </c>
       <c r="BH8" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BI8" t="n">
         <v>4</v>
@@ -2552,13 +2552,13 @@
         <v>12</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BN8" t="n">
         <v>4.1</v>
@@ -2570,41 +2570,41 @@
         <v>7.8</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BR8" t="n">
         <v>22</v>
       </c>
       <c r="BS8" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BT8" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ8" t="n">
         <v>11</v>
       </c>
       <c r="CA8" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-16 14:07:56</t>
+          <t>2026-07-16 16:29:12</t>
         </is>
       </c>
     </row>
@@ -2635,124 +2635,124 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="G9" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="H9" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="I9" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="J9" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="K9" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="L9" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="M9" t="n">
         <v>1.02</v>
       </c>
       <c r="N9" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="O9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="V9" t="n">
         <v>1.15</v>
       </c>
-      <c r="P9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.14</v>
-      </c>
       <c r="W9" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="X9" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="Y9" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="Z9" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AA9" t="n">
         <v>220</v>
       </c>
       <c r="AB9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF9" t="n">
         <v>14.5</v>
       </c>
-      <c r="AC9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>29</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>12</v>
-      </c>
       <c r="AG9" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AJ9" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AK9" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AL9" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AM9" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AN9" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AO9" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AP9" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="AQ9" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AR9" t="n">
         <v>60</v>
       </c>
       <c r="AS9" t="n">
-        <v>16</v>
+        <v>9.4</v>
       </c>
       <c r="AT9" t="n">
         <v>12.5</v>
@@ -2761,104 +2761,104 @@
         <v>11.5</v>
       </c>
       <c r="AV9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW9" t="n">
-        <v>14</v>
+        <v>9.6</v>
       </c>
       <c r="AX9" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ9" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="BB9" t="n">
         <v>12.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BG9" t="n">
-        <v>48</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH9" t="n">
         <v>5.4</v>
       </c>
       <c r="BI9" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BJ9" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK9" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BN9" t="n">
         <v>4.7</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BP9" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BR9" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BS9" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BT9" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BU9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>50</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>44</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="CA9" t="n">
         <v>5.2</v>
       </c>
-      <c r="BV9" t="n">
-        <v>55</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>8</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>46</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BZ9" t="n">
-        <v>10</v>
-      </c>
-      <c r="CA9" t="n">
-        <v>4.8</v>
-      </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-16 14:07:56</t>
+          <t>2026-07-16 16:29:12</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="G10" t="n">
         <v>2.72</v>
@@ -2898,7 +2898,7 @@
         <v>2.52</v>
       </c>
       <c r="I10" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="J10" t="n">
         <v>4</v>
@@ -2922,37 +2922,37 @@
         <v>3.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="R10" t="n">
         <v>1.94</v>
       </c>
       <c r="S10" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="T10" t="n">
         <v>1.4</v>
       </c>
       <c r="U10" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="V10" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W10" t="n">
         <v>1.58</v>
       </c>
       <c r="X10" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="Y10" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Z10" t="n">
         <v>26</v>
       </c>
       <c r="AA10" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AB10" t="n">
         <v>24</v>
@@ -2961,10 +2961,10 @@
         <v>11.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF10" t="n">
         <v>27</v>
@@ -2982,7 +2982,7 @@
         <v>42</v>
       </c>
       <c r="AK10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL10" t="n">
         <v>25</v>
@@ -2994,7 +2994,7 @@
         <v>11</v>
       </c>
       <c r="AO10" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AP10" t="n">
         <v>23</v>
@@ -3018,13 +3018,13 @@
         <v>12</v>
       </c>
       <c r="AW10" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AX10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY10" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ10" t="n">
         <v>11.5</v>
@@ -3048,7 +3048,7 @@
         <v>9.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH10" t="n">
         <v>5.4</v>
@@ -3060,13 +3060,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BK10" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="BL10" t="n">
         <v>55</v>
       </c>
       <c r="BM10" t="n">
-        <v>6.8</v>
+        <v>11.5</v>
       </c>
       <c r="BN10" t="n">
         <v>6.8</v>
@@ -3078,31 +3078,31 @@
         <v>17</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.3</v>
+        <v>8</v>
       </c>
       <c r="BR10" t="n">
         <v>21</v>
       </c>
       <c r="BS10" t="n">
-        <v>5.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT10" t="n">
         <v>6.4</v>
       </c>
       <c r="BU10" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BV10" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BW10" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BX10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BY10" t="n">
-        <v>5.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-16 14:07:56</t>
+          <t>2026-07-16 16:29:12</t>
         </is>
       </c>
     </row>
@@ -3143,10 +3143,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="G11" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="H11" t="n">
         <v>3.1</v>
@@ -3194,7 +3194,7 @@
         <v>1.42</v>
       </c>
       <c r="W11" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X11" t="n">
         <v>11.5</v>
@@ -3209,7 +3209,7 @@
         <v>70</v>
       </c>
       <c r="AB11" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC11" t="n">
         <v>7.8</v>
@@ -3251,7 +3251,7 @@
         <v>48</v>
       </c>
       <c r="AP11" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AQ11" t="n">
         <v>9</v>
@@ -3260,7 +3260,7 @@
         <v>15</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.2</v>
+        <v>40</v>
       </c>
       <c r="AT11" t="n">
         <v>7.8</v>
@@ -3272,7 +3272,7 @@
         <v>10</v>
       </c>
       <c r="AW11" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AX11" t="n">
         <v>11.5</v>
@@ -3284,16 +3284,16 @@
         <v>16.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>7.2</v>
+        <v>42</v>
       </c>
       <c r="BB11" t="n">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="BC11" t="n">
         <v>6.6</v>
       </c>
       <c r="BD11" t="n">
-        <v>40</v>
+        <v>7.2</v>
       </c>
       <c r="BE11" t="n">
         <v>7.8</v>
@@ -3326,7 +3326,7 @@
         <v>5.7</v>
       </c>
       <c r="BO11" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="BP11" t="n">
         <v>23</v>
@@ -3344,7 +3344,7 @@
         <v>6.4</v>
       </c>
       <c r="BU11" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="BV11" t="n">
         <v>28</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-16 14:07:56</t>
+          <t>2026-07-16 16:29:12</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
         <v>7</v>
       </c>
       <c r="H12" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="I12" t="n">
         <v>1.63</v>
@@ -3427,13 +3427,13 @@
         <v>1.19</v>
       </c>
       <c r="P12" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q12" t="n">
         <v>1.58</v>
       </c>
       <c r="R12" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S12" t="n">
         <v>2.44</v>
@@ -3448,7 +3448,7 @@
         <v>2.58</v>
       </c>
       <c r="W12" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X12" t="n">
         <v>25</v>
@@ -3574,7 +3574,7 @@
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>3.15</v>
+        <v>10.5</v>
       </c>
       <c r="BN12" t="n">
         <v>10.5</v>
@@ -3598,7 +3598,7 @@
         <v>4.5</v>
       </c>
       <c r="BU12" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="BV12" t="n">
         <v>9.800000000000001</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-16 14:07:56</t>
+          <t>2026-07-16 16:29:12</t>
         </is>
       </c>
     </row>
@@ -3654,19 +3654,19 @@
         <v>1.31</v>
       </c>
       <c r="G13" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="H13" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="I13" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="J13" t="n">
         <v>6</v>
       </c>
       <c r="K13" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
@@ -3675,7 +3675,7 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="O13" t="n">
         <v>1.1</v>
@@ -3702,7 +3702,7 @@
         <v>1.1</v>
       </c>
       <c r="W13" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="X13" t="n">
         <v>60</v>
@@ -3720,10 +3720,10 @@
         <v>19.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AD13" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AE13" t="n">
         <v>120</v>
@@ -3753,22 +3753,22 @@
         <v>80</v>
       </c>
       <c r="AN13" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="AO13" t="n">
         <v>90</v>
       </c>
       <c r="AP13" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AQ13" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AR13" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AS13" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AT13" t="n">
         <v>13</v>
@@ -3777,10 +3777,10 @@
         <v>13</v>
       </c>
       <c r="AV13" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AW13" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AX13" t="n">
         <v>10.5</v>
@@ -3792,7 +3792,7 @@
         <v>17.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BB13" t="n">
         <v>11</v>
@@ -3804,13 +3804,13 @@
         <v>21</v>
       </c>
       <c r="BE13" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BF13" t="n">
         <v>3</v>
       </c>
       <c r="BG13" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BH13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-16 14:07:56</t>
+          <t>2026-07-16 16:29:12</t>
         </is>
       </c>
     </row>
@@ -3938,7 +3938,7 @@
         <v>1.92</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="R14" t="n">
         <v>1.33</v>
@@ -3950,7 +3950,7 @@
         <v>1.94</v>
       </c>
       <c r="U14" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="V14" t="n">
         <v>2.32</v>
@@ -3983,7 +3983,7 @@
         <v>23</v>
       </c>
       <c r="AF14" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AG14" t="n">
         <v>29</v>
@@ -4013,10 +4013,10 @@
         <v>13.5</v>
       </c>
       <c r="AP14" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AQ14" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AR14" t="n">
         <v>8.4</v>
@@ -4025,7 +4025,7 @@
         <v>12</v>
       </c>
       <c r="AT14" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AU14" t="n">
         <v>7.8</v>
@@ -4037,25 +4037,25 @@
         <v>13.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="AY14" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AZ14" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="BA14" t="n">
-        <v>3.95</v>
+        <v>29</v>
       </c>
       <c r="BB14" t="n">
         <v>4.2</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BE14" t="n">
         <v>4.2</v>
@@ -4064,7 +4064,7 @@
         <v>4.2</v>
       </c>
       <c r="BG14" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BH14" t="n">
         <v>3.45</v>
@@ -4088,7 +4088,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BO14" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
@@ -4106,7 +4106,7 @@
         <v>4.3</v>
       </c>
       <c r="BU14" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="BV14" t="n">
         <v>11.5</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-16 14:07:56</t>
+          <t>2026-07-16 16:29:12</t>
         </is>
       </c>
     </row>
@@ -4162,13 +4162,13 @@
         <v>1.96</v>
       </c>
       <c r="G15" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
         <v>4</v>
       </c>
       <c r="I15" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J15" t="n">
         <v>4</v>
@@ -4189,40 +4189,40 @@
         <v>1.23</v>
       </c>
       <c r="P15" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R15" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="S15" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="T15" t="n">
         <v>1.65</v>
       </c>
       <c r="U15" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="V15" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W15" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="X15" t="n">
         <v>20</v>
       </c>
       <c r="Y15" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Z15" t="n">
         <v>32</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB15" t="n">
         <v>12</v>
@@ -4285,7 +4285,7 @@
         <v>8.4</v>
       </c>
       <c r="AV15" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AW15" t="n">
         <v>38</v>
@@ -4297,7 +4297,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ15" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA15" t="n">
         <v>40</v>
@@ -4309,7 +4309,7 @@
         <v>16.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BE15" t="n">
         <v>60</v>
@@ -4318,7 +4318,7 @@
         <v>9.4</v>
       </c>
       <c r="BG15" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BH15" t="n">
         <v>4.2</v>
@@ -4336,7 +4336,7 @@
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN15" t="n">
         <v>5.2</v>
@@ -4345,7 +4345,7 @@
         <v>4.3</v>
       </c>
       <c r="BP15" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BQ15" t="n">
         <v>5.7</v>
@@ -4366,13 +4366,13 @@
         <v>32</v>
       </c>
       <c r="BW15" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BX15" t="n">
         <v>38</v>
       </c>
       <c r="BY15" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BZ15" t="n">
         <v>19</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-16 14:07:56</t>
+          <t>2026-07-16 16:29:12</t>
         </is>
       </c>
     </row>
@@ -4413,16 +4413,16 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="G16" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="H16" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I16" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J16" t="n">
         <v>4.1</v>
@@ -4431,7 +4431,7 @@
         <v>4.3</v>
       </c>
       <c r="L16" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="M16" t="n">
         <v>1.04</v>
@@ -4446,25 +4446,25 @@
         <v>2.32</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R16" t="n">
         <v>1.53</v>
       </c>
       <c r="S16" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="T16" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="U16" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="V16" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W16" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="X16" t="n">
         <v>21</v>
@@ -4473,25 +4473,25 @@
         <v>21</v>
       </c>
       <c r="Z16" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AB16" t="n">
         <v>11.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD16" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE16" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF16" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG16" t="n">
         <v>10.5</v>
@@ -4506,28 +4506,28 @@
         <v>21</v>
       </c>
       <c r="AK16" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AL16" t="n">
         <v>29</v>
       </c>
       <c r="AM16" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN16" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AO16" t="n">
-        <v>130</v>
+        <v>44</v>
       </c>
       <c r="AP16" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AQ16" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AR16" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AS16" t="n">
         <v>36</v>
@@ -4539,16 +4539,16 @@
         <v>8.4</v>
       </c>
       <c r="AV16" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AW16" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AX16" t="n">
         <v>11</v>
       </c>
       <c r="AY16" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ16" t="n">
         <v>15</v>
@@ -4572,13 +4572,13 @@
         <v>8.6</v>
       </c>
       <c r="BG16" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="BH16" t="n">
         <v>4.2</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="BJ16" t="n">
         <v>9.6</v>
@@ -4590,31 +4590,31 @@
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BN16" t="n">
         <v>5</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BP16" t="n">
         <v>13</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.7</v>
+        <v>9.4</v>
       </c>
       <c r="BR16" t="n">
         <v>24</v>
       </c>
       <c r="BS16" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BT16" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BU16" t="n">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="BV16" t="n">
         <v>34</v>
@@ -4626,17 +4626,17 @@
         <v>40</v>
       </c>
       <c r="BY16" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BZ16" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="CA16" t="n">
-        <v>6.4</v>
+        <v>13</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-16 14:07:56</t>
+          <t>2026-07-16 16:29:12</t>
         </is>
       </c>
     </row>
@@ -4673,10 +4673,10 @@
         <v>1.2</v>
       </c>
       <c r="H17" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="I17" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="J17" t="n">
         <v>9.199999999999999</v>
@@ -4697,19 +4697,19 @@
         <v>1.1</v>
       </c>
       <c r="P17" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Q17" t="n">
         <v>1.3</v>
       </c>
       <c r="R17" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="S17" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="T17" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U17" t="n">
         <v>2.04</v>
@@ -4721,10 +4721,10 @@
         <v>1.01</v>
       </c>
       <c r="X17" t="n">
-        <v>1000</v>
+        <v>940</v>
       </c>
       <c r="Y17" t="n">
-        <v>1000</v>
+        <v>940</v>
       </c>
       <c r="Z17" t="n">
         <v>1000</v>
@@ -4739,13 +4739,13 @@
         <v>23</v>
       </c>
       <c r="AD17" t="n">
-        <v>520</v>
+        <v>590</v>
       </c>
       <c r="AE17" t="n">
         <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG17" t="n">
         <v>13.5</v>
@@ -4769,13 +4769,13 @@
         <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="AO17" t="n">
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AQ17" t="n">
         <v>34</v>
@@ -4787,10 +4787,10 @@
         <v>60</v>
       </c>
       <c r="AT17" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AU17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AV17" t="n">
         <v>29</v>
@@ -4802,7 +4802,7 @@
         <v>10</v>
       </c>
       <c r="AY17" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ17" t="n">
         <v>22</v>
@@ -4817,80 +4817,80 @@
         <v>11.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BE17" t="n">
         <v>42</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="BG17" t="n">
         <v>46</v>
       </c>
       <c r="BH17" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BI17" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BJ17" t="n">
         <v>12.5</v>
       </c>
       <c r="BK17" t="n">
-        <v>7.2</v>
+        <v>9.6</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BN17" t="n">
         <v>4.2</v>
       </c>
       <c r="BO17" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BP17" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BQ17" t="n">
         <v>4.7</v>
       </c>
       <c r="BR17" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BS17" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BT17" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BU17" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BZ17" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="CA17" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-16 14:07:56</t>
+          <t>2026-07-16 16:29:12</t>
         </is>
       </c>
     </row>
@@ -4924,7 +4924,7 @@
         <v>2.78</v>
       </c>
       <c r="G18" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="H18" t="n">
         <v>2.58</v>
@@ -4933,16 +4933,16 @@
         <v>3.45</v>
       </c>
       <c r="J18" t="n">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="K18" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="L18" t="n">
         <v>1.6</v>
       </c>
       <c r="M18" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="N18" t="n">
         <v>2.16</v>
@@ -4960,7 +4960,7 @@
         <v>1.13</v>
       </c>
       <c r="S18" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="T18" t="n">
         <v>2.28</v>
@@ -4972,115 +4972,115 @@
         <v>1.41</v>
       </c>
       <c r="W18" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="X18" t="n">
         <v>7.8</v>
       </c>
       <c r="Y18" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z18" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AA18" t="n">
         <v>70</v>
       </c>
       <c r="AB18" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC18" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AE18" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AF18" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AG18" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AH18" t="n">
-        <v>34</v>
+        <v>950</v>
       </c>
       <c r="AI18" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ18" t="n">
         <v>80</v>
       </c>
       <c r="AK18" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AL18" t="n">
         <v>120</v>
       </c>
       <c r="AM18" t="n">
-        <v>320</v>
+        <v>1000</v>
       </c>
       <c r="AN18" t="n">
         <v>110</v>
       </c>
       <c r="AO18" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.01</v>
+        <v>2.8</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.01</v>
+        <v>2.8</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH18" t="n">
         <v>2.66</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-16 14:07:56</t>
+          <t>2026-07-16 16:29:12</t>
         </is>
       </c>
     </row>
@@ -5175,28 +5175,28 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="G19" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="H19" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="I19" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="J19" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="K19" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
       </c>
       <c r="M19" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="N19" t="n">
         <v>2.12</v>
@@ -5205,31 +5205,31 @@
         <v>1.69</v>
       </c>
       <c r="P19" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.58</v>
+        <v>2.84</v>
       </c>
       <c r="R19" t="n">
         <v>1.12</v>
       </c>
       <c r="S19" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="T19" t="n">
-        <v>2.36</v>
+        <v>2.18</v>
       </c>
       <c r="U19" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="V19" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="W19" t="n">
         <v>1.64</v>
       </c>
       <c r="X19" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Y19" t="n">
         <v>10.5</v>
@@ -5244,22 +5244,22 @@
         <v>6.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AE19" t="n">
         <v>120</v>
       </c>
       <c r="AF19" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AG19" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AI19" t="n">
         <v>170</v>
@@ -5268,73 +5268,73 @@
         <v>46</v>
       </c>
       <c r="AK19" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AL19" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AM19" t="n">
         <v>390</v>
       </c>
       <c r="AN19" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AO19" t="n">
         <v>210</v>
       </c>
       <c r="AP19" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AQ19" t="n">
         <v>3.55</v>
       </c>
-      <c r="AQ19" t="n">
-        <v>3.95</v>
-      </c>
       <c r="AR19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE19" t="n">
         <v>5.3</v>
       </c>
-      <c r="AS19" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AV19" t="n">
+      <c r="BF19" t="n">
         <v>4.9</v>
       </c>
-      <c r="AW19" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BG19" t="n">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="BH19" t="n">
         <v>1000</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-16 14:07:56</t>
+          <t>2026-07-16 16:29:12</t>
         </is>
       </c>
     </row>
@@ -5429,13 +5429,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="G20" t="n">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="H20" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="I20" t="n">
         <v>4.4</v>
@@ -5444,7 +5444,7 @@
         <v>2.54</v>
       </c>
       <c r="K20" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L20" t="n">
         <v>1.59</v>
@@ -5462,22 +5462,22 @@
         <v>1.38</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="R20" t="n">
         <v>1.13</v>
       </c>
       <c r="S20" t="n">
-        <v>3.45</v>
+        <v>5.1</v>
       </c>
       <c r="T20" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="U20" t="n">
         <v>1.59</v>
       </c>
       <c r="V20" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W20" t="n">
         <v>1.54</v>
@@ -5537,58 +5537,58 @@
         <v>140</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BH20" t="n">
         <v>2.7</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-16 14:07:56</t>
+          <t>2026-07-16 16:29:12</t>
         </is>
       </c>
     </row>
@@ -5689,13 +5689,13 @@
         <v>2.96</v>
       </c>
       <c r="H21" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="I21" t="n">
         <v>4.1</v>
       </c>
       <c r="J21" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="K21" t="n">
         <v>3.4</v>
@@ -5710,22 +5710,22 @@
         <v>2.38</v>
       </c>
       <c r="O21" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="P21" t="n">
         <v>1.52</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="R21" t="n">
         <v>1.18</v>
       </c>
       <c r="S21" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="T21" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="U21" t="n">
         <v>1.75</v>
@@ -5752,16 +5752,16 @@
         <v>9.4</v>
       </c>
       <c r="AC21" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AE21" t="n">
         <v>70</v>
       </c>
       <c r="AF21" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AG21" t="n">
         <v>15</v>
@@ -5791,58 +5791,58 @@
         <v>90</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH21" t="n">
         <v>3.2</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-16 14:07:56</t>
+          <t>2026-07-16 16:29:12</t>
         </is>
       </c>
     </row>
@@ -5940,16 +5940,16 @@
         <v>2.08</v>
       </c>
       <c r="G22" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H22" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="J22" t="n">
         <v>3.6</v>
-      </c>
-      <c r="I22" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J22" t="n">
-        <v>3.65</v>
       </c>
       <c r="K22" t="n">
         <v>4</v>
@@ -5976,7 +5976,7 @@
         <v>1.43</v>
       </c>
       <c r="S22" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="T22" t="n">
         <v>1.67</v>
@@ -5985,22 +5985,22 @@
         <v>2.24</v>
       </c>
       <c r="V22" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W22" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="X22" t="n">
         <v>18.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z22" t="n">
         <v>42</v>
       </c>
       <c r="AA22" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AB22" t="n">
         <v>11.5</v>
@@ -6009,25 +6009,25 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD22" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE22" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AF22" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AG22" t="n">
         <v>11.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI22" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ22" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="AK22" t="n">
         <v>22</v>
@@ -6036,7 +6036,7 @@
         <v>40</v>
       </c>
       <c r="AM22" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN22" t="n">
         <v>15.5</v>
@@ -6045,16 +6045,16 @@
         <v>48</v>
       </c>
       <c r="AP22" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AQ22" t="n">
         <v>13.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>22</v>
+        <v>6.8</v>
       </c>
       <c r="AS22" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AT22" t="n">
         <v>9.4</v>
@@ -6063,10 +6063,10 @@
         <v>7.6</v>
       </c>
       <c r="AV22" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>32</v>
+        <v>7.2</v>
       </c>
       <c r="AX22" t="n">
         <v>11.5</v>
@@ -6078,7 +6078,7 @@
         <v>14</v>
       </c>
       <c r="BA22" t="n">
-        <v>34</v>
+        <v>7.4</v>
       </c>
       <c r="BB22" t="n">
         <v>21</v>
@@ -6090,19 +6090,19 @@
         <v>24</v>
       </c>
       <c r="BE22" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BF22" t="n">
         <v>10.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="BH22" t="n">
         <v>3.9</v>
       </c>
       <c r="BI22" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="BJ22" t="n">
         <v>9.6</v>
@@ -6117,50 +6117,50 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BN22" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BO22" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="BP22" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BQ22" t="n">
+        <v>8</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BT22" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BU22" t="n">
         <v>6</v>
       </c>
-      <c r="BR22" t="n">
-        <v>27</v>
-      </c>
-      <c r="BS22" t="n">
+      <c r="BV22" t="n">
+        <v>29</v>
+      </c>
+      <c r="BW22" t="n">
         <v>7.4</v>
       </c>
-      <c r="BT22" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BU22" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BV22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW22" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BX22" t="n">
         <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BZ22" t="n">
         <v>22</v>
       </c>
       <c r="CA22" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-16 14:07:56</t>
+          <t>2026-07-16 16:29:12</t>
         </is>
       </c>
     </row>
@@ -6218,13 +6218,13 @@
         <v>3.2</v>
       </c>
       <c r="O23" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P23" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="R23" t="n">
         <v>1.29</v>
@@ -6308,7 +6308,7 @@
         <v>24</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AT23" t="n">
         <v>6.6</v>
@@ -6320,7 +6320,7 @@
         <v>16.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.05</v>
+        <v>6</v>
       </c>
       <c r="AX23" t="n">
         <v>8.800000000000001</v>
@@ -6332,7 +6332,7 @@
         <v>16.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BB23" t="n">
         <v>16</v>
@@ -6344,13 +6344,13 @@
         <v>24</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BF23" t="n">
         <v>11</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BH23" t="n">
         <v>1000</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-16 14:07:56</t>
+          <t>2026-07-16 16:29:12</t>
         </is>
       </c>
     </row>
@@ -6457,7 +6457,7 @@
         <v>85</v>
       </c>
       <c r="J24" t="n">
-        <v>4.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K24" t="n">
         <v>19</v>
@@ -6469,22 +6469,22 @@
         <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>3.45</v>
+        <v>6.6</v>
       </c>
       <c r="O24" t="n">
         <v>1.09</v>
       </c>
       <c r="P24" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="Q24" t="n">
         <v>1.28</v>
       </c>
       <c r="R24" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="S24" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="T24" t="n">
         <v>2.96</v>
@@ -6514,7 +6514,7 @@
         <v>15.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>50</v>
+        <v>950</v>
       </c>
       <c r="AD24" t="n">
         <v>950</v>
@@ -6547,64 +6547,64 @@
         <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AO24" t="n">
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="AT24" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="BD24" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="BH24" t="n">
         <v>1000</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-16 14:07:56</t>
+          <t>2026-07-16 16:29:12</t>
         </is>
       </c>
     </row>
@@ -6699,10 +6699,10 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G25" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="H25" t="n">
         <v>3.4</v>
@@ -6711,10 +6711,10 @@
         <v>3.85</v>
       </c>
       <c r="J25" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="K25" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L25" t="n">
         <v>1.48</v>
@@ -6723,7 +6723,7 @@
         <v>1.1</v>
       </c>
       <c r="N25" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O25" t="n">
         <v>1.4</v>
@@ -6732,7 +6732,7 @@
         <v>1.67</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R25" t="n">
         <v>1.25</v>
@@ -6741,10 +6741,10 @@
         <v>4.2</v>
       </c>
       <c r="T25" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="U25" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="V25" t="n">
         <v>1.35</v>
@@ -6756,31 +6756,31 @@
         <v>12.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z25" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AA25" t="n">
         <v>85</v>
       </c>
       <c r="AB25" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC25" t="n">
         <v>8.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE25" t="n">
         <v>60</v>
       </c>
       <c r="AF25" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AG25" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AH25" t="n">
         <v>23</v>
@@ -6816,7 +6816,7 @@
         <v>18.5</v>
       </c>
       <c r="AS25" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="AT25" t="n">
         <v>6.8</v>
@@ -6828,7 +6828,7 @@
         <v>11.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="AX25" t="n">
         <v>11</v>
@@ -6840,25 +6840,25 @@
         <v>15</v>
       </c>
       <c r="BA25" t="n">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="BB25" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="BC25" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="BD25" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="BE25" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="BF25" t="n">
         <v>20</v>
       </c>
       <c r="BG25" t="n">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="BH25" t="n">
         <v>3.05</v>
@@ -6870,34 +6870,34 @@
         <v>10.5</v>
       </c>
       <c r="BK25" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BN25" t="n">
         <v>5.1</v>
       </c>
       <c r="BO25" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BP25" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BQ25" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BR25" t="n">
         <v>38</v>
       </c>
       <c r="BS25" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BT25" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BU25" t="n">
         <v>5.3</v>
@@ -6906,13 +6906,13 @@
         <v>34</v>
       </c>
       <c r="BW25" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX25" t="n">
         <v>1000</v>
       </c>
       <c r="BY25" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ25" t="n">
         <v>0</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-16 14:07:56</t>
+          <t>2026-07-16 16:29:12</t>
         </is>
       </c>
     </row>
@@ -6992,7 +6992,7 @@
         <v>1.64</v>
       </c>
       <c r="S26" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="T26" t="n">
         <v>1.89</v>
@@ -7055,7 +7055,7 @@
         <v>150</v>
       </c>
       <c r="AN26" t="n">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="AO26" t="n">
         <v>190</v>
@@ -7064,13 +7064,13 @@
         <v>19.5</v>
       </c>
       <c r="AQ26" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="AR26" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AS26" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="AT26" t="n">
         <v>8</v>
@@ -7079,10 +7079,10 @@
         <v>10</v>
       </c>
       <c r="AV26" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="AW26" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AX26" t="n">
         <v>7</v>
@@ -7094,7 +7094,7 @@
         <v>18.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BB26" t="n">
         <v>8.4</v>
@@ -7103,16 +7103,16 @@
         <v>10</v>
       </c>
       <c r="BD26" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BE26" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BF26" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="BG26" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BH26" t="n">
         <v>4.6</v>
@@ -7124,7 +7124,7 @@
         <v>11.5</v>
       </c>
       <c r="BK26" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
@@ -7136,22 +7136,22 @@
         <v>4.1</v>
       </c>
       <c r="BO26" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="BP26" t="n">
         <v>7.8</v>
       </c>
       <c r="BQ26" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BR26" t="n">
         <v>21</v>
       </c>
       <c r="BS26" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT26" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BU26" t="n">
         <v>6.6</v>
@@ -7160,7 +7160,7 @@
         <v>1000</v>
       </c>
       <c r="BW26" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BX26" t="n">
         <v>1000</v>
@@ -7172,11 +7172,11 @@
         <v>11</v>
       </c>
       <c r="CA26" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-16 14:07:56</t>
+          <t>2026-07-16 16:29:12</t>
         </is>
       </c>
     </row>
@@ -7234,25 +7234,25 @@
         <v>5.2</v>
       </c>
       <c r="O27" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P27" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="R27" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="S27" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="T27" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="U27" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="V27" t="n">
         <v>1.03</v>
@@ -7264,7 +7264,7 @@
         <v>36</v>
       </c>
       <c r="Y27" t="n">
-        <v>75</v>
+        <v>950</v>
       </c>
       <c r="Z27" t="n">
         <v>370</v>
@@ -7279,7 +7279,7 @@
         <v>22</v>
       </c>
       <c r="AD27" t="n">
-        <v>120</v>
+        <v>950</v>
       </c>
       <c r="AE27" t="n">
         <v>1000</v>
@@ -7291,13 +7291,13 @@
         <v>14.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>75</v>
+        <v>950</v>
       </c>
       <c r="AI27" t="n">
         <v>540</v>
       </c>
       <c r="AJ27" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AK27" t="n">
         <v>17</v>
@@ -7306,7 +7306,7 @@
         <v>70</v>
       </c>
       <c r="AM27" t="n">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="AN27" t="n">
         <v>3.8</v>
@@ -7318,25 +7318,25 @@
         <v>21</v>
       </c>
       <c r="AQ27" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR27" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AS27" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT27" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AU27" t="n">
         <v>15.5</v>
       </c>
       <c r="AV27" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW27" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AX27" t="n">
         <v>5.9</v>
@@ -7345,10 +7345,10 @@
         <v>10.5</v>
       </c>
       <c r="AZ27" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BA27" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BB27" t="n">
         <v>6.4</v>
@@ -7357,34 +7357,34 @@
         <v>12</v>
       </c>
       <c r="BD27" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE27" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BF27" t="n">
         <v>3.25</v>
       </c>
       <c r="BG27" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BH27" t="n">
         <v>4.7</v>
       </c>
       <c r="BI27" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="BJ27" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BK27" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BL27" t="n">
         <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BN27" t="n">
         <v>3.55</v>
@@ -7402,25 +7402,25 @@
         <v>1000</v>
       </c>
       <c r="BS27" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BT27" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BU27" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BV27" t="n">
         <v>1000</v>
       </c>
       <c r="BW27" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BX27" t="n">
         <v>1000</v>
       </c>
       <c r="BY27" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ27" t="n">
         <v>9</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-16 14:07:56</t>
+          <t>2026-07-16 16:29:12</t>
         </is>
       </c>
     </row>
@@ -7467,7 +7467,7 @@
         <v>1.7</v>
       </c>
       <c r="H28" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="I28" t="n">
         <v>6.4</v>
@@ -7476,10 +7476,10 @@
         <v>4.1</v>
       </c>
       <c r="K28" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="L28" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M28" t="n">
         <v>1.06</v>
@@ -7491,13 +7491,13 @@
         <v>1.3</v>
       </c>
       <c r="P28" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R28" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="S28" t="n">
         <v>3.25</v>
@@ -7506,25 +7506,25 @@
         <v>1.9</v>
       </c>
       <c r="U28" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="V28" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W28" t="n">
         <v>2.42</v>
       </c>
       <c r="X28" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z28" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AA28" t="n">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="AB28" t="n">
         <v>8.4</v>
@@ -7533,10 +7533,10 @@
         <v>10.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE28" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AF28" t="n">
         <v>10.5</v>
@@ -7548,7 +7548,7 @@
         <v>24</v>
       </c>
       <c r="AI28" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ28" t="n">
         <v>21</v>
@@ -7560,16 +7560,16 @@
         <v>46</v>
       </c>
       <c r="AM28" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AN28" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AO28" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AP28" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ28" t="n">
         <v>16</v>
@@ -7578,7 +7578,7 @@
         <v>38</v>
       </c>
       <c r="AS28" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AT28" t="n">
         <v>7</v>
@@ -7590,7 +7590,7 @@
         <v>19.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AX28" t="n">
         <v>8.199999999999999</v>
@@ -7602,7 +7602,7 @@
         <v>19.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BB28" t="n">
         <v>13.5</v>
@@ -7614,13 +7614,13 @@
         <v>26</v>
       </c>
       <c r="BE28" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BF28" t="n">
         <v>8.6</v>
       </c>
       <c r="BG28" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BH28" t="n">
         <v>3.6</v>
@@ -7638,7 +7638,7 @@
         <v>1000</v>
       </c>
       <c r="BM28" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN28" t="n">
         <v>4.4</v>
@@ -7656,22 +7656,22 @@
         <v>28</v>
       </c>
       <c r="BS28" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT28" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BU28" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BV28" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BW28" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BX28" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BY28" t="n">
         <v>9</v>
@@ -7680,11 +7680,11 @@
         <v>22</v>
       </c>
       <c r="CA28" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-16 14:07:56</t>
+          <t>2026-07-16 16:29:12</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
         <v>1.87</v>
       </c>
       <c r="G29" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H29" t="n">
         <v>3.55</v>
@@ -7730,19 +7730,19 @@
         <v>4</v>
       </c>
       <c r="K29" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L29" t="n">
         <v>1.23</v>
       </c>
       <c r="M29" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N29" t="n">
         <v>5.7</v>
       </c>
       <c r="O29" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P29" t="n">
         <v>2.6</v>
@@ -7754,7 +7754,7 @@
         <v>1.65</v>
       </c>
       <c r="S29" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="T29" t="n">
         <v>1.51</v>
@@ -7763,10 +7763,10 @@
         <v>2.56</v>
       </c>
       <c r="V29" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W29" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="X29" t="n">
         <v>32</v>
@@ -7838,7 +7838,7 @@
         <v>11</v>
       </c>
       <c r="AU29" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV29" t="n">
         <v>12.5</v>
@@ -7850,7 +7850,7 @@
         <v>12</v>
       </c>
       <c r="AY29" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ29" t="n">
         <v>11.5</v>
@@ -7871,7 +7871,7 @@
         <v>5</v>
       </c>
       <c r="BF29" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BG29" t="n">
         <v>19</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-16 14:07:56</t>
+          <t>2026-07-16 16:29:12</t>
         </is>
       </c>
     </row>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-16 14:07:56</t>
+          <t>2026-07-16 16:29:12</t>
         </is>
       </c>
     </row>
@@ -8235,7 +8235,7 @@
         <v>1000</v>
       </c>
       <c r="J31" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="K31" t="n">
         <v>1000</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-16 14:07:56</t>
+          <t>2026-07-16 16:29:12</t>
         </is>
       </c>
     </row>
@@ -8483,7 +8483,7 @@
         <v>1000</v>
       </c>
       <c r="H32" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="I32" t="n">
         <v>1000</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-16 14:07:56</t>
+          <t>2026-07-16 16:29:12</t>
         </is>
       </c>
     </row>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-16 14:07:56</t>
+          <t>2026-07-16 16:29:12</t>
         </is>
       </c>
     </row>
@@ -8985,13 +8985,13 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="G34" t="n">
         <v>1000</v>
       </c>
       <c r="H34" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="I34" t="n">
         <v>1000</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-16 14:07:56</t>
+          <t>2026-07-16 16:29:12</t>
         </is>
       </c>
     </row>
@@ -9248,7 +9248,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="J35" t="n">
         <v>4.8</v>
@@ -9272,13 +9272,13 @@
         <v>2.12</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="R35" t="n">
         <v>1.44</v>
       </c>
       <c r="S35" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="T35" t="n">
         <v>2.02</v>
@@ -9347,7 +9347,7 @@
         <v>240</v>
       </c>
       <c r="AP35" t="n">
-        <v>14.5</v>
+        <v>4.1</v>
       </c>
       <c r="AQ35" t="n">
         <v>4.4</v>
@@ -9359,10 +9359,10 @@
         <v>5</v>
       </c>
       <c r="AT35" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU35" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV35" t="n">
         <v>4.5</v>
@@ -9383,7 +9383,7 @@
         <v>4.9</v>
       </c>
       <c r="BB35" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BC35" t="n">
         <v>12</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-16 14:07:56</t>
+          <t>2026-07-16 16:29:12</t>
         </is>
       </c>
     </row>
@@ -9502,13 +9502,13 @@
         <v>2.7</v>
       </c>
       <c r="I36" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="J36" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="K36" t="n">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="L36" t="n">
         <v>1.4</v>
@@ -9526,25 +9526,25 @@
         <v>1.68</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.16</v>
+        <v>1.86</v>
       </c>
       <c r="R36" t="n">
         <v>1.25</v>
       </c>
       <c r="S36" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="T36" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="U36" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="V36" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W36" t="n">
         <v>1.48</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.47</v>
       </c>
       <c r="X36" t="n">
         <v>11.5</v>
@@ -9556,7 +9556,7 @@
         <v>19.5</v>
       </c>
       <c r="AA36" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AB36" t="n">
         <v>10.5</v>
@@ -9568,7 +9568,7 @@
         <v>14</v>
       </c>
       <c r="AE36" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AF36" t="n">
         <v>19.5</v>
@@ -9580,79 +9580,79 @@
         <v>20</v>
       </c>
       <c r="AI36" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AJ36" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AK36" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AL36" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AM36" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN36" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AO36" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AS36" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AT36" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AU36" t="n">
         <v>4.9</v>
       </c>
       <c r="AV36" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.05</v>
+        <v>6.8</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.05</v>
+        <v>6.8</v>
       </c>
       <c r="BD36" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.05</v>
+        <v>7</v>
       </c>
       <c r="BG36" t="n">
-        <v>1.05</v>
+        <v>7</v>
       </c>
       <c r="BH36" t="n">
         <v>3.5</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-16 14:07:56</t>
+          <t>2026-07-16 16:29:12</t>
         </is>
       </c>
     </row>
@@ -9756,7 +9756,7 @@
         <v>4.4</v>
       </c>
       <c r="I37" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J37" t="n">
         <v>2.9</v>
@@ -9765,13 +9765,13 @@
         <v>3.15</v>
       </c>
       <c r="L37" t="n">
-        <v>1.68</v>
+        <v>1.56</v>
       </c>
       <c r="M37" t="n">
         <v>1.16</v>
       </c>
       <c r="N37" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="O37" t="n">
         <v>1.69</v>
@@ -9831,7 +9831,7 @@
         <v>15.5</v>
       </c>
       <c r="AH37" t="n">
-        <v>36</v>
+        <v>950</v>
       </c>
       <c r="AI37" t="n">
         <v>170</v>
@@ -9861,10 +9861,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AR37" t="n">
-        <v>25</v>
+        <v>4.8</v>
       </c>
       <c r="AS37" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AT37" t="n">
         <v>5.4</v>
@@ -9873,10 +9873,10 @@
         <v>6.4</v>
       </c>
       <c r="AV37" t="n">
-        <v>19</v>
+        <v>5.1</v>
       </c>
       <c r="AW37" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AX37" t="n">
         <v>10</v>
@@ -9888,25 +9888,25 @@
         <v>4.7</v>
       </c>
       <c r="BA37" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BB37" t="n">
-        <v>5.1</v>
+        <v>27</v>
       </c>
       <c r="BC37" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BD37" t="n">
         <v>5.2</v>
       </c>
       <c r="BE37" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BF37" t="n">
         <v>28</v>
       </c>
       <c r="BG37" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BH37" t="n">
         <v>2.46</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-16 14:07:56</t>
+          <t>2026-07-16 16:29:12</t>
         </is>
       </c>
     </row>
@@ -10013,13 +10013,13 @@
         <v>4.7</v>
       </c>
       <c r="J38" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K38" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L38" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="M38" t="n">
         <v>1.1</v>
@@ -10049,7 +10049,7 @@
         <v>1.92</v>
       </c>
       <c r="V38" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W38" t="n">
         <v>1.86</v>
@@ -10064,7 +10064,7 @@
         <v>32</v>
       </c>
       <c r="AA38" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB38" t="n">
         <v>8</v>
@@ -10142,7 +10142,7 @@
         <v>17.5</v>
       </c>
       <c r="BA38" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB38" t="n">
         <v>21</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-16 14:07:56</t>
+          <t>2026-07-16 16:29:12</t>
         </is>
       </c>
     </row>
@@ -10288,7 +10288,7 @@
         <v>1.64</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="R39" t="n">
         <v>1.23</v>
@@ -10315,37 +10315,37 @@
         <v>12.5</v>
       </c>
       <c r="Z39" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AA39" t="n">
         <v>75</v>
       </c>
       <c r="AB39" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC39" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD39" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE39" t="n">
         <v>55</v>
       </c>
       <c r="AF39" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AG39" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AH39" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AI39" t="n">
         <v>75</v>
       </c>
       <c r="AJ39" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AK39" t="n">
         <v>42</v>
@@ -10363,58 +10363,58 @@
         <v>65</v>
       </c>
       <c r="AP39" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ39" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR39" t="n">
         <v>15</v>
       </c>
       <c r="AS39" t="n">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="AT39" t="n">
         <v>7.4</v>
       </c>
       <c r="AU39" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV39" t="n">
         <v>10</v>
       </c>
       <c r="AW39" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="AX39" t="n">
         <v>11.5</v>
       </c>
       <c r="AY39" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AZ39" t="n">
         <v>17.5</v>
       </c>
       <c r="BA39" t="n">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="BB39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BC39" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="BD39" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="BE39" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="BF39" t="n">
-        <v>3.95</v>
+        <v>5</v>
       </c>
       <c r="BG39" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="BH39" t="n">
         <v>3</v>
@@ -10432,7 +10432,7 @@
         <v>1000</v>
       </c>
       <c r="BM39" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN39" t="n">
         <v>5.6</v>
@@ -10441,7 +10441,7 @@
         <v>4.1</v>
       </c>
       <c r="BP39" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BQ39" t="n">
         <v>7.4</v>
@@ -10450,7 +10450,7 @@
         <v>42</v>
       </c>
       <c r="BS39" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT39" t="n">
         <v>6.4</v>
@@ -10468,17 +10468,17 @@
         <v>48</v>
       </c>
       <c r="BY39" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BZ39" t="n">
         <v>42</v>
       </c>
       <c r="CA39" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-16 14:07:56</t>
+          <t>2026-07-16 16:29:12</t>
         </is>
       </c>
     </row>
@@ -10518,7 +10518,7 @@
         <v>6</v>
       </c>
       <c r="I40" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J40" t="n">
         <v>4</v>
@@ -10527,7 +10527,7 @@
         <v>4.4</v>
       </c>
       <c r="L40" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="M40" t="n">
         <v>1.07</v>
@@ -10578,7 +10578,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AC40" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AD40" t="n">
         <v>28</v>
@@ -10590,7 +10590,7 @@
         <v>11.5</v>
       </c>
       <c r="AG40" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AH40" t="n">
         <v>26</v>
@@ -10611,7 +10611,7 @@
         <v>160</v>
       </c>
       <c r="AN40" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AO40" t="n">
         <v>150</v>
@@ -10623,34 +10623,34 @@
         <v>16.5</v>
       </c>
       <c r="AR40" t="n">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="AS40" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="AT40" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AU40" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV40" t="n">
         <v>21</v>
       </c>
       <c r="AW40" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="AX40" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AY40" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ40" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="BA40" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="BB40" t="n">
         <v>12.5</v>
@@ -10659,16 +10659,16 @@
         <v>14</v>
       </c>
       <c r="BD40" t="n">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="BE40" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="BF40" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG40" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="BH40" t="n">
         <v>3.45</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-16 14:07:56</t>
+          <t>2026-07-16 16:29:12</t>
         </is>
       </c>
     </row>
@@ -10769,7 +10769,7 @@
         <v>1.49</v>
       </c>
       <c r="H41" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="I41" t="n">
         <v>7.8</v>
@@ -10778,7 +10778,7 @@
         <v>5.1</v>
       </c>
       <c r="K41" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L41" t="n">
         <v>1.3</v>
@@ -10796,13 +10796,13 @@
         <v>2.46</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="R41" t="n">
         <v>1.58</v>
       </c>
       <c r="S41" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="T41" t="n">
         <v>1.84</v>
@@ -10814,7 +10814,7 @@
         <v>1.14</v>
       </c>
       <c r="W41" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="X41" t="n">
         <v>24</v>
@@ -10835,10 +10835,10 @@
         <v>12</v>
       </c>
       <c r="AD41" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE41" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AF41" t="n">
         <v>10</v>
@@ -10892,7 +10892,7 @@
         <v>24</v>
       </c>
       <c r="AW41" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AX41" t="n">
         <v>9.199999999999999</v>
@@ -10922,61 +10922,61 @@
         <v>5.3</v>
       </c>
       <c r="BG41" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="BH41" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BI41" t="n">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="BJ41" t="n">
         <v>10.5</v>
       </c>
       <c r="BK41" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BL41" t="n">
         <v>1000</v>
       </c>
       <c r="BM41" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="BN41" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BO41" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="BP41" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BQ41" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BR41" t="n">
         <v>22</v>
       </c>
       <c r="BS41" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BT41" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BU41" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BV41" t="n">
         <v>1000</v>
       </c>
       <c r="BW41" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BX41" t="n">
         <v>60</v>
       </c>
       <c r="BY41" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BZ41" t="n">
         <v>13</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-16 14:07:56</t>
+          <t>2026-07-16 16:29:12</t>
         </is>
       </c>
     </row>
@@ -11035,7 +11035,7 @@
         <v>3.55</v>
       </c>
       <c r="L42" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="M42" t="n">
         <v>1.09</v>
@@ -11056,22 +11056,22 @@
         <v>1.3</v>
       </c>
       <c r="S42" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="T42" t="n">
         <v>1.92</v>
       </c>
       <c r="U42" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="V42" t="n">
         <v>1.3</v>
       </c>
       <c r="W42" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="X42" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y42" t="n">
         <v>14</v>
@@ -11134,10 +11134,10 @@
         <v>26</v>
       </c>
       <c r="AS42" t="n">
-        <v>75</v>
+        <v>12.5</v>
       </c>
       <c r="AT42" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AU42" t="n">
         <v>7.2</v>
@@ -11152,7 +11152,7 @@
         <v>10.5</v>
       </c>
       <c r="AY42" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ42" t="n">
         <v>17.5</v>
@@ -11170,7 +11170,7 @@
         <v>36</v>
       </c>
       <c r="BE42" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BF42" t="n">
         <v>16</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-16 14:07:56</t>
+          <t>2026-07-16 16:29:12</t>
         </is>
       </c>
     </row>
@@ -11271,7 +11271,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="G43" t="n">
         <v>2.06</v>
@@ -11283,10 +11283,10 @@
         <v>4.6</v>
       </c>
       <c r="J43" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K43" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L43" t="n">
         <v>1.44</v>
@@ -11310,7 +11310,7 @@
         <v>1.31</v>
       </c>
       <c r="S43" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T43" t="n">
         <v>1.9</v>
@@ -11382,10 +11382,10 @@
         <v>10.5</v>
       </c>
       <c r="AQ43" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR43" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AS43" t="n">
         <v>10</v>
@@ -11424,7 +11424,7 @@
         <v>30</v>
       </c>
       <c r="BE43" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF43" t="n">
         <v>14.5</v>
@@ -11448,7 +11448,7 @@
         <v>1000</v>
       </c>
       <c r="BM43" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BN43" t="n">
         <v>4.8</v>
@@ -11460,7 +11460,7 @@
         <v>15.5</v>
       </c>
       <c r="BQ43" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR43" t="n">
         <v>34</v>
@@ -11478,7 +11478,7 @@
         <v>1000</v>
       </c>
       <c r="BW43" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX43" t="n">
         <v>1000</v>
@@ -11487,14 +11487,14 @@
         <v>8.6</v>
       </c>
       <c r="BZ43" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="CA43" t="n">
         <v>7.6</v>
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-16 14:07:56</t>
+          <t>2026-07-16 16:29:12</t>
         </is>
       </c>
     </row>
@@ -11525,22 +11525,22 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.04</v>
+        <v>1.87</v>
       </c>
       <c r="G44" t="n">
-        <v>1000</v>
+        <v>2.08</v>
       </c>
       <c r="H44" t="n">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="I44" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="J44" t="n">
-        <v>1.02</v>
+        <v>3.6</v>
       </c>
       <c r="K44" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="L44" t="n">
         <v>1.01</v>
@@ -11549,22 +11549,22 @@
         <v>1.01</v>
       </c>
       <c r="N44" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="O44" t="n">
         <v>1.25</v>
       </c>
-      <c r="O44" t="n">
-        <v>1.24</v>
-      </c>
       <c r="P44" t="n">
-        <v>1.25</v>
+        <v>1.86</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.24</v>
+        <v>1.52</v>
       </c>
       <c r="R44" t="n">
         <v>1.07</v>
       </c>
       <c r="S44" t="n">
-        <v>2.58</v>
+        <v>1.93</v>
       </c>
       <c r="T44" t="n">
         <v>1.11</v>
@@ -11573,10 +11573,10 @@
         <v>1.11</v>
       </c>
       <c r="V44" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="W44" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="X44" t="n">
         <v>1000</v>
@@ -11633,52 +11633,52 @@
         <v>1000</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR44" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS44" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT44" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU44" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV44" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW44" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX44" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY44" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ44" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA44" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB44" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC44" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD44" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE44" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF44" t="n">
         <v>1.01</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-16 14:07:56</t>
+          <t>2026-07-16 16:29:12</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11779,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="G45" t="n">
         <v>2.76</v>
@@ -11866,7 +11866,7 @@
         <v>18.5</v>
       </c>
       <c r="AI45" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AJ45" t="n">
         <v>44</v>
@@ -11890,37 +11890,37 @@
         <v>13.5</v>
       </c>
       <c r="AQ45" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AR45" t="n">
         <v>15.5</v>
       </c>
       <c r="AS45" t="n">
-        <v>30</v>
+        <v>1.03</v>
       </c>
       <c r="AT45" t="n">
         <v>10</v>
       </c>
       <c r="AU45" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV45" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW45" t="n">
         <v>21</v>
       </c>
       <c r="AX45" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AY45" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AZ45" t="n">
         <v>12</v>
       </c>
       <c r="BA45" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="BB45" t="n">
         <v>1.03</v>
@@ -11929,10 +11929,10 @@
         <v>20</v>
       </c>
       <c r="BD45" t="n">
-        <v>28</v>
+        <v>1.05</v>
       </c>
       <c r="BE45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF45" t="n">
         <v>15</v>
@@ -11944,7 +11944,7 @@
         <v>3.85</v>
       </c>
       <c r="BI45" t="n">
-        <v>2.96</v>
+        <v>3.35</v>
       </c>
       <c r="BJ45" t="n">
         <v>9.199999999999999</v>
@@ -11980,7 +11980,7 @@
         <v>6.2</v>
       </c>
       <c r="BU45" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="BV45" t="n">
         <v>21</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-07-16 14:07:56</t>
+          <t>2026-07-16 16:29:12</t>
         </is>
       </c>
     </row>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-07-16 14:07:56</t>
+          <t>2026-07-16 16:29:12</t>
         </is>
       </c>
     </row>
@@ -12287,19 +12287,19 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="G47" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="H47" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="I47" t="n">
         <v>4.1</v>
       </c>
       <c r="J47" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K47" t="n">
         <v>3.35</v>
@@ -12311,13 +12311,13 @@
         <v>1.11</v>
       </c>
       <c r="N47" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="O47" t="n">
         <v>1.49</v>
       </c>
       <c r="P47" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="Q47" t="n">
         <v>2.46</v>
@@ -12326,34 +12326,34 @@
         <v>1.22</v>
       </c>
       <c r="S47" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="T47" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U47" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="V47" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W47" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="X47" t="n">
         <v>11.5</v>
       </c>
       <c r="Y47" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z47" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AA47" t="n">
         <v>100</v>
       </c>
       <c r="AB47" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AC47" t="n">
         <v>7.6</v>
@@ -12362,7 +12362,7 @@
         <v>17</v>
       </c>
       <c r="AE47" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AF47" t="n">
         <v>13</v>
@@ -12377,25 +12377,25 @@
         <v>90</v>
       </c>
       <c r="AJ47" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AK47" t="n">
         <v>46</v>
       </c>
       <c r="AL47" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM47" t="n">
         <v>200</v>
       </c>
       <c r="AN47" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO47" t="n">
         <v>90</v>
       </c>
       <c r="AP47" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AQ47" t="n">
         <v>9.800000000000001</v>
@@ -12407,7 +12407,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AT47" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AU47" t="n">
         <v>6.6</v>
@@ -12416,10 +12416,10 @@
         <v>14.5</v>
       </c>
       <c r="AW47" t="n">
-        <v>32</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX47" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AY47" t="n">
         <v>10.5</v>
@@ -12431,10 +12431,10 @@
         <v>9</v>
       </c>
       <c r="BB47" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="BC47" t="n">
-        <v>24</v>
+        <v>7.6</v>
       </c>
       <c r="BD47" t="n">
         <v>40</v>
@@ -12446,71 +12446,71 @@
         <v>20</v>
       </c>
       <c r="BG47" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH47" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="BI47" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="BJ47" t="n">
         <v>11</v>
       </c>
       <c r="BK47" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BL47" t="n">
         <v>1000</v>
       </c>
       <c r="BM47" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BN47" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BO47" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="BP47" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BQ47" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BR47" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS47" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BT47" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BU47" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BV47" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BW47" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BX47" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BY47" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BZ47" t="n">
         <v>1000</v>
       </c>
       <c r="CA47" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-07-16 14:07:56</t>
+          <t>2026-07-16 16:29:12</t>
         </is>
       </c>
     </row>
@@ -12571,7 +12571,7 @@
         <v>1.64</v>
       </c>
       <c r="P48" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Q48" t="n">
         <v>2.92</v>
@@ -12583,10 +12583,10 @@
         <v>6.4</v>
       </c>
       <c r="T48" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="U48" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="V48" t="n">
         <v>1.45</v>
@@ -12601,13 +12601,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="Z48" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AA48" t="n">
         <v>75</v>
       </c>
       <c r="AB48" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC48" t="n">
         <v>7.4</v>
@@ -12628,13 +12628,13 @@
         <v>32</v>
       </c>
       <c r="AI48" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ48" t="n">
         <v>65</v>
       </c>
       <c r="AK48" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AL48" t="n">
         <v>110</v>
@@ -12646,10 +12646,10 @@
         <v>80</v>
       </c>
       <c r="AO48" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AP48" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AQ48" t="n">
         <v>6.6</v>
@@ -12658,7 +12658,7 @@
         <v>13</v>
       </c>
       <c r="AS48" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AT48" t="n">
         <v>6.8</v>
@@ -12670,7 +12670,7 @@
         <v>10.5</v>
       </c>
       <c r="AW48" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="AX48" t="n">
         <v>13.5</v>
@@ -12682,25 +12682,25 @@
         <v>18.5</v>
       </c>
       <c r="BA48" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BB48" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BC48" t="n">
         <v>38</v>
       </c>
       <c r="BD48" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BE48" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BF48" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BG48" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BH48" t="n">
         <v>1000</v>
@@ -12724,7 +12724,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BO48" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BP48" t="n">
         <v>46</v>
@@ -12742,7 +12742,7 @@
         <v>8</v>
       </c>
       <c r="BU48" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BV48" t="n">
         <v>44</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-07-16 14:07:56</t>
+          <t>2026-07-16 16:29:12</t>
         </is>
       </c>
     </row>
@@ -12795,7 +12795,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="G49" t="n">
         <v>1.5</v>
@@ -12834,7 +12834,7 @@
         <v>1.49</v>
       </c>
       <c r="S49" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="T49" t="n">
         <v>1.91</v>
@@ -12867,7 +12867,7 @@
         <v>11</v>
       </c>
       <c r="AD49" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="AE49" t="n">
         <v>1000</v>
@@ -12915,7 +12915,7 @@
         <v>48</v>
       </c>
       <c r="AT49" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU49" t="n">
         <v>10</v>
@@ -12945,7 +12945,7 @@
         <v>13.5</v>
       </c>
       <c r="BD49" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="BE49" t="n">
         <v>42</v>
@@ -12978,13 +12978,13 @@
         <v>4.2</v>
       </c>
       <c r="BO49" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="BP49" t="n">
         <v>9.6</v>
       </c>
       <c r="BQ49" t="n">
-        <v>7.2</v>
+        <v>4.9</v>
       </c>
       <c r="BR49" t="n">
         <v>25</v>
@@ -12996,7 +12996,7 @@
         <v>11.5</v>
       </c>
       <c r="BU49" t="n">
-        <v>8.6</v>
+        <v>5.3</v>
       </c>
       <c r="BV49" t="n">
         <v>1000</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-07-16 14:07:56</t>
+          <t>2026-07-16 16:29:12</t>
         </is>
       </c>
     </row>
@@ -13049,13 +13049,13 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="G50" t="n">
         <v>4.5</v>
       </c>
       <c r="H50" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="I50" t="n">
         <v>1.99</v>
@@ -13079,7 +13079,7 @@
         <v>1.26</v>
       </c>
       <c r="P50" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q50" t="n">
         <v>1.76</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-07-16 14:07:56</t>
+          <t>2026-07-16 16:29:12</t>
         </is>
       </c>
     </row>
@@ -13306,16 +13306,16 @@
         <v>1.95</v>
       </c>
       <c r="G51" t="n">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="H51" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="I51" t="n">
         <v>4.4</v>
       </c>
       <c r="J51" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K51" t="n">
         <v>3.9</v>
@@ -13354,7 +13354,7 @@
         <v>1.29</v>
       </c>
       <c r="W51" t="n">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="X51" t="n">
         <v>17</v>
@@ -13402,7 +13402,7 @@
         <v>38</v>
       </c>
       <c r="AM51" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN51" t="n">
         <v>13.5</v>
@@ -13417,10 +13417,10 @@
         <v>13.5</v>
       </c>
       <c r="AR51" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AS51" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT51" t="n">
         <v>9.4</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-07-16 14:07:56</t>
+          <t>2026-07-16 16:29:12</t>
         </is>
       </c>
     </row>
@@ -13557,7 +13557,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="G52" t="n">
         <v>2.2</v>
@@ -13590,7 +13590,7 @@
         <v>2</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="R52" t="n">
         <v>1.38</v>
@@ -13722,13 +13722,13 @@
         <v>3.7</v>
       </c>
       <c r="BI52" t="n">
-        <v>3.15</v>
+        <v>2.86</v>
       </c>
       <c r="BJ52" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BK52" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="BL52" t="n">
         <v>1000</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-07-16 14:07:56</t>
+          <t>2026-07-16 16:29:12</t>
         </is>
       </c>
     </row>
@@ -13817,7 +13817,7 @@
         <v>3.1</v>
       </c>
       <c r="H53" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="I53" t="n">
         <v>2.4</v>
@@ -13835,19 +13835,19 @@
         <v>1.04</v>
       </c>
       <c r="N53" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="O53" t="n">
         <v>1.19</v>
       </c>
       <c r="P53" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="Q53" t="n">
         <v>1.59</v>
       </c>
       <c r="R53" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="S53" t="n">
         <v>2.48</v>
@@ -13868,10 +13868,10 @@
         <v>27</v>
       </c>
       <c r="Y53" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Z53" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AA53" t="n">
         <v>34</v>
@@ -13880,7 +13880,7 @@
         <v>20</v>
       </c>
       <c r="AC53" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AD53" t="n">
         <v>12.5</v>
@@ -13895,7 +13895,7 @@
         <v>15</v>
       </c>
       <c r="AH53" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI53" t="n">
         <v>32</v>
@@ -13913,7 +13913,7 @@
         <v>65</v>
       </c>
       <c r="AN53" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO53" t="n">
         <v>13</v>
@@ -13943,28 +13943,28 @@
         <v>18.5</v>
       </c>
       <c r="AX53" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AY53" t="n">
         <v>12.5</v>
       </c>
       <c r="AZ53" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BA53" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BB53" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC53" t="n">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="BD53" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="BE53" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BF53" t="n">
         <v>16.5</v>
@@ -13985,7 +13985,7 @@
         <v>1.04</v>
       </c>
       <c r="BL53" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="BM53" t="n">
         <v>1.04</v>
@@ -14003,7 +14003,7 @@
         <v>1.04</v>
       </c>
       <c r="BR53" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BS53" t="n">
         <v>1.04</v>
@@ -14015,13 +14015,13 @@
         <v>4.5</v>
       </c>
       <c r="BV53" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BW53" t="n">
         <v>1.04</v>
       </c>
       <c r="BX53" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BY53" t="n">
         <v>1.04</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-07-16 14:07:56</t>
+          <t>2026-07-16 16:29:12</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-17.xlsx
@@ -860,10 +860,10 @@
         <v>3.75</v>
       </c>
       <c r="G2" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="H2" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="I2" t="n">
         <v>2.16</v>
@@ -872,7 +872,7 @@
         <v>3.6</v>
       </c>
       <c r="K2" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L2" t="n">
         <v>1.42</v>
@@ -881,22 +881,22 @@
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="O2" t="n">
         <v>1.33</v>
       </c>
       <c r="P2" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T2" t="n">
         <v>1.78</v>
@@ -914,28 +914,28 @@
         <v>17</v>
       </c>
       <c r="Y2" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="Z2" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AA2" t="n">
         <v>30</v>
       </c>
       <c r="AB2" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC2" t="n">
         <v>9.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AF2" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AG2" t="n">
         <v>18.5</v>
@@ -953,10 +953,10 @@
         <v>55</v>
       </c>
       <c r="AL2" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AM2" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AN2" t="n">
         <v>55</v>
@@ -968,7 +968,7 @@
         <v>13</v>
       </c>
       <c r="AQ2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AR2" t="n">
         <v>11.5</v>
@@ -983,37 +983,37 @@
         <v>7.2</v>
       </c>
       <c r="AV2" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW2" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AX2" t="n">
         <v>24</v>
       </c>
       <c r="AY2" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA2" t="n">
         <v>30</v>
       </c>
       <c r="BB2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BE2" t="n">
         <v>70</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BG2" t="n">
         <v>14.5</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -1141,13 +1141,13 @@
         <v>1.29</v>
       </c>
       <c r="P3" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
         <v>1.87</v>
       </c>
       <c r="R3" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S3" t="n">
         <v>3.2</v>
@@ -1195,13 +1195,13 @@
         <v>13</v>
       </c>
       <c r="AH3" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AI3" t="n">
         <v>55</v>
       </c>
       <c r="AJ3" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK3" t="n">
         <v>27</v>
@@ -1213,7 +1213,7 @@
         <v>110</v>
       </c>
       <c r="AN3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO3" t="n">
         <v>55</v>
@@ -1228,7 +1228,7 @@
         <v>20</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AT3" t="n">
         <v>8.800000000000001</v>
@@ -1240,7 +1240,7 @@
         <v>11.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="AX3" t="n">
         <v>10</v>
@@ -1252,7 +1252,7 @@
         <v>12</v>
       </c>
       <c r="BA3" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="BB3" t="n">
         <v>19</v>
@@ -1261,16 +1261,16 @@
         <v>16</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.9</v>
+        <v>18</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BF3" t="n">
         <v>11</v>
       </c>
       <c r="BG3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="BH3" t="n">
         <v>3.55</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -1365,70 +1365,70 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="G4" t="n">
         <v>4.6</v>
       </c>
       <c r="H4" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="I4" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="J4" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K4" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="O4" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="P4" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="R4" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="S4" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="T4" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="U4" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="V4" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="W4" t="n">
         <v>1.28</v>
       </c>
       <c r="X4" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="Y4" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AB4" t="n">
         <v>18.5</v>
@@ -1440,43 +1440,43 @@
         <v>12</v>
       </c>
       <c r="AE4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF4" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AG4" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AJ4" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AK4" t="n">
-        <v>55</v>
+        <v>320</v>
       </c>
       <c r="AL4" t="n">
+        <v>320</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN4" t="n">
         <v>60</v>
       </c>
-      <c r="AM4" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>65</v>
-      </c>
       <c r="AO4" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AP4" t="n">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="AQ4" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AR4" t="n">
         <v>9.800000000000001</v>
@@ -1485,19 +1485,19 @@
         <v>17.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AU4" t="n">
         <v>7.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AW4" t="n">
         <v>15</v>
       </c>
       <c r="AX4" t="n">
-        <v>4.6</v>
+        <v>13</v>
       </c>
       <c r="AY4" t="n">
         <v>13</v>
@@ -1506,43 +1506,43 @@
         <v>13.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.6</v>
+        <v>20</v>
       </c>
       <c r="BB4" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BE4" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.9</v>
+        <v>10.5</v>
       </c>
       <c r="BG4" t="n">
         <v>10</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="BJ4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK4" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN4" t="n">
         <v>7.8</v>
@@ -1554,41 +1554,41 @@
         <v>36</v>
       </c>
       <c r="BQ4" t="n">
+        <v>10</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>44</v>
+      </c>
+      <c r="BS4" t="n">
         <v>10.5</v>
       </c>
-      <c r="BR4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BT4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BU4" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BV4" t="n">
         <v>14</v>
       </c>
       <c r="BW4" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BX4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BY4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="CA4" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -1625,10 +1625,10 @@
         <v>4.8</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="I5" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="J5" t="n">
         <v>4.1</v>
@@ -1649,31 +1649,31 @@
         <v>1.21</v>
       </c>
       <c r="P5" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="R5" t="n">
         <v>1.58</v>
       </c>
       <c r="S5" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="T5" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="U5" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="V5" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="W5" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X5" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="Y5" t="n">
         <v>12.5</v>
@@ -1682,22 +1682,22 @@
         <v>13.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AC5" t="n">
         <v>10</v>
       </c>
       <c r="AD5" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AE5" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AG5" t="n">
         <v>18.5</v>
@@ -1706,28 +1706,28 @@
         <v>17</v>
       </c>
       <c r="AI5" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>490</v>
       </c>
       <c r="AK5" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AL5" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN5" t="n">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AO5" t="n">
         <v>8.6</v>
       </c>
       <c r="AP5" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AQ5" t="n">
         <v>11</v>
@@ -1736,7 +1736,7 @@
         <v>11.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AT5" t="n">
         <v>18.5</v>
@@ -1745,13 +1745,13 @@
         <v>9</v>
       </c>
       <c r="AV5" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW5" t="n">
         <v>14.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AY5" t="n">
         <v>15.5</v>
@@ -1760,13 +1760,13 @@
         <v>14</v>
       </c>
       <c r="BA5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BB5" t="n">
         <v>36</v>
       </c>
       <c r="BC5" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BD5" t="n">
         <v>38</v>
@@ -1775,7 +1775,7 @@
         <v>32</v>
       </c>
       <c r="BF5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BG5" t="n">
         <v>7.6</v>
@@ -1784,7 +1784,7 @@
         <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="BJ5" t="n">
         <v>12.5</v>
@@ -1805,7 +1805,7 @@
         <v>5.4</v>
       </c>
       <c r="BP5" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BQ5" t="n">
         <v>1.95</v>
@@ -1838,11 +1838,11 @@
         <v>22</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1891,7 @@
         <v>3.55</v>
       </c>
       <c r="L6" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="M6" t="n">
         <v>1.1</v>
@@ -1906,7 +1906,7 @@
         <v>1.63</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R6" t="n">
         <v>1.23</v>
@@ -1942,7 +1942,7 @@
         <v>16</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD6" t="n">
         <v>13.5</v>
@@ -1963,19 +1963,19 @@
         <v>60</v>
       </c>
       <c r="AJ6" t="n">
-        <v>140</v>
+        <v>500</v>
       </c>
       <c r="AK6" t="n">
         <v>85</v>
       </c>
       <c r="AL6" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AM6" t="n">
-        <v>190</v>
+        <v>500</v>
       </c>
       <c r="AN6" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AO6" t="n">
         <v>26</v>
@@ -1984,7 +1984,7 @@
         <v>7.6</v>
       </c>
       <c r="AQ6" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AR6" t="n">
         <v>8.6</v>
@@ -2005,7 +2005,7 @@
         <v>18.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="AY6" t="n">
         <v>13.5</v>
@@ -2014,22 +2014,22 @@
         <v>16</v>
       </c>
       <c r="BA6" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BG6" t="n">
         <v>15.5</v>
@@ -2038,19 +2038,19 @@
         <v>3.05</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.64</v>
+        <v>2.4</v>
       </c>
       <c r="BJ6" t="n">
         <v>11.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="BN6" t="n">
         <v>8</v>
@@ -2062,16 +2062,16 @@
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="BT6" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BU6" t="n">
         <v>3.55</v>
@@ -2080,23 +2080,23 @@
         <v>16.5</v>
       </c>
       <c r="BW6" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
         <v>2.44</v>
       </c>
       <c r="J7" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="K7" t="n">
         <v>3.3</v>
@@ -2151,7 +2151,7 @@
         <v>1.1</v>
       </c>
       <c r="N7" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="O7" t="n">
         <v>1.5</v>
@@ -2226,7 +2226,7 @@
         <v>100</v>
       </c>
       <c r="AM7" t="n">
-        <v>210</v>
+        <v>500</v>
       </c>
       <c r="AN7" t="n">
         <v>110</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -2381,25 +2381,25 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="G8" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="H8" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="I8" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="K8" t="n">
         <v>6</v>
       </c>
       <c r="L8" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="M8" t="n">
         <v>1.03</v>
@@ -2414,7 +2414,7 @@
         <v>2.58</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="R8" t="n">
         <v>1.64</v>
@@ -2432,13 +2432,13 @@
         <v>1.11</v>
       </c>
       <c r="W8" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="X8" t="n">
         <v>27</v>
       </c>
       <c r="Y8" t="n">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="Z8" t="n">
         <v>1000</v>
@@ -2456,10 +2456,10 @@
         <v>34</v>
       </c>
       <c r="AE8" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AG8" t="n">
         <v>11</v>
@@ -2483,10 +2483,10 @@
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AO8" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AP8" t="n">
         <v>22</v>
@@ -2501,13 +2501,13 @@
         <v>50</v>
       </c>
       <c r="AT8" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU8" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AV8" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="AW8" t="n">
         <v>40</v>
@@ -2516,7 +2516,7 @@
         <v>8.4</v>
       </c>
       <c r="AY8" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ8" t="n">
         <v>22</v>
@@ -2525,86 +2525,86 @@
         <v>38</v>
       </c>
       <c r="BB8" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BD8" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="BE8" t="n">
         <v>40</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BG8" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BH8" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BI8" t="n">
         <v>4</v>
       </c>
       <c r="BJ8" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BN8" t="n">
         <v>4.1</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BP8" t="n">
         <v>7.8</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="BR8" t="n">
         <v>22</v>
       </c>
       <c r="BS8" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BT8" t="n">
         <v>13.5</v>
       </c>
       <c r="BU8" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BZ8" t="n">
         <v>11</v>
       </c>
       <c r="CA8" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -2635,97 +2635,97 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="G9" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="H9" t="n">
         <v>7.2</v>
       </c>
       <c r="I9" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="J9" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="K9" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="L9" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="M9" t="n">
         <v>1.02</v>
       </c>
       <c r="N9" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="O9" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="P9" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="R9" t="n">
         <v>1.91</v>
       </c>
       <c r="S9" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="T9" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="U9" t="n">
         <v>2.48</v>
       </c>
       <c r="V9" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W9" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="X9" t="n">
+        <v>36</v>
+      </c>
+      <c r="Y9" t="n">
         <v>40</v>
       </c>
-      <c r="Y9" t="n">
-        <v>46</v>
-      </c>
       <c r="Z9" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AA9" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AB9" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AE9" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AF9" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AG9" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH9" t="n">
         <v>18.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ9" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AK9" t="n">
         <v>13.5</v>
@@ -2734,73 +2734,73 @@
         <v>24</v>
       </c>
       <c r="AM9" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AN9" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AO9" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP9" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AQ9" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AR9" t="n">
         <v>60</v>
       </c>
       <c r="AS9" t="n">
-        <v>9.4</v>
+        <v>18</v>
       </c>
       <c r="AT9" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU9" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AV9" t="n">
         <v>24</v>
       </c>
       <c r="AW9" t="n">
-        <v>9.6</v>
+        <v>16.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AY9" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ9" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BA9" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BB9" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BC9" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BD9" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BE9" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BF9" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BG9" t="n">
-        <v>9.199999999999999</v>
+        <v>15</v>
       </c>
       <c r="BH9" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BI9" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BJ9" t="n">
         <v>10</v>
@@ -2809,16 +2809,16 @@
         <v>5</v>
       </c>
       <c r="BL9" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BM9" t="n">
         <v>9</v>
       </c>
       <c r="BN9" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BP9" t="n">
         <v>8.800000000000001</v>
@@ -2839,7 +2839,7 @@
         <v>5.4</v>
       </c>
       <c r="BV9" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BW9" t="n">
         <v>8.4</v>
@@ -2851,14 +2851,14 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BZ9" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CA9" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -2889,19 +2889,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="G10" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="H10" t="n">
         <v>2.52</v>
       </c>
       <c r="I10" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="J10" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K10" t="n">
         <v>4.3</v>
@@ -2922,28 +2922,28 @@
         <v>3.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="R10" t="n">
         <v>1.94</v>
       </c>
       <c r="S10" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="T10" t="n">
         <v>1.4</v>
       </c>
       <c r="U10" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="V10" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="W10" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="X10" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Y10" t="n">
         <v>24</v>
@@ -2952,22 +2952,22 @@
         <v>26</v>
       </c>
       <c r="AA10" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AB10" t="n">
         <v>24</v>
       </c>
       <c r="AC10" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD10" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE10" t="n">
         <v>23</v>
       </c>
       <c r="AF10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AG10" t="n">
         <v>14</v>
@@ -2979,7 +2979,7 @@
         <v>25</v>
       </c>
       <c r="AJ10" t="n">
-        <v>42</v>
+        <v>120</v>
       </c>
       <c r="AK10" t="n">
         <v>24</v>
@@ -3003,7 +3003,7 @@
         <v>21</v>
       </c>
       <c r="AR10" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AS10" t="n">
         <v>23</v>
@@ -3012,13 +3012,13 @@
         <v>20</v>
       </c>
       <c r="AU10" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AV10" t="n">
         <v>12</v>
       </c>
       <c r="AW10" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AX10" t="n">
         <v>21</v>
@@ -3045,10 +3045,10 @@
         <v>23</v>
       </c>
       <c r="BF10" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BG10" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH10" t="n">
         <v>5.4</v>
@@ -3090,7 +3090,7 @@
         <v>6.4</v>
       </c>
       <c r="BU10" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BV10" t="n">
         <v>15.5</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -3149,16 +3149,16 @@
         <v>2.72</v>
       </c>
       <c r="H11" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I11" t="n">
         <v>3.35</v>
       </c>
       <c r="J11" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K11" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L11" t="n">
         <v>1.47</v>
@@ -3170,13 +3170,13 @@
         <v>2.98</v>
       </c>
       <c r="O11" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P11" t="n">
         <v>1.67</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="R11" t="n">
         <v>1.25</v>
@@ -3206,7 +3206,7 @@
         <v>22</v>
       </c>
       <c r="AA11" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AB11" t="n">
         <v>9.4</v>
@@ -3287,7 +3287,7 @@
         <v>42</v>
       </c>
       <c r="BB11" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BC11" t="n">
         <v>6.6</v>
@@ -3296,7 +3296,7 @@
         <v>7.2</v>
       </c>
       <c r="BE11" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF11" t="n">
         <v>6.6</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
         <v>7</v>
       </c>
       <c r="H12" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="I12" t="n">
         <v>1.63</v>
@@ -3412,7 +3412,7 @@
         <v>4.5</v>
       </c>
       <c r="K12" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -3487,19 +3487,19 @@
         <v>40</v>
       </c>
       <c r="AJ12" t="n">
-        <v>180</v>
+        <v>700</v>
       </c>
       <c r="AK12" t="n">
-        <v>85</v>
+        <v>700</v>
       </c>
       <c r="AL12" t="n">
-        <v>75</v>
+        <v>700</v>
       </c>
       <c r="AM12" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AN12" t="n">
-        <v>80</v>
+        <v>700</v>
       </c>
       <c r="AO12" t="n">
         <v>6.6</v>
@@ -3517,7 +3517,7 @@
         <v>13</v>
       </c>
       <c r="AT12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU12" t="n">
         <v>9.6</v>
@@ -3529,7 +3529,7 @@
         <v>13</v>
       </c>
       <c r="AX12" t="n">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="AY12" t="n">
         <v>20</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -3663,10 +3663,10 @@
         <v>11</v>
       </c>
       <c r="J13" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="K13" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
@@ -3693,7 +3693,7 @@
         <v>1.78</v>
       </c>
       <c r="T13" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U13" t="n">
         <v>2.28</v>
@@ -3747,7 +3747,7 @@
         <v>15.5</v>
       </c>
       <c r="AL13" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM13" t="n">
         <v>80</v>
@@ -3777,7 +3777,7 @@
         <v>13</v>
       </c>
       <c r="AV13" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AW13" t="n">
         <v>6.4</v>
@@ -3792,7 +3792,7 @@
         <v>17.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB13" t="n">
         <v>11</v>
@@ -3804,13 +3804,13 @@
         <v>21</v>
       </c>
       <c r="BE13" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF13" t="n">
         <v>3</v>
       </c>
       <c r="BG13" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
         <v>5.8</v>
       </c>
       <c r="G14" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="H14" t="n">
         <v>1.64</v>
@@ -3956,7 +3956,7 @@
         <v>2.32</v>
       </c>
       <c r="W14" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="X14" t="n">
         <v>17.5</v>
@@ -3983,7 +3983,7 @@
         <v>23</v>
       </c>
       <c r="AF14" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AG14" t="n">
         <v>29</v>
@@ -3992,22 +3992,22 @@
         <v>27</v>
       </c>
       <c r="AI14" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AJ14" t="n">
-        <v>220</v>
+        <v>700</v>
       </c>
       <c r="AK14" t="n">
-        <v>120</v>
+        <v>700</v>
       </c>
       <c r="AL14" t="n">
-        <v>120</v>
+        <v>700</v>
       </c>
       <c r="AM14" t="n">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="AN14" t="n">
-        <v>160</v>
+        <v>700</v>
       </c>
       <c r="AO14" t="n">
         <v>13.5</v>
@@ -4040,16 +4040,16 @@
         <v>36</v>
       </c>
       <c r="AY14" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AZ14" t="n">
         <v>19</v>
       </c>
       <c r="BA14" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BC14" t="n">
         <v>4.2</v>
@@ -4058,10 +4058,10 @@
         <v>4.2</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF14" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BG14" t="n">
         <v>9.6</v>
@@ -4088,7 +4088,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BO14" t="n">
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
@@ -4106,7 +4106,7 @@
         <v>4.3</v>
       </c>
       <c r="BU14" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="BV14" t="n">
         <v>11.5</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -4162,10 +4162,10 @@
         <v>1.96</v>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I15" t="n">
         <v>4.2</v>
@@ -4192,7 +4192,7 @@
         <v>2.34</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="R15" t="n">
         <v>1.53</v>
@@ -4210,13 +4210,13 @@
         <v>1.31</v>
       </c>
       <c r="W15" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X15" t="n">
         <v>20</v>
       </c>
       <c r="Y15" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Z15" t="n">
         <v>32</v>
@@ -4246,7 +4246,7 @@
         <v>16</v>
       </c>
       <c r="AI15" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AJ15" t="n">
         <v>23</v>
@@ -4285,7 +4285,7 @@
         <v>8.4</v>
       </c>
       <c r="AV15" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AW15" t="n">
         <v>38</v>
@@ -4318,10 +4318,10 @@
         <v>9.4</v>
       </c>
       <c r="BG15" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BH15" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BI15" t="n">
         <v>3.15</v>
@@ -4336,10 +4336,10 @@
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN15" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BO15" t="n">
         <v>4.3</v>
@@ -4348,13 +4348,13 @@
         <v>14</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BR15" t="n">
         <v>25</v>
       </c>
       <c r="BS15" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BT15" t="n">
         <v>7.8</v>
@@ -4363,26 +4363,26 @@
         <v>5.7</v>
       </c>
       <c r="BV15" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BW15" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BX15" t="n">
         <v>38</v>
       </c>
       <c r="BY15" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BZ15" t="n">
         <v>19</v>
       </c>
       <c r="CA15" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -4413,37 +4413,37 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="G16" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="H16" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I16" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="J16" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K16" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L16" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="M16" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N16" t="n">
         <v>4.9</v>
       </c>
       <c r="O16" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P16" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="Q16" t="n">
         <v>1.7</v>
@@ -4458,25 +4458,25 @@
         <v>1.67</v>
       </c>
       <c r="U16" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="V16" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W16" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="X16" t="n">
         <v>21</v>
       </c>
       <c r="Y16" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Z16" t="n">
         <v>36</v>
       </c>
       <c r="AA16" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
         <v>11.5</v>
@@ -4485,7 +4485,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD16" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE16" t="n">
         <v>50</v>
@@ -4500,31 +4500,31 @@
         <v>17</v>
       </c>
       <c r="AI16" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK16" t="n">
         <v>18</v>
       </c>
       <c r="AL16" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AM16" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AN16" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO16" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AP16" t="n">
         <v>18</v>
       </c>
       <c r="AQ16" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AR16" t="n">
         <v>30</v>
@@ -4533,28 +4533,28 @@
         <v>36</v>
       </c>
       <c r="AT16" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU16" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV16" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AX16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY16" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ16" t="n">
         <v>15</v>
       </c>
       <c r="BA16" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BB16" t="n">
         <v>18.5</v>
@@ -4569,16 +4569,16 @@
         <v>34</v>
       </c>
       <c r="BF16" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BG16" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="BH16" t="n">
         <v>4.2</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="BJ16" t="n">
         <v>9.6</v>
@@ -4602,7 +4602,7 @@
         <v>13</v>
       </c>
       <c r="BQ16" t="n">
-        <v>9.4</v>
+        <v>5.7</v>
       </c>
       <c r="BR16" t="n">
         <v>24</v>
@@ -4632,11 +4632,11 @@
         <v>18.5</v>
       </c>
       <c r="CA16" t="n">
-        <v>13</v>
+        <v>6.4</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -4667,25 +4667,25 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="G17" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="H17" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="I17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="K17" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="L17" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="M17" t="n">
         <v>1.01</v>
@@ -4694,7 +4694,7 @@
         <v>9.6</v>
       </c>
       <c r="O17" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="P17" t="n">
         <v>4</v>
@@ -4703,13 +4703,13 @@
         <v>1.3</v>
       </c>
       <c r="R17" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="S17" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="T17" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U17" t="n">
         <v>2.04</v>
@@ -4733,19 +4733,19 @@
         <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AC17" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AD17" t="n">
-        <v>590</v>
+        <v>830</v>
       </c>
       <c r="AE17" t="n">
         <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG17" t="n">
         <v>13.5</v>
@@ -4760,10 +4760,10 @@
         <v>10.5</v>
       </c>
       <c r="AK17" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AL17" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="AM17" t="n">
         <v>1000</v>
@@ -4793,7 +4793,7 @@
         <v>20</v>
       </c>
       <c r="AV17" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AW17" t="n">
         <v>48</v>
@@ -4805,34 +4805,34 @@
         <v>12</v>
       </c>
       <c r="AZ17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA17" t="n">
         <v>42</v>
       </c>
       <c r="BB17" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BC17" t="n">
         <v>11.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BE17" t="n">
         <v>42</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="BG17" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BH17" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BI17" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BJ17" t="n">
         <v>12.5</v>
@@ -4844,53 +4844,53 @@
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>15.5</v>
+        <v>7.8</v>
       </c>
       <c r="BN17" t="n">
         <v>4.2</v>
       </c>
       <c r="BO17" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="BP17" t="n">
         <v>6</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BR17" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT17" t="n">
         <v>20</v>
       </c>
       <c r="BU17" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>15.5</v>
+        <v>7.8</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>15</v>
+        <v>7.6</v>
       </c>
       <c r="BZ17" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="CA17" t="n">
         <v>5.3</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -4921,16 +4921,16 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.78</v>
+        <v>2.94</v>
       </c>
       <c r="G18" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="H18" t="n">
-        <v>2.58</v>
+        <v>2.74</v>
       </c>
       <c r="I18" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="J18" t="n">
         <v>2.62</v>
@@ -4942,7 +4942,7 @@
         <v>1.6</v>
       </c>
       <c r="M18" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="N18" t="n">
         <v>2.16</v>
@@ -4954,13 +4954,13 @@
         <v>1.38</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="R18" t="n">
         <v>1.13</v>
       </c>
       <c r="S18" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="T18" t="n">
         <v>2.28</v>
@@ -4969,118 +4969,118 @@
         <v>1.61</v>
       </c>
       <c r="V18" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W18" t="n">
         <v>1.4</v>
       </c>
       <c r="X18" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="Y18" t="n">
-        <v>9.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="Z18" t="n">
-        <v>24</v>
+        <v>18.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AB18" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AC18" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE18" t="n">
-        <v>75</v>
+        <v>290</v>
       </c>
       <c r="AF18" t="n">
         <v>21</v>
       </c>
       <c r="AG18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH18" t="n">
-        <v>950</v>
+        <v>85</v>
       </c>
       <c r="AI18" t="n">
-        <v>1000</v>
+        <v>540</v>
       </c>
       <c r="AJ18" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AK18" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AL18" t="n">
-        <v>120</v>
+        <v>540</v>
       </c>
       <c r="AM18" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN18" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AO18" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP18" t="n">
-        <v>2.8</v>
+        <v>3.85</v>
       </c>
       <c r="AQ18" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="AR18" t="n">
-        <v>3.7</v>
+        <v>5.7</v>
       </c>
       <c r="AS18" t="n">
-        <v>4.1</v>
+        <v>7.2</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.92</v>
+        <v>4.4</v>
       </c>
       <c r="AU18" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="AV18" t="n">
-        <v>3.45</v>
+        <v>5.4</v>
       </c>
       <c r="AW18" t="n">
-        <v>4.1</v>
+        <v>7.2</v>
       </c>
       <c r="AX18" t="n">
-        <v>3.6</v>
+        <v>5.9</v>
       </c>
       <c r="AY18" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="AZ18" t="n">
-        <v>3.9</v>
+        <v>6.4</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.3</v>
+        <v>7.6</v>
       </c>
       <c r="BB18" t="n">
-        <v>4.1</v>
+        <v>7.4</v>
       </c>
       <c r="BC18" t="n">
-        <v>4.1</v>
+        <v>7.2</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.2</v>
+        <v>7.6</v>
       </c>
       <c r="BE18" t="n">
-        <v>4.3</v>
+        <v>8</v>
       </c>
       <c r="BF18" t="n">
-        <v>4.2</v>
+        <v>7.6</v>
       </c>
       <c r="BG18" t="n">
-        <v>4.3</v>
+        <v>7.4</v>
       </c>
       <c r="BH18" t="n">
         <v>2.66</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -5175,22 +5175,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="G19" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="H19" t="n">
         <v>3.55</v>
       </c>
       <c r="I19" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="J19" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="K19" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
@@ -5208,7 +5208,7 @@
         <v>1.36</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="R19" t="n">
         <v>1.12</v>
@@ -5217,22 +5217,22 @@
         <v>6.6</v>
       </c>
       <c r="T19" t="n">
-        <v>2.18</v>
+        <v>2.36</v>
       </c>
       <c r="U19" t="n">
         <v>1.57</v>
       </c>
       <c r="V19" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="W19" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="X19" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="Y19" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z19" t="n">
         <v>32</v>
@@ -5241,22 +5241,22 @@
         <v>150</v>
       </c>
       <c r="AB19" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AC19" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AE19" t="n">
         <v>120</v>
       </c>
       <c r="AF19" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AG19" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH19" t="n">
         <v>32</v>
@@ -5265,7 +5265,7 @@
         <v>170</v>
       </c>
       <c r="AJ19" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AK19" t="n">
         <v>46</v>
@@ -5274,67 +5274,67 @@
         <v>120</v>
       </c>
       <c r="AM19" t="n">
-        <v>390</v>
+        <v>500</v>
       </c>
       <c r="AN19" t="n">
         <v>55</v>
       </c>
       <c r="AO19" t="n">
-        <v>210</v>
+        <v>500</v>
       </c>
       <c r="AP19" t="n">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="AQ19" t="n">
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="AR19" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="AS19" t="n">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="AT19" t="n">
-        <v>2.96</v>
+        <v>3.6</v>
       </c>
       <c r="AU19" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="AV19" t="n">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="AW19" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="AX19" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="AY19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="BA19" t="n">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB19" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="BD19" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="BE19" t="n">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
       <c r="BF19" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="BG19" t="n">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH19" t="n">
         <v>1000</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G20" t="n">
         <v>2.86</v>
@@ -5438,10 +5438,10 @@
         <v>3.3</v>
       </c>
       <c r="I20" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J20" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="K20" t="n">
         <v>3.15</v>
@@ -5471,7 +5471,7 @@
         <v>5.1</v>
       </c>
       <c r="T20" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="U20" t="n">
         <v>1.59</v>
@@ -5483,7 +5483,7 @@
         <v>1.54</v>
       </c>
       <c r="X20" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Y20" t="n">
         <v>10.5</v>
@@ -5492,19 +5492,19 @@
         <v>28</v>
       </c>
       <c r="AA20" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AB20" t="n">
         <v>7.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD20" t="n">
         <v>21</v>
       </c>
       <c r="AE20" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AF20" t="n">
         <v>17</v>
@@ -5516,7 +5516,7 @@
         <v>32</v>
       </c>
       <c r="AI20" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AJ20" t="n">
         <v>50</v>
@@ -5525,70 +5525,70 @@
         <v>50</v>
       </c>
       <c r="AL20" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AM20" t="n">
-        <v>310</v>
+        <v>500</v>
       </c>
       <c r="AN20" t="n">
         <v>65</v>
       </c>
       <c r="AO20" t="n">
-        <v>140</v>
+        <v>500</v>
       </c>
       <c r="AP20" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AQ20" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="AR20" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AS20" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BF20" t="n">
         <v>5.1</v>
       </c>
-      <c r="AT20" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>4</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>5</v>
-      </c>
       <c r="BG20" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BH20" t="n">
         <v>2.7</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -5686,10 +5686,10 @@
         <v>2.26</v>
       </c>
       <c r="G21" t="n">
-        <v>2.96</v>
+        <v>2.78</v>
       </c>
       <c r="H21" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="I21" t="n">
         <v>4.1</v>
@@ -5713,7 +5713,7 @@
         <v>1.46</v>
       </c>
       <c r="P21" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="Q21" t="n">
         <v>2.3</v>
@@ -5722,10 +5722,10 @@
         <v>1.18</v>
       </c>
       <c r="S21" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="T21" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="U21" t="n">
         <v>1.75</v>
@@ -5734,115 +5734,115 @@
         <v>1.32</v>
       </c>
       <c r="W21" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="X21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Y21" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AA21" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AB21" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC21" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AD21" t="n">
         <v>19</v>
       </c>
       <c r="AE21" t="n">
-        <v>70</v>
+        <v>440</v>
       </c>
       <c r="AF21" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AI21" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AJ21" t="n">
-        <v>48</v>
+        <v>150</v>
       </c>
       <c r="AK21" t="n">
-        <v>42</v>
+        <v>110</v>
       </c>
       <c r="AL21" t="n">
-        <v>75</v>
+        <v>450</v>
       </c>
       <c r="AM21" t="n">
-        <v>210</v>
+        <v>500</v>
       </c>
       <c r="AN21" t="n">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="AO21" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AP21" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="AQ21" t="n">
-        <v>3.2</v>
+        <v>5.8</v>
       </c>
       <c r="AR21" t="n">
-        <v>3.8</v>
+        <v>4.9</v>
       </c>
       <c r="AS21" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY21" t="n">
         <v>4.1</v>
       </c>
-      <c r="AT21" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>3.35</v>
-      </c>
       <c r="AZ21" t="n">
-        <v>3.75</v>
+        <v>4.8</v>
       </c>
       <c r="BA21" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="BB21" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="BC21" t="n">
-        <v>3.95</v>
+        <v>5.2</v>
       </c>
       <c r="BD21" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="BE21" t="n">
-        <v>4.2</v>
+        <v>5.9</v>
       </c>
       <c r="BF21" t="n">
-        <v>3.95</v>
+        <v>5.2</v>
       </c>
       <c r="BG21" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="BH21" t="n">
         <v>3.2</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -5937,25 +5937,25 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G22" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="H22" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="I22" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="J22" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K22" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L22" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M22" t="n">
         <v>1.05</v>
@@ -5964,10 +5964,10 @@
         <v>4.2</v>
       </c>
       <c r="O22" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P22" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q22" t="n">
         <v>1.84</v>
@@ -5976,43 +5976,43 @@
         <v>1.43</v>
       </c>
       <c r="S22" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="T22" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="U22" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V22" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W22" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="X22" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Y22" t="n">
-        <v>16.5</v>
+        <v>22</v>
       </c>
       <c r="Z22" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="AA22" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AB22" t="n">
         <v>11.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD22" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AE22" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AF22" t="n">
         <v>15.5</v>
@@ -6024,37 +6024,37 @@
         <v>17</v>
       </c>
       <c r="AI22" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ22" t="n">
         <v>36</v>
       </c>
       <c r="AK22" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL22" t="n">
         <v>40</v>
       </c>
       <c r="AM22" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AN22" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AO22" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AP22" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AQ22" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>6.8</v>
+        <v>20</v>
       </c>
       <c r="AS22" t="n">
-        <v>7.8</v>
+        <v>42</v>
       </c>
       <c r="AT22" t="n">
         <v>9.4</v>
@@ -6066,7 +6066,7 @@
         <v>12.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>7.2</v>
+        <v>5.2</v>
       </c>
       <c r="AX22" t="n">
         <v>11.5</v>
@@ -6078,7 +6078,7 @@
         <v>14</v>
       </c>
       <c r="BA22" t="n">
-        <v>7.4</v>
+        <v>5.8</v>
       </c>
       <c r="BB22" t="n">
         <v>21</v>
@@ -6090,19 +6090,19 @@
         <v>24</v>
       </c>
       <c r="BE22" t="n">
-        <v>7.8</v>
+        <v>5.4</v>
       </c>
       <c r="BF22" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BG22" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="BH22" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BI22" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="BJ22" t="n">
         <v>9.6</v>
@@ -6117,31 +6117,31 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BN22" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BO22" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="BP22" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BQ22" t="n">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="BR22" t="n">
         <v>1000</v>
       </c>
       <c r="BS22" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BT22" t="n">
         <v>7.2</v>
       </c>
-      <c r="BT22" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BU22" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="BV22" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BW22" t="n">
         <v>7.4</v>
@@ -6153,14 +6153,14 @@
         <v>7.8</v>
       </c>
       <c r="BZ22" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="CA22" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -6191,166 +6191,166 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="G23" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="H23" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="I23" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J23" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K23" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="L23" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="M23" t="n">
         <v>1.07</v>
       </c>
       <c r="N23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S23" t="n">
         <v>3.2</v>
       </c>
-      <c r="O23" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.45</v>
-      </c>
       <c r="T23" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="U23" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="V23" t="n">
         <v>1.2</v>
       </c>
       <c r="W23" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X23" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA23" t="n">
-        <v>150</v>
+        <v>700</v>
       </c>
       <c r="AB23" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC23" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE23" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AF23" t="n">
         <v>12</v>
       </c>
       <c r="AG23" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI23" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AJ23" t="n">
         <v>22</v>
       </c>
       <c r="AK23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL23" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AM23" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AN23" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV23" t="n">
         <v>15</v>
       </c>
-      <c r="AO23" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>24</v>
-      </c>
-      <c r="AS23" t="n">
+      <c r="AW23" t="n">
         <v>6.4</v>
       </c>
-      <c r="AT23" t="n">
+      <c r="AX23" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BE23" t="n">
         <v>6.6</v>
       </c>
-      <c r="AU23" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>16</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>24</v>
-      </c>
-      <c r="BE23" t="n">
+      <c r="BF23" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BG23" t="n">
         <v>6.4</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>11</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>6.2</v>
       </c>
       <c r="BH23" t="n">
         <v>1000</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -6451,16 +6451,16 @@
         <v>1.09</v>
       </c>
       <c r="H24" t="n">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="I24" t="n">
         <v>85</v>
       </c>
       <c r="J24" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="K24" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="L24" t="n">
         <v>1.01</v>
@@ -6475,7 +6475,7 @@
         <v>1.09</v>
       </c>
       <c r="P24" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="Q24" t="n">
         <v>1.28</v>
@@ -6496,7 +6496,7 @@
         <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="X24" t="n">
         <v>75</v>
@@ -6523,13 +6523,13 @@
         <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG24" t="n">
         <v>21</v>
       </c>
       <c r="AH24" t="n">
-        <v>130</v>
+        <v>950</v>
       </c>
       <c r="AI24" t="n">
         <v>1000</v>
@@ -6547,64 +6547,64 @@
         <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>2.42</v>
+        <v>2.16</v>
       </c>
       <c r="AO24" t="n">
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AY24" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AQ24" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AZ24" t="n">
-        <v>1.85</v>
+        <v>2.12</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.88</v>
+        <v>4.2</v>
       </c>
       <c r="BB24" t="n">
-        <v>3.95</v>
+        <v>5</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD24" t="n">
-        <v>1.85</v>
+        <v>2.12</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.88</v>
+        <v>2.16</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.88</v>
+        <v>4.2</v>
       </c>
       <c r="BH24" t="n">
         <v>1000</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -6699,28 +6699,28 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="G25" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="H25" t="n">
         <v>3.4</v>
       </c>
       <c r="I25" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="J25" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="K25" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="L25" t="n">
         <v>1.48</v>
       </c>
       <c r="M25" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N25" t="n">
         <v>3.05</v>
@@ -6729,7 +6729,7 @@
         <v>1.4</v>
       </c>
       <c r="P25" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="Q25" t="n">
         <v>2.24</v>
@@ -6741,13 +6741,13 @@
         <v>4.2</v>
       </c>
       <c r="T25" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="U25" t="n">
         <v>1.93</v>
       </c>
       <c r="V25" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W25" t="n">
         <v>1.68</v>
@@ -6759,13 +6759,13 @@
         <v>12</v>
       </c>
       <c r="Z25" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA25" t="n">
         <v>85</v>
       </c>
       <c r="AB25" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC25" t="n">
         <v>8.4</v>
@@ -6777,7 +6777,7 @@
         <v>60</v>
       </c>
       <c r="AF25" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG25" t="n">
         <v>12.5</v>
@@ -6798,7 +6798,7 @@
         <v>60</v>
       </c>
       <c r="AM25" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AN25" t="n">
         <v>32</v>
@@ -6807,7 +6807,7 @@
         <v>70</v>
       </c>
       <c r="AP25" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AQ25" t="n">
         <v>8.6</v>
@@ -6816,19 +6816,19 @@
         <v>18.5</v>
       </c>
       <c r="AS25" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT25" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AU25" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV25" t="n">
         <v>11.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AX25" t="n">
         <v>11</v>
@@ -6840,25 +6840,25 @@
         <v>15</v>
       </c>
       <c r="BA25" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BB25" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BC25" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BD25" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BE25" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF25" t="n">
         <v>20</v>
       </c>
       <c r="BG25" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BH25" t="n">
         <v>3.05</v>
@@ -6876,22 +6876,22 @@
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN25" t="n">
         <v>5.1</v>
       </c>
       <c r="BO25" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="BP25" t="n">
         <v>18.5</v>
       </c>
       <c r="BQ25" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR25" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS25" t="n">
         <v>10</v>
@@ -6906,13 +6906,13 @@
         <v>34</v>
       </c>
       <c r="BW25" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BX25" t="n">
         <v>1000</v>
       </c>
       <c r="BY25" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ25" t="n">
         <v>0</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -7007,7 +7007,7 @@
         <v>3.55</v>
       </c>
       <c r="X26" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Y26" t="n">
         <v>46</v>
@@ -7052,7 +7052,7 @@
         <v>40</v>
       </c>
       <c r="AM26" t="n">
-        <v>150</v>
+        <v>380</v>
       </c>
       <c r="AN26" t="n">
         <v>4.7</v>
@@ -7064,13 +7064,13 @@
         <v>19.5</v>
       </c>
       <c r="AQ26" t="n">
-        <v>4.7</v>
+        <v>27</v>
       </c>
       <c r="AR26" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AS26" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AT26" t="n">
         <v>8</v>
@@ -7079,10 +7079,10 @@
         <v>10</v>
       </c>
       <c r="AV26" t="n">
-        <v>4.7</v>
+        <v>14.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AX26" t="n">
         <v>7</v>
@@ -7094,7 +7094,7 @@
         <v>18.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BB26" t="n">
         <v>8.4</v>
@@ -7103,16 +7103,16 @@
         <v>10</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.6</v>
+        <v>16</v>
       </c>
       <c r="BE26" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BF26" t="n">
         <v>4.2</v>
       </c>
       <c r="BG26" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BH26" t="n">
         <v>4.6</v>
@@ -7136,7 +7136,7 @@
         <v>4.1</v>
       </c>
       <c r="BO26" t="n">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="BP26" t="n">
         <v>7.8</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -7291,10 +7291,10 @@
         <v>14.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>950</v>
+        <v>430</v>
       </c>
       <c r="AI27" t="n">
-        <v>540</v>
+        <v>580</v>
       </c>
       <c r="AJ27" t="n">
         <v>7.8</v>
@@ -7303,7 +7303,7 @@
         <v>17</v>
       </c>
       <c r="AL27" t="n">
-        <v>70</v>
+        <v>430</v>
       </c>
       <c r="AM27" t="n">
         <v>480</v>
@@ -7318,7 +7318,7 @@
         <v>21</v>
       </c>
       <c r="AQ27" t="n">
-        <v>9.199999999999999</v>
+        <v>20</v>
       </c>
       <c r="AR27" t="n">
         <v>10</v>
@@ -7327,10 +7327,10 @@
         <v>7</v>
       </c>
       <c r="AT27" t="n">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="AU27" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AV27" t="n">
         <v>9.800000000000001</v>
@@ -7345,7 +7345,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ27" t="n">
-        <v>9.199999999999999</v>
+        <v>28</v>
       </c>
       <c r="BA27" t="n">
         <v>7</v>
@@ -7354,13 +7354,13 @@
         <v>6.4</v>
       </c>
       <c r="BC27" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BD27" t="n">
-        <v>9.199999999999999</v>
+        <v>28</v>
       </c>
       <c r="BE27" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BF27" t="n">
         <v>3.25</v>
@@ -7426,11 +7426,11 @@
         <v>9</v>
       </c>
       <c r="CA27" t="n">
-        <v>6.8</v>
+        <v>4.8</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -7461,16 +7461,16 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="G28" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="H28" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="I28" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="J28" t="n">
         <v>4.1</v>
@@ -7479,7 +7479,7 @@
         <v>4.4</v>
       </c>
       <c r="L28" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M28" t="n">
         <v>1.06</v>
@@ -7491,7 +7491,7 @@
         <v>1.3</v>
       </c>
       <c r="P28" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="Q28" t="n">
         <v>1.87</v>
@@ -7500,43 +7500,43 @@
         <v>1.4</v>
       </c>
       <c r="S28" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T28" t="n">
         <v>1.9</v>
       </c>
       <c r="U28" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="V28" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W28" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="X28" t="n">
         <v>16.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Z28" t="n">
         <v>60</v>
       </c>
       <c r="AA28" t="n">
-        <v>190</v>
+        <v>700</v>
       </c>
       <c r="AB28" t="n">
         <v>8.4</v>
       </c>
       <c r="AC28" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD28" t="n">
         <v>23</v>
       </c>
       <c r="AE28" t="n">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="AF28" t="n">
         <v>10.5</v>
@@ -7548,7 +7548,7 @@
         <v>24</v>
       </c>
       <c r="AI28" t="n">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="AJ28" t="n">
         <v>21</v>
@@ -7557,16 +7557,16 @@
         <v>22</v>
       </c>
       <c r="AL28" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AM28" t="n">
-        <v>160</v>
+        <v>390</v>
       </c>
       <c r="AN28" t="n">
         <v>10.5</v>
       </c>
       <c r="AO28" t="n">
-        <v>130</v>
+        <v>440</v>
       </c>
       <c r="AP28" t="n">
         <v>12</v>
@@ -7575,10 +7575,10 @@
         <v>16</v>
       </c>
       <c r="AR28" t="n">
-        <v>38</v>
+        <v>7.4</v>
       </c>
       <c r="AS28" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT28" t="n">
         <v>7</v>
@@ -7587,10 +7587,10 @@
         <v>8.4</v>
       </c>
       <c r="AV28" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX28" t="n">
         <v>8.199999999999999</v>
@@ -7602,7 +7602,7 @@
         <v>19.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB28" t="n">
         <v>13.5</v>
@@ -7614,13 +7614,13 @@
         <v>26</v>
       </c>
       <c r="BE28" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BF28" t="n">
         <v>8.6</v>
       </c>
       <c r="BG28" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH28" t="n">
         <v>3.6</v>
@@ -7638,7 +7638,7 @@
         <v>1000</v>
       </c>
       <c r="BM28" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN28" t="n">
         <v>4.4</v>
@@ -7656,7 +7656,7 @@
         <v>28</v>
       </c>
       <c r="BS28" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BT28" t="n">
         <v>9.800000000000001</v>
@@ -7668,10 +7668,10 @@
         <v>60</v>
       </c>
       <c r="BW28" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX28" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY28" t="n">
         <v>9</v>
@@ -7680,11 +7680,11 @@
         <v>22</v>
       </c>
       <c r="CA28" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -7721,7 +7721,7 @@
         <v>2.04</v>
       </c>
       <c r="H29" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I29" t="n">
         <v>4.2</v>
@@ -7757,7 +7757,7 @@
         <v>2.24</v>
       </c>
       <c r="T29" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="U29" t="n">
         <v>2.56</v>
@@ -7769,7 +7769,7 @@
         <v>1.96</v>
       </c>
       <c r="X29" t="n">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="Y29" t="n">
         <v>26</v>
@@ -7778,43 +7778,43 @@
         <v>38</v>
       </c>
       <c r="AA29" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AB29" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD29" t="n">
         <v>17.5</v>
       </c>
       <c r="AE29" t="n">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="AF29" t="n">
         <v>18.5</v>
       </c>
       <c r="AG29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH29" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AI29" t="n">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="AJ29" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AK29" t="n">
         <v>19</v>
       </c>
       <c r="AL29" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AM29" t="n">
-        <v>65</v>
+        <v>200</v>
       </c>
       <c r="AN29" t="n">
         <v>9.6</v>
@@ -7829,10 +7829,10 @@
         <v>16.5</v>
       </c>
       <c r="AR29" t="n">
-        <v>4.7</v>
+        <v>16</v>
       </c>
       <c r="AS29" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="AT29" t="n">
         <v>11</v>
@@ -7844,7 +7844,7 @@
         <v>12.5</v>
       </c>
       <c r="AW29" t="n">
-        <v>4.9</v>
+        <v>16</v>
       </c>
       <c r="AX29" t="n">
         <v>12</v>
@@ -7856,7 +7856,7 @@
         <v>11.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>4.9</v>
+        <v>18</v>
       </c>
       <c r="BB29" t="n">
         <v>17.5</v>
@@ -7868,7 +7868,7 @@
         <v>19</v>
       </c>
       <c r="BE29" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="BF29" t="n">
         <v>6.4</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -7969,19 +7969,19 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.03</v>
+        <v>1.29</v>
       </c>
       <c r="G30" t="n">
-        <v>1000</v>
+        <v>1.68</v>
       </c>
       <c r="H30" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="I30" t="n">
         <v>1000</v>
       </c>
       <c r="J30" t="n">
-        <v>1.05</v>
+        <v>5</v>
       </c>
       <c r="K30" t="n">
         <v>1000</v>
@@ -7993,13 +7993,13 @@
         <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="O30" t="n">
         <v>1.06</v>
       </c>
       <c r="P30" t="n">
-        <v>2.24</v>
+        <v>2.7</v>
       </c>
       <c r="Q30" t="n">
         <v>1.06</v>
@@ -8008,7 +8008,7 @@
         <v>2.24</v>
       </c>
       <c r="S30" t="n">
-        <v>1.06</v>
+        <v>1.41</v>
       </c>
       <c r="T30" t="n">
         <v>1.11</v>
@@ -8017,10 +8017,10 @@
         <v>1.11</v>
       </c>
       <c r="V30" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="W30" t="n">
-        <v>1.03</v>
+        <v>2.46</v>
       </c>
       <c r="X30" t="n">
         <v>1000</v>
@@ -8071,7 +8071,7 @@
         <v>1000</v>
       </c>
       <c r="AN30" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AO30" t="n">
         <v>1000</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -8223,22 +8223,22 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="G31" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="H31" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="I31" t="n">
-        <v>1000</v>
+        <v>1.88</v>
       </c>
       <c r="J31" t="n">
-        <v>1.1</v>
+        <v>4.6</v>
       </c>
       <c r="K31" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="L31" t="n">
         <v>1.01</v>
@@ -8247,22 +8247,22 @@
         <v>1.01</v>
       </c>
       <c r="N31" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="O31" t="n">
         <v>1.04</v>
       </c>
       <c r="P31" t="n">
-        <v>1.25</v>
+        <v>2.36</v>
       </c>
       <c r="Q31" t="n">
         <v>1.04</v>
       </c>
       <c r="R31" t="n">
-        <v>1.25</v>
+        <v>2.36</v>
       </c>
       <c r="S31" t="n">
-        <v>1.05</v>
+        <v>1.48</v>
       </c>
       <c r="T31" t="n">
         <v>1.11</v>
@@ -8271,10 +8271,10 @@
         <v>1.11</v>
       </c>
       <c r="V31" t="n">
-        <v>1.02</v>
+        <v>2.12</v>
       </c>
       <c r="W31" t="n">
-        <v>1.03</v>
+        <v>1.25</v>
       </c>
       <c r="X31" t="n">
         <v>1000</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -8477,22 +8477,22 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.03</v>
+        <v>1.75</v>
       </c>
       <c r="G32" t="n">
-        <v>1000</v>
+        <v>1.93</v>
       </c>
       <c r="H32" t="n">
-        <v>1.05</v>
+        <v>3.45</v>
       </c>
       <c r="I32" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="J32" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="K32" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="L32" t="n">
         <v>1.01</v>
@@ -8501,22 +8501,22 @@
         <v>1.01</v>
       </c>
       <c r="N32" t="n">
-        <v>1.26</v>
+        <v>2.82</v>
       </c>
       <c r="O32" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="P32" t="n">
-        <v>1.25</v>
+        <v>2.82</v>
       </c>
       <c r="Q32" t="n">
         <v>1.06</v>
       </c>
       <c r="R32" t="n">
-        <v>1.25</v>
+        <v>2.06</v>
       </c>
       <c r="S32" t="n">
-        <v>1.06</v>
+        <v>1.57</v>
       </c>
       <c r="T32" t="n">
         <v>1.11</v>
@@ -8525,61 +8525,61 @@
         <v>1.11</v>
       </c>
       <c r="V32" t="n">
-        <v>1.02</v>
+        <v>1.3</v>
       </c>
       <c r="W32" t="n">
-        <v>1.02</v>
+        <v>2.06</v>
       </c>
       <c r="X32" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y32" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z32" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA32" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB32" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC32" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD32" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE32" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF32" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG32" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH32" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI32" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK32" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL32" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM32" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN32" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO32" t="n">
         <v>1000</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -8731,166 +8731,166 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.03</v>
+        <v>1.32</v>
       </c>
       <c r="G33" t="n">
-        <v>1000</v>
+        <v>1.44</v>
       </c>
       <c r="H33" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="I33" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J33" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="K33" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L33" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="M33" t="n">
         <v>1.01</v>
       </c>
       <c r="N33" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="O33" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="P33" t="n">
-        <v>1.25</v>
+        <v>4.3</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="R33" t="n">
-        <v>1.25</v>
+        <v>2.36</v>
       </c>
       <c r="S33" t="n">
-        <v>1.05</v>
+        <v>1.48</v>
       </c>
       <c r="T33" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="V33" t="n">
         <v>1.11</v>
       </c>
-      <c r="U33" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.02</v>
-      </c>
       <c r="W33" t="n">
-        <v>1.02</v>
+        <v>3.15</v>
       </c>
       <c r="X33" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y33" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z33" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AA33" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AB33" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AC33" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AD33" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AE33" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AF33" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG33" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH33" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI33" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AK33" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AL33" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AM33" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN33" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="AO33" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AU33" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AV33" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BD33" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="BG33" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BH33" t="n">
         <v>1000</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -8985,22 +8985,22 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="G34" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="H34" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="I34" t="n">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="J34" t="n">
-        <v>1.05</v>
+        <v>3.25</v>
       </c>
       <c r="K34" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="L34" t="n">
         <v>1.01</v>
@@ -9009,22 +9009,22 @@
         <v>1.01</v>
       </c>
       <c r="N34" t="n">
-        <v>1.26</v>
+        <v>2.66</v>
       </c>
       <c r="O34" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="P34" t="n">
-        <v>1.25</v>
+        <v>2.34</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="R34" t="n">
-        <v>1.25</v>
+        <v>1.78</v>
       </c>
       <c r="S34" t="n">
-        <v>1.09</v>
+        <v>1.81</v>
       </c>
       <c r="T34" t="n">
         <v>1.11</v>
@@ -9033,64 +9033,64 @@
         <v>1.11</v>
       </c>
       <c r="V34" t="n">
-        <v>1.02</v>
+        <v>1.44</v>
       </c>
       <c r="W34" t="n">
-        <v>1.03</v>
+        <v>1.45</v>
       </c>
       <c r="X34" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y34" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z34" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA34" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB34" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC34" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD34" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE34" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF34" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG34" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH34" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI34" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK34" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL34" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM34" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN34" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO34" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP34" t="n">
         <v>1.01</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -9242,7 +9242,7 @@
         <v>1.4</v>
       </c>
       <c r="G35" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="H35" t="n">
         <v>8.800000000000001</v>
@@ -9254,7 +9254,7 @@
         <v>4.8</v>
       </c>
       <c r="K35" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="L35" t="n">
         <v>1.34</v>
@@ -9269,13 +9269,13 @@
         <v>1.25</v>
       </c>
       <c r="P35" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="R35" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S35" t="n">
         <v>2.88</v>
@@ -9284,13 +9284,13 @@
         <v>2.02</v>
       </c>
       <c r="U35" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="V35" t="n">
         <v>1.1</v>
       </c>
       <c r="W35" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="X35" t="n">
         <v>22</v>
@@ -9299,10 +9299,10 @@
         <v>34</v>
       </c>
       <c r="Z35" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AA35" t="n">
-        <v>390</v>
+        <v>370</v>
       </c>
       <c r="AB35" t="n">
         <v>9.6</v>
@@ -9314,7 +9314,7 @@
         <v>40</v>
       </c>
       <c r="AE35" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AF35" t="n">
         <v>9.800000000000001</v>
@@ -9323,10 +9323,10 @@
         <v>12</v>
       </c>
       <c r="AH35" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI35" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AJ35" t="n">
         <v>14</v>
@@ -9338,37 +9338,37 @@
         <v>44</v>
       </c>
       <c r="AM35" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AN35" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AO35" t="n">
         <v>240</v>
       </c>
       <c r="AP35" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AQ35" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AR35" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AS35" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AT35" t="n">
         <v>7.4</v>
       </c>
       <c r="AU35" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AV35" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AW35" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AX35" t="n">
         <v>6.6</v>
@@ -9380,7 +9380,7 @@
         <v>20</v>
       </c>
       <c r="BA35" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BB35" t="n">
         <v>10.5</v>
@@ -9389,19 +9389,19 @@
         <v>12</v>
       </c>
       <c r="BD35" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BE35" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BF35" t="n">
         <v>5.2</v>
       </c>
       <c r="BG35" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BH35" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BI35" t="n">
         <v>3.15</v>
@@ -9416,7 +9416,7 @@
         <v>1000</v>
       </c>
       <c r="BM35" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BN35" t="n">
         <v>3.9</v>
@@ -9434,7 +9434,7 @@
         <v>1000</v>
       </c>
       <c r="BS35" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT35" t="n">
         <v>12.5</v>
@@ -9452,17 +9452,17 @@
         <v>1000</v>
       </c>
       <c r="BY35" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BZ35" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="CA35" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -9493,230 +9493,230 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.68</v>
+        <v>1.67</v>
       </c>
       <c r="G36" t="n">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="H36" t="n">
-        <v>2.7</v>
+        <v>1.68</v>
       </c>
       <c r="I36" t="n">
-        <v>3.15</v>
+        <v>1000</v>
       </c>
       <c r="J36" t="n">
-        <v>2.78</v>
+        <v>2.26</v>
       </c>
       <c r="K36" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="L36" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M36" t="n">
         <v>1.09</v>
       </c>
       <c r="N36" t="n">
-        <v>2.68</v>
+        <v>1.25</v>
       </c>
       <c r="O36" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S36" t="n">
         <v>1.4</v>
       </c>
-      <c r="P36" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S36" t="n">
-        <v>3.5</v>
-      </c>
       <c r="T36" t="n">
-        <v>1.84</v>
+        <v>1.11</v>
       </c>
       <c r="U36" t="n">
-        <v>1.95</v>
+        <v>1.11</v>
       </c>
       <c r="V36" t="n">
-        <v>1.46</v>
+        <v>1.07</v>
       </c>
       <c r="W36" t="n">
-        <v>1.48</v>
+        <v>1.07</v>
       </c>
       <c r="X36" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Y36" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Z36" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AA36" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB36" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC36" t="n">
-        <v>7.8</v>
+        <v>970</v>
       </c>
       <c r="AD36" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AE36" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF36" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AG36" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH36" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AI36" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AJ36" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AK36" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AL36" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM36" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN36" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AO36" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AP36" t="n">
-        <v>4.8</v>
+        <v>1.09</v>
       </c>
       <c r="AQ36" t="n">
-        <v>4.7</v>
+        <v>1.09</v>
       </c>
       <c r="AR36" t="n">
-        <v>5.9</v>
+        <v>1.09</v>
       </c>
       <c r="AS36" t="n">
-        <v>7.2</v>
+        <v>1.09</v>
       </c>
       <c r="AT36" t="n">
-        <v>4.7</v>
+        <v>1.09</v>
       </c>
       <c r="AU36" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AV36" t="n">
-        <v>5.2</v>
+        <v>1.09</v>
       </c>
       <c r="AW36" t="n">
-        <v>6.8</v>
+        <v>1.09</v>
       </c>
       <c r="AX36" t="n">
-        <v>5.9</v>
+        <v>1.09</v>
       </c>
       <c r="AY36" t="n">
-        <v>5.2</v>
+        <v>1.09</v>
       </c>
       <c r="AZ36" t="n">
-        <v>5.9</v>
+        <v>1.09</v>
       </c>
       <c r="BA36" t="n">
-        <v>7.2</v>
+        <v>1.08</v>
       </c>
       <c r="BB36" t="n">
-        <v>7.2</v>
+        <v>1.09</v>
       </c>
       <c r="BC36" t="n">
-        <v>6.8</v>
+        <v>1.09</v>
       </c>
       <c r="BD36" t="n">
-        <v>7.2</v>
+        <v>1.09</v>
       </c>
       <c r="BE36" t="n">
-        <v>8.4</v>
+        <v>1.08</v>
       </c>
       <c r="BF36" t="n">
-        <v>7</v>
+        <v>1.09</v>
       </c>
       <c r="BG36" t="n">
-        <v>7</v>
+        <v>1.09</v>
       </c>
       <c r="BH36" t="n">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="BI36" t="n">
-        <v>2.46</v>
+        <v>1.04</v>
       </c>
       <c r="BJ36" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK36" t="n">
-        <v>3.55</v>
+        <v>1.04</v>
       </c>
       <c r="BL36" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="BM36" t="n">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BN36" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BO36" t="n">
-        <v>2.88</v>
+        <v>1.04</v>
       </c>
       <c r="BP36" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BQ36" t="n">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BR36" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS36" t="n">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT36" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BU36" t="n">
-        <v>2.88</v>
+        <v>1.04</v>
       </c>
       <c r="BV36" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BW36" t="n">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BX36" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BY36" t="n">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ36" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="CA36" t="n">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -9756,7 +9756,7 @@
         <v>4.4</v>
       </c>
       <c r="I37" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J37" t="n">
         <v>2.9</v>
@@ -9765,7 +9765,7 @@
         <v>3.15</v>
       </c>
       <c r="L37" t="n">
-        <v>1.56</v>
+        <v>1.68</v>
       </c>
       <c r="M37" t="n">
         <v>1.16</v>
@@ -9789,7 +9789,7 @@
         <v>7</v>
       </c>
       <c r="T37" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="U37" t="n">
         <v>1.62</v>
@@ -9810,7 +9810,7 @@
         <v>40</v>
       </c>
       <c r="AA37" t="n">
-        <v>170</v>
+        <v>700</v>
       </c>
       <c r="AB37" t="n">
         <v>6.8</v>
@@ -9822,7 +9822,7 @@
         <v>26</v>
       </c>
       <c r="AE37" t="n">
-        <v>120</v>
+        <v>700</v>
       </c>
       <c r="AF37" t="n">
         <v>13</v>
@@ -9831,28 +9831,28 @@
         <v>15.5</v>
       </c>
       <c r="AH37" t="n">
-        <v>950</v>
+        <v>32</v>
       </c>
       <c r="AI37" t="n">
-        <v>170</v>
+        <v>700</v>
       </c>
       <c r="AJ37" t="n">
-        <v>32</v>
+        <v>150</v>
       </c>
       <c r="AK37" t="n">
         <v>46</v>
       </c>
       <c r="AL37" t="n">
-        <v>100</v>
+        <v>540</v>
       </c>
       <c r="AM37" t="n">
-        <v>370</v>
+        <v>500</v>
       </c>
       <c r="AN37" t="n">
         <v>48</v>
       </c>
       <c r="AO37" t="n">
-        <v>230</v>
+        <v>700</v>
       </c>
       <c r="AP37" t="n">
         <v>6.2</v>
@@ -9861,7 +9861,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AR37" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AS37" t="n">
         <v>5.4</v>
@@ -9873,10 +9873,10 @@
         <v>6.4</v>
       </c>
       <c r="AV37" t="n">
-        <v>5.1</v>
+        <v>11.5</v>
       </c>
       <c r="AW37" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="AX37" t="n">
         <v>10</v>
@@ -9888,13 +9888,13 @@
         <v>4.7</v>
       </c>
       <c r="BA37" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BB37" t="n">
         <v>27</v>
       </c>
       <c r="BC37" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BD37" t="n">
         <v>5.2</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -10019,7 +10019,7 @@
         <v>3.45</v>
       </c>
       <c r="L38" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="M38" t="n">
         <v>1.1</v>
@@ -10034,7 +10034,7 @@
         <v>1.7</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R38" t="n">
         <v>1.26</v>
@@ -10088,7 +10088,7 @@
         <v>21</v>
       </c>
       <c r="AI38" t="n">
-        <v>100</v>
+        <v>380</v>
       </c>
       <c r="AJ38" t="n">
         <v>26</v>
@@ -10100,7 +10100,7 @@
         <v>60</v>
       </c>
       <c r="AM38" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AN38" t="n">
         <v>23</v>
@@ -10115,7 +10115,7 @@
         <v>11.5</v>
       </c>
       <c r="AR38" t="n">
-        <v>8.4</v>
+        <v>14.5</v>
       </c>
       <c r="AS38" t="n">
         <v>10.5</v>
@@ -10130,7 +10130,7 @@
         <v>16</v>
       </c>
       <c r="AW38" t="n">
-        <v>9.800000000000001</v>
+        <v>23</v>
       </c>
       <c r="AX38" t="n">
         <v>9.4</v>
@@ -10142,7 +10142,7 @@
         <v>17.5</v>
       </c>
       <c r="BA38" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="BB38" t="n">
         <v>21</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -10267,13 +10267,13 @@
         <v>3.3</v>
       </c>
       <c r="J39" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K39" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L39" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="M39" t="n">
         <v>1.1</v>
@@ -10282,7 +10282,7 @@
         <v>2.92</v>
       </c>
       <c r="O39" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P39" t="n">
         <v>1.64</v>
@@ -10294,7 +10294,7 @@
         <v>1.23</v>
       </c>
       <c r="S39" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="T39" t="n">
         <v>1.93</v>
@@ -10309,7 +10309,7 @@
         <v>1.58</v>
       </c>
       <c r="X39" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Y39" t="n">
         <v>12.5</v>
@@ -10372,7 +10372,7 @@
         <v>15</v>
       </c>
       <c r="AS39" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AT39" t="n">
         <v>7.4</v>
@@ -10384,7 +10384,7 @@
         <v>10</v>
       </c>
       <c r="AW39" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AX39" t="n">
         <v>11.5</v>
@@ -10396,25 +10396,25 @@
         <v>17.5</v>
       </c>
       <c r="BA39" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB39" t="n">
         <v>5.3</v>
       </c>
-      <c r="BB39" t="n">
-        <v>5</v>
-      </c>
       <c r="BC39" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BD39" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BE39" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BF39" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BG39" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BH39" t="n">
         <v>3</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -10518,7 +10518,7 @@
         <v>6</v>
       </c>
       <c r="I40" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J40" t="n">
         <v>4</v>
@@ -10527,31 +10527,31 @@
         <v>4.4</v>
       </c>
       <c r="L40" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="M40" t="n">
         <v>1.07</v>
       </c>
       <c r="N40" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="O40" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P40" t="n">
         <v>1.92</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="R40" t="n">
         <v>1.35</v>
       </c>
       <c r="S40" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="T40" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="U40" t="n">
         <v>1.92</v>
@@ -10572,7 +10572,7 @@
         <v>60</v>
       </c>
       <c r="AA40" t="n">
-        <v>220</v>
+        <v>700</v>
       </c>
       <c r="AB40" t="n">
         <v>9.199999999999999</v>
@@ -10584,10 +10584,10 @@
         <v>28</v>
       </c>
       <c r="AE40" t="n">
-        <v>110</v>
+        <v>700</v>
       </c>
       <c r="AF40" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG40" t="n">
         <v>10</v>
@@ -10596,25 +10596,25 @@
         <v>26</v>
       </c>
       <c r="AI40" t="n">
-        <v>110</v>
+        <v>700</v>
       </c>
       <c r="AJ40" t="n">
         <v>19</v>
       </c>
       <c r="AK40" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AL40" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AM40" t="n">
-        <v>160</v>
+        <v>700</v>
       </c>
       <c r="AN40" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AO40" t="n">
-        <v>150</v>
+        <v>700</v>
       </c>
       <c r="AP40" t="n">
         <v>11</v>
@@ -10623,10 +10623,10 @@
         <v>16.5</v>
       </c>
       <c r="AR40" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AS40" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AT40" t="n">
         <v>7</v>
@@ -10638,7 +10638,7 @@
         <v>21</v>
       </c>
       <c r="AW40" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX40" t="n">
         <v>8.6</v>
@@ -10650,7 +10650,7 @@
         <v>18.5</v>
       </c>
       <c r="BA40" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB40" t="n">
         <v>12.5</v>
@@ -10659,28 +10659,28 @@
         <v>14</v>
       </c>
       <c r="BD40" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BE40" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF40" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BG40" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH40" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BI40" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="BJ40" t="n">
         <v>11</v>
       </c>
       <c r="BK40" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL40" t="n">
         <v>1000</v>
@@ -10695,7 +10695,7 @@
         <v>3.35</v>
       </c>
       <c r="BP40" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BQ40" t="n">
         <v>6.4</v>
@@ -10710,7 +10710,7 @@
         <v>9.6</v>
       </c>
       <c r="BU40" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BV40" t="n">
         <v>1000</v>
@@ -10728,11 +10728,11 @@
         <v>22</v>
       </c>
       <c r="CA40" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -10763,22 +10763,22 @@
         </is>
       </c>
       <c r="F41" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="G41" t="n">
         <v>1.48</v>
-      </c>
-      <c r="G41" t="n">
-        <v>1.49</v>
       </c>
       <c r="H41" t="n">
         <v>7.4</v>
       </c>
       <c r="I41" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J41" t="n">
         <v>5.1</v>
       </c>
       <c r="K41" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L41" t="n">
         <v>1.3</v>
@@ -10820,7 +10820,7 @@
         <v>24</v>
       </c>
       <c r="Y41" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="Z41" t="n">
         <v>70</v>
@@ -10850,7 +10850,7 @@
         <v>22</v>
       </c>
       <c r="AI41" t="n">
-        <v>85</v>
+        <v>390</v>
       </c>
       <c r="AJ41" t="n">
         <v>13.5</v>
@@ -10880,7 +10880,7 @@
         <v>55</v>
       </c>
       <c r="AS41" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AT41" t="n">
         <v>9.4</v>
@@ -10892,7 +10892,7 @@
         <v>24</v>
       </c>
       <c r="AW41" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AX41" t="n">
         <v>9.199999999999999</v>
@@ -10904,7 +10904,7 @@
         <v>19</v>
       </c>
       <c r="BA41" t="n">
-        <v>18.5</v>
+        <v>28</v>
       </c>
       <c r="BB41" t="n">
         <v>12</v>
@@ -10916,13 +10916,13 @@
         <v>24</v>
       </c>
       <c r="BE41" t="n">
-        <v>19.5</v>
+        <v>29</v>
       </c>
       <c r="BF41" t="n">
         <v>5.3</v>
       </c>
       <c r="BG41" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BH41" t="n">
         <v>4.2</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -11044,7 +11044,7 @@
         <v>3.25</v>
       </c>
       <c r="O42" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P42" t="n">
         <v>1.78</v>
@@ -11059,7 +11059,7 @@
         <v>4.1</v>
       </c>
       <c r="T42" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="U42" t="n">
         <v>1.98</v>
@@ -11098,7 +11098,7 @@
         <v>12.5</v>
       </c>
       <c r="AG42" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH42" t="n">
         <v>21</v>
@@ -11134,7 +11134,7 @@
         <v>26</v>
       </c>
       <c r="AS42" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AT42" t="n">
         <v>7.6</v>
@@ -11152,7 +11152,7 @@
         <v>10.5</v>
       </c>
       <c r="AY42" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ42" t="n">
         <v>17.5</v>
@@ -11170,13 +11170,13 @@
         <v>36</v>
       </c>
       <c r="BE42" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF42" t="n">
         <v>16</v>
       </c>
       <c r="BG42" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BH42" t="n">
         <v>3.25</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -11274,7 +11274,7 @@
         <v>2</v>
       </c>
       <c r="G43" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H43" t="n">
         <v>4.3</v>
@@ -11283,10 +11283,10 @@
         <v>4.6</v>
       </c>
       <c r="J43" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K43" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L43" t="n">
         <v>1.44</v>
@@ -11295,34 +11295,34 @@
         <v>1.08</v>
       </c>
       <c r="N43" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O43" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P43" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R43" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="S43" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="T43" t="n">
         <v>1.9</v>
       </c>
       <c r="U43" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="V43" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W43" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="X43" t="n">
         <v>13</v>
@@ -11340,7 +11340,7 @@
         <v>8.4</v>
       </c>
       <c r="AC43" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD43" t="n">
         <v>18</v>
@@ -11349,7 +11349,7 @@
         <v>75</v>
       </c>
       <c r="AF43" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG43" t="n">
         <v>11</v>
@@ -11385,10 +11385,10 @@
         <v>13</v>
       </c>
       <c r="AR43" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS43" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT43" t="n">
         <v>7.4</v>
@@ -11430,7 +11430,7 @@
         <v>14.5</v>
       </c>
       <c r="BG43" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BH43" t="n">
         <v>3.3</v>
@@ -11448,19 +11448,19 @@
         <v>1000</v>
       </c>
       <c r="BM43" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BN43" t="n">
         <v>4.8</v>
       </c>
       <c r="BO43" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="BP43" t="n">
         <v>15.5</v>
       </c>
       <c r="BQ43" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BR43" t="n">
         <v>34</v>
@@ -11478,7 +11478,7 @@
         <v>1000</v>
       </c>
       <c r="BW43" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BX43" t="n">
         <v>1000</v>
@@ -11487,14 +11487,14 @@
         <v>8.6</v>
       </c>
       <c r="BZ43" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="CA43" t="n">
         <v>7.6</v>
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -11534,10 +11534,10 @@
         <v>3.6</v>
       </c>
       <c r="I44" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="J44" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K44" t="n">
         <v>4.2</v>
@@ -11573,7 +11573,7 @@
         <v>1.11</v>
       </c>
       <c r="V44" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="W44" t="n">
         <v>1.94</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -11788,10 +11788,10 @@
         <v>2.68</v>
       </c>
       <c r="I45" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="J45" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="K45" t="n">
         <v>3.95</v>
@@ -11824,10 +11824,10 @@
         <v>1.64</v>
       </c>
       <c r="U45" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V45" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W45" t="n">
         <v>1.56</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -12287,16 +12287,16 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="G47" t="n">
-        <v>2.32</v>
+        <v>2.44</v>
       </c>
       <c r="H47" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="I47" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="J47" t="n">
         <v>3.15</v>
@@ -12305,7 +12305,7 @@
         <v>3.35</v>
       </c>
       <c r="L47" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="M47" t="n">
         <v>1.11</v>
@@ -12317,7 +12317,7 @@
         <v>1.49</v>
       </c>
       <c r="P47" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="Q47" t="n">
         <v>2.46</v>
@@ -12335,10 +12335,10 @@
         <v>1.82</v>
       </c>
       <c r="V47" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W47" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="X47" t="n">
         <v>11.5</v>
@@ -12347,25 +12347,25 @@
         <v>13</v>
       </c>
       <c r="Z47" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AA47" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AB47" t="n">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC47" t="n">
         <v>7.6</v>
       </c>
       <c r="AD47" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE47" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AF47" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AG47" t="n">
         <v>12</v>
@@ -12377,10 +12377,10 @@
         <v>90</v>
       </c>
       <c r="AJ47" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AK47" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="AL47" t="n">
         <v>60</v>
@@ -12389,22 +12389,22 @@
         <v>200</v>
       </c>
       <c r="AN47" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AO47" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AP47" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AQ47" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AR47" t="n">
         <v>17.5</v>
       </c>
       <c r="AS47" t="n">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AT47" t="n">
         <v>6.6</v>
@@ -12416,7 +12416,7 @@
         <v>14.5</v>
       </c>
       <c r="AW47" t="n">
-        <v>8.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="AX47" t="n">
         <v>11</v>
@@ -12428,28 +12428,28 @@
         <v>19.5</v>
       </c>
       <c r="BA47" t="n">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="BB47" t="n">
         <v>20</v>
       </c>
       <c r="BC47" t="n">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="BD47" t="n">
         <v>40</v>
       </c>
       <c r="BE47" t="n">
-        <v>9.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="BF47" t="n">
         <v>20</v>
       </c>
       <c r="BG47" t="n">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="BH47" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="BI47" t="n">
         <v>2.42</v>
@@ -12458,7 +12458,7 @@
         <v>11</v>
       </c>
       <c r="BK47" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BL47" t="n">
         <v>1000</v>
@@ -12467,16 +12467,16 @@
         <v>15</v>
       </c>
       <c r="BN47" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BO47" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="BP47" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BQ47" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR47" t="n">
         <v>40</v>
@@ -12485,22 +12485,22 @@
         <v>11.5</v>
       </c>
       <c r="BT47" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BU47" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BV47" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BW47" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BX47" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY47" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BZ47" t="n">
         <v>1000</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -12640,7 +12640,7 @@
         <v>110</v>
       </c>
       <c r="AM48" t="n">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AN48" t="n">
         <v>80</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -12795,67 +12795,67 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="G49" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="H49" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="I49" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="J49" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="K49" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="L49" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M49" t="n">
         <v>1.05</v>
       </c>
       <c r="N49" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="O49" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P49" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="R49" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="S49" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="T49" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="U49" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="V49" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W49" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="X49" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Y49" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="Z49" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AA49" t="n">
         <v>1000</v>
@@ -12864,28 +12864,28 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AC49" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD49" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AE49" t="n">
         <v>1000</v>
       </c>
       <c r="AF49" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AG49" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH49" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI49" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ49" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AK49" t="n">
         <v>15.5</v>
@@ -12897,64 +12897,64 @@
         <v>130</v>
       </c>
       <c r="AN49" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AO49" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AP49" t="n">
         <v>17.5</v>
       </c>
       <c r="AQ49" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AR49" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AS49" t="n">
         <v>48</v>
       </c>
       <c r="AT49" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU49" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AV49" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AW49" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AX49" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY49" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ49" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA49" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BB49" t="n">
         <v>12</v>
       </c>
       <c r="BC49" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BD49" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="BE49" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BF49" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BG49" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BH49" t="n">
         <v>4.1</v>
@@ -12963,16 +12963,16 @@
         <v>3.2</v>
       </c>
       <c r="BJ49" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK49" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BL49" t="n">
         <v>1000</v>
       </c>
       <c r="BM49" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BN49" t="n">
         <v>4.2</v>
@@ -12984,41 +12984,41 @@
         <v>9.6</v>
       </c>
       <c r="BQ49" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BR49" t="n">
         <v>25</v>
       </c>
       <c r="BS49" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BT49" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BU49" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BV49" t="n">
         <v>1000</v>
       </c>
       <c r="BW49" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX49" t="n">
         <v>1000</v>
       </c>
       <c r="BY49" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ49" t="n">
         <v>16</v>
       </c>
       <c r="CA49" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -13055,16 +13055,16 @@
         <v>4.5</v>
       </c>
       <c r="H50" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="I50" t="n">
         <v>1.99</v>
       </c>
       <c r="J50" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K50" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L50" t="n">
         <v>1.29</v>
@@ -13214,7 +13214,7 @@
         <v>3.8</v>
       </c>
       <c r="BI50" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="BJ50" t="n">
         <v>9.4</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -13303,7 +13303,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="G51" t="n">
         <v>2.06</v>
@@ -13312,10 +13312,10 @@
         <v>3.85</v>
       </c>
       <c r="I51" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J51" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K51" t="n">
         <v>3.9</v>
@@ -13336,22 +13336,22 @@
         <v>2.02</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="R51" t="n">
         <v>1.41</v>
       </c>
       <c r="S51" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="T51" t="n">
         <v>1.68</v>
       </c>
       <c r="U51" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V51" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W51" t="n">
         <v>1.94</v>
@@ -13375,7 +13375,7 @@
         <v>8.6</v>
       </c>
       <c r="AD51" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE51" t="n">
         <v>60</v>
@@ -13408,7 +13408,7 @@
         <v>13.5</v>
       </c>
       <c r="AO51" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AP51" t="n">
         <v>13.5</v>
@@ -13417,10 +13417,10 @@
         <v>13.5</v>
       </c>
       <c r="AR51" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AS51" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT51" t="n">
         <v>9.4</v>
@@ -13453,10 +13453,10 @@
         <v>17.5</v>
       </c>
       <c r="BD51" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BE51" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF51" t="n">
         <v>10.5</v>
@@ -13468,65 +13468,65 @@
         <v>3.85</v>
       </c>
       <c r="BI51" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="BJ51" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BK51" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BL51" t="n">
         <v>1000</v>
       </c>
       <c r="BM51" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BN51" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BO51" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BP51" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BQ51" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BR51" t="n">
         <v>27</v>
       </c>
       <c r="BS51" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BT51" t="n">
         <v>8</v>
       </c>
       <c r="BU51" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BV51" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BW51" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BX51" t="n">
         <v>42</v>
       </c>
       <c r="BY51" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ51" t="n">
         <v>22</v>
       </c>
       <c r="CA51" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -13722,13 +13722,13 @@
         <v>3.7</v>
       </c>
       <c r="BI52" t="n">
-        <v>2.86</v>
+        <v>3.15</v>
       </c>
       <c r="BJ52" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BK52" t="n">
-        <v>6.8</v>
+        <v>5</v>
       </c>
       <c r="BL52" t="n">
         <v>1000</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>
@@ -13820,19 +13820,19 @@
         <v>2.34</v>
       </c>
       <c r="I53" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="J53" t="n">
         <v>3.9</v>
       </c>
       <c r="K53" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L53" t="n">
         <v>1.29</v>
       </c>
       <c r="M53" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N53" t="n">
         <v>5.7</v>
@@ -13859,7 +13859,7 @@
         <v>2.72</v>
       </c>
       <c r="V53" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="W53" t="n">
         <v>1.47</v>
@@ -13871,7 +13871,7 @@
         <v>17.5</v>
       </c>
       <c r="Z53" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AA53" t="n">
         <v>34</v>
@@ -13880,7 +13880,7 @@
         <v>20</v>
       </c>
       <c r="AC53" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD53" t="n">
         <v>12.5</v>
@@ -13892,7 +13892,7 @@
         <v>27</v>
       </c>
       <c r="AG53" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH53" t="n">
         <v>15</v>
@@ -13916,7 +13916,7 @@
         <v>21</v>
       </c>
       <c r="AO53" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AP53" t="n">
         <v>21</v>
@@ -13976,10 +13976,10 @@
         <v>5</v>
       </c>
       <c r="BI53" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BJ53" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK53" t="n">
         <v>1.04</v>
@@ -14009,13 +14009,13 @@
         <v>1.04</v>
       </c>
       <c r="BT53" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BU53" t="n">
         <v>4.5</v>
       </c>
       <c r="BV53" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="BW53" t="n">
         <v>1.04</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-07-16 16:29:12</t>
+          <t>2026-07-16 18:49:10</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-17.xlsx
@@ -860,7 +860,7 @@
         <v>3.75</v>
       </c>
       <c r="G2" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="H2" t="n">
         <v>2.12</v>
@@ -881,28 +881,28 @@
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="O2" t="n">
         <v>1.33</v>
       </c>
       <c r="P2" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="R2" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S2" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="T2" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="U2" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V2" t="n">
         <v>1.86</v>
@@ -911,7 +911,7 @@
         <v>1.34</v>
       </c>
       <c r="X2" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="Y2" t="n">
         <v>10</v>
@@ -926,7 +926,7 @@
         <v>14.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="AD2" t="n">
         <v>10.5</v>
@@ -935,28 +935,28 @@
         <v>23</v>
       </c>
       <c r="AF2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG2" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH2" t="n">
         <v>20</v>
       </c>
       <c r="AI2" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AJ2" t="n">
         <v>90</v>
       </c>
       <c r="AK2" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL2" t="n">
         <v>55</v>
       </c>
-      <c r="AL2" t="n">
-        <v>65</v>
-      </c>
       <c r="AM2" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN2" t="n">
         <v>55</v>
@@ -965,16 +965,16 @@
         <v>17.5</v>
       </c>
       <c r="AP2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR2" t="n">
         <v>11.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AT2" t="n">
         <v>12.5</v>
@@ -992,7 +992,7 @@
         <v>24</v>
       </c>
       <c r="AY2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AZ2" t="n">
         <v>15.5</v>
@@ -1001,19 +1001,19 @@
         <v>30</v>
       </c>
       <c r="BB2" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>6.6</v>
+        <v>38</v>
       </c>
       <c r="BD2" t="n">
-        <v>6.8</v>
+        <v>44</v>
       </c>
       <c r="BE2" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BF2" t="n">
-        <v>6.8</v>
+        <v>9.6</v>
       </c>
       <c r="BG2" t="n">
         <v>14.5</v>
@@ -1028,16 +1028,16 @@
         <v>9.6</v>
       </c>
       <c r="BK2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="BN2" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BO2" t="n">
         <v>5</v>
@@ -1046,41 +1046,41 @@
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BR2" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BT2" t="n">
         <v>4.9</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="BV2" t="n">
         <v>15.5</v>
       </c>
       <c r="BW2" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
+        <v>11</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA2" t="n">
         <v>10.5</v>
       </c>
-      <c r="BZ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>10</v>
-      </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -1114,10 +1114,10 @@
         <v>2.06</v>
       </c>
       <c r="G3" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="H3" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="I3" t="n">
         <v>4.1</v>
@@ -1147,88 +1147,88 @@
         <v>1.87</v>
       </c>
       <c r="R3" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S3" t="n">
         <v>3.2</v>
       </c>
       <c r="T3" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U3" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V3" t="n">
         <v>1.32</v>
       </c>
       <c r="W3" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="X3" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="AA3" t="n">
         <v>90</v>
       </c>
       <c r="AB3" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AF3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH3" t="n">
         <v>17</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>17.5</v>
       </c>
       <c r="AI3" t="n">
         <v>55</v>
       </c>
       <c r="AJ3" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AK3" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AL3" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AM3" t="n">
-        <v>110</v>
+        <v>320</v>
       </c>
       <c r="AN3" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AP3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AR3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.5</v>
+        <v>50</v>
       </c>
       <c r="AT3" t="n">
         <v>8.800000000000001</v>
@@ -1237,58 +1237,58 @@
         <v>7.2</v>
       </c>
       <c r="AV3" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.7</v>
+        <v>27</v>
       </c>
       <c r="AX3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AY3" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.7</v>
+        <v>30</v>
       </c>
       <c r="BB3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BC3" t="n">
-        <v>16</v>
+        <v>19.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.5</v>
+        <v>60</v>
       </c>
       <c r="BF3" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="BJ3" t="n">
         <v>9.4</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN3" t="n">
         <v>5.1</v>
@@ -1300,41 +1300,41 @@
         <v>15.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BR3" t="n">
         <v>28</v>
       </c>
       <c r="BS3" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BT3" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BV3" t="n">
         <v>29</v>
       </c>
       <c r="BW3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY3" t="n">
         <v>10</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>40</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>11</v>
       </c>
       <c r="BZ3" t="n">
         <v>24</v>
       </c>
       <c r="CA3" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -1368,19 +1368,19 @@
         <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="H4" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="I4" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="J4" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L4" t="n">
         <v>1.38</v>
@@ -1389,16 +1389,16 @@
         <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="O4" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P4" t="n">
         <v>2.08</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="R4" t="n">
         <v>1.42</v>
@@ -1410,46 +1410,46 @@
         <v>1.71</v>
       </c>
       <c r="U4" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V4" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="W4" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X4" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>23</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE4" t="n">
         <v>20</v>
       </c>
-      <c r="Y4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>26</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>23</v>
-      </c>
       <c r="AF4" t="n">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="AG4" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AH4" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AI4" t="n">
         <v>34</v>
@@ -1458,79 +1458,79 @@
         <v>100</v>
       </c>
       <c r="AK4" t="n">
-        <v>320</v>
+        <v>120</v>
       </c>
       <c r="AL4" t="n">
-        <v>320</v>
+        <v>55</v>
       </c>
       <c r="AM4" t="n">
-        <v>100</v>
+        <v>390</v>
       </c>
       <c r="AN4" t="n">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="AO4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AP4" t="n">
         <v>14.5</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>15</v>
       </c>
       <c r="AQ4" t="n">
         <v>9.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AS4" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AT4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AU4" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AX4" t="n">
         <v>13</v>
       </c>
       <c r="AY4" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA4" t="n">
         <v>20</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BC4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BE4" t="n">
         <v>5.4</v>
       </c>
-      <c r="BD4" t="n">
+      <c r="BF4" t="n">
         <v>5.1</v>
       </c>
-      <c r="BE4" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BG4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BH4" t="n">
         <v>3.6</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="BJ4" t="n">
         <v>9.6</v>
@@ -1548,10 +1548,10 @@
         <v>7.8</v>
       </c>
       <c r="BO4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BP4" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
         <v>10</v>
@@ -1578,17 +1578,17 @@
         <v>27</v>
       </c>
       <c r="BY4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BZ4" t="n">
         <v>23</v>
       </c>
       <c r="CA4" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
         <v>1.79</v>
       </c>
       <c r="I5" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="J5" t="n">
         <v>4.1</v>
@@ -1646,16 +1646,16 @@
         <v>5.3</v>
       </c>
       <c r="O5" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P5" t="n">
         <v>2.52</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="R5" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="S5" t="n">
         <v>2.6</v>
@@ -1664,13 +1664,13 @@
         <v>1.63</v>
       </c>
       <c r="U5" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="V5" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="W5" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="X5" t="n">
         <v>34</v>
@@ -1697,13 +1697,13 @@
         <v>16.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AG5" t="n">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="AH5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI5" t="n">
         <v>44</v>
@@ -1712,10 +1712,10 @@
         <v>490</v>
       </c>
       <c r="AK5" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="AL5" t="n">
-        <v>190</v>
+        <v>100</v>
       </c>
       <c r="AM5" t="n">
         <v>190</v>
@@ -1733,7 +1733,7 @@
         <v>11</v>
       </c>
       <c r="AR5" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AS5" t="n">
         <v>16.5</v>
@@ -1745,13 +1745,13 @@
         <v>9</v>
       </c>
       <c r="AV5" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AW5" t="n">
         <v>14.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AY5" t="n">
         <v>15.5</v>
@@ -1760,89 +1760,89 @@
         <v>14</v>
       </c>
       <c r="BA5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BB5" t="n">
         <v>36</v>
       </c>
       <c r="BC5" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="BD5" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BE5" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="BF5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BG5" t="n">
         <v>7.6</v>
       </c>
       <c r="BH5" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.02</v>
+        <v>3.4</v>
       </c>
       <c r="BJ5" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.75</v>
+        <v>3.7</v>
       </c>
       <c r="BL5" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BM5" t="n">
-        <v>2.04</v>
+        <v>5.5</v>
       </c>
       <c r="BN5" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="BO5" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>38</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>5</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>44</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BT5" t="n">
         <v>5.4</v>
       </c>
-      <c r="BP5" t="n">
-        <v>48</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>50</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BU5" t="n">
-        <v>3.35</v>
+        <v>4.3</v>
       </c>
       <c r="BV5" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.81</v>
+        <v>4</v>
       </c>
       <c r="BX5" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.91</v>
+        <v>4.7</v>
       </c>
       <c r="BZ5" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.86</v>
+        <v>4.3</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -1876,19 +1876,19 @@
         <v>4.2</v>
       </c>
       <c r="G6" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="I6" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="J6" t="n">
         <v>3.15</v>
       </c>
       <c r="K6" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L6" t="n">
         <v>1.49</v>
@@ -1912,7 +1912,7 @@
         <v>1.23</v>
       </c>
       <c r="S6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T6" t="n">
         <v>1.99</v>
@@ -1921,73 +1921,73 @@
         <v>1.83</v>
       </c>
       <c r="V6" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="W6" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="X6" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Z6" t="n">
         <v>12.5</v>
       </c>
-      <c r="Y6" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>14.5</v>
-      </c>
       <c r="AA6" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AB6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AC6" t="n">
         <v>8</v>
       </c>
       <c r="AD6" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="AF6" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AG6" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AH6" t="n">
         <v>27</v>
       </c>
       <c r="AI6" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AJ6" t="n">
         <v>500</v>
       </c>
       <c r="AK6" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AL6" t="n">
         <v>500</v>
       </c>
       <c r="AM6" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN6" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO6" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AP6" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ6" t="n">
         <v>6.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AS6" t="n">
         <v>18.5</v>
@@ -1996,43 +1996,43 @@
         <v>9.6</v>
       </c>
       <c r="AU6" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AW6" t="n">
         <v>18.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="AY6" t="n">
         <v>13.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.5</v>
+        <v>7.2</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.5</v>
+        <v>7.8</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.4</v>
+        <v>7.6</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.5</v>
+        <v>7.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.6</v>
+        <v>8</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.5</v>
+        <v>7.8</v>
       </c>
       <c r="BG6" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="BH6" t="n">
         <v>3.05</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -2130,16 +2130,16 @@
         <v>3.7</v>
       </c>
       <c r="G7" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="H7" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="I7" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="J7" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
         <v>3.3</v>
@@ -2166,7 +2166,7 @@
         <v>1.19</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T7" t="n">
         <v>2.06</v>
@@ -2175,13 +2175,13 @@
         <v>1.77</v>
       </c>
       <c r="V7" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="W7" t="n">
         <v>1.3</v>
       </c>
       <c r="X7" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="Y7" t="n">
         <v>7.6</v>
@@ -2205,10 +2205,10 @@
         <v>34</v>
       </c>
       <c r="AF7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG7" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AH7" t="n">
         <v>24</v>
@@ -2223,7 +2223,7 @@
         <v>80</v>
       </c>
       <c r="AL7" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AM7" t="n">
         <v>500</v>
@@ -2235,7 +2235,7 @@
         <v>34</v>
       </c>
       <c r="AP7" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AQ7" t="n">
         <v>6.2</v>
@@ -2268,25 +2268,25 @@
         <v>19</v>
       </c>
       <c r="BA7" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BB7" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BC7" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BG7" t="n">
         <v>7.4</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>6.6</v>
       </c>
       <c r="BH7" t="n">
         <v>2.84</v>
@@ -2298,7 +2298,7 @@
         <v>12</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
@@ -2307,16 +2307,16 @@
         <v>10</v>
       </c>
       <c r="BN7" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BO7" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BP7" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BQ7" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BR7" t="n">
         <v>65</v>
@@ -2325,13 +2325,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BT7" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BU7" t="n">
         <v>3.9</v>
       </c>
       <c r="BV7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BW7" t="n">
         <v>7</v>
@@ -2346,11 +2346,11 @@
         <v>48</v>
       </c>
       <c r="CA7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="G8" t="n">
         <v>1.39</v>
@@ -2390,16 +2390,16 @@
         <v>9</v>
       </c>
       <c r="I8" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="J8" t="n">
         <v>5.7</v>
       </c>
       <c r="K8" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="L8" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="M8" t="n">
         <v>1.03</v>
@@ -2411,7 +2411,7 @@
         <v>1.19</v>
       </c>
       <c r="P8" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="Q8" t="n">
         <v>1.57</v>
@@ -2420,13 +2420,13 @@
         <v>1.64</v>
       </c>
       <c r="S8" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="T8" t="n">
         <v>1.92</v>
       </c>
       <c r="U8" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V8" t="n">
         <v>1.11</v>
@@ -2435,10 +2435,10 @@
         <v>3.55</v>
       </c>
       <c r="X8" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="Y8" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="Z8" t="n">
         <v>1000</v>
@@ -2453,22 +2453,22 @@
         <v>13.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="AE8" t="n">
         <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG8" t="n">
         <v>11</v>
       </c>
       <c r="AH8" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="AI8" t="n">
-        <v>120</v>
+        <v>230</v>
       </c>
       <c r="AJ8" t="n">
         <v>11.5</v>
@@ -2480,13 +2480,13 @@
         <v>32</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN8" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AO8" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AP8" t="n">
         <v>22</v>
@@ -2495,7 +2495,7 @@
         <v>30</v>
       </c>
       <c r="AR8" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AS8" t="n">
         <v>50</v>
@@ -2507,16 +2507,16 @@
         <v>12</v>
       </c>
       <c r="AV8" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AW8" t="n">
         <v>40</v>
       </c>
       <c r="AX8" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY8" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ8" t="n">
         <v>22</v>
@@ -2528,7 +2528,7 @@
         <v>10.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD8" t="n">
         <v>26</v>
@@ -2537,74 +2537,74 @@
         <v>40</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BH8" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BI8" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="BJ8" t="n">
         <v>11.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BN8" t="n">
         <v>4.1</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="BP8" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BQ8" t="n">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="BR8" t="n">
         <v>22</v>
       </c>
       <c r="BS8" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BT8" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BU8" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ8" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="CA8" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="G9" t="n">
         <v>1.48</v>
@@ -2647,22 +2647,22 @@
         <v>8</v>
       </c>
       <c r="J9" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="K9" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L9" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="M9" t="n">
         <v>1.02</v>
       </c>
       <c r="N9" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="O9" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P9" t="n">
         <v>3.1</v>
@@ -2674,13 +2674,13 @@
         <v>1.91</v>
       </c>
       <c r="S9" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="T9" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="U9" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="V9" t="n">
         <v>1.14</v>
@@ -2695,25 +2695,25 @@
         <v>40</v>
       </c>
       <c r="Z9" t="n">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AA9" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AB9" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD9" t="n">
         <v>32</v>
       </c>
       <c r="AE9" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AF9" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AG9" t="n">
         <v>11</v>
@@ -2722,10 +2722,10 @@
         <v>18.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AJ9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK9" t="n">
         <v>13.5</v>
@@ -2734,7 +2734,7 @@
         <v>24</v>
       </c>
       <c r="AM9" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN9" t="n">
         <v>4.3</v>
@@ -2746,13 +2746,13 @@
         <v>30</v>
       </c>
       <c r="AQ9" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AR9" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AS9" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AT9" t="n">
         <v>13</v>
@@ -2764,7 +2764,7 @@
         <v>24</v>
       </c>
       <c r="AW9" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AX9" t="n">
         <v>11</v>
@@ -2776,7 +2776,7 @@
         <v>17</v>
       </c>
       <c r="BA9" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BB9" t="n">
         <v>14</v>
@@ -2788,7 +2788,7 @@
         <v>20</v>
       </c>
       <c r="BE9" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BF9" t="n">
         <v>4.1</v>
@@ -2800,7 +2800,7 @@
         <v>5.5</v>
       </c>
       <c r="BI9" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BJ9" t="n">
         <v>10</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -2889,16 +2889,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="G10" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="H10" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="I10" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="J10" t="n">
         <v>4.1</v>
@@ -2919,40 +2919,40 @@
         <v>1.12</v>
       </c>
       <c r="P10" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="R10" t="n">
         <v>1.94</v>
       </c>
       <c r="S10" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="T10" t="n">
         <v>1.4</v>
       </c>
       <c r="U10" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="V10" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="W10" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="X10" t="n">
         <v>40</v>
       </c>
       <c r="Y10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Z10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AA10" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AB10" t="n">
         <v>24</v>
@@ -2961,13 +2961,13 @@
         <v>11</v>
       </c>
       <c r="AD10" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE10" t="n">
         <v>23</v>
       </c>
       <c r="AF10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG10" t="n">
         <v>14</v>
@@ -2976,97 +2976,97 @@
         <v>13.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AJ10" t="n">
-        <v>120</v>
+        <v>42</v>
       </c>
       <c r="AK10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL10" t="n">
         <v>25</v>
       </c>
       <c r="AM10" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AN10" t="n">
         <v>11</v>
       </c>
       <c r="AO10" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AP10" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AQ10" t="n">
         <v>21</v>
       </c>
       <c r="AR10" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AT10" t="n">
         <v>20</v>
       </c>
       <c r="AU10" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AV10" t="n">
         <v>12</v>
       </c>
       <c r="AW10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY10" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AZ10" t="n">
         <v>11.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BB10" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="BC10" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BD10" t="n">
         <v>21</v>
       </c>
       <c r="BE10" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="BF10" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH10" t="n">
         <v>5.4</v>
       </c>
       <c r="BI10" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="BJ10" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BL10" t="n">
         <v>55</v>
       </c>
       <c r="BM10" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BN10" t="n">
         <v>6.8</v>
@@ -3078,31 +3078,31 @@
         <v>17</v>
       </c>
       <c r="BQ10" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BR10" t="n">
         <v>21</v>
       </c>
       <c r="BS10" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BT10" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BU10" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="BV10" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BW10" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BX10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BY10" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="G11" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="H11" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I11" t="n">
         <v>3.35</v>
       </c>
       <c r="J11" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K11" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L11" t="n">
         <v>1.47</v>
@@ -3179,10 +3179,10 @@
         <v>2.22</v>
       </c>
       <c r="R11" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S11" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T11" t="n">
         <v>1.9</v>
@@ -3191,7 +3191,7 @@
         <v>1.93</v>
       </c>
       <c r="V11" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W11" t="n">
         <v>1.58</v>
@@ -3206,7 +3206,7 @@
         <v>22</v>
       </c>
       <c r="AA11" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AB11" t="n">
         <v>9.4</v>
@@ -3218,7 +3218,7 @@
         <v>15</v>
       </c>
       <c r="AE11" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AF11" t="n">
         <v>17</v>
@@ -3230,37 +3230,37 @@
         <v>21</v>
       </c>
       <c r="AI11" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ11" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AK11" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AL11" t="n">
         <v>55</v>
       </c>
       <c r="AM11" t="n">
-        <v>160</v>
+        <v>580</v>
       </c>
       <c r="AN11" t="n">
         <v>34</v>
       </c>
       <c r="AO11" t="n">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="AP11" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ11" t="n">
         <v>9</v>
       </c>
       <c r="AR11" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>40</v>
+        <v>7.8</v>
       </c>
       <c r="AT11" t="n">
         <v>7.8</v>
@@ -3269,13 +3269,13 @@
         <v>6.4</v>
       </c>
       <c r="AV11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AW11" t="n">
-        <v>7.2</v>
+        <v>34</v>
       </c>
       <c r="AX11" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY11" t="n">
         <v>10</v>
@@ -3284,25 +3284,25 @@
         <v>16.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="BB11" t="n">
-        <v>7.2</v>
+        <v>32</v>
       </c>
       <c r="BC11" t="n">
-        <v>6.6</v>
+        <v>14.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BF11" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BG11" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="BH11" t="n">
         <v>3.1</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
         <v>1.63</v>
       </c>
       <c r="J12" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K12" t="n">
         <v>5.2</v>
@@ -3460,10 +3460,10 @@
         <v>13</v>
       </c>
       <c r="AA12" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AB12" t="n">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="AC12" t="n">
         <v>11.5</v>
@@ -3490,13 +3490,13 @@
         <v>700</v>
       </c>
       <c r="AK12" t="n">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="AL12" t="n">
-        <v>700</v>
+        <v>320</v>
       </c>
       <c r="AM12" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN12" t="n">
         <v>700</v>
@@ -3538,22 +3538,22 @@
         <v>16.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>9.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="BB12" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BC12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD12" t="n">
         <v>7.2</v>
       </c>
-      <c r="BD12" t="n">
-        <v>7</v>
-      </c>
       <c r="BE12" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF12" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BG12" t="n">
         <v>5.6</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -3651,22 +3651,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="G13" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="H13" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I13" t="n">
         <v>11</v>
       </c>
       <c r="J13" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="K13" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
@@ -3681,7 +3681,7 @@
         <v>1.1</v>
       </c>
       <c r="P13" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="Q13" t="n">
         <v>1.31</v>
@@ -3693,7 +3693,7 @@
         <v>1.78</v>
       </c>
       <c r="T13" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="U13" t="n">
         <v>2.28</v>
@@ -3702,7 +3702,7 @@
         <v>1.1</v>
       </c>
       <c r="W13" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="X13" t="n">
         <v>60</v>
@@ -3720,34 +3720,34 @@
         <v>19.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AE13" t="n">
-        <v>120</v>
+        <v>260</v>
       </c>
       <c r="AF13" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AG13" t="n">
         <v>14</v>
       </c>
       <c r="AH13" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>200</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AL13" t="n">
         <v>27</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>15</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>29</v>
       </c>
       <c r="AM13" t="n">
         <v>80</v>
@@ -3759,16 +3759,16 @@
         <v>90</v>
       </c>
       <c r="AP13" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="AQ13" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="AR13" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="AS13" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="AT13" t="n">
         <v>13</v>
@@ -3777,10 +3777,10 @@
         <v>13</v>
       </c>
       <c r="AV13" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="AW13" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="AX13" t="n">
         <v>10.5</v>
@@ -3792,7 +3792,7 @@
         <v>17.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB13" t="n">
         <v>11</v>
@@ -3804,13 +3804,13 @@
         <v>21</v>
       </c>
       <c r="BE13" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BF13" t="n">
         <v>3</v>
       </c>
       <c r="BG13" t="n">
-        <v>6.4</v>
+        <v>15</v>
       </c>
       <c r="BH13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -3920,7 +3920,7 @@
         <v>3.75</v>
       </c>
       <c r="K14" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L14" t="n">
         <v>1.4</v>
@@ -3956,7 +3956,7 @@
         <v>2.32</v>
       </c>
       <c r="W14" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="X14" t="n">
         <v>17.5</v>
@@ -3983,10 +3983,10 @@
         <v>23</v>
       </c>
       <c r="AF14" t="n">
-        <v>500</v>
+        <v>230</v>
       </c>
       <c r="AG14" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AH14" t="n">
         <v>27</v>
@@ -3998,19 +3998,19 @@
         <v>700</v>
       </c>
       <c r="AK14" t="n">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="AL14" t="n">
-        <v>700</v>
+        <v>320</v>
       </c>
       <c r="AM14" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN14" t="n">
         <v>700</v>
       </c>
       <c r="AO14" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AP14" t="n">
         <v>12</v>
@@ -4049,19 +4049,19 @@
         <v>28</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BF14" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BG14" t="n">
         <v>9.6</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -4165,13 +4165,13 @@
         <v>1.98</v>
       </c>
       <c r="H15" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I15" t="n">
         <v>4.2</v>
       </c>
       <c r="J15" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K15" t="n">
         <v>4.1</v>
@@ -4189,7 +4189,7 @@
         <v>1.23</v>
       </c>
       <c r="P15" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="Q15" t="n">
         <v>1.69</v>
@@ -4198,13 +4198,13 @@
         <v>1.53</v>
       </c>
       <c r="S15" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="T15" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U15" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="V15" t="n">
         <v>1.31</v>
@@ -4219,7 +4219,7 @@
         <v>19</v>
       </c>
       <c r="Z15" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AA15" t="n">
         <v>85</v>
@@ -4246,7 +4246,7 @@
         <v>16</v>
       </c>
       <c r="AI15" t="n">
-        <v>160</v>
+        <v>95</v>
       </c>
       <c r="AJ15" t="n">
         <v>23</v>
@@ -4255,7 +4255,7 @@
         <v>18.5</v>
       </c>
       <c r="AL15" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM15" t="n">
         <v>75</v>
@@ -4315,7 +4315,7 @@
         <v>60</v>
       </c>
       <c r="BF15" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG15" t="n">
         <v>30</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -4419,19 +4419,19 @@
         <v>1.94</v>
       </c>
       <c r="H16" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I16" t="n">
         <v>4.4</v>
       </c>
       <c r="J16" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K16" t="n">
         <v>4.2</v>
       </c>
       <c r="L16" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="M16" t="n">
         <v>1.05</v>
@@ -4440,10 +4440,10 @@
         <v>4.9</v>
       </c>
       <c r="O16" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q16" t="n">
         <v>1.7</v>
@@ -4458,7 +4458,7 @@
         <v>1.67</v>
       </c>
       <c r="U16" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="V16" t="n">
         <v>1.29</v>
@@ -4470,13 +4470,13 @@
         <v>21</v>
       </c>
       <c r="Y16" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Z16" t="n">
         <v>36</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>490</v>
       </c>
       <c r="AB16" t="n">
         <v>11.5</v>
@@ -4488,10 +4488,10 @@
         <v>17.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AF16" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AG16" t="n">
         <v>10.5</v>
@@ -4509,16 +4509,16 @@
         <v>18</v>
       </c>
       <c r="AL16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM16" t="n">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AN16" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AO16" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AP16" t="n">
         <v>18</v>
@@ -4536,7 +4536,7 @@
         <v>10.5</v>
       </c>
       <c r="AU16" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV16" t="n">
         <v>15.5</v>
@@ -4602,7 +4602,7 @@
         <v>13</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.7</v>
+        <v>9.6</v>
       </c>
       <c r="BR16" t="n">
         <v>24</v>
@@ -4632,11 +4632,11 @@
         <v>18.5</v>
       </c>
       <c r="CA16" t="n">
-        <v>6.4</v>
+        <v>13</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -4667,22 +4667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="G17" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="H17" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="I17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J17" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="L17" t="n">
         <v>1.17</v>
@@ -4691,28 +4691,28 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="O17" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="P17" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="R17" t="n">
         <v>2.26</v>
       </c>
       <c r="S17" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="T17" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="U17" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V17" t="n">
         <v>1.04</v>
@@ -4721,7 +4721,7 @@
         <v>1.01</v>
       </c>
       <c r="X17" t="n">
-        <v>940</v>
+        <v>310</v>
       </c>
       <c r="Y17" t="n">
         <v>940</v>
@@ -4739,7 +4739,7 @@
         <v>25</v>
       </c>
       <c r="AD17" t="n">
-        <v>830</v>
+        <v>500</v>
       </c>
       <c r="AE17" t="n">
         <v>1000</v>
@@ -4748,10 +4748,10 @@
         <v>11</v>
       </c>
       <c r="AG17" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH17" t="n">
-        <v>36</v>
+        <v>90</v>
       </c>
       <c r="AI17" t="n">
         <v>1000</v>
@@ -4760,16 +4760,16 @@
         <v>10.5</v>
       </c>
       <c r="AK17" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AL17" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="AM17" t="n">
-        <v>1000</v>
+        <v>490</v>
       </c>
       <c r="AN17" t="n">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="AO17" t="n">
         <v>1000</v>
@@ -4784,16 +4784,16 @@
         <v>46</v>
       </c>
       <c r="AS17" t="n">
-        <v>60</v>
+        <v>18.5</v>
       </c>
       <c r="AT17" t="n">
         <v>15</v>
       </c>
       <c r="AU17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV17" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="AW17" t="n">
         <v>48</v>
@@ -4802,16 +4802,16 @@
         <v>10</v>
       </c>
       <c r="AY17" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ17" t="n">
         <v>23</v>
       </c>
       <c r="BA17" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BB17" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC17" t="n">
         <v>11.5</v>
@@ -4823,7 +4823,7 @@
         <v>42</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="BG17" t="n">
         <v>48</v>
@@ -4835,16 +4835,16 @@
         <v>5.1</v>
       </c>
       <c r="BJ17" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BK17" t="n">
-        <v>9.6</v>
+        <v>7</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>7.8</v>
+        <v>14</v>
       </c>
       <c r="BN17" t="n">
         <v>4.2</v>
@@ -4853,44 +4853,44 @@
         <v>3.8</v>
       </c>
       <c r="BP17" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BR17" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BS17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BT17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BU17" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>7.8</v>
+        <v>14</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>7.6</v>
+        <v>13.5</v>
       </c>
       <c r="BZ17" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="CA17" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
         <v>1.13</v>
       </c>
       <c r="S18" t="n">
-        <v>6.2</v>
+        <v>1.05</v>
       </c>
       <c r="T18" t="n">
         <v>2.28</v>
@@ -4984,7 +4984,7 @@
         <v>18.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>500</v>
+        <v>320</v>
       </c>
       <c r="AB18" t="n">
         <v>8.4</v>
@@ -5005,16 +5005,16 @@
         <v>17</v>
       </c>
       <c r="AH18" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AI18" t="n">
         <v>540</v>
       </c>
       <c r="AJ18" t="n">
-        <v>500</v>
+        <v>420</v>
       </c>
       <c r="AK18" t="n">
-        <v>500</v>
+        <v>440</v>
       </c>
       <c r="AL18" t="n">
         <v>540</v>
@@ -5029,10 +5029,10 @@
         <v>500</v>
       </c>
       <c r="AP18" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AQ18" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AR18" t="n">
         <v>5.7</v>
@@ -5041,10 +5041,10 @@
         <v>7.2</v>
       </c>
       <c r="AT18" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="AU18" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AV18" t="n">
         <v>5.4</v>
@@ -5083,68 +5083,68 @@
         <v>7.4</v>
       </c>
       <c r="BH18" t="n">
-        <v>2.66</v>
+        <v>1000</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.06</v>
+        <v>1.04</v>
       </c>
       <c r="BJ18" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BK18" t="n">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL18" t="n">
-        <v>330</v>
+        <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>1.87</v>
+        <v>1.04</v>
       </c>
       <c r="BN18" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BO18" t="n">
-        <v>3.25</v>
+        <v>1.04</v>
       </c>
       <c r="BP18" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR18" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>1.83</v>
+        <v>1.04</v>
       </c>
       <c r="BT18" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BU18" t="n">
-        <v>3.2</v>
+        <v>1.04</v>
       </c>
       <c r="BV18" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX18" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.83</v>
+        <v>1.04</v>
       </c>
       <c r="BZ18" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>1.84</v>
+        <v>1.04</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -5187,13 +5187,13 @@
         <v>4.7</v>
       </c>
       <c r="J19" t="n">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="K19" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="L19" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="M19" t="n">
         <v>1.17</v>
@@ -5214,7 +5214,7 @@
         <v>1.12</v>
       </c>
       <c r="S19" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="T19" t="n">
         <v>2.36</v>
@@ -5223,10 +5223,10 @@
         <v>1.57</v>
       </c>
       <c r="V19" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W19" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="X19" t="n">
         <v>7</v>
@@ -5235,10 +5235,10 @@
         <v>10</v>
       </c>
       <c r="Z19" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA19" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AB19" t="n">
         <v>6.8</v>
@@ -5250,7 +5250,7 @@
         <v>22</v>
       </c>
       <c r="AE19" t="n">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="AF19" t="n">
         <v>14</v>
@@ -5262,7 +5262,7 @@
         <v>32</v>
       </c>
       <c r="AI19" t="n">
-        <v>170</v>
+        <v>540</v>
       </c>
       <c r="AJ19" t="n">
         <v>40</v>
@@ -5271,7 +5271,7 @@
         <v>46</v>
       </c>
       <c r="AL19" t="n">
-        <v>120</v>
+        <v>260</v>
       </c>
       <c r="AM19" t="n">
         <v>500</v>
@@ -5283,58 +5283,58 @@
         <v>500</v>
       </c>
       <c r="AP19" t="n">
-        <v>3.65</v>
+        <v>4.4</v>
       </c>
       <c r="AQ19" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="AR19" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS19" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AT19" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AU19" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AV19" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AW19" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AX19" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="AY19" t="n">
-        <v>5</v>
+        <v>7.6</v>
       </c>
       <c r="AZ19" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BA19" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB19" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BC19" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BD19" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BE19" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BF19" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BG19" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH19" t="n">
         <v>1000</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
         <v>1.59</v>
       </c>
       <c r="M20" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N20" t="n">
         <v>2.16</v>
@@ -5471,7 +5471,7 @@
         <v>5.1</v>
       </c>
       <c r="T20" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="U20" t="n">
         <v>1.59</v>
@@ -5480,115 +5480,115 @@
         <v>1.3</v>
       </c>
       <c r="W20" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="X20" t="n">
         <v>7.8</v>
       </c>
       <c r="Y20" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA20" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB20" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AC20" t="n">
         <v>7.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AE20" t="n">
         <v>500</v>
       </c>
       <c r="AF20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG20" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH20" t="n">
         <v>32</v>
       </c>
       <c r="AI20" t="n">
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="AJ20" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="AK20" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="AL20" t="n">
-        <v>500</v>
+        <v>460</v>
       </c>
       <c r="AM20" t="n">
         <v>500</v>
       </c>
       <c r="AN20" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AO20" t="n">
         <v>500</v>
       </c>
       <c r="AP20" t="n">
-        <v>3.25</v>
+        <v>3.85</v>
       </c>
       <c r="AQ20" t="n">
-        <v>3.65</v>
+        <v>5.1</v>
       </c>
       <c r="AR20" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="AS20" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AT20" t="n">
-        <v>3.25</v>
+        <v>3.85</v>
       </c>
       <c r="AU20" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="AV20" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AW20" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AX20" t="n">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="AY20" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BA20" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BB20" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BC20" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BD20" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BE20" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BF20" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BG20" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BH20" t="n">
         <v>2.7</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -5686,7 +5686,7 @@
         <v>2.26</v>
       </c>
       <c r="G21" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="H21" t="n">
         <v>3.15</v>
@@ -5704,10 +5704,10 @@
         <v>1.46</v>
       </c>
       <c r="M21" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N21" t="n">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="O21" t="n">
         <v>1.46</v>
@@ -5722,7 +5722,7 @@
         <v>1.18</v>
       </c>
       <c r="S21" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="T21" t="n">
         <v>1.95</v>
@@ -5734,7 +5734,7 @@
         <v>1.32</v>
       </c>
       <c r="W21" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="X21" t="n">
         <v>10</v>
@@ -5749,16 +5749,16 @@
         <v>500</v>
       </c>
       <c r="AB21" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC21" t="n">
         <v>8</v>
       </c>
       <c r="AD21" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>440</v>
+        <v>150</v>
       </c>
       <c r="AF21" t="n">
         <v>16.5</v>
@@ -5773,10 +5773,10 @@
         <v>500</v>
       </c>
       <c r="AJ21" t="n">
-        <v>150</v>
+        <v>95</v>
       </c>
       <c r="AK21" t="n">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="AL21" t="n">
         <v>450</v>
@@ -5797,10 +5797,10 @@
         <v>5.8</v>
       </c>
       <c r="AR21" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AS21" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AT21" t="n">
         <v>4.4</v>
@@ -5809,40 +5809,40 @@
         <v>4.2</v>
       </c>
       <c r="AV21" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AW21" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB21" t="n">
         <v>5.5</v>
       </c>
-      <c r="AX21" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BC21" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BD21" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BE21" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BG21" t="n">
         <v>5.9</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>5.6</v>
       </c>
       <c r="BH21" t="n">
         <v>3.2</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -5940,13 +5940,13 @@
         <v>2.1</v>
       </c>
       <c r="G22" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="H22" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I22" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="J22" t="n">
         <v>3.65</v>
@@ -5955,64 +5955,64 @@
         <v>4.1</v>
       </c>
       <c r="L22" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M22" t="n">
         <v>1.05</v>
       </c>
       <c r="N22" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O22" t="n">
         <v>1.26</v>
       </c>
       <c r="P22" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q22" t="n">
         <v>1.84</v>
       </c>
       <c r="R22" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S22" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="T22" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U22" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V22" t="n">
         <v>1.37</v>
       </c>
       <c r="W22" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="X22" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="Y22" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="Z22" t="n">
         <v>32</v>
       </c>
       <c r="AA22" t="n">
-        <v>500</v>
+        <v>440</v>
       </c>
       <c r="AB22" t="n">
         <v>11.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD22" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AF22" t="n">
         <v>15.5</v>
@@ -6021,146 +6021,146 @@
         <v>11.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AI22" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ22" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="AK22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL22" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AM22" t="n">
-        <v>500</v>
+        <v>320</v>
       </c>
       <c r="AN22" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AO22" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AP22" t="n">
-        <v>14.5</v>
+        <v>6.6</v>
       </c>
       <c r="AQ22" t="n">
         <v>12.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS22" t="n">
         <v>42</v>
       </c>
       <c r="AT22" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AU22" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV22" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW22" t="n">
-        <v>5.2</v>
+        <v>25</v>
       </c>
       <c r="AX22" t="n">
         <v>11.5</v>
       </c>
       <c r="AY22" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ22" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>5.8</v>
+        <v>30</v>
       </c>
       <c r="BB22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC22" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="BE22" t="n">
-        <v>5.4</v>
+        <v>8.4</v>
       </c>
       <c r="BF22" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BH22" t="n">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="BI22" t="n">
-        <v>2.96</v>
+        <v>1.04</v>
       </c>
       <c r="BJ22" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BK22" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BN22" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BO22" t="n">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="BP22" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BQ22" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="BR22" t="n">
         <v>1000</v>
       </c>
       <c r="BS22" t="n">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BT22" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BU22" t="n">
-        <v>4.7</v>
+        <v>1.85</v>
       </c>
       <c r="BV22" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="BX22" t="n">
         <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BZ22" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="CA22" t="n">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -6200,34 +6200,34 @@
         <v>4.5</v>
       </c>
       <c r="I23" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="J23" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K23" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="L23" t="n">
         <v>1.26</v>
       </c>
       <c r="M23" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N23" t="n">
         <v>3.4</v>
       </c>
       <c r="O23" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P23" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="Q23" t="n">
         <v>2</v>
       </c>
       <c r="R23" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S23" t="n">
         <v>3.2</v>
@@ -6254,7 +6254,7 @@
         <v>42</v>
       </c>
       <c r="AA23" t="n">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="AB23" t="n">
         <v>9.199999999999999</v>
@@ -6290,13 +6290,13 @@
         <v>40</v>
       </c>
       <c r="AM23" t="n">
-        <v>130</v>
+        <v>580</v>
       </c>
       <c r="AN23" t="n">
         <v>14</v>
       </c>
       <c r="AO23" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AP23" t="n">
         <v>11</v>
@@ -6305,7 +6305,7 @@
         <v>13</v>
       </c>
       <c r="AR23" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="AS23" t="n">
         <v>6.6</v>
@@ -6320,7 +6320,7 @@
         <v>15</v>
       </c>
       <c r="AW23" t="n">
-        <v>6.4</v>
+        <v>20</v>
       </c>
       <c r="AX23" t="n">
         <v>8.6</v>
@@ -6332,7 +6332,7 @@
         <v>15</v>
       </c>
       <c r="BA23" t="n">
-        <v>6.4</v>
+        <v>23</v>
       </c>
       <c r="BB23" t="n">
         <v>15</v>
@@ -6341,7 +6341,7 @@
         <v>15</v>
       </c>
       <c r="BD23" t="n">
-        <v>5.9</v>
+        <v>14.5</v>
       </c>
       <c r="BE23" t="n">
         <v>6.6</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -6457,7 +6457,7 @@
         <v>85</v>
       </c>
       <c r="J24" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="K24" t="n">
         <v>18.5</v>
@@ -6490,7 +6490,7 @@
         <v>2.96</v>
       </c>
       <c r="U24" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="V24" t="n">
         <v>1.01</v>
@@ -6604,7 +6604,7 @@
         <v>2</v>
       </c>
       <c r="BG24" t="n">
-        <v>4.2</v>
+        <v>10.5</v>
       </c>
       <c r="BH24" t="n">
         <v>1000</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -6705,13 +6705,13 @@
         <v>2.46</v>
       </c>
       <c r="H25" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="I25" t="n">
         <v>3.75</v>
       </c>
       <c r="J25" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K25" t="n">
         <v>3.65</v>
@@ -6723,16 +6723,16 @@
         <v>1.09</v>
       </c>
       <c r="N25" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O25" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P25" t="n">
         <v>1.69</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="R25" t="n">
         <v>1.25</v>
@@ -6741,7 +6741,7 @@
         <v>4.2</v>
       </c>
       <c r="T25" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="U25" t="n">
         <v>1.93</v>
@@ -6753,112 +6753,112 @@
         <v>1.68</v>
       </c>
       <c r="X25" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z25" t="n">
         <v>25</v>
       </c>
       <c r="AA25" t="n">
-        <v>85</v>
+        <v>900</v>
       </c>
       <c r="AB25" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC25" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AD25" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE25" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AF25" t="n">
         <v>14.5</v>
       </c>
       <c r="AG25" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH25" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI25" t="n">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AJ25" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AK25" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AL25" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AM25" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN25" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AO25" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AP25" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ25" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR25" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AS25" t="n">
-        <v>6.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT25" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU25" t="n">
         <v>6.6</v>
       </c>
       <c r="AV25" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AW25" t="n">
-        <v>6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY25" t="n">
         <v>10</v>
       </c>
       <c r="AZ25" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>6.2</v>
+        <v>9.6</v>
       </c>
       <c r="BB25" t="n">
-        <v>5.7</v>
+        <v>13</v>
       </c>
       <c r="BC25" t="n">
-        <v>5.6</v>
+        <v>13</v>
       </c>
       <c r="BD25" t="n">
-        <v>6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE25" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="BF25" t="n">
-        <v>20</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG25" t="n">
-        <v>6</v>
+        <v>9.4</v>
       </c>
       <c r="BH25" t="n">
         <v>3.05</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -7112,7 +7112,7 @@
         <v>4.2</v>
       </c>
       <c r="BG26" t="n">
-        <v>5.3</v>
+        <v>15</v>
       </c>
       <c r="BH26" t="n">
         <v>4.6</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
         <v>26</v>
       </c>
       <c r="I27" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J27" t="n">
         <v>8.199999999999999</v>
@@ -7237,22 +7237,22 @@
         <v>1.19</v>
       </c>
       <c r="P27" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="Q27" t="n">
         <v>1.56</v>
       </c>
       <c r="R27" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="S27" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="T27" t="n">
         <v>2.72</v>
       </c>
       <c r="U27" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="V27" t="n">
         <v>1.03</v>
@@ -7261,7 +7261,7 @@
         <v>6.4</v>
       </c>
       <c r="X27" t="n">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="Y27" t="n">
         <v>950</v>
@@ -7273,7 +7273,7 @@
         <v>1000</v>
       </c>
       <c r="AB27" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AC27" t="n">
         <v>22</v>
@@ -7285,19 +7285,19 @@
         <v>1000</v>
       </c>
       <c r="AF27" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AG27" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AH27" t="n">
-        <v>430</v>
+        <v>950</v>
       </c>
       <c r="AI27" t="n">
-        <v>580</v>
+        <v>570</v>
       </c>
       <c r="AJ27" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AK27" t="n">
         <v>17</v>
@@ -7306,73 +7306,73 @@
         <v>430</v>
       </c>
       <c r="AM27" t="n">
-        <v>480</v>
+        <v>510</v>
       </c>
       <c r="AN27" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AO27" t="n">
         <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>21</v>
+        <v>11.5</v>
       </c>
       <c r="AQ27" t="n">
-        <v>20</v>
+        <v>6.8</v>
       </c>
       <c r="AR27" t="n">
-        <v>10</v>
+        <v>7.2</v>
       </c>
       <c r="AS27" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AT27" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AU27" t="n">
         <v>17.5</v>
       </c>
       <c r="AV27" t="n">
-        <v>9.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="AW27" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AX27" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB27" t="n">
         <v>5.9</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>28</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>6.4</v>
       </c>
       <c r="BC27" t="n">
         <v>13.5</v>
       </c>
       <c r="BD27" t="n">
-        <v>28</v>
+        <v>6.6</v>
       </c>
       <c r="BE27" t="n">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="BF27" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="BG27" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BH27" t="n">
         <v>4.7</v>
       </c>
       <c r="BI27" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="BJ27" t="n">
         <v>18.5</v>
@@ -7390,13 +7390,13 @@
         <v>3.55</v>
       </c>
       <c r="BO27" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="BP27" t="n">
         <v>6.2</v>
       </c>
       <c r="BQ27" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="BR27" t="n">
         <v>1000</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -7461,43 +7461,43 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="G28" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="H28" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="I28" t="n">
         <v>6</v>
       </c>
       <c r="J28" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K28" t="n">
         <v>4.4</v>
       </c>
       <c r="L28" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="M28" t="n">
         <v>1.06</v>
       </c>
       <c r="N28" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="O28" t="n">
         <v>1.3</v>
       </c>
       <c r="P28" t="n">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="R28" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="S28" t="n">
         <v>3.3</v>
@@ -7512,22 +7512,22 @@
         <v>1.2</v>
       </c>
       <c r="W28" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="X28" t="n">
         <v>16.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="AA28" t="n">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="AB28" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC28" t="n">
         <v>10</v>
@@ -7536,7 +7536,7 @@
         <v>23</v>
       </c>
       <c r="AE28" t="n">
-        <v>400</v>
+        <v>190</v>
       </c>
       <c r="AF28" t="n">
         <v>10.5</v>
@@ -7548,64 +7548,64 @@
         <v>24</v>
       </c>
       <c r="AI28" t="n">
-        <v>700</v>
+        <v>170</v>
       </c>
       <c r="AJ28" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AK28" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AL28" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM28" t="n">
-        <v>390</v>
+        <v>580</v>
       </c>
       <c r="AN28" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AO28" t="n">
         <v>440</v>
       </c>
       <c r="AP28" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AQ28" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AR28" t="n">
-        <v>7.4</v>
+        <v>34</v>
       </c>
       <c r="AS28" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AT28" t="n">
         <v>7</v>
       </c>
       <c r="AU28" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV28" t="n">
         <v>18.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AX28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AY28" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ28" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA28" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BB28" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BC28" t="n">
         <v>15</v>
@@ -7614,25 +7614,25 @@
         <v>26</v>
       </c>
       <c r="BE28" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF28" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH28" t="n">
         <v>3.6</v>
       </c>
       <c r="BI28" t="n">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="BJ28" t="n">
         <v>11</v>
       </c>
       <c r="BK28" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BL28" t="n">
         <v>1000</v>
@@ -7650,7 +7650,7 @@
         <v>11.5</v>
       </c>
       <c r="BQ28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BR28" t="n">
         <v>28</v>
@@ -7662,10 +7662,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BU28" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BV28" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BW28" t="n">
         <v>8.800000000000001</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -7718,10 +7718,10 @@
         <v>1.87</v>
       </c>
       <c r="G29" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="H29" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I29" t="n">
         <v>4.2</v>
@@ -7745,7 +7745,7 @@
         <v>1.17</v>
       </c>
       <c r="P29" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="Q29" t="n">
         <v>1.5</v>
@@ -7766,13 +7766,13 @@
         <v>1.32</v>
       </c>
       <c r="W29" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="X29" t="n">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="Y29" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Z29" t="n">
         <v>38</v>
@@ -7790,10 +7790,10 @@
         <v>17.5</v>
       </c>
       <c r="AE29" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AF29" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AG29" t="n">
         <v>12</v>
@@ -7805,10 +7805,10 @@
         <v>95</v>
       </c>
       <c r="AJ29" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="AK29" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL29" t="n">
         <v>27</v>
@@ -7817,7 +7817,7 @@
         <v>200</v>
       </c>
       <c r="AN29" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AO29" t="n">
         <v>29</v>
@@ -7832,7 +7832,7 @@
         <v>16</v>
       </c>
       <c r="AS29" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT29" t="n">
         <v>11</v>
@@ -7868,7 +7868,7 @@
         <v>19</v>
       </c>
       <c r="BE29" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF29" t="n">
         <v>6.4</v>
@@ -7877,68 +7877,68 @@
         <v>19</v>
       </c>
       <c r="BH29" t="n">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="BI29" t="n">
-        <v>3.75</v>
+        <v>1.04</v>
       </c>
       <c r="BJ29" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BK29" t="n">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BL29" t="n">
         <v>1000</v>
       </c>
       <c r="BM29" t="n">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="BN29" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="BO29" t="n">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BP29" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BQ29" t="n">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR29" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BS29" t="n">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="BT29" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BU29" t="n">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BV29" t="n">
         <v>1000</v>
       </c>
       <c r="BW29" t="n">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BX29" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BY29" t="n">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BZ29" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="CA29" t="n">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -7969,19 +7969,19 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="G30" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="H30" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="I30" t="n">
         <v>1000</v>
       </c>
       <c r="J30" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="K30" t="n">
         <v>1000</v>
@@ -7993,13 +7993,13 @@
         <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="O30" t="n">
         <v>1.06</v>
       </c>
       <c r="P30" t="n">
-        <v>2.7</v>
+        <v>2.24</v>
       </c>
       <c r="Q30" t="n">
         <v>1.06</v>
@@ -8008,7 +8008,7 @@
         <v>2.24</v>
       </c>
       <c r="S30" t="n">
-        <v>1.41</v>
+        <v>1.06</v>
       </c>
       <c r="T30" t="n">
         <v>1.11</v>
@@ -8020,7 +8020,7 @@
         <v>1.09</v>
       </c>
       <c r="W30" t="n">
-        <v>2.46</v>
+        <v>2.24</v>
       </c>
       <c r="X30" t="n">
         <v>1000</v>
@@ -8038,7 +8038,7 @@
         <v>1000</v>
       </c>
       <c r="AC30" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD30" t="n">
         <v>1000</v>
@@ -8059,7 +8059,7 @@
         <v>1000</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK30" t="n">
         <v>1000</v>
@@ -8071,64 +8071,64 @@
         <v>1000</v>
       </c>
       <c r="AN30" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AO30" t="n">
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BD30" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH30" t="n">
         <v>1000</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -8223,22 +8223,22 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="G31" t="n">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="H31" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="I31" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="J31" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="K31" t="n">
-        <v>10.5</v>
+        <v>6</v>
       </c>
       <c r="L31" t="n">
         <v>1.01</v>
@@ -8250,139 +8250,139 @@
         <v>1.1</v>
       </c>
       <c r="O31" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="P31" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="R31" t="n">
-        <v>2.36</v>
+        <v>2.52</v>
       </c>
       <c r="S31" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="T31" t="n">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="U31" t="n">
-        <v>1.11</v>
+        <v>3.45</v>
       </c>
       <c r="V31" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="W31" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="X31" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y31" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="Z31" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA31" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB31" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC31" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AD31" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE31" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AF31" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG31" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AH31" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AI31" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK31" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL31" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM31" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AN31" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AO31" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AS31" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AT31" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BA31" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BD31" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BG31" t="n">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="BH31" t="n">
         <v>1000</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -8483,7 +8483,7 @@
         <v>1.93</v>
       </c>
       <c r="H32" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="I32" t="n">
         <v>4.3</v>
@@ -8501,22 +8501,22 @@
         <v>1.01</v>
       </c>
       <c r="N32" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="O32" t="n">
         <v>1.05</v>
       </c>
       <c r="P32" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="R32" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="S32" t="n">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="T32" t="n">
         <v>1.11</v>
@@ -8540,13 +8540,13 @@
         <v>500</v>
       </c>
       <c r="AA32" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB32" t="n">
         <v>950</v>
       </c>
       <c r="AC32" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AD32" t="n">
         <v>950</v>
@@ -8567,7 +8567,7 @@
         <v>500</v>
       </c>
       <c r="AJ32" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK32" t="n">
         <v>500</v>
@@ -8582,61 +8582,61 @@
         <v>500</v>
       </c>
       <c r="AO32" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AS32" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="AT32" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="AU32" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="AV32" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BA32" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BC32" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="BD32" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BG32" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH32" t="n">
         <v>1000</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -8731,25 +8731,25 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="G33" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="H33" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="I33" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J33" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="K33" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="L33" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="M33" t="n">
         <v>1.01</v>
@@ -8767,22 +8767,22 @@
         <v>1.19</v>
       </c>
       <c r="R33" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="S33" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="T33" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="U33" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="V33" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W33" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="X33" t="n">
         <v>950</v>
@@ -8791,170 +8791,170 @@
         <v>950</v>
       </c>
       <c r="Z33" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AA33" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="AB33" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AC33" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AD33" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AE33" t="n">
-        <v>95</v>
+        <v>210</v>
       </c>
       <c r="AF33" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AG33" t="n">
         <v>17</v>
       </c>
       <c r="AH33" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI33" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AJ33" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AK33" t="n">
         <v>17</v>
       </c>
       <c r="AL33" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AM33" t="n">
         <v>60</v>
       </c>
       <c r="AN33" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="AO33" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AP33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AR33" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="AS33" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD33" t="n">
         <v>5.2</v>
       </c>
-      <c r="AT33" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>4</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BE33" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="BF33" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="BG33" t="n">
-        <v>4.7</v>
+        <v>10.5</v>
       </c>
       <c r="BH33" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BI33" t="n">
         <v>1.04</v>
       </c>
       <c r="BJ33" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK33" t="n">
         <v>1.04</v>
       </c>
       <c r="BL33" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BM33" t="n">
         <v>1.04</v>
       </c>
       <c r="BN33" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO33" t="n">
         <v>1.04</v>
       </c>
       <c r="BP33" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BQ33" t="n">
         <v>1.04</v>
       </c>
       <c r="BR33" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BS33" t="n">
         <v>1.04</v>
       </c>
       <c r="BT33" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BU33" t="n">
         <v>1.04</v>
       </c>
       <c r="BV33" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW33" t="n">
         <v>1.04</v>
       </c>
       <c r="BX33" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY33" t="n">
         <v>1.04</v>
       </c>
       <c r="BZ33" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="CA33" t="n">
         <v>1.04</v>
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -8985,22 +8985,22 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.2</v>
+        <v>1.71</v>
       </c>
       <c r="G34" t="n">
-        <v>3.2</v>
+        <v>990</v>
       </c>
       <c r="H34" t="n">
-        <v>2.16</v>
+        <v>1.51</v>
       </c>
       <c r="I34" t="n">
-        <v>3.3</v>
+        <v>1000</v>
       </c>
       <c r="J34" t="n">
-        <v>3.25</v>
+        <v>2.06</v>
       </c>
       <c r="K34" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="L34" t="n">
         <v>1.01</v>
@@ -9009,22 +9009,22 @@
         <v>1.01</v>
       </c>
       <c r="N34" t="n">
-        <v>2.66</v>
+        <v>1.1</v>
       </c>
       <c r="O34" t="n">
         <v>1.1</v>
       </c>
       <c r="P34" t="n">
-        <v>2.34</v>
+        <v>1.33</v>
       </c>
       <c r="Q34" t="n">
         <v>1.1</v>
       </c>
       <c r="R34" t="n">
-        <v>1.78</v>
+        <v>1.33</v>
       </c>
       <c r="S34" t="n">
-        <v>1.81</v>
+        <v>1.1</v>
       </c>
       <c r="T34" t="n">
         <v>1.11</v>
@@ -9033,10 +9033,10 @@
         <v>1.11</v>
       </c>
       <c r="V34" t="n">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="W34" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="X34" t="n">
         <v>950</v>
@@ -9048,13 +9048,13 @@
         <v>500</v>
       </c>
       <c r="AA34" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB34" t="n">
         <v>950</v>
       </c>
       <c r="AC34" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AD34" t="n">
         <v>950</v>
@@ -9075,7 +9075,7 @@
         <v>500</v>
       </c>
       <c r="AJ34" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK34" t="n">
         <v>500</v>
@@ -9093,58 +9093,58 @@
         <v>500</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AT34" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV34" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BD34" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG34" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH34" t="n">
         <v>1000</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -9245,7 +9245,7 @@
         <v>1.46</v>
       </c>
       <c r="H35" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="I35" t="n">
         <v>11</v>
@@ -9269,7 +9269,7 @@
         <v>1.25</v>
       </c>
       <c r="P35" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="Q35" t="n">
         <v>1.73</v>
@@ -9284,7 +9284,7 @@
         <v>2.02</v>
       </c>
       <c r="U35" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="V35" t="n">
         <v>1.1</v>
@@ -9320,7 +9320,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AG35" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH35" t="n">
         <v>30</v>
@@ -9341,22 +9341,22 @@
         <v>170</v>
       </c>
       <c r="AN35" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AO35" t="n">
         <v>240</v>
       </c>
       <c r="AP35" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="AQ35" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="AR35" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="AS35" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="AT35" t="n">
         <v>7.4</v>
@@ -9365,22 +9365,22 @@
         <v>10</v>
       </c>
       <c r="AV35" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="AW35" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AX35" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AY35" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ35" t="n">
         <v>20</v>
       </c>
       <c r="BA35" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BB35" t="n">
         <v>10.5</v>
@@ -9389,16 +9389,16 @@
         <v>12</v>
       </c>
       <c r="BD35" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BE35" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BF35" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BG35" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BH35" t="n">
         <v>3.95</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -9493,230 +9493,230 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.67</v>
+        <v>2.7</v>
       </c>
       <c r="G36" t="n">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="H36" t="n">
-        <v>1.68</v>
+        <v>2.72</v>
       </c>
       <c r="I36" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="J36" t="n">
-        <v>2.26</v>
+        <v>3.05</v>
       </c>
       <c r="K36" t="n">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="L36" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M36" t="n">
         <v>1.09</v>
       </c>
       <c r="N36" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R36" t="n">
         <v>1.25</v>
       </c>
-      <c r="O36" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="P36" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.18</v>
-      </c>
       <c r="S36" t="n">
-        <v>1.4</v>
+        <v>3.6</v>
       </c>
       <c r="T36" t="n">
-        <v>1.11</v>
+        <v>1.85</v>
       </c>
       <c r="U36" t="n">
-        <v>1.11</v>
+        <v>1.94</v>
       </c>
       <c r="V36" t="n">
-        <v>1.07</v>
+        <v>1.46</v>
       </c>
       <c r="W36" t="n">
-        <v>1.07</v>
+        <v>1.47</v>
       </c>
       <c r="X36" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y36" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z36" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AA36" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB36" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC36" t="n">
-        <v>970</v>
+        <v>7.8</v>
       </c>
       <c r="AD36" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE36" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF36" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AG36" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH36" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI36" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AK36" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL36" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AM36" t="n">
         <v>500</v>
       </c>
       <c r="AN36" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AO36" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.09</v>
+        <v>5</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.09</v>
+        <v>4.5</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.09</v>
+        <v>5.7</v>
       </c>
       <c r="AS36" t="n">
-        <v>1.09</v>
+        <v>6.8</v>
       </c>
       <c r="AT36" t="n">
-        <v>1.09</v>
+        <v>4.5</v>
       </c>
       <c r="AU36" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AV36" t="n">
-        <v>1.09</v>
+        <v>5.1</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.09</v>
+        <v>6.6</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.09</v>
+        <v>5.7</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.09</v>
+        <v>5</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1.09</v>
+        <v>5.7</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.08</v>
+        <v>7</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.09</v>
+        <v>6.8</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.09</v>
+        <v>6.6</v>
       </c>
       <c r="BD36" t="n">
-        <v>1.09</v>
+        <v>7</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.08</v>
+        <v>7.6</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.09</v>
+        <v>6.6</v>
       </c>
       <c r="BG36" t="n">
-        <v>1.09</v>
+        <v>6.6</v>
       </c>
       <c r="BH36" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="BI36" t="n">
-        <v>1.04</v>
+        <v>2.46</v>
       </c>
       <c r="BJ36" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK36" t="n">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BL36" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="BM36" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BN36" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BO36" t="n">
-        <v>1.04</v>
+        <v>2.88</v>
       </c>
       <c r="BP36" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BQ36" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BR36" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS36" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BT36" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU36" t="n">
-        <v>1.04</v>
+        <v>2.88</v>
       </c>
       <c r="BV36" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BW36" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BX36" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY36" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BZ36" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="CA36" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -9747,13 +9747,13 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G37" t="n">
         <v>2.24</v>
       </c>
       <c r="H37" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I37" t="n">
         <v>4.9</v>
@@ -9762,7 +9762,7 @@
         <v>2.9</v>
       </c>
       <c r="K37" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L37" t="n">
         <v>1.68</v>
@@ -9771,13 +9771,13 @@
         <v>1.16</v>
       </c>
       <c r="N37" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="O37" t="n">
         <v>1.69</v>
       </c>
       <c r="P37" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="Q37" t="n">
         <v>3.1</v>
@@ -9786,7 +9786,7 @@
         <v>1.15</v>
       </c>
       <c r="S37" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T37" t="n">
         <v>2.44</v>
@@ -9801,37 +9801,37 @@
         <v>1.8</v>
       </c>
       <c r="X37" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="Y37" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z37" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AA37" t="n">
         <v>700</v>
       </c>
       <c r="AB37" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="AC37" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AD37" t="n">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="AE37" t="n">
         <v>700</v>
       </c>
       <c r="AF37" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG37" t="n">
         <v>13</v>
       </c>
-      <c r="AG37" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AH37" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AI37" t="n">
         <v>700</v>
@@ -9840,7 +9840,7 @@
         <v>150</v>
       </c>
       <c r="AK37" t="n">
-        <v>46</v>
+        <v>140</v>
       </c>
       <c r="AL37" t="n">
         <v>540</v>
@@ -9849,34 +9849,34 @@
         <v>500</v>
       </c>
       <c r="AN37" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AO37" t="n">
         <v>700</v>
       </c>
       <c r="AP37" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ37" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AR37" t="n">
-        <v>5.5</v>
+        <v>13</v>
       </c>
       <c r="AS37" t="n">
-        <v>5.4</v>
+        <v>13.5</v>
       </c>
       <c r="AT37" t="n">
         <v>5.4</v>
       </c>
       <c r="AU37" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV37" t="n">
         <v>11.5</v>
       </c>
       <c r="AW37" t="n">
-        <v>5.9</v>
+        <v>13</v>
       </c>
       <c r="AX37" t="n">
         <v>10</v>
@@ -9885,34 +9885,34 @@
         <v>11</v>
       </c>
       <c r="AZ37" t="n">
-        <v>4.7</v>
+        <v>10</v>
       </c>
       <c r="BA37" t="n">
-        <v>6</v>
+        <v>13.5</v>
       </c>
       <c r="BB37" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="BC37" t="n">
-        <v>5.4</v>
+        <v>11</v>
       </c>
       <c r="BD37" t="n">
-        <v>5.2</v>
+        <v>12.5</v>
       </c>
       <c r="BE37" t="n">
-        <v>5.5</v>
+        <v>14</v>
       </c>
       <c r="BF37" t="n">
-        <v>28</v>
+        <v>10.5</v>
       </c>
       <c r="BG37" t="n">
-        <v>5.4</v>
+        <v>14</v>
       </c>
       <c r="BH37" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="BI37" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="BJ37" t="n">
         <v>13</v>
@@ -9924,53 +9924,53 @@
         <v>1000</v>
       </c>
       <c r="BM37" t="n">
-        <v>16</v>
+        <v>1.47</v>
       </c>
       <c r="BN37" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BO37" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BP37" t="n">
         <v>1000</v>
       </c>
       <c r="BQ37" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BR37" t="n">
         <v>1000</v>
       </c>
       <c r="BS37" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BT37" t="n">
         <v>7.8</v>
       </c>
       <c r="BU37" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="BV37" t="n">
         <v>1000</v>
       </c>
       <c r="BW37" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BX37" t="n">
         <v>1000</v>
       </c>
       <c r="BY37" t="n">
-        <v>14</v>
+        <v>2.12</v>
       </c>
       <c r="BZ37" t="n">
         <v>1000</v>
       </c>
       <c r="CA37" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -10001,19 +10001,19 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="G38" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="H38" t="n">
         <v>4.2</v>
       </c>
       <c r="I38" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J38" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K38" t="n">
         <v>3.45</v>
@@ -10025,10 +10025,10 @@
         <v>1.1</v>
       </c>
       <c r="N38" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O38" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P38" t="n">
         <v>1.7</v>
@@ -10043,7 +10043,7 @@
         <v>4.2</v>
       </c>
       <c r="T38" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="U38" t="n">
         <v>1.92</v>
@@ -10052,7 +10052,7 @@
         <v>1.27</v>
       </c>
       <c r="W38" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="X38" t="n">
         <v>11</v>
@@ -10064,7 +10064,7 @@
         <v>32</v>
       </c>
       <c r="AA38" t="n">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="AB38" t="n">
         <v>8</v>
@@ -10088,7 +10088,7 @@
         <v>21</v>
       </c>
       <c r="AI38" t="n">
-        <v>380</v>
+        <v>170</v>
       </c>
       <c r="AJ38" t="n">
         <v>26</v>
@@ -10100,13 +10100,13 @@
         <v>60</v>
       </c>
       <c r="AM38" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN38" t="n">
         <v>23</v>
       </c>
       <c r="AO38" t="n">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="AP38" t="n">
         <v>9.6</v>
@@ -10133,7 +10133,7 @@
         <v>23</v>
       </c>
       <c r="AX38" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AY38" t="n">
         <v>9.6</v>
@@ -10166,65 +10166,65 @@
         <v>3.05</v>
       </c>
       <c r="BI38" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="BJ38" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK38" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL38" t="n">
         <v>1000</v>
       </c>
       <c r="BM38" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN38" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BO38" t="n">
         <v>3.7</v>
       </c>
       <c r="BP38" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BQ38" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BR38" t="n">
         <v>34</v>
       </c>
       <c r="BS38" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BT38" t="n">
         <v>7.6</v>
       </c>
       <c r="BU38" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BV38" t="n">
         <v>42</v>
       </c>
       <c r="BW38" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BX38" t="n">
         <v>1000</v>
       </c>
       <c r="BY38" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BZ38" t="n">
         <v>34</v>
       </c>
       <c r="CA38" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -10270,10 +10270,10 @@
         <v>3.25</v>
       </c>
       <c r="K39" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L39" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="M39" t="n">
         <v>1.1</v>
@@ -10282,13 +10282,13 @@
         <v>2.92</v>
       </c>
       <c r="O39" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="P39" t="n">
         <v>1.64</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="R39" t="n">
         <v>1.23</v>
@@ -10300,7 +10300,7 @@
         <v>1.93</v>
       </c>
       <c r="U39" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="V39" t="n">
         <v>1.43</v>
@@ -10312,49 +10312,49 @@
         <v>11</v>
       </c>
       <c r="Y39" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="Z39" t="n">
         <v>22</v>
       </c>
       <c r="AA39" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AB39" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AC39" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AD39" t="n">
         <v>15</v>
       </c>
       <c r="AE39" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AF39" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG39" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH39" t="n">
         <v>22</v>
       </c>
       <c r="AI39" t="n">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AJ39" t="n">
         <v>44</v>
       </c>
       <c r="AK39" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AL39" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM39" t="n">
-        <v>170</v>
+        <v>580</v>
       </c>
       <c r="AN39" t="n">
         <v>44</v>
@@ -10369,25 +10369,25 @@
         <v>8.6</v>
       </c>
       <c r="AR39" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AS39" t="n">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="AT39" t="n">
         <v>7.4</v>
       </c>
       <c r="AU39" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV39" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AW39" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="AX39" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY39" t="n">
         <v>10.5</v>
@@ -10396,25 +10396,25 @@
         <v>17.5</v>
       </c>
       <c r="BA39" t="n">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="BB39" t="n">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="BC39" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="BD39" t="n">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="BE39" t="n">
-        <v>5.8</v>
+        <v>7.8</v>
       </c>
       <c r="BF39" t="n">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="BG39" t="n">
-        <v>5.4</v>
+        <v>7.4</v>
       </c>
       <c r="BH39" t="n">
         <v>3</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -10509,7 +10509,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="G40" t="n">
         <v>1.7</v>
@@ -10524,10 +10524,10 @@
         <v>4</v>
       </c>
       <c r="K40" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L40" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="M40" t="n">
         <v>1.07</v>
@@ -10554,7 +10554,7 @@
         <v>1.97</v>
       </c>
       <c r="U40" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="V40" t="n">
         <v>1.17</v>
@@ -10569,16 +10569,16 @@
         <v>23</v>
       </c>
       <c r="Z40" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AA40" t="n">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="AB40" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AC40" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD40" t="n">
         <v>28</v>
@@ -10605,7 +10605,7 @@
         <v>19.5</v>
       </c>
       <c r="AL40" t="n">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="AM40" t="n">
         <v>700</v>
@@ -10620,10 +10620,10 @@
         <v>11</v>
       </c>
       <c r="AQ40" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AR40" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AS40" t="n">
         <v>6.6</v>
@@ -10635,7 +10635,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV40" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AW40" t="n">
         <v>6.4</v>
@@ -10647,7 +10647,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ40" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="BA40" t="n">
         <v>6.4</v>
@@ -10659,28 +10659,28 @@
         <v>14</v>
       </c>
       <c r="BD40" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BE40" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF40" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BG40" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH40" t="n">
         <v>3.4</v>
       </c>
       <c r="BI40" t="n">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="BJ40" t="n">
         <v>11</v>
       </c>
       <c r="BK40" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BL40" t="n">
         <v>1000</v>
@@ -10689,50 +10689,50 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BN40" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BO40" t="n">
         <v>3.35</v>
       </c>
       <c r="BP40" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BQ40" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BR40" t="n">
         <v>1000</v>
       </c>
       <c r="BS40" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BT40" t="n">
         <v>9.6</v>
       </c>
       <c r="BU40" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BV40" t="n">
         <v>1000</v>
       </c>
       <c r="BW40" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BX40" t="n">
         <v>1000</v>
       </c>
       <c r="BY40" t="n">
-        <v>12</v>
+        <v>8.4</v>
       </c>
       <c r="BZ40" t="n">
         <v>22</v>
       </c>
       <c r="CA40" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -10769,16 +10769,16 @@
         <v>1.48</v>
       </c>
       <c r="H41" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="I41" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="J41" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="K41" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L41" t="n">
         <v>1.3</v>
@@ -10808,7 +10808,7 @@
         <v>1.84</v>
       </c>
       <c r="U41" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V41" t="n">
         <v>1.14</v>
@@ -10850,7 +10850,7 @@
         <v>22</v>
       </c>
       <c r="AI41" t="n">
-        <v>390</v>
+        <v>95</v>
       </c>
       <c r="AJ41" t="n">
         <v>13.5</v>
@@ -10880,7 +10880,7 @@
         <v>55</v>
       </c>
       <c r="AS41" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AT41" t="n">
         <v>9.4</v>
@@ -10892,10 +10892,10 @@
         <v>24</v>
       </c>
       <c r="AW41" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AX41" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY41" t="n">
         <v>9.199999999999999</v>
@@ -10919,10 +10919,10 @@
         <v>29</v>
       </c>
       <c r="BF41" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BG41" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BH41" t="n">
         <v>4.2</v>
@@ -10940,19 +10940,19 @@
         <v>1000</v>
       </c>
       <c r="BM41" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BN41" t="n">
         <v>4.1</v>
       </c>
       <c r="BO41" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="BP41" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BQ41" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BR41" t="n">
         <v>22</v>
@@ -10964,16 +10964,16 @@
         <v>11</v>
       </c>
       <c r="BU41" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BV41" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BW41" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BX41" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY41" t="n">
         <v>14</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -11044,10 +11044,10 @@
         <v>3.25</v>
       </c>
       <c r="O42" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P42" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q42" t="n">
         <v>2.16</v>
@@ -11062,7 +11062,7 @@
         <v>1.93</v>
       </c>
       <c r="U42" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="V42" t="n">
         <v>1.3</v>
@@ -11074,13 +11074,13 @@
         <v>12</v>
       </c>
       <c r="Y42" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z42" t="n">
         <v>30</v>
       </c>
       <c r="AA42" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AB42" t="n">
         <v>8.6</v>
@@ -11089,22 +11089,22 @@
         <v>8</v>
       </c>
       <c r="AD42" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AE42" t="n">
         <v>60</v>
       </c>
       <c r="AF42" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG42" t="n">
         <v>12.5</v>
       </c>
       <c r="AH42" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI42" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ42" t="n">
         <v>25</v>
@@ -11113,7 +11113,7 @@
         <v>25</v>
       </c>
       <c r="AL42" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM42" t="n">
         <v>130</v>
@@ -11122,7 +11122,7 @@
         <v>18.5</v>
       </c>
       <c r="AO42" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AP42" t="n">
         <v>10.5</v>
@@ -11134,10 +11134,10 @@
         <v>26</v>
       </c>
       <c r="AS42" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AT42" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU42" t="n">
         <v>7.2</v>
@@ -11146,7 +11146,7 @@
         <v>15</v>
       </c>
       <c r="AW42" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AX42" t="n">
         <v>10.5</v>
@@ -11164,7 +11164,7 @@
         <v>22</v>
       </c>
       <c r="BC42" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD42" t="n">
         <v>36</v>
@@ -11200,7 +11200,7 @@
         <v>4.8</v>
       </c>
       <c r="BO42" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BP42" t="n">
         <v>16</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -11271,7 +11271,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G43" t="n">
         <v>2.04</v>
@@ -11286,10 +11286,10 @@
         <v>3.5</v>
       </c>
       <c r="K43" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L43" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="M43" t="n">
         <v>1.08</v>
@@ -11304,19 +11304,19 @@
         <v>1.8</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R43" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S43" t="n">
         <v>4</v>
       </c>
       <c r="T43" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="U43" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="V43" t="n">
         <v>1.28</v>
@@ -11364,7 +11364,7 @@
         <v>24</v>
       </c>
       <c r="AK43" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AL43" t="n">
         <v>48</v>
@@ -11373,7 +11373,7 @@
         <v>140</v>
       </c>
       <c r="AN43" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AO43" t="n">
         <v>85</v>
@@ -11385,10 +11385,10 @@
         <v>13</v>
       </c>
       <c r="AR43" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AS43" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AT43" t="n">
         <v>7.4</v>
@@ -11412,25 +11412,25 @@
         <v>17</v>
       </c>
       <c r="BA43" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BB43" t="n">
         <v>19.5</v>
       </c>
       <c r="BC43" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BD43" t="n">
         <v>30</v>
       </c>
       <c r="BE43" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BF43" t="n">
         <v>14.5</v>
       </c>
       <c r="BG43" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH43" t="n">
         <v>3.3</v>
@@ -11442,7 +11442,7 @@
         <v>11</v>
       </c>
       <c r="BK43" t="n">
-        <v>8</v>
+        <v>5.3</v>
       </c>
       <c r="BL43" t="n">
         <v>1000</v>
@@ -11472,16 +11472,16 @@
         <v>8</v>
       </c>
       <c r="BU43" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="BV43" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BW43" t="n">
         <v>8</v>
       </c>
       <c r="BX43" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY43" t="n">
         <v>8.6</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -11531,16 +11531,16 @@
         <v>2.08</v>
       </c>
       <c r="H44" t="n">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="I44" t="n">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="J44" t="n">
-        <v>3.5</v>
+        <v>1.94</v>
       </c>
       <c r="K44" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="L44" t="n">
         <v>1.01</v>
@@ -11558,7 +11558,7 @@
         <v>1.86</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.52</v>
+        <v>1.24</v>
       </c>
       <c r="R44" t="n">
         <v>1.07</v>
@@ -11573,7 +11573,7 @@
         <v>1.11</v>
       </c>
       <c r="V44" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="W44" t="n">
         <v>1.94</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -11782,13 +11782,13 @@
         <v>2.56</v>
       </c>
       <c r="G45" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="H45" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="I45" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="J45" t="n">
         <v>3.5</v>
@@ -11830,7 +11830,7 @@
         <v>1.52</v>
       </c>
       <c r="W45" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="X45" t="n">
         <v>21</v>
@@ -11893,7 +11893,7 @@
         <v>10</v>
       </c>
       <c r="AR45" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AS45" t="n">
         <v>1.03</v>
@@ -11905,7 +11905,7 @@
         <v>7.4</v>
       </c>
       <c r="AV45" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AW45" t="n">
         <v>21</v>
@@ -11944,65 +11944,65 @@
         <v>3.85</v>
       </c>
       <c r="BI45" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="BJ45" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK45" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BL45" t="n">
         <v>1000</v>
       </c>
       <c r="BM45" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BN45" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BO45" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BP45" t="n">
         <v>19.5</v>
       </c>
       <c r="BQ45" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BR45" t="n">
         <v>1000</v>
       </c>
       <c r="BS45" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BT45" t="n">
         <v>6.2</v>
       </c>
       <c r="BU45" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BV45" t="n">
         <v>21</v>
       </c>
       <c r="BW45" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BX45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY45" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BZ45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA45" t="n">
         <v>7.8</v>
       </c>
-      <c r="BX45" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY45" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BZ45" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA45" t="n">
-        <v>8</v>
-      </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -12057,7 +12057,7 @@
         <v>1.01</v>
       </c>
       <c r="N46" t="n">
-        <v>1.91</v>
+        <v>1.1</v>
       </c>
       <c r="O46" t="n">
         <v>1.09</v>
@@ -12069,7 +12069,7 @@
         <v>1.09</v>
       </c>
       <c r="R46" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S46" t="n">
         <v>1.09</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -12287,19 +12287,19 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="G47" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="H47" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="I47" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="J47" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K47" t="n">
         <v>3.35</v>
@@ -12311,206 +12311,206 @@
         <v>1.11</v>
       </c>
       <c r="N47" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="O47" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="P47" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="R47" t="n">
         <v>1.22</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="T47" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U47" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="V47" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W47" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="X47" t="n">
         <v>11.5</v>
       </c>
       <c r="Y47" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z47" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AA47" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AB47" t="n">
         <v>9.4</v>
       </c>
       <c r="AC47" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD47" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF47" t="n">
         <v>16.5</v>
       </c>
-      <c r="AE47" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AG47" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AH47" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AI47" t="n">
         <v>90</v>
       </c>
       <c r="AJ47" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AK47" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AL47" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AM47" t="n">
         <v>200</v>
       </c>
       <c r="AN47" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="AO47" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AP47" t="n">
         <v>8.6</v>
       </c>
       <c r="AQ47" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR47" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AS47" t="n">
-        <v>7.2</v>
+        <v>4.3</v>
       </c>
       <c r="AT47" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AU47" t="n">
         <v>6.6</v>
       </c>
       <c r="AV47" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AW47" t="n">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="AX47" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY47" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ47" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA47" t="n">
-        <v>7.2</v>
+        <v>4.3</v>
       </c>
       <c r="BB47" t="n">
-        <v>20</v>
+        <v>4.1</v>
       </c>
       <c r="BC47" t="n">
-        <v>6.2</v>
+        <v>4</v>
       </c>
       <c r="BD47" t="n">
-        <v>40</v>
+        <v>4.2</v>
       </c>
       <c r="BE47" t="n">
-        <v>7.6</v>
+        <v>4.4</v>
       </c>
       <c r="BF47" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="BG47" t="n">
-        <v>7.2</v>
+        <v>4.3</v>
       </c>
       <c r="BH47" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="BI47" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="BJ47" t="n">
         <v>11</v>
       </c>
       <c r="BK47" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL47" t="n">
         <v>1000</v>
       </c>
       <c r="BM47" t="n">
-        <v>15</v>
+        <v>2.4</v>
       </c>
       <c r="BN47" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BO47" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BP47" t="n">
+        <v>20</v>
+      </c>
+      <c r="BQ47" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BR47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS47" t="n">
+        <v>12</v>
+      </c>
+      <c r="BT47" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BU47" t="n">
         <v>5</v>
       </c>
-      <c r="BO47" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BP47" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BQ47" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BR47" t="n">
-        <v>40</v>
-      </c>
-      <c r="BS47" t="n">
+      <c r="BV47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW47" t="n">
         <v>11.5</v>
       </c>
-      <c r="BT47" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BU47" t="n">
-        <v>6</v>
-      </c>
-      <c r="BV47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW47" t="n">
-        <v>11</v>
-      </c>
       <c r="BX47" t="n">
         <v>1000</v>
       </c>
       <c r="BY47" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BZ47" t="n">
         <v>1000</v>
       </c>
       <c r="CA47" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -12553,7 +12553,7 @@
         <v>3.2</v>
       </c>
       <c r="J48" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="K48" t="n">
         <v>2.98</v>
@@ -12607,7 +12607,7 @@
         <v>75</v>
       </c>
       <c r="AB48" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC48" t="n">
         <v>7.4</v>
@@ -12658,7 +12658,7 @@
         <v>13</v>
       </c>
       <c r="AS48" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT48" t="n">
         <v>6.8</v>
@@ -12670,7 +12670,7 @@
         <v>10.5</v>
       </c>
       <c r="AW48" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AX48" t="n">
         <v>13.5</v>
@@ -12694,10 +12694,10 @@
         <v>6.2</v>
       </c>
       <c r="BE48" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF48" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BG48" t="n">
         <v>6</v>
@@ -12724,7 +12724,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BO48" t="n">
-        <v>4.3</v>
+        <v>1.35</v>
       </c>
       <c r="BP48" t="n">
         <v>46</v>
@@ -12742,7 +12742,7 @@
         <v>8</v>
       </c>
       <c r="BU48" t="n">
-        <v>4.2</v>
+        <v>1.35</v>
       </c>
       <c r="BV48" t="n">
         <v>44</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -12795,16 +12795,16 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="G49" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="H49" t="n">
         <v>6.8</v>
       </c>
       <c r="I49" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="J49" t="n">
         <v>4.6</v>
@@ -12825,28 +12825,28 @@
         <v>1.26</v>
       </c>
       <c r="P49" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="R49" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S49" t="n">
         <v>3</v>
       </c>
       <c r="T49" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U49" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V49" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W49" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="X49" t="n">
         <v>19.5</v>
@@ -12855,7 +12855,7 @@
         <v>25</v>
       </c>
       <c r="Z49" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AA49" t="n">
         <v>1000</v>
@@ -12870,22 +12870,22 @@
         <v>26</v>
       </c>
       <c r="AE49" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AF49" t="n">
         <v>10</v>
       </c>
       <c r="AG49" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AH49" t="n">
         <v>23</v>
       </c>
       <c r="AI49" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ49" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AK49" t="n">
         <v>15.5</v>
@@ -12894,7 +12894,7 @@
         <v>34</v>
       </c>
       <c r="AM49" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN49" t="n">
         <v>7.4</v>
@@ -12903,7 +12903,7 @@
         <v>110</v>
       </c>
       <c r="AP49" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AQ49" t="n">
         <v>21</v>
@@ -12933,7 +12933,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ49" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BA49" t="n">
         <v>36</v>
@@ -12960,65 +12960,65 @@
         <v>4.1</v>
       </c>
       <c r="BI49" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BJ49" t="n">
         <v>11</v>
       </c>
       <c r="BK49" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BL49" t="n">
         <v>1000</v>
       </c>
       <c r="BM49" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN49" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BO49" t="n">
         <v>3.3</v>
       </c>
       <c r="BP49" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BQ49" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BR49" t="n">
         <v>25</v>
       </c>
       <c r="BS49" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BT49" t="n">
         <v>11</v>
       </c>
       <c r="BU49" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BV49" t="n">
         <v>1000</v>
       </c>
       <c r="BW49" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BX49" t="n">
         <v>1000</v>
       </c>
       <c r="BY49" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BZ49" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="CA49" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -13058,7 +13058,7 @@
         <v>1.89</v>
       </c>
       <c r="I50" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="J50" t="n">
         <v>3.85</v>
@@ -13082,22 +13082,22 @@
         <v>2.16</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="R50" t="n">
         <v>1.45</v>
       </c>
       <c r="S50" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="T50" t="n">
         <v>1.71</v>
       </c>
       <c r="U50" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V50" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="W50" t="n">
         <v>1.28</v>
@@ -13106,55 +13106,55 @@
         <v>23</v>
       </c>
       <c r="Y50" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z50" t="n">
         <v>13</v>
       </c>
-      <c r="Z50" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AA50" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AB50" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AC50" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD50" t="n">
         <v>10.5</v>
       </c>
-      <c r="AD50" t="n">
-        <v>12</v>
-      </c>
       <c r="AE50" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AF50" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AG50" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AH50" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AI50" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AJ50" t="n">
         <v>110</v>
       </c>
       <c r="AK50" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AL50" t="n">
         <v>55</v>
       </c>
       <c r="AM50" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AN50" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AO50" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AP50" t="n">
         <v>16</v>
@@ -13163,13 +13163,13 @@
         <v>9.4</v>
       </c>
       <c r="AR50" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AS50" t="n">
         <v>19</v>
       </c>
       <c r="AT50" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AU50" t="n">
         <v>8</v>
@@ -13178,34 +13178,34 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW50" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AX50" t="n">
-        <v>4.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY50" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AZ50" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BA50" t="n">
-        <v>4.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB50" t="n">
-        <v>4.6</v>
+        <v>10</v>
       </c>
       <c r="BC50" t="n">
-        <v>4.4</v>
+        <v>9</v>
       </c>
       <c r="BD50" t="n">
-        <v>4.4</v>
+        <v>44</v>
       </c>
       <c r="BE50" t="n">
-        <v>4.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF50" t="n">
-        <v>4.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG50" t="n">
         <v>9.800000000000001</v>
@@ -13241,7 +13241,7 @@
         <v>11</v>
       </c>
       <c r="BR50" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS50" t="n">
         <v>11.5</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -13306,10 +13306,10 @@
         <v>1.98</v>
       </c>
       <c r="G51" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H51" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="I51" t="n">
         <v>4.3</v>
@@ -13357,58 +13357,58 @@
         <v>1.94</v>
       </c>
       <c r="X51" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF51" t="n">
         <v>17</v>
       </c>
-      <c r="Y51" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE51" t="n">
+      <c r="AG51" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI51" t="n">
         <v>60</v>
       </c>
-      <c r="AF51" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI51" t="n">
+      <c r="AJ51" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK51" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AO51" t="n">
         <v>55</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK51" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL51" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM51" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN51" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AO51" t="n">
-        <v>46</v>
       </c>
       <c r="AP51" t="n">
         <v>13.5</v>
@@ -13417,10 +13417,10 @@
         <v>13.5</v>
       </c>
       <c r="AR51" t="n">
-        <v>7</v>
+        <v>3.85</v>
       </c>
       <c r="AS51" t="n">
-        <v>8.199999999999999</v>
+        <v>4.1</v>
       </c>
       <c r="AT51" t="n">
         <v>9.4</v>
@@ -13432,10 +13432,10 @@
         <v>13.5</v>
       </c>
       <c r="AW51" t="n">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="AX51" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AY51" t="n">
         <v>9.6</v>
@@ -13444,25 +13444,25 @@
         <v>13.5</v>
       </c>
       <c r="BA51" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="BB51" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="BC51" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="BD51" t="n">
-        <v>7.2</v>
+        <v>3.9</v>
       </c>
       <c r="BE51" t="n">
-        <v>8.199999999999999</v>
+        <v>4.1</v>
       </c>
       <c r="BF51" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BG51" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="BH51" t="n">
         <v>3.85</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -13560,7 +13560,7 @@
         <v>2.06</v>
       </c>
       <c r="G52" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="H52" t="n">
         <v>3.65</v>
@@ -13569,10 +13569,10 @@
         <v>4.1</v>
       </c>
       <c r="J52" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K52" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L52" t="n">
         <v>1.31</v>
@@ -13581,22 +13581,22 @@
         <v>1.06</v>
       </c>
       <c r="N52" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="O52" t="n">
         <v>1.28</v>
       </c>
       <c r="P52" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="R52" t="n">
         <v>1.38</v>
       </c>
       <c r="S52" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="T52" t="n">
         <v>1.73</v>
@@ -13608,7 +13608,7 @@
         <v>1.32</v>
       </c>
       <c r="W52" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="X52" t="n">
         <v>19</v>
@@ -13617,7 +13617,7 @@
         <v>18.5</v>
       </c>
       <c r="Z52" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA52" t="n">
         <v>90</v>
@@ -13629,10 +13629,10 @@
         <v>10</v>
       </c>
       <c r="AD52" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE52" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF52" t="n">
         <v>16.5</v>
@@ -13659,37 +13659,37 @@
         <v>110</v>
       </c>
       <c r="AN52" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AO52" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AP52" t="n">
         <v>13.5</v>
       </c>
       <c r="AQ52" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AR52" t="n">
-        <v>20</v>
+        <v>3.85</v>
       </c>
       <c r="AS52" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AT52" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU52" t="n">
         <v>7</v>
       </c>
       <c r="AV52" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AW52" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AX52" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AY52" t="n">
         <v>9.199999999999999</v>
@@ -13698,34 +13698,34 @@
         <v>14.5</v>
       </c>
       <c r="BA52" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB52" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BC52" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD52" t="n">
         <v>3.95</v>
       </c>
-      <c r="BB52" t="n">
-        <v>19</v>
-      </c>
-      <c r="BC52" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD52" t="n">
-        <v>3.85</v>
-      </c>
       <c r="BE52" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BF52" t="n">
         <v>10.5</v>
       </c>
       <c r="BG52" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BH52" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BI52" t="n">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="BJ52" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK52" t="n">
         <v>5</v>
@@ -13734,7 +13734,7 @@
         <v>1000</v>
       </c>
       <c r="BM52" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN52" t="n">
         <v>5.2</v>
@@ -13749,10 +13749,10 @@
         <v>6.2</v>
       </c>
       <c r="BR52" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BS52" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT52" t="n">
         <v>7.4</v>
@@ -13761,7 +13761,7 @@
         <v>5.3</v>
       </c>
       <c r="BV52" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BW52" t="n">
         <v>7.8</v>
@@ -13770,17 +13770,17 @@
         <v>40</v>
       </c>
       <c r="BY52" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BZ52" t="n">
         <v>24</v>
       </c>
       <c r="CA52" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>
@@ -13817,10 +13817,10 @@
         <v>3.1</v>
       </c>
       <c r="H53" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="I53" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="J53" t="n">
         <v>3.9</v>
@@ -13829,7 +13829,7 @@
         <v>4.1</v>
       </c>
       <c r="L53" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M53" t="n">
         <v>1.03</v>
@@ -13844,10 +13844,10 @@
         <v>2.6</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R53" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="S53" t="n">
         <v>2.48</v>
@@ -13856,7 +13856,7 @@
         <v>1.54</v>
       </c>
       <c r="U53" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="V53" t="n">
         <v>1.72</v>
@@ -13868,19 +13868,19 @@
         <v>27</v>
       </c>
       <c r="Y53" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="Z53" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AA53" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AB53" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AC53" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD53" t="n">
         <v>12.5</v>
@@ -13904,7 +13904,7 @@
         <v>55</v>
       </c>
       <c r="AK53" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AL53" t="n">
         <v>34</v>
@@ -13934,7 +13934,7 @@
         <v>16</v>
       </c>
       <c r="AU53" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV53" t="n">
         <v>10.5</v>
@@ -13946,10 +13946,10 @@
         <v>17</v>
       </c>
       <c r="AY53" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AZ53" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BA53" t="n">
         <v>18.5</v>
@@ -13973,7 +13973,7 @@
         <v>11</v>
       </c>
       <c r="BH53" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BI53" t="n">
         <v>3.6</v>
@@ -13997,7 +13997,7 @@
         <v>5.2</v>
       </c>
       <c r="BP53" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BQ53" t="n">
         <v>1.04</v>
@@ -14015,7 +14015,7 @@
         <v>4.5</v>
       </c>
       <c r="BV53" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BW53" t="n">
         <v>1.04</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-07-16 18:49:10</t>
+          <t>2026-07-16 21:09:14</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-17.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="G2" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="H2" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="I2" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K2" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L2" t="n">
         <v>1.42</v>
@@ -881,49 +881,49 @@
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="O2" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P2" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S2" t="n">
         <v>3.55</v>
       </c>
       <c r="T2" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="U2" t="n">
         <v>2.18</v>
       </c>
       <c r="V2" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="W2" t="n">
         <v>1.34</v>
       </c>
       <c r="X2" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="Z2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>27</v>
+      </c>
+      <c r="AB2" t="n">
         <v>14</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>30</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>14.5</v>
       </c>
       <c r="AC2" t="n">
         <v>8</v>
@@ -932,37 +932,37 @@
         <v>10.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF2" t="n">
         <v>28</v>
       </c>
       <c r="AG2" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AH2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI2" t="n">
         <v>38</v>
       </c>
       <c r="AJ2" t="n">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="AK2" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AL2" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM2" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN2" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AO2" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AP2" t="n">
         <v>13.5</v>
@@ -971,64 +971,64 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AR2" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AS2" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW2" t="n">
         <v>20</v>
       </c>
-      <c r="AT2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>17.5</v>
-      </c>
       <c r="AX2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AY2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ2" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BB2" t="n">
-        <v>10.5</v>
+        <v>32</v>
       </c>
       <c r="BC2" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BD2" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BE2" t="n">
         <v>75</v>
       </c>
       <c r="BF2" t="n">
-        <v>9.6</v>
+        <v>42</v>
       </c>
       <c r="BG2" t="n">
         <v>14.5</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="BJ2" t="n">
         <v>9.6</v>
       </c>
       <c r="BK2" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
@@ -1040,19 +1040,19 @@
         <v>7</v>
       </c>
       <c r="BO2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BR2" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BT2" t="n">
         <v>4.9</v>
@@ -1064,23 +1064,23 @@
         <v>15.5</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA2" t="n">
         <v>11</v>
       </c>
-      <c r="BZ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>10.5</v>
-      </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -1117,13 +1117,13 @@
         <v>2.22</v>
       </c>
       <c r="H3" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="I3" t="n">
         <v>4.1</v>
       </c>
       <c r="J3" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K3" t="n">
         <v>3.85</v>
@@ -1135,37 +1135,37 @@
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="O3" t="n">
         <v>1.29</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="R3" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="S3" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="T3" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="U3" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="V3" t="n">
         <v>1.32</v>
       </c>
       <c r="W3" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="X3" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y3" t="n">
         <v>15.5</v>
@@ -1174,7 +1174,7 @@
         <v>29</v>
       </c>
       <c r="AA3" t="n">
-        <v>90</v>
+        <v>160</v>
       </c>
       <c r="AB3" t="n">
         <v>10.5</v>
@@ -1186,7 +1186,7 @@
         <v>16.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AF3" t="n">
         <v>14.5</v>
@@ -1201,22 +1201,22 @@
         <v>55</v>
       </c>
       <c r="AJ3" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AK3" t="n">
         <v>22</v>
       </c>
       <c r="AL3" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM3" t="n">
         <v>320</v>
       </c>
       <c r="AN3" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AO3" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AP3" t="n">
         <v>13</v>
@@ -1225,7 +1225,7 @@
         <v>13</v>
       </c>
       <c r="AR3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS3" t="n">
         <v>50</v>
@@ -1261,80 +1261,80 @@
         <v>19.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BE3" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BF3" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="BJ3" t="n">
         <v>9.4</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BN3" t="n">
         <v>5.1</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="BP3" t="n">
         <v>15.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BR3" t="n">
         <v>28</v>
       </c>
       <c r="BS3" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT3" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BV3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BW3" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="CA3" t="n">
         <v>9</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
         <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="H4" t="n">
         <v>1.96</v>
@@ -1383,19 +1383,19 @@
         <v>3.9</v>
       </c>
       <c r="L4" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="O4" t="n">
         <v>1.27</v>
       </c>
       <c r="P4" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q4" t="n">
         <v>1.79</v>
@@ -1419,10 +1419,10 @@
         <v>1.29</v>
       </c>
       <c r="X4" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="Y4" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="Z4" t="n">
         <v>13.5</v>
@@ -1431,7 +1431,7 @@
         <v>23</v>
       </c>
       <c r="AB4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AC4" t="n">
         <v>9.800000000000001</v>
@@ -1446,16 +1446,16 @@
         <v>70</v>
       </c>
       <c r="AG4" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI4" t="n">
         <v>34</v>
       </c>
       <c r="AJ4" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AK4" t="n">
         <v>120</v>
@@ -1470,7 +1470,7 @@
         <v>140</v>
       </c>
       <c r="AO4" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AP4" t="n">
         <v>14.5</v>
@@ -1485,7 +1485,7 @@
         <v>20</v>
       </c>
       <c r="AT4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AU4" t="n">
         <v>7.4</v>
@@ -1497,7 +1497,7 @@
         <v>17</v>
       </c>
       <c r="AX4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AY4" t="n">
         <v>14.5</v>
@@ -1509,19 +1509,19 @@
         <v>20</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.1</v>
+        <v>23</v>
       </c>
       <c r="BD4" t="n">
-        <v>9.6</v>
+        <v>36</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.4</v>
+        <v>10.5</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.1</v>
+        <v>10.5</v>
       </c>
       <c r="BG4" t="n">
         <v>11</v>
@@ -1530,65 +1530,65 @@
         <v>3.6</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="BJ4" t="n">
         <v>9.6</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN4" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BO4" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BR4" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BS4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT4" t="n">
         <v>4.8</v>
       </c>
       <c r="BU4" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="BV4" t="n">
         <v>14</v>
       </c>
       <c r="BW4" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BX4" t="n">
         <v>27</v>
       </c>
       <c r="BY4" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ4" t="n">
         <v>23</v>
       </c>
       <c r="CA4" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="G5" t="n">
         <v>4.8</v>
       </c>
       <c r="H5" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="I5" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="J5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K5" t="n">
         <v>4.4</v>
@@ -1643,16 +1643,16 @@
         <v>1.04</v>
       </c>
       <c r="N5" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="O5" t="n">
         <v>1.2</v>
       </c>
       <c r="P5" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="R5" t="n">
         <v>1.59</v>
@@ -1667,13 +1667,13 @@
         <v>2.48</v>
       </c>
       <c r="V5" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="W5" t="n">
         <v>1.26</v>
       </c>
       <c r="X5" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Y5" t="n">
         <v>12.5</v>
@@ -1700,7 +1700,7 @@
         <v>80</v>
       </c>
       <c r="AG5" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AH5" t="n">
         <v>16</v>
@@ -1727,7 +1727,7 @@
         <v>8.6</v>
       </c>
       <c r="AP5" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AQ5" t="n">
         <v>11</v>
@@ -1736,10 +1736,10 @@
         <v>12</v>
       </c>
       <c r="AS5" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AT5" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AU5" t="n">
         <v>9</v>
@@ -1751,7 +1751,7 @@
         <v>14.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY5" t="n">
         <v>15.5</v>
@@ -1763,61 +1763,61 @@
         <v>22</v>
       </c>
       <c r="BB5" t="n">
+        <v>42</v>
+      </c>
+      <c r="BC5" t="n">
         <v>36</v>
       </c>
-      <c r="BC5" t="n">
-        <v>34</v>
-      </c>
       <c r="BD5" t="n">
+        <v>29</v>
+      </c>
+      <c r="BE5" t="n">
         <v>36</v>
       </c>
-      <c r="BE5" t="n">
-        <v>48</v>
-      </c>
       <c r="BF5" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BG5" t="n">
         <v>7.6</v>
       </c>
       <c r="BH5" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="BJ5" t="n">
         <v>10.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="BL5" t="n">
         <v>100</v>
       </c>
       <c r="BM5" t="n">
-        <v>5.5</v>
+        <v>7.4</v>
       </c>
       <c r="BN5" t="n">
         <v>9.4</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.55</v>
+        <v>7.2</v>
       </c>
       <c r="BP5" t="n">
         <v>38</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="BR5" t="n">
         <v>44</v>
       </c>
       <c r="BS5" t="n">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="BT5" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="BU5" t="n">
         <v>4.3</v>
@@ -1826,23 +1826,23 @@
         <v>13.5</v>
       </c>
       <c r="BW5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BX5" t="n">
         <v>25</v>
       </c>
       <c r="BY5" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="BZ5" t="n">
         <v>18</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
         <v>1.98</v>
       </c>
       <c r="I6" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="J6" t="n">
         <v>3.15</v>
@@ -1891,13 +1891,13 @@
         <v>3.6</v>
       </c>
       <c r="L6" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="M6" t="n">
         <v>1.1</v>
       </c>
       <c r="N6" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="O6" t="n">
         <v>1.43</v>
@@ -1906,7 +1906,7 @@
         <v>1.63</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="R6" t="n">
         <v>1.23</v>
@@ -1915,10 +1915,10 @@
         <v>4.4</v>
       </c>
       <c r="T6" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="U6" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V6" t="n">
         <v>1.84</v>
@@ -1981,7 +1981,7 @@
         <v>23</v>
       </c>
       <c r="AP6" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ6" t="n">
         <v>6.4</v>
@@ -2005,7 +2005,7 @@
         <v>18.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AY6" t="n">
         <v>13.5</v>
@@ -2038,65 +2038,65 @@
         <v>3.05</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.4</v>
+        <v>2.66</v>
       </c>
       <c r="BJ6" t="n">
         <v>11.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="BN6" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BO6" t="n">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="BT6" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="BV6" t="n">
         <v>16.5</v>
       </c>
       <c r="BW6" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>2.22</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -2136,10 +2136,10 @@
         <v>2.2</v>
       </c>
       <c r="I7" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="K7" t="n">
         <v>3.3</v>
@@ -2151,31 +2151,31 @@
         <v>1.1</v>
       </c>
       <c r="N7" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="O7" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="P7" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="Q7" t="n">
         <v>2.5</v>
       </c>
       <c r="R7" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S7" t="n">
         <v>5.1</v>
       </c>
       <c r="T7" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U7" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="V7" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="W7" t="n">
         <v>1.3</v>
@@ -2289,68 +2289,68 @@
         <v>7.4</v>
       </c>
       <c r="BH7" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.32</v>
+        <v>2.48</v>
       </c>
       <c r="BJ7" t="n">
         <v>12</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BN7" t="n">
         <v>7.2</v>
       </c>
       <c r="BO7" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BP7" t="n">
         <v>40</v>
       </c>
       <c r="BQ7" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BR7" t="n">
         <v>65</v>
       </c>
       <c r="BS7" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BT7" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BU7" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BV7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BW7" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BX7" t="n">
         <v>44</v>
       </c>
       <c r="BY7" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ7" t="n">
         <v>48</v>
       </c>
       <c r="CA7" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -2384,19 +2384,19 @@
         <v>1.36</v>
       </c>
       <c r="G8" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="H8" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="I8" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="J8" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="K8" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="L8" t="n">
         <v>1.28</v>
@@ -2405,55 +2405,55 @@
         <v>1.03</v>
       </c>
       <c r="N8" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="O8" t="n">
         <v>1.19</v>
       </c>
       <c r="P8" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="R8" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="S8" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="T8" t="n">
         <v>1.92</v>
       </c>
       <c r="U8" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V8" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="W8" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="X8" t="n">
+        <v>27</v>
+      </c>
+      <c r="Y8" t="n">
         <v>42</v>
       </c>
-      <c r="Y8" t="n">
-        <v>44</v>
-      </c>
       <c r="Z8" t="n">
         <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AB8" t="n">
         <v>11</v>
       </c>
       <c r="AC8" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AD8" t="n">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="AE8" t="n">
         <v>1000</v>
@@ -2468,13 +2468,13 @@
         <v>26</v>
       </c>
       <c r="AI8" t="n">
-        <v>230</v>
+        <v>120</v>
       </c>
       <c r="AJ8" t="n">
         <v>11.5</v>
       </c>
       <c r="AK8" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AL8" t="n">
         <v>32</v>
@@ -2489,16 +2489,16 @@
         <v>140</v>
       </c>
       <c r="AP8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ8" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AR8" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AS8" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="AT8" t="n">
         <v>9.800000000000001</v>
@@ -2507,104 +2507,104 @@
         <v>12</v>
       </c>
       <c r="AV8" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AW8" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="AX8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AY8" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ8" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="BA8" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="BB8" t="n">
         <v>10.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD8" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BE8" t="n">
         <v>40</v>
       </c>
       <c r="BF8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>80</v>
+      </c>
+      <c r="BH8" t="n">
         <v>4.5</v>
       </c>
-      <c r="BG8" t="n">
-        <v>42</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BI8" t="n">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="BJ8" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN8" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="BP8" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BR8" t="n">
         <v>22</v>
       </c>
       <c r="BS8" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="BT8" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BU8" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>9.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>9.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="BZ8" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="CA8" t="n">
-        <v>5.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="G9" t="n">
         <v>1.48</v>
       </c>
       <c r="H9" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="I9" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="J9" t="n">
         <v>5.1</v>
       </c>
       <c r="K9" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L9" t="n">
         <v>1.23</v>
@@ -2659,49 +2659,49 @@
         <v>1.02</v>
       </c>
       <c r="N9" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="O9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="V9" t="n">
         <v>1.13</v>
-      </c>
-      <c r="P9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.14</v>
       </c>
       <c r="W9" t="n">
         <v>3.05</v>
       </c>
       <c r="X9" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Y9" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Z9" t="n">
         <v>160</v>
       </c>
       <c r="AA9" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AB9" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC9" t="n">
         <v>13</v>
@@ -2710,19 +2710,19 @@
         <v>32</v>
       </c>
       <c r="AE9" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AF9" t="n">
         <v>12.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH9" t="n">
         <v>18.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>150</v>
+        <v>70</v>
       </c>
       <c r="AJ9" t="n">
         <v>15</v>
@@ -2737,25 +2737,25 @@
         <v>70</v>
       </c>
       <c r="AN9" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AO9" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AP9" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AQ9" t="n">
         <v>36</v>
       </c>
       <c r="AR9" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="AS9" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AU9" t="n">
         <v>12</v>
@@ -2764,10 +2764,10 @@
         <v>24</v>
       </c>
       <c r="AW9" t="n">
-        <v>15.5</v>
+        <v>50</v>
       </c>
       <c r="AX9" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY9" t="n">
         <v>10</v>
@@ -2779,86 +2779,86 @@
         <v>55</v>
       </c>
       <c r="BB9" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BC9" t="n">
         <v>12</v>
       </c>
       <c r="BD9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BE9" t="n">
         <v>55</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BG9" t="n">
         <v>15</v>
       </c>
       <c r="BH9" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="BI9" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BJ9" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BK9" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="BL9" t="n">
         <v>80</v>
       </c>
       <c r="BM9" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="BN9" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="BP9" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BR9" t="n">
         <v>18.5</v>
       </c>
       <c r="BS9" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="BT9" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BV9" t="n">
         <v>48</v>
       </c>
       <c r="BW9" t="n">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="BX9" t="n">
         <v>44</v>
       </c>
       <c r="BY9" t="n">
-        <v>8.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BZ9" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="CA9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -2904,10 +2904,10 @@
         <v>4.1</v>
       </c>
       <c r="K10" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L10" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="M10" t="n">
         <v>1.02</v>
@@ -2922,13 +2922,13 @@
         <v>3.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="R10" t="n">
         <v>1.94</v>
       </c>
       <c r="S10" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="T10" t="n">
         <v>1.4</v>
@@ -2946,13 +2946,13 @@
         <v>40</v>
       </c>
       <c r="Y10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z10" t="n">
         <v>27</v>
       </c>
       <c r="AA10" t="n">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="AB10" t="n">
         <v>24</v>
@@ -2970,7 +2970,7 @@
         <v>27</v>
       </c>
       <c r="AG10" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH10" t="n">
         <v>13.5</v>
@@ -2997,13 +2997,13 @@
         <v>10.5</v>
       </c>
       <c r="AP10" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AQ10" t="n">
         <v>21</v>
       </c>
       <c r="AR10" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AS10" t="n">
         <v>28</v>
@@ -3021,7 +3021,7 @@
         <v>20</v>
       </c>
       <c r="AX10" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AY10" t="n">
         <v>12</v>
@@ -3030,7 +3030,7 @@
         <v>11.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BB10" t="n">
         <v>28</v>
@@ -3042,7 +3042,7 @@
         <v>21</v>
       </c>
       <c r="BE10" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BF10" t="n">
         <v>9.6</v>
@@ -3054,55 +3054,55 @@
         <v>5.4</v>
       </c>
       <c r="BI10" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BJ10" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BK10" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="BL10" t="n">
         <v>55</v>
       </c>
       <c r="BM10" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BN10" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BO10" t="n">
         <v>5.2</v>
       </c>
       <c r="BP10" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BQ10" t="n">
-        <v>7.4</v>
+        <v>12</v>
       </c>
       <c r="BR10" t="n">
         <v>21</v>
       </c>
       <c r="BS10" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BT10" t="n">
         <v>6.6</v>
       </c>
       <c r="BU10" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BV10" t="n">
         <v>16</v>
       </c>
       <c r="BW10" t="n">
-        <v>7.2</v>
+        <v>12.5</v>
       </c>
       <c r="BX10" t="n">
         <v>22</v>
       </c>
       <c r="BY10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
         <v>1.42</v>
       </c>
       <c r="P11" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="Q11" t="n">
         <v>2.22</v>
@@ -3185,13 +3185,13 @@
         <v>4.2</v>
       </c>
       <c r="T11" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="U11" t="n">
         <v>1.93</v>
       </c>
       <c r="V11" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W11" t="n">
         <v>1.58</v>
@@ -3218,7 +3218,7 @@
         <v>15</v>
       </c>
       <c r="AE11" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF11" t="n">
         <v>17</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="G12" t="n">
         <v>7</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
         <v>1.33</v>
       </c>
       <c r="G13" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="H13" t="n">
         <v>9.199999999999999</v>
@@ -3681,19 +3681,19 @@
         <v>1.1</v>
       </c>
       <c r="P13" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="Q13" t="n">
         <v>1.31</v>
       </c>
       <c r="R13" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="S13" t="n">
         <v>1.78</v>
       </c>
       <c r="T13" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="U13" t="n">
         <v>2.28</v>
@@ -3702,7 +3702,7 @@
         <v>1.1</v>
       </c>
       <c r="W13" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="X13" t="n">
         <v>60</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -3947,10 +3947,10 @@
         <v>3.4</v>
       </c>
       <c r="T14" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="U14" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V14" t="n">
         <v>2.32</v>
@@ -3962,28 +3962,28 @@
         <v>17.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z14" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AB14" t="n">
         <v>24</v>
       </c>
       <c r="AC14" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD14" t="n">
         <v>12</v>
       </c>
       <c r="AE14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF14" t="n">
-        <v>230</v>
+        <v>55</v>
       </c>
       <c r="AG14" t="n">
         <v>25</v>
@@ -4049,19 +4049,19 @@
         <v>28</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BF14" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BG14" t="n">
         <v>9.6</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -4198,7 +4198,7 @@
         <v>1.53</v>
       </c>
       <c r="S15" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="T15" t="n">
         <v>1.64</v>
@@ -4222,7 +4222,7 @@
         <v>34</v>
       </c>
       <c r="AA15" t="n">
-        <v>85</v>
+        <v>160</v>
       </c>
       <c r="AB15" t="n">
         <v>12</v>
@@ -4315,7 +4315,7 @@
         <v>60</v>
       </c>
       <c r="BF15" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BG15" t="n">
         <v>30</v>
@@ -4336,7 +4336,7 @@
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN15" t="n">
         <v>5.1</v>
@@ -4345,7 +4345,7 @@
         <v>4.3</v>
       </c>
       <c r="BP15" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BQ15" t="n">
         <v>6</v>
@@ -4366,23 +4366,23 @@
         <v>30</v>
       </c>
       <c r="BW15" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX15" t="n">
         <v>38</v>
       </c>
       <c r="BY15" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BZ15" t="n">
         <v>19</v>
       </c>
       <c r="CA15" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4416,7 @@
         <v>1.91</v>
       </c>
       <c r="G16" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="H16" t="n">
         <v>4.3</v>
@@ -4431,7 +4431,7 @@
         <v>4.2</v>
       </c>
       <c r="L16" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M16" t="n">
         <v>1.05</v>
@@ -4452,7 +4452,7 @@
         <v>1.53</v>
       </c>
       <c r="S16" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="T16" t="n">
         <v>1.67</v>
@@ -4602,7 +4602,7 @@
         <v>13</v>
       </c>
       <c r="BQ16" t="n">
-        <v>9.6</v>
+        <v>5.7</v>
       </c>
       <c r="BR16" t="n">
         <v>24</v>
@@ -4632,11 +4632,11 @@
         <v>18.5</v>
       </c>
       <c r="CA16" t="n">
-        <v>13</v>
+        <v>6.4</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -4673,10 +4673,10 @@
         <v>1.18</v>
       </c>
       <c r="H17" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="I17" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J17" t="n">
         <v>9.800000000000001</v>
@@ -4694,7 +4694,7 @@
         <v>10.5</v>
       </c>
       <c r="O17" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="P17" t="n">
         <v>4.1</v>
@@ -4703,13 +4703,13 @@
         <v>1.29</v>
       </c>
       <c r="R17" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="S17" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="T17" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="U17" t="n">
         <v>2.02</v>
@@ -4733,7 +4733,7 @@
         <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AC17" t="n">
         <v>25</v>
@@ -4745,13 +4745,13 @@
         <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AI17" t="n">
         <v>1000</v>
@@ -4760,10 +4760,10 @@
         <v>10.5</v>
       </c>
       <c r="AK17" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AL17" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM17" t="n">
         <v>490</v>
@@ -4781,10 +4781,10 @@
         <v>34</v>
       </c>
       <c r="AR17" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AS17" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AT17" t="n">
         <v>15</v>
@@ -4793,7 +4793,7 @@
         <v>21</v>
       </c>
       <c r="AV17" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="AW17" t="n">
         <v>48</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
         <v>3.25</v>
       </c>
       <c r="J18" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="K18" t="n">
         <v>3.1</v>
@@ -4960,7 +4960,7 @@
         <v>1.13</v>
       </c>
       <c r="S18" t="n">
-        <v>1.05</v>
+        <v>5.5</v>
       </c>
       <c r="T18" t="n">
         <v>2.28</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -5178,7 +5178,7 @@
         <v>2.24</v>
       </c>
       <c r="G19" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="H19" t="n">
         <v>3.55</v>
@@ -5187,7 +5187,7 @@
         <v>4.7</v>
       </c>
       <c r="J19" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="K19" t="n">
         <v>3.1</v>
@@ -5205,7 +5205,7 @@
         <v>1.69</v>
       </c>
       <c r="P19" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="Q19" t="n">
         <v>3.05</v>
@@ -5214,7 +5214,7 @@
         <v>1.12</v>
       </c>
       <c r="S19" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="T19" t="n">
         <v>2.36</v>
@@ -5223,10 +5223,10 @@
         <v>1.57</v>
       </c>
       <c r="V19" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W19" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X19" t="n">
         <v>7</v>
@@ -5283,10 +5283,10 @@
         <v>500</v>
       </c>
       <c r="AP19" t="n">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="AQ19" t="n">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="AR19" t="n">
         <v>6.4</v>
@@ -5298,7 +5298,7 @@
         <v>3.7</v>
       </c>
       <c r="AU19" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="AV19" t="n">
         <v>5.9</v>
@@ -5310,7 +5310,7 @@
         <v>5.8</v>
       </c>
       <c r="AY19" t="n">
-        <v>7.6</v>
+        <v>5.2</v>
       </c>
       <c r="AZ19" t="n">
         <v>6.4</v>
@@ -5337,68 +5337,68 @@
         <v>7.8</v>
       </c>
       <c r="BH19" t="n">
-        <v>1000</v>
+        <v>2.7</v>
       </c>
       <c r="BI19" t="n">
-        <v>1.04</v>
+        <v>2</v>
       </c>
       <c r="BJ19" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BK19" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BL19" t="n">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BN19" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.04</v>
+        <v>2.76</v>
       </c>
       <c r="BP19" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BQ19" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BR19" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BS19" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BT19" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU19" t="n">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="BV19" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BW19" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BX19" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BZ19" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="CA19" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -5429,28 +5429,28 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.32</v>
+        <v>1.78</v>
       </c>
       <c r="G20" t="n">
-        <v>2.86</v>
+        <v>2.98</v>
       </c>
       <c r="H20" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="I20" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="J20" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="K20" t="n">
-        <v>3.15</v>
+        <v>7</v>
       </c>
       <c r="L20" t="n">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="M20" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="N20" t="n">
         <v>2.16</v>
@@ -5459,73 +5459,73 @@
         <v>1.61</v>
       </c>
       <c r="P20" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.78</v>
+        <v>2</v>
       </c>
       <c r="R20" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="S20" t="n">
-        <v>5.1</v>
+        <v>2.68</v>
       </c>
       <c r="T20" t="n">
-        <v>2.14</v>
+        <v>1.11</v>
       </c>
       <c r="U20" t="n">
-        <v>1.59</v>
+        <v>1.11</v>
       </c>
       <c r="V20" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="W20" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="X20" t="n">
-        <v>7.8</v>
+        <v>970</v>
       </c>
       <c r="Y20" t="n">
-        <v>10</v>
+        <v>970</v>
       </c>
       <c r="Z20" t="n">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="AA20" t="n">
         <v>900</v>
       </c>
       <c r="AB20" t="n">
-        <v>7.6</v>
+        <v>970</v>
       </c>
       <c r="AC20" t="n">
-        <v>7.8</v>
+        <v>42</v>
       </c>
       <c r="AD20" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AE20" t="n">
         <v>500</v>
       </c>
       <c r="AF20" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AG20" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AH20" t="n">
-        <v>32</v>
+        <v>950</v>
       </c>
       <c r="AI20" t="n">
         <v>540</v>
       </c>
       <c r="AJ20" t="n">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="AK20" t="n">
-        <v>120</v>
+        <v>230</v>
       </c>
       <c r="AL20" t="n">
-        <v>460</v>
+        <v>500</v>
       </c>
       <c r="AM20" t="n">
         <v>500</v>
@@ -5543,10 +5543,10 @@
         <v>5.1</v>
       </c>
       <c r="AR20" t="n">
-        <v>5.2</v>
+        <v>1.74</v>
       </c>
       <c r="AS20" t="n">
-        <v>6</v>
+        <v>1.76</v>
       </c>
       <c r="AT20" t="n">
         <v>3.85</v>
@@ -5555,40 +5555,40 @@
         <v>4.2</v>
       </c>
       <c r="AV20" t="n">
-        <v>4.8</v>
+        <v>1.73</v>
       </c>
       <c r="AW20" t="n">
-        <v>6</v>
+        <v>1.76</v>
       </c>
       <c r="AX20" t="n">
         <v>6.4</v>
       </c>
       <c r="AY20" t="n">
-        <v>4.5</v>
+        <v>1.66</v>
       </c>
       <c r="AZ20" t="n">
-        <v>5.4</v>
+        <v>1.74</v>
       </c>
       <c r="BA20" t="n">
-        <v>6</v>
+        <v>1.77</v>
       </c>
       <c r="BB20" t="n">
-        <v>5.7</v>
+        <v>1.75</v>
       </c>
       <c r="BC20" t="n">
-        <v>5.7</v>
+        <v>1.75</v>
       </c>
       <c r="BD20" t="n">
-        <v>6</v>
+        <v>1.76</v>
       </c>
       <c r="BE20" t="n">
-        <v>6.2</v>
+        <v>1.77</v>
       </c>
       <c r="BF20" t="n">
-        <v>5.8</v>
+        <v>1.76</v>
       </c>
       <c r="BG20" t="n">
-        <v>6.2</v>
+        <v>1.77</v>
       </c>
       <c r="BH20" t="n">
         <v>2.7</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -5698,13 +5698,13 @@
         <v>2.8</v>
       </c>
       <c r="K21" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="L21" t="n">
         <v>1.46</v>
       </c>
       <c r="M21" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N21" t="n">
         <v>2.52</v>
@@ -5716,13 +5716,13 @@
         <v>1.51</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R21" t="n">
         <v>1.18</v>
       </c>
       <c r="S21" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="T21" t="n">
         <v>1.95</v>
@@ -5746,7 +5746,7 @@
         <v>26</v>
       </c>
       <c r="AA21" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB21" t="n">
         <v>8.6</v>
@@ -5800,7 +5800,7 @@
         <v>5.1</v>
       </c>
       <c r="AS21" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AT21" t="n">
         <v>4.4</v>
@@ -5809,28 +5809,28 @@
         <v>4.2</v>
       </c>
       <c r="AV21" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="AW21" t="n">
         <v>5.8</v>
       </c>
       <c r="AX21" t="n">
-        <v>7</v>
+        <v>4.6</v>
       </c>
       <c r="AY21" t="n">
-        <v>7</v>
+        <v>4.3</v>
       </c>
       <c r="AZ21" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BA21" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BB21" t="n">
         <v>5.5</v>
       </c>
       <c r="BC21" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BD21" t="n">
         <v>5.8</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -5937,34 +5937,34 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="G22" t="n">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="H22" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="I22" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="J22" t="n">
         <v>3.65</v>
       </c>
       <c r="K22" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="L22" t="n">
         <v>1.29</v>
       </c>
       <c r="M22" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N22" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O22" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P22" t="n">
         <v>2.1</v>
@@ -5976,127 +5976,127 @@
         <v>1.44</v>
       </c>
       <c r="S22" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="T22" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="U22" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V22" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="W22" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="X22" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="Y22" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF22" t="n">
         <v>16</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>440</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>50</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>15.5</v>
       </c>
       <c r="AG22" t="n">
         <v>11.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI22" t="n">
-        <v>110</v>
+        <v>44</v>
       </c>
       <c r="AJ22" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AK22" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AL22" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AM22" t="n">
-        <v>320</v>
+        <v>95</v>
       </c>
       <c r="AN22" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AO22" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="AP22" t="n">
-        <v>6.6</v>
+        <v>14.5</v>
       </c>
       <c r="AQ22" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR22" t="n">
         <v>21</v>
       </c>
       <c r="AS22" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AT22" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AU22" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV22" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW22" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB22" t="n">
         <v>25</v>
       </c>
-      <c r="AX22" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA22" t="n">
+      <c r="BC22" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD22" t="n">
         <v>30</v>
       </c>
-      <c r="BB22" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>16</v>
-      </c>
       <c r="BE22" t="n">
-        <v>8.4</v>
+        <v>60</v>
       </c>
       <c r="BF22" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BH22" t="n">
         <v>1000</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -6203,7 +6203,7 @@
         <v>5.8</v>
       </c>
       <c r="J23" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K23" t="n">
         <v>4.3</v>
@@ -6227,7 +6227,7 @@
         <v>2</v>
       </c>
       <c r="R23" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S23" t="n">
         <v>3.2</v>
@@ -6257,7 +6257,7 @@
         <v>900</v>
       </c>
       <c r="AB23" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC23" t="n">
         <v>9.4</v>
@@ -6308,7 +6308,7 @@
         <v>16</v>
       </c>
       <c r="AS23" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT23" t="n">
         <v>7</v>
@@ -6350,7 +6350,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BG23" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH23" t="n">
         <v>1000</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -6457,7 +6457,7 @@
         <v>85</v>
       </c>
       <c r="J24" t="n">
-        <v>11.5</v>
+        <v>7</v>
       </c>
       <c r="K24" t="n">
         <v>18.5</v>
@@ -6469,7 +6469,7 @@
         <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>6.6</v>
+        <v>4.4</v>
       </c>
       <c r="O24" t="n">
         <v>1.09</v>
@@ -6481,25 +6481,25 @@
         <v>1.28</v>
       </c>
       <c r="R24" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="S24" t="n">
-        <v>1.71</v>
+        <v>1.59</v>
       </c>
       <c r="T24" t="n">
-        <v>2.96</v>
+        <v>2.62</v>
       </c>
       <c r="U24" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="V24" t="n">
         <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="X24" t="n">
-        <v>75</v>
+        <v>950</v>
       </c>
       <c r="Y24" t="n">
         <v>950</v>
@@ -6514,7 +6514,7 @@
         <v>15.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>950</v>
+        <v>80</v>
       </c>
       <c r="AD24" t="n">
         <v>950</v>
@@ -6538,16 +6538,16 @@
         <v>7.6</v>
       </c>
       <c r="AK24" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AL24" t="n">
-        <v>110</v>
+        <v>510</v>
       </c>
       <c r="AM24" t="n">
         <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="AO24" t="n">
         <v>1000</v>
@@ -6568,7 +6568,7 @@
         <v>7.6</v>
       </c>
       <c r="AU24" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="AV24" t="n">
         <v>4.2</v>
@@ -6583,7 +6583,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ24" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="BA24" t="n">
         <v>4.2</v>
@@ -6592,16 +6592,16 @@
         <v>5</v>
       </c>
       <c r="BC24" t="n">
-        <v>8.199999999999999</v>
+        <v>1.96</v>
       </c>
       <c r="BD24" t="n">
         <v>2.12</v>
       </c>
       <c r="BE24" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="BF24" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="BG24" t="n">
         <v>10.5</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -6705,13 +6705,13 @@
         <v>2.46</v>
       </c>
       <c r="H25" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="I25" t="n">
         <v>3.75</v>
       </c>
       <c r="J25" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K25" t="n">
         <v>3.65</v>
@@ -6750,7 +6750,7 @@
         <v>1.36</v>
       </c>
       <c r="W25" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="X25" t="n">
         <v>11.5</v>
@@ -6771,7 +6771,7 @@
         <v>7.8</v>
       </c>
       <c r="AD25" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AE25" t="n">
         <v>130</v>
@@ -6855,7 +6855,7 @@
         <v>10.5</v>
       </c>
       <c r="BF25" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BG25" t="n">
         <v>9.4</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -6956,7 +6956,7 @@
         <v>1.33</v>
       </c>
       <c r="G26" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="H26" t="n">
         <v>9.6</v>
@@ -6974,7 +6974,7 @@
         <v>1.23</v>
       </c>
       <c r="M26" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N26" t="n">
         <v>5.6</v>
@@ -7004,7 +7004,7 @@
         <v>1.1</v>
       </c>
       <c r="W26" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="X26" t="n">
         <v>28</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -7228,16 +7228,16 @@
         <v>1.24</v>
       </c>
       <c r="M27" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N27" t="n">
         <v>5.2</v>
       </c>
       <c r="O27" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P27" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="Q27" t="n">
         <v>1.56</v>
@@ -7252,7 +7252,7 @@
         <v>2.72</v>
       </c>
       <c r="U27" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="V27" t="n">
         <v>1.03</v>
@@ -7267,13 +7267,13 @@
         <v>950</v>
       </c>
       <c r="Z27" t="n">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="AA27" t="n">
         <v>1000</v>
       </c>
       <c r="AB27" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC27" t="n">
         <v>22</v>
@@ -7285,19 +7285,19 @@
         <v>1000</v>
       </c>
       <c r="AF27" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AG27" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH27" t="n">
         <v>950</v>
       </c>
       <c r="AI27" t="n">
-        <v>570</v>
+        <v>550</v>
       </c>
       <c r="AJ27" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AK27" t="n">
         <v>17</v>
@@ -7306,7 +7306,7 @@
         <v>430</v>
       </c>
       <c r="AM27" t="n">
-        <v>510</v>
+        <v>490</v>
       </c>
       <c r="AN27" t="n">
         <v>3.85</v>
@@ -7318,61 +7318,61 @@
         <v>11.5</v>
       </c>
       <c r="AQ27" t="n">
-        <v>6.8</v>
+        <v>20</v>
       </c>
       <c r="AR27" t="n">
-        <v>7.2</v>
+        <v>9.6</v>
       </c>
       <c r="AS27" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AT27" t="n">
         <v>7.4</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>6.8</v>
       </c>
       <c r="AU27" t="n">
         <v>17.5</v>
       </c>
       <c r="AV27" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AW27" t="n">
-        <v>7.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX27" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="AY27" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ27" t="n">
-        <v>6.6</v>
+        <v>28</v>
       </c>
       <c r="BA27" t="n">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="BB27" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BC27" t="n">
         <v>13.5</v>
       </c>
       <c r="BD27" t="n">
-        <v>6.6</v>
+        <v>28</v>
       </c>
       <c r="BE27" t="n">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="BF27" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="BG27" t="n">
-        <v>7.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH27" t="n">
         <v>4.7</v>
       </c>
       <c r="BI27" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="BJ27" t="n">
         <v>18.5</v>
@@ -7390,22 +7390,22 @@
         <v>3.55</v>
       </c>
       <c r="BO27" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="BP27" t="n">
         <v>6.2</v>
       </c>
       <c r="BQ27" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BR27" t="n">
         <v>1000</v>
       </c>
       <c r="BS27" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT27" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BU27" t="n">
         <v>7.4</v>
@@ -7420,7 +7420,7 @@
         <v>1000</v>
       </c>
       <c r="BY27" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ27" t="n">
         <v>9</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -7470,7 +7470,7 @@
         <v>5.3</v>
       </c>
       <c r="I28" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="J28" t="n">
         <v>4</v>
@@ -7485,19 +7485,19 @@
         <v>1.06</v>
       </c>
       <c r="N28" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O28" t="n">
         <v>1.3</v>
       </c>
       <c r="P28" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="Q28" t="n">
         <v>1.89</v>
       </c>
       <c r="R28" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="S28" t="n">
         <v>3.3</v>
@@ -7527,7 +7527,7 @@
         <v>900</v>
       </c>
       <c r="AB28" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC28" t="n">
         <v>10</v>
@@ -7566,7 +7566,7 @@
         <v>11</v>
       </c>
       <c r="AO28" t="n">
-        <v>440</v>
+        <v>700</v>
       </c>
       <c r="AP28" t="n">
         <v>13.5</v>
@@ -7578,7 +7578,7 @@
         <v>34</v>
       </c>
       <c r="AS28" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT28" t="n">
         <v>7</v>
@@ -7590,7 +7590,7 @@
         <v>18.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX28" t="n">
         <v>8.4</v>
@@ -7602,7 +7602,7 @@
         <v>19</v>
       </c>
       <c r="BA28" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB28" t="n">
         <v>14</v>
@@ -7614,13 +7614,13 @@
         <v>26</v>
       </c>
       <c r="BE28" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF28" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BG28" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH28" t="n">
         <v>3.6</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -7733,7 +7733,7 @@
         <v>4.7</v>
       </c>
       <c r="L29" t="n">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="M29" t="n">
         <v>1.02</v>
@@ -7745,7 +7745,7 @@
         <v>1.17</v>
       </c>
       <c r="P29" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="Q29" t="n">
         <v>1.5</v>
@@ -7796,7 +7796,7 @@
         <v>16.5</v>
       </c>
       <c r="AG29" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH29" t="n">
         <v>16.5</v>
@@ -7820,7 +7820,7 @@
         <v>8.6</v>
       </c>
       <c r="AO29" t="n">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="AP29" t="n">
         <v>21</v>
@@ -7832,7 +7832,7 @@
         <v>16</v>
       </c>
       <c r="AS29" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AT29" t="n">
         <v>11</v>
@@ -7868,7 +7868,7 @@
         <v>19</v>
       </c>
       <c r="BE29" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BF29" t="n">
         <v>6.4</v>
@@ -7877,68 +7877,68 @@
         <v>19</v>
       </c>
       <c r="BH29" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BI29" t="n">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="BJ29" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK29" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BL29" t="n">
         <v>1000</v>
       </c>
       <c r="BM29" t="n">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN29" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BO29" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BP29" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BQ29" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BR29" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BS29" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BT29" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BU29" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BV29" t="n">
         <v>1000</v>
       </c>
       <c r="BW29" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BX29" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY29" t="n">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BZ29" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="CA29" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -7969,22 +7969,22 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="G30" t="n">
-        <v>1.7</v>
+        <v>1.42</v>
       </c>
       <c r="H30" t="n">
-        <v>3.25</v>
+        <v>6.4</v>
       </c>
       <c r="I30" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J30" t="n">
-        <v>3.9</v>
+        <v>5.5</v>
       </c>
       <c r="K30" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="L30" t="n">
         <v>1.01</v>
@@ -7993,142 +7993,142 @@
         <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>1.1</v>
+        <v>2.52</v>
       </c>
       <c r="O30" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="P30" t="n">
-        <v>2.24</v>
+        <v>3.55</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.06</v>
+        <v>1.27</v>
       </c>
       <c r="R30" t="n">
         <v>2.24</v>
       </c>
       <c r="S30" t="n">
-        <v>1.06</v>
+        <v>1.62</v>
       </c>
       <c r="T30" t="n">
-        <v>1.11</v>
+        <v>1.47</v>
       </c>
       <c r="U30" t="n">
-        <v>1.11</v>
+        <v>2.54</v>
       </c>
       <c r="V30" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="W30" t="n">
-        <v>2.24</v>
+        <v>3.4</v>
       </c>
       <c r="X30" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y30" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z30" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AA30" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AB30" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AC30" t="n">
-        <v>950</v>
+        <v>18.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AE30" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AF30" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AG30" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH30" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI30" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AJ30" t="n">
-        <v>900</v>
+        <v>16</v>
       </c>
       <c r="AK30" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AL30" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AM30" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN30" t="n">
-        <v>55</v>
+        <v>3.45</v>
       </c>
       <c r="AO30" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.05</v>
+        <v>7</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.05</v>
+        <v>7</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.05</v>
+        <v>7.4</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.05</v>
+        <v>7.8</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.05</v>
+        <v>5.8</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.05</v>
+        <v>6.4</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.05</v>
+        <v>7.4</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.05</v>
+        <v>5.3</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.05</v>
+        <v>4.9</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.05</v>
+        <v>5.9</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.05</v>
+        <v>7.2</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.05</v>
+        <v>5.3</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.05</v>
+        <v>5.3</v>
       </c>
       <c r="BD30" t="n">
-        <v>1.05</v>
+        <v>6.2</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.05</v>
+        <v>7.2</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.03</v>
+        <v>2.76</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.55</v>
+        <v>10.5</v>
       </c>
       <c r="BH30" t="n">
         <v>1000</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -8232,7 +8232,7 @@
         <v>1.66</v>
       </c>
       <c r="I31" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="J31" t="n">
         <v>4.3</v>
@@ -8253,7 +8253,7 @@
         <v>1.06</v>
       </c>
       <c r="P31" t="n">
-        <v>2.38</v>
+        <v>1.25</v>
       </c>
       <c r="Q31" t="n">
         <v>1.2</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -8896,65 +8896,65 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BI33" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="BJ33" t="n">
         <v>11.5</v>
       </c>
       <c r="BK33" t="n">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="BL33" t="n">
         <v>65</v>
       </c>
       <c r="BM33" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BN33" t="n">
         <v>6.4</v>
       </c>
       <c r="BO33" t="n">
-        <v>1.04</v>
+        <v>2.64</v>
       </c>
       <c r="BP33" t="n">
         <v>9.4</v>
       </c>
       <c r="BQ33" t="n">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="BR33" t="n">
         <v>17</v>
       </c>
       <c r="BS33" t="n">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BT33" t="n">
         <v>16</v>
       </c>
       <c r="BU33" t="n">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="BV33" t="n">
         <v>55</v>
       </c>
       <c r="BW33" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BX33" t="n">
         <v>42</v>
       </c>
       <c r="BY33" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BZ33" t="n">
         <v>7</v>
       </c>
       <c r="CA33" t="n">
-        <v>1.04</v>
+        <v>2.74</v>
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -8985,22 +8985,22 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.71</v>
+        <v>2.16</v>
       </c>
       <c r="G34" t="n">
-        <v>990</v>
+        <v>3.2</v>
       </c>
       <c r="H34" t="n">
-        <v>1.51</v>
+        <v>2.22</v>
       </c>
       <c r="I34" t="n">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="J34" t="n">
-        <v>2.06</v>
+        <v>3.3</v>
       </c>
       <c r="K34" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="L34" t="n">
         <v>1.01</v>
@@ -9009,22 +9009,22 @@
         <v>1.01</v>
       </c>
       <c r="N34" t="n">
-        <v>1.1</v>
+        <v>6.2</v>
       </c>
       <c r="O34" t="n">
         <v>1.1</v>
       </c>
       <c r="P34" t="n">
-        <v>1.33</v>
+        <v>2.78</v>
       </c>
       <c r="Q34" t="n">
         <v>1.1</v>
       </c>
       <c r="R34" t="n">
-        <v>1.33</v>
+        <v>1.78</v>
       </c>
       <c r="S34" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="T34" t="n">
         <v>1.11</v>
@@ -9033,10 +9033,10 @@
         <v>1.11</v>
       </c>
       <c r="V34" t="n">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="W34" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="X34" t="n">
         <v>950</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -9239,7 +9239,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="G35" t="n">
         <v>1.46</v>
@@ -9422,7 +9422,7 @@
         <v>3.9</v>
       </c>
       <c r="BO35" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="BP35" t="n">
         <v>8.6</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -9508,10 +9508,10 @@
         <v>3.05</v>
       </c>
       <c r="K36" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L36" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="M36" t="n">
         <v>1.09</v>
@@ -9526,19 +9526,19 @@
         <v>1.68</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="R36" t="n">
         <v>1.25</v>
       </c>
       <c r="S36" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="T36" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="U36" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V36" t="n">
         <v>1.46</v>
@@ -9568,7 +9568,7 @@
         <v>14</v>
       </c>
       <c r="AE36" t="n">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="AF36" t="n">
         <v>19.5</v>
@@ -9583,7 +9583,7 @@
         <v>120</v>
       </c>
       <c r="AJ36" t="n">
-        <v>230</v>
+        <v>120</v>
       </c>
       <c r="AK36" t="n">
         <v>50</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -9753,16 +9753,16 @@
         <v>2.24</v>
       </c>
       <c r="H37" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I37" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="J37" t="n">
         <v>2.9</v>
       </c>
       <c r="K37" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="L37" t="n">
         <v>1.68</v>
@@ -9771,49 +9771,49 @@
         <v>1.16</v>
       </c>
       <c r="N37" t="n">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="O37" t="n">
-        <v>1.69</v>
+        <v>1.78</v>
       </c>
       <c r="P37" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="R37" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="S37" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="T37" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="U37" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="V37" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W37" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="X37" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="Y37" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z37" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AA37" t="n">
         <v>700</v>
       </c>
       <c r="AB37" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="AC37" t="n">
         <v>7.4</v>
@@ -9831,16 +9831,16 @@
         <v>13</v>
       </c>
       <c r="AH37" t="n">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AI37" t="n">
         <v>700</v>
       </c>
       <c r="AJ37" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AK37" t="n">
-        <v>140</v>
+        <v>42</v>
       </c>
       <c r="AL37" t="n">
         <v>540</v>
@@ -9849,16 +9849,16 @@
         <v>500</v>
       </c>
       <c r="AN37" t="n">
-        <v>500</v>
+        <v>46</v>
       </c>
       <c r="AO37" t="n">
         <v>700</v>
       </c>
       <c r="AP37" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="AQ37" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR37" t="n">
         <v>13</v>
@@ -9867,7 +9867,7 @@
         <v>13.5</v>
       </c>
       <c r="AT37" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="AU37" t="n">
         <v>6.6</v>
@@ -9882,19 +9882,19 @@
         <v>10</v>
       </c>
       <c r="AY37" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ37" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BA37" t="n">
         <v>13.5</v>
       </c>
       <c r="BB37" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BC37" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="BD37" t="n">
         <v>12.5</v>
@@ -9903,58 +9903,58 @@
         <v>14</v>
       </c>
       <c r="BF37" t="n">
-        <v>10.5</v>
+        <v>38</v>
       </c>
       <c r="BG37" t="n">
         <v>14</v>
       </c>
       <c r="BH37" t="n">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="BI37" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="BJ37" t="n">
         <v>13</v>
       </c>
       <c r="BK37" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BL37" t="n">
         <v>1000</v>
       </c>
       <c r="BM37" t="n">
-        <v>1.47</v>
+        <v>2.14</v>
       </c>
       <c r="BN37" t="n">
         <v>4.6</v>
       </c>
       <c r="BO37" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="BP37" t="n">
         <v>1000</v>
       </c>
       <c r="BQ37" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BR37" t="n">
         <v>1000</v>
       </c>
       <c r="BS37" t="n">
-        <v>13.5</v>
+        <v>2.08</v>
       </c>
       <c r="BT37" t="n">
         <v>7.8</v>
       </c>
       <c r="BU37" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BV37" t="n">
         <v>1000</v>
       </c>
       <c r="BW37" t="n">
-        <v>13.5</v>
+        <v>2.08</v>
       </c>
       <c r="BX37" t="n">
         <v>1000</v>
@@ -9966,11 +9966,11 @@
         <v>1000</v>
       </c>
       <c r="CA37" t="n">
-        <v>13.5</v>
+        <v>2.08</v>
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -10019,7 +10019,7 @@
         <v>3.45</v>
       </c>
       <c r="L38" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="M38" t="n">
         <v>1.1</v>
@@ -10034,13 +10034,13 @@
         <v>1.7</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="R38" t="n">
         <v>1.26</v>
       </c>
       <c r="S38" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T38" t="n">
         <v>1.98</v>
@@ -10115,7 +10115,7 @@
         <v>11.5</v>
       </c>
       <c r="AR38" t="n">
-        <v>14.5</v>
+        <v>24</v>
       </c>
       <c r="AS38" t="n">
         <v>10.5</v>
@@ -10166,65 +10166,65 @@
         <v>3.05</v>
       </c>
       <c r="BI38" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="BJ38" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK38" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL38" t="n">
         <v>1000</v>
       </c>
       <c r="BM38" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BN38" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BO38" t="n">
         <v>3.7</v>
       </c>
       <c r="BP38" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BQ38" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR38" t="n">
         <v>34</v>
       </c>
       <c r="BS38" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BT38" t="n">
         <v>7.6</v>
       </c>
       <c r="BU38" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BV38" t="n">
         <v>42</v>
       </c>
       <c r="BW38" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BX38" t="n">
         <v>1000</v>
       </c>
       <c r="BY38" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BZ38" t="n">
         <v>34</v>
       </c>
       <c r="CA38" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -10255,7 +10255,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="G39" t="n">
         <v>2.7</v>
@@ -10273,34 +10273,34 @@
         <v>3.3</v>
       </c>
       <c r="L39" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="M39" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N39" t="n">
-        <v>2.92</v>
+        <v>2.76</v>
       </c>
       <c r="O39" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="P39" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.32</v>
+        <v>2.52</v>
       </c>
       <c r="R39" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="S39" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="T39" t="n">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="U39" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="V39" t="n">
         <v>1.43</v>
@@ -10309,10 +10309,10 @@
         <v>1.58</v>
       </c>
       <c r="X39" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="Y39" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="Z39" t="n">
         <v>22</v>
@@ -10321,25 +10321,25 @@
         <v>65</v>
       </c>
       <c r="AB39" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC39" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD39" t="n">
         <v>15</v>
       </c>
       <c r="AE39" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AF39" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG39" t="n">
         <v>13</v>
       </c>
       <c r="AH39" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AI39" t="n">
         <v>160</v>
@@ -10348,43 +10348,43 @@
         <v>44</v>
       </c>
       <c r="AK39" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AL39" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="AM39" t="n">
         <v>580</v>
       </c>
       <c r="AN39" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AO39" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AP39" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ39" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR39" t="n">
         <v>17.5</v>
       </c>
       <c r="AS39" t="n">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="AT39" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AU39" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV39" t="n">
         <v>12</v>
       </c>
       <c r="AW39" t="n">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX39" t="n">
         <v>13.5</v>
@@ -10396,61 +10396,61 @@
         <v>17.5</v>
       </c>
       <c r="BA39" t="n">
-        <v>7.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB39" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BC39" t="n">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD39" t="n">
-        <v>7.2</v>
+        <v>9.4</v>
       </c>
       <c r="BE39" t="n">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="BF39" t="n">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG39" t="n">
-        <v>7.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH39" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="BI39" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="BJ39" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK39" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BL39" t="n">
         <v>1000</v>
       </c>
       <c r="BM39" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN39" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BO39" t="n">
         <v>4.1</v>
       </c>
       <c r="BP39" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BQ39" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BR39" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BS39" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BT39" t="n">
         <v>6.4</v>
@@ -10459,26 +10459,26 @@
         <v>4.6</v>
       </c>
       <c r="BV39" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BW39" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BX39" t="n">
+        <v>50</v>
+      </c>
+      <c r="BY39" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BZ39" t="n">
         <v>48</v>
       </c>
-      <c r="BY39" t="n">
-        <v>9</v>
-      </c>
-      <c r="BZ39" t="n">
-        <v>42</v>
-      </c>
       <c r="CA39" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-07-16 21:09:14</t>
+          <t>2026-07-16 23:28:44</t>
         </is>
       </c>
     </row>
@@ -10527,7 +10527,7 @@
         <v>4.3</v>
       </c>
       <c r="L40" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="M40" t="n">
         <v>1.07</v>
@@ -10554,7 +10554,7 @@
         <v>1.97</v>
       </c>
       <c r="U40" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="V40" t="n">
         <v>1.17</v>
@@ -10575,7 +10575,7 @@
         <v>900</v>
       </c>
       <c r="AB40" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC40" t="n">
         <v>9.199999999999999</v>
@@ -10626,7 +10626,7 @@
         <v>6.2</v>
       </c>
       <c r="AS40" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c